--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -354,7 +354,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -376,6 +376,19 @@
         <color rgb="00C8102E"/>
         <sz val="10"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <i val="1"/>
+        <color rgb="007A7A7A"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00C9C9C9"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4881,7 +4894,7 @@
       </c>
       <c r="T36" s="15" t="inlineStr">
         <is>
-          <t>F-110</t>
+          <t>F-109</t>
         </is>
       </c>
       <c r="U36" s="19" t="inlineStr">
@@ -4989,7 +5002,7 @@
       </c>
       <c r="T37" s="15" t="inlineStr">
         <is>
-          <t>F-111</t>
+          <t>F-110</t>
         </is>
       </c>
       <c r="U37" s="19" t="inlineStr">
@@ -16545,7 +16558,7 @@
       </c>
       <c r="T144" s="15" t="inlineStr">
         <is>
-          <t>F-112</t>
+          <t>F-111</t>
         </is>
       </c>
       <c r="U144" s="19" t="inlineStr">
@@ -16599,6 +16612,11 @@
   <conditionalFormatting sqref="F3:F144">
     <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M3:M144">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"entfällt"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -354,11 +354,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <bgColor rgb="00E4E4E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00DCDCDC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -16606,16 +16613,19 @@
       <formula>"reserviert"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"teilverkauft"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F144">
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M3:M144">
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16639,7 +16649,7 @@
       <formula1>"nur Abholung,Versand möglich,Spedition"</formula1>
     </dataValidation>
     <dataValidation sqref="U3:U803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"verfügbar,reserviert,verkauft,gespendet,entsorgt"</formula1>
+      <formula1>"verfügbar,reserviert,teilverkauft,verkauft,gespendet,entsorgt"</formula1>
     </dataValidation>
     <dataValidation sqref="V3:V803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Klinik,Kleinanzeigen,eBay,Direkt,Händler,Verkaufstag"</formula1>
@@ -16728,32 +16738,43 @@
     <row r="8">
       <c r="A8" s="26" t="inlineStr">
         <is>
-          <t>davon verkauft</t>
+          <t>davon teilverkauft</t>
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$U$3:$U$144,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$U$3:$U$144,"teilverkauft")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="26" t="inlineStr">
         <is>
+          <t>davon verkauft</t>
+        </is>
+      </c>
+      <c r="B9" s="27">
+        <f>COUNTIF(Artikelstamm!$U$3:$U$144,"verkauft")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
           <t>Einheiten noch im Bestand</t>
         </is>
       </c>
-      <c r="B9" s="27">
+      <c r="B10" s="27">
         <f>SUM(Artikelstamm!$I$3:$I$144)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="28" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Restbestand zu Wunschpreisen (netto)</t>
         </is>
       </c>
-      <c r="B10" s="29">
+      <c r="B11" s="29">
         <f>SUM(Artikelstamm!$R$3:$R$144)</f>
         <v/>
       </c>
@@ -16845,7 +16866,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$U$3:$U$144,"verkauft",Artikelstamm!$AB$3:$AB$144,"")</f>
+        <f>COUNTIFS(Artikelstamm!$U$3:$U$144,"*verkauft",Artikelstamm!$AB$3:$AB$144,"")</f>
         <v/>
       </c>
     </row>
@@ -16856,7 +16877,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$U$3:$U$144,"verkauft",Artikelstamm!$AC$3:$AC$144,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$U$3:$U$144,"*verkauft",Artikelstamm!$AC$3:$AC$144,"offen")</f>
         <v/>
       </c>
     </row>
@@ -20006,7 +20027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -20128,7 +20149,7 @@
       </c>
       <c r="B10" s="41" t="inlineStr">
         <is>
-          <t>jenny@kikripp.de</t>
+          <t>jennyp@kikripp.de</t>
         </is>
       </c>
       <c r="C10" s="51" t="inlineStr"/>
@@ -20235,164 +20256,194 @@
     <row r="18">
       <c r="A18" s="50" t="inlineStr">
         <is>
-          <t>Farbe_Rot</t>
+          <t>Katalog_URL</t>
         </is>
       </c>
       <c r="B18" s="41" t="inlineStr">
         <is>
-          <t>C8102E</t>
-        </is>
-      </c>
-      <c r="C18" s="52" t="inlineStr">
-        <is>
-          <t>Bollenhut-Rot - nur als Akzent verwenden</t>
+          <t>https://www.kikripp.de/katalog</t>
+        </is>
+      </c>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>Adresse des Webkatalogs, erscheint im Klinik-Angebot</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="50" t="inlineStr">
         <is>
-          <t>Farbe_Schwarz</t>
-        </is>
-      </c>
-      <c r="B19" s="41" t="inlineStr">
-        <is>
-          <t>1A1A1A</t>
-        </is>
-      </c>
-      <c r="C19" s="53" t="inlineStr">
-        <is>
-          <t>Kopfzeilen und Struktur</t>
+          <t>Katalog_Passwort</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr"/>
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>Bewusst leer - Passwort gehoert nicht ins Projekt. Vor dem Erzeugen setzen: export KIKRIPP_KATALOG_PW=...</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="50" t="inlineStr">
         <is>
-          <t>Farbe_Papier</t>
+          <t>Farbe_Rot</t>
         </is>
       </c>
       <c r="B20" s="41" t="inlineStr">
         <is>
-          <t>F7F5F2</t>
-        </is>
-      </c>
-      <c r="C20" s="54" t="inlineStr">
-        <is>
-          <t>warme Fläche</t>
+          <t>C8102E</t>
+        </is>
+      </c>
+      <c r="C20" s="52" t="inlineStr">
+        <is>
+          <t>Bollenhut-Rot - nur als Akzent verwenden</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="50" t="inlineStr">
         <is>
-          <t>Farbe_Grau</t>
+          <t>Farbe_Schwarz</t>
         </is>
       </c>
       <c r="B21" s="41" t="inlineStr">
         <is>
-          <t>6B7280</t>
-        </is>
-      </c>
-      <c r="C21" s="55" t="inlineStr">
-        <is>
-          <t>Sekundärtext</t>
+          <t>1A1A1A</t>
+        </is>
+      </c>
+      <c r="C21" s="53" t="inlineStr">
+        <is>
+          <t>Kopfzeilen und Struktur</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="50" t="inlineStr">
         <is>
-          <t>Farbe_Linie</t>
+          <t>Farbe_Papier</t>
         </is>
       </c>
       <c r="B22" s="41" t="inlineStr">
         <is>
-          <t>DCDCDC</t>
-        </is>
-      </c>
-      <c r="C22" s="56" t="inlineStr">
-        <is>
-          <t>feine Linien und Rahmen</t>
+          <t>F7F5F2</t>
+        </is>
+      </c>
+      <c r="C22" s="54" t="inlineStr">
+        <is>
+          <t>warme Fläche</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="50" t="inlineStr">
         <is>
-          <t>Feld_Klinik</t>
+          <t>Farbe_Grau</t>
         </is>
       </c>
       <c r="B23" s="41" t="inlineStr">
         <is>
-          <t>E4E4E4</t>
-        </is>
-      </c>
-      <c r="C23" s="57" t="inlineStr">
-        <is>
-          <t>Ausfüllfelder für die Klinik (mittleres Grau)</t>
+          <t>6B7280</t>
+        </is>
+      </c>
+      <c r="C23" s="55" t="inlineStr">
+        <is>
+          <t>Sekundärtext</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="50" t="inlineStr">
         <is>
-          <t>Feld_Intern</t>
+          <t>Farbe_Linie</t>
         </is>
       </c>
       <c r="B24" s="41" t="inlineStr">
         <is>
-          <t>F2F2F2</t>
-        </is>
-      </c>
-      <c r="C24" s="58" t="inlineStr">
-        <is>
-          <t>interne Ausfüllfelder (helles Grau)</t>
+          <t>DCDCDC</t>
+        </is>
+      </c>
+      <c r="C24" s="56" t="inlineStr">
+        <is>
+          <t>feine Linien und Rahmen</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="50" t="inlineStr">
         <is>
-          <t>Zeile_Wechsel</t>
+          <t>Feld_Klinik</t>
         </is>
       </c>
       <c r="B25" s="41" t="inlineStr">
         <is>
-          <t>FAFAFA</t>
-        </is>
-      </c>
-      <c r="C25" s="59" t="inlineStr">
-        <is>
-          <t>Zeilenwechsel in Tabellen</t>
+          <t>E4E4E4</t>
+        </is>
+      </c>
+      <c r="C25" s="57" t="inlineStr">
+        <is>
+          <t>Ausfüllfelder für die Klinik (mittleres Grau)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="50" t="inlineStr">
         <is>
-          <t>Schrift_Excel</t>
+          <t>Feld_Intern</t>
         </is>
       </c>
       <c r="B26" s="41" t="inlineStr">
         <is>
-          <t>Arial</t>
-        </is>
-      </c>
-      <c r="C26" s="51" t="inlineStr"/>
+          <t>F2F2F2</t>
+        </is>
+      </c>
+      <c r="C26" s="58" t="inlineStr">
+        <is>
+          <t>interne Ausfüllfelder (helles Grau)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="50" t="inlineStr">
         <is>
+          <t>Zeile_Wechsel</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>FAFAFA</t>
+        </is>
+      </c>
+      <c r="C27" s="59" t="inlineStr">
+        <is>
+          <t>Zeilenwechsel in Tabellen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="inlineStr">
+        <is>
+          <t>Schrift_Excel</t>
+        </is>
+      </c>
+      <c r="B28" s="41" t="inlineStr">
+        <is>
+          <t>Arial</t>
+        </is>
+      </c>
+      <c r="C28" s="51" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="50" t="inlineStr">
+        <is>
           <t>Schrift_Web</t>
         </is>
       </c>
-      <c r="B27" s="41" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>Poppins</t>
         </is>
       </c>
-      <c r="C27" s="51" t="inlineStr">
+      <c r="C29" s="51" t="inlineStr">
         <is>
           <t>Google-Font für den Webkatalog, mit Systemschrift als Rückfall</t>
         </is>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -1385,11 +1385,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z3" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z3" s="19" t="n"/>
       <c r="AA3" s="19" t="n"/>
       <c r="AB3" s="20" t="n"/>
       <c r="AC3" s="21">
@@ -1509,11 +1505,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z4" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z4" s="19" t="n"/>
       <c r="AA4" s="19" t="n"/>
       <c r="AB4" s="20" t="n"/>
       <c r="AC4" s="21">
@@ -1637,11 +1629,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z5" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z5" s="19" t="n"/>
       <c r="AA5" s="19" t="n"/>
       <c r="AB5" s="20" t="n"/>
       <c r="AC5" s="21">
@@ -1761,11 +1749,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z6" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z6" s="19" t="n"/>
       <c r="AA6" s="19" t="n"/>
       <c r="AB6" s="20" t="n"/>
       <c r="AC6" s="21">
@@ -1885,11 +1869,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z7" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z7" s="19" t="n"/>
       <c r="AA7" s="19" t="n"/>
       <c r="AB7" s="20" t="n"/>
       <c r="AC7" s="21">
@@ -2009,11 +1989,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z8" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z8" s="19" t="n"/>
       <c r="AA8" s="19" t="n"/>
       <c r="AB8" s="20" t="n"/>
       <c r="AC8" s="21">
@@ -2133,11 +2109,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z9" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z9" s="19" t="n"/>
       <c r="AA9" s="19" t="n"/>
       <c r="AB9" s="20" t="n"/>
       <c r="AC9" s="21">
@@ -2257,11 +2229,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z10" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z10" s="19" t="n"/>
       <c r="AA10" s="19" t="n"/>
       <c r="AB10" s="20" t="n"/>
       <c r="AC10" s="21">
@@ -2381,11 +2349,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z11" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z11" s="19" t="n"/>
       <c r="AA11" s="19" t="n"/>
       <c r="AB11" s="20" t="n"/>
       <c r="AC11" s="21">
@@ -2509,11 +2473,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z12" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z12" s="19" t="n"/>
       <c r="AA12" s="19" t="n"/>
       <c r="AB12" s="20" t="n"/>
       <c r="AC12" s="21">
@@ -2633,11 +2593,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z13" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z13" s="19" t="n"/>
       <c r="AA13" s="19" t="n"/>
       <c r="AB13" s="20" t="n"/>
       <c r="AC13" s="21">
@@ -2757,11 +2713,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z14" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z14" s="19" t="n"/>
       <c r="AA14" s="19" t="n"/>
       <c r="AB14" s="20" t="n"/>
       <c r="AC14" s="21">
@@ -2881,11 +2833,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z15" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z15" s="19" t="n"/>
       <c r="AA15" s="19" t="n"/>
       <c r="AB15" s="20" t="n"/>
       <c r="AC15" s="21">
@@ -3006,11 +2954,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z16" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z16" s="19" t="n"/>
       <c r="AA16" s="19" t="n"/>
       <c r="AB16" s="20" t="n"/>
       <c r="AC16" s="21">
@@ -3131,11 +3075,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z17" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z17" s="19" t="n"/>
       <c r="AA17" s="19" t="n"/>
       <c r="AB17" s="20" t="n"/>
       <c r="AC17" s="21">
@@ -3255,11 +3195,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z18" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z18" s="19" t="n"/>
       <c r="AA18" s="19" t="n"/>
       <c r="AB18" s="20" t="n"/>
       <c r="AC18" s="21">
@@ -3379,11 +3315,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z19" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z19" s="19" t="n"/>
       <c r="AA19" s="19" t="n"/>
       <c r="AB19" s="20" t="n"/>
       <c r="AC19" s="21">
@@ -3503,11 +3435,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z20" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z20" s="19" t="n"/>
       <c r="AA20" s="19" t="n"/>
       <c r="AB20" s="20" t="n"/>
       <c r="AC20" s="21">
@@ -3627,11 +3555,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z21" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z21" s="19" t="n"/>
       <c r="AA21" s="19" t="n"/>
       <c r="AB21" s="20" t="n"/>
       <c r="AC21" s="21">
@@ -3751,11 +3675,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z22" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z22" s="19" t="n"/>
       <c r="AA22" s="19" t="n"/>
       <c r="AB22" s="20" t="n"/>
       <c r="AC22" s="21">
@@ -3875,11 +3795,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z23" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z23" s="19" t="n"/>
       <c r="AA23" s="19" t="n"/>
       <c r="AB23" s="20" t="n"/>
       <c r="AC23" s="21">
@@ -3999,11 +3915,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z24" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z24" s="19" t="n"/>
       <c r="AA24" s="19" t="n"/>
       <c r="AB24" s="20" t="n"/>
       <c r="AC24" s="21">
@@ -4123,11 +4035,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z25" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z25" s="19" t="n"/>
       <c r="AA25" s="19" t="n"/>
       <c r="AB25" s="20" t="n"/>
       <c r="AC25" s="21">
@@ -4247,11 +4155,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z26" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z26" s="19" t="n"/>
       <c r="AA26" s="19" t="n"/>
       <c r="AB26" s="20" t="n"/>
       <c r="AC26" s="21">
@@ -4371,11 +4275,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z27" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z27" s="19" t="n"/>
       <c r="AA27" s="19" t="n"/>
       <c r="AB27" s="20" t="n"/>
       <c r="AC27" s="21">
@@ -4495,11 +4395,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z28" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z28" s="19" t="n"/>
       <c r="AA28" s="19" t="n"/>
       <c r="AB28" s="20" t="n"/>
       <c r="AC28" s="21">
@@ -4619,11 +4515,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z29" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z29" s="19" t="n"/>
       <c r="AA29" s="19" t="n"/>
       <c r="AB29" s="20" t="n"/>
       <c r="AC29" s="21">
@@ -4743,11 +4635,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z30" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z30" s="19" t="n"/>
       <c r="AA30" s="19" t="n"/>
       <c r="AB30" s="20" t="n"/>
       <c r="AC30" s="21">
@@ -4867,11 +4755,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z31" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z31" s="19" t="n"/>
       <c r="AA31" s="19" t="n"/>
       <c r="AB31" s="20" t="n"/>
       <c r="AC31" s="21">
@@ -4991,11 +4875,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z32" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z32" s="19" t="n"/>
       <c r="AA32" s="19" t="n"/>
       <c r="AB32" s="20" t="n"/>
       <c r="AC32" s="21">
@@ -5115,11 +4995,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z33" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z33" s="19" t="n"/>
       <c r="AA33" s="19" t="n"/>
       <c r="AB33" s="20" t="n"/>
       <c r="AC33" s="21">
@@ -5239,11 +5115,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z34" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z34" s="19" t="n"/>
       <c r="AA34" s="19" t="n"/>
       <c r="AB34" s="20" t="n"/>
       <c r="AC34" s="21">
@@ -5363,11 +5235,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z35" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z35" s="19" t="n"/>
       <c r="AA35" s="19" t="n"/>
       <c r="AB35" s="20" t="n"/>
       <c r="AC35" s="21">
@@ -5487,11 +5355,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z36" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z36" s="19" t="n"/>
       <c r="AA36" s="19" t="n"/>
       <c r="AB36" s="20" t="n"/>
       <c r="AC36" s="21">
@@ -5611,11 +5475,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z37" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z37" s="19" t="n"/>
       <c r="AA37" s="19" t="n"/>
       <c r="AB37" s="20" t="n"/>
       <c r="AC37" s="21">
@@ -5735,11 +5595,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z38" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z38" s="19" t="n"/>
       <c r="AA38" s="19" t="n"/>
       <c r="AB38" s="20" t="n"/>
       <c r="AC38" s="21">
@@ -5859,11 +5715,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z39" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z39" s="19" t="n"/>
       <c r="AA39" s="19" t="n"/>
       <c r="AB39" s="20" t="n"/>
       <c r="AC39" s="21">
@@ -5983,11 +5835,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z40" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z40" s="19" t="n"/>
       <c r="AA40" s="19" t="n"/>
       <c r="AB40" s="20" t="n"/>
       <c r="AC40" s="21">
@@ -6103,11 +5951,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z41" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z41" s="19" t="n"/>
       <c r="AA41" s="19" t="n"/>
       <c r="AB41" s="20" t="n"/>
       <c r="AC41" s="21">
@@ -6223,11 +6067,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z42" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z42" s="19" t="n"/>
       <c r="AA42" s="19" t="n"/>
       <c r="AB42" s="20" t="n"/>
       <c r="AC42" s="21">
@@ -6343,11 +6183,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z43" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z43" s="19" t="n"/>
       <c r="AA43" s="19" t="n"/>
       <c r="AB43" s="20" t="n"/>
       <c r="AC43" s="21">
@@ -6463,11 +6299,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z44" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z44" s="19" t="n"/>
       <c r="AA44" s="19" t="n"/>
       <c r="AB44" s="20" t="n"/>
       <c r="AC44" s="21">
@@ -6583,11 +6415,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z45" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z45" s="19" t="n"/>
       <c r="AA45" s="19" t="n"/>
       <c r="AB45" s="20" t="n"/>
       <c r="AC45" s="21">
@@ -6703,11 +6531,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z46" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z46" s="19" t="n"/>
       <c r="AA46" s="19" t="n"/>
       <c r="AB46" s="20" t="n"/>
       <c r="AC46" s="21">
@@ -6823,11 +6647,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z47" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z47" s="19" t="n"/>
       <c r="AA47" s="19" t="n"/>
       <c r="AB47" s="20" t="n"/>
       <c r="AC47" s="21">
@@ -6943,11 +6763,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z48" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z48" s="19" t="n"/>
       <c r="AA48" s="19" t="n"/>
       <c r="AB48" s="20" t="n"/>
       <c r="AC48" s="21">
@@ -7063,11 +6879,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z49" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z49" s="19" t="n"/>
       <c r="AA49" s="19" t="n"/>
       <c r="AB49" s="20" t="n"/>
       <c r="AC49" s="21">
@@ -7183,11 +6995,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z50" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z50" s="19" t="n"/>
       <c r="AA50" s="19" t="n"/>
       <c r="AB50" s="20" t="n"/>
       <c r="AC50" s="21">
@@ -7303,11 +7111,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z51" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z51" s="19" t="n"/>
       <c r="AA51" s="19" t="n"/>
       <c r="AB51" s="20" t="n"/>
       <c r="AC51" s="21">
@@ -7423,11 +7227,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z52" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z52" s="19" t="n"/>
       <c r="AA52" s="19" t="n"/>
       <c r="AB52" s="20" t="n"/>
       <c r="AC52" s="21">
@@ -7543,11 +7343,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z53" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z53" s="19" t="n"/>
       <c r="AA53" s="19" t="n"/>
       <c r="AB53" s="20" t="n"/>
       <c r="AC53" s="21">
@@ -7663,11 +7459,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z54" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z54" s="19" t="n"/>
       <c r="AA54" s="19" t="n"/>
       <c r="AB54" s="20" t="n"/>
       <c r="AC54" s="21">
@@ -7783,11 +7575,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z55" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z55" s="19" t="n"/>
       <c r="AA55" s="19" t="n"/>
       <c r="AB55" s="20" t="n"/>
       <c r="AC55" s="21">
@@ -7903,11 +7691,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z56" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z56" s="19" t="n"/>
       <c r="AA56" s="19" t="n"/>
       <c r="AB56" s="20" t="n"/>
       <c r="AC56" s="21">
@@ -8023,11 +7807,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z57" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z57" s="19" t="n"/>
       <c r="AA57" s="19" t="n"/>
       <c r="AB57" s="20" t="n"/>
       <c r="AC57" s="21">
@@ -8143,11 +7923,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z58" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z58" s="19" t="n"/>
       <c r="AA58" s="19" t="n"/>
       <c r="AB58" s="20" t="n"/>
       <c r="AC58" s="21">
@@ -8263,11 +8039,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z59" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z59" s="19" t="n"/>
       <c r="AA59" s="19" t="n"/>
       <c r="AB59" s="20" t="n"/>
       <c r="AC59" s="21">
@@ -8383,11 +8155,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z60" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z60" s="19" t="n"/>
       <c r="AA60" s="19" t="n"/>
       <c r="AB60" s="20" t="n"/>
       <c r="AC60" s="21">
@@ -8503,11 +8271,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z61" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z61" s="19" t="n"/>
       <c r="AA61" s="19" t="n"/>
       <c r="AB61" s="20" t="n"/>
       <c r="AC61" s="21">
@@ -8623,11 +8387,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z62" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z62" s="19" t="n"/>
       <c r="AA62" s="19" t="n"/>
       <c r="AB62" s="20" t="n"/>
       <c r="AC62" s="21">
@@ -8743,11 +8503,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z63" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z63" s="19" t="n"/>
       <c r="AA63" s="19" t="n"/>
       <c r="AB63" s="20" t="n"/>
       <c r="AC63" s="21">
@@ -8863,11 +8619,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z64" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z64" s="19" t="n"/>
       <c r="AA64" s="19" t="n"/>
       <c r="AB64" s="20" t="n"/>
       <c r="AC64" s="21">
@@ -8983,11 +8735,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z65" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z65" s="19" t="n"/>
       <c r="AA65" s="19" t="n"/>
       <c r="AB65" s="20" t="n"/>
       <c r="AC65" s="21">
@@ -9103,11 +8851,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z66" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z66" s="19" t="n"/>
       <c r="AA66" s="19" t="n"/>
       <c r="AB66" s="20" t="n"/>
       <c r="AC66" s="21">
@@ -9223,11 +8967,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z67" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z67" s="19" t="n"/>
       <c r="AA67" s="19" t="n"/>
       <c r="AB67" s="20" t="n"/>
       <c r="AC67" s="21">
@@ -9343,11 +9083,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z68" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z68" s="19" t="n"/>
       <c r="AA68" s="19" t="n"/>
       <c r="AB68" s="20" t="n"/>
       <c r="AC68" s="21">
@@ -9463,11 +9199,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z69" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z69" s="19" t="n"/>
       <c r="AA69" s="19" t="n"/>
       <c r="AB69" s="20" t="n"/>
       <c r="AC69" s="21">
@@ -9583,11 +9315,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z70" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z70" s="19" t="n"/>
       <c r="AA70" s="19" t="n"/>
       <c r="AB70" s="20" t="n"/>
       <c r="AC70" s="21">
@@ -9703,11 +9431,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z71" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z71" s="19" t="n"/>
       <c r="AA71" s="19" t="n"/>
       <c r="AB71" s="20" t="n"/>
       <c r="AC71" s="21">
@@ -9823,11 +9547,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z72" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z72" s="19" t="n"/>
       <c r="AA72" s="19" t="n"/>
       <c r="AB72" s="20" t="n"/>
       <c r="AC72" s="21">
@@ -9943,11 +9663,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z73" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z73" s="19" t="n"/>
       <c r="AA73" s="19" t="n"/>
       <c r="AB73" s="20" t="n"/>
       <c r="AC73" s="21">
@@ -10063,11 +9779,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z74" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z74" s="19" t="n"/>
       <c r="AA74" s="19" t="n"/>
       <c r="AB74" s="20" t="n"/>
       <c r="AC74" s="21">
@@ -10183,11 +9895,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z75" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z75" s="19" t="n"/>
       <c r="AA75" s="19" t="n"/>
       <c r="AB75" s="20" t="n"/>
       <c r="AC75" s="21">
@@ -10303,11 +10011,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z76" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z76" s="19" t="n"/>
       <c r="AA76" s="19" t="n"/>
       <c r="AB76" s="20" t="n"/>
       <c r="AC76" s="21">
@@ -10423,11 +10127,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z77" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z77" s="19" t="n"/>
       <c r="AA77" s="19" t="n"/>
       <c r="AB77" s="20" t="n"/>
       <c r="AC77" s="21">
@@ -10543,11 +10243,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z78" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z78" s="19" t="n"/>
       <c r="AA78" s="19" t="n"/>
       <c r="AB78" s="20" t="n"/>
       <c r="AC78" s="21">
@@ -10663,11 +10359,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z79" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z79" s="19" t="n"/>
       <c r="AA79" s="19" t="n"/>
       <c r="AB79" s="20" t="n"/>
       <c r="AC79" s="21">
@@ -10783,11 +10475,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z80" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z80" s="19" t="n"/>
       <c r="AA80" s="19" t="n"/>
       <c r="AB80" s="20" t="n"/>
       <c r="AC80" s="21">
@@ -10903,11 +10591,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z81" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z81" s="19" t="n"/>
       <c r="AA81" s="19" t="n"/>
       <c r="AB81" s="20" t="n"/>
       <c r="AC81" s="21">
@@ -11023,11 +10707,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z82" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z82" s="19" t="n"/>
       <c r="AA82" s="19" t="n"/>
       <c r="AB82" s="20" t="n"/>
       <c r="AC82" s="21">
@@ -11143,11 +10823,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z83" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z83" s="19" t="n"/>
       <c r="AA83" s="19" t="n"/>
       <c r="AB83" s="20" t="n"/>
       <c r="AC83" s="21">
@@ -11263,11 +10939,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z84" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z84" s="19" t="n"/>
       <c r="AA84" s="19" t="n"/>
       <c r="AB84" s="20" t="n"/>
       <c r="AC84" s="21">
@@ -11383,11 +11055,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z85" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z85" s="19" t="n"/>
       <c r="AA85" s="19" t="n"/>
       <c r="AB85" s="20" t="n"/>
       <c r="AC85" s="21">
@@ -11503,11 +11171,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z86" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z86" s="19" t="n"/>
       <c r="AA86" s="19" t="n"/>
       <c r="AB86" s="20" t="n"/>
       <c r="AC86" s="21">
@@ -11623,11 +11287,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z87" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z87" s="19" t="n"/>
       <c r="AA87" s="19" t="n"/>
       <c r="AB87" s="20" t="n"/>
       <c r="AC87" s="21">
@@ -11743,11 +11403,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z88" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z88" s="19" t="n"/>
       <c r="AA88" s="19" t="n"/>
       <c r="AB88" s="20" t="n"/>
       <c r="AC88" s="21">
@@ -11863,11 +11519,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z89" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z89" s="19" t="n"/>
       <c r="AA89" s="19" t="n"/>
       <c r="AB89" s="20" t="n"/>
       <c r="AC89" s="21">
@@ -11983,11 +11635,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z90" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z90" s="19" t="n"/>
       <c r="AA90" s="19" t="n"/>
       <c r="AB90" s="20" t="n"/>
       <c r="AC90" s="21">
@@ -12103,11 +11751,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z91" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z91" s="19" t="n"/>
       <c r="AA91" s="19" t="n"/>
       <c r="AB91" s="20" t="n"/>
       <c r="AC91" s="21">
@@ -12223,11 +11867,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z92" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z92" s="19" t="n"/>
       <c r="AA92" s="19" t="n"/>
       <c r="AB92" s="20" t="n"/>
       <c r="AC92" s="21">
@@ -12343,11 +11983,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z93" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z93" s="19" t="n"/>
       <c r="AA93" s="19" t="n"/>
       <c r="AB93" s="20" t="n"/>
       <c r="AC93" s="21">
@@ -12463,11 +12099,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z94" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z94" s="19" t="n"/>
       <c r="AA94" s="19" t="n"/>
       <c r="AB94" s="20" t="n"/>
       <c r="AC94" s="21">
@@ -12583,11 +12215,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z95" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z95" s="19" t="n"/>
       <c r="AA95" s="19" t="n"/>
       <c r="AB95" s="20" t="n"/>
       <c r="AC95" s="21">
@@ -12707,11 +12335,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z96" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z96" s="19" t="n"/>
       <c r="AA96" s="19" t="n"/>
       <c r="AB96" s="20" t="n"/>
       <c r="AC96" s="21">
@@ -12835,11 +12459,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z97" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z97" s="19" t="n"/>
       <c r="AA97" s="19" t="n"/>
       <c r="AB97" s="20" t="n"/>
       <c r="AC97" s="21">
@@ -12963,11 +12583,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z98" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z98" s="19" t="n"/>
       <c r="AA98" s="19" t="n"/>
       <c r="AB98" s="20" t="n"/>
       <c r="AC98" s="21">
@@ -13087,11 +12703,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z99" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z99" s="19" t="n"/>
       <c r="AA99" s="19" t="n"/>
       <c r="AB99" s="20" t="n"/>
       <c r="AC99" s="21">
@@ -13211,11 +12823,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z100" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z100" s="19" t="n"/>
       <c r="AA100" s="19" t="n"/>
       <c r="AB100" s="20" t="n"/>
       <c r="AC100" s="21">
@@ -13335,11 +12943,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z101" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z101" s="19" t="n"/>
       <c r="AA101" s="19" t="n"/>
       <c r="AB101" s="20" t="n"/>
       <c r="AC101" s="21">
@@ -13459,11 +13063,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z102" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z102" s="19" t="n"/>
       <c r="AA102" s="19" t="n"/>
       <c r="AB102" s="20" t="n"/>
       <c r="AC102" s="21">
@@ -13583,11 +13183,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z103" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z103" s="19" t="n"/>
       <c r="AA103" s="19" t="n"/>
       <c r="AB103" s="20" t="n"/>
       <c r="AC103" s="21">
@@ -13707,11 +13303,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z104" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z104" s="19" t="n"/>
       <c r="AA104" s="19" t="n"/>
       <c r="AB104" s="20" t="n"/>
       <c r="AC104" s="21">
@@ -13831,11 +13423,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z105" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z105" s="19" t="n"/>
       <c r="AA105" s="19" t="n"/>
       <c r="AB105" s="20" t="n"/>
       <c r="AC105" s="21">
@@ -13955,11 +13543,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z106" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z106" s="19" t="n"/>
       <c r="AA106" s="19" t="n"/>
       <c r="AB106" s="20" t="n"/>
       <c r="AC106" s="21">
@@ -14079,11 +13663,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z107" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z107" s="19" t="n"/>
       <c r="AA107" s="19" t="n"/>
       <c r="AB107" s="20" t="n"/>
       <c r="AC107" s="21">
@@ -14203,11 +13783,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z108" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z108" s="19" t="n"/>
       <c r="AA108" s="19" t="n"/>
       <c r="AB108" s="20" t="n"/>
       <c r="AC108" s="21">
@@ -14327,11 +13903,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z109" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z109" s="19" t="n"/>
       <c r="AA109" s="19" t="n"/>
       <c r="AB109" s="20" t="n"/>
       <c r="AC109" s="21">
@@ -14451,11 +14023,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z110" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z110" s="19" t="n"/>
       <c r="AA110" s="19" t="n"/>
       <c r="AB110" s="20" t="n"/>
       <c r="AC110" s="21">
@@ -14575,11 +14143,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z111" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z111" s="19" t="n"/>
       <c r="AA111" s="19" t="n"/>
       <c r="AB111" s="20" t="n"/>
       <c r="AC111" s="21">
@@ -14699,11 +14263,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z112" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z112" s="19" t="n"/>
       <c r="AA112" s="19" t="n"/>
       <c r="AB112" s="20" t="n"/>
       <c r="AC112" s="21">
@@ -14823,11 +14383,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z113" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z113" s="19" t="n"/>
       <c r="AA113" s="19" t="n"/>
       <c r="AB113" s="20" t="n"/>
       <c r="AC113" s="21">
@@ -14947,11 +14503,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z114" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z114" s="19" t="n"/>
       <c r="AA114" s="19" t="n"/>
       <c r="AB114" s="20" t="n"/>
       <c r="AC114" s="21">
@@ -15071,11 +14623,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z115" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z115" s="19" t="n"/>
       <c r="AA115" s="19" t="n"/>
       <c r="AB115" s="20" t="n"/>
       <c r="AC115" s="21">
@@ -15195,11 +14743,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z116" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z116" s="19" t="n"/>
       <c r="AA116" s="19" t="n"/>
       <c r="AB116" s="20" t="n"/>
       <c r="AC116" s="21">
@@ -15323,11 +14867,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z117" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z117" s="19" t="n"/>
       <c r="AA117" s="19" t="n"/>
       <c r="AB117" s="20" t="n"/>
       <c r="AC117" s="21">
@@ -15447,11 +14987,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z118" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z118" s="19" t="n"/>
       <c r="AA118" s="19" t="n"/>
       <c r="AB118" s="20" t="n"/>
       <c r="AC118" s="21">
@@ -15571,11 +15107,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z119" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z119" s="19" t="n"/>
       <c r="AA119" s="19" t="n"/>
       <c r="AB119" s="20" t="n"/>
       <c r="AC119" s="21">
@@ -15695,11 +15227,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z120" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z120" s="19" t="n"/>
       <c r="AA120" s="19" t="n"/>
       <c r="AB120" s="20" t="n"/>
       <c r="AC120" s="21">
@@ -15823,11 +15351,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z121" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z121" s="19" t="n"/>
       <c r="AA121" s="19" t="n"/>
       <c r="AB121" s="20" t="n"/>
       <c r="AC121" s="21">
@@ -15951,11 +15475,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z122" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z122" s="19" t="n"/>
       <c r="AA122" s="19" t="n"/>
       <c r="AB122" s="20" t="n"/>
       <c r="AC122" s="21">
@@ -16079,11 +15599,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z123" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z123" s="19" t="n"/>
       <c r="AA123" s="19" t="n"/>
       <c r="AB123" s="20" t="n"/>
       <c r="AC123" s="21">
@@ -16203,11 +15719,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z124" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z124" s="19" t="n"/>
       <c r="AA124" s="19" t="n"/>
       <c r="AB124" s="20" t="n"/>
       <c r="AC124" s="21">
@@ -16327,11 +15839,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z125" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z125" s="19" t="n"/>
       <c r="AA125" s="19" t="n"/>
       <c r="AB125" s="20" t="n"/>
       <c r="AC125" s="21">
@@ -16434,7 +15942,7 @@
       <c r="V126" s="15" t="n"/>
       <c r="W126" s="19" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="X126" s="19" t="n"/>
@@ -16443,11 +15951,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z126" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z126" s="19" t="n"/>
       <c r="AA126" s="19" t="n"/>
       <c r="AB126" s="20" t="n"/>
       <c r="AC126" s="21">
@@ -16571,11 +16075,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z127" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z127" s="19" t="n"/>
       <c r="AA127" s="19" t="n"/>
       <c r="AB127" s="20" t="n"/>
       <c r="AC127" s="21">
@@ -16695,11 +16195,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z128" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z128" s="19" t="n"/>
       <c r="AA128" s="19" t="n"/>
       <c r="AB128" s="20" t="n"/>
       <c r="AC128" s="21">
@@ -16819,11 +16315,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z129" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z129" s="19" t="n"/>
       <c r="AA129" s="19" t="n"/>
       <c r="AB129" s="20" t="n"/>
       <c r="AC129" s="21">
@@ -16943,11 +16435,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z130" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z130" s="19" t="n"/>
       <c r="AA130" s="19" t="n"/>
       <c r="AB130" s="20" t="n"/>
       <c r="AC130" s="21">
@@ -17067,11 +16555,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z131" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z131" s="19" t="n"/>
       <c r="AA131" s="19" t="n"/>
       <c r="AB131" s="20" t="n"/>
       <c r="AC131" s="21">
@@ -17191,11 +16675,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z132" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z132" s="19" t="n"/>
       <c r="AA132" s="19" t="n"/>
       <c r="AB132" s="20" t="n"/>
       <c r="AC132" s="21">
@@ -17315,11 +16795,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z133" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z133" s="19" t="n"/>
       <c r="AA133" s="19" t="n"/>
       <c r="AB133" s="20" t="n"/>
       <c r="AC133" s="21">
@@ -17439,11 +16915,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z134" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z134" s="19" t="n"/>
       <c r="AA134" s="19" t="n"/>
       <c r="AB134" s="20" t="n"/>
       <c r="AC134" s="21">
@@ -17564,11 +17036,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z135" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z135" s="19" t="n"/>
       <c r="AA135" s="19" t="n"/>
       <c r="AB135" s="20" t="n"/>
       <c r="AC135" s="21">
@@ -17688,11 +17156,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z136" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z136" s="19" t="n"/>
       <c r="AA136" s="19" t="n"/>
       <c r="AB136" s="20" t="n"/>
       <c r="AC136" s="21">
@@ -17812,11 +17276,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z137" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z137" s="19" t="n"/>
       <c r="AA137" s="19" t="n"/>
       <c r="AB137" s="20" t="n"/>
       <c r="AC137" s="21">
@@ -17940,11 +17400,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z138" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z138" s="19" t="n"/>
       <c r="AA138" s="19" t="n"/>
       <c r="AB138" s="20" t="n"/>
       <c r="AC138" s="21">
@@ -18064,11 +17520,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z139" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z139" s="19" t="n"/>
       <c r="AA139" s="19" t="n"/>
       <c r="AB139" s="20" t="n"/>
       <c r="AC139" s="21">
@@ -18188,11 +17640,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z140" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z140" s="19" t="n"/>
       <c r="AA140" s="19" t="n"/>
       <c r="AB140" s="20" t="n"/>
       <c r="AC140" s="21">
@@ -18312,11 +17760,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z141" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z141" s="19" t="n"/>
       <c r="AA141" s="19" t="n"/>
       <c r="AB141" s="20" t="n"/>
       <c r="AC141" s="21">
@@ -18436,11 +17880,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z142" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z142" s="19" t="n"/>
       <c r="AA142" s="19" t="n"/>
       <c r="AB142" s="20" t="n"/>
       <c r="AC142" s="21">
@@ -18560,11 +18000,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z143" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z143" s="19" t="n"/>
       <c r="AA143" s="19" t="n"/>
       <c r="AB143" s="20" t="n"/>
       <c r="AC143" s="21">
@@ -18684,11 +18120,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z144" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z144" s="19" t="n"/>
       <c r="AA144" s="19" t="n"/>
       <c r="AB144" s="20" t="n"/>
       <c r="AC144" s="21">
@@ -18808,11 +18240,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z145" s="19" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
+      <c r="Z145" s="19" t="n"/>
       <c r="AA145" s="19" t="n"/>
       <c r="AB145" s="20" t="n"/>
       <c r="AC145" s="21">
@@ -18893,7 +18321,7 @@
       <formula1>"verfügbar,reserviert,teilverkauft,verkauft,gespendet,entsorgt"</formula1>
     </dataValidation>
     <dataValidation sqref="Z3:Z803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Klinik,Kleinanzeigen,eBay,Direkt,Händler,Verkaufstag"</formula1>
+      <formula1>"Webkatalog,Kleinanzeigen,eBay,Direkt,Händler,Verkaufstag"</formula1>
     </dataValidation>
     <dataValidation sqref="AG3:AG803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"offen,bezahlt,teilbezahlt"</formula1>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AK$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AK$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK145"/>
+  <dimension ref="A1:AK154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18260,8 +18260,1068 @@
       </c>
       <c r="AK145" s="22" t="n"/>
     </row>
+    <row r="146" ht="30" customHeight="1">
+      <c r="A146" s="15" t="inlineStr">
+        <is>
+          <t>NU01-13</t>
+        </is>
+      </c>
+      <c r="B146" s="15" t="n"/>
+      <c r="C146" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>Vitrine Nussbaum, vierteilig</t>
+        </is>
+      </c>
+      <c r="E146" s="16" t="inlineStr">
+        <is>
+          <t>Wohnzimmervitrine im Barockstil, Nussbaum furniert. Vier Türen, davon zwei mit Glas und Glaseinlegeböden, geschnitzte Zierleisten, Schloss vorhanden.</t>
+        </is>
+      </c>
+      <c r="F146" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="G146" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I146" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J146" s="17" t="n"/>
+      <c r="K146" s="18">
+        <f>I146-IF(J146="",0,J146)</f>
+        <v/>
+      </c>
+      <c r="L146" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M146" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="N146" s="19" t="n"/>
+      <c r="O146" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P146" s="19" t="n"/>
+      <c r="Q146" s="20" t="n"/>
+      <c r="R146" s="20" t="n">
+        <v>120</v>
+      </c>
+      <c r="S146" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T146" s="21">
+        <f>K146*R146</f>
+        <v/>
+      </c>
+      <c r="U146" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V146" s="15" t="inlineStr">
+        <is>
+          <t>F-114</t>
+        </is>
+      </c>
+      <c r="W146" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X146" s="19" t="n"/>
+      <c r="Y146" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z146" s="19" t="n"/>
+      <c r="AA146" s="19" t="n"/>
+      <c r="AB146" s="20" t="n"/>
+      <c r="AC146" s="21">
+        <f>IF(J146="","",J146*AB146)</f>
+        <v/>
+      </c>
+      <c r="AD146" s="19" t="n"/>
+      <c r="AE146" s="19" t="n"/>
+      <c r="AF146" s="19" t="n"/>
+      <c r="AG146" s="19" t="n"/>
+      <c r="AH146" s="19" t="n"/>
+      <c r="AI146" s="19" t="n"/>
+      <c r="AJ146" s="16" t="inlineStr">
+        <is>
+          <t>1 Vitrine. Die Dekoration darin ist Position NU01-03 und wird getrennt verkauft.</t>
+        </is>
+      </c>
+      <c r="AK146" s="22" t="inlineStr">
+        <is>
+          <t>Auf dem Foto sind gerahmte Personenfotos in der Vitrine maskiert – ein neues Foto ohne die Rahmen wäre besser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>NU01-14</t>
+        </is>
+      </c>
+      <c r="B147" s="15" t="n"/>
+      <c r="C147" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D147" s="15" t="inlineStr">
+        <is>
+          <t>Kindergarderobe mit Sitzbank, weiß</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>Schreinerarbeit aus weiß beschichteter Platte mit Multiplex-Kanten. Oben vier offene Fächer, darunter vier weiße Doppelhaken, Sitzbank mit Schuhrost aus Holzlatten.</t>
+        </is>
+      </c>
+      <c r="F147" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="G147" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H147" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I147" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="J147" s="17" t="n"/>
+      <c r="K147" s="18">
+        <f>I147-IF(J147="",0,J147)</f>
+        <v/>
+      </c>
+      <c r="L147" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M147" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="N147" s="19" t="n"/>
+      <c r="O147" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P147" s="19" t="n"/>
+      <c r="Q147" s="20" t="n"/>
+      <c r="R147" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="S147" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T147" s="21">
+        <f>K147*R147</f>
+        <v/>
+      </c>
+      <c r="U147" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V147" s="15" t="inlineStr">
+        <is>
+          <t>F-115</t>
+        </is>
+      </c>
+      <c r="W147" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X147" s="19" t="n"/>
+      <c r="Y147" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z147" s="19" t="n"/>
+      <c r="AA147" s="19" t="n"/>
+      <c r="AB147" s="20" t="n"/>
+      <c r="AC147" s="21">
+        <f>IF(J147="","",J147*AB147)</f>
+        <v/>
+      </c>
+      <c r="AD147" s="19" t="n"/>
+      <c r="AE147" s="19" t="n"/>
+      <c r="AF147" s="19" t="n"/>
+      <c r="AG147" s="19" t="n"/>
+      <c r="AH147" s="19" t="n"/>
+      <c r="AI147" s="19" t="n"/>
+      <c r="AJ147" s="16" t="inlineStr">
+        <is>
+          <t>5 gleiche Einheiten laut Erfassungsblatt – abgebildet ist eine davon.</t>
+        </is>
+      </c>
+      <c r="AK147" s="22" t="n"/>
+    </row>
+    <row r="148" ht="30" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
+        <is>
+          <t>NU01-15</t>
+        </is>
+      </c>
+      <c r="B148" s="15" t="n"/>
+      <c r="C148" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="inlineStr">
+        <is>
+          <t>Garderobenschrank weiß mit Grafikfront</t>
+        </is>
+      </c>
+      <c r="E148" s="16" t="inlineStr">
+        <is>
+          <t>Weiß beschichteter Schrank mit hoher Tür und Schubladen, Griffmulden ohne Beschläge. Die Fronten tragen eine schwarze Grafik (Straße mit Fahrzeugen), die sich über alle vier Schränke fortsetzt und nur zusammen ein Bild ergibt.</t>
+        </is>
+      </c>
+      <c r="F148" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="G148" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I148" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J148" s="17" t="n"/>
+      <c r="K148" s="18">
+        <f>I148-IF(J148="",0,J148)</f>
+        <v/>
+      </c>
+      <c r="L148" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M148" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="N148" s="19" t="n"/>
+      <c r="O148" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P148" s="19" t="n"/>
+      <c r="Q148" s="20" t="n"/>
+      <c r="R148" s="20" t="n">
+        <v>120</v>
+      </c>
+      <c r="S148" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T148" s="21">
+        <f>K148*R148</f>
+        <v/>
+      </c>
+      <c r="U148" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V148" s="15" t="inlineStr">
+        <is>
+          <t>F-118</t>
+        </is>
+      </c>
+      <c r="W148" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X148" s="19" t="n"/>
+      <c r="Y148" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z148" s="19" t="n"/>
+      <c r="AA148" s="19" t="n"/>
+      <c r="AB148" s="20" t="n"/>
+      <c r="AC148" s="21">
+        <f>IF(J148="","",J148*AB148)</f>
+        <v/>
+      </c>
+      <c r="AD148" s="19" t="n"/>
+      <c r="AE148" s="19" t="n"/>
+      <c r="AF148" s="19" t="n"/>
+      <c r="AG148" s="19" t="n"/>
+      <c r="AH148" s="19" t="n"/>
+      <c r="AI148" s="19" t="n"/>
+      <c r="AJ148" s="16" t="inlineStr">
+        <is>
+          <t>4 gleiche Schränke laut Erfassungsblatt – abgebildet ist die Schrankwand im Ganzen.</t>
+        </is>
+      </c>
+      <c r="AK148" s="22" t="n"/>
+    </row>
+    <row r="149" ht="30" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
+        <is>
+          <t>NU01-16</t>
+        </is>
+      </c>
+      <c r="B149" s="15" t="n"/>
+      <c r="C149" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="inlineStr">
+        <is>
+          <t>Waschmaschine LG 17 kg, F11WM17VT2</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>LG Vollwaschautomat, Inverter Direct Drive, TrueSteam, 17 kg Füllmenge. Modell F11WM17VT2 laut Typenschild, 2000–2250 W. Gewerblich genutzt.</t>
+        </is>
+      </c>
+      <c r="F149" s="15" t="inlineStr">
+        <is>
+          <t>Technik</t>
+        </is>
+      </c>
+      <c r="G149" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H149" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I149" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="17" t="n"/>
+      <c r="K149" s="18">
+        <f>I149-IF(J149="",0,J149)</f>
+        <v/>
+      </c>
+      <c r="L149" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M149" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="N149" s="19" t="inlineStr">
+        <is>
+          <t>99 × 70 × 77 cm (H×B×T)</t>
+        </is>
+      </c>
+      <c r="O149" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P149" s="19" t="n"/>
+      <c r="Q149" s="20" t="n"/>
+      <c r="R149" s="20" t="n">
+        <v>350</v>
+      </c>
+      <c r="S149" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T149" s="21">
+        <f>K149*R149</f>
+        <v/>
+      </c>
+      <c r="U149" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V149" s="15" t="inlineStr">
+        <is>
+          <t>F-119</t>
+        </is>
+      </c>
+      <c r="W149" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X149" s="19" t="n"/>
+      <c r="Y149" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z149" s="19" t="n"/>
+      <c r="AA149" s="19" t="n"/>
+      <c r="AB149" s="20" t="n"/>
+      <c r="AC149" s="21">
+        <f>IF(J149="","",J149*AB149)</f>
+        <v/>
+      </c>
+      <c r="AD149" s="19" t="n"/>
+      <c r="AE149" s="19" t="n"/>
+      <c r="AF149" s="19" t="n"/>
+      <c r="AG149" s="19" t="n"/>
+      <c r="AH149" s="19" t="n"/>
+      <c r="AI149" s="19" t="n"/>
+      <c r="AJ149" s="16" t="inlineStr">
+        <is>
+          <t>1 Gerät. Typenschild ist abfotografiert (Foto F-121).</t>
+        </is>
+      </c>
+      <c r="AK149" s="22" t="n"/>
+    </row>
+    <row r="150" ht="30" customHeight="1">
+      <c r="A150" s="15" t="inlineStr">
+        <is>
+          <t>NU01-17</t>
+        </is>
+      </c>
+      <c r="B150" s="15" t="n"/>
+      <c r="C150" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D150" s="15" t="inlineStr">
+        <is>
+          <t>Wärmepumpentrockner Miele T1 Excellence, 8 kg</t>
+        </is>
+      </c>
+      <c r="E150" s="16" t="inlineStr">
+        <is>
+          <t>Miele Wärmepumpentrockner der Reihe T1 Excellence, 8 kg. Typenschild: TEC235WP, Type HT30. Aufkleber des Elektrofachbetriebs Frommer, VS-Schwenningen.</t>
+        </is>
+      </c>
+      <c r="F150" s="15" t="inlineStr">
+        <is>
+          <t>Technik</t>
+        </is>
+      </c>
+      <c r="G150" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H150" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I150" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="17" t="n"/>
+      <c r="K150" s="18">
+        <f>I150-IF(J150="",0,J150)</f>
+        <v/>
+      </c>
+      <c r="L150" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M150" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="N150" s="19" t="n"/>
+      <c r="O150" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P150" s="19" t="n"/>
+      <c r="Q150" s="20" t="n"/>
+      <c r="R150" s="20" t="n">
+        <v>400</v>
+      </c>
+      <c r="S150" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T150" s="21">
+        <f>K150*R150</f>
+        <v/>
+      </c>
+      <c r="U150" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V150" s="15" t="inlineStr">
+        <is>
+          <t>F-120</t>
+        </is>
+      </c>
+      <c r="W150" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X150" s="19" t="n"/>
+      <c r="Y150" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z150" s="19" t="n"/>
+      <c r="AA150" s="19" t="n"/>
+      <c r="AB150" s="20" t="n"/>
+      <c r="AC150" s="21">
+        <f>IF(J150="","",J150*AB150)</f>
+        <v/>
+      </c>
+      <c r="AD150" s="19" t="n"/>
+      <c r="AE150" s="19" t="n"/>
+      <c r="AF150" s="19" t="n"/>
+      <c r="AG150" s="19" t="n"/>
+      <c r="AH150" s="19" t="n"/>
+      <c r="AI150" s="19" t="n"/>
+      <c r="AJ150" s="16" t="inlineStr">
+        <is>
+          <t>1 Gerät. Typenschild ist abfotografiert (Foto F-122).</t>
+        </is>
+      </c>
+      <c r="AK150" s="22" t="n"/>
+    </row>
+    <row r="151" ht="30" customHeight="1">
+      <c r="A151" s="15" t="inlineStr">
+        <is>
+          <t>NU01-18</t>
+        </is>
+      </c>
+      <c r="B151" s="15" t="n"/>
+      <c r="C151" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="inlineStr">
+        <is>
+          <t>Waschmaschine Candy RapidÓ, 9 kg</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>Candy RapidÓ, 9 kg, 1400 Touren, Speed-Drive-Inverter, Simply-Fi (App-Anbindung), Kg Detector. Modell RO14960WMC5/1-S laut Typenschild, 1600 W.</t>
+        </is>
+      </c>
+      <c r="F151" s="15" t="inlineStr">
+        <is>
+          <t>Technik</t>
+        </is>
+      </c>
+      <c r="G151" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H151" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I151" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="17" t="n"/>
+      <c r="K151" s="18">
+        <f>I151-IF(J151="",0,J151)</f>
+        <v/>
+      </c>
+      <c r="L151" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M151" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="N151" s="19" t="n"/>
+      <c r="O151" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P151" s="19" t="n"/>
+      <c r="Q151" s="20" t="n"/>
+      <c r="R151" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="S151" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T151" s="21">
+        <f>K151*R151</f>
+        <v/>
+      </c>
+      <c r="U151" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V151" s="15" t="inlineStr">
+        <is>
+          <t>F-123</t>
+        </is>
+      </c>
+      <c r="W151" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X151" s="19" t="n"/>
+      <c r="Y151" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z151" s="19" t="n"/>
+      <c r="AA151" s="19" t="n"/>
+      <c r="AB151" s="20" t="n"/>
+      <c r="AC151" s="21">
+        <f>IF(J151="","",J151*AB151)</f>
+        <v/>
+      </c>
+      <c r="AD151" s="19" t="n"/>
+      <c r="AE151" s="19" t="n"/>
+      <c r="AF151" s="19" t="n"/>
+      <c r="AG151" s="19" t="n"/>
+      <c r="AH151" s="19" t="n"/>
+      <c r="AI151" s="19" t="n"/>
+      <c r="AJ151" s="16" t="inlineStr">
+        <is>
+          <t>1 Gerät. Typenschild ist abfotografiert (Foto F-124).</t>
+        </is>
+      </c>
+      <c r="AK151" s="22" t="n"/>
+    </row>
+    <row r="152" ht="30" customHeight="1">
+      <c r="A152" s="15" t="inlineStr">
+        <is>
+          <t>NU01-19</t>
+        </is>
+      </c>
+      <c r="B152" s="15" t="n"/>
+      <c r="C152" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D152" s="15" t="inlineStr">
+        <is>
+          <t>Kindergarderobe mit Hakenleiste und Wannen, weiß</t>
+        </is>
+      </c>
+      <c r="E152" s="16" t="inlineStr">
+        <is>
+          <t>Weißes Wandelement mit vier offenen Fächern und darin liegenden Kunststoffwannen, darunter vier rote Doppelhaken. Davor eine weiße Sitzbank aus Holz mit Schublade.</t>
+        </is>
+      </c>
+      <c r="F152" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="G152" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H152" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I152" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J152" s="17" t="n"/>
+      <c r="K152" s="18">
+        <f>I152-IF(J152="",0,J152)</f>
+        <v/>
+      </c>
+      <c r="L152" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M152" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="N152" s="19" t="n"/>
+      <c r="O152" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P152" s="19" t="n"/>
+      <c r="Q152" s="20" t="n"/>
+      <c r="R152" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="S152" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T152" s="21">
+        <f>K152*R152</f>
+        <v/>
+      </c>
+      <c r="U152" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V152" s="15" t="inlineStr">
+        <is>
+          <t>F-125</t>
+        </is>
+      </c>
+      <c r="W152" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X152" s="19" t="n"/>
+      <c r="Y152" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z152" s="19" t="n"/>
+      <c r="AA152" s="19" t="n"/>
+      <c r="AB152" s="20" t="n"/>
+      <c r="AC152" s="21">
+        <f>IF(J152="","",J152*AB152)</f>
+        <v/>
+      </c>
+      <c r="AD152" s="19" t="n"/>
+      <c r="AE152" s="19" t="n"/>
+      <c r="AF152" s="19" t="n"/>
+      <c r="AG152" s="19" t="n"/>
+      <c r="AH152" s="19" t="n"/>
+      <c r="AI152" s="19" t="n"/>
+      <c r="AJ152" s="16" t="inlineStr">
+        <is>
+          <t>4 gleiche Einheiten laut Erfassungsblatt – abgebildet ist eine davon.</t>
+        </is>
+      </c>
+      <c r="AK152" s="22" t="inlineStr">
+        <is>
+          <t>Offen: gehört die Sitzbank zur Position oder ist sie eigenständig zu erfassen?</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="30" customHeight="1">
+      <c r="A153" s="15" t="inlineStr">
+        <is>
+          <t>NU01-20</t>
+        </is>
+      </c>
+      <c r="B153" s="15" t="n"/>
+      <c r="C153" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="inlineStr">
+        <is>
+          <t>Clubsessel rot, Kunstleder</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>Runder Clubsessel in Tonnenform, roter Kunstlederbezug, niedrige Sitzhöhe – im Haus als Kindersessel genutzt. Gebrauchsspuren an Kanten und Sitzfläche, kleine Risse im Bezug.</t>
+        </is>
+      </c>
+      <c r="F153" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="G153" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H153" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I153" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J153" s="17" t="n"/>
+      <c r="K153" s="18">
+        <f>I153-IF(J153="",0,J153)</f>
+        <v/>
+      </c>
+      <c r="L153" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M153" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="N153" s="19" t="n"/>
+      <c r="O153" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P153" s="19" t="n"/>
+      <c r="Q153" s="20" t="n"/>
+      <c r="R153" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="S153" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T153" s="21">
+        <f>K153*R153</f>
+        <v/>
+      </c>
+      <c r="U153" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V153" s="15" t="inlineStr">
+        <is>
+          <t>F-127</t>
+        </is>
+      </c>
+      <c r="W153" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X153" s="19" t="n"/>
+      <c r="Y153" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z153" s="19" t="n"/>
+      <c r="AA153" s="19" t="n"/>
+      <c r="AB153" s="20" t="n"/>
+      <c r="AC153" s="21">
+        <f>IF(J153="","",J153*AB153)</f>
+        <v/>
+      </c>
+      <c r="AD153" s="19" t="n"/>
+      <c r="AE153" s="19" t="n"/>
+      <c r="AF153" s="19" t="n"/>
+      <c r="AG153" s="19" t="n"/>
+      <c r="AH153" s="19" t="n"/>
+      <c r="AI153" s="19" t="n"/>
+      <c r="AJ153" s="16" t="inlineStr">
+        <is>
+          <t>2 Sessel, beide abgebildet.</t>
+        </is>
+      </c>
+      <c r="AK153" s="22" t="n"/>
+    </row>
+    <row r="154" ht="30" customHeight="1">
+      <c r="A154" s="15" t="inlineStr">
+        <is>
+          <t>NU01-21</t>
+        </is>
+      </c>
+      <c r="B154" s="15" t="n"/>
+      <c r="C154" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D154" s="15" t="inlineStr">
+        <is>
+          <t>Leuchte Mr Maria „Miffy“, groß und klein</t>
+        </is>
+      </c>
+      <c r="E154" s="16" t="inlineStr">
+        <is>
+          <t>Zwei Leuchten in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Typenschild: MR LED8. Ein großes und ein kleines Exemplar.</t>
+        </is>
+      </c>
+      <c r="F154" s="15" t="inlineStr">
+        <is>
+          <t>Leuchten</t>
+        </is>
+      </c>
+      <c r="G154" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H154" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I154" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J154" s="17" t="n"/>
+      <c r="K154" s="18">
+        <f>I154-IF(J154="",0,J154)</f>
+        <v/>
+      </c>
+      <c r="L154" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M154" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="N154" s="19" t="n"/>
+      <c r="O154" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P154" s="19" t="n"/>
+      <c r="Q154" s="20" t="n"/>
+      <c r="R154" s="20" t="n">
+        <v>95</v>
+      </c>
+      <c r="S154" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T154" s="21">
+        <f>K154*R154</f>
+        <v/>
+      </c>
+      <c r="U154" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V154" s="15" t="inlineStr">
+        <is>
+          <t>F-132</t>
+        </is>
+      </c>
+      <c r="W154" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X154" s="19" t="n"/>
+      <c r="Y154" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z154" s="19" t="n"/>
+      <c r="AA154" s="19" t="n"/>
+      <c r="AB154" s="20" t="n"/>
+      <c r="AC154" s="21">
+        <f>IF(J154="","",J154*AB154)</f>
+        <v/>
+      </c>
+      <c r="AD154" s="19" t="n"/>
+      <c r="AE154" s="19" t="n"/>
+      <c r="AF154" s="19" t="n"/>
+      <c r="AG154" s="19" t="n"/>
+      <c r="AH154" s="19" t="n"/>
+      <c r="AI154" s="19" t="n"/>
+      <c r="AJ154" s="16" t="inlineStr">
+        <is>
+          <t>2 Leuchten: ein großes und ein kleines Exemplar, beide abgebildet. Bei Teilabnahme bitte angeben, welches Exemplar gewünscht ist.</t>
+        </is>
+      </c>
+      <c r="AK154" s="22" t="inlineStr">
+        <is>
+          <t>Zu klären: als eine Position mit 2 Stück lassen oder in groß und klein trennen – die Größen sind unterschiedlich viel wert.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AK145"/>
+  <autoFilter ref="A2:AK154"/>
   <mergeCells count="7">
     <mergeCell ref="AJ1:AK1"/>
     <mergeCell ref="A1:O1"/>
@@ -18271,7 +19331,7 @@
     <mergeCell ref="AF1:AI1"/>
     <mergeCell ref="U1:AA1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Y3:Y145">
+  <conditionalFormatting sqref="Y3:Y154">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -18282,12 +19342,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H145">
+  <conditionalFormatting sqref="H3:H154">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O145">
+  <conditionalFormatting sqref="O3:O154">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -18378,7 +19438,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$145)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$154)</f>
         <v/>
       </c>
     </row>
@@ -18389,7 +19449,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Y$3:$Y$145,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Y$3:$Y$154,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -18400,7 +19460,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Y$3:$Y$145,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Y$3:$Y$154,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -18411,7 +19471,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Y$3:$Y$145,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Y$3:$Y$154,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -18422,7 +19482,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Y$3:$Y$145,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Y$3:$Y$154,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -18433,7 +19493,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$145)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$154)</f>
         <v/>
       </c>
     </row>
@@ -18444,7 +19504,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$T$3:$T$145)</f>
+        <f>SUM(Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18462,7 +19522,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$J$3:$J$145)</f>
+        <f>SUM(Artikelstamm!$J$3:$J$154)</f>
         <v/>
       </c>
     </row>
@@ -18473,7 +19533,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$J$3:$J$145,Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT(Artikelstamm!$J$3:$J$154,Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
     </row>
@@ -18506,7 +19566,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AG$3:$AG$145="bezahlt")*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AG$3:$AG$154="bezahlt")*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
     </row>
@@ -18535,7 +19595,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$145,"*verkauft",Artikelstamm!$AF$3:$AF$145,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$154,"*verkauft",Artikelstamm!$AF$3:$AF$154,"")</f>
         <v/>
       </c>
     </row>
@@ -18546,7 +19606,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$145,"*verkauft",Artikelstamm!$AG$3:$AG$145,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$154,"*verkauft",Artikelstamm!$AG$3:$AG$154,"offen")</f>
         <v/>
       </c>
     </row>
@@ -18557,7 +19617,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$145,"reserviert",Artikelstamm!$AI$3:$AI$145,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$154,"reserviert",Artikelstamm!$AI$3:$AI$154,"")</f>
         <v/>
       </c>
     </row>
@@ -18568,7 +19628,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$R$3:$R$145,"")</f>
+        <f>COUNTIFS(Artikelstamm!$R$3:$R$154,"")</f>
         <v/>
       </c>
     </row>
@@ -18579,7 +19639,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$N$3:$N$145,"")</f>
+        <f>COUNTIFS(Artikelstamm!$N$3:$N$154,"")</f>
         <v/>
       </c>
     </row>
@@ -18619,15 +19679,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$145,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$154,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$145=$A30)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$154=$A30)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$145,$A30,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$154,$A30,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18638,15 +19698,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$145,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$154,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$145=$A31)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$154=$A31)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$145,$A31,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$154,$A31,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18657,15 +19717,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$145,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$154,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$145=$A32)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$154=$A32)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$145,$A32,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$154,$A32,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18724,15 +19784,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A37)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A37)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A37,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A37,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18743,15 +19803,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A38)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A38)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A38,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A38,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18762,15 +19822,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A39)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A39)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A39,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A39,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18781,15 +19841,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A40)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A40)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A40,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A40,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18800,15 +19860,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A41)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A41)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A41,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A41,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18819,15 +19879,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A42)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A42)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A42,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A42,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18838,15 +19898,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A43)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A43)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A43,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A43,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18857,15 +19917,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A44)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A44)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A44,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A44,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18876,15 +19936,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A45)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A45)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A45,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A45,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18895,15 +19955,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A46)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A46)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A46,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A46,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18914,15 +19974,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A47)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A47)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A47,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A47,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18933,15 +19993,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A48)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A48)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A48,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A48,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18952,15 +20012,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A49)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A49)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A49,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A49,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -18971,15 +20031,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$145,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$145=$A50)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A50)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$145,$A50,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A50,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19038,15 +20098,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A55)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A55)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A55,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A55,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19057,15 +20117,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A56)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A56)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A56,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A56,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19076,15 +20136,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A57)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A57)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A57,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A57,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19095,15 +20155,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A58)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A58)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A58,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A58,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19114,15 +20174,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A59)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A59)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A59,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A59,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19133,15 +20193,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A60)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A60)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A60,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A60,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19152,15 +20212,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A61)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A61)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A61,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A61,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19171,15 +20231,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A62)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A62)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A62,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A62,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19190,15 +20250,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A63)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A63)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A63,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A63,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19209,15 +20269,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A64)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A64)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A64,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A64,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19228,15 +20288,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A65)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A65)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A65,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A65,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19247,15 +20307,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A66)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A66)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A66,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A66,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19266,15 +20326,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A67)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A67)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A67,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A67,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19285,15 +20345,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A68)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A68)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A68,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A68,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19304,15 +20364,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A69)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A69)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A69,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A69,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19323,15 +20383,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A70)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A70)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A70,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A70,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19342,15 +20402,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A71)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A71)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A71,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A71,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19361,15 +20421,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A72)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A72)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A72,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A72,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19380,15 +20440,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$145,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$145=$A73)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A73)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$145,$A73,Artikelstamm!$T$3:$T$145)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A73,Artikelstamm!$T$3:$T$154)</f>
         <v/>
       </c>
     </row>
@@ -19442,11 +20502,11 @@
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$145,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$145=$A78)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A78)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
     </row>
@@ -19457,11 +20517,11 @@
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$145,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$145=$A79)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A79)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
     </row>
@@ -19472,11 +20532,11 @@
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$145,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$145=$A80)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A80)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
     </row>
@@ -19487,11 +20547,11 @@
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$145,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$145=$A81)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A81)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
     </row>
@@ -19502,11 +20562,11 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$145,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$145=$A82)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A82)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
     </row>
@@ -19517,11 +20577,11 @@
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$145,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$145=$A83)*Artikelstamm!$J$3:$J$145*Artikelstamm!$AB$3:$AB$145)</f>
+        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A83)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AK$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AL$155</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK154"/>
+  <dimension ref="A1:AL155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1048,17 +1048,18 @@
     <col width="18" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
-    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="29" max="29"/>
     <col width="14" customWidth="1" min="30" max="30"/>
-    <col width="24" customWidth="1" min="31" max="31"/>
-    <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="13" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="24" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="40" customWidth="1" min="36" max="36"/>
-    <col width="32" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="40" customWidth="1" min="37" max="37"/>
+    <col width="32" customWidth="1" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1082,17 +1083,17 @@
           <t>VERMARKTUNG</t>
         </is>
       </c>
-      <c r="AB1" s="10" t="inlineStr">
+      <c r="AC1" s="10" t="inlineStr">
         <is>
           <t>VERKAUF</t>
         </is>
       </c>
-      <c r="AF1" s="9" t="inlineStr">
+      <c r="AG1" s="9" t="inlineStr">
         <is>
           <t>KAUFMÄNNISCH</t>
         </is>
       </c>
-      <c r="AJ1" s="12" t="inlineStr">
+      <c r="AK1" s="12" t="inlineStr">
         <is>
           <t>NOTIZEN</t>
         </is>
@@ -1226,60 +1227,65 @@
       </c>
       <c r="Z2" s="14" t="inlineStr">
         <is>
+          <t>Marke</t>
+        </is>
+      </c>
+      <c r="AA2" s="14" t="inlineStr">
+        <is>
           <t>Kanal</t>
         </is>
       </c>
-      <c r="AA2" s="14" t="inlineStr">
+      <c r="AB2" s="14" t="inlineStr">
         <is>
           <t>Reserviert_für</t>
         </is>
       </c>
-      <c r="AB2" s="14" t="inlineStr">
+      <c r="AC2" s="14" t="inlineStr">
         <is>
           <t>Verkaufspreis_netto</t>
         </is>
       </c>
-      <c r="AC2" s="13" t="inlineStr">
+      <c r="AD2" s="13" t="inlineStr">
         <is>
           <t>Umsatz_netto</t>
         </is>
       </c>
-      <c r="AD2" s="14" t="inlineStr">
+      <c r="AE2" s="14" t="inlineStr">
         <is>
           <t>Verkaufsdatum</t>
         </is>
       </c>
-      <c r="AE2" s="14" t="inlineStr">
+      <c r="AF2" s="14" t="inlineStr">
         <is>
           <t>Käufer</t>
         </is>
       </c>
-      <c r="AF2" s="14" t="inlineStr">
+      <c r="AG2" s="14" t="inlineStr">
         <is>
           <t>Rechnungsnr</t>
         </is>
       </c>
-      <c r="AG2" s="14" t="inlineStr">
+      <c r="AH2" s="14" t="inlineStr">
         <is>
           <t>Zahlung</t>
         </is>
       </c>
-      <c r="AH2" s="14" t="inlineStr">
+      <c r="AI2" s="14" t="inlineStr">
         <is>
           <t>Zahlart</t>
         </is>
       </c>
-      <c r="AI2" s="14" t="inlineStr">
+      <c r="AJ2" s="14" t="inlineStr">
         <is>
           <t>Abholtermin</t>
         </is>
       </c>
-      <c r="AJ2" s="13" t="inlineStr">
+      <c r="AK2" s="13" t="inlineStr">
         <is>
           <t>Mengenhinweis</t>
         </is>
       </c>
-      <c r="AK2" s="14" t="inlineStr">
+      <c r="AL2" s="14" t="inlineStr">
         <is>
           <t>Bemerkung</t>
         </is>
@@ -1353,7 +1359,7 @@
       <c r="P3" s="19" t="n"/>
       <c r="Q3" s="20" t="n"/>
       <c r="R3" s="20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="S3" s="19" t="inlineStr">
         <is>
@@ -1387,23 +1393,24 @@
       </c>
       <c r="Z3" s="19" t="n"/>
       <c r="AA3" s="19" t="n"/>
-      <c r="AB3" s="20" t="n"/>
-      <c r="AC3" s="21">
-        <f>IF(J3="","",J3*AB3)</f>
-        <v/>
-      </c>
-      <c r="AD3" s="19" t="n"/>
+      <c r="AB3" s="19" t="n"/>
+      <c r="AC3" s="20" t="n"/>
+      <c r="AD3" s="21">
+        <f>IF(J3="","",J3*AC3)</f>
+        <v/>
+      </c>
       <c r="AE3" s="19" t="n"/>
       <c r="AF3" s="19" t="n"/>
       <c r="AG3" s="19" t="n"/>
       <c r="AH3" s="19" t="n"/>
       <c r="AI3" s="19" t="n"/>
-      <c r="AJ3" s="16" t="inlineStr">
+      <c r="AJ3" s="19" t="n"/>
+      <c r="AK3" s="16" t="inlineStr">
         <is>
           <t>1 Regal mit 6 Körben im Bild</t>
         </is>
       </c>
-      <c r="AK3" s="22" t="n"/>
+      <c r="AL3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
@@ -1507,23 +1514,24 @@
       </c>
       <c r="Z4" s="19" t="n"/>
       <c r="AA4" s="19" t="n"/>
-      <c r="AB4" s="20" t="n"/>
-      <c r="AC4" s="21">
-        <f>IF(J4="","",J4*AB4)</f>
-        <v/>
-      </c>
-      <c r="AD4" s="19" t="n"/>
+      <c r="AB4" s="19" t="n"/>
+      <c r="AC4" s="20" t="n"/>
+      <c r="AD4" s="21">
+        <f>IF(J4="","",J4*AC4)</f>
+        <v/>
+      </c>
       <c r="AE4" s="19" t="n"/>
       <c r="AF4" s="19" t="n"/>
       <c r="AG4" s="19" t="n"/>
       <c r="AH4" s="19" t="n"/>
       <c r="AI4" s="19" t="n"/>
-      <c r="AJ4" s="16" t="inlineStr">
+      <c r="AJ4" s="19" t="n"/>
+      <c r="AK4" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK4" s="22" t="n"/>
+      <c r="AL4" s="22" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
@@ -1631,23 +1639,24 @@
       </c>
       <c r="Z5" s="19" t="n"/>
       <c r="AA5" s="19" t="n"/>
-      <c r="AB5" s="20" t="n"/>
-      <c r="AC5" s="21">
-        <f>IF(J5="","",J5*AB5)</f>
-        <v/>
-      </c>
-      <c r="AD5" s="19" t="n"/>
+      <c r="AB5" s="19" t="n"/>
+      <c r="AC5" s="20" t="n"/>
+      <c r="AD5" s="21">
+        <f>IF(J5="","",J5*AC5)</f>
+        <v/>
+      </c>
       <c r="AE5" s="19" t="n"/>
       <c r="AF5" s="19" t="n"/>
       <c r="AG5" s="19" t="n"/>
       <c r="AH5" s="19" t="n"/>
       <c r="AI5" s="19" t="n"/>
-      <c r="AJ5" s="16" t="inlineStr">
+      <c r="AJ5" s="19" t="n"/>
+      <c r="AK5" s="16" t="inlineStr">
         <is>
           <t>mehrere Schrankfächer - Menge bitte vor Ort festlegen</t>
         </is>
       </c>
-      <c r="AK5" s="22" t="n"/>
+      <c r="AL5" s="22" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
@@ -1751,23 +1760,24 @@
       </c>
       <c r="Z6" s="19" t="n"/>
       <c r="AA6" s="19" t="n"/>
-      <c r="AB6" s="20" t="n"/>
-      <c r="AC6" s="21">
-        <f>IF(J6="","",J6*AB6)</f>
-        <v/>
-      </c>
-      <c r="AD6" s="19" t="n"/>
+      <c r="AB6" s="19" t="n"/>
+      <c r="AC6" s="20" t="n"/>
+      <c r="AD6" s="21">
+        <f>IF(J6="","",J6*AC6)</f>
+        <v/>
+      </c>
       <c r="AE6" s="19" t="n"/>
       <c r="AF6" s="19" t="n"/>
       <c r="AG6" s="19" t="n"/>
       <c r="AH6" s="19" t="n"/>
       <c r="AI6" s="19" t="n"/>
-      <c r="AJ6" s="16" t="inlineStr">
+      <c r="AJ6" s="19" t="n"/>
+      <c r="AK6" s="16" t="inlineStr">
         <is>
           <t>1 Sortierkasten im Bild</t>
         </is>
       </c>
-      <c r="AK6" s="22" t="n"/>
+      <c r="AL6" s="22" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
@@ -1871,23 +1881,24 @@
       </c>
       <c r="Z7" s="19" t="n"/>
       <c r="AA7" s="19" t="n"/>
-      <c r="AB7" s="20" t="n"/>
-      <c r="AC7" s="21">
-        <f>IF(J7="","",J7*AB7)</f>
-        <v/>
-      </c>
-      <c r="AD7" s="19" t="n"/>
+      <c r="AB7" s="19" t="n"/>
+      <c r="AC7" s="20" t="n"/>
+      <c r="AD7" s="21">
+        <f>IF(J7="","",J7*AC7)</f>
+        <v/>
+      </c>
       <c r="AE7" s="19" t="n"/>
       <c r="AF7" s="19" t="n"/>
       <c r="AG7" s="19" t="n"/>
       <c r="AH7" s="19" t="n"/>
       <c r="AI7" s="19" t="n"/>
-      <c r="AJ7" s="16" t="inlineStr">
+      <c r="AJ7" s="19" t="n"/>
+      <c r="AK7" s="16" t="inlineStr">
         <is>
           <t>2 Regalböden im Bild</t>
         </is>
       </c>
-      <c r="AK7" s="22" t="n"/>
+      <c r="AL7" s="22" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
@@ -1991,23 +2002,24 @@
       </c>
       <c r="Z8" s="19" t="n"/>
       <c r="AA8" s="19" t="n"/>
-      <c r="AB8" s="20" t="n"/>
-      <c r="AC8" s="21">
-        <f>IF(J8="","",J8*AB8)</f>
-        <v/>
-      </c>
-      <c r="AD8" s="19" t="n"/>
+      <c r="AB8" s="19" t="n"/>
+      <c r="AC8" s="20" t="n"/>
+      <c r="AD8" s="21">
+        <f>IF(J8="","",J8*AC8)</f>
+        <v/>
+      </c>
       <c r="AE8" s="19" t="n"/>
       <c r="AF8" s="19" t="n"/>
       <c r="AG8" s="19" t="n"/>
       <c r="AH8" s="19" t="n"/>
       <c r="AI8" s="19" t="n"/>
-      <c r="AJ8" s="16" t="inlineStr">
+      <c r="AJ8" s="19" t="n"/>
+      <c r="AK8" s="16" t="inlineStr">
         <is>
           <t>1 Schrank inkl. Restbestand Papier</t>
         </is>
       </c>
-      <c r="AK8" s="22" t="n"/>
+      <c r="AL8" s="22" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
@@ -2111,23 +2123,24 @@
       </c>
       <c r="Z9" s="19" t="n"/>
       <c r="AA9" s="19" t="n"/>
-      <c r="AB9" s="20" t="n"/>
-      <c r="AC9" s="21">
-        <f>IF(J9="","",J9*AB9)</f>
-        <v/>
-      </c>
-      <c r="AD9" s="19" t="n"/>
+      <c r="AB9" s="19" t="n"/>
+      <c r="AC9" s="20" t="n"/>
+      <c r="AD9" s="21">
+        <f>IF(J9="","",J9*AC9)</f>
+        <v/>
+      </c>
       <c r="AE9" s="19" t="n"/>
       <c r="AF9" s="19" t="n"/>
       <c r="AG9" s="19" t="n"/>
       <c r="AH9" s="19" t="n"/>
       <c r="AI9" s="19" t="n"/>
-      <c r="AJ9" s="16" t="inlineStr">
+      <c r="AJ9" s="19" t="n"/>
+      <c r="AK9" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK9" s="22" t="n"/>
+      <c r="AL9" s="22" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
@@ -2231,23 +2244,24 @@
       </c>
       <c r="Z10" s="19" t="n"/>
       <c r="AA10" s="19" t="n"/>
-      <c r="AB10" s="20" t="n"/>
-      <c r="AC10" s="21">
-        <f>IF(J10="","",J10*AB10)</f>
-        <v/>
-      </c>
-      <c r="AD10" s="19" t="n"/>
+      <c r="AB10" s="19" t="n"/>
+      <c r="AC10" s="20" t="n"/>
+      <c r="AD10" s="21">
+        <f>IF(J10="","",J10*AC10)</f>
+        <v/>
+      </c>
       <c r="AE10" s="19" t="n"/>
       <c r="AF10" s="19" t="n"/>
       <c r="AG10" s="19" t="n"/>
       <c r="AH10" s="19" t="n"/>
       <c r="AI10" s="19" t="n"/>
-      <c r="AJ10" s="16" t="inlineStr">
+      <c r="AJ10" s="19" t="n"/>
+      <c r="AK10" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AK10" s="22" t="n"/>
+      <c r="AL10" s="22" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
@@ -2351,23 +2365,24 @@
       </c>
       <c r="Z11" s="19" t="n"/>
       <c r="AA11" s="19" t="n"/>
-      <c r="AB11" s="20" t="n"/>
-      <c r="AC11" s="21">
-        <f>IF(J11="","",J11*AB11)</f>
-        <v/>
-      </c>
-      <c r="AD11" s="19" t="n"/>
+      <c r="AB11" s="19" t="n"/>
+      <c r="AC11" s="20" t="n"/>
+      <c r="AD11" s="21">
+        <f>IF(J11="","",J11*AC11)</f>
+        <v/>
+      </c>
       <c r="AE11" s="19" t="n"/>
       <c r="AF11" s="19" t="n"/>
       <c r="AG11" s="19" t="n"/>
       <c r="AH11" s="19" t="n"/>
       <c r="AI11" s="19" t="n"/>
-      <c r="AJ11" s="16" t="inlineStr">
+      <c r="AJ11" s="19" t="n"/>
+      <c r="AK11" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK11" s="22" t="n"/>
+      <c r="AL11" s="22" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
@@ -2473,25 +2488,30 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z12" s="19" t="n"/>
+      <c r="Z12" s="19" t="inlineStr">
+        <is>
+          <t>USM Haller</t>
+        </is>
+      </c>
       <c r="AA12" s="19" t="n"/>
-      <c r="AB12" s="20" t="n"/>
-      <c r="AC12" s="21">
-        <f>IF(J12="","",J12*AB12)</f>
-        <v/>
-      </c>
-      <c r="AD12" s="19" t="n"/>
+      <c r="AB12" s="19" t="n"/>
+      <c r="AC12" s="20" t="n"/>
+      <c r="AD12" s="21">
+        <f>IF(J12="","",J12*AC12)</f>
+        <v/>
+      </c>
       <c r="AE12" s="19" t="n"/>
       <c r="AF12" s="19" t="n"/>
       <c r="AG12" s="19" t="n"/>
       <c r="AH12" s="19" t="n"/>
       <c r="AI12" s="19" t="n"/>
-      <c r="AJ12" s="16" t="inlineStr">
+      <c r="AJ12" s="19" t="n"/>
+      <c r="AK12" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AK12" s="22" t="n"/>
+      <c r="AL12" s="22" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
@@ -2593,25 +2613,30 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z13" s="19" t="n"/>
+      <c r="Z13" s="19" t="inlineStr">
+        <is>
+          <t>Kartell</t>
+        </is>
+      </c>
       <c r="AA13" s="19" t="n"/>
-      <c r="AB13" s="20" t="n"/>
-      <c r="AC13" s="21">
-        <f>IF(J13="","",J13*AB13)</f>
-        <v/>
-      </c>
-      <c r="AD13" s="19" t="n"/>
+      <c r="AB13" s="19" t="n"/>
+      <c r="AC13" s="20" t="n"/>
+      <c r="AD13" s="21">
+        <f>IF(J13="","",J13*AC13)</f>
+        <v/>
+      </c>
       <c r="AE13" s="19" t="n"/>
       <c r="AF13" s="19" t="n"/>
       <c r="AG13" s="19" t="n"/>
       <c r="AH13" s="19" t="n"/>
       <c r="AI13" s="19" t="n"/>
-      <c r="AJ13" s="16" t="inlineStr">
+      <c r="AJ13" s="19" t="n"/>
+      <c r="AK13" s="16" t="inlineStr">
         <is>
           <t>mindestens 6 Stück erkennbar - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AK13" s="22" t="n"/>
+      <c r="AL13" s="22" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -2715,23 +2740,24 @@
       </c>
       <c r="Z14" s="19" t="n"/>
       <c r="AA14" s="19" t="n"/>
-      <c r="AB14" s="20" t="n"/>
-      <c r="AC14" s="21">
-        <f>IF(J14="","",J14*AB14)</f>
-        <v/>
-      </c>
-      <c r="AD14" s="19" t="n"/>
+      <c r="AB14" s="19" t="n"/>
+      <c r="AC14" s="20" t="n"/>
+      <c r="AD14" s="21">
+        <f>IF(J14="","",J14*AC14)</f>
+        <v/>
+      </c>
       <c r="AE14" s="19" t="n"/>
       <c r="AF14" s="19" t="n"/>
       <c r="AG14" s="19" t="n"/>
       <c r="AH14" s="19" t="n"/>
       <c r="AI14" s="19" t="n"/>
-      <c r="AJ14" s="16" t="inlineStr">
+      <c r="AJ14" s="19" t="n"/>
+      <c r="AK14" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AK14" s="22" t="n"/>
+      <c r="AL14" s="22" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
@@ -2835,23 +2861,24 @@
       </c>
       <c r="Z15" s="19" t="n"/>
       <c r="AA15" s="19" t="n"/>
-      <c r="AB15" s="20" t="n"/>
-      <c r="AC15" s="21">
-        <f>IF(J15="","",J15*AB15)</f>
-        <v/>
-      </c>
-      <c r="AD15" s="19" t="n"/>
+      <c r="AB15" s="19" t="n"/>
+      <c r="AC15" s="20" t="n"/>
+      <c r="AD15" s="21">
+        <f>IF(J15="","",J15*AC15)</f>
+        <v/>
+      </c>
       <c r="AE15" s="19" t="n"/>
       <c r="AF15" s="19" t="n"/>
       <c r="AG15" s="19" t="n"/>
       <c r="AH15" s="19" t="n"/>
       <c r="AI15" s="19" t="n"/>
-      <c r="AJ15" s="16" t="inlineStr">
+      <c r="AJ15" s="19" t="n"/>
+      <c r="AK15" s="16" t="inlineStr">
         <is>
           <t>1 Sofa im Bild</t>
         </is>
       </c>
-      <c r="AK15" s="22" t="n"/>
+      <c r="AL15" s="22" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -2956,23 +2983,24 @@
       </c>
       <c r="Z16" s="19" t="n"/>
       <c r="AA16" s="19" t="n"/>
-      <c r="AB16" s="20" t="n"/>
-      <c r="AC16" s="21">
-        <f>IF(J16="","",J16*AB16)</f>
-        <v/>
-      </c>
-      <c r="AD16" s="19" t="n"/>
+      <c r="AB16" s="19" t="n"/>
+      <c r="AC16" s="20" t="n"/>
+      <c r="AD16" s="21">
+        <f>IF(J16="","",J16*AC16)</f>
+        <v/>
+      </c>
       <c r="AE16" s="19" t="n"/>
       <c r="AF16" s="19" t="n"/>
       <c r="AG16" s="19" t="n"/>
       <c r="AH16" s="19" t="n"/>
       <c r="AI16" s="19" t="n"/>
-      <c r="AJ16" s="16" t="inlineStr">
+      <c r="AJ16" s="19" t="n"/>
+      <c r="AK16" s="16" t="inlineStr">
         <is>
           <t>1 Sessel im Bild</t>
         </is>
       </c>
-      <c r="AK16" s="22" t="n"/>
+      <c r="AL16" s="22" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -3077,23 +3105,24 @@
       </c>
       <c r="Z17" s="19" t="n"/>
       <c r="AA17" s="19" t="n"/>
-      <c r="AB17" s="20" t="n"/>
-      <c r="AC17" s="21">
-        <f>IF(J17="","",J17*AB17)</f>
-        <v/>
-      </c>
-      <c r="AD17" s="19" t="n"/>
+      <c r="AB17" s="19" t="n"/>
+      <c r="AC17" s="20" t="n"/>
+      <c r="AD17" s="21">
+        <f>IF(J17="","",J17*AC17)</f>
+        <v/>
+      </c>
       <c r="AE17" s="19" t="n"/>
       <c r="AF17" s="19" t="n"/>
       <c r="AG17" s="19" t="n"/>
       <c r="AH17" s="19" t="n"/>
       <c r="AI17" s="19" t="n"/>
-      <c r="AJ17" s="16" t="inlineStr">
+      <c r="AJ17" s="19" t="n"/>
+      <c r="AK17" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK17" s="22" t="n"/>
+      <c r="AL17" s="22" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -3197,23 +3226,24 @@
       </c>
       <c r="Z18" s="19" t="n"/>
       <c r="AA18" s="19" t="n"/>
-      <c r="AB18" s="20" t="n"/>
-      <c r="AC18" s="21">
-        <f>IF(J18="","",J18*AB18)</f>
-        <v/>
-      </c>
-      <c r="AD18" s="19" t="n"/>
+      <c r="AB18" s="19" t="n"/>
+      <c r="AC18" s="20" t="n"/>
+      <c r="AD18" s="21">
+        <f>IF(J18="","",J18*AC18)</f>
+        <v/>
+      </c>
       <c r="AE18" s="19" t="n"/>
       <c r="AF18" s="19" t="n"/>
       <c r="AG18" s="19" t="n"/>
       <c r="AH18" s="19" t="n"/>
       <c r="AI18" s="19" t="n"/>
-      <c r="AJ18" s="16" t="inlineStr">
+      <c r="AJ18" s="19" t="n"/>
+      <c r="AK18" s="16" t="inlineStr">
         <is>
           <t>2 Sessel im Bild</t>
         </is>
       </c>
-      <c r="AK18" s="22" t="n"/>
+      <c r="AL18" s="22" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
@@ -3317,23 +3347,24 @@
       </c>
       <c r="Z19" s="19" t="n"/>
       <c r="AA19" s="19" t="n"/>
-      <c r="AB19" s="20" t="n"/>
-      <c r="AC19" s="21">
-        <f>IF(J19="","",J19*AB19)</f>
-        <v/>
-      </c>
-      <c r="AD19" s="19" t="n"/>
+      <c r="AB19" s="19" t="n"/>
+      <c r="AC19" s="20" t="n"/>
+      <c r="AD19" s="21">
+        <f>IF(J19="","",J19*AC19)</f>
+        <v/>
+      </c>
       <c r="AE19" s="19" t="n"/>
       <c r="AF19" s="19" t="n"/>
       <c r="AG19" s="19" t="n"/>
       <c r="AH19" s="19" t="n"/>
       <c r="AI19" s="19" t="n"/>
-      <c r="AJ19" s="16" t="inlineStr">
+      <c r="AJ19" s="19" t="n"/>
+      <c r="AK19" s="16" t="inlineStr">
         <is>
           <t>2 Hocker im Bild</t>
         </is>
       </c>
-      <c r="AK19" s="22" t="n"/>
+      <c r="AL19" s="22" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -3437,23 +3468,24 @@
       </c>
       <c r="Z20" s="19" t="n"/>
       <c r="AA20" s="19" t="n"/>
-      <c r="AB20" s="20" t="n"/>
-      <c r="AC20" s="21">
-        <f>IF(J20="","",J20*AB20)</f>
-        <v/>
-      </c>
-      <c r="AD20" s="19" t="n"/>
+      <c r="AB20" s="19" t="n"/>
+      <c r="AC20" s="20" t="n"/>
+      <c r="AD20" s="21">
+        <f>IF(J20="","",J20*AC20)</f>
+        <v/>
+      </c>
       <c r="AE20" s="19" t="n"/>
       <c r="AF20" s="19" t="n"/>
       <c r="AG20" s="19" t="n"/>
       <c r="AH20" s="19" t="n"/>
       <c r="AI20" s="19" t="n"/>
-      <c r="AJ20" s="16" t="inlineStr">
+      <c r="AJ20" s="19" t="n"/>
+      <c r="AK20" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AK20" s="22" t="n"/>
+      <c r="AL20" s="22" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -3557,23 +3589,24 @@
       </c>
       <c r="Z21" s="19" t="n"/>
       <c r="AA21" s="19" t="n"/>
-      <c r="AB21" s="20" t="n"/>
-      <c r="AC21" s="21">
-        <f>IF(J21="","",J21*AB21)</f>
-        <v/>
-      </c>
-      <c r="AD21" s="19" t="n"/>
+      <c r="AB21" s="19" t="n"/>
+      <c r="AC21" s="20" t="n"/>
+      <c r="AD21" s="21">
+        <f>IF(J21="","",J21*AC21)</f>
+        <v/>
+      </c>
       <c r="AE21" s="19" t="n"/>
       <c r="AF21" s="19" t="n"/>
       <c r="AG21" s="19" t="n"/>
       <c r="AH21" s="19" t="n"/>
       <c r="AI21" s="19" t="n"/>
-      <c r="AJ21" s="16" t="inlineStr">
+      <c r="AJ21" s="19" t="n"/>
+      <c r="AK21" s="16" t="inlineStr">
         <is>
           <t>1 Leuchte im Bild</t>
         </is>
       </c>
-      <c r="AK21" s="22" t="n"/>
+      <c r="AL21" s="22" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
@@ -3677,23 +3710,24 @@
       </c>
       <c r="Z22" s="19" t="n"/>
       <c r="AA22" s="19" t="n"/>
-      <c r="AB22" s="20" t="n"/>
-      <c r="AC22" s="21">
-        <f>IF(J22="","",J22*AB22)</f>
-        <v/>
-      </c>
-      <c r="AD22" s="19" t="n"/>
+      <c r="AB22" s="19" t="n"/>
+      <c r="AC22" s="20" t="n"/>
+      <c r="AD22" s="21">
+        <f>IF(J22="","",J22*AC22)</f>
+        <v/>
+      </c>
       <c r="AE22" s="19" t="n"/>
       <c r="AF22" s="19" t="n"/>
       <c r="AG22" s="19" t="n"/>
       <c r="AH22" s="19" t="n"/>
       <c r="AI22" s="19" t="n"/>
-      <c r="AJ22" s="16" t="inlineStr">
+      <c r="AJ22" s="19" t="n"/>
+      <c r="AK22" s="16" t="inlineStr">
         <is>
           <t>1 Mobile im Bild</t>
         </is>
       </c>
-      <c r="AK22" s="22" t="n"/>
+      <c r="AL22" s="22" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
@@ -3797,23 +3831,24 @@
       </c>
       <c r="Z23" s="19" t="n"/>
       <c r="AA23" s="19" t="n"/>
-      <c r="AB23" s="20" t="n"/>
-      <c r="AC23" s="21">
-        <f>IF(J23="","",J23*AB23)</f>
-        <v/>
-      </c>
-      <c r="AD23" s="19" t="n"/>
+      <c r="AB23" s="19" t="n"/>
+      <c r="AC23" s="20" t="n"/>
+      <c r="AD23" s="21">
+        <f>IF(J23="","",J23*AC23)</f>
+        <v/>
+      </c>
       <c r="AE23" s="19" t="n"/>
       <c r="AF23" s="19" t="n"/>
       <c r="AG23" s="19" t="n"/>
       <c r="AH23" s="19" t="n"/>
       <c r="AI23" s="19" t="n"/>
-      <c r="AJ23" s="16" t="inlineStr">
+      <c r="AJ23" s="19" t="n"/>
+      <c r="AK23" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK23" s="22" t="n"/>
+      <c r="AL23" s="22" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
@@ -3917,23 +3952,24 @@
       </c>
       <c r="Z24" s="19" t="n"/>
       <c r="AA24" s="19" t="n"/>
-      <c r="AB24" s="20" t="n"/>
-      <c r="AC24" s="21">
-        <f>IF(J24="","",J24*AB24)</f>
-        <v/>
-      </c>
-      <c r="AD24" s="19" t="n"/>
+      <c r="AB24" s="19" t="n"/>
+      <c r="AC24" s="20" t="n"/>
+      <c r="AD24" s="21">
+        <f>IF(J24="","",J24*AC24)</f>
+        <v/>
+      </c>
       <c r="AE24" s="19" t="n"/>
       <c r="AF24" s="19" t="n"/>
       <c r="AG24" s="19" t="n"/>
       <c r="AH24" s="19" t="n"/>
       <c r="AI24" s="19" t="n"/>
-      <c r="AJ24" s="16" t="inlineStr">
+      <c r="AJ24" s="19" t="n"/>
+      <c r="AK24" s="16" t="inlineStr">
         <is>
           <t>3 Rahmen im Bild</t>
         </is>
       </c>
-      <c r="AK24" s="22" t="n"/>
+      <c r="AL24" s="22" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -4037,23 +4073,24 @@
       </c>
       <c r="Z25" s="19" t="n"/>
       <c r="AA25" s="19" t="n"/>
-      <c r="AB25" s="20" t="n"/>
-      <c r="AC25" s="21">
-        <f>IF(J25="","",J25*AB25)</f>
-        <v/>
-      </c>
-      <c r="AD25" s="19" t="n"/>
+      <c r="AB25" s="19" t="n"/>
+      <c r="AC25" s="20" t="n"/>
+      <c r="AD25" s="21">
+        <f>IF(J25="","",J25*AC25)</f>
+        <v/>
+      </c>
       <c r="AE25" s="19" t="n"/>
       <c r="AF25" s="19" t="n"/>
       <c r="AG25" s="19" t="n"/>
       <c r="AH25" s="19" t="n"/>
       <c r="AI25" s="19" t="n"/>
-      <c r="AJ25" s="16" t="inlineStr">
+      <c r="AJ25" s="19" t="n"/>
+      <c r="AK25" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK25" s="22" t="n"/>
+      <c r="AL25" s="22" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
@@ -4157,23 +4194,24 @@
       </c>
       <c r="Z26" s="19" t="n"/>
       <c r="AA26" s="19" t="n"/>
-      <c r="AB26" s="20" t="n"/>
-      <c r="AC26" s="21">
-        <f>IF(J26="","",J26*AB26)</f>
-        <v/>
-      </c>
-      <c r="AD26" s="19" t="n"/>
+      <c r="AB26" s="19" t="n"/>
+      <c r="AC26" s="20" t="n"/>
+      <c r="AD26" s="21">
+        <f>IF(J26="","",J26*AC26)</f>
+        <v/>
+      </c>
       <c r="AE26" s="19" t="n"/>
       <c r="AF26" s="19" t="n"/>
       <c r="AG26" s="19" t="n"/>
       <c r="AH26" s="19" t="n"/>
       <c r="AI26" s="19" t="n"/>
-      <c r="AJ26" s="16" t="inlineStr">
+      <c r="AJ26" s="19" t="n"/>
+      <c r="AK26" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK26" s="22" t="n"/>
+      <c r="AL26" s="22" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
@@ -4277,23 +4315,24 @@
       </c>
       <c r="Z27" s="19" t="n"/>
       <c r="AA27" s="19" t="n"/>
-      <c r="AB27" s="20" t="n"/>
-      <c r="AC27" s="21">
-        <f>IF(J27="","",J27*AB27)</f>
-        <v/>
-      </c>
-      <c r="AD27" s="19" t="n"/>
+      <c r="AB27" s="19" t="n"/>
+      <c r="AC27" s="20" t="n"/>
+      <c r="AD27" s="21">
+        <f>IF(J27="","",J27*AC27)</f>
+        <v/>
+      </c>
       <c r="AE27" s="19" t="n"/>
       <c r="AF27" s="19" t="n"/>
       <c r="AG27" s="19" t="n"/>
       <c r="AH27" s="19" t="n"/>
       <c r="AI27" s="19" t="n"/>
-      <c r="AJ27" s="16" t="inlineStr">
+      <c r="AJ27" s="19" t="n"/>
+      <c r="AK27" s="16" t="inlineStr">
         <is>
           <t>1 Sofa im Bild</t>
         </is>
       </c>
-      <c r="AK27" s="22" t="n"/>
+      <c r="AL27" s="22" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
@@ -4397,23 +4436,24 @@
       </c>
       <c r="Z28" s="19" t="n"/>
       <c r="AA28" s="19" t="n"/>
-      <c r="AB28" s="20" t="n"/>
-      <c r="AC28" s="21">
-        <f>IF(J28="","",J28*AB28)</f>
-        <v/>
-      </c>
-      <c r="AD28" s="19" t="n"/>
+      <c r="AB28" s="19" t="n"/>
+      <c r="AC28" s="20" t="n"/>
+      <c r="AD28" s="21">
+        <f>IF(J28="","",J28*AC28)</f>
+        <v/>
+      </c>
       <c r="AE28" s="19" t="n"/>
       <c r="AF28" s="19" t="n"/>
       <c r="AG28" s="19" t="n"/>
       <c r="AH28" s="19" t="n"/>
       <c r="AI28" s="19" t="n"/>
-      <c r="AJ28" s="16" t="inlineStr">
+      <c r="AJ28" s="19" t="n"/>
+      <c r="AK28" s="16" t="inlineStr">
         <is>
           <t>1 Leuchte im Bild</t>
         </is>
       </c>
-      <c r="AK28" s="22" t="n"/>
+      <c r="AL28" s="22" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
@@ -4517,23 +4557,24 @@
       </c>
       <c r="Z29" s="19" t="n"/>
       <c r="AA29" s="19" t="n"/>
-      <c r="AB29" s="20" t="n"/>
-      <c r="AC29" s="21">
-        <f>IF(J29="","",J29*AB29)</f>
-        <v/>
-      </c>
-      <c r="AD29" s="19" t="n"/>
+      <c r="AB29" s="19" t="n"/>
+      <c r="AC29" s="20" t="n"/>
+      <c r="AD29" s="21">
+        <f>IF(J29="","",J29*AC29)</f>
+        <v/>
+      </c>
       <c r="AE29" s="19" t="n"/>
       <c r="AF29" s="19" t="n"/>
       <c r="AG29" s="19" t="n"/>
       <c r="AH29" s="19" t="n"/>
       <c r="AI29" s="19" t="n"/>
-      <c r="AJ29" s="16" t="inlineStr">
+      <c r="AJ29" s="19" t="n"/>
+      <c r="AK29" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AK29" s="22" t="n"/>
+      <c r="AL29" s="22" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
@@ -4637,23 +4678,24 @@
       </c>
       <c r="Z30" s="19" t="n"/>
       <c r="AA30" s="19" t="n"/>
-      <c r="AB30" s="20" t="n"/>
-      <c r="AC30" s="21">
-        <f>IF(J30="","",J30*AB30)</f>
-        <v/>
-      </c>
-      <c r="AD30" s="19" t="n"/>
+      <c r="AB30" s="19" t="n"/>
+      <c r="AC30" s="20" t="n"/>
+      <c r="AD30" s="21">
+        <f>IF(J30="","",J30*AC30)</f>
+        <v/>
+      </c>
       <c r="AE30" s="19" t="n"/>
       <c r="AF30" s="19" t="n"/>
       <c r="AG30" s="19" t="n"/>
       <c r="AH30" s="19" t="n"/>
       <c r="AI30" s="19" t="n"/>
-      <c r="AJ30" s="16" t="inlineStr">
+      <c r="AJ30" s="19" t="n"/>
+      <c r="AK30" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK30" s="22" t="n"/>
+      <c r="AL30" s="22" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -4757,23 +4799,24 @@
       </c>
       <c r="Z31" s="19" t="n"/>
       <c r="AA31" s="19" t="n"/>
-      <c r="AB31" s="20" t="n"/>
-      <c r="AC31" s="21">
-        <f>IF(J31="","",J31*AB31)</f>
-        <v/>
-      </c>
-      <c r="AD31" s="19" t="n"/>
+      <c r="AB31" s="19" t="n"/>
+      <c r="AC31" s="20" t="n"/>
+      <c r="AD31" s="21">
+        <f>IF(J31="","",J31*AC31)</f>
+        <v/>
+      </c>
       <c r="AE31" s="19" t="n"/>
       <c r="AF31" s="19" t="n"/>
       <c r="AG31" s="19" t="n"/>
       <c r="AH31" s="19" t="n"/>
       <c r="AI31" s="19" t="n"/>
-      <c r="AJ31" s="16" t="inlineStr">
+      <c r="AJ31" s="19" t="n"/>
+      <c r="AK31" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AK31" s="22" t="n"/>
+      <c r="AL31" s="22" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -4877,23 +4920,24 @@
       </c>
       <c r="Z32" s="19" t="n"/>
       <c r="AA32" s="19" t="n"/>
-      <c r="AB32" s="20" t="n"/>
-      <c r="AC32" s="21">
-        <f>IF(J32="","",J32*AB32)</f>
-        <v/>
-      </c>
-      <c r="AD32" s="19" t="n"/>
+      <c r="AB32" s="19" t="n"/>
+      <c r="AC32" s="20" t="n"/>
+      <c r="AD32" s="21">
+        <f>IF(J32="","",J32*AC32)</f>
+        <v/>
+      </c>
       <c r="AE32" s="19" t="n"/>
       <c r="AF32" s="19" t="n"/>
       <c r="AG32" s="19" t="n"/>
       <c r="AH32" s="19" t="n"/>
       <c r="AI32" s="19" t="n"/>
-      <c r="AJ32" s="16" t="inlineStr">
+      <c r="AJ32" s="19" t="n"/>
+      <c r="AK32" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AK32" s="22" t="n"/>
+      <c r="AL32" s="22" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
@@ -4997,23 +5041,24 @@
       </c>
       <c r="Z33" s="19" t="n"/>
       <c r="AA33" s="19" t="n"/>
-      <c r="AB33" s="20" t="n"/>
-      <c r="AC33" s="21">
-        <f>IF(J33="","",J33*AB33)</f>
-        <v/>
-      </c>
-      <c r="AD33" s="19" t="n"/>
+      <c r="AB33" s="19" t="n"/>
+      <c r="AC33" s="20" t="n"/>
+      <c r="AD33" s="21">
+        <f>IF(J33="","",J33*AC33)</f>
+        <v/>
+      </c>
       <c r="AE33" s="19" t="n"/>
       <c r="AF33" s="19" t="n"/>
       <c r="AG33" s="19" t="n"/>
       <c r="AH33" s="19" t="n"/>
       <c r="AI33" s="19" t="n"/>
-      <c r="AJ33" s="16" t="inlineStr">
+      <c r="AJ33" s="19" t="n"/>
+      <c r="AK33" s="16" t="inlineStr">
         <is>
           <t>1 Kübel im Bild (Bepflanzung enthalten)</t>
         </is>
       </c>
-      <c r="AK33" s="22" t="n"/>
+      <c r="AL33" s="22" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
@@ -5117,23 +5162,24 @@
       </c>
       <c r="Z34" s="19" t="n"/>
       <c r="AA34" s="19" t="n"/>
-      <c r="AB34" s="20" t="n"/>
-      <c r="AC34" s="21">
-        <f>IF(J34="","",J34*AB34)</f>
-        <v/>
-      </c>
-      <c r="AD34" s="19" t="n"/>
+      <c r="AB34" s="19" t="n"/>
+      <c r="AC34" s="20" t="n"/>
+      <c r="AD34" s="21">
+        <f>IF(J34="","",J34*AC34)</f>
+        <v/>
+      </c>
       <c r="AE34" s="19" t="n"/>
       <c r="AF34" s="19" t="n"/>
       <c r="AG34" s="19" t="n"/>
       <c r="AH34" s="19" t="n"/>
       <c r="AI34" s="19" t="n"/>
-      <c r="AJ34" s="16" t="inlineStr">
+      <c r="AJ34" s="19" t="n"/>
+      <c r="AK34" s="16" t="inlineStr">
         <is>
           <t>1 Teppich im Bild</t>
         </is>
       </c>
-      <c r="AK34" s="22" t="n"/>
+      <c r="AL34" s="22" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="15" t="inlineStr">
@@ -5237,23 +5283,24 @@
       </c>
       <c r="Z35" s="19" t="n"/>
       <c r="AA35" s="19" t="n"/>
-      <c r="AB35" s="20" t="n"/>
-      <c r="AC35" s="21">
-        <f>IF(J35="","",J35*AB35)</f>
-        <v/>
-      </c>
-      <c r="AD35" s="19" t="n"/>
+      <c r="AB35" s="19" t="n"/>
+      <c r="AC35" s="20" t="n"/>
+      <c r="AD35" s="21">
+        <f>IF(J35="","",J35*AC35)</f>
+        <v/>
+      </c>
       <c r="AE35" s="19" t="n"/>
       <c r="AF35" s="19" t="n"/>
       <c r="AG35" s="19" t="n"/>
       <c r="AH35" s="19" t="n"/>
       <c r="AI35" s="19" t="n"/>
-      <c r="AJ35" s="16" t="inlineStr">
+      <c r="AJ35" s="19" t="n"/>
+      <c r="AK35" s="16" t="inlineStr">
         <is>
           <t>2 Regale im Bild</t>
         </is>
       </c>
-      <c r="AK35" s="22" t="n"/>
+      <c r="AL35" s="22" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="15" t="inlineStr">
@@ -5357,23 +5404,24 @@
       </c>
       <c r="Z36" s="19" t="n"/>
       <c r="AA36" s="19" t="n"/>
-      <c r="AB36" s="20" t="n"/>
-      <c r="AC36" s="21">
-        <f>IF(J36="","",J36*AB36)</f>
-        <v/>
-      </c>
-      <c r="AD36" s="19" t="n"/>
+      <c r="AB36" s="19" t="n"/>
+      <c r="AC36" s="20" t="n"/>
+      <c r="AD36" s="21">
+        <f>IF(J36="","",J36*AC36)</f>
+        <v/>
+      </c>
       <c r="AE36" s="19" t="n"/>
       <c r="AF36" s="19" t="n"/>
       <c r="AG36" s="19" t="n"/>
       <c r="AH36" s="19" t="n"/>
       <c r="AI36" s="19" t="n"/>
-      <c r="AJ36" s="16" t="inlineStr">
+      <c r="AJ36" s="19" t="n"/>
+      <c r="AK36" s="16" t="inlineStr">
         <is>
           <t>1 Set im Bild</t>
         </is>
       </c>
-      <c r="AK36" s="22" t="n"/>
+      <c r="AL36" s="22" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
@@ -5477,23 +5525,24 @@
       </c>
       <c r="Z37" s="19" t="n"/>
       <c r="AA37" s="19" t="n"/>
-      <c r="AB37" s="20" t="n"/>
-      <c r="AC37" s="21">
-        <f>IF(J37="","",J37*AB37)</f>
-        <v/>
-      </c>
-      <c r="AD37" s="19" t="n"/>
+      <c r="AB37" s="19" t="n"/>
+      <c r="AC37" s="20" t="n"/>
+      <c r="AD37" s="21">
+        <f>IF(J37="","",J37*AC37)</f>
+        <v/>
+      </c>
       <c r="AE37" s="19" t="n"/>
       <c r="AF37" s="19" t="n"/>
       <c r="AG37" s="19" t="n"/>
       <c r="AH37" s="19" t="n"/>
       <c r="AI37" s="19" t="n"/>
-      <c r="AJ37" s="16" t="inlineStr">
+      <c r="AJ37" s="19" t="n"/>
+      <c r="AK37" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK37" s="22" t="n"/>
+      <c r="AL37" s="22" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
@@ -5597,23 +5646,24 @@
       </c>
       <c r="Z38" s="19" t="n"/>
       <c r="AA38" s="19" t="n"/>
-      <c r="AB38" s="20" t="n"/>
-      <c r="AC38" s="21">
-        <f>IF(J38="","",J38*AB38)</f>
-        <v/>
-      </c>
-      <c r="AD38" s="19" t="n"/>
+      <c r="AB38" s="19" t="n"/>
+      <c r="AC38" s="20" t="n"/>
+      <c r="AD38" s="21">
+        <f>IF(J38="","",J38*AC38)</f>
+        <v/>
+      </c>
       <c r="AE38" s="19" t="n"/>
       <c r="AF38" s="19" t="n"/>
       <c r="AG38" s="19" t="n"/>
       <c r="AH38" s="19" t="n"/>
       <c r="AI38" s="19" t="n"/>
-      <c r="AJ38" s="16" t="inlineStr">
+      <c r="AJ38" s="19" t="n"/>
+      <c r="AK38" s="16" t="inlineStr">
         <is>
           <t>mehrere Kisten im Bild</t>
         </is>
       </c>
-      <c r="AK38" s="22" t="n"/>
+      <c r="AL38" s="22" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
@@ -5717,23 +5767,24 @@
       </c>
       <c r="Z39" s="19" t="n"/>
       <c r="AA39" s="19" t="n"/>
-      <c r="AB39" s="20" t="n"/>
-      <c r="AC39" s="21">
-        <f>IF(J39="","",J39*AB39)</f>
-        <v/>
-      </c>
-      <c r="AD39" s="19" t="n"/>
+      <c r="AB39" s="19" t="n"/>
+      <c r="AC39" s="20" t="n"/>
+      <c r="AD39" s="21">
+        <f>IF(J39="","",J39*AC39)</f>
+        <v/>
+      </c>
       <c r="AE39" s="19" t="n"/>
       <c r="AF39" s="19" t="n"/>
       <c r="AG39" s="19" t="n"/>
       <c r="AH39" s="19" t="n"/>
       <c r="AI39" s="19" t="n"/>
-      <c r="AJ39" s="16" t="inlineStr">
+      <c r="AJ39" s="19" t="n"/>
+      <c r="AK39" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK39" s="22" t="n"/>
+      <c r="AL39" s="22" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
@@ -5837,23 +5888,24 @@
       </c>
       <c r="Z40" s="19" t="n"/>
       <c r="AA40" s="19" t="n"/>
-      <c r="AB40" s="20" t="n"/>
-      <c r="AC40" s="21">
-        <f>IF(J40="","",J40*AB40)</f>
-        <v/>
-      </c>
-      <c r="AD40" s="19" t="n"/>
+      <c r="AB40" s="19" t="n"/>
+      <c r="AC40" s="20" t="n"/>
+      <c r="AD40" s="21">
+        <f>IF(J40="","",J40*AC40)</f>
+        <v/>
+      </c>
       <c r="AE40" s="19" t="n"/>
       <c r="AF40" s="19" t="n"/>
       <c r="AG40" s="19" t="n"/>
       <c r="AH40" s="19" t="n"/>
       <c r="AI40" s="19" t="n"/>
-      <c r="AJ40" s="16" t="inlineStr">
+      <c r="AJ40" s="19" t="n"/>
+      <c r="AK40" s="16" t="inlineStr">
         <is>
           <t>1 Liege im Bild</t>
         </is>
       </c>
-      <c r="AK40" s="22" t="n"/>
+      <c r="AL40" s="22" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
@@ -5953,23 +6005,24 @@
       </c>
       <c r="Z41" s="19" t="n"/>
       <c r="AA41" s="19" t="n"/>
-      <c r="AB41" s="20" t="n"/>
-      <c r="AC41" s="21">
-        <f>IF(J41="","",J41*AB41)</f>
-        <v/>
-      </c>
-      <c r="AD41" s="19" t="n"/>
+      <c r="AB41" s="19" t="n"/>
+      <c r="AC41" s="20" t="n"/>
+      <c r="AD41" s="21">
+        <f>IF(J41="","",J41*AC41)</f>
+        <v/>
+      </c>
       <c r="AE41" s="19" t="n"/>
       <c r="AF41" s="19" t="n"/>
       <c r="AG41" s="19" t="n"/>
       <c r="AH41" s="19" t="n"/>
       <c r="AI41" s="19" t="n"/>
-      <c r="AJ41" s="16" t="inlineStr">
+      <c r="AJ41" s="19" t="n"/>
+      <c r="AK41" s="16" t="inlineStr">
         <is>
           <t>1 Einheit aus 3 Modulen im Bild</t>
         </is>
       </c>
-      <c r="AK41" s="22" t="n"/>
+      <c r="AL41" s="22" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="15" t="inlineStr">
@@ -6069,23 +6122,24 @@
       </c>
       <c r="Z42" s="19" t="n"/>
       <c r="AA42" s="19" t="n"/>
-      <c r="AB42" s="20" t="n"/>
-      <c r="AC42" s="21">
-        <f>IF(J42="","",J42*AB42)</f>
-        <v/>
-      </c>
-      <c r="AD42" s="19" t="n"/>
+      <c r="AB42" s="19" t="n"/>
+      <c r="AC42" s="20" t="n"/>
+      <c r="AD42" s="21">
+        <f>IF(J42="","",J42*AC42)</f>
+        <v/>
+      </c>
       <c r="AE42" s="19" t="n"/>
       <c r="AF42" s="19" t="n"/>
       <c r="AG42" s="19" t="n"/>
       <c r="AH42" s="19" t="n"/>
       <c r="AI42" s="19" t="n"/>
-      <c r="AJ42" s="16" t="inlineStr">
+      <c r="AJ42" s="19" t="n"/>
+      <c r="AK42" s="16" t="inlineStr">
         <is>
           <t>3 Teile im Bild</t>
         </is>
       </c>
-      <c r="AK42" s="22" t="n"/>
+      <c r="AL42" s="22" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
@@ -6185,23 +6239,24 @@
       </c>
       <c r="Z43" s="19" t="n"/>
       <c r="AA43" s="19" t="n"/>
-      <c r="AB43" s="20" t="n"/>
-      <c r="AC43" s="21">
-        <f>IF(J43="","",J43*AB43)</f>
-        <v/>
-      </c>
-      <c r="AD43" s="19" t="n"/>
+      <c r="AB43" s="19" t="n"/>
+      <c r="AC43" s="20" t="n"/>
+      <c r="AD43" s="21">
+        <f>IF(J43="","",J43*AC43)</f>
+        <v/>
+      </c>
       <c r="AE43" s="19" t="n"/>
       <c r="AF43" s="19" t="n"/>
       <c r="AG43" s="19" t="n"/>
       <c r="AH43" s="19" t="n"/>
       <c r="AI43" s="19" t="n"/>
-      <c r="AJ43" s="16" t="inlineStr">
+      <c r="AJ43" s="19" t="n"/>
+      <c r="AK43" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK43" s="22" t="n"/>
+      <c r="AL43" s="22" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
@@ -6301,23 +6356,24 @@
       </c>
       <c r="Z44" s="19" t="n"/>
       <c r="AA44" s="19" t="n"/>
-      <c r="AB44" s="20" t="n"/>
-      <c r="AC44" s="21">
-        <f>IF(J44="","",J44*AB44)</f>
-        <v/>
-      </c>
-      <c r="AD44" s="19" t="n"/>
+      <c r="AB44" s="19" t="n"/>
+      <c r="AC44" s="20" t="n"/>
+      <c r="AD44" s="21">
+        <f>IF(J44="","",J44*AC44)</f>
+        <v/>
+      </c>
       <c r="AE44" s="19" t="n"/>
       <c r="AF44" s="19" t="n"/>
       <c r="AG44" s="19" t="n"/>
       <c r="AH44" s="19" t="n"/>
       <c r="AI44" s="19" t="n"/>
-      <c r="AJ44" s="16" t="inlineStr">
+      <c r="AJ44" s="19" t="n"/>
+      <c r="AK44" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK44" s="22" t="n"/>
+      <c r="AL44" s="22" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
@@ -6417,23 +6473,24 @@
       </c>
       <c r="Z45" s="19" t="n"/>
       <c r="AA45" s="19" t="n"/>
-      <c r="AB45" s="20" t="n"/>
-      <c r="AC45" s="21">
-        <f>IF(J45="","",J45*AB45)</f>
-        <v/>
-      </c>
-      <c r="AD45" s="19" t="n"/>
+      <c r="AB45" s="19" t="n"/>
+      <c r="AC45" s="20" t="n"/>
+      <c r="AD45" s="21">
+        <f>IF(J45="","",J45*AC45)</f>
+        <v/>
+      </c>
       <c r="AE45" s="19" t="n"/>
       <c r="AF45" s="19" t="n"/>
       <c r="AG45" s="19" t="n"/>
       <c r="AH45" s="19" t="n"/>
       <c r="AI45" s="19" t="n"/>
-      <c r="AJ45" s="16" t="inlineStr">
+      <c r="AJ45" s="19" t="n"/>
+      <c r="AK45" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK45" s="22" t="n"/>
+      <c r="AL45" s="22" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
@@ -6533,23 +6590,24 @@
       </c>
       <c r="Z46" s="19" t="n"/>
       <c r="AA46" s="19" t="n"/>
-      <c r="AB46" s="20" t="n"/>
-      <c r="AC46" s="21">
-        <f>IF(J46="","",J46*AB46)</f>
-        <v/>
-      </c>
-      <c r="AD46" s="19" t="n"/>
+      <c r="AB46" s="19" t="n"/>
+      <c r="AC46" s="20" t="n"/>
+      <c r="AD46" s="21">
+        <f>IF(J46="","",J46*AC46)</f>
+        <v/>
+      </c>
       <c r="AE46" s="19" t="n"/>
       <c r="AF46" s="19" t="n"/>
       <c r="AG46" s="19" t="n"/>
       <c r="AH46" s="19" t="n"/>
       <c r="AI46" s="19" t="n"/>
-      <c r="AJ46" s="16" t="inlineStr">
+      <c r="AJ46" s="19" t="n"/>
+      <c r="AK46" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK46" s="22" t="n"/>
+      <c r="AL46" s="22" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
@@ -6649,23 +6707,24 @@
       </c>
       <c r="Z47" s="19" t="n"/>
       <c r="AA47" s="19" t="n"/>
-      <c r="AB47" s="20" t="n"/>
-      <c r="AC47" s="21">
-        <f>IF(J47="","",J47*AB47)</f>
-        <v/>
-      </c>
-      <c r="AD47" s="19" t="n"/>
+      <c r="AB47" s="19" t="n"/>
+      <c r="AC47" s="20" t="n"/>
+      <c r="AD47" s="21">
+        <f>IF(J47="","",J47*AC47)</f>
+        <v/>
+      </c>
       <c r="AE47" s="19" t="n"/>
       <c r="AF47" s="19" t="n"/>
       <c r="AG47" s="19" t="n"/>
       <c r="AH47" s="19" t="n"/>
       <c r="AI47" s="19" t="n"/>
-      <c r="AJ47" s="16" t="inlineStr">
+      <c r="AJ47" s="19" t="n"/>
+      <c r="AK47" s="16" t="inlineStr">
         <is>
           <t>3 Regale im Bild erkennbar</t>
         </is>
       </c>
-      <c r="AK47" s="22" t="n"/>
+      <c r="AL47" s="22" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="15" t="inlineStr">
@@ -6765,23 +6824,24 @@
       </c>
       <c r="Z48" s="19" t="n"/>
       <c r="AA48" s="19" t="n"/>
-      <c r="AB48" s="20" t="n"/>
-      <c r="AC48" s="21">
-        <f>IF(J48="","",J48*AB48)</f>
-        <v/>
-      </c>
-      <c r="AD48" s="19" t="n"/>
+      <c r="AB48" s="19" t="n"/>
+      <c r="AC48" s="20" t="n"/>
+      <c r="AD48" s="21">
+        <f>IF(J48="","",J48*AC48)</f>
+        <v/>
+      </c>
       <c r="AE48" s="19" t="n"/>
       <c r="AF48" s="19" t="n"/>
       <c r="AG48" s="19" t="n"/>
       <c r="AH48" s="19" t="n"/>
       <c r="AI48" s="19" t="n"/>
-      <c r="AJ48" s="16" t="inlineStr">
+      <c r="AJ48" s="19" t="n"/>
+      <c r="AK48" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK48" s="22" t="n"/>
+      <c r="AL48" s="22" t="n"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
@@ -6881,23 +6941,24 @@
       </c>
       <c r="Z49" s="19" t="n"/>
       <c r="AA49" s="19" t="n"/>
-      <c r="AB49" s="20" t="n"/>
-      <c r="AC49" s="21">
-        <f>IF(J49="","",J49*AB49)</f>
-        <v/>
-      </c>
-      <c r="AD49" s="19" t="n"/>
+      <c r="AB49" s="19" t="n"/>
+      <c r="AC49" s="20" t="n"/>
+      <c r="AD49" s="21">
+        <f>IF(J49="","",J49*AC49)</f>
+        <v/>
+      </c>
       <c r="AE49" s="19" t="n"/>
       <c r="AF49" s="19" t="n"/>
       <c r="AG49" s="19" t="n"/>
       <c r="AH49" s="19" t="n"/>
       <c r="AI49" s="19" t="n"/>
-      <c r="AJ49" s="16" t="inlineStr">
+      <c r="AJ49" s="19" t="n"/>
+      <c r="AK49" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK49" s="22" t="n"/>
+      <c r="AL49" s="22" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="15" t="inlineStr">
@@ -6997,23 +7058,24 @@
       </c>
       <c r="Z50" s="19" t="n"/>
       <c r="AA50" s="19" t="n"/>
-      <c r="AB50" s="20" t="n"/>
-      <c r="AC50" s="21">
-        <f>IF(J50="","",J50*AB50)</f>
-        <v/>
-      </c>
-      <c r="AD50" s="19" t="n"/>
+      <c r="AB50" s="19" t="n"/>
+      <c r="AC50" s="20" t="n"/>
+      <c r="AD50" s="21">
+        <f>IF(J50="","",J50*AC50)</f>
+        <v/>
+      </c>
       <c r="AE50" s="19" t="n"/>
       <c r="AF50" s="19" t="n"/>
       <c r="AG50" s="19" t="n"/>
       <c r="AH50" s="19" t="n"/>
       <c r="AI50" s="19" t="n"/>
-      <c r="AJ50" s="16" t="inlineStr">
+      <c r="AJ50" s="19" t="n"/>
+      <c r="AK50" s="16" t="inlineStr">
         <is>
           <t>2 Bilder im Bild</t>
         </is>
       </c>
-      <c r="AK50" s="22" t="n"/>
+      <c r="AL50" s="22" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
@@ -7113,23 +7175,24 @@
       </c>
       <c r="Z51" s="19" t="n"/>
       <c r="AA51" s="19" t="n"/>
-      <c r="AB51" s="20" t="n"/>
-      <c r="AC51" s="21">
-        <f>IF(J51="","",J51*AB51)</f>
-        <v/>
-      </c>
-      <c r="AD51" s="19" t="n"/>
+      <c r="AB51" s="19" t="n"/>
+      <c r="AC51" s="20" t="n"/>
+      <c r="AD51" s="21">
+        <f>IF(J51="","",J51*AC51)</f>
+        <v/>
+      </c>
       <c r="AE51" s="19" t="n"/>
       <c r="AF51" s="19" t="n"/>
       <c r="AG51" s="19" t="n"/>
       <c r="AH51" s="19" t="n"/>
       <c r="AI51" s="19" t="n"/>
-      <c r="AJ51" s="16" t="inlineStr">
+      <c r="AJ51" s="19" t="n"/>
+      <c r="AK51" s="16" t="inlineStr">
         <is>
           <t>1 Set im Bild</t>
         </is>
       </c>
-      <c r="AK51" s="22" t="n"/>
+      <c r="AL51" s="22" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="15" t="inlineStr">
@@ -7229,23 +7292,24 @@
       </c>
       <c r="Z52" s="19" t="n"/>
       <c r="AA52" s="19" t="n"/>
-      <c r="AB52" s="20" t="n"/>
-      <c r="AC52" s="21">
-        <f>IF(J52="","",J52*AB52)</f>
-        <v/>
-      </c>
-      <c r="AD52" s="19" t="n"/>
+      <c r="AB52" s="19" t="n"/>
+      <c r="AC52" s="20" t="n"/>
+      <c r="AD52" s="21">
+        <f>IF(J52="","",J52*AC52)</f>
+        <v/>
+      </c>
       <c r="AE52" s="19" t="n"/>
       <c r="AF52" s="19" t="n"/>
       <c r="AG52" s="19" t="n"/>
       <c r="AH52" s="19" t="n"/>
       <c r="AI52" s="19" t="n"/>
-      <c r="AJ52" s="16" t="inlineStr">
+      <c r="AJ52" s="19" t="n"/>
+      <c r="AK52" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AK52" s="22" t="n"/>
+      <c r="AL52" s="22" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
@@ -7345,23 +7409,24 @@
       </c>
       <c r="Z53" s="19" t="n"/>
       <c r="AA53" s="19" t="n"/>
-      <c r="AB53" s="20" t="n"/>
-      <c r="AC53" s="21">
-        <f>IF(J53="","",J53*AB53)</f>
-        <v/>
-      </c>
-      <c r="AD53" s="19" t="n"/>
+      <c r="AB53" s="19" t="n"/>
+      <c r="AC53" s="20" t="n"/>
+      <c r="AD53" s="21">
+        <f>IF(J53="","",J53*AC53)</f>
+        <v/>
+      </c>
       <c r="AE53" s="19" t="n"/>
       <c r="AF53" s="19" t="n"/>
       <c r="AG53" s="19" t="n"/>
       <c r="AH53" s="19" t="n"/>
       <c r="AI53" s="19" t="n"/>
-      <c r="AJ53" s="16" t="inlineStr">
+      <c r="AJ53" s="19" t="n"/>
+      <c r="AK53" s="16" t="inlineStr">
         <is>
           <t>ca. 6 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AK53" s="22" t="n"/>
+      <c r="AL53" s="22" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="15" t="inlineStr">
@@ -7461,23 +7526,24 @@
       </c>
       <c r="Z54" s="19" t="n"/>
       <c r="AA54" s="19" t="n"/>
-      <c r="AB54" s="20" t="n"/>
-      <c r="AC54" s="21">
-        <f>IF(J54="","",J54*AB54)</f>
-        <v/>
-      </c>
-      <c r="AD54" s="19" t="n"/>
+      <c r="AB54" s="19" t="n"/>
+      <c r="AC54" s="20" t="n"/>
+      <c r="AD54" s="21">
+        <f>IF(J54="","",J54*AC54)</f>
+        <v/>
+      </c>
       <c r="AE54" s="19" t="n"/>
       <c r="AF54" s="19" t="n"/>
       <c r="AG54" s="19" t="n"/>
       <c r="AH54" s="19" t="n"/>
       <c r="AI54" s="19" t="n"/>
-      <c r="AJ54" s="16" t="inlineStr">
+      <c r="AJ54" s="19" t="n"/>
+      <c r="AK54" s="16" t="inlineStr">
         <is>
           <t>ca. 8 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AK54" s="22" t="n"/>
+      <c r="AL54" s="22" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
@@ -7577,23 +7643,24 @@
       </c>
       <c r="Z55" s="19" t="n"/>
       <c r="AA55" s="19" t="n"/>
-      <c r="AB55" s="20" t="n"/>
-      <c r="AC55" s="21">
-        <f>IF(J55="","",J55*AB55)</f>
-        <v/>
-      </c>
-      <c r="AD55" s="19" t="n"/>
+      <c r="AB55" s="19" t="n"/>
+      <c r="AC55" s="20" t="n"/>
+      <c r="AD55" s="21">
+        <f>IF(J55="","",J55*AC55)</f>
+        <v/>
+      </c>
       <c r="AE55" s="19" t="n"/>
       <c r="AF55" s="19" t="n"/>
       <c r="AG55" s="19" t="n"/>
       <c r="AH55" s="19" t="n"/>
       <c r="AI55" s="19" t="n"/>
-      <c r="AJ55" s="16" t="inlineStr">
+      <c r="AJ55" s="19" t="n"/>
+      <c r="AK55" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK55" s="22" t="n"/>
+      <c r="AL55" s="22" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
@@ -7693,23 +7760,24 @@
       </c>
       <c r="Z56" s="19" t="n"/>
       <c r="AA56" s="19" t="n"/>
-      <c r="AB56" s="20" t="n"/>
-      <c r="AC56" s="21">
-        <f>IF(J56="","",J56*AB56)</f>
-        <v/>
-      </c>
-      <c r="AD56" s="19" t="n"/>
+      <c r="AB56" s="19" t="n"/>
+      <c r="AC56" s="20" t="n"/>
+      <c r="AD56" s="21">
+        <f>IF(J56="","",J56*AC56)</f>
+        <v/>
+      </c>
       <c r="AE56" s="19" t="n"/>
       <c r="AF56" s="19" t="n"/>
       <c r="AG56" s="19" t="n"/>
       <c r="AH56" s="19" t="n"/>
       <c r="AI56" s="19" t="n"/>
-      <c r="AJ56" s="16" t="inlineStr">
+      <c r="AJ56" s="19" t="n"/>
+      <c r="AK56" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK56" s="22" t="n"/>
+      <c r="AL56" s="22" t="n"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
@@ -7809,23 +7877,24 @@
       </c>
       <c r="Z57" s="19" t="n"/>
       <c r="AA57" s="19" t="n"/>
-      <c r="AB57" s="20" t="n"/>
-      <c r="AC57" s="21">
-        <f>IF(J57="","",J57*AB57)</f>
-        <v/>
-      </c>
-      <c r="AD57" s="19" t="n"/>
+      <c r="AB57" s="19" t="n"/>
+      <c r="AC57" s="20" t="n"/>
+      <c r="AD57" s="21">
+        <f>IF(J57="","",J57*AC57)</f>
+        <v/>
+      </c>
       <c r="AE57" s="19" t="n"/>
       <c r="AF57" s="19" t="n"/>
       <c r="AG57" s="19" t="n"/>
       <c r="AH57" s="19" t="n"/>
       <c r="AI57" s="19" t="n"/>
-      <c r="AJ57" s="16" t="inlineStr">
+      <c r="AJ57" s="19" t="n"/>
+      <c r="AK57" s="16" t="inlineStr">
         <is>
           <t>1 Schrank im Bild (Bücher nicht enthalten)</t>
         </is>
       </c>
-      <c r="AK57" s="22" t="n"/>
+      <c r="AL57" s="22" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
@@ -7925,23 +7994,24 @@
       </c>
       <c r="Z58" s="19" t="n"/>
       <c r="AA58" s="19" t="n"/>
-      <c r="AB58" s="20" t="n"/>
-      <c r="AC58" s="21">
-        <f>IF(J58="","",J58*AB58)</f>
-        <v/>
-      </c>
-      <c r="AD58" s="19" t="n"/>
+      <c r="AB58" s="19" t="n"/>
+      <c r="AC58" s="20" t="n"/>
+      <c r="AD58" s="21">
+        <f>IF(J58="","",J58*AC58)</f>
+        <v/>
+      </c>
       <c r="AE58" s="19" t="n"/>
       <c r="AF58" s="19" t="n"/>
       <c r="AG58" s="19" t="n"/>
       <c r="AH58" s="19" t="n"/>
       <c r="AI58" s="19" t="n"/>
-      <c r="AJ58" s="16" t="inlineStr">
+      <c r="AJ58" s="19" t="n"/>
+      <c r="AK58" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK58" s="22" t="n"/>
+      <c r="AL58" s="22" t="n"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
@@ -8041,23 +8111,24 @@
       </c>
       <c r="Z59" s="19" t="n"/>
       <c r="AA59" s="19" t="n"/>
-      <c r="AB59" s="20" t="n"/>
-      <c r="AC59" s="21">
-        <f>IF(J59="","",J59*AB59)</f>
-        <v/>
-      </c>
-      <c r="AD59" s="19" t="n"/>
+      <c r="AB59" s="19" t="n"/>
+      <c r="AC59" s="20" t="n"/>
+      <c r="AD59" s="21">
+        <f>IF(J59="","",J59*AC59)</f>
+        <v/>
+      </c>
       <c r="AE59" s="19" t="n"/>
       <c r="AF59" s="19" t="n"/>
       <c r="AG59" s="19" t="n"/>
       <c r="AH59" s="19" t="n"/>
       <c r="AI59" s="19" t="n"/>
-      <c r="AJ59" s="16" t="inlineStr">
+      <c r="AJ59" s="19" t="n"/>
+      <c r="AK59" s="16" t="inlineStr">
         <is>
           <t>2 Regale im Bild</t>
         </is>
       </c>
-      <c r="AK59" s="22" t="n"/>
+      <c r="AL59" s="22" t="n"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="15" t="inlineStr">
@@ -8157,23 +8228,24 @@
       </c>
       <c r="Z60" s="19" t="n"/>
       <c r="AA60" s="19" t="n"/>
-      <c r="AB60" s="20" t="n"/>
-      <c r="AC60" s="21">
-        <f>IF(J60="","",J60*AB60)</f>
-        <v/>
-      </c>
-      <c r="AD60" s="19" t="n"/>
+      <c r="AB60" s="19" t="n"/>
+      <c r="AC60" s="20" t="n"/>
+      <c r="AD60" s="21">
+        <f>IF(J60="","",J60*AC60)</f>
+        <v/>
+      </c>
       <c r="AE60" s="19" t="n"/>
       <c r="AF60" s="19" t="n"/>
       <c r="AG60" s="19" t="n"/>
       <c r="AH60" s="19" t="n"/>
       <c r="AI60" s="19" t="n"/>
-      <c r="AJ60" s="16" t="inlineStr">
+      <c r="AJ60" s="19" t="n"/>
+      <c r="AK60" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK60" s="22" t="n"/>
+      <c r="AL60" s="22" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
@@ -8273,23 +8345,24 @@
       </c>
       <c r="Z61" s="19" t="n"/>
       <c r="AA61" s="19" t="n"/>
-      <c r="AB61" s="20" t="n"/>
-      <c r="AC61" s="21">
-        <f>IF(J61="","",J61*AB61)</f>
-        <v/>
-      </c>
-      <c r="AD61" s="19" t="n"/>
+      <c r="AB61" s="19" t="n"/>
+      <c r="AC61" s="20" t="n"/>
+      <c r="AD61" s="21">
+        <f>IF(J61="","",J61*AC61)</f>
+        <v/>
+      </c>
       <c r="AE61" s="19" t="n"/>
       <c r="AF61" s="19" t="n"/>
       <c r="AG61" s="19" t="n"/>
       <c r="AH61" s="19" t="n"/>
       <c r="AI61" s="19" t="n"/>
-      <c r="AJ61" s="16" t="inlineStr">
+      <c r="AJ61" s="19" t="n"/>
+      <c r="AK61" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK61" s="22" t="n"/>
+      <c r="AL61" s="22" t="n"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="15" t="inlineStr">
@@ -8389,23 +8462,24 @@
       </c>
       <c r="Z62" s="19" t="n"/>
       <c r="AA62" s="19" t="n"/>
-      <c r="AB62" s="20" t="n"/>
-      <c r="AC62" s="21">
-        <f>IF(J62="","",J62*AB62)</f>
-        <v/>
-      </c>
-      <c r="AD62" s="19" t="n"/>
+      <c r="AB62" s="19" t="n"/>
+      <c r="AC62" s="20" t="n"/>
+      <c r="AD62" s="21">
+        <f>IF(J62="","",J62*AC62)</f>
+        <v/>
+      </c>
       <c r="AE62" s="19" t="n"/>
       <c r="AF62" s="19" t="n"/>
       <c r="AG62" s="19" t="n"/>
       <c r="AH62" s="19" t="n"/>
       <c r="AI62" s="19" t="n"/>
-      <c r="AJ62" s="16" t="inlineStr">
+      <c r="AJ62" s="19" t="n"/>
+      <c r="AK62" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK62" s="22" t="n"/>
+      <c r="AL62" s="22" t="n"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
@@ -8505,23 +8579,24 @@
       </c>
       <c r="Z63" s="19" t="n"/>
       <c r="AA63" s="19" t="n"/>
-      <c r="AB63" s="20" t="n"/>
-      <c r="AC63" s="21">
-        <f>IF(J63="","",J63*AB63)</f>
-        <v/>
-      </c>
-      <c r="AD63" s="19" t="n"/>
+      <c r="AB63" s="19" t="n"/>
+      <c r="AC63" s="20" t="n"/>
+      <c r="AD63" s="21">
+        <f>IF(J63="","",J63*AC63)</f>
+        <v/>
+      </c>
       <c r="AE63" s="19" t="n"/>
       <c r="AF63" s="19" t="n"/>
       <c r="AG63" s="19" t="n"/>
       <c r="AH63" s="19" t="n"/>
       <c r="AI63" s="19" t="n"/>
-      <c r="AJ63" s="16" t="inlineStr">
+      <c r="AJ63" s="19" t="n"/>
+      <c r="AK63" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK63" s="22" t="n"/>
+      <c r="AL63" s="22" t="n"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="15" t="inlineStr">
@@ -8621,23 +8696,24 @@
       </c>
       <c r="Z64" s="19" t="n"/>
       <c r="AA64" s="19" t="n"/>
-      <c r="AB64" s="20" t="n"/>
-      <c r="AC64" s="21">
-        <f>IF(J64="","",J64*AB64)</f>
-        <v/>
-      </c>
-      <c r="AD64" s="19" t="n"/>
+      <c r="AB64" s="19" t="n"/>
+      <c r="AC64" s="20" t="n"/>
+      <c r="AD64" s="21">
+        <f>IF(J64="","",J64*AC64)</f>
+        <v/>
+      </c>
       <c r="AE64" s="19" t="n"/>
       <c r="AF64" s="19" t="n"/>
       <c r="AG64" s="19" t="n"/>
       <c r="AH64" s="19" t="n"/>
       <c r="AI64" s="19" t="n"/>
-      <c r="AJ64" s="16" t="inlineStr">
+      <c r="AJ64" s="19" t="n"/>
+      <c r="AK64" s="16" t="inlineStr">
         <is>
           <t>ca. 8 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AK64" s="22" t="n"/>
+      <c r="AL64" s="22" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
@@ -8737,23 +8813,24 @@
       </c>
       <c r="Z65" s="19" t="n"/>
       <c r="AA65" s="19" t="n"/>
-      <c r="AB65" s="20" t="n"/>
-      <c r="AC65" s="21">
-        <f>IF(J65="","",J65*AB65)</f>
-        <v/>
-      </c>
-      <c r="AD65" s="19" t="n"/>
+      <c r="AB65" s="19" t="n"/>
+      <c r="AC65" s="20" t="n"/>
+      <c r="AD65" s="21">
+        <f>IF(J65="","",J65*AC65)</f>
+        <v/>
+      </c>
       <c r="AE65" s="19" t="n"/>
       <c r="AF65" s="19" t="n"/>
       <c r="AG65" s="19" t="n"/>
       <c r="AH65" s="19" t="n"/>
       <c r="AI65" s="19" t="n"/>
-      <c r="AJ65" s="16" t="inlineStr">
+      <c r="AJ65" s="19" t="n"/>
+      <c r="AK65" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK65" s="22" t="n"/>
+      <c r="AL65" s="22" t="n"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
@@ -8853,23 +8930,24 @@
       </c>
       <c r="Z66" s="19" t="n"/>
       <c r="AA66" s="19" t="n"/>
-      <c r="AB66" s="20" t="n"/>
-      <c r="AC66" s="21">
-        <f>IF(J66="","",J66*AB66)</f>
-        <v/>
-      </c>
-      <c r="AD66" s="19" t="n"/>
+      <c r="AB66" s="19" t="n"/>
+      <c r="AC66" s="20" t="n"/>
+      <c r="AD66" s="21">
+        <f>IF(J66="","",J66*AC66)</f>
+        <v/>
+      </c>
       <c r="AE66" s="19" t="n"/>
       <c r="AF66" s="19" t="n"/>
       <c r="AG66" s="19" t="n"/>
       <c r="AH66" s="19" t="n"/>
       <c r="AI66" s="19" t="n"/>
-      <c r="AJ66" s="16" t="inlineStr">
+      <c r="AJ66" s="19" t="n"/>
+      <c r="AK66" s="16" t="inlineStr">
         <is>
           <t>2 Schränke im Bild</t>
         </is>
       </c>
-      <c r="AK66" s="22" t="n"/>
+      <c r="AL66" s="22" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="15" t="inlineStr">
@@ -8969,23 +9047,24 @@
       </c>
       <c r="Z67" s="19" t="n"/>
       <c r="AA67" s="19" t="n"/>
-      <c r="AB67" s="20" t="n"/>
-      <c r="AC67" s="21">
-        <f>IF(J67="","",J67*AB67)</f>
-        <v/>
-      </c>
-      <c r="AD67" s="19" t="n"/>
+      <c r="AB67" s="19" t="n"/>
+      <c r="AC67" s="20" t="n"/>
+      <c r="AD67" s="21">
+        <f>IF(J67="","",J67*AC67)</f>
+        <v/>
+      </c>
       <c r="AE67" s="19" t="n"/>
       <c r="AF67" s="19" t="n"/>
       <c r="AG67" s="19" t="n"/>
       <c r="AH67" s="19" t="n"/>
       <c r="AI67" s="19" t="n"/>
-      <c r="AJ67" s="16" t="inlineStr">
+      <c r="AJ67" s="19" t="n"/>
+      <c r="AK67" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK67" s="22" t="n"/>
+      <c r="AL67" s="22" t="n"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="15" t="inlineStr">
@@ -9085,23 +9164,24 @@
       </c>
       <c r="Z68" s="19" t="n"/>
       <c r="AA68" s="19" t="n"/>
-      <c r="AB68" s="20" t="n"/>
-      <c r="AC68" s="21">
-        <f>IF(J68="","",J68*AB68)</f>
-        <v/>
-      </c>
-      <c r="AD68" s="19" t="n"/>
+      <c r="AB68" s="19" t="n"/>
+      <c r="AC68" s="20" t="n"/>
+      <c r="AD68" s="21">
+        <f>IF(J68="","",J68*AC68)</f>
+        <v/>
+      </c>
       <c r="AE68" s="19" t="n"/>
       <c r="AF68" s="19" t="n"/>
       <c r="AG68" s="19" t="n"/>
       <c r="AH68" s="19" t="n"/>
       <c r="AI68" s="19" t="n"/>
-      <c r="AJ68" s="16" t="inlineStr">
+      <c r="AJ68" s="19" t="n"/>
+      <c r="AK68" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK68" s="22" t="n"/>
+      <c r="AL68" s="22" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
@@ -9201,23 +9281,24 @@
       </c>
       <c r="Z69" s="19" t="n"/>
       <c r="AA69" s="19" t="n"/>
-      <c r="AB69" s="20" t="n"/>
-      <c r="AC69" s="21">
-        <f>IF(J69="","",J69*AB69)</f>
-        <v/>
-      </c>
-      <c r="AD69" s="19" t="n"/>
+      <c r="AB69" s="19" t="n"/>
+      <c r="AC69" s="20" t="n"/>
+      <c r="AD69" s="21">
+        <f>IF(J69="","",J69*AC69)</f>
+        <v/>
+      </c>
       <c r="AE69" s="19" t="n"/>
       <c r="AF69" s="19" t="n"/>
       <c r="AG69" s="19" t="n"/>
       <c r="AH69" s="19" t="n"/>
       <c r="AI69" s="19" t="n"/>
-      <c r="AJ69" s="16" t="inlineStr">
+      <c r="AJ69" s="19" t="n"/>
+      <c r="AK69" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK69" s="22" t="n"/>
+      <c r="AL69" s="22" t="n"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="15" t="inlineStr">
@@ -9317,23 +9398,24 @@
       </c>
       <c r="Z70" s="19" t="n"/>
       <c r="AA70" s="19" t="n"/>
-      <c r="AB70" s="20" t="n"/>
-      <c r="AC70" s="21">
-        <f>IF(J70="","",J70*AB70)</f>
-        <v/>
-      </c>
-      <c r="AD70" s="19" t="n"/>
+      <c r="AB70" s="19" t="n"/>
+      <c r="AC70" s="20" t="n"/>
+      <c r="AD70" s="21">
+        <f>IF(J70="","",J70*AC70)</f>
+        <v/>
+      </c>
       <c r="AE70" s="19" t="n"/>
       <c r="AF70" s="19" t="n"/>
       <c r="AG70" s="19" t="n"/>
       <c r="AH70" s="19" t="n"/>
       <c r="AI70" s="19" t="n"/>
-      <c r="AJ70" s="16" t="inlineStr">
+      <c r="AJ70" s="19" t="n"/>
+      <c r="AK70" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK70" s="22" t="n"/>
+      <c r="AL70" s="22" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
@@ -9433,23 +9515,24 @@
       </c>
       <c r="Z71" s="19" t="n"/>
       <c r="AA71" s="19" t="n"/>
-      <c r="AB71" s="20" t="n"/>
-      <c r="AC71" s="21">
-        <f>IF(J71="","",J71*AB71)</f>
-        <v/>
-      </c>
-      <c r="AD71" s="19" t="n"/>
+      <c r="AB71" s="19" t="n"/>
+      <c r="AC71" s="20" t="n"/>
+      <c r="AD71" s="21">
+        <f>IF(J71="","",J71*AC71)</f>
+        <v/>
+      </c>
       <c r="AE71" s="19" t="n"/>
       <c r="AF71" s="19" t="n"/>
       <c r="AG71" s="19" t="n"/>
       <c r="AH71" s="19" t="n"/>
       <c r="AI71" s="19" t="n"/>
-      <c r="AJ71" s="16" t="inlineStr">
+      <c r="AJ71" s="19" t="n"/>
+      <c r="AK71" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild (ohne Treibholz)</t>
         </is>
       </c>
-      <c r="AK71" s="22" t="n"/>
+      <c r="AL71" s="22" t="n"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="15" t="inlineStr">
@@ -9549,23 +9632,24 @@
       </c>
       <c r="Z72" s="19" t="n"/>
       <c r="AA72" s="19" t="n"/>
-      <c r="AB72" s="20" t="n"/>
-      <c r="AC72" s="21">
-        <f>IF(J72="","",J72*AB72)</f>
-        <v/>
-      </c>
-      <c r="AD72" s="19" t="n"/>
+      <c r="AB72" s="19" t="n"/>
+      <c r="AC72" s="20" t="n"/>
+      <c r="AD72" s="21">
+        <f>IF(J72="","",J72*AC72)</f>
+        <v/>
+      </c>
       <c r="AE72" s="19" t="n"/>
       <c r="AF72" s="19" t="n"/>
       <c r="AG72" s="19" t="n"/>
       <c r="AH72" s="19" t="n"/>
       <c r="AI72" s="19" t="n"/>
-      <c r="AJ72" s="16" t="inlineStr">
+      <c r="AJ72" s="19" t="n"/>
+      <c r="AK72" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK72" s="22" t="n"/>
+      <c r="AL72" s="22" t="n"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
@@ -9665,23 +9749,24 @@
       </c>
       <c r="Z73" s="19" t="n"/>
       <c r="AA73" s="19" t="n"/>
-      <c r="AB73" s="20" t="n"/>
-      <c r="AC73" s="21">
-        <f>IF(J73="","",J73*AB73)</f>
-        <v/>
-      </c>
-      <c r="AD73" s="19" t="n"/>
+      <c r="AB73" s="19" t="n"/>
+      <c r="AC73" s="20" t="n"/>
+      <c r="AD73" s="21">
+        <f>IF(J73="","",J73*AC73)</f>
+        <v/>
+      </c>
       <c r="AE73" s="19" t="n"/>
       <c r="AF73" s="19" t="n"/>
       <c r="AG73" s="19" t="n"/>
       <c r="AH73" s="19" t="n"/>
       <c r="AI73" s="19" t="n"/>
-      <c r="AJ73" s="16" t="inlineStr">
+      <c r="AJ73" s="19" t="n"/>
+      <c r="AK73" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK73" s="22" t="n"/>
+      <c r="AL73" s="22" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="15" t="inlineStr">
@@ -9781,23 +9866,24 @@
       </c>
       <c r="Z74" s="19" t="n"/>
       <c r="AA74" s="19" t="n"/>
-      <c r="AB74" s="20" t="n"/>
-      <c r="AC74" s="21">
-        <f>IF(J74="","",J74*AB74)</f>
-        <v/>
-      </c>
-      <c r="AD74" s="19" t="n"/>
+      <c r="AB74" s="19" t="n"/>
+      <c r="AC74" s="20" t="n"/>
+      <c r="AD74" s="21">
+        <f>IF(J74="","",J74*AC74)</f>
+        <v/>
+      </c>
       <c r="AE74" s="19" t="n"/>
       <c r="AF74" s="19" t="n"/>
       <c r="AG74" s="19" t="n"/>
       <c r="AH74" s="19" t="n"/>
       <c r="AI74" s="19" t="n"/>
-      <c r="AJ74" s="16" t="inlineStr">
+      <c r="AJ74" s="19" t="n"/>
+      <c r="AK74" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK74" s="22" t="n"/>
+      <c r="AL74" s="22" t="n"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
@@ -9897,23 +9983,24 @@
       </c>
       <c r="Z75" s="19" t="n"/>
       <c r="AA75" s="19" t="n"/>
-      <c r="AB75" s="20" t="n"/>
-      <c r="AC75" s="21">
-        <f>IF(J75="","",J75*AB75)</f>
-        <v/>
-      </c>
-      <c r="AD75" s="19" t="n"/>
+      <c r="AB75" s="19" t="n"/>
+      <c r="AC75" s="20" t="n"/>
+      <c r="AD75" s="21">
+        <f>IF(J75="","",J75*AC75)</f>
+        <v/>
+      </c>
       <c r="AE75" s="19" t="n"/>
       <c r="AF75" s="19" t="n"/>
       <c r="AG75" s="19" t="n"/>
       <c r="AH75" s="19" t="n"/>
       <c r="AI75" s="19" t="n"/>
-      <c r="AJ75" s="16" t="inlineStr">
+      <c r="AJ75" s="19" t="n"/>
+      <c r="AK75" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK75" s="22" t="n"/>
+      <c r="AL75" s="22" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="15" t="inlineStr">
@@ -10013,23 +10100,24 @@
       </c>
       <c r="Z76" s="19" t="n"/>
       <c r="AA76" s="19" t="n"/>
-      <c r="AB76" s="20" t="n"/>
-      <c r="AC76" s="21">
-        <f>IF(J76="","",J76*AB76)</f>
-        <v/>
-      </c>
-      <c r="AD76" s="19" t="n"/>
+      <c r="AB76" s="19" t="n"/>
+      <c r="AC76" s="20" t="n"/>
+      <c r="AD76" s="21">
+        <f>IF(J76="","",J76*AC76)</f>
+        <v/>
+      </c>
       <c r="AE76" s="19" t="n"/>
       <c r="AF76" s="19" t="n"/>
       <c r="AG76" s="19" t="n"/>
       <c r="AH76" s="19" t="n"/>
       <c r="AI76" s="19" t="n"/>
-      <c r="AJ76" s="16" t="inlineStr">
+      <c r="AJ76" s="19" t="n"/>
+      <c r="AK76" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AK76" s="22" t="n"/>
+      <c r="AL76" s="22" t="n"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
@@ -10129,23 +10217,24 @@
       </c>
       <c r="Z77" s="19" t="n"/>
       <c r="AA77" s="19" t="n"/>
-      <c r="AB77" s="20" t="n"/>
-      <c r="AC77" s="21">
-        <f>IF(J77="","",J77*AB77)</f>
-        <v/>
-      </c>
-      <c r="AD77" s="19" t="n"/>
+      <c r="AB77" s="19" t="n"/>
+      <c r="AC77" s="20" t="n"/>
+      <c r="AD77" s="21">
+        <f>IF(J77="","",J77*AC77)</f>
+        <v/>
+      </c>
       <c r="AE77" s="19" t="n"/>
       <c r="AF77" s="19" t="n"/>
       <c r="AG77" s="19" t="n"/>
       <c r="AH77" s="19" t="n"/>
       <c r="AI77" s="19" t="n"/>
-      <c r="AJ77" s="16" t="inlineStr">
+      <c r="AJ77" s="19" t="n"/>
+      <c r="AK77" s="16" t="inlineStr">
         <is>
           <t>1 Leuchte im Bild</t>
         </is>
       </c>
-      <c r="AK77" s="22" t="n"/>
+      <c r="AL77" s="22" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="15" t="inlineStr">
@@ -10245,23 +10334,24 @@
       </c>
       <c r="Z78" s="19" t="n"/>
       <c r="AA78" s="19" t="n"/>
-      <c r="AB78" s="20" t="n"/>
-      <c r="AC78" s="21">
-        <f>IF(J78="","",J78*AB78)</f>
-        <v/>
-      </c>
-      <c r="AD78" s="19" t="n"/>
+      <c r="AB78" s="19" t="n"/>
+      <c r="AC78" s="20" t="n"/>
+      <c r="AD78" s="21">
+        <f>IF(J78="","",J78*AC78)</f>
+        <v/>
+      </c>
       <c r="AE78" s="19" t="n"/>
       <c r="AF78" s="19" t="n"/>
       <c r="AG78" s="19" t="n"/>
       <c r="AH78" s="19" t="n"/>
       <c r="AI78" s="19" t="n"/>
-      <c r="AJ78" s="16" t="inlineStr">
+      <c r="AJ78" s="19" t="n"/>
+      <c r="AK78" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK78" s="22" t="n"/>
+      <c r="AL78" s="22" t="n"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
@@ -10361,23 +10451,24 @@
       </c>
       <c r="Z79" s="19" t="n"/>
       <c r="AA79" s="19" t="n"/>
-      <c r="AB79" s="20" t="n"/>
-      <c r="AC79" s="21">
-        <f>IF(J79="","",J79*AB79)</f>
-        <v/>
-      </c>
-      <c r="AD79" s="19" t="n"/>
+      <c r="AB79" s="19" t="n"/>
+      <c r="AC79" s="20" t="n"/>
+      <c r="AD79" s="21">
+        <f>IF(J79="","",J79*AC79)</f>
+        <v/>
+      </c>
       <c r="AE79" s="19" t="n"/>
       <c r="AF79" s="19" t="n"/>
       <c r="AG79" s="19" t="n"/>
       <c r="AH79" s="19" t="n"/>
       <c r="AI79" s="19" t="n"/>
-      <c r="AJ79" s="16" t="inlineStr">
+      <c r="AJ79" s="19" t="n"/>
+      <c r="AK79" s="16" t="inlineStr">
         <is>
           <t>1 Sessel im Bild</t>
         </is>
       </c>
-      <c r="AK79" s="22" t="n"/>
+      <c r="AL79" s="22" t="n"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
@@ -10477,23 +10568,24 @@
       </c>
       <c r="Z80" s="19" t="n"/>
       <c r="AA80" s="19" t="n"/>
-      <c r="AB80" s="20" t="n"/>
-      <c r="AC80" s="21">
-        <f>IF(J80="","",J80*AB80)</f>
-        <v/>
-      </c>
-      <c r="AD80" s="19" t="n"/>
+      <c r="AB80" s="19" t="n"/>
+      <c r="AC80" s="20" t="n"/>
+      <c r="AD80" s="21">
+        <f>IF(J80="","",J80*AC80)</f>
+        <v/>
+      </c>
       <c r="AE80" s="19" t="n"/>
       <c r="AF80" s="19" t="n"/>
       <c r="AG80" s="19" t="n"/>
       <c r="AH80" s="19" t="n"/>
       <c r="AI80" s="19" t="n"/>
-      <c r="AJ80" s="16" t="inlineStr">
+      <c r="AJ80" s="19" t="n"/>
+      <c r="AK80" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK80" s="22" t="n"/>
+      <c r="AL80" s="22" t="n"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
@@ -10593,23 +10685,24 @@
       </c>
       <c r="Z81" s="19" t="n"/>
       <c r="AA81" s="19" t="n"/>
-      <c r="AB81" s="20" t="n"/>
-      <c r="AC81" s="21">
-        <f>IF(J81="","",J81*AB81)</f>
-        <v/>
-      </c>
-      <c r="AD81" s="19" t="n"/>
+      <c r="AB81" s="19" t="n"/>
+      <c r="AC81" s="20" t="n"/>
+      <c r="AD81" s="21">
+        <f>IF(J81="","",J81*AC81)</f>
+        <v/>
+      </c>
       <c r="AE81" s="19" t="n"/>
       <c r="AF81" s="19" t="n"/>
       <c r="AG81" s="19" t="n"/>
       <c r="AH81" s="19" t="n"/>
       <c r="AI81" s="19" t="n"/>
-      <c r="AJ81" s="16" t="inlineStr">
+      <c r="AJ81" s="19" t="n"/>
+      <c r="AK81" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK81" s="22" t="n"/>
+      <c r="AL81" s="22" t="n"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
@@ -10709,23 +10802,24 @@
       </c>
       <c r="Z82" s="19" t="n"/>
       <c r="AA82" s="19" t="n"/>
-      <c r="AB82" s="20" t="n"/>
-      <c r="AC82" s="21">
-        <f>IF(J82="","",J82*AB82)</f>
-        <v/>
-      </c>
-      <c r="AD82" s="19" t="n"/>
+      <c r="AB82" s="19" t="n"/>
+      <c r="AC82" s="20" t="n"/>
+      <c r="AD82" s="21">
+        <f>IF(J82="","",J82*AC82)</f>
+        <v/>
+      </c>
       <c r="AE82" s="19" t="n"/>
       <c r="AF82" s="19" t="n"/>
       <c r="AG82" s="19" t="n"/>
       <c r="AH82" s="19" t="n"/>
       <c r="AI82" s="19" t="n"/>
-      <c r="AJ82" s="16" t="inlineStr">
+      <c r="AJ82" s="19" t="n"/>
+      <c r="AK82" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK82" s="22" t="n"/>
+      <c r="AL82" s="22" t="n"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
@@ -10825,23 +10919,24 @@
       </c>
       <c r="Z83" s="19" t="n"/>
       <c r="AA83" s="19" t="n"/>
-      <c r="AB83" s="20" t="n"/>
-      <c r="AC83" s="21">
-        <f>IF(J83="","",J83*AB83)</f>
-        <v/>
-      </c>
-      <c r="AD83" s="19" t="n"/>
+      <c r="AB83" s="19" t="n"/>
+      <c r="AC83" s="20" t="n"/>
+      <c r="AD83" s="21">
+        <f>IF(J83="","",J83*AC83)</f>
+        <v/>
+      </c>
       <c r="AE83" s="19" t="n"/>
       <c r="AF83" s="19" t="n"/>
       <c r="AG83" s="19" t="n"/>
       <c r="AH83" s="19" t="n"/>
       <c r="AI83" s="19" t="n"/>
-      <c r="AJ83" s="16" t="inlineStr">
+      <c r="AJ83" s="19" t="n"/>
+      <c r="AK83" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK83" s="22" t="n"/>
+      <c r="AL83" s="22" t="n"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="15" t="inlineStr">
@@ -10941,23 +11036,24 @@
       </c>
       <c r="Z84" s="19" t="n"/>
       <c r="AA84" s="19" t="n"/>
-      <c r="AB84" s="20" t="n"/>
-      <c r="AC84" s="21">
-        <f>IF(J84="","",J84*AB84)</f>
-        <v/>
-      </c>
-      <c r="AD84" s="19" t="n"/>
+      <c r="AB84" s="19" t="n"/>
+      <c r="AC84" s="20" t="n"/>
+      <c r="AD84" s="21">
+        <f>IF(J84="","",J84*AC84)</f>
+        <v/>
+      </c>
       <c r="AE84" s="19" t="n"/>
       <c r="AF84" s="19" t="n"/>
       <c r="AG84" s="19" t="n"/>
       <c r="AH84" s="19" t="n"/>
       <c r="AI84" s="19" t="n"/>
-      <c r="AJ84" s="16" t="inlineStr">
+      <c r="AJ84" s="19" t="n"/>
+      <c r="AK84" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK84" s="22" t="n"/>
+      <c r="AL84" s="22" t="n"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
@@ -11057,23 +11153,24 @@
       </c>
       <c r="Z85" s="19" t="n"/>
       <c r="AA85" s="19" t="n"/>
-      <c r="AB85" s="20" t="n"/>
-      <c r="AC85" s="21">
-        <f>IF(J85="","",J85*AB85)</f>
-        <v/>
-      </c>
-      <c r="AD85" s="19" t="n"/>
+      <c r="AB85" s="19" t="n"/>
+      <c r="AC85" s="20" t="n"/>
+      <c r="AD85" s="21">
+        <f>IF(J85="","",J85*AC85)</f>
+        <v/>
+      </c>
       <c r="AE85" s="19" t="n"/>
       <c r="AF85" s="19" t="n"/>
       <c r="AG85" s="19" t="n"/>
       <c r="AH85" s="19" t="n"/>
       <c r="AI85" s="19" t="n"/>
-      <c r="AJ85" s="16" t="inlineStr">
+      <c r="AJ85" s="19" t="n"/>
+      <c r="AK85" s="16" t="inlineStr">
         <is>
           <t>1 Stuhl im Bild - vermutlich mehrere vorhanden</t>
         </is>
       </c>
-      <c r="AK85" s="22" t="n"/>
+      <c r="AL85" s="22" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="15" t="inlineStr">
@@ -11173,23 +11270,24 @@
       </c>
       <c r="Z86" s="19" t="n"/>
       <c r="AA86" s="19" t="n"/>
-      <c r="AB86" s="20" t="n"/>
-      <c r="AC86" s="21">
-        <f>IF(J86="","",J86*AB86)</f>
-        <v/>
-      </c>
-      <c r="AD86" s="19" t="n"/>
+      <c r="AB86" s="19" t="n"/>
+      <c r="AC86" s="20" t="n"/>
+      <c r="AD86" s="21">
+        <f>IF(J86="","",J86*AC86)</f>
+        <v/>
+      </c>
       <c r="AE86" s="19" t="n"/>
       <c r="AF86" s="19" t="n"/>
       <c r="AG86" s="19" t="n"/>
       <c r="AH86" s="19" t="n"/>
       <c r="AI86" s="19" t="n"/>
-      <c r="AJ86" s="16" t="inlineStr">
+      <c r="AJ86" s="19" t="n"/>
+      <c r="AK86" s="16" t="inlineStr">
         <is>
           <t>1 Box im Bild - bitte prüfen ob 2 oder 3 Boxen gesamt</t>
         </is>
       </c>
-      <c r="AK86" s="22" t="n"/>
+      <c r="AL86" s="22" t="n"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
@@ -11289,23 +11387,24 @@
       </c>
       <c r="Z87" s="19" t="n"/>
       <c r="AA87" s="19" t="n"/>
-      <c r="AB87" s="20" t="n"/>
-      <c r="AC87" s="21">
-        <f>IF(J87="","",J87*AB87)</f>
-        <v/>
-      </c>
-      <c r="AD87" s="19" t="n"/>
+      <c r="AB87" s="19" t="n"/>
+      <c r="AC87" s="20" t="n"/>
+      <c r="AD87" s="21">
+        <f>IF(J87="","",J87*AC87)</f>
+        <v/>
+      </c>
       <c r="AE87" s="19" t="n"/>
       <c r="AF87" s="19" t="n"/>
       <c r="AG87" s="19" t="n"/>
       <c r="AH87" s="19" t="n"/>
       <c r="AI87" s="19" t="n"/>
-      <c r="AJ87" s="16" t="inlineStr">
+      <c r="AJ87" s="19" t="n"/>
+      <c r="AK87" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK87" s="22" t="n"/>
+      <c r="AL87" s="22" t="n"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="15" t="inlineStr">
@@ -11405,23 +11504,24 @@
       </c>
       <c r="Z88" s="19" t="n"/>
       <c r="AA88" s="19" t="n"/>
-      <c r="AB88" s="20" t="n"/>
-      <c r="AC88" s="21">
-        <f>IF(J88="","",J88*AB88)</f>
-        <v/>
-      </c>
-      <c r="AD88" s="19" t="n"/>
+      <c r="AB88" s="19" t="n"/>
+      <c r="AC88" s="20" t="n"/>
+      <c r="AD88" s="21">
+        <f>IF(J88="","",J88*AC88)</f>
+        <v/>
+      </c>
       <c r="AE88" s="19" t="n"/>
       <c r="AF88" s="19" t="n"/>
       <c r="AG88" s="19" t="n"/>
       <c r="AH88" s="19" t="n"/>
       <c r="AI88" s="19" t="n"/>
-      <c r="AJ88" s="16" t="inlineStr">
+      <c r="AJ88" s="19" t="n"/>
+      <c r="AK88" s="16" t="inlineStr">
         <is>
           <t>1 Box im Bild</t>
         </is>
       </c>
-      <c r="AK88" s="22" t="n"/>
+      <c r="AL88" s="22" t="n"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
@@ -11521,23 +11621,24 @@
       </c>
       <c r="Z89" s="19" t="n"/>
       <c r="AA89" s="19" t="n"/>
-      <c r="AB89" s="20" t="n"/>
-      <c r="AC89" s="21">
-        <f>IF(J89="","",J89*AB89)</f>
-        <v/>
-      </c>
-      <c r="AD89" s="19" t="n"/>
+      <c r="AB89" s="19" t="n"/>
+      <c r="AC89" s="20" t="n"/>
+      <c r="AD89" s="21">
+        <f>IF(J89="","",J89*AC89)</f>
+        <v/>
+      </c>
       <c r="AE89" s="19" t="n"/>
       <c r="AF89" s="19" t="n"/>
       <c r="AG89" s="19" t="n"/>
       <c r="AH89" s="19" t="n"/>
       <c r="AI89" s="19" t="n"/>
-      <c r="AJ89" s="16" t="inlineStr">
+      <c r="AJ89" s="19" t="n"/>
+      <c r="AK89" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK89" s="22" t="n"/>
+      <c r="AL89" s="22" t="n"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="15" t="inlineStr">
@@ -11637,23 +11738,24 @@
       </c>
       <c r="Z90" s="19" t="n"/>
       <c r="AA90" s="19" t="n"/>
-      <c r="AB90" s="20" t="n"/>
-      <c r="AC90" s="21">
-        <f>IF(J90="","",J90*AB90)</f>
-        <v/>
-      </c>
-      <c r="AD90" s="19" t="n"/>
+      <c r="AB90" s="19" t="n"/>
+      <c r="AC90" s="20" t="n"/>
+      <c r="AD90" s="21">
+        <f>IF(J90="","",J90*AC90)</f>
+        <v/>
+      </c>
       <c r="AE90" s="19" t="n"/>
       <c r="AF90" s="19" t="n"/>
       <c r="AG90" s="19" t="n"/>
       <c r="AH90" s="19" t="n"/>
       <c r="AI90" s="19" t="n"/>
-      <c r="AJ90" s="16" t="inlineStr">
+      <c r="AJ90" s="19" t="n"/>
+      <c r="AK90" s="16" t="inlineStr">
         <is>
           <t>4 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK90" s="22" t="n"/>
+      <c r="AL90" s="22" t="n"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
@@ -11753,23 +11855,24 @@
       </c>
       <c r="Z91" s="19" t="n"/>
       <c r="AA91" s="19" t="n"/>
-      <c r="AB91" s="20" t="n"/>
-      <c r="AC91" s="21">
-        <f>IF(J91="","",J91*AB91)</f>
-        <v/>
-      </c>
-      <c r="AD91" s="19" t="n"/>
+      <c r="AB91" s="19" t="n"/>
+      <c r="AC91" s="20" t="n"/>
+      <c r="AD91" s="21">
+        <f>IF(J91="","",J91*AC91)</f>
+        <v/>
+      </c>
       <c r="AE91" s="19" t="n"/>
       <c r="AF91" s="19" t="n"/>
       <c r="AG91" s="19" t="n"/>
       <c r="AH91" s="19" t="n"/>
       <c r="AI91" s="19" t="n"/>
-      <c r="AJ91" s="16" t="inlineStr">
+      <c r="AJ91" s="19" t="n"/>
+      <c r="AK91" s="16" t="inlineStr">
         <is>
           <t>2 Stück gestapelt im Bild</t>
         </is>
       </c>
-      <c r="AK91" s="22" t="n"/>
+      <c r="AL91" s="22" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="15" t="inlineStr">
@@ -11869,23 +11972,24 @@
       </c>
       <c r="Z92" s="19" t="n"/>
       <c r="AA92" s="19" t="n"/>
-      <c r="AB92" s="20" t="n"/>
-      <c r="AC92" s="21">
-        <f>IF(J92="","",J92*AB92)</f>
-        <v/>
-      </c>
-      <c r="AD92" s="19" t="n"/>
+      <c r="AB92" s="19" t="n"/>
+      <c r="AC92" s="20" t="n"/>
+      <c r="AD92" s="21">
+        <f>IF(J92="","",J92*AC92)</f>
+        <v/>
+      </c>
       <c r="AE92" s="19" t="n"/>
       <c r="AF92" s="19" t="n"/>
       <c r="AG92" s="19" t="n"/>
       <c r="AH92" s="19" t="n"/>
       <c r="AI92" s="19" t="n"/>
-      <c r="AJ92" s="16" t="inlineStr">
+      <c r="AJ92" s="19" t="n"/>
+      <c r="AK92" s="16" t="inlineStr">
         <is>
           <t>1 Sessel im Bild</t>
         </is>
       </c>
-      <c r="AK92" s="22" t="n"/>
+      <c r="AL92" s="22" t="n"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
@@ -11985,23 +12089,24 @@
       </c>
       <c r="Z93" s="19" t="n"/>
       <c r="AA93" s="19" t="n"/>
-      <c r="AB93" s="20" t="n"/>
-      <c r="AC93" s="21">
-        <f>IF(J93="","",J93*AB93)</f>
-        <v/>
-      </c>
-      <c r="AD93" s="19" t="n"/>
+      <c r="AB93" s="19" t="n"/>
+      <c r="AC93" s="20" t="n"/>
+      <c r="AD93" s="21">
+        <f>IF(J93="","",J93*AC93)</f>
+        <v/>
+      </c>
       <c r="AE93" s="19" t="n"/>
       <c r="AF93" s="19" t="n"/>
       <c r="AG93" s="19" t="n"/>
       <c r="AH93" s="19" t="n"/>
       <c r="AI93" s="19" t="n"/>
-      <c r="AJ93" s="16" t="inlineStr">
+      <c r="AJ93" s="19" t="n"/>
+      <c r="AK93" s="16" t="inlineStr">
         <is>
           <t>ca. 3 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AK93" s="22" t="n"/>
+      <c r="AL93" s="22" t="n"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="15" t="inlineStr">
@@ -12101,23 +12206,24 @@
       </c>
       <c r="Z94" s="19" t="n"/>
       <c r="AA94" s="19" t="n"/>
-      <c r="AB94" s="20" t="n"/>
-      <c r="AC94" s="21">
-        <f>IF(J94="","",J94*AB94)</f>
-        <v/>
-      </c>
-      <c r="AD94" s="19" t="n"/>
+      <c r="AB94" s="19" t="n"/>
+      <c r="AC94" s="20" t="n"/>
+      <c r="AD94" s="21">
+        <f>IF(J94="","",J94*AC94)</f>
+        <v/>
+      </c>
       <c r="AE94" s="19" t="n"/>
       <c r="AF94" s="19" t="n"/>
       <c r="AG94" s="19" t="n"/>
       <c r="AH94" s="19" t="n"/>
       <c r="AI94" s="19" t="n"/>
-      <c r="AJ94" s="16" t="inlineStr">
+      <c r="AJ94" s="19" t="n"/>
+      <c r="AK94" s="16" t="inlineStr">
         <is>
           <t>ca. 6 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AK94" s="22" t="n"/>
+      <c r="AL94" s="22" t="n"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
@@ -12217,23 +12323,24 @@
       </c>
       <c r="Z95" s="19" t="n"/>
       <c r="AA95" s="19" t="n"/>
-      <c r="AB95" s="20" t="n"/>
-      <c r="AC95" s="21">
-        <f>IF(J95="","",J95*AB95)</f>
-        <v/>
-      </c>
-      <c r="AD95" s="19" t="n"/>
+      <c r="AB95" s="19" t="n"/>
+      <c r="AC95" s="20" t="n"/>
+      <c r="AD95" s="21">
+        <f>IF(J95="","",J95*AC95)</f>
+        <v/>
+      </c>
       <c r="AE95" s="19" t="n"/>
       <c r="AF95" s="19" t="n"/>
       <c r="AG95" s="19" t="n"/>
       <c r="AH95" s="19" t="n"/>
       <c r="AI95" s="19" t="n"/>
-      <c r="AJ95" s="16" t="inlineStr">
+      <c r="AJ95" s="19" t="n"/>
+      <c r="AK95" s="16" t="inlineStr">
         <is>
           <t>1 Tisch mit 2 Stühlen im Bild</t>
         </is>
       </c>
-      <c r="AK95" s="22" t="n"/>
+      <c r="AL95" s="22" t="n"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="15" t="inlineStr">
@@ -12337,23 +12444,24 @@
       </c>
       <c r="Z96" s="19" t="n"/>
       <c r="AA96" s="19" t="n"/>
-      <c r="AB96" s="20" t="n"/>
-      <c r="AC96" s="21">
-        <f>IF(J96="","",J96*AB96)</f>
-        <v/>
-      </c>
-      <c r="AD96" s="19" t="n"/>
+      <c r="AB96" s="19" t="n"/>
+      <c r="AC96" s="20" t="n"/>
+      <c r="AD96" s="21">
+        <f>IF(J96="","",J96*AC96)</f>
+        <v/>
+      </c>
       <c r="AE96" s="19" t="n"/>
       <c r="AF96" s="19" t="n"/>
       <c r="AG96" s="19" t="n"/>
       <c r="AH96" s="19" t="n"/>
       <c r="AI96" s="19" t="n"/>
-      <c r="AJ96" s="16" t="inlineStr">
+      <c r="AJ96" s="19" t="n"/>
+      <c r="AK96" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK96" s="22" t="n"/>
+      <c r="AL96" s="22" t="n"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="15" t="inlineStr">
@@ -12461,23 +12569,24 @@
       </c>
       <c r="Z97" s="19" t="n"/>
       <c r="AA97" s="19" t="n"/>
-      <c r="AB97" s="20" t="n"/>
-      <c r="AC97" s="21">
-        <f>IF(J97="","",J97*AB97)</f>
-        <v/>
-      </c>
-      <c r="AD97" s="19" t="n"/>
+      <c r="AB97" s="19" t="n"/>
+      <c r="AC97" s="20" t="n"/>
+      <c r="AD97" s="21">
+        <f>IF(J97="","",J97*AC97)</f>
+        <v/>
+      </c>
       <c r="AE97" s="19" t="n"/>
       <c r="AF97" s="19" t="n"/>
       <c r="AG97" s="19" t="n"/>
       <c r="AH97" s="19" t="n"/>
       <c r="AI97" s="19" t="n"/>
-      <c r="AJ97" s="16" t="inlineStr">
+      <c r="AJ97" s="19" t="n"/>
+      <c r="AK97" s="16" t="inlineStr">
         <is>
           <t>5 Rahmen im Bild</t>
         </is>
       </c>
-      <c r="AK97" s="22" t="n"/>
+      <c r="AL97" s="22" t="n"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="15" t="inlineStr">
@@ -12585,23 +12694,24 @@
       </c>
       <c r="Z98" s="19" t="n"/>
       <c r="AA98" s="19" t="n"/>
-      <c r="AB98" s="20" t="n"/>
-      <c r="AC98" s="21">
-        <f>IF(J98="","",J98*AB98)</f>
-        <v/>
-      </c>
-      <c r="AD98" s="19" t="n"/>
+      <c r="AB98" s="19" t="n"/>
+      <c r="AC98" s="20" t="n"/>
+      <c r="AD98" s="21">
+        <f>IF(J98="","",J98*AC98)</f>
+        <v/>
+      </c>
       <c r="AE98" s="19" t="n"/>
       <c r="AF98" s="19" t="n"/>
       <c r="AG98" s="19" t="n"/>
       <c r="AH98" s="19" t="n"/>
       <c r="AI98" s="19" t="n"/>
-      <c r="AJ98" s="16" t="inlineStr">
+      <c r="AJ98" s="19" t="n"/>
+      <c r="AK98" s="16" t="inlineStr">
         <is>
           <t>3 Rahmen im Bild</t>
         </is>
       </c>
-      <c r="AK98" s="22" t="n"/>
+      <c r="AL98" s="22" t="n"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="15" t="inlineStr">
@@ -12705,23 +12815,24 @@
       </c>
       <c r="Z99" s="19" t="n"/>
       <c r="AA99" s="19" t="n"/>
-      <c r="AB99" s="20" t="n"/>
-      <c r="AC99" s="21">
-        <f>IF(J99="","",J99*AB99)</f>
-        <v/>
-      </c>
-      <c r="AD99" s="19" t="n"/>
+      <c r="AB99" s="19" t="n"/>
+      <c r="AC99" s="20" t="n"/>
+      <c r="AD99" s="21">
+        <f>IF(J99="","",J99*AC99)</f>
+        <v/>
+      </c>
       <c r="AE99" s="19" t="n"/>
       <c r="AF99" s="19" t="n"/>
       <c r="AG99" s="19" t="n"/>
       <c r="AH99" s="19" t="n"/>
       <c r="AI99" s="19" t="n"/>
-      <c r="AJ99" s="16" t="inlineStr">
+      <c r="AJ99" s="19" t="n"/>
+      <c r="AK99" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK99" s="22" t="n"/>
+      <c r="AL99" s="22" t="n"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="15" t="inlineStr">
@@ -12825,23 +12936,24 @@
       </c>
       <c r="Z100" s="19" t="n"/>
       <c r="AA100" s="19" t="n"/>
-      <c r="AB100" s="20" t="n"/>
-      <c r="AC100" s="21">
-        <f>IF(J100="","",J100*AB100)</f>
-        <v/>
-      </c>
-      <c r="AD100" s="19" t="n"/>
+      <c r="AB100" s="19" t="n"/>
+      <c r="AC100" s="20" t="n"/>
+      <c r="AD100" s="21">
+        <f>IF(J100="","",J100*AC100)</f>
+        <v/>
+      </c>
       <c r="AE100" s="19" t="n"/>
       <c r="AF100" s="19" t="n"/>
       <c r="AG100" s="19" t="n"/>
       <c r="AH100" s="19" t="n"/>
       <c r="AI100" s="19" t="n"/>
-      <c r="AJ100" s="16" t="inlineStr">
+      <c r="AJ100" s="19" t="n"/>
+      <c r="AK100" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AK100" s="22" t="n"/>
+      <c r="AL100" s="22" t="n"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="15" t="inlineStr">
@@ -12945,23 +13057,24 @@
       </c>
       <c r="Z101" s="19" t="n"/>
       <c r="AA101" s="19" t="n"/>
-      <c r="AB101" s="20" t="n"/>
-      <c r="AC101" s="21">
-        <f>IF(J101="","",J101*AB101)</f>
-        <v/>
-      </c>
-      <c r="AD101" s="19" t="n"/>
+      <c r="AB101" s="19" t="n"/>
+      <c r="AC101" s="20" t="n"/>
+      <c r="AD101" s="21">
+        <f>IF(J101="","",J101*AC101)</f>
+        <v/>
+      </c>
       <c r="AE101" s="19" t="n"/>
       <c r="AF101" s="19" t="n"/>
       <c r="AG101" s="19" t="n"/>
       <c r="AH101" s="19" t="n"/>
       <c r="AI101" s="19" t="n"/>
-      <c r="AJ101" s="16" t="inlineStr">
+      <c r="AJ101" s="19" t="n"/>
+      <c r="AK101" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK101" s="22" t="n"/>
+      <c r="AL101" s="22" t="n"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="15" t="inlineStr">
@@ -13065,23 +13178,24 @@
       </c>
       <c r="Z102" s="19" t="n"/>
       <c r="AA102" s="19" t="n"/>
-      <c r="AB102" s="20" t="n"/>
-      <c r="AC102" s="21">
-        <f>IF(J102="","",J102*AB102)</f>
-        <v/>
-      </c>
-      <c r="AD102" s="19" t="n"/>
+      <c r="AB102" s="19" t="n"/>
+      <c r="AC102" s="20" t="n"/>
+      <c r="AD102" s="21">
+        <f>IF(J102="","",J102*AC102)</f>
+        <v/>
+      </c>
       <c r="AE102" s="19" t="n"/>
       <c r="AF102" s="19" t="n"/>
       <c r="AG102" s="19" t="n"/>
       <c r="AH102" s="19" t="n"/>
       <c r="AI102" s="19" t="n"/>
-      <c r="AJ102" s="16" t="inlineStr">
+      <c r="AJ102" s="19" t="n"/>
+      <c r="AK102" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK102" s="22" t="n"/>
+      <c r="AL102" s="22" t="n"/>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
@@ -13185,23 +13299,24 @@
       </c>
       <c r="Z103" s="19" t="n"/>
       <c r="AA103" s="19" t="n"/>
-      <c r="AB103" s="20" t="n"/>
-      <c r="AC103" s="21">
-        <f>IF(J103="","",J103*AB103)</f>
-        <v/>
-      </c>
-      <c r="AD103" s="19" t="n"/>
+      <c r="AB103" s="19" t="n"/>
+      <c r="AC103" s="20" t="n"/>
+      <c r="AD103" s="21">
+        <f>IF(J103="","",J103*AC103)</f>
+        <v/>
+      </c>
       <c r="AE103" s="19" t="n"/>
       <c r="AF103" s="19" t="n"/>
       <c r="AG103" s="19" t="n"/>
       <c r="AH103" s="19" t="n"/>
       <c r="AI103" s="19" t="n"/>
-      <c r="AJ103" s="16" t="inlineStr">
+      <c r="AJ103" s="19" t="n"/>
+      <c r="AK103" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AK103" s="22" t="n"/>
+      <c r="AL103" s="22" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="15" t="inlineStr">
@@ -13305,23 +13420,24 @@
       </c>
       <c r="Z104" s="19" t="n"/>
       <c r="AA104" s="19" t="n"/>
-      <c r="AB104" s="20" t="n"/>
-      <c r="AC104" s="21">
-        <f>IF(J104="","",J104*AB104)</f>
-        <v/>
-      </c>
-      <c r="AD104" s="19" t="n"/>
+      <c r="AB104" s="19" t="n"/>
+      <c r="AC104" s="20" t="n"/>
+      <c r="AD104" s="21">
+        <f>IF(J104="","",J104*AC104)</f>
+        <v/>
+      </c>
       <c r="AE104" s="19" t="n"/>
       <c r="AF104" s="19" t="n"/>
       <c r="AG104" s="19" t="n"/>
       <c r="AH104" s="19" t="n"/>
       <c r="AI104" s="19" t="n"/>
-      <c r="AJ104" s="16" t="inlineStr">
+      <c r="AJ104" s="19" t="n"/>
+      <c r="AK104" s="16" t="inlineStr">
         <is>
           <t>2 Stück (klein und groß)</t>
         </is>
       </c>
-      <c r="AK104" s="22" t="n"/>
+      <c r="AL104" s="22" t="n"/>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="15" t="inlineStr">
@@ -13425,23 +13541,24 @@
       </c>
       <c r="Z105" s="19" t="n"/>
       <c r="AA105" s="19" t="n"/>
-      <c r="AB105" s="20" t="n"/>
-      <c r="AC105" s="21">
-        <f>IF(J105="","",J105*AB105)</f>
-        <v/>
-      </c>
-      <c r="AD105" s="19" t="n"/>
+      <c r="AB105" s="19" t="n"/>
+      <c r="AC105" s="20" t="n"/>
+      <c r="AD105" s="21">
+        <f>IF(J105="","",J105*AC105)</f>
+        <v/>
+      </c>
       <c r="AE105" s="19" t="n"/>
       <c r="AF105" s="19" t="n"/>
       <c r="AG105" s="19" t="n"/>
       <c r="AH105" s="19" t="n"/>
       <c r="AI105" s="19" t="n"/>
-      <c r="AJ105" s="16" t="inlineStr">
+      <c r="AJ105" s="19" t="n"/>
+      <c r="AK105" s="16" t="inlineStr">
         <is>
           <t>2 Stück (zwei Fotos, klein und groß)</t>
         </is>
       </c>
-      <c r="AK105" s="22" t="n"/>
+      <c r="AL105" s="22" t="n"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="15" t="inlineStr">
@@ -13545,23 +13662,24 @@
       </c>
       <c r="Z106" s="19" t="n"/>
       <c r="AA106" s="19" t="n"/>
-      <c r="AB106" s="20" t="n"/>
-      <c r="AC106" s="21">
-        <f>IF(J106="","",J106*AB106)</f>
-        <v/>
-      </c>
-      <c r="AD106" s="19" t="n"/>
+      <c r="AB106" s="19" t="n"/>
+      <c r="AC106" s="20" t="n"/>
+      <c r="AD106" s="21">
+        <f>IF(J106="","",J106*AC106)</f>
+        <v/>
+      </c>
       <c r="AE106" s="19" t="n"/>
       <c r="AF106" s="19" t="n"/>
       <c r="AG106" s="19" t="n"/>
       <c r="AH106" s="19" t="n"/>
       <c r="AI106" s="19" t="n"/>
-      <c r="AJ106" s="16" t="inlineStr">
+      <c r="AJ106" s="19" t="n"/>
+      <c r="AK106" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK106" s="22" t="n"/>
+      <c r="AL106" s="22" t="n"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
@@ -13665,23 +13783,24 @@
       </c>
       <c r="Z107" s="19" t="n"/>
       <c r="AA107" s="19" t="n"/>
-      <c r="AB107" s="20" t="n"/>
-      <c r="AC107" s="21">
-        <f>IF(J107="","",J107*AB107)</f>
-        <v/>
-      </c>
-      <c r="AD107" s="19" t="n"/>
+      <c r="AB107" s="19" t="n"/>
+      <c r="AC107" s="20" t="n"/>
+      <c r="AD107" s="21">
+        <f>IF(J107="","",J107*AC107)</f>
+        <v/>
+      </c>
       <c r="AE107" s="19" t="n"/>
       <c r="AF107" s="19" t="n"/>
       <c r="AG107" s="19" t="n"/>
       <c r="AH107" s="19" t="n"/>
       <c r="AI107" s="19" t="n"/>
-      <c r="AJ107" s="16" t="inlineStr">
+      <c r="AJ107" s="19" t="n"/>
+      <c r="AK107" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK107" s="22" t="n"/>
+      <c r="AL107" s="22" t="n"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="15" t="inlineStr">
@@ -13785,23 +13904,24 @@
       </c>
       <c r="Z108" s="19" t="n"/>
       <c r="AA108" s="19" t="n"/>
-      <c r="AB108" s="20" t="n"/>
-      <c r="AC108" s="21">
-        <f>IF(J108="","",J108*AB108)</f>
-        <v/>
-      </c>
-      <c r="AD108" s="19" t="n"/>
+      <c r="AB108" s="19" t="n"/>
+      <c r="AC108" s="20" t="n"/>
+      <c r="AD108" s="21">
+        <f>IF(J108="","",J108*AC108)</f>
+        <v/>
+      </c>
       <c r="AE108" s="19" t="n"/>
       <c r="AF108" s="19" t="n"/>
       <c r="AG108" s="19" t="n"/>
       <c r="AH108" s="19" t="n"/>
       <c r="AI108" s="19" t="n"/>
-      <c r="AJ108" s="16" t="inlineStr">
+      <c r="AJ108" s="19" t="n"/>
+      <c r="AK108" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK108" s="22" t="n"/>
+      <c r="AL108" s="22" t="n"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="15" t="inlineStr">
@@ -13905,23 +14025,24 @@
       </c>
       <c r="Z109" s="19" t="n"/>
       <c r="AA109" s="19" t="n"/>
-      <c r="AB109" s="20" t="n"/>
-      <c r="AC109" s="21">
-        <f>IF(J109="","",J109*AB109)</f>
-        <v/>
-      </c>
-      <c r="AD109" s="19" t="n"/>
+      <c r="AB109" s="19" t="n"/>
+      <c r="AC109" s="20" t="n"/>
+      <c r="AD109" s="21">
+        <f>IF(J109="","",J109*AC109)</f>
+        <v/>
+      </c>
       <c r="AE109" s="19" t="n"/>
       <c r="AF109" s="19" t="n"/>
       <c r="AG109" s="19" t="n"/>
       <c r="AH109" s="19" t="n"/>
       <c r="AI109" s="19" t="n"/>
-      <c r="AJ109" s="16" t="inlineStr">
+      <c r="AJ109" s="19" t="n"/>
+      <c r="AK109" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK109" s="22" t="n"/>
+      <c r="AL109" s="22" t="n"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="15" t="inlineStr">
@@ -14025,23 +14146,24 @@
       </c>
       <c r="Z110" s="19" t="n"/>
       <c r="AA110" s="19" t="n"/>
-      <c r="AB110" s="20" t="n"/>
-      <c r="AC110" s="21">
-        <f>IF(J110="","",J110*AB110)</f>
-        <v/>
-      </c>
-      <c r="AD110" s="19" t="n"/>
+      <c r="AB110" s="19" t="n"/>
+      <c r="AC110" s="20" t="n"/>
+      <c r="AD110" s="21">
+        <f>IF(J110="","",J110*AC110)</f>
+        <v/>
+      </c>
       <c r="AE110" s="19" t="n"/>
       <c r="AF110" s="19" t="n"/>
       <c r="AG110" s="19" t="n"/>
       <c r="AH110" s="19" t="n"/>
       <c r="AI110" s="19" t="n"/>
-      <c r="AJ110" s="16" t="inlineStr">
+      <c r="AJ110" s="19" t="n"/>
+      <c r="AK110" s="16" t="inlineStr">
         <is>
           <t>3 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK110" s="22" t="n"/>
+      <c r="AL110" s="22" t="n"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="15" t="inlineStr">
@@ -14071,7 +14193,7 @@
       </c>
       <c r="F111" s="15" t="inlineStr">
         <is>
-          <t>Leuchten</t>
+          <t>Pflanzen</t>
         </is>
       </c>
       <c r="G111" s="15" t="inlineStr">
@@ -14145,23 +14267,24 @@
       </c>
       <c r="Z111" s="19" t="n"/>
       <c r="AA111" s="19" t="n"/>
-      <c r="AB111" s="20" t="n"/>
-      <c r="AC111" s="21">
-        <f>IF(J111="","",J111*AB111)</f>
-        <v/>
-      </c>
-      <c r="AD111" s="19" t="n"/>
+      <c r="AB111" s="19" t="n"/>
+      <c r="AC111" s="20" t="n"/>
+      <c r="AD111" s="21">
+        <f>IF(J111="","",J111*AC111)</f>
+        <v/>
+      </c>
       <c r="AE111" s="19" t="n"/>
       <c r="AF111" s="19" t="n"/>
       <c r="AG111" s="19" t="n"/>
       <c r="AH111" s="19" t="n"/>
       <c r="AI111" s="19" t="n"/>
-      <c r="AJ111" s="16" t="inlineStr">
+      <c r="AJ111" s="19" t="n"/>
+      <c r="AK111" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK111" s="22" t="n"/>
+      <c r="AL111" s="22" t="n"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="15" t="inlineStr">
@@ -14265,23 +14388,24 @@
       </c>
       <c r="Z112" s="19" t="n"/>
       <c r="AA112" s="19" t="n"/>
-      <c r="AB112" s="20" t="n"/>
-      <c r="AC112" s="21">
-        <f>IF(J112="","",J112*AB112)</f>
-        <v/>
-      </c>
-      <c r="AD112" s="19" t="n"/>
+      <c r="AB112" s="19" t="n"/>
+      <c r="AC112" s="20" t="n"/>
+      <c r="AD112" s="21">
+        <f>IF(J112="","",J112*AC112)</f>
+        <v/>
+      </c>
       <c r="AE112" s="19" t="n"/>
       <c r="AF112" s="19" t="n"/>
       <c r="AG112" s="19" t="n"/>
       <c r="AH112" s="19" t="n"/>
       <c r="AI112" s="19" t="n"/>
-      <c r="AJ112" s="16" t="inlineStr">
+      <c r="AJ112" s="19" t="n"/>
+      <c r="AK112" s="16" t="inlineStr">
         <is>
           <t>mindestens 4 Tische im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AK112" s="22" t="n"/>
+      <c r="AL112" s="22" t="n"/>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="15" t="inlineStr">
@@ -14385,23 +14509,24 @@
       </c>
       <c r="Z113" s="19" t="n"/>
       <c r="AA113" s="19" t="n"/>
-      <c r="AB113" s="20" t="n"/>
-      <c r="AC113" s="21">
-        <f>IF(J113="","",J113*AB113)</f>
-        <v/>
-      </c>
-      <c r="AD113" s="19" t="n"/>
+      <c r="AB113" s="19" t="n"/>
+      <c r="AC113" s="20" t="n"/>
+      <c r="AD113" s="21">
+        <f>IF(J113="","",J113*AC113)</f>
+        <v/>
+      </c>
       <c r="AE113" s="19" t="n"/>
       <c r="AF113" s="19" t="n"/>
       <c r="AG113" s="19" t="n"/>
       <c r="AH113" s="19" t="n"/>
       <c r="AI113" s="19" t="n"/>
-      <c r="AJ113" s="16" t="inlineStr">
+      <c r="AJ113" s="19" t="n"/>
+      <c r="AK113" s="16" t="inlineStr">
         <is>
           <t>2 Bänke im Bild erkennbar</t>
         </is>
       </c>
-      <c r="AK113" s="22" t="n"/>
+      <c r="AL113" s="22" t="n"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="15" t="inlineStr">
@@ -14505,23 +14630,24 @@
       </c>
       <c r="Z114" s="19" t="n"/>
       <c r="AA114" s="19" t="n"/>
-      <c r="AB114" s="20" t="n"/>
-      <c r="AC114" s="21">
-        <f>IF(J114="","",J114*AB114)</f>
-        <v/>
-      </c>
-      <c r="AD114" s="19" t="n"/>
+      <c r="AB114" s="19" t="n"/>
+      <c r="AC114" s="20" t="n"/>
+      <c r="AD114" s="21">
+        <f>IF(J114="","",J114*AC114)</f>
+        <v/>
+      </c>
       <c r="AE114" s="19" t="n"/>
       <c r="AF114" s="19" t="n"/>
       <c r="AG114" s="19" t="n"/>
       <c r="AH114" s="19" t="n"/>
       <c r="AI114" s="19" t="n"/>
-      <c r="AJ114" s="16" t="inlineStr">
+      <c r="AJ114" s="19" t="n"/>
+      <c r="AK114" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK114" s="22" t="n"/>
+      <c r="AL114" s="22" t="n"/>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="15" t="inlineStr">
@@ -14591,7 +14717,7 @@
       <c r="P115" s="19" t="n"/>
       <c r="Q115" s="20" t="n"/>
       <c r="R115" s="20" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="S115" s="19" t="inlineStr">
         <is>
@@ -14623,25 +14749,30 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z115" s="19" t="n"/>
+      <c r="Z115" s="19" t="inlineStr">
+        <is>
+          <t>Vitra</t>
+        </is>
+      </c>
       <c r="AA115" s="19" t="n"/>
-      <c r="AB115" s="20" t="n"/>
-      <c r="AC115" s="21">
-        <f>IF(J115="","",J115*AB115)</f>
-        <v/>
-      </c>
-      <c r="AD115" s="19" t="n"/>
+      <c r="AB115" s="19" t="n"/>
+      <c r="AC115" s="20" t="n"/>
+      <c r="AD115" s="21">
+        <f>IF(J115="","",J115*AC115)</f>
+        <v/>
+      </c>
       <c r="AE115" s="19" t="n"/>
       <c r="AF115" s="19" t="n"/>
       <c r="AG115" s="19" t="n"/>
       <c r="AH115" s="19" t="n"/>
       <c r="AI115" s="19" t="n"/>
-      <c r="AJ115" s="16" t="inlineStr">
+      <c r="AJ115" s="19" t="n"/>
+      <c r="AK115" s="16" t="inlineStr">
         <is>
           <t>2 Elemente im Bild - bitte prüfen ob 3</t>
         </is>
       </c>
-      <c r="AK115" s="22" t="n"/>
+      <c r="AL115" s="22" t="n"/>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="15" t="inlineStr">
@@ -14745,23 +14876,24 @@
       </c>
       <c r="Z116" s="19" t="n"/>
       <c r="AA116" s="19" t="n"/>
-      <c r="AB116" s="20" t="n"/>
-      <c r="AC116" s="21">
-        <f>IF(J116="","",J116*AB116)</f>
-        <v/>
-      </c>
-      <c r="AD116" s="19" t="n"/>
+      <c r="AB116" s="19" t="n"/>
+      <c r="AC116" s="20" t="n"/>
+      <c r="AD116" s="21">
+        <f>IF(J116="","",J116*AC116)</f>
+        <v/>
+      </c>
       <c r="AE116" s="19" t="n"/>
       <c r="AF116" s="19" t="n"/>
       <c r="AG116" s="19" t="n"/>
       <c r="AH116" s="19" t="n"/>
       <c r="AI116" s="19" t="n"/>
-      <c r="AJ116" s="16" t="inlineStr">
+      <c r="AJ116" s="19" t="n"/>
+      <c r="AK116" s="16" t="inlineStr">
         <is>
           <t>5 Uhren im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AK116" s="22" t="n"/>
+      <c r="AL116" s="22" t="n"/>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="15" t="inlineStr">
@@ -14869,23 +15001,24 @@
       </c>
       <c r="Z117" s="19" t="n"/>
       <c r="AA117" s="19" t="n"/>
-      <c r="AB117" s="20" t="n"/>
-      <c r="AC117" s="21">
-        <f>IF(J117="","",J117*AB117)</f>
-        <v/>
-      </c>
-      <c r="AD117" s="19" t="n"/>
+      <c r="AB117" s="19" t="n"/>
+      <c r="AC117" s="20" t="n"/>
+      <c r="AD117" s="21">
+        <f>IF(J117="","",J117*AC117)</f>
+        <v/>
+      </c>
       <c r="AE117" s="19" t="n"/>
       <c r="AF117" s="19" t="n"/>
       <c r="AG117" s="19" t="n"/>
       <c r="AH117" s="19" t="n"/>
       <c r="AI117" s="19" t="n"/>
-      <c r="AJ117" s="16" t="inlineStr">
+      <c r="AJ117" s="19" t="n"/>
+      <c r="AK117" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild (Inhalt nicht enthalten)</t>
         </is>
       </c>
-      <c r="AK117" s="22" t="n"/>
+      <c r="AL117" s="22" t="n"/>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="15" t="inlineStr">
@@ -14989,23 +15122,24 @@
       </c>
       <c r="Z118" s="19" t="n"/>
       <c r="AA118" s="19" t="n"/>
-      <c r="AB118" s="20" t="n"/>
-      <c r="AC118" s="21">
-        <f>IF(J118="","",J118*AB118)</f>
-        <v/>
-      </c>
-      <c r="AD118" s="19" t="n"/>
+      <c r="AB118" s="19" t="n"/>
+      <c r="AC118" s="20" t="n"/>
+      <c r="AD118" s="21">
+        <f>IF(J118="","",J118*AC118)</f>
+        <v/>
+      </c>
       <c r="AE118" s="19" t="n"/>
       <c r="AF118" s="19" t="n"/>
       <c r="AG118" s="19" t="n"/>
       <c r="AH118" s="19" t="n"/>
       <c r="AI118" s="19" t="n"/>
-      <c r="AJ118" s="16" t="inlineStr">
+      <c r="AJ118" s="19" t="n"/>
+      <c r="AK118" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK118" s="22" t="n"/>
+      <c r="AL118" s="22" t="n"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="15" t="inlineStr">
@@ -15109,23 +15243,24 @@
       </c>
       <c r="Z119" s="19" t="n"/>
       <c r="AA119" s="19" t="n"/>
-      <c r="AB119" s="20" t="n"/>
-      <c r="AC119" s="21">
-        <f>IF(J119="","",J119*AB119)</f>
-        <v/>
-      </c>
-      <c r="AD119" s="19" t="n"/>
+      <c r="AB119" s="19" t="n"/>
+      <c r="AC119" s="20" t="n"/>
+      <c r="AD119" s="21">
+        <f>IF(J119="","",J119*AC119)</f>
+        <v/>
+      </c>
       <c r="AE119" s="19" t="n"/>
       <c r="AF119" s="19" t="n"/>
       <c r="AG119" s="19" t="n"/>
       <c r="AH119" s="19" t="n"/>
       <c r="AI119" s="19" t="n"/>
-      <c r="AJ119" s="16" t="inlineStr">
+      <c r="AJ119" s="19" t="n"/>
+      <c r="AK119" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK119" s="22" t="n"/>
+      <c r="AL119" s="22" t="n"/>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="15" t="inlineStr">
@@ -15229,23 +15364,24 @@
       </c>
       <c r="Z120" s="19" t="n"/>
       <c r="AA120" s="19" t="n"/>
-      <c r="AB120" s="20" t="n"/>
-      <c r="AC120" s="21">
-        <f>IF(J120="","",J120*AB120)</f>
-        <v/>
-      </c>
-      <c r="AD120" s="19" t="n"/>
+      <c r="AB120" s="19" t="n"/>
+      <c r="AC120" s="20" t="n"/>
+      <c r="AD120" s="21">
+        <f>IF(J120="","",J120*AC120)</f>
+        <v/>
+      </c>
       <c r="AE120" s="19" t="n"/>
       <c r="AF120" s="19" t="n"/>
       <c r="AG120" s="19" t="n"/>
       <c r="AH120" s="19" t="n"/>
       <c r="AI120" s="19" t="n"/>
-      <c r="AJ120" s="16" t="inlineStr">
+      <c r="AJ120" s="19" t="n"/>
+      <c r="AK120" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK120" s="22" t="n"/>
+      <c r="AL120" s="22" t="n"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="15" t="inlineStr">
@@ -15353,23 +15489,24 @@
       </c>
       <c r="Z121" s="19" t="n"/>
       <c r="AA121" s="19" t="n"/>
-      <c r="AB121" s="20" t="n"/>
-      <c r="AC121" s="21">
-        <f>IF(J121="","",J121*AB121)</f>
-        <v/>
-      </c>
-      <c r="AD121" s="19" t="n"/>
+      <c r="AB121" s="19" t="n"/>
+      <c r="AC121" s="20" t="n"/>
+      <c r="AD121" s="21">
+        <f>IF(J121="","",J121*AC121)</f>
+        <v/>
+      </c>
       <c r="AE121" s="19" t="n"/>
       <c r="AF121" s="19" t="n"/>
       <c r="AG121" s="19" t="n"/>
       <c r="AH121" s="19" t="n"/>
       <c r="AI121" s="19" t="n"/>
-      <c r="AJ121" s="16" t="inlineStr">
+      <c r="AJ121" s="19" t="n"/>
+      <c r="AK121" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK121" s="22" t="n"/>
+      <c r="AL121" s="22" t="n"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="15" t="inlineStr">
@@ -15477,23 +15614,24 @@
       </c>
       <c r="Z122" s="19" t="n"/>
       <c r="AA122" s="19" t="n"/>
-      <c r="AB122" s="20" t="n"/>
-      <c r="AC122" s="21">
-        <f>IF(J122="","",J122*AB122)</f>
-        <v/>
-      </c>
-      <c r="AD122" s="19" t="n"/>
+      <c r="AB122" s="19" t="n"/>
+      <c r="AC122" s="20" t="n"/>
+      <c r="AD122" s="21">
+        <f>IF(J122="","",J122*AC122)</f>
+        <v/>
+      </c>
       <c r="AE122" s="19" t="n"/>
       <c r="AF122" s="19" t="n"/>
       <c r="AG122" s="19" t="n"/>
       <c r="AH122" s="19" t="n"/>
       <c r="AI122" s="19" t="n"/>
-      <c r="AJ122" s="16" t="inlineStr">
+      <c r="AJ122" s="19" t="n"/>
+      <c r="AK122" s="16" t="inlineStr">
         <is>
           <t>5 Rahmen im Bild</t>
         </is>
       </c>
-      <c r="AK122" s="22" t="n"/>
+      <c r="AL122" s="22" t="n"/>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="15" t="inlineStr">
@@ -15601,23 +15739,24 @@
       </c>
       <c r="Z123" s="19" t="n"/>
       <c r="AA123" s="19" t="n"/>
-      <c r="AB123" s="20" t="n"/>
-      <c r="AC123" s="21">
-        <f>IF(J123="","",J123*AB123)</f>
-        <v/>
-      </c>
-      <c r="AD123" s="19" t="n"/>
+      <c r="AB123" s="19" t="n"/>
+      <c r="AC123" s="20" t="n"/>
+      <c r="AD123" s="21">
+        <f>IF(J123="","",J123*AC123)</f>
+        <v/>
+      </c>
       <c r="AE123" s="19" t="n"/>
       <c r="AF123" s="19" t="n"/>
       <c r="AG123" s="19" t="n"/>
       <c r="AH123" s="19" t="n"/>
       <c r="AI123" s="19" t="n"/>
-      <c r="AJ123" s="16" t="inlineStr">
+      <c r="AJ123" s="19" t="n"/>
+      <c r="AK123" s="16" t="inlineStr">
         <is>
           <t>4 Rahmen im Bild, ggf. mehr</t>
         </is>
       </c>
-      <c r="AK123" s="22" t="n"/>
+      <c r="AL123" s="22" t="n"/>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="15" t="inlineStr">
@@ -15721,23 +15860,24 @@
       </c>
       <c r="Z124" s="19" t="n"/>
       <c r="AA124" s="19" t="n"/>
-      <c r="AB124" s="20" t="n"/>
-      <c r="AC124" s="21">
-        <f>IF(J124="","",J124*AB124)</f>
-        <v/>
-      </c>
-      <c r="AD124" s="19" t="n"/>
+      <c r="AB124" s="19" t="n"/>
+      <c r="AC124" s="20" t="n"/>
+      <c r="AD124" s="21">
+        <f>IF(J124="","",J124*AC124)</f>
+        <v/>
+      </c>
       <c r="AE124" s="19" t="n"/>
       <c r="AF124" s="19" t="n"/>
       <c r="AG124" s="19" t="n"/>
       <c r="AH124" s="19" t="n"/>
       <c r="AI124" s="19" t="n"/>
-      <c r="AJ124" s="16" t="inlineStr">
+      <c r="AJ124" s="19" t="n"/>
+      <c r="AK124" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AK124" s="22" t="n"/>
+      <c r="AL124" s="22" t="n"/>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="15" t="inlineStr">
@@ -15841,23 +15981,24 @@
       </c>
       <c r="Z125" s="19" t="n"/>
       <c r="AA125" s="19" t="n"/>
-      <c r="AB125" s="20" t="n"/>
-      <c r="AC125" s="21">
-        <f>IF(J125="","",J125*AB125)</f>
-        <v/>
-      </c>
-      <c r="AD125" s="19" t="n"/>
+      <c r="AB125" s="19" t="n"/>
+      <c r="AC125" s="20" t="n"/>
+      <c r="AD125" s="21">
+        <f>IF(J125="","",J125*AC125)</f>
+        <v/>
+      </c>
       <c r="AE125" s="19" t="n"/>
       <c r="AF125" s="19" t="n"/>
       <c r="AG125" s="19" t="n"/>
       <c r="AH125" s="19" t="n"/>
       <c r="AI125" s="19" t="n"/>
-      <c r="AJ125" s="16" t="inlineStr">
+      <c r="AJ125" s="19" t="n"/>
+      <c r="AK125" s="16" t="inlineStr">
         <is>
           <t>4 Rahmen erkennbar</t>
         </is>
       </c>
-      <c r="AK125" s="22" t="n"/>
+      <c r="AL125" s="22" t="n"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="15" t="inlineStr">
@@ -15878,7 +16019,7 @@
       </c>
       <c r="E126" s="16" t="inlineStr">
         <is>
-          <t>IKEA Morum, Flachgewebe dunkelgrau, für innen und außen geeignet, schmaler Läufer – 15 Stück verfügbar</t>
+          <t>Flachgewebter Läufer in Dunkelgrau, IKEA Morum (In-/Outdoor-Qualität), strukturierte Webung. 15 gleiche Läufer aus den Fluren.</t>
         </is>
       </c>
       <c r="F126" s="15" t="inlineStr">
@@ -15923,7 +16064,7 @@
       <c r="P126" s="19" t="n"/>
       <c r="Q126" s="20" t="n"/>
       <c r="R126" s="20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="S126" s="19" t="inlineStr">
         <is>
@@ -15939,7 +16080,11 @@
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="V126" s="15" t="n"/>
+      <c r="V126" s="15" t="inlineStr">
+        <is>
+          <t>F-134</t>
+        </is>
+      </c>
       <c r="W126" s="19" t="inlineStr">
         <is>
           <t>ja</t>
@@ -15951,29 +16096,30 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z126" s="19" t="n"/>
+      <c r="Z126" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
       <c r="AA126" s="19" t="n"/>
-      <c r="AB126" s="20" t="n"/>
-      <c r="AC126" s="21">
-        <f>IF(J126="","",J126*AB126)</f>
-        <v/>
-      </c>
-      <c r="AD126" s="19" t="n"/>
+      <c r="AB126" s="19" t="n"/>
+      <c r="AC126" s="20" t="n"/>
+      <c r="AD126" s="21">
+        <f>IF(J126="","",J126*AC126)</f>
+        <v/>
+      </c>
       <c r="AE126" s="19" t="n"/>
       <c r="AF126" s="19" t="n"/>
       <c r="AG126" s="19" t="n"/>
       <c r="AH126" s="19" t="n"/>
       <c r="AI126" s="19" t="n"/>
-      <c r="AJ126" s="16" t="inlineStr">
-        <is>
-          <t>15 Stück laut Angabe im Haus – Foto folgt</t>
-        </is>
-      </c>
-      <c r="AK126" s="22" t="inlineStr">
-        <is>
-          <t>Foto noch nachzuliefern</t>
-        </is>
-      </c>
+      <c r="AJ126" s="19" t="n"/>
+      <c r="AK126" s="16" t="inlineStr">
+        <is>
+          <t>15 Läufer laut Angabe im Haus – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AL126" s="22" t="n"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="15" t="inlineStr">
@@ -16077,23 +16223,24 @@
       </c>
       <c r="Z127" s="19" t="n"/>
       <c r="AA127" s="19" t="n"/>
-      <c r="AB127" s="20" t="n"/>
-      <c r="AC127" s="21">
-        <f>IF(J127="","",J127*AB127)</f>
-        <v/>
-      </c>
-      <c r="AD127" s="19" t="n"/>
+      <c r="AB127" s="19" t="n"/>
+      <c r="AC127" s="20" t="n"/>
+      <c r="AD127" s="21">
+        <f>IF(J127="","",J127*AC127)</f>
+        <v/>
+      </c>
       <c r="AE127" s="19" t="n"/>
       <c r="AF127" s="19" t="n"/>
       <c r="AG127" s="19" t="n"/>
       <c r="AH127" s="19" t="n"/>
       <c r="AI127" s="19" t="n"/>
-      <c r="AJ127" s="16" t="inlineStr">
+      <c r="AJ127" s="19" t="n"/>
+      <c r="AK127" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK127" s="22" t="n"/>
+      <c r="AL127" s="22" t="n"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="15" t="inlineStr">
@@ -16197,23 +16344,24 @@
       </c>
       <c r="Z128" s="19" t="n"/>
       <c r="AA128" s="19" t="n"/>
-      <c r="AB128" s="20" t="n"/>
-      <c r="AC128" s="21">
-        <f>IF(J128="","",J128*AB128)</f>
-        <v/>
-      </c>
-      <c r="AD128" s="19" t="n"/>
+      <c r="AB128" s="19" t="n"/>
+      <c r="AC128" s="20" t="n"/>
+      <c r="AD128" s="21">
+        <f>IF(J128="","",J128*AC128)</f>
+        <v/>
+      </c>
       <c r="AE128" s="19" t="n"/>
       <c r="AF128" s="19" t="n"/>
       <c r="AG128" s="19" t="n"/>
       <c r="AH128" s="19" t="n"/>
       <c r="AI128" s="19" t="n"/>
-      <c r="AJ128" s="16" t="inlineStr">
+      <c r="AJ128" s="19" t="n"/>
+      <c r="AK128" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK128" s="22" t="n"/>
+      <c r="AL128" s="22" t="n"/>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="15" t="inlineStr">
@@ -16317,23 +16465,24 @@
       </c>
       <c r="Z129" s="19" t="n"/>
       <c r="AA129" s="19" t="n"/>
-      <c r="AB129" s="20" t="n"/>
-      <c r="AC129" s="21">
-        <f>IF(J129="","",J129*AB129)</f>
-        <v/>
-      </c>
-      <c r="AD129" s="19" t="n"/>
+      <c r="AB129" s="19" t="n"/>
+      <c r="AC129" s="20" t="n"/>
+      <c r="AD129" s="21">
+        <f>IF(J129="","",J129*AC129)</f>
+        <v/>
+      </c>
       <c r="AE129" s="19" t="n"/>
       <c r="AF129" s="19" t="n"/>
       <c r="AG129" s="19" t="n"/>
       <c r="AH129" s="19" t="n"/>
       <c r="AI129" s="19" t="n"/>
-      <c r="AJ129" s="16" t="inlineStr">
+      <c r="AJ129" s="19" t="n"/>
+      <c r="AK129" s="16" t="inlineStr">
         <is>
           <t>3 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK129" s="22" t="n"/>
+      <c r="AL129" s="22" t="n"/>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="15" t="inlineStr">
@@ -16437,23 +16586,24 @@
       </c>
       <c r="Z130" s="19" t="n"/>
       <c r="AA130" s="19" t="n"/>
-      <c r="AB130" s="20" t="n"/>
-      <c r="AC130" s="21">
-        <f>IF(J130="","",J130*AB130)</f>
-        <v/>
-      </c>
-      <c r="AD130" s="19" t="n"/>
+      <c r="AB130" s="19" t="n"/>
+      <c r="AC130" s="20" t="n"/>
+      <c r="AD130" s="21">
+        <f>IF(J130="","",J130*AC130)</f>
+        <v/>
+      </c>
       <c r="AE130" s="19" t="n"/>
       <c r="AF130" s="19" t="n"/>
       <c r="AG130" s="19" t="n"/>
       <c r="AH130" s="19" t="n"/>
       <c r="AI130" s="19" t="n"/>
-      <c r="AJ130" s="16" t="inlineStr">
+      <c r="AJ130" s="19" t="n"/>
+      <c r="AK130" s="16" t="inlineStr">
         <is>
           <t>1 große Einheit im Bild</t>
         </is>
       </c>
-      <c r="AK130" s="22" t="n"/>
+      <c r="AL130" s="22" t="n"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="15" t="inlineStr">
@@ -16557,23 +16707,24 @@
       </c>
       <c r="Z131" s="19" t="n"/>
       <c r="AA131" s="19" t="n"/>
-      <c r="AB131" s="20" t="n"/>
-      <c r="AC131" s="21">
-        <f>IF(J131="","",J131*AB131)</f>
-        <v/>
-      </c>
-      <c r="AD131" s="19" t="n"/>
+      <c r="AB131" s="19" t="n"/>
+      <c r="AC131" s="20" t="n"/>
+      <c r="AD131" s="21">
+        <f>IF(J131="","",J131*AC131)</f>
+        <v/>
+      </c>
       <c r="AE131" s="19" t="n"/>
       <c r="AF131" s="19" t="n"/>
       <c r="AG131" s="19" t="n"/>
       <c r="AH131" s="19" t="n"/>
       <c r="AI131" s="19" t="n"/>
-      <c r="AJ131" s="16" t="inlineStr">
+      <c r="AJ131" s="19" t="n"/>
+      <c r="AK131" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Vordergrund, weitere im Hintergrund</t>
         </is>
       </c>
-      <c r="AK131" s="22" t="n"/>
+      <c r="AL131" s="22" t="n"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="15" t="inlineStr">
@@ -16677,23 +16828,24 @@
       </c>
       <c r="Z132" s="19" t="n"/>
       <c r="AA132" s="19" t="n"/>
-      <c r="AB132" s="20" t="n"/>
-      <c r="AC132" s="21">
-        <f>IF(J132="","",J132*AB132)</f>
-        <v/>
-      </c>
-      <c r="AD132" s="19" t="n"/>
+      <c r="AB132" s="19" t="n"/>
+      <c r="AC132" s="20" t="n"/>
+      <c r="AD132" s="21">
+        <f>IF(J132="","",J132*AC132)</f>
+        <v/>
+      </c>
       <c r="AE132" s="19" t="n"/>
       <c r="AF132" s="19" t="n"/>
       <c r="AG132" s="19" t="n"/>
       <c r="AH132" s="19" t="n"/>
       <c r="AI132" s="19" t="n"/>
-      <c r="AJ132" s="16" t="inlineStr">
+      <c r="AJ132" s="19" t="n"/>
+      <c r="AK132" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK132" s="22" t="n"/>
+      <c r="AL132" s="22" t="n"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="15" t="inlineStr">
@@ -16797,23 +16949,24 @@
       </c>
       <c r="Z133" s="19" t="n"/>
       <c r="AA133" s="19" t="n"/>
-      <c r="AB133" s="20" t="n"/>
-      <c r="AC133" s="21">
-        <f>IF(J133="","",J133*AB133)</f>
-        <v/>
-      </c>
-      <c r="AD133" s="19" t="n"/>
+      <c r="AB133" s="19" t="n"/>
+      <c r="AC133" s="20" t="n"/>
+      <c r="AD133" s="21">
+        <f>IF(J133="","",J133*AC133)</f>
+        <v/>
+      </c>
       <c r="AE133" s="19" t="n"/>
       <c r="AF133" s="19" t="n"/>
       <c r="AG133" s="19" t="n"/>
       <c r="AH133" s="19" t="n"/>
       <c r="AI133" s="19" t="n"/>
-      <c r="AJ133" s="16" t="inlineStr">
+      <c r="AJ133" s="19" t="n"/>
+      <c r="AK133" s="16" t="inlineStr">
         <is>
           <t>2 Stück (zwei Einzelfotos)</t>
         </is>
       </c>
-      <c r="AK133" s="22" t="n"/>
+      <c r="AL133" s="22" t="n"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="15" t="inlineStr">
@@ -16917,23 +17070,24 @@
       </c>
       <c r="Z134" s="19" t="n"/>
       <c r="AA134" s="19" t="n"/>
-      <c r="AB134" s="20" t="n"/>
-      <c r="AC134" s="21">
-        <f>IF(J134="","",J134*AB134)</f>
-        <v/>
-      </c>
-      <c r="AD134" s="19" t="n"/>
+      <c r="AB134" s="19" t="n"/>
+      <c r="AC134" s="20" t="n"/>
+      <c r="AD134" s="21">
+        <f>IF(J134="","",J134*AC134)</f>
+        <v/>
+      </c>
       <c r="AE134" s="19" t="n"/>
       <c r="AF134" s="19" t="n"/>
       <c r="AG134" s="19" t="n"/>
       <c r="AH134" s="19" t="n"/>
       <c r="AI134" s="19" t="n"/>
-      <c r="AJ134" s="16" t="inlineStr">
+      <c r="AJ134" s="19" t="n"/>
+      <c r="AK134" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK134" s="22" t="n"/>
+      <c r="AL134" s="22" t="n"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="15" t="inlineStr">
@@ -17036,25 +17190,30 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z135" s="19" t="n"/>
+      <c r="Z135" s="19" t="inlineStr">
+        <is>
+          <t>Biohort</t>
+        </is>
+      </c>
       <c r="AA135" s="19" t="n"/>
-      <c r="AB135" s="20" t="n"/>
-      <c r="AC135" s="21">
-        <f>IF(J135="","",J135*AB135)</f>
-        <v/>
-      </c>
-      <c r="AD135" s="19" t="n"/>
+      <c r="AB135" s="19" t="n"/>
+      <c r="AC135" s="20" t="n"/>
+      <c r="AD135" s="21">
+        <f>IF(J135="","",J135*AC135)</f>
+        <v/>
+      </c>
       <c r="AE135" s="19" t="n"/>
       <c r="AF135" s="19" t="n"/>
       <c r="AG135" s="19" t="n"/>
       <c r="AH135" s="19" t="n"/>
       <c r="AI135" s="19" t="n"/>
-      <c r="AJ135" s="16" t="inlineStr">
+      <c r="AJ135" s="19" t="n"/>
+      <c r="AK135" s="16" t="inlineStr">
         <is>
           <t>1 Box im Bild</t>
         </is>
       </c>
-      <c r="AK135" s="22" t="n"/>
+      <c r="AL135" s="22" t="n"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="15" t="inlineStr">
@@ -17158,23 +17317,24 @@
       </c>
       <c r="Z136" s="19" t="n"/>
       <c r="AA136" s="19" t="n"/>
-      <c r="AB136" s="20" t="n"/>
-      <c r="AC136" s="21">
-        <f>IF(J136="","",J136*AB136)</f>
-        <v/>
-      </c>
-      <c r="AD136" s="19" t="n"/>
+      <c r="AB136" s="19" t="n"/>
+      <c r="AC136" s="20" t="n"/>
+      <c r="AD136" s="21">
+        <f>IF(J136="","",J136*AC136)</f>
+        <v/>
+      </c>
       <c r="AE136" s="19" t="n"/>
       <c r="AF136" s="19" t="n"/>
       <c r="AG136" s="19" t="n"/>
       <c r="AH136" s="19" t="n"/>
       <c r="AI136" s="19" t="n"/>
-      <c r="AJ136" s="16" t="inlineStr">
+      <c r="AJ136" s="19" t="n"/>
+      <c r="AK136" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AK136" s="22" t="n"/>
+      <c r="AL136" s="22" t="n"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="15" t="inlineStr">
@@ -17278,23 +17438,24 @@
       </c>
       <c r="Z137" s="19" t="n"/>
       <c r="AA137" s="19" t="n"/>
-      <c r="AB137" s="20" t="n"/>
-      <c r="AC137" s="21">
-        <f>IF(J137="","",J137*AB137)</f>
-        <v/>
-      </c>
-      <c r="AD137" s="19" t="n"/>
+      <c r="AB137" s="19" t="n"/>
+      <c r="AC137" s="20" t="n"/>
+      <c r="AD137" s="21">
+        <f>IF(J137="","",J137*AC137)</f>
+        <v/>
+      </c>
       <c r="AE137" s="19" t="n"/>
       <c r="AF137" s="19" t="n"/>
       <c r="AG137" s="19" t="n"/>
       <c r="AH137" s="19" t="n"/>
       <c r="AI137" s="19" t="n"/>
-      <c r="AJ137" s="16" t="inlineStr">
+      <c r="AJ137" s="19" t="n"/>
+      <c r="AK137" s="16" t="inlineStr">
         <is>
           <t>4 Stück im Bild</t>
         </is>
       </c>
-      <c r="AK137" s="22" t="n"/>
+      <c r="AL137" s="22" t="n"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="15" t="inlineStr">
@@ -17400,25 +17561,30 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z138" s="19" t="n"/>
+      <c r="Z138" s="19" t="inlineStr">
+        <is>
+          <t>Weber</t>
+        </is>
+      </c>
       <c r="AA138" s="19" t="n"/>
-      <c r="AB138" s="20" t="n"/>
-      <c r="AC138" s="21">
-        <f>IF(J138="","",J138*AB138)</f>
-        <v/>
-      </c>
-      <c r="AD138" s="19" t="n"/>
+      <c r="AB138" s="19" t="n"/>
+      <c r="AC138" s="20" t="n"/>
+      <c r="AD138" s="21">
+        <f>IF(J138="","",J138*AC138)</f>
+        <v/>
+      </c>
       <c r="AE138" s="19" t="n"/>
       <c r="AF138" s="19" t="n"/>
       <c r="AG138" s="19" t="n"/>
       <c r="AH138" s="19" t="n"/>
       <c r="AI138" s="19" t="n"/>
-      <c r="AJ138" s="16" t="inlineStr">
+      <c r="AJ138" s="19" t="n"/>
+      <c r="AK138" s="16" t="inlineStr">
         <is>
           <t>1 Grill im Bild</t>
         </is>
       </c>
-      <c r="AK138" s="22" t="n"/>
+      <c r="AL138" s="22" t="n"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="15" t="inlineStr">
@@ -17522,23 +17688,24 @@
       </c>
       <c r="Z139" s="19" t="n"/>
       <c r="AA139" s="19" t="n"/>
-      <c r="AB139" s="20" t="n"/>
-      <c r="AC139" s="21">
-        <f>IF(J139="","",J139*AB139)</f>
-        <v/>
-      </c>
-      <c r="AD139" s="19" t="n"/>
+      <c r="AB139" s="19" t="n"/>
+      <c r="AC139" s="20" t="n"/>
+      <c r="AD139" s="21">
+        <f>IF(J139="","",J139*AC139)</f>
+        <v/>
+      </c>
       <c r="AE139" s="19" t="n"/>
       <c r="AF139" s="19" t="n"/>
       <c r="AG139" s="19" t="n"/>
       <c r="AH139" s="19" t="n"/>
       <c r="AI139" s="19" t="n"/>
-      <c r="AJ139" s="16" t="inlineStr">
+      <c r="AJ139" s="19" t="n"/>
+      <c r="AK139" s="16" t="inlineStr">
         <is>
           <t>1 Schirm im Bild</t>
         </is>
       </c>
-      <c r="AK139" s="22" t="n"/>
+      <c r="AL139" s="22" t="n"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="15" t="inlineStr">
@@ -17642,23 +17809,24 @@
       </c>
       <c r="Z140" s="19" t="n"/>
       <c r="AA140" s="19" t="n"/>
-      <c r="AB140" s="20" t="n"/>
-      <c r="AC140" s="21">
-        <f>IF(J140="","",J140*AB140)</f>
-        <v/>
-      </c>
-      <c r="AD140" s="19" t="n"/>
+      <c r="AB140" s="19" t="n"/>
+      <c r="AC140" s="20" t="n"/>
+      <c r="AD140" s="21">
+        <f>IF(J140="","",J140*AC140)</f>
+        <v/>
+      </c>
       <c r="AE140" s="19" t="n"/>
       <c r="AF140" s="19" t="n"/>
       <c r="AG140" s="19" t="n"/>
       <c r="AH140" s="19" t="n"/>
       <c r="AI140" s="19" t="n"/>
-      <c r="AJ140" s="16" t="inlineStr">
+      <c r="AJ140" s="19" t="n"/>
+      <c r="AK140" s="16" t="inlineStr">
         <is>
           <t>3 Kübel im Bild</t>
         </is>
       </c>
-      <c r="AK140" s="22" t="n"/>
+      <c r="AL140" s="22" t="n"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="15" t="inlineStr">
@@ -17762,23 +17930,24 @@
       </c>
       <c r="Z141" s="19" t="n"/>
       <c r="AA141" s="19" t="n"/>
-      <c r="AB141" s="20" t="n"/>
-      <c r="AC141" s="21">
-        <f>IF(J141="","",J141*AB141)</f>
-        <v/>
-      </c>
-      <c r="AD141" s="19" t="n"/>
+      <c r="AB141" s="19" t="n"/>
+      <c r="AC141" s="20" t="n"/>
+      <c r="AD141" s="21">
+        <f>IF(J141="","",J141*AC141)</f>
+        <v/>
+      </c>
       <c r="AE141" s="19" t="n"/>
       <c r="AF141" s="19" t="n"/>
       <c r="AG141" s="19" t="n"/>
       <c r="AH141" s="19" t="n"/>
       <c r="AI141" s="19" t="n"/>
-      <c r="AJ141" s="16" t="inlineStr">
+      <c r="AJ141" s="19" t="n"/>
+      <c r="AK141" s="16" t="inlineStr">
         <is>
           <t>4 Stück gestapelt im Bild</t>
         </is>
       </c>
-      <c r="AK141" s="22" t="n"/>
+      <c r="AL141" s="22" t="n"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="15" t="inlineStr">
@@ -17882,23 +18051,24 @@
       </c>
       <c r="Z142" s="19" t="n"/>
       <c r="AA142" s="19" t="n"/>
-      <c r="AB142" s="20" t="n"/>
-      <c r="AC142" s="21">
-        <f>IF(J142="","",J142*AB142)</f>
-        <v/>
-      </c>
-      <c r="AD142" s="19" t="n"/>
+      <c r="AB142" s="19" t="n"/>
+      <c r="AC142" s="20" t="n"/>
+      <c r="AD142" s="21">
+        <f>IF(J142="","",J142*AC142)</f>
+        <v/>
+      </c>
       <c r="AE142" s="19" t="n"/>
       <c r="AF142" s="19" t="n"/>
       <c r="AG142" s="19" t="n"/>
       <c r="AH142" s="19" t="n"/>
       <c r="AI142" s="19" t="n"/>
-      <c r="AJ142" s="16" t="inlineStr">
+      <c r="AJ142" s="19" t="n"/>
+      <c r="AK142" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AK142" s="22" t="n"/>
+      <c r="AL142" s="22" t="n"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="15" t="inlineStr">
@@ -18002,23 +18172,24 @@
       </c>
       <c r="Z143" s="19" t="n"/>
       <c r="AA143" s="19" t="n"/>
-      <c r="AB143" s="20" t="n"/>
-      <c r="AC143" s="21">
-        <f>IF(J143="","",J143*AB143)</f>
-        <v/>
-      </c>
-      <c r="AD143" s="19" t="n"/>
+      <c r="AB143" s="19" t="n"/>
+      <c r="AC143" s="20" t="n"/>
+      <c r="AD143" s="21">
+        <f>IF(J143="","",J143*AC143)</f>
+        <v/>
+      </c>
       <c r="AE143" s="19" t="n"/>
       <c r="AF143" s="19" t="n"/>
       <c r="AG143" s="19" t="n"/>
       <c r="AH143" s="19" t="n"/>
       <c r="AI143" s="19" t="n"/>
-      <c r="AJ143" s="16" t="inlineStr">
+      <c r="AJ143" s="19" t="n"/>
+      <c r="AK143" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AK143" s="22" t="n"/>
+      <c r="AL143" s="22" t="n"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="15" t="inlineStr">
@@ -18122,23 +18293,24 @@
       </c>
       <c r="Z144" s="19" t="n"/>
       <c r="AA144" s="19" t="n"/>
-      <c r="AB144" s="20" t="n"/>
-      <c r="AC144" s="21">
-        <f>IF(J144="","",J144*AB144)</f>
-        <v/>
-      </c>
-      <c r="AD144" s="19" t="n"/>
+      <c r="AB144" s="19" t="n"/>
+      <c r="AC144" s="20" t="n"/>
+      <c r="AD144" s="21">
+        <f>IF(J144="","",J144*AC144)</f>
+        <v/>
+      </c>
       <c r="AE144" s="19" t="n"/>
       <c r="AF144" s="19" t="n"/>
       <c r="AG144" s="19" t="n"/>
       <c r="AH144" s="19" t="n"/>
       <c r="AI144" s="19" t="n"/>
-      <c r="AJ144" s="16" t="inlineStr">
+      <c r="AJ144" s="19" t="n"/>
+      <c r="AK144" s="16" t="inlineStr">
         <is>
           <t>1 Kübel im Bild</t>
         </is>
       </c>
-      <c r="AK144" s="22" t="n"/>
+      <c r="AL144" s="22" t="n"/>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="15" t="inlineStr">
@@ -18242,23 +18414,24 @@
       </c>
       <c r="Z145" s="19" t="n"/>
       <c r="AA145" s="19" t="n"/>
-      <c r="AB145" s="20" t="n"/>
-      <c r="AC145" s="21">
-        <f>IF(J145="","",J145*AB145)</f>
-        <v/>
-      </c>
-      <c r="AD145" s="19" t="n"/>
+      <c r="AB145" s="19" t="n"/>
+      <c r="AC145" s="20" t="n"/>
+      <c r="AD145" s="21">
+        <f>IF(J145="","",J145*AC145)</f>
+        <v/>
+      </c>
       <c r="AE145" s="19" t="n"/>
       <c r="AF145" s="19" t="n"/>
       <c r="AG145" s="19" t="n"/>
       <c r="AH145" s="19" t="n"/>
       <c r="AI145" s="19" t="n"/>
-      <c r="AJ145" s="16" t="inlineStr">
+      <c r="AJ145" s="19" t="n"/>
+      <c r="AK145" s="16" t="inlineStr">
         <is>
           <t>1 Stern im Bild</t>
         </is>
       </c>
-      <c r="AK145" s="22" t="n"/>
+      <c r="AL145" s="22" t="n"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="15" t="inlineStr">
@@ -18358,25 +18531,26 @@
       </c>
       <c r="Z146" s="19" t="n"/>
       <c r="AA146" s="19" t="n"/>
-      <c r="AB146" s="20" t="n"/>
-      <c r="AC146" s="21">
-        <f>IF(J146="","",J146*AB146)</f>
-        <v/>
-      </c>
-      <c r="AD146" s="19" t="n"/>
+      <c r="AB146" s="19" t="n"/>
+      <c r="AC146" s="20" t="n"/>
+      <c r="AD146" s="21">
+        <f>IF(J146="","",J146*AC146)</f>
+        <v/>
+      </c>
       <c r="AE146" s="19" t="n"/>
       <c r="AF146" s="19" t="n"/>
       <c r="AG146" s="19" t="n"/>
       <c r="AH146" s="19" t="n"/>
       <c r="AI146" s="19" t="n"/>
-      <c r="AJ146" s="16" t="inlineStr">
+      <c r="AJ146" s="19" t="n"/>
+      <c r="AK146" s="16" t="inlineStr">
         <is>
           <t>1 Vitrine. Die Dekoration darin ist Position NU01-03 und wird getrennt verkauft.</t>
         </is>
       </c>
-      <c r="AK146" s="22" t="inlineStr">
-        <is>
-          <t>Auf dem Foto sind gerahmte Personenfotos in der Vitrine maskiert – ein neues Foto ohne die Rahmen wäre besser.</t>
+      <c r="AL146" s="22" t="inlineStr">
+        <is>
+          <t>Personenfotos in der Vitrine sind im Bild maskiert (so gewollt).</t>
         </is>
       </c>
     </row>
@@ -18478,23 +18652,24 @@
       </c>
       <c r="Z147" s="19" t="n"/>
       <c r="AA147" s="19" t="n"/>
-      <c r="AB147" s="20" t="n"/>
-      <c r="AC147" s="21">
-        <f>IF(J147="","",J147*AB147)</f>
-        <v/>
-      </c>
-      <c r="AD147" s="19" t="n"/>
+      <c r="AB147" s="19" t="n"/>
+      <c r="AC147" s="20" t="n"/>
+      <c r="AD147" s="21">
+        <f>IF(J147="","",J147*AC147)</f>
+        <v/>
+      </c>
       <c r="AE147" s="19" t="n"/>
       <c r="AF147" s="19" t="n"/>
       <c r="AG147" s="19" t="n"/>
       <c r="AH147" s="19" t="n"/>
       <c r="AI147" s="19" t="n"/>
-      <c r="AJ147" s="16" t="inlineStr">
+      <c r="AJ147" s="19" t="n"/>
+      <c r="AK147" s="16" t="inlineStr">
         <is>
           <t>5 gleiche Einheiten laut Erfassungsblatt – abgebildet ist eine davon.</t>
         </is>
       </c>
-      <c r="AK147" s="22" t="n"/>
+      <c r="AL147" s="22" t="n"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="15" t="inlineStr">
@@ -18594,23 +18769,24 @@
       </c>
       <c r="Z148" s="19" t="n"/>
       <c r="AA148" s="19" t="n"/>
-      <c r="AB148" s="20" t="n"/>
-      <c r="AC148" s="21">
-        <f>IF(J148="","",J148*AB148)</f>
-        <v/>
-      </c>
-      <c r="AD148" s="19" t="n"/>
+      <c r="AB148" s="19" t="n"/>
+      <c r="AC148" s="20" t="n"/>
+      <c r="AD148" s="21">
+        <f>IF(J148="","",J148*AC148)</f>
+        <v/>
+      </c>
       <c r="AE148" s="19" t="n"/>
       <c r="AF148" s="19" t="n"/>
       <c r="AG148" s="19" t="n"/>
       <c r="AH148" s="19" t="n"/>
       <c r="AI148" s="19" t="n"/>
-      <c r="AJ148" s="16" t="inlineStr">
+      <c r="AJ148" s="19" t="n"/>
+      <c r="AK148" s="16" t="inlineStr">
         <is>
           <t>4 gleiche Schränke laut Erfassungsblatt – abgebildet ist die Schrankwand im Ganzen.</t>
         </is>
       </c>
-      <c r="AK148" s="22" t="n"/>
+      <c r="AL148" s="22" t="n"/>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="15" t="inlineStr">
@@ -18712,25 +18888,30 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z149" s="19" t="n"/>
+      <c r="Z149" s="19" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
       <c r="AA149" s="19" t="n"/>
-      <c r="AB149" s="20" t="n"/>
-      <c r="AC149" s="21">
-        <f>IF(J149="","",J149*AB149)</f>
-        <v/>
-      </c>
-      <c r="AD149" s="19" t="n"/>
+      <c r="AB149" s="19" t="n"/>
+      <c r="AC149" s="20" t="n"/>
+      <c r="AD149" s="21">
+        <f>IF(J149="","",J149*AC149)</f>
+        <v/>
+      </c>
       <c r="AE149" s="19" t="n"/>
       <c r="AF149" s="19" t="n"/>
       <c r="AG149" s="19" t="n"/>
       <c r="AH149" s="19" t="n"/>
       <c r="AI149" s="19" t="n"/>
-      <c r="AJ149" s="16" t="inlineStr">
+      <c r="AJ149" s="19" t="n"/>
+      <c r="AK149" s="16" t="inlineStr">
         <is>
           <t>1 Gerät. Typenschild ist abfotografiert (Foto F-121).</t>
         </is>
       </c>
-      <c r="AK149" s="22" t="n"/>
+      <c r="AL149" s="22" t="n"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="15" t="inlineStr">
@@ -18828,25 +19009,30 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z150" s="19" t="n"/>
+      <c r="Z150" s="19" t="inlineStr">
+        <is>
+          <t>Miele</t>
+        </is>
+      </c>
       <c r="AA150" s="19" t="n"/>
-      <c r="AB150" s="20" t="n"/>
-      <c r="AC150" s="21">
-        <f>IF(J150="","",J150*AB150)</f>
-        <v/>
-      </c>
-      <c r="AD150" s="19" t="n"/>
+      <c r="AB150" s="19" t="n"/>
+      <c r="AC150" s="20" t="n"/>
+      <c r="AD150" s="21">
+        <f>IF(J150="","",J150*AC150)</f>
+        <v/>
+      </c>
       <c r="AE150" s="19" t="n"/>
       <c r="AF150" s="19" t="n"/>
       <c r="AG150" s="19" t="n"/>
       <c r="AH150" s="19" t="n"/>
       <c r="AI150" s="19" t="n"/>
-      <c r="AJ150" s="16" t="inlineStr">
+      <c r="AJ150" s="19" t="n"/>
+      <c r="AK150" s="16" t="inlineStr">
         <is>
           <t>1 Gerät. Typenschild ist abfotografiert (Foto F-122).</t>
         </is>
       </c>
-      <c r="AK150" s="22" t="n"/>
+      <c r="AL150" s="22" t="n"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="15" t="inlineStr">
@@ -18944,25 +19130,30 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z151" s="19" t="n"/>
+      <c r="Z151" s="19" t="inlineStr">
+        <is>
+          <t>Candy</t>
+        </is>
+      </c>
       <c r="AA151" s="19" t="n"/>
-      <c r="AB151" s="20" t="n"/>
-      <c r="AC151" s="21">
-        <f>IF(J151="","",J151*AB151)</f>
-        <v/>
-      </c>
-      <c r="AD151" s="19" t="n"/>
+      <c r="AB151" s="19" t="n"/>
+      <c r="AC151" s="20" t="n"/>
+      <c r="AD151" s="21">
+        <f>IF(J151="","",J151*AC151)</f>
+        <v/>
+      </c>
       <c r="AE151" s="19" t="n"/>
       <c r="AF151" s="19" t="n"/>
       <c r="AG151" s="19" t="n"/>
       <c r="AH151" s="19" t="n"/>
       <c r="AI151" s="19" t="n"/>
-      <c r="AJ151" s="16" t="inlineStr">
+      <c r="AJ151" s="19" t="n"/>
+      <c r="AK151" s="16" t="inlineStr">
         <is>
           <t>1 Gerät. Typenschild ist abfotografiert (Foto F-124).</t>
         </is>
       </c>
-      <c r="AK151" s="22" t="n"/>
+      <c r="AL151" s="22" t="n"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="15" t="inlineStr">
@@ -18983,7 +19174,7 @@
       </c>
       <c r="E152" s="16" t="inlineStr">
         <is>
-          <t>Weißes Wandelement mit vier offenen Fächern und darin liegenden Kunststoffwannen, darunter vier rote Doppelhaken. Davor eine weiße Sitzbank aus Holz mit Schublade.</t>
+          <t>Zweiteilige Kindergarderobe: oben ein Wandelement mit vier offenen Fächern und darin liegenden Kunststoffwannen sowie vier roten Doppelhaken, unten eine weiße Sitzbank aus Holz mit Schublade. Beide Teile gehören zusammen.</t>
         </is>
       </c>
       <c r="F152" s="15" t="inlineStr">
@@ -19028,7 +19219,7 @@
       <c r="P152" s="19" t="n"/>
       <c r="Q152" s="20" t="n"/>
       <c r="R152" s="20" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="S152" s="19" t="inlineStr">
         <is>
@@ -19062,27 +19253,24 @@
       </c>
       <c r="Z152" s="19" t="n"/>
       <c r="AA152" s="19" t="n"/>
-      <c r="AB152" s="20" t="n"/>
-      <c r="AC152" s="21">
-        <f>IF(J152="","",J152*AB152)</f>
-        <v/>
-      </c>
-      <c r="AD152" s="19" t="n"/>
+      <c r="AB152" s="19" t="n"/>
+      <c r="AC152" s="20" t="n"/>
+      <c r="AD152" s="21">
+        <f>IF(J152="","",J152*AC152)</f>
+        <v/>
+      </c>
       <c r="AE152" s="19" t="n"/>
       <c r="AF152" s="19" t="n"/>
       <c r="AG152" s="19" t="n"/>
       <c r="AH152" s="19" t="n"/>
       <c r="AI152" s="19" t="n"/>
-      <c r="AJ152" s="16" t="inlineStr">
-        <is>
-          <t>4 gleiche Einheiten laut Erfassungsblatt – abgebildet ist eine davon.</t>
-        </is>
-      </c>
-      <c r="AK152" s="22" t="inlineStr">
-        <is>
-          <t>Offen: gehört die Sitzbank zur Position oder ist sie eigenständig zu erfassen?</t>
-        </is>
-      </c>
+      <c r="AJ152" s="19" t="n"/>
+      <c r="AK152" s="16" t="inlineStr">
+        <is>
+          <t>4 gleiche Garderoben, jede aus Wandelement und Sitzbank – abgebildet ist eine davon.</t>
+        </is>
+      </c>
+      <c r="AL152" s="22" t="n"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="15" t="inlineStr">
@@ -19182,23 +19370,24 @@
       </c>
       <c r="Z153" s="19" t="n"/>
       <c r="AA153" s="19" t="n"/>
-      <c r="AB153" s="20" t="n"/>
-      <c r="AC153" s="21">
-        <f>IF(J153="","",J153*AB153)</f>
-        <v/>
-      </c>
-      <c r="AD153" s="19" t="n"/>
+      <c r="AB153" s="19" t="n"/>
+      <c r="AC153" s="20" t="n"/>
+      <c r="AD153" s="21">
+        <f>IF(J153="","",J153*AC153)</f>
+        <v/>
+      </c>
       <c r="AE153" s="19" t="n"/>
       <c r="AF153" s="19" t="n"/>
       <c r="AG153" s="19" t="n"/>
       <c r="AH153" s="19" t="n"/>
       <c r="AI153" s="19" t="n"/>
-      <c r="AJ153" s="16" t="inlineStr">
+      <c r="AJ153" s="19" t="n"/>
+      <c r="AK153" s="16" t="inlineStr">
         <is>
           <t>2 Sessel, beide abgebildet.</t>
         </is>
       </c>
-      <c r="AK153" s="22" t="n"/>
+      <c r="AL153" s="22" t="n"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="15" t="inlineStr">
@@ -19214,12 +19403,12 @@
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>Leuchte Mr Maria „Miffy“, groß und klein</t>
+          <t>Leuchte Mr Maria „Miffy", groß</t>
         </is>
       </c>
       <c r="E154" s="16" t="inlineStr">
         <is>
-          <t>Zwei Leuchten in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Typenschild: MR LED8. Ein großes und ein kleines Exemplar.</t>
+          <t>Steh-/Tischleuchte in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Typenschild: MR LED8. Das größere der beiden Exemplare.</t>
         </is>
       </c>
       <c r="F154" s="15" t="inlineStr">
@@ -19238,7 +19427,7 @@
         </is>
       </c>
       <c r="I154" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J154" s="17" t="n"/>
       <c r="K154" s="18">
@@ -19264,7 +19453,7 @@
       <c r="P154" s="19" t="n"/>
       <c r="Q154" s="20" t="n"/>
       <c r="R154" s="20" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="S154" s="19" t="inlineStr">
         <is>
@@ -19296,42 +19485,164 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="Z154" s="19" t="n"/>
+      <c r="Z154" s="19" t="inlineStr">
+        <is>
+          <t>Mr Maria</t>
+        </is>
+      </c>
       <c r="AA154" s="19" t="n"/>
-      <c r="AB154" s="20" t="n"/>
-      <c r="AC154" s="21">
-        <f>IF(J154="","",J154*AB154)</f>
-        <v/>
-      </c>
-      <c r="AD154" s="19" t="n"/>
+      <c r="AB154" s="19" t="n"/>
+      <c r="AC154" s="20" t="n"/>
+      <c r="AD154" s="21">
+        <f>IF(J154="","",J154*AC154)</f>
+        <v/>
+      </c>
       <c r="AE154" s="19" t="n"/>
       <c r="AF154" s="19" t="n"/>
       <c r="AG154" s="19" t="n"/>
       <c r="AH154" s="19" t="n"/>
       <c r="AI154" s="19" t="n"/>
-      <c r="AJ154" s="16" t="inlineStr">
-        <is>
-          <t>2 Leuchten: ein großes und ein kleines Exemplar, beide abgebildet. Bei Teilabnahme bitte angeben, welches Exemplar gewünscht ist.</t>
-        </is>
-      </c>
-      <c r="AK154" s="22" t="inlineStr">
-        <is>
-          <t>Zu klären: als eine Position mit 2 Stück lassen oder in groß und klein trennen – die Größen sind unterschiedlich viel wert.</t>
-        </is>
-      </c>
+      <c r="AJ154" s="19" t="n"/>
+      <c r="AK154" s="16" t="inlineStr">
+        <is>
+          <t>1 Leuchte, das große Exemplar – links auf dem Foto.</t>
+        </is>
+      </c>
+      <c r="AL154" s="22" t="n"/>
+    </row>
+    <row r="155" ht="30" customHeight="1">
+      <c r="A155" s="15" t="inlineStr">
+        <is>
+          <t>NU01-22</t>
+        </is>
+      </c>
+      <c r="B155" s="15" t="n"/>
+      <c r="C155" s="15" t="inlineStr">
+        <is>
+          <t>NU01</t>
+        </is>
+      </c>
+      <c r="D155" s="15" t="inlineStr">
+        <is>
+          <t>Leuchte Mr Maria „Miffy", klein</t>
+        </is>
+      </c>
+      <c r="E155" s="16" t="inlineStr">
+        <is>
+          <t>Tischleuchte in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Das kleinere der beiden Exemplare.</t>
+        </is>
+      </c>
+      <c r="F155" s="15" t="inlineStr">
+        <is>
+          <t>Leuchten</t>
+        </is>
+      </c>
+      <c r="G155" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="H155" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I155" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="17" t="n"/>
+      <c r="K155" s="18">
+        <f>I155-IF(J155="",0,J155)</f>
+        <v/>
+      </c>
+      <c r="L155" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="M155" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="N155" s="19" t="n"/>
+      <c r="O155" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="P155" s="19" t="n"/>
+      <c r="Q155" s="20" t="n"/>
+      <c r="R155" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="S155" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="T155" s="21">
+        <f>K155*R155</f>
+        <v/>
+      </c>
+      <c r="U155" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="V155" s="15" t="inlineStr">
+        <is>
+          <t>F-132</t>
+        </is>
+      </c>
+      <c r="W155" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="X155" s="19" t="n"/>
+      <c r="Y155" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="Z155" s="19" t="inlineStr">
+        <is>
+          <t>Mr Maria</t>
+        </is>
+      </c>
+      <c r="AA155" s="19" t="n"/>
+      <c r="AB155" s="19" t="n"/>
+      <c r="AC155" s="20" t="n"/>
+      <c r="AD155" s="21">
+        <f>IF(J155="","",J155*AC155)</f>
+        <v/>
+      </c>
+      <c r="AE155" s="19" t="n"/>
+      <c r="AF155" s="19" t="n"/>
+      <c r="AG155" s="19" t="n"/>
+      <c r="AH155" s="19" t="n"/>
+      <c r="AI155" s="19" t="n"/>
+      <c r="AJ155" s="19" t="n"/>
+      <c r="AK155" s="16" t="inlineStr">
+        <is>
+          <t>1 Leuchte, das kleine Exemplar – rechts auf dem Foto.</t>
+        </is>
+      </c>
+      <c r="AL155" s="22" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AK154"/>
+  <autoFilter ref="A2:AL155"/>
   <mergeCells count="7">
-    <mergeCell ref="AJ1:AK1"/>
+    <mergeCell ref="AK1:AL1"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="P1:Q1"/>
     <mergeCell ref="R1:T1"/>
-    <mergeCell ref="AB1:AE1"/>
-    <mergeCell ref="AF1:AI1"/>
-    <mergeCell ref="U1:AA1"/>
+    <mergeCell ref="U1:AB1"/>
+    <mergeCell ref="AC1:AF1"/>
+    <mergeCell ref="AG1:AJ1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Y3:Y154">
+  <conditionalFormatting sqref="Y3:Y155">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -19342,12 +19653,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H154">
+  <conditionalFormatting sqref="H3:H155">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O154">
+  <conditionalFormatting sqref="O3:O155">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -19380,13 +19691,13 @@
     <dataValidation sqref="Y3:Y803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"verfügbar,reserviert,teilverkauft,verkauft,gespendet,entsorgt"</formula1>
     </dataValidation>
-    <dataValidation sqref="Z3:Z803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AA3:AA803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Webkatalog,Kleinanzeigen,eBay,Direkt,Händler,Verkaufstag"</formula1>
     </dataValidation>
-    <dataValidation sqref="AG3:AG803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AH3:AH803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"offen,bezahlt,teilbezahlt"</formula1>
     </dataValidation>
-    <dataValidation sqref="AH3:AH803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AI3:AI803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Überweisung,bar,PayPal"</formula1>
     </dataValidation>
   </dataValidations>
@@ -19438,7 +19749,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$154)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$155)</f>
         <v/>
       </c>
     </row>
@@ -19449,7 +19760,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Y$3:$Y$154,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Y$3:$Y$155,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -19460,7 +19771,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Y$3:$Y$154,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Y$3:$Y$155,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -19471,7 +19782,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Y$3:$Y$154,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Y$3:$Y$155,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -19482,7 +19793,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Y$3:$Y$154,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Y$3:$Y$155,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -19493,7 +19804,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$154)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$155)</f>
         <v/>
       </c>
     </row>
@@ -19504,7 +19815,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$T$3:$T$154)</f>
+        <f>SUM(Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19522,7 +19833,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$J$3:$J$154)</f>
+        <f>SUM(Artikelstamm!$J$3:$J$155)</f>
         <v/>
       </c>
     </row>
@@ -19533,7 +19844,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$J$3:$J$154,Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT(Artikelstamm!$J$3:$J$155,Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
     </row>
@@ -19566,7 +19877,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AG$3:$AG$154="bezahlt")*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AH$3:$AH$155="bezahlt")*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
     </row>
@@ -19595,7 +19906,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$154,"*verkauft",Artikelstamm!$AF$3:$AF$154,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$155,"*verkauft",Artikelstamm!$AG$3:$AG$155,"")</f>
         <v/>
       </c>
     </row>
@@ -19606,7 +19917,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$154,"*verkauft",Artikelstamm!$AG$3:$AG$154,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$155,"*verkauft",Artikelstamm!$AH$3:$AH$155,"offen")</f>
         <v/>
       </c>
     </row>
@@ -19617,7 +19928,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$154,"reserviert",Artikelstamm!$AI$3:$AI$154,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Y$3:$Y$155,"reserviert",Artikelstamm!$AJ$3:$AJ$155,"")</f>
         <v/>
       </c>
     </row>
@@ -19628,7 +19939,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$R$3:$R$154,"")</f>
+        <f>COUNTIFS(Artikelstamm!$R$3:$R$155,"")</f>
         <v/>
       </c>
     </row>
@@ -19639,7 +19950,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$N$3:$N$154,"")</f>
+        <f>COUNTIFS(Artikelstamm!$N$3:$N$155,"")</f>
         <v/>
       </c>
     </row>
@@ -19679,15 +19990,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$154,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$155,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$154=$A30)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$155=$A30)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$154,$A30,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$155,$A30,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19698,15 +20009,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$154,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$155,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$154=$A31)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$155=$A31)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$154,$A31,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$155,$A31,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19717,15 +20028,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$154,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$155,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$154=$A32)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$155=$A32)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$154,$A32,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$155,$A32,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19784,15 +20095,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A37)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A37)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A37,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A37,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19803,15 +20114,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A38)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A38)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A38,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A38,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19822,15 +20133,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A39)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A39)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A39,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A39,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19841,15 +20152,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A40)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A40)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A40,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A40,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19860,15 +20171,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A41)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A41)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A41,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A41,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19879,15 +20190,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A42)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A42)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A42,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A42,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19898,15 +20209,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A43)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A43)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A43,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A43,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19917,15 +20228,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A44)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A44)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A44,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A44,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19936,15 +20247,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A45)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A45)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A45,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A45,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19955,15 +20266,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A46)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A46)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A46,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A46,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19974,15 +20285,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A47)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A47)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A47,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A47,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -19993,15 +20304,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A48)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A48)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A48,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A48,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20012,15 +20323,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A49)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A49)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A49,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A49,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20031,15 +20342,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$F$3:$F$154,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$F$3:$F$155,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$154=$A50)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$F$3:$F$155=$A50)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$F$3:$F$154,$A50,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$F$3:$F$155,$A50,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20098,15 +20409,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A55)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A55)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A55,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A55,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20117,15 +20428,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A56)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A56)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A56,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A56,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20136,15 +20447,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A57)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A57)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A57,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A57,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20155,15 +20466,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A58)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A58)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A58,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A58,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20174,15 +20485,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A59)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A59)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A59,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A59,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20193,15 +20504,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A60)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A60)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A60,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A60,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20212,15 +20523,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A61)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A61)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A61,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A61,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20231,15 +20542,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A62)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A62)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A62,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A62,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20250,15 +20561,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A63)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A63)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A63,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A63,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20269,15 +20580,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A64)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A64)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A64,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A64,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20288,15 +20599,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A65)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A65)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A65,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A65,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20307,15 +20618,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A66)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A66)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A66,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A66,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20326,15 +20637,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A67)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A67)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A67,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A67,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20345,15 +20656,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A68)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A68)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A68,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A68,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20364,15 +20675,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A69)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A69)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A69,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A69,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20383,15 +20694,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A70)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A70)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A70,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A70,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20402,15 +20713,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A71)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A71)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A71,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A71,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20421,15 +20732,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A72)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A72)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A72,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A72,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20440,15 +20751,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$154,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$155,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$154=$A73)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$155=$A73)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$154,$A73,Artikelstamm!$T$3:$T$154)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$155,$A73,Artikelstamm!$T$3:$T$155)</f>
         <v/>
       </c>
     </row>
@@ -20502,11 +20813,11 @@
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$AA$3:$AA$155,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A78)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AA$3:$AA$155=$A78)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
     </row>
@@ -20517,11 +20828,11 @@
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$AA$3:$AA$155,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A79)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AA$3:$AA$155=$A79)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
     </row>
@@ -20532,11 +20843,11 @@
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$AA$3:$AA$155,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A80)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AA$3:$AA$155=$A80)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
     </row>
@@ -20547,11 +20858,11 @@
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$AA$3:$AA$155,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A81)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AA$3:$AA$155=$A81)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
     </row>
@@ -20562,11 +20873,11 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AA$3:$AA$155,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A82)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AA$3:$AA$155=$A82)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
     </row>
@@ -20577,11 +20888,11 @@
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$154,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AA$3:$AA$155,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$Z$3:$Z$154=$A83)*Artikelstamm!$J$3:$J$154*Artikelstamm!$AB$3:$AB$154)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AA$3:$AA$155=$A83)*Artikelstamm!$J$3:$J$155*Artikelstamm!$AC$3:$AC$155)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -1329,7 +1329,7 @@
       </c>
       <c r="H3" s="15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I3" s="17" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="M3" s="15" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="N3" s="19" t="n"/>
@@ -1359,7 +1359,7 @@
       <c r="P3" s="19" t="n"/>
       <c r="Q3" s="20" t="n"/>
       <c r="R3" s="20" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="S3" s="19" t="inlineStr">
         <is>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M15" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N15" s="19" t="n"/>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="M16" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N16" s="19" t="n"/>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="M17" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N17" s="19" t="n"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="M18" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N18" s="19" t="n"/>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="M19" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N19" s="19" t="n"/>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="M20" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N20" s="19" t="n"/>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="M25" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N25" s="19" t="n"/>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="M26" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N26" s="19" t="n"/>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="M27" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N27" s="19" t="n"/>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="M35" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N35" s="19" t="n"/>
@@ -5721,7 +5721,7 @@
       </c>
       <c r="M39" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N39" s="19" t="n"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N112" s="19" t="n"/>
@@ -14463,7 +14463,7 @@
       </c>
       <c r="M113" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N113" s="19" t="n"/>
@@ -14705,7 +14705,7 @@
       </c>
       <c r="M115" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N115" s="19" t="n"/>
@@ -16177,7 +16177,7 @@
       </c>
       <c r="M127" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N127" s="19" t="n"/>
@@ -16298,7 +16298,7 @@
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N128" s="19" t="n"/>
@@ -16661,7 +16661,7 @@
       </c>
       <c r="M131" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N131" s="19" t="n"/>
@@ -16782,7 +16782,7 @@
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N132" s="19" t="n"/>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="M147" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N147" s="19" t="n"/>
@@ -18723,7 +18723,7 @@
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N148" s="19" t="n"/>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="N152" s="19" t="n"/>
@@ -19471,7 +19471,7 @@
       </c>
       <c r="V154" s="15" t="inlineStr">
         <is>
-          <t>F-132</t>
+          <t>F-135</t>
         </is>
       </c>
       <c r="W154" s="19" t="inlineStr">
@@ -19505,7 +19505,7 @@
       <c r="AJ154" s="19" t="n"/>
       <c r="AK154" s="16" t="inlineStr">
         <is>
-          <t>1 Leuchte, das große Exemplar – links auf dem Foto.</t>
+          <t>1 Leuchte, das große Exemplar.</t>
         </is>
       </c>
       <c r="AL154" s="22" t="n"/>
@@ -19529,7 +19529,7 @@
       </c>
       <c r="E155" s="16" t="inlineStr">
         <is>
-          <t>Tischleuchte in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Das kleinere der beiden Exemplare.</t>
+          <t>Tischleuchte in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Die kleinere Ausführung.</t>
         </is>
       </c>
       <c r="F155" s="15" t="inlineStr">
@@ -19548,7 +19548,7 @@
         </is>
       </c>
       <c r="I155" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J155" s="17" t="n"/>
       <c r="K155" s="18">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="V155" s="15" t="inlineStr">
         <is>
-          <t>F-132</t>
+          <t>F-136</t>
         </is>
       </c>
       <c r="W155" s="19" t="inlineStr">
@@ -19626,7 +19626,7 @@
       <c r="AJ155" s="19" t="n"/>
       <c r="AK155" s="16" t="inlineStr">
         <is>
-          <t>1 Leuchte, das kleine Exemplar – rechts auf dem Foto.</t>
+          <t>3 gleiche Leuchten in der kleinen Ausführung – abgebildet ist eine davon.</t>
         </is>
       </c>
       <c r="AL155" s="22" t="n"/>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -5278,7 +5278,7 @@
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J35" s="17" t="n">
@@ -5308,7 +5308,7 @@
       <c r="Q35" s="19" t="n"/>
       <c r="R35" s="20" t="n"/>
       <c r="S35" s="20" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="T35" s="19" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
       </c>
       <c r="N158" s="15" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="O158" s="19" t="n"/>
@@ -20131,7 +20131,7 @@
       <c r="Q158" s="19" t="n"/>
       <c r="R158" s="20" t="n"/>
       <c r="S158" s="20" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="T158" s="19" t="inlineStr">
         <is>
@@ -20186,11 +20186,7 @@
           <t>8 Stück – abgebildet ist einer davon. Das Logo auf der Lehne ist auf Foto F-143 zu sehen.</t>
         </is>
       </c>
-      <c r="AM158" s="22" t="inlineStr">
-        <is>
-          <t>Stückzahl auf dem Erfassungsblatt korrigiert – bitte 8 bestätigen.</t>
-        </is>
-      </c>
+      <c r="AM158" s="22" t="n"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="15" t="inlineStr">
@@ -21041,12 +21037,12 @@
       </c>
       <c r="E166" s="15" t="inlineStr">
         <is>
-          <t>IKEA Mammut Kinderstuhl, rosa und grün</t>
+          <t>IKEA Mammut Kinderstuhl, verschiedene Farben</t>
         </is>
       </c>
       <c r="F166" s="16" t="inlineStr">
         <is>
-          <t>Kinderstuhl aus Kunststoff, IKEA Mammut. Stand im Freien, Farbe deutlich ausgeblichen.</t>
+          <t>Kinderstuhl aus Kunststoff, IKEA Mammut, in verschiedenen Farben. Stand im Freien, Farben deutlich ausgeblichen.</t>
         </is>
       </c>
       <c r="G166" s="15" t="inlineStr">
@@ -21143,10 +21139,14 @@
       <c r="AK166" s="19" t="n"/>
       <c r="AL166" s="16" t="inlineStr">
         <is>
-          <t>3 Stühle: zwei rosa, einer grün. Abgebildet ist ein rosa Stuhl, der grüne auf Foto F-159.</t>
-        </is>
-      </c>
-      <c r="AM166" s="22" t="n"/>
+          <t>Bisher erfasst: zwei rosa und einer grün. Es gibt sie in weiteren Farben, auch in den Außenanlagen – Stückzahl wird am Ende des Rundgangs zusammengezählt.</t>
+        </is>
+      </c>
+      <c r="AM166" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN – Stueckzahl und Farben unvollstaendig. Die Nutzerin liefert die restlichen Fotos am Ende des Rundgangs nach; dann wird diese Position auf die Gesamtzahl gebracht und die Post-it-Nummern der anderen Raeume kommen in Weitere_ArtNr.</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="15" t="inlineStr">
@@ -21163,12 +21163,12 @@
       </c>
       <c r="E167" s="15" t="inlineStr">
         <is>
-          <t>Konsole Bambus mit weißer Ablagewanne</t>
+          <t>Ablagetisch Bambus mit Wanne</t>
         </is>
       </c>
       <c r="F167" s="16" t="inlineStr">
         <is>
-          <t>Schmales Gestell aus Bambus mit Lattenboden und aufgelegter weißer Wanne als Ablage.</t>
+          <t>Schmales Gestell aus Bambus mit Lattenboden und aufgelegter weißer Wanne. Im Haus als Aufbewahrung und Servierwagen genutzt.</t>
         </is>
       </c>
       <c r="G167" s="15" t="inlineStr">
@@ -21517,12 +21517,12 @@
       </c>
       <c r="E170" s="15" t="inlineStr">
         <is>
-          <t>Sitztier Elefant, weiß</t>
+          <t>Sitztier Elefant, weiß und schwarz</t>
         </is>
       </c>
       <c r="F170" s="16" t="inlineStr">
         <is>
-          <t>Sitztier in Elefantenform aus weißem Kunststoff. Am Ohr ein ovales Metallplättchen mit eingravierter Signatur.</t>
+          <t>Sitztier in Elefantenform aus Kunststoff, ein weißes und ein schwarzes Exemplar in gleicher Größe. Am Ohr ein ovales Metallplättchen mit eingravierter Signatur.</t>
         </is>
       </c>
       <c r="G170" s="15" t="inlineStr">
@@ -21541,7 +21541,7 @@
         </is>
       </c>
       <c r="J170" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K170" s="17" t="n"/>
       <c r="L170" s="18">
@@ -21615,12 +21615,12 @@
       <c r="AK170" s="19" t="n"/>
       <c r="AL170" s="16" t="inlineStr">
         <is>
-          <t>1 Elefant. Laut Haus gibt es dazu einen schwarzen in gleicher Größe und einen kleineren schwarzen; beide noch ohne Foto.</t>
+          <t>2 Elefanten, weiß und schwarz. Abgebildet ist der weiße; der schwarze wird nachfotografiert. Ein kleinerer schwarzer folgt als eigene Position.</t>
         </is>
       </c>
       <c r="AM170" s="22" t="inlineStr">
         <is>
-          <t>NICHT VEROEFFENTLICHEN, bis die Marke geklaert ist: Form und Plaettchen sprechen fuer einen Vitra Eames Elephant (gebraucht 150-280 EUR), ein Nachbau waere 20-40 EUR wert. Nahaufnahme des Plaettchens und der Unterseite anfordern.</t>
+          <t>OFFEN – NICHT VEROEFFENTLICHEN, bis die Marke geklaert ist: Form und Signaturplaettchen sprechen fuer einen Vitra Eames Elephant (gebraucht 150-280 EUR je Stueck), ein Nachbau waere 20-40 EUR wert. Nahaufnahme des Plaettchens und der Unterseite steht aus; die Nutzerin liefert sie am Ende des Rundgangs. Der kleinere schwarze wird dann eine eigene Position.</t>
         </is>
       </c>
     </row>
@@ -22111,12 +22111,12 @@
       </c>
       <c r="E175" s="15" t="inlineStr">
         <is>
-          <t>Konferenztisch weiß aus Segmenten</t>
+          <t>Kindertisch weiß aus vier Segmenten</t>
         </is>
       </c>
       <c r="F175" s="16" t="inlineStr">
         <is>
-          <t>Mehrere trapezförmige Tischsegmente mit weißer Platte, Multiplex-Kante und verchromten Rundfüßen. Zusammengestellt ergeben sie einen großen Besprechungstisch, einzeln sind sie als Gruppentische nutzbar.</t>
+          <t>Vier trapezförmige Tischsegmente mit weißer Platte, Multiplex-Kante und verchromten Rundfüßen in Kinderhöhe. Zusammengestellt ergeben sie einen großen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
         </is>
       </c>
       <c r="G175" s="15" t="inlineStr">
@@ -22161,7 +22161,7 @@
       <c r="Q175" s="19" t="n"/>
       <c r="R175" s="20" t="n"/>
       <c r="S175" s="20" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="T175" s="19" t="inlineStr">
         <is>
@@ -22209,14 +22209,10 @@
       <c r="AK175" s="19" t="n"/>
       <c r="AL175" s="16" t="inlineStr">
         <is>
-          <t>1 Tischgruppe. Bitte die Anzahl der Segmente bestätigen – auf dem Foto sind es etwa fünf.</t>
-        </is>
-      </c>
-      <c r="AM175" s="22" t="inlineStr">
-        <is>
-          <t>Anzahl der Segmente unbestätigt; der Preis hängt daran.</t>
-        </is>
-      </c>
+          <t>1 Tischgruppe aus vier Segmenten.</t>
+        </is>
+      </c>
+      <c r="AM175" s="22" t="n"/>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="15" t="inlineStr">

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$176</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM176"/>
+  <dimension ref="A1:AM185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22332,8 +22332,1098 @@
       </c>
       <c r="AM176" s="22" t="n"/>
     </row>
+    <row r="177" ht="30" customHeight="1">
+      <c r="A177" s="15" t="inlineStr">
+        <is>
+          <t>NU03-02</t>
+        </is>
+      </c>
+      <c r="B177" s="15" t="n"/>
+      <c r="C177" s="15" t="n"/>
+      <c r="D177" s="15" t="inlineStr">
+        <is>
+          <t>NU03</t>
+        </is>
+      </c>
+      <c r="E177" s="15" t="inlineStr">
+        <is>
+          <t>Stockbett weiß mit Absturzsicherung</t>
+        </is>
+      </c>
+      <c r="F177" s="16" t="inlineStr">
+        <is>
+          <t>Etagenbett in Weiß mit sichtbaren Multiplex-Kanten, abgerundeten Ausschnitten und durchgehender Absturzsicherung oben. Solide Bauweise aus dem Kita-Betrieb.</t>
+        </is>
+      </c>
+      <c r="G177" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H177" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="I177" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J177" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K177" s="17" t="n"/>
+      <c r="L177" s="18">
+        <f>J177-IF(K177="",0,K177)</f>
+        <v/>
+      </c>
+      <c r="M177" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N177" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O177" s="19" t="n"/>
+      <c r="P177" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q177" s="19" t="n"/>
+      <c r="R177" s="20" t="n"/>
+      <c r="S177" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="T177" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U177" s="21">
+        <f>L177*S177</f>
+        <v/>
+      </c>
+      <c r="V177" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W177" s="15" t="inlineStr">
+        <is>
+          <t>F-175</t>
+        </is>
+      </c>
+      <c r="X177" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y177" s="19" t="n"/>
+      <c r="Z177" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA177" s="19" t="n"/>
+      <c r="AB177" s="19" t="n"/>
+      <c r="AC177" s="19" t="n"/>
+      <c r="AD177" s="20" t="n"/>
+      <c r="AE177" s="21">
+        <f>IF(K177="","",K177*AD177)</f>
+        <v/>
+      </c>
+      <c r="AF177" s="19" t="n"/>
+      <c r="AG177" s="19" t="n"/>
+      <c r="AH177" s="19" t="n"/>
+      <c r="AI177" s="19" t="n"/>
+      <c r="AJ177" s="19" t="n"/>
+      <c r="AK177" s="19" t="n"/>
+      <c r="AL177" s="16" t="inlineStr">
+        <is>
+          <t>4 Betten: 2 aufgebaut im Schlafraum, 2 zusätzlich eingelagert.</t>
+        </is>
+      </c>
+      <c r="AM177" s="22" t="inlineStr">
+        <is>
+          <t>Stueckzahl aus der Bemerkung "+2 lagernd" auf 4 gesetzt - bitte bestaetigen. Offen: gehen die Matratzen mit?</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="30" customHeight="1">
+      <c r="A178" s="15" t="inlineStr">
+        <is>
+          <t>NU03-03</t>
+        </is>
+      </c>
+      <c r="B178" s="15" t="n"/>
+      <c r="C178" s="15" t="n"/>
+      <c r="D178" s="15" t="inlineStr">
+        <is>
+          <t>NU03</t>
+        </is>
+      </c>
+      <c r="E178" s="15" t="inlineStr">
+        <is>
+          <t>Wesco Spielküche, mehrteilig</t>
+        </is>
+      </c>
+      <c r="F178" s="16" t="inlineStr">
+        <is>
+          <t>Spielküche von Wesco aus Birke-Multiplex: Spülmodul mit Becken, Kochmodul mit Drehknöpfen, Backofenmodul mit Sichtfenster sowie Kühl- und Gefriermodule. Weiße Fronten mit Holzgriffen, Module einzeln stellbar.</t>
+        </is>
+      </c>
+      <c r="G178" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H178" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="I178" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J178" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K178" s="17" t="n"/>
+      <c r="L178" s="18">
+        <f>J178-IF(K178="",0,K178)</f>
+        <v/>
+      </c>
+      <c r="M178" s="15" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N178" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O178" s="19" t="n"/>
+      <c r="P178" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q178" s="19" t="n"/>
+      <c r="R178" s="20" t="n"/>
+      <c r="S178" s="20" t="n">
+        <v>650</v>
+      </c>
+      <c r="T178" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U178" s="21">
+        <f>L178*S178</f>
+        <v/>
+      </c>
+      <c r="V178" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W178" s="15" t="inlineStr">
+        <is>
+          <t>F-176</t>
+        </is>
+      </c>
+      <c r="X178" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y178" s="19" t="n"/>
+      <c r="Z178" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA178" s="19" t="inlineStr">
+        <is>
+          <t>Wesco</t>
+        </is>
+      </c>
+      <c r="AB178" s="19" t="n"/>
+      <c r="AC178" s="19" t="n"/>
+      <c r="AD178" s="20" t="n"/>
+      <c r="AE178" s="21">
+        <f>IF(K178="","",K178*AD178)</f>
+        <v/>
+      </c>
+      <c r="AF178" s="19" t="n"/>
+      <c r="AG178" s="19" t="n"/>
+      <c r="AH178" s="19" t="n"/>
+      <c r="AI178" s="19" t="n"/>
+      <c r="AJ178" s="19" t="n"/>
+      <c r="AK178" s="19" t="n"/>
+      <c r="AL178" s="16" t="inlineStr">
+        <is>
+          <t>1 Küche aus mehreren Modulen – auf dem Foto sind etwa fünf zu sehen. Bitte die Anzahl der Module bestätigen, der Preis hängt daran.</t>
+        </is>
+      </c>
+      <c r="AM178" s="22" t="inlineStr">
+        <is>
+          <t>Anzahl der Module unbestaetigt. Wesco ist institutionelle Qualitaet, neu kostet ein Modul 300-600 EUR - das ist nach dem Vitra Alcove die wertvollste Position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="30" customHeight="1">
+      <c r="A179" s="15" t="inlineStr">
+        <is>
+          <t>NU03-04</t>
+        </is>
+      </c>
+      <c r="B179" s="15" t="n"/>
+      <c r="C179" s="15" t="n"/>
+      <c r="D179" s="15" t="inlineStr">
+        <is>
+          <t>NU03</t>
+        </is>
+      </c>
+      <c r="E179" s="15" t="inlineStr">
+        <is>
+          <t>Wesco Bügelbrett und Wäscheständer, Kindergröße</t>
+        </is>
+      </c>
+      <c r="F179" s="16" t="inlineStr">
+        <is>
+          <t>Kinder-Bügelbrett von Wesco aus Birke-Multiplex mit gelbem Aufdruck, klappbar, sowie ein passender Wäscheständer aus Holz mit Schnüren.</t>
+        </is>
+      </c>
+      <c r="G179" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H179" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="I179" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J179" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K179" s="17" t="n"/>
+      <c r="L179" s="18">
+        <f>J179-IF(K179="",0,K179)</f>
+        <v/>
+      </c>
+      <c r="M179" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N179" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O179" s="19" t="n"/>
+      <c r="P179" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q179" s="19" t="n"/>
+      <c r="R179" s="20" t="n"/>
+      <c r="S179" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T179" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U179" s="21">
+        <f>L179*S179</f>
+        <v/>
+      </c>
+      <c r="V179" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W179" s="15" t="inlineStr">
+        <is>
+          <t>F-177</t>
+        </is>
+      </c>
+      <c r="X179" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y179" s="19" t="n"/>
+      <c r="Z179" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA179" s="19" t="inlineStr">
+        <is>
+          <t>Wesco</t>
+        </is>
+      </c>
+      <c r="AB179" s="19" t="n"/>
+      <c r="AC179" s="19" t="n"/>
+      <c r="AD179" s="20" t="n"/>
+      <c r="AE179" s="21">
+        <f>IF(K179="","",K179*AD179)</f>
+        <v/>
+      </c>
+      <c r="AF179" s="19" t="n"/>
+      <c r="AG179" s="19" t="n"/>
+      <c r="AH179" s="19" t="n"/>
+      <c r="AI179" s="19" t="n"/>
+      <c r="AJ179" s="19" t="n"/>
+      <c r="AK179" s="19" t="n"/>
+      <c r="AL179" s="16" t="inlineStr">
+        <is>
+          <t>2 Teile: ein Bügelbrett und ein Wäscheständer, beide auf Foto F-178 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AM179" s="22" t="n"/>
+    </row>
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="15" t="inlineStr">
+        <is>
+          <t>NU03-05</t>
+        </is>
+      </c>
+      <c r="B180" s="15" t="n"/>
+      <c r="C180" s="15" t="n"/>
+      <c r="D180" s="15" t="inlineStr">
+        <is>
+          <t>NU03</t>
+        </is>
+      </c>
+      <c r="E180" s="15" t="inlineStr">
+        <is>
+          <t>Flumi Kindersessel, beige Bouclé</t>
+        </is>
+      </c>
+      <c r="F180" s="16" t="inlineStr">
+        <is>
+          <t>Kindersessel von Flumi, beigefarbener Bouclé-Bezug, runde Form mit zwei kleinen Ohren an der Lehne. Markenetikett an der Vorderseite.</t>
+        </is>
+      </c>
+      <c r="G180" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H180" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="I180" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J180" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" s="17" t="n"/>
+      <c r="L180" s="18">
+        <f>J180-IF(K180="",0,K180)</f>
+        <v/>
+      </c>
+      <c r="M180" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N180" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O180" s="19" t="n"/>
+      <c r="P180" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q180" s="19" t="n"/>
+      <c r="R180" s="20" t="n"/>
+      <c r="S180" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T180" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U180" s="21">
+        <f>L180*S180</f>
+        <v/>
+      </c>
+      <c r="V180" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W180" s="15" t="inlineStr">
+        <is>
+          <t>F-179</t>
+        </is>
+      </c>
+      <c r="X180" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y180" s="19" t="n"/>
+      <c r="Z180" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA180" s="19" t="inlineStr">
+        <is>
+          <t>Flumi</t>
+        </is>
+      </c>
+      <c r="AB180" s="19" t="n"/>
+      <c r="AC180" s="19" t="n"/>
+      <c r="AD180" s="20" t="n"/>
+      <c r="AE180" s="21">
+        <f>IF(K180="","",K180*AD180)</f>
+        <v/>
+      </c>
+      <c r="AF180" s="19" t="n"/>
+      <c r="AG180" s="19" t="n"/>
+      <c r="AH180" s="19" t="n"/>
+      <c r="AI180" s="19" t="n"/>
+      <c r="AJ180" s="19" t="n"/>
+      <c r="AK180" s="19" t="n"/>
+      <c r="AL180" s="16" t="inlineStr">
+        <is>
+          <t>1 Sessel.</t>
+        </is>
+      </c>
+      <c r="AM180" s="22" t="n"/>
+    </row>
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="15" t="inlineStr">
+        <is>
+          <t>NU03-06</t>
+        </is>
+      </c>
+      <c r="B181" s="15" t="n"/>
+      <c r="C181" s="15" t="n"/>
+      <c r="D181" s="15" t="inlineStr">
+        <is>
+          <t>NU03</t>
+        </is>
+      </c>
+      <c r="E181" s="15" t="inlineStr">
+        <is>
+          <t>Wandregal Kiefer mit Fächern</t>
+        </is>
+      </c>
+      <c r="F181" s="16" t="inlineStr">
+        <is>
+          <t>Wandregal aus Kiefer massiv mit eingenuteten Trennbrettern, drei Fächer.</t>
+        </is>
+      </c>
+      <c r="G181" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H181" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="I181" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J181" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K181" s="17" t="n"/>
+      <c r="L181" s="18">
+        <f>J181-IF(K181="",0,K181)</f>
+        <v/>
+      </c>
+      <c r="M181" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N181" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O181" s="19" t="n"/>
+      <c r="P181" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q181" s="19" t="n"/>
+      <c r="R181" s="20" t="n"/>
+      <c r="S181" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T181" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U181" s="21">
+        <f>L181*S181</f>
+        <v/>
+      </c>
+      <c r="V181" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W181" s="15" t="inlineStr">
+        <is>
+          <t>F-180</t>
+        </is>
+      </c>
+      <c r="X181" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y181" s="19" t="n"/>
+      <c r="Z181" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA181" s="19" t="n"/>
+      <c r="AB181" s="19" t="n"/>
+      <c r="AC181" s="19" t="n"/>
+      <c r="AD181" s="20" t="n"/>
+      <c r="AE181" s="21">
+        <f>IF(K181="","",K181*AD181)</f>
+        <v/>
+      </c>
+      <c r="AF181" s="19" t="n"/>
+      <c r="AG181" s="19" t="n"/>
+      <c r="AH181" s="19" t="n"/>
+      <c r="AI181" s="19" t="n"/>
+      <c r="AJ181" s="19" t="n"/>
+      <c r="AK181" s="19" t="n"/>
+      <c r="AL181" s="16" t="inlineStr">
+        <is>
+          <t>2 Regale – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AM181" s="22" t="n"/>
+    </row>
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="15" t="inlineStr">
+        <is>
+          <t>NU03-07</t>
+        </is>
+      </c>
+      <c r="B182" s="15" t="n"/>
+      <c r="C182" s="15" t="n"/>
+      <c r="D182" s="15" t="inlineStr">
+        <is>
+          <t>NU03</t>
+        </is>
+      </c>
+      <c r="E182" s="15" t="inlineStr">
+        <is>
+          <t>Offenes Regal Kiefer, drei Fächer</t>
+        </is>
+      </c>
+      <c r="F182" s="16" t="inlineStr">
+        <is>
+          <t>Niedriges offenes Regal aus Kiefer massiv mit eingenuteten Trennbrettern, drei Fächer, zum Stellen oder Stapeln.</t>
+        </is>
+      </c>
+      <c r="G182" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H182" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="I182" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J182" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K182" s="17" t="n"/>
+      <c r="L182" s="18">
+        <f>J182-IF(K182="",0,K182)</f>
+        <v/>
+      </c>
+      <c r="M182" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N182" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O182" s="19" t="n"/>
+      <c r="P182" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q182" s="19" t="n"/>
+      <c r="R182" s="20" t="n"/>
+      <c r="S182" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T182" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U182" s="21">
+        <f>L182*S182</f>
+        <v/>
+      </c>
+      <c r="V182" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W182" s="15" t="inlineStr">
+        <is>
+          <t>F-181</t>
+        </is>
+      </c>
+      <c r="X182" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y182" s="19" t="n"/>
+      <c r="Z182" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA182" s="19" t="n"/>
+      <c r="AB182" s="19" t="n"/>
+      <c r="AC182" s="19" t="n"/>
+      <c r="AD182" s="20" t="n"/>
+      <c r="AE182" s="21">
+        <f>IF(K182="","",K182*AD182)</f>
+        <v/>
+      </c>
+      <c r="AF182" s="19" t="n"/>
+      <c r="AG182" s="19" t="n"/>
+      <c r="AH182" s="19" t="n"/>
+      <c r="AI182" s="19" t="n"/>
+      <c r="AJ182" s="19" t="n"/>
+      <c r="AK182" s="19" t="n"/>
+      <c r="AL182" s="16" t="inlineStr">
+        <is>
+          <t>1 Regal. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM182" s="22" t="n"/>
+    </row>
+    <row r="183" ht="30" customHeight="1">
+      <c r="A183" s="15" t="inlineStr">
+        <is>
+          <t>NU03-08</t>
+        </is>
+      </c>
+      <c r="B183" s="15" t="n"/>
+      <c r="C183" s="15" t="n"/>
+      <c r="D183" s="15" t="inlineStr">
+        <is>
+          <t>NU03</t>
+        </is>
+      </c>
+      <c r="E183" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Malm Kommode, 3 Schubladen, weiß</t>
+        </is>
+      </c>
+      <c r="F183" s="16" t="inlineStr">
+        <is>
+          <t>Kommode IKEA Malm in Weiß mit drei Schubladen, griffmuldenlos. Fronten mit Beschriftungsaufklebern, die sich abziehen lassen.</t>
+        </is>
+      </c>
+      <c r="G183" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H183" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="I183" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J183" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K183" s="17" t="n"/>
+      <c r="L183" s="18">
+        <f>J183-IF(K183="",0,K183)</f>
+        <v/>
+      </c>
+      <c r="M183" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N183" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O183" s="19" t="n"/>
+      <c r="P183" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q183" s="19" t="n"/>
+      <c r="R183" s="20" t="n"/>
+      <c r="S183" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T183" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U183" s="21">
+        <f>L183*S183</f>
+        <v/>
+      </c>
+      <c r="V183" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W183" s="15" t="inlineStr">
+        <is>
+          <t>F-183</t>
+        </is>
+      </c>
+      <c r="X183" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y183" s="19" t="n"/>
+      <c r="Z183" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA183" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB183" s="19" t="n"/>
+      <c r="AC183" s="19" t="n"/>
+      <c r="AD183" s="20" t="n"/>
+      <c r="AE183" s="21">
+        <f>IF(K183="","",K183*AD183)</f>
+        <v/>
+      </c>
+      <c r="AF183" s="19" t="n"/>
+      <c r="AG183" s="19" t="n"/>
+      <c r="AH183" s="19" t="n"/>
+      <c r="AI183" s="19" t="n"/>
+      <c r="AJ183" s="19" t="n"/>
+      <c r="AK183" s="19" t="n"/>
+      <c r="AL183" s="16" t="inlineStr">
+        <is>
+          <t>2 Kommoden – abgebildet ist eine davon, die zweite steht rechts daneben.</t>
+        </is>
+      </c>
+      <c r="AM183" s="22" t="n"/>
+    </row>
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="15" t="inlineStr">
+        <is>
+          <t>NU03-09</t>
+        </is>
+      </c>
+      <c r="B184" s="15" t="n"/>
+      <c r="C184" s="15" t="n"/>
+      <c r="D184" s="15" t="inlineStr">
+        <is>
+          <t>NU03</t>
+        </is>
+      </c>
+      <c r="E184" s="15" t="inlineStr">
+        <is>
+          <t>Treppenregal Kiefer mit Wannen</t>
+        </is>
+      </c>
+      <c r="F184" s="16" t="inlineStr">
+        <is>
+          <t>Stufenförmiges Regal aus Kiefer massiv mit eingehängten Kunststoffwannen, als Raumteiler und Spielzeugaufbewahrung genutzt.</t>
+        </is>
+      </c>
+      <c r="G184" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H184" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="I184" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J184" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K184" s="17" t="n"/>
+      <c r="L184" s="18">
+        <f>J184-IF(K184="",0,K184)</f>
+        <v/>
+      </c>
+      <c r="M184" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N184" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O184" s="19" t="n"/>
+      <c r="P184" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q184" s="19" t="n"/>
+      <c r="R184" s="20" t="n"/>
+      <c r="S184" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T184" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U184" s="21">
+        <f>L184*S184</f>
+        <v/>
+      </c>
+      <c r="V184" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W184" s="15" t="inlineStr">
+        <is>
+          <t>F-182</t>
+        </is>
+      </c>
+      <c r="X184" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y184" s="19" t="n"/>
+      <c r="Z184" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA184" s="19" t="n"/>
+      <c r="AB184" s="19" t="n"/>
+      <c r="AC184" s="19" t="n"/>
+      <c r="AD184" s="20" t="n"/>
+      <c r="AE184" s="21">
+        <f>IF(K184="","",K184*AD184)</f>
+        <v/>
+      </c>
+      <c r="AF184" s="19" t="n"/>
+      <c r="AG184" s="19" t="n"/>
+      <c r="AH184" s="19" t="n"/>
+      <c r="AI184" s="19" t="n"/>
+      <c r="AJ184" s="19" t="n"/>
+      <c r="AK184" s="19" t="n"/>
+      <c r="AL184" s="16" t="inlineStr">
+        <is>
+          <t>2 Regale einschließlich der eingehängten Wannen – abgebildet ist eines davon. Der Inhalt der Wannen gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM184" s="22" t="n"/>
+    </row>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="15" t="inlineStr">
+        <is>
+          <t>NU03-10</t>
+        </is>
+      </c>
+      <c r="B185" s="15" t="n"/>
+      <c r="C185" s="15" t="n"/>
+      <c r="D185" s="15" t="inlineStr">
+        <is>
+          <t>NU03</t>
+        </is>
+      </c>
+      <c r="E185" s="15" t="inlineStr">
+        <is>
+          <t>Kinderhochstuhl Kunststoff mit Gurt</t>
+        </is>
+      </c>
+      <c r="F185" s="16" t="inlineStr">
+        <is>
+          <t>Hochstuhl mit weißer Kunststoffschale, grauen Stahlbeinen und Sicherheitsgurt. Ohne Esstablett.</t>
+        </is>
+      </c>
+      <c r="G185" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H185" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="I185" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J185" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="K185" s="17" t="n"/>
+      <c r="L185" s="18">
+        <f>J185-IF(K185="",0,K185)</f>
+        <v/>
+      </c>
+      <c r="M185" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N185" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O185" s="19" t="n"/>
+      <c r="P185" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q185" s="19" t="n"/>
+      <c r="R185" s="20" t="n"/>
+      <c r="S185" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U185" s="21">
+        <f>L185*S185</f>
+        <v/>
+      </c>
+      <c r="V185" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W185" s="15" t="inlineStr">
+        <is>
+          <t>F-184</t>
+        </is>
+      </c>
+      <c r="X185" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y185" s="19" t="n"/>
+      <c r="Z185" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA185" s="19" t="n"/>
+      <c r="AB185" s="19" t="n"/>
+      <c r="AC185" s="19" t="n"/>
+      <c r="AD185" s="20" t="n"/>
+      <c r="AE185" s="21">
+        <f>IF(K185="","",K185*AD185)</f>
+        <v/>
+      </c>
+      <c r="AF185" s="19" t="n"/>
+      <c r="AG185" s="19" t="n"/>
+      <c r="AH185" s="19" t="n"/>
+      <c r="AI185" s="19" t="n"/>
+      <c r="AJ185" s="19" t="n"/>
+      <c r="AK185" s="19" t="n"/>
+      <c r="AL185" s="16" t="inlineStr">
+        <is>
+          <t>9 Stühle – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AM185" s="22" t="inlineStr">
+        <is>
+          <t>Stueckzahl auf dem Erfassungsblatt mehrfach korrigiert, gelesen als 9 - bitte bestaetigen. Form spricht fuer IKEA Antilop, ein Etikett war nicht zu sehen; deshalb keine Marke eingetragen.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AM176"/>
+  <autoFilter ref="A2:AM185"/>
   <mergeCells count="7">
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="S1:U1"/>
@@ -22343,7 +23433,7 @@
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AD1:AG1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z176">
+  <conditionalFormatting sqref="Z3:Z185">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -22354,12 +23444,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I176">
+  <conditionalFormatting sqref="I3:I185">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P176">
+  <conditionalFormatting sqref="P3:P185">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -22450,7 +23540,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$176)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$185)</f>
         <v/>
       </c>
     </row>
@@ -22461,7 +23551,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$176,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$185,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -22472,7 +23562,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$176,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$185,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -22483,7 +23573,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$176,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$185,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -22494,7 +23584,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$176,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$185,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -22505,7 +23595,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$176)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$185)</f>
         <v/>
       </c>
     </row>
@@ -22516,7 +23606,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$176)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22534,7 +23624,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$176)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$185)</f>
         <v/>
       </c>
     </row>
@@ -22545,7 +23635,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$176,Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$185,Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
     </row>
@@ -22578,7 +23668,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$176="bezahlt")*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$185="bezahlt")*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
     </row>
@@ -22607,7 +23697,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$176,"*verkauft",Artikelstamm!$AH$3:$AH$176,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$185,"*verkauft",Artikelstamm!$AH$3:$AH$185,"")</f>
         <v/>
       </c>
     </row>
@@ -22618,7 +23708,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$176,"*verkauft",Artikelstamm!$AI$3:$AI$176,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$185,"*verkauft",Artikelstamm!$AI$3:$AI$185,"offen")</f>
         <v/>
       </c>
     </row>
@@ -22629,7 +23719,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$176,"reserviert",Artikelstamm!$AK$3:$AK$176,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$185,"reserviert",Artikelstamm!$AK$3:$AK$185,"")</f>
         <v/>
       </c>
     </row>
@@ -22640,7 +23730,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$176,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$185,"")</f>
         <v/>
       </c>
     </row>
@@ -22651,7 +23741,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$176,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$185,"")</f>
         <v/>
       </c>
     </row>
@@ -22691,15 +23781,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$176,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$185,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$176=$A30)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$185=$A30)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$176,$A30,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$185,$A30,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22710,15 +23800,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$176,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$185,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$176=$A31)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$185=$A31)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$176,$A31,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$185,$A31,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22729,15 +23819,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$176,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$185,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$176=$A32)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$185=$A32)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$176,$A32,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$185,$A32,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22796,15 +23886,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A37)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A37)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A37,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A37,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22815,15 +23905,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A38)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A38)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A38,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A38,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22834,15 +23924,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A39)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A39)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A39,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A39,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22853,15 +23943,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A40)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A40)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A40,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A40,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22872,15 +23962,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A41)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A41)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A41,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A41,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22891,15 +23981,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A42)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A42)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A42,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A42,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22910,15 +24000,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A43)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A43)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A43,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A43,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22929,15 +24019,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A44)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A44)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A44,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A44,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22948,15 +24038,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A45)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A45)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A45,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A45,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22967,15 +24057,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A46)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A46)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A46,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A46,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -22986,15 +24076,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A47)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A47)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A47,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A47,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23005,15 +24095,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A48)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A48)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A48,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A48,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23024,15 +24114,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A49)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A49)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A49,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A49,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23043,15 +24133,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$176,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$176=$A50)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A50)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$176,$A50,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A50,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23110,15 +24200,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A55)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A55)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A55,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A55,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23129,15 +24219,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A56)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A56)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A56,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A56,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23148,15 +24238,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A57)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A57)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A57,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A57,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23167,15 +24257,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A58)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A58)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A58,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A58,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23186,15 +24276,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A59)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A59)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A59,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A59,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23205,15 +24295,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A60)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A60)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A60,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A60,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23224,15 +24314,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A61)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A61)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A61,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A61,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23243,15 +24333,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A62)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A62)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A62,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A62,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23262,15 +24352,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A63)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A63)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A63,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A63,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23281,15 +24371,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A64)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A64)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A64,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A64,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23300,15 +24390,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A65)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A65)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A65,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A65,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23319,15 +24409,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A66)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A66)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A66,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A66,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23338,15 +24428,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A67)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A67)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A67,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A67,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23357,15 +24447,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A68)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A68)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A68,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A68,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23376,15 +24466,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A69)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A69)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A69,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A69,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23395,15 +24485,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A70)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A70)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A70,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A70,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23414,15 +24504,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A71)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A71)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A71,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A71,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23433,15 +24523,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A72)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A72)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A72,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A72,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23452,15 +24542,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$176,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$176=$A73)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A73)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$176,$A73,Artikelstamm!$U$3:$U$176)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A73,Artikelstamm!$U$3:$U$185)</f>
         <v/>
       </c>
     </row>
@@ -23514,11 +24604,11 @@
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$176,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$176=$A78)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A78)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
     </row>
@@ -23529,11 +24619,11 @@
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$176,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$176=$A79)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A79)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
     </row>
@@ -23544,11 +24634,11 @@
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$176,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$176=$A80)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A80)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
     </row>
@@ -23559,11 +24649,11 @@
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$176,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$176=$A81)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A81)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
     </row>
@@ -23574,11 +24664,11 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$176,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$176=$A82)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A82)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
     </row>
@@ -23589,11 +24679,11 @@
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$176,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$176=$A83)*Artikelstamm!$K$3:$K$176*Artikelstamm!$AD$3:$AD$176)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A83)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -21144,7 +21144,7 @@
       </c>
       <c r="AM166" s="22" t="inlineStr">
         <is>
-          <t>OFFEN – Stueckzahl und Farben unvollstaendig. Die Nutzerin liefert die restlichen Fotos am Ende des Rundgangs nach; dann wird diese Position auf die Gesamtzahl gebracht und die Post-it-Nummern der anderen Raeume kommen in Weitere_ArtNr.</t>
+          <t>OFFEN: Stueckzahl und Farben unvollstaendig. Die Nutzerin liefert die restlichen Fotos am Ende des Rundgangs nach; dann wird diese Position auf die Gesamtzahl gebracht und die Post-it-Nummern der anderen Raeume kommen in Weitere_ArtNr.</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21620,7 @@
       </c>
       <c r="AM170" s="22" t="inlineStr">
         <is>
-          <t>OFFEN – NICHT VEROEFFENTLICHEN, bis die Marke geklaert ist: Form und Signaturplaettchen sprechen fuer einen Vitra Eames Elephant (gebraucht 150-280 EUR je Stueck), ein Nachbau waere 20-40 EUR wert. Nahaufnahme des Plaettchens und der Unterseite steht aus; die Nutzerin liefert sie am Ende des Rundgangs. Der kleinere schwarze wird dann eine eigene Position.</t>
+          <t>OFFEN: NICHT VEROEFFENTLICHEN, bis die Marke geklaert ist: Form und Signaturplaettchen sprechen fuer einen Vitra Eames Elephant (gebraucht 150-280 EUR je Stueck), ein Nachbau waere 20-40 EUR wert. Nahaufnahme des Plaettchens und der Unterseite steht aus; die Nutzerin liefert sie am Ende des Rundgangs. Der kleinere schwarze wird dann eine eigene Position.</t>
         </is>
       </c>
     </row>
@@ -22352,7 +22352,7 @@
       </c>
       <c r="F177" s="16" t="inlineStr">
         <is>
-          <t>Etagenbett in Weiß mit sichtbaren Multiplex-Kanten, abgerundeten Ausschnitten und durchgehender Absturzsicherung oben. Solide Bauweise aus dem Kita-Betrieb.</t>
+          <t>Etagenbett in Weiß mit sichtbaren Multiplex-Kanten, abgerundeten Ausschnitten und durchgehender Absturzsicherung oben. Solide Bauweise aus dem Kita-Betrieb. Die Matratzen können auf Wunsch mitgenommen werden.</t>
         </is>
       </c>
       <c r="G177" s="15" t="inlineStr">
@@ -22445,12 +22445,12 @@
       <c r="AK177" s="19" t="n"/>
       <c r="AL177" s="16" t="inlineStr">
         <is>
-          <t>4 Betten: 2 aufgebaut im Schlafraum, 2 zusätzlich eingelagert.</t>
+          <t>4 Betten, alle aufgebaut: 2 im Schlafraum 4 und 2 in einem weiteren Schlafraum.</t>
         </is>
       </c>
       <c r="AM177" s="22" t="inlineStr">
         <is>
-          <t>Stueckzahl aus der Bemerkung "+2 lagernd" auf 4 gesetzt - bitte bestaetigen. Offen: gehen die Matratzen mit?</t>
+          <t>OFFEN: waechst noch. Aus den weiteren Schlafraeumen kommen zusaetzliche Betten dazu - am Ende des Rundgangs auf die Gesamtzahl bringen und die Post-it-Nummern der anderen Raeume in Weitere_ArtNr.</t>
         </is>
       </c>
     </row>
@@ -22469,12 +22469,12 @@
       </c>
       <c r="E178" s="15" t="inlineStr">
         <is>
-          <t>Wesco Spielküche, mehrteilig</t>
+          <t>Wesco Spielküche, 5 Module</t>
         </is>
       </c>
       <c r="F178" s="16" t="inlineStr">
         <is>
-          <t>Spielküche von Wesco aus Birke-Multiplex: Spülmodul mit Becken, Kochmodul mit Drehknöpfen, Backofenmodul mit Sichtfenster sowie Kühl- und Gefriermodule. Weiße Fronten mit Holzgriffen, Module einzeln stellbar.</t>
+          <t>Spielküche von Wesco aus Birke-Multiplex, fünf Module: Spüle mit Becken, Kochfeld mit Drehknöpfen, Backofen mit Sichtfenster sowie Kühl- und Gefriermodul. Weiße Fronten mit Holzgriffen, die Module stehen frei und sind einzeln aufstellbar.</t>
         </is>
       </c>
       <c r="G178" s="15" t="inlineStr">
@@ -22571,12 +22571,12 @@
       <c r="AK178" s="19" t="n"/>
       <c r="AL178" s="16" t="inlineStr">
         <is>
-          <t>1 Küche aus mehreren Modulen – auf dem Foto sind etwa fünf zu sehen. Bitte die Anzahl der Module bestätigen, der Preis hängt daran.</t>
+          <t>1 Küche aus 5 Modulen, vom Haus bestätigt.</t>
         </is>
       </c>
       <c r="AM178" s="22" t="inlineStr">
         <is>
-          <t>Anzahl der Module unbestaetigt. Wesco ist institutionelle Qualitaet, neu kostet ein Modul 300-600 EUR - das ist nach dem Vitra Alcove die wertvollste Position.</t>
+          <t>Wesco ist institutionelle Qualitaet, neu kostet ein Modul 300-600 EUR. Nach dem Vitra Alcove die wertvollste Position.</t>
         </is>
       </c>
     </row>
@@ -23315,12 +23315,12 @@
       </c>
       <c r="E185" s="15" t="inlineStr">
         <is>
-          <t>Kinderhochstuhl Kunststoff mit Gurt</t>
+          <t>IKEA Kinderhochstuhl mit Gurt</t>
         </is>
       </c>
       <c r="F185" s="16" t="inlineStr">
         <is>
-          <t>Hochstuhl mit weißer Kunststoffschale, grauen Stahlbeinen und Sicherheitsgurt. Ohne Esstablett.</t>
+          <t>Kinderhochstuhl von IKEA: weiße Kunststoffschale, graue Stahlbeine, Sicherheitsgurt. Ohne Esstablett.</t>
         </is>
       </c>
       <c r="G185" s="15" t="inlineStr">
@@ -23397,7 +23397,11 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="AA185" s="19" t="n"/>
+      <c r="AA185" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
       <c r="AB185" s="19" t="n"/>
       <c r="AC185" s="19" t="n"/>
       <c r="AD185" s="20" t="n"/>
@@ -23418,7 +23422,7 @@
       </c>
       <c r="AM185" s="22" t="inlineStr">
         <is>
-          <t>Stueckzahl auf dem Erfassungsblatt mehrfach korrigiert, gelesen als 9 - bitte bestaetigen. Form spricht fuer IKEA Antilop, ein Etikett war nicht zu sehen; deshalb keine Marke eingetragen.</t>
+          <t>OFFEN: waechst noch. Aus weiteren Raeumen kommen zusaetzliche Hochstuehle dazu - am Ende des Rundgangs auf die Gesamtzahl bringen und die Post-it-Nummern der anderen Raeume in Weitere_ArtNr.</t>
         </is>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$200</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM185"/>
+  <dimension ref="A1:AM200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="F133" s="16" t="inlineStr">
         <is>
-          <t>Shaggy/Hochflor, beige, ca. 200 x 300 cm, gereinigt</t>
+          <t>Hochflorteppich in Beige, IKEA Ådum. Gereinigt.</t>
         </is>
       </c>
       <c r="G133" s="15" t="inlineStr">
@@ -17071,7 +17071,11 @@
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="O133" s="19" t="n"/>
+      <c r="O133" s="19" t="inlineStr">
+        <is>
+          <t>120 × 240 cm</t>
+        </is>
+      </c>
       <c r="P133" s="19" t="inlineStr">
         <is>
           <t>ja</t>
@@ -17112,7 +17116,11 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="AA133" s="19" t="n"/>
+      <c r="AA133" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
       <c r="AB133" s="19" t="n"/>
       <c r="AC133" s="19" t="n"/>
       <c r="AD133" s="20" t="n"/>
@@ -17128,7 +17136,7 @@
       <c r="AK133" s="19" t="n"/>
       <c r="AL133" s="16" t="inlineStr">
         <is>
-          <t>2 Stück (zwei Einzelfotos)</t>
+          <t>2 Teppiche, Maße vom Erfassungsblatt.</t>
         </is>
       </c>
       <c r="AM133" s="22" t="n"/>
@@ -17157,7 +17165,7 @@
       </c>
       <c r="F134" s="16" t="inlineStr">
         <is>
-          <t>Flachgewebe, Rautenmuster schwarz/weiß, ca. 200 x 300 cm</t>
+          <t>Flachgewebter Teppich mit schwarz-weißem Rautenmuster, IKEA Lappljung Ruta.</t>
         </is>
       </c>
       <c r="G134" s="15" t="inlineStr">
@@ -17193,7 +17201,11 @@
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="O134" s="19" t="n"/>
+      <c r="O134" s="19" t="inlineStr">
+        <is>
+          <t>200 × 300 cm</t>
+        </is>
+      </c>
       <c r="P134" s="19" t="inlineStr">
         <is>
           <t>ja</t>
@@ -17234,7 +17246,11 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="AA134" s="19" t="n"/>
+      <c r="AA134" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
       <c r="AB134" s="19" t="n"/>
       <c r="AC134" s="19" t="n"/>
       <c r="AD134" s="20" t="n"/>
@@ -17250,7 +17266,7 @@
       <c r="AK134" s="19" t="n"/>
       <c r="AL134" s="16" t="inlineStr">
         <is>
-          <t>2 Stück im Bild</t>
+          <t>2 Teppiche, Maße vom Erfassungsblatt.</t>
         </is>
       </c>
       <c r="AM134" s="22" t="n"/>
@@ -19825,7 +19841,11 @@
         </is>
       </c>
       <c r="B156" s="15" t="n"/>
-      <c r="C156" s="15" t="n"/>
+      <c r="C156" s="15" t="inlineStr">
+        <is>
+          <t>NU04-12</t>
+        </is>
+      </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
           <t>NU02</t>
@@ -19857,7 +19877,7 @@
         </is>
       </c>
       <c r="J156" s="17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K156" s="17" t="n"/>
       <c r="L156" s="18">
@@ -19935,12 +19955,12 @@
       <c r="AK156" s="19" t="n"/>
       <c r="AL156" s="16" t="inlineStr">
         <is>
-          <t>10 Stück – abgebildet ist einer davon.</t>
+          <t>16 Stühle insgesamt: 10 im Gruppenraum 5 und im Nachbarraum NU03, 6 im Schlafraum 5 (dort mit NU04-12 beschriftet).</t>
         </is>
       </c>
       <c r="AM156" s="22" t="inlineStr">
         <is>
-          <t>Gesamtstückzahl über Gruppenraum 5 und den Nachbarraum NU02/NU03 hinweg, so vom Haus gezählt. In NU03 nicht erneut anlegen.</t>
+          <t>Zusammengefasste Position ueber drei Raeume. Post-it-Nummer im Schlafraum 5: NU04-12. In NU03 nicht erneut anlegen.</t>
         </is>
       </c>
     </row>
@@ -23426,8 +23446,1818 @@
         </is>
       </c>
     </row>
+    <row r="186" ht="30" customHeight="1">
+      <c r="A186" s="15" t="inlineStr">
+        <is>
+          <t>NU04-07</t>
+        </is>
+      </c>
+      <c r="B186" s="15" t="n"/>
+      <c r="C186" s="15" t="n"/>
+      <c r="D186" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E186" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Agam Kinderstuhl, schwarz</t>
+        </is>
+      </c>
+      <c r="F186" s="16" t="inlineStr">
+        <is>
+          <t>Kinderstuhl IKEA Agam aus Massivholz, schwarz lackiert, mit Sprossenlehne. Etikett an der Unterseite: Agam, Herstelldatum 2019. Sitzfläche mit Kratzern.</t>
+        </is>
+      </c>
+      <c r="G186" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H186" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I186" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J186" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="K186" s="17" t="n"/>
+      <c r="L186" s="18">
+        <f>J186-IF(K186="",0,K186)</f>
+        <v/>
+      </c>
+      <c r="M186" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N186" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O186" s="19" t="n"/>
+      <c r="P186" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q186" s="19" t="n"/>
+      <c r="R186" s="20" t="n"/>
+      <c r="S186" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T186" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U186" s="21">
+        <f>L186*S186</f>
+        <v/>
+      </c>
+      <c r="V186" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W186" s="15" t="inlineStr">
+        <is>
+          <t>F-188</t>
+        </is>
+      </c>
+      <c r="X186" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y186" s="19" t="n"/>
+      <c r="Z186" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA186" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB186" s="19" t="n"/>
+      <c r="AC186" s="19" t="n"/>
+      <c r="AD186" s="20" t="n"/>
+      <c r="AE186" s="21">
+        <f>IF(K186="","",K186*AD186)</f>
+        <v/>
+      </c>
+      <c r="AF186" s="19" t="n"/>
+      <c r="AG186" s="19" t="n"/>
+      <c r="AH186" s="19" t="n"/>
+      <c r="AI186" s="19" t="n"/>
+      <c r="AJ186" s="19" t="n"/>
+      <c r="AK186" s="19" t="n"/>
+      <c r="AL186" s="16" t="inlineStr">
+        <is>
+          <t>13 Stühle – abgebildet ist einer davon, das Etikett auf Foto F-189.</t>
+        </is>
+      </c>
+      <c r="AM186" s="22" t="n"/>
+    </row>
+    <row r="187" ht="30" customHeight="1">
+      <c r="A187" s="15" t="inlineStr">
+        <is>
+          <t>NU04-08</t>
+        </is>
+      </c>
+      <c r="B187" s="15" t="n"/>
+      <c r="C187" s="15" t="n"/>
+      <c r="D187" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E187" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Urban Kinderstuhl, Kunststoff</t>
+        </is>
+      </c>
+      <c r="F187" s="16" t="inlineStr">
+        <is>
+          <t>Kinderstuhl IKEA Urban, Sitzschale aus Kunststoff mit Fußstütze am Gestell. Etikett an der Unterseite: Urban, 001.652.13.</t>
+        </is>
+      </c>
+      <c r="G187" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H187" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I187" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J187" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K187" s="17" t="n"/>
+      <c r="L187" s="18">
+        <f>J187-IF(K187="",0,K187)</f>
+        <v/>
+      </c>
+      <c r="M187" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N187" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O187" s="19" t="n"/>
+      <c r="P187" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q187" s="19" t="n"/>
+      <c r="R187" s="20" t="n"/>
+      <c r="S187" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T187" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U187" s="21">
+        <f>L187*S187</f>
+        <v/>
+      </c>
+      <c r="V187" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W187" s="15" t="inlineStr">
+        <is>
+          <t>F-190</t>
+        </is>
+      </c>
+      <c r="X187" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y187" s="19" t="n"/>
+      <c r="Z187" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA187" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB187" s="19" t="n"/>
+      <c r="AC187" s="19" t="n"/>
+      <c r="AD187" s="20" t="n"/>
+      <c r="AE187" s="21">
+        <f>IF(K187="","",K187*AD187)</f>
+        <v/>
+      </c>
+      <c r="AF187" s="19" t="n"/>
+      <c r="AG187" s="19" t="n"/>
+      <c r="AH187" s="19" t="n"/>
+      <c r="AI187" s="19" t="n"/>
+      <c r="AJ187" s="19" t="n"/>
+      <c r="AK187" s="19" t="n"/>
+      <c r="AL187" s="16" t="inlineStr">
+        <is>
+          <t>7 Stühle – abgebildet ist einer davon, das Etikett auf Foto F-191.</t>
+        </is>
+      </c>
+      <c r="AM187" s="22" t="inlineStr">
+        <is>
+          <t>Farbe klaeren: auf dem Erfassungsblatt steht weiss, das Foto wirkt hellgrau-gruen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="30" customHeight="1">
+      <c r="A188" s="15" t="inlineStr">
+        <is>
+          <t>NU04-09</t>
+        </is>
+      </c>
+      <c r="B188" s="15" t="n"/>
+      <c r="C188" s="15" t="n"/>
+      <c r="D188" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E188" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Regal weiß, 8 Fächer</t>
+        </is>
+      </c>
+      <c r="F188" s="16" t="inlineStr">
+        <is>
+          <t>Regal IKEA in Weiß mit acht Fächern, liegend oder stehend nutzbar.</t>
+        </is>
+      </c>
+      <c r="G188" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H188" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I188" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J188" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" s="17" t="n"/>
+      <c r="L188" s="18">
+        <f>J188-IF(K188="",0,K188)</f>
+        <v/>
+      </c>
+      <c r="M188" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N188" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O188" s="19" t="n"/>
+      <c r="P188" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q188" s="19" t="n"/>
+      <c r="R188" s="20" t="n"/>
+      <c r="S188" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="T188" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U188" s="21">
+        <f>L188*S188</f>
+        <v/>
+      </c>
+      <c r="V188" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W188" s="15" t="inlineStr">
+        <is>
+          <t>F-192</t>
+        </is>
+      </c>
+      <c r="X188" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y188" s="19" t="n"/>
+      <c r="Z188" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA188" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB188" s="19" t="n"/>
+      <c r="AC188" s="19" t="n"/>
+      <c r="AD188" s="20" t="n"/>
+      <c r="AE188" s="21">
+        <f>IF(K188="","",K188*AD188)</f>
+        <v/>
+      </c>
+      <c r="AF188" s="19" t="n"/>
+      <c r="AG188" s="19" t="n"/>
+      <c r="AH188" s="19" t="n"/>
+      <c r="AI188" s="19" t="n"/>
+      <c r="AJ188" s="19" t="n"/>
+      <c r="AK188" s="19" t="n"/>
+      <c r="AL188" s="16" t="inlineStr">
+        <is>
+          <t>3 Regale – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AM188" s="22" t="n"/>
+    </row>
+    <row r="189" ht="30" customHeight="1">
+      <c r="A189" s="15" t="inlineStr">
+        <is>
+          <t>NU04-10</t>
+        </is>
+      </c>
+      <c r="B189" s="15" t="n"/>
+      <c r="C189" s="15" t="n"/>
+      <c r="D189" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E189" s="15" t="inlineStr">
+        <is>
+          <t>Schalenstuhl mit Sitzpolster und Holzbeinen</t>
+        </is>
+      </c>
+      <c r="F189" s="16" t="inlineStr">
+        <is>
+          <t>Schalenstuhl mit grauer Kunststoffschale, hellem Sitzpolster und konischen Beinen aus massivem Holz.</t>
+        </is>
+      </c>
+      <c r="G189" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H189" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I189" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J189" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K189" s="17" t="n"/>
+      <c r="L189" s="18">
+        <f>J189-IF(K189="",0,K189)</f>
+        <v/>
+      </c>
+      <c r="M189" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N189" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O189" s="19" t="n"/>
+      <c r="P189" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q189" s="19" t="n"/>
+      <c r="R189" s="20" t="n"/>
+      <c r="S189" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T189" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U189" s="21">
+        <f>L189*S189</f>
+        <v/>
+      </c>
+      <c r="V189" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W189" s="15" t="inlineStr">
+        <is>
+          <t>F-193</t>
+        </is>
+      </c>
+      <c r="X189" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y189" s="19" t="n"/>
+      <c r="Z189" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA189" s="19" t="n"/>
+      <c r="AB189" s="19" t="n"/>
+      <c r="AC189" s="19" t="n"/>
+      <c r="AD189" s="20" t="n"/>
+      <c r="AE189" s="21">
+        <f>IF(K189="","",K189*AD189)</f>
+        <v/>
+      </c>
+      <c r="AF189" s="19" t="n"/>
+      <c r="AG189" s="19" t="n"/>
+      <c r="AH189" s="19" t="n"/>
+      <c r="AI189" s="19" t="n"/>
+      <c r="AJ189" s="19" t="n"/>
+      <c r="AK189" s="19" t="n"/>
+      <c r="AL189" s="16" t="inlineStr">
+        <is>
+          <t>4 Stühle – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AM189" s="22" t="inlineStr">
+        <is>
+          <t>Farbe klaeren: auf dem Erfassungsblatt steht weiss, die Schale wirkt auf dem Foto grau-beige.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="30" customHeight="1">
+      <c r="A190" s="15" t="inlineStr">
+        <is>
+          <t>NU04-11</t>
+        </is>
+      </c>
+      <c r="B190" s="15" t="n"/>
+      <c r="C190" s="15" t="n"/>
+      <c r="D190" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E190" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Stuva Tisch weiß</t>
+        </is>
+      </c>
+      <c r="F190" s="16" t="inlineStr">
+        <is>
+          <t>Tisch beziehungsweise Sitzbank IKEA Stuva in Weiß mit Seitenwangen und Gleitern. Etikett an der Unterseite: Stuva.</t>
+        </is>
+      </c>
+      <c r="G190" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H190" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I190" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J190" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K190" s="17" t="n"/>
+      <c r="L190" s="18">
+        <f>J190-IF(K190="",0,K190)</f>
+        <v/>
+      </c>
+      <c r="M190" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N190" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O190" s="19" t="n"/>
+      <c r="P190" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q190" s="19" t="n"/>
+      <c r="R190" s="20" t="n"/>
+      <c r="S190" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T190" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U190" s="21">
+        <f>L190*S190</f>
+        <v/>
+      </c>
+      <c r="V190" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W190" s="15" t="inlineStr">
+        <is>
+          <t>F-194</t>
+        </is>
+      </c>
+      <c r="X190" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y190" s="19" t="n"/>
+      <c r="Z190" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA190" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB190" s="19" t="n"/>
+      <c r="AC190" s="19" t="n"/>
+      <c r="AD190" s="20" t="n"/>
+      <c r="AE190" s="21">
+        <f>IF(K190="","",K190*AD190)</f>
+        <v/>
+      </c>
+      <c r="AF190" s="19" t="n"/>
+      <c r="AG190" s="19" t="n"/>
+      <c r="AH190" s="19" t="n"/>
+      <c r="AI190" s="19" t="n"/>
+      <c r="AJ190" s="19" t="n"/>
+      <c r="AK190" s="19" t="n"/>
+      <c r="AL190" s="16" t="inlineStr">
+        <is>
+          <t>2 Stück – abgebildet ist eines davon, das Etikett auf Foto F-195.</t>
+        </is>
+      </c>
+      <c r="AM190" s="22" t="n"/>
+    </row>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="15" t="inlineStr">
+        <is>
+          <t>NU04-13</t>
+        </is>
+      </c>
+      <c r="B191" s="15" t="n"/>
+      <c r="C191" s="15" t="n"/>
+      <c r="D191" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E191" s="15" t="inlineStr">
+        <is>
+          <t>Kindertisch rund weiß mit Holzbeinen</t>
+        </is>
+      </c>
+      <c r="F191" s="16" t="inlineStr">
+        <is>
+          <t>Runder Kindertisch, weiße Platte auf konischen Beinen aus massivem Holz. Die Plattenkante ist an einer Stelle beschädigt und dunkel abgestoßen.</t>
+        </is>
+      </c>
+      <c r="G191" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H191" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I191" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J191" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" s="17" t="n"/>
+      <c r="L191" s="18">
+        <f>J191-IF(K191="",0,K191)</f>
+        <v/>
+      </c>
+      <c r="M191" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N191" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O191" s="19" t="n"/>
+      <c r="P191" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q191" s="19" t="n"/>
+      <c r="R191" s="20" t="n"/>
+      <c r="S191" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T191" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U191" s="21">
+        <f>L191*S191</f>
+        <v/>
+      </c>
+      <c r="V191" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W191" s="15" t="inlineStr">
+        <is>
+          <t>F-197</t>
+        </is>
+      </c>
+      <c r="X191" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y191" s="19" t="n"/>
+      <c r="Z191" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA191" s="19" t="n"/>
+      <c r="AB191" s="19" t="n"/>
+      <c r="AC191" s="19" t="n"/>
+      <c r="AD191" s="20" t="n"/>
+      <c r="AE191" s="21">
+        <f>IF(K191="","",K191*AD191)</f>
+        <v/>
+      </c>
+      <c r="AF191" s="19" t="n"/>
+      <c r="AG191" s="19" t="n"/>
+      <c r="AH191" s="19" t="n"/>
+      <c r="AI191" s="19" t="n"/>
+      <c r="AJ191" s="19" t="n"/>
+      <c r="AK191" s="19" t="n"/>
+      <c r="AL191" s="16" t="inlineStr">
+        <is>
+          <t>1 Tisch.</t>
+        </is>
+      </c>
+      <c r="AM191" s="22" t="n"/>
+    </row>
+    <row r="192" ht="30" customHeight="1">
+      <c r="A192" s="15" t="inlineStr">
+        <is>
+          <t>NU04-14</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="n"/>
+      <c r="C192" s="15" t="n"/>
+      <c r="D192" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E192" s="15" t="inlineStr">
+        <is>
+          <t>Raumteiler Metallgitter, schwarz</t>
+        </is>
+      </c>
+      <c r="F192" s="16" t="inlineStr">
+        <is>
+          <t>Freistehender Raumteiler: schwarz beschichtetes Metallgitter mit Rautenmuster auf ovalem Standfuß. Auch als Rankgitter oder zum Aufhängen nutzbar.</t>
+        </is>
+      </c>
+      <c r="G192" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H192" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J192" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" s="17" t="n"/>
+      <c r="L192" s="18">
+        <f>J192-IF(K192="",0,K192)</f>
+        <v/>
+      </c>
+      <c r="M192" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N192" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O192" s="19" t="n"/>
+      <c r="P192" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q192" s="19" t="n"/>
+      <c r="R192" s="20" t="n"/>
+      <c r="S192" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T192" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U192" s="21">
+        <f>L192*S192</f>
+        <v/>
+      </c>
+      <c r="V192" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W192" s="15" t="inlineStr">
+        <is>
+          <t>F-198</t>
+        </is>
+      </c>
+      <c r="X192" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y192" s="19" t="n"/>
+      <c r="Z192" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA192" s="19" t="n"/>
+      <c r="AB192" s="19" t="n"/>
+      <c r="AC192" s="19" t="n"/>
+      <c r="AD192" s="20" t="n"/>
+      <c r="AE192" s="21">
+        <f>IF(K192="","",K192*AD192)</f>
+        <v/>
+      </c>
+      <c r="AF192" s="19" t="n"/>
+      <c r="AG192" s="19" t="n"/>
+      <c r="AH192" s="19" t="n"/>
+      <c r="AI192" s="19" t="n"/>
+      <c r="AJ192" s="19" t="n"/>
+      <c r="AK192" s="19" t="n"/>
+      <c r="AL192" s="16" t="inlineStr">
+        <is>
+          <t>1 Raumteiler.</t>
+        </is>
+      </c>
+      <c r="AM192" s="22" t="n"/>
+    </row>
+    <row r="193" ht="30" customHeight="1">
+      <c r="A193" s="15" t="inlineStr">
+        <is>
+          <t>NU04-15</t>
+        </is>
+      </c>
+      <c r="B193" s="15" t="n"/>
+      <c r="C193" s="15" t="n"/>
+      <c r="D193" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E193" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Regal weiß, 3 Fächer, schmal</t>
+        </is>
+      </c>
+      <c r="F193" s="16" t="inlineStr">
+        <is>
+          <t>Schmales hohes Regal IKEA in Weiß mit drei Fächern.</t>
+        </is>
+      </c>
+      <c r="G193" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H193" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I193" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J193" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" s="17" t="n"/>
+      <c r="L193" s="18">
+        <f>J193-IF(K193="",0,K193)</f>
+        <v/>
+      </c>
+      <c r="M193" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N193" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O193" s="19" t="n"/>
+      <c r="P193" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q193" s="19" t="n"/>
+      <c r="R193" s="20" t="n"/>
+      <c r="S193" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T193" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U193" s="21">
+        <f>L193*S193</f>
+        <v/>
+      </c>
+      <c r="V193" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W193" s="15" t="inlineStr">
+        <is>
+          <t>F-200</t>
+        </is>
+      </c>
+      <c r="X193" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y193" s="19" t="n"/>
+      <c r="Z193" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA193" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB193" s="19" t="n"/>
+      <c r="AC193" s="19" t="n"/>
+      <c r="AD193" s="20" t="n"/>
+      <c r="AE193" s="21">
+        <f>IF(K193="","",K193*AD193)</f>
+        <v/>
+      </c>
+      <c r="AF193" s="19" t="n"/>
+      <c r="AG193" s="19" t="n"/>
+      <c r="AH193" s="19" t="n"/>
+      <c r="AI193" s="19" t="n"/>
+      <c r="AJ193" s="19" t="n"/>
+      <c r="AK193" s="19" t="n"/>
+      <c r="AL193" s="16" t="inlineStr">
+        <is>
+          <t>1 Regal. Die Bücher gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM193" s="22" t="n"/>
+    </row>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="15" t="inlineStr">
+        <is>
+          <t>NU04-16</t>
+        </is>
+      </c>
+      <c r="B194" s="15" t="n"/>
+      <c r="C194" s="15" t="n"/>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E194" s="15" t="inlineStr">
+        <is>
+          <t>Bällebad mit Bällen</t>
+        </is>
+      </c>
+      <c r="F194" s="16" t="inlineStr">
+        <is>
+          <t>Bällebad in Quadratform: Polsterrand in Grau, Sockel in weißem Kunstleder mit Rautennaht, einschließlich der Bälle in Grau, Weiß und Bunt.</t>
+        </is>
+      </c>
+      <c r="G194" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H194" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I194" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J194" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" s="17" t="n"/>
+      <c r="L194" s="18">
+        <f>J194-IF(K194="",0,K194)</f>
+        <v/>
+      </c>
+      <c r="M194" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N194" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O194" s="19" t="n"/>
+      <c r="P194" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q194" s="19" t="n"/>
+      <c r="R194" s="20" t="n"/>
+      <c r="S194" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="T194" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U194" s="21">
+        <f>L194*S194</f>
+        <v/>
+      </c>
+      <c r="V194" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W194" s="15" t="inlineStr">
+        <is>
+          <t>F-202</t>
+        </is>
+      </c>
+      <c r="X194" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y194" s="19" t="n"/>
+      <c r="Z194" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA194" s="19" t="n"/>
+      <c r="AB194" s="19" t="n"/>
+      <c r="AC194" s="19" t="n"/>
+      <c r="AD194" s="20" t="n"/>
+      <c r="AE194" s="21">
+        <f>IF(K194="","",K194*AD194)</f>
+        <v/>
+      </c>
+      <c r="AF194" s="19" t="n"/>
+      <c r="AG194" s="19" t="n"/>
+      <c r="AH194" s="19" t="n"/>
+      <c r="AI194" s="19" t="n"/>
+      <c r="AJ194" s="19" t="n"/>
+      <c r="AK194" s="19" t="n"/>
+      <c r="AL194" s="16" t="inlineStr">
+        <is>
+          <t>1 Bällebad einschließlich der Bälle.</t>
+        </is>
+      </c>
+      <c r="AM194" s="22" t="n"/>
+    </row>
+    <row r="195" ht="30" customHeight="1">
+      <c r="A195" s="15" t="inlineStr">
+        <is>
+          <t>NU04-17</t>
+        </is>
+      </c>
+      <c r="B195" s="15" t="n"/>
+      <c r="C195" s="15" t="n"/>
+      <c r="D195" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E195" s="15" t="inlineStr">
+        <is>
+          <t>Spielregal Kiefer mit Wannen und Wandaufsatz</t>
+        </is>
+      </c>
+      <c r="F195" s="16" t="inlineStr">
+        <is>
+          <t>Werkbankhohes Gestell aus Kiefer massiv mit weißen Kunststoffwannen und durchgehender Arbeitsplatte, dazu ein passender Wandaufsatz mit sechs Wannen.</t>
+        </is>
+      </c>
+      <c r="G195" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H195" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I195" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J195" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K195" s="17" t="n"/>
+      <c r="L195" s="18">
+        <f>J195-IF(K195="",0,K195)</f>
+        <v/>
+      </c>
+      <c r="M195" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N195" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O195" s="19" t="n"/>
+      <c r="P195" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q195" s="19" t="n"/>
+      <c r="R195" s="20" t="n"/>
+      <c r="S195" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="T195" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U195" s="21">
+        <f>L195*S195</f>
+        <v/>
+      </c>
+      <c r="V195" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W195" s="15" t="inlineStr">
+        <is>
+          <t>F-203</t>
+        </is>
+      </c>
+      <c r="X195" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y195" s="19" t="n"/>
+      <c r="Z195" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA195" s="19" t="n"/>
+      <c r="AB195" s="19" t="n"/>
+      <c r="AC195" s="19" t="n"/>
+      <c r="AD195" s="20" t="n"/>
+      <c r="AE195" s="21">
+        <f>IF(K195="","",K195*AD195)</f>
+        <v/>
+      </c>
+      <c r="AF195" s="19" t="n"/>
+      <c r="AG195" s="19" t="n"/>
+      <c r="AH195" s="19" t="n"/>
+      <c r="AI195" s="19" t="n"/>
+      <c r="AJ195" s="19" t="n"/>
+      <c r="AK195" s="19" t="n"/>
+      <c r="AL195" s="16" t="inlineStr">
+        <is>
+          <t>2 Einheiten, jeweils Unterteil und Wandaufsatz. Der Inhalt der Wannen gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM195" s="22" t="n"/>
+    </row>
+    <row r="196" ht="30" customHeight="1">
+      <c r="A196" s="15" t="inlineStr">
+        <is>
+          <t>NU04-18</t>
+        </is>
+      </c>
+      <c r="B196" s="15" t="n"/>
+      <c r="C196" s="15" t="n"/>
+      <c r="D196" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E196" s="15" t="inlineStr">
+        <is>
+          <t>Kinderwerkbank Holz mit Tafel</t>
+        </is>
+      </c>
+      <c r="F196" s="16" t="inlineStr">
+        <is>
+          <t>Kinderwerkbank aus Holz mit Lochplatte, drei Werkzeugkästen, Tafellackfläche oben, Zollstockaufdruck an der Kante und Ablage unten.</t>
+        </is>
+      </c>
+      <c r="G196" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H196" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I196" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J196" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" s="17" t="n"/>
+      <c r="L196" s="18">
+        <f>J196-IF(K196="",0,K196)</f>
+        <v/>
+      </c>
+      <c r="M196" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N196" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O196" s="19" t="n"/>
+      <c r="P196" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q196" s="19" t="n"/>
+      <c r="R196" s="20" t="n"/>
+      <c r="S196" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T196" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U196" s="21">
+        <f>L196*S196</f>
+        <v/>
+      </c>
+      <c r="V196" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W196" s="15" t="inlineStr">
+        <is>
+          <t>F-204</t>
+        </is>
+      </c>
+      <c r="X196" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y196" s="19" t="n"/>
+      <c r="Z196" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA196" s="19" t="n"/>
+      <c r="AB196" s="19" t="n"/>
+      <c r="AC196" s="19" t="n"/>
+      <c r="AD196" s="20" t="n"/>
+      <c r="AE196" s="21">
+        <f>IF(K196="","",K196*AD196)</f>
+        <v/>
+      </c>
+      <c r="AF196" s="19" t="n"/>
+      <c r="AG196" s="19" t="n"/>
+      <c r="AH196" s="19" t="n"/>
+      <c r="AI196" s="19" t="n"/>
+      <c r="AJ196" s="19" t="n"/>
+      <c r="AK196" s="19" t="n"/>
+      <c r="AL196" s="16" t="inlineStr">
+        <is>
+          <t>1 Werkbank. Werkzeug, Helm und Zubehör gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM196" s="22" t="inlineStr">
+        <is>
+          <t>Stueckzahl auf dem Erfassungsblatt nicht eingetragen, als 1 angenommen - bitte bestaetigen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="15" t="inlineStr">
+        <is>
+          <t>NU04-19</t>
+        </is>
+      </c>
+      <c r="B197" s="15" t="n"/>
+      <c r="C197" s="15" t="n"/>
+      <c r="D197" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E197" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Kleiderschrank weiß mit drei Böden</t>
+        </is>
+      </c>
+      <c r="F197" s="16" t="inlineStr">
+        <is>
+          <t>Hoher Schrank IKEA in Weiß mit zwei Türen, ovalen Griffmulden und drei Einlegeböden.</t>
+        </is>
+      </c>
+      <c r="G197" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H197" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I197" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J197" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K197" s="17" t="n"/>
+      <c r="L197" s="18">
+        <f>J197-IF(K197="",0,K197)</f>
+        <v/>
+      </c>
+      <c r="M197" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N197" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O197" s="19" t="n"/>
+      <c r="P197" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q197" s="19" t="n"/>
+      <c r="R197" s="20" t="n"/>
+      <c r="S197" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T197" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U197" s="21">
+        <f>L197*S197</f>
+        <v/>
+      </c>
+      <c r="V197" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W197" s="15" t="inlineStr">
+        <is>
+          <t>F-205</t>
+        </is>
+      </c>
+      <c r="X197" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y197" s="19" t="n"/>
+      <c r="Z197" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA197" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB197" s="19" t="n"/>
+      <c r="AC197" s="19" t="n"/>
+      <c r="AD197" s="20" t="n"/>
+      <c r="AE197" s="21">
+        <f>IF(K197="","",K197*AD197)</f>
+        <v/>
+      </c>
+      <c r="AF197" s="19" t="n"/>
+      <c r="AG197" s="19" t="n"/>
+      <c r="AH197" s="19" t="n"/>
+      <c r="AI197" s="19" t="n"/>
+      <c r="AJ197" s="19" t="n"/>
+      <c r="AK197" s="19" t="n"/>
+      <c r="AL197" s="16" t="inlineStr">
+        <is>
+          <t>2 Schränke – abgebildet ist einer davon, innen auf Foto F-206.</t>
+        </is>
+      </c>
+      <c r="AM197" s="22" t="n"/>
+    </row>
+    <row r="198" ht="30" customHeight="1">
+      <c r="A198" s="15" t="inlineStr">
+        <is>
+          <t>NU04-20</t>
+        </is>
+      </c>
+      <c r="B198" s="15" t="n"/>
+      <c r="C198" s="15" t="n"/>
+      <c r="D198" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E198" s="15" t="inlineStr">
+        <is>
+          <t>Freischwinger schwarz, Kunststoff</t>
+        </is>
+      </c>
+      <c r="F198" s="16" t="inlineStr">
+        <is>
+          <t>Freischwinger aus einem Stück Kunststoff, schwarz matt, S-förmig geschwungen. Erwachsenengröße.</t>
+        </is>
+      </c>
+      <c r="G198" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H198" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I198" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J198" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K198" s="17" t="n"/>
+      <c r="L198" s="18">
+        <f>J198-IF(K198="",0,K198)</f>
+        <v/>
+      </c>
+      <c r="M198" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N198" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O198" s="19" t="n"/>
+      <c r="P198" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q198" s="19" t="n"/>
+      <c r="R198" s="20" t="n"/>
+      <c r="S198" s="20" t="n">
+        <v>180</v>
+      </c>
+      <c r="T198" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U198" s="21">
+        <f>L198*S198</f>
+        <v/>
+      </c>
+      <c r="V198" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W198" s="15" t="inlineStr">
+        <is>
+          <t>F-208</t>
+        </is>
+      </c>
+      <c r="X198" s="19" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="Y198" s="19" t="n"/>
+      <c r="Z198" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA198" s="19" t="n"/>
+      <c r="AB198" s="19" t="n"/>
+      <c r="AC198" s="19" t="n"/>
+      <c r="AD198" s="20" t="n"/>
+      <c r="AE198" s="21">
+        <f>IF(K198="","",K198*AD198)</f>
+        <v/>
+      </c>
+      <c r="AF198" s="19" t="n"/>
+      <c r="AG198" s="19" t="n"/>
+      <c r="AH198" s="19" t="n"/>
+      <c r="AI198" s="19" t="n"/>
+      <c r="AJ198" s="19" t="n"/>
+      <c r="AK198" s="19" t="n"/>
+      <c r="AL198" s="16" t="inlineStr">
+        <is>
+          <t>1 Stuhl.</t>
+        </is>
+      </c>
+      <c r="AM198" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: NICHT VEROEFFENTLICHEN, bis die Marke geklaert ist. Die Form ist der Panton Chair von Verner Panton, Original von Vitra - gebraucht 120-250 EUR, ein Nachbau 30-50 EUR. Das Original traegt auf der Unterseite eine eingeformte Vitra-Kennzeichnung. Nahaufnahme der Unterseite anfordern, dann entscheiden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="30" customHeight="1">
+      <c r="A199" s="15" t="inlineStr">
+        <is>
+          <t>NU04-21</t>
+        </is>
+      </c>
+      <c r="B199" s="15" t="n"/>
+      <c r="C199" s="15" t="n"/>
+      <c r="D199" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E199" s="15" t="inlineStr">
+        <is>
+          <t>Spieltisch Kiefer mit abnehmbaren Platten</t>
+        </is>
+      </c>
+      <c r="F199" s="16" t="inlineStr">
+        <is>
+          <t>Tisch aus Kiefer massiv mit zwei abnehmbaren weißen Kunststoffplatten. Darunter lässt sich eine Wanne einsetzen, im Haus für Bausteine und Sandspiel genutzt.</t>
+        </is>
+      </c>
+      <c r="G199" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H199" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I199" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J199" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K199" s="17" t="n"/>
+      <c r="L199" s="18">
+        <f>J199-IF(K199="",0,K199)</f>
+        <v/>
+      </c>
+      <c r="M199" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N199" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O199" s="19" t="n"/>
+      <c r="P199" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q199" s="19" t="n"/>
+      <c r="R199" s="20" t="n"/>
+      <c r="S199" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T199" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U199" s="21">
+        <f>L199*S199</f>
+        <v/>
+      </c>
+      <c r="V199" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W199" s="15" t="inlineStr">
+        <is>
+          <t>F-209</t>
+        </is>
+      </c>
+      <c r="X199" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y199" s="19" t="n"/>
+      <c r="Z199" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA199" s="19" t="n"/>
+      <c r="AB199" s="19" t="n"/>
+      <c r="AC199" s="19" t="n"/>
+      <c r="AD199" s="20" t="n"/>
+      <c r="AE199" s="21">
+        <f>IF(K199="","",K199*AD199)</f>
+        <v/>
+      </c>
+      <c r="AF199" s="19" t="n"/>
+      <c r="AG199" s="19" t="n"/>
+      <c r="AH199" s="19" t="n"/>
+      <c r="AI199" s="19" t="n"/>
+      <c r="AJ199" s="19" t="n"/>
+      <c r="AK199" s="19" t="n"/>
+      <c r="AL199" s="16" t="inlineStr">
+        <is>
+          <t>1 Tisch mit Platten und Wanne. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM199" s="22" t="n"/>
+    </row>
+    <row r="200" ht="30" customHeight="1">
+      <c r="A200" s="15" t="inlineStr">
+        <is>
+          <t>NU04-22</t>
+        </is>
+      </c>
+      <c r="B200" s="15" t="n"/>
+      <c r="C200" s="15" t="n"/>
+      <c r="D200" s="15" t="inlineStr">
+        <is>
+          <t>NU04</t>
+        </is>
+      </c>
+      <c r="E200" s="15" t="inlineStr">
+        <is>
+          <t>Wandregal weiß, schmal</t>
+        </is>
+      </c>
+      <c r="F200" s="16" t="inlineStr">
+        <is>
+          <t>Schmales weißes Wandregal, sichtbar verschraubt.</t>
+        </is>
+      </c>
+      <c r="G200" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H200" s="15" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="I200" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J200" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" s="17" t="n"/>
+      <c r="L200" s="18">
+        <f>J200-IF(K200="",0,K200)</f>
+        <v/>
+      </c>
+      <c r="M200" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N200" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O200" s="19" t="n"/>
+      <c r="P200" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q200" s="19" t="n"/>
+      <c r="R200" s="20" t="n"/>
+      <c r="S200" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T200" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U200" s="21">
+        <f>L200*S200</f>
+        <v/>
+      </c>
+      <c r="V200" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W200" s="15" t="inlineStr">
+        <is>
+          <t>F-210</t>
+        </is>
+      </c>
+      <c r="X200" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y200" s="19" t="n"/>
+      <c r="Z200" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA200" s="19" t="n"/>
+      <c r="AB200" s="19" t="n"/>
+      <c r="AC200" s="19" t="n"/>
+      <c r="AD200" s="20" t="n"/>
+      <c r="AE200" s="21">
+        <f>IF(K200="","",K200*AD200)</f>
+        <v/>
+      </c>
+      <c r="AF200" s="19" t="n"/>
+      <c r="AG200" s="19" t="n"/>
+      <c r="AH200" s="19" t="n"/>
+      <c r="AI200" s="19" t="n"/>
+      <c r="AJ200" s="19" t="n"/>
+      <c r="AK200" s="19" t="n"/>
+      <c r="AL200" s="16" t="inlineStr">
+        <is>
+          <t>3 Regale – abgebildet sind zwei davon.</t>
+        </is>
+      </c>
+      <c r="AM200" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AM185"/>
+  <autoFilter ref="A2:AM200"/>
   <mergeCells count="7">
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="S1:U1"/>
@@ -23437,7 +25267,7 @@
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AD1:AG1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z185">
+  <conditionalFormatting sqref="Z3:Z200">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -23448,12 +25278,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I185">
+  <conditionalFormatting sqref="I3:I200">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P185">
+  <conditionalFormatting sqref="P3:P200">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -23544,7 +25374,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$185)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$200)</f>
         <v/>
       </c>
     </row>
@@ -23555,7 +25385,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$185,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$200,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -23566,7 +25396,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$185,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$200,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -23577,7 +25407,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$185,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$200,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -23588,7 +25418,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$185,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$200,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -23599,7 +25429,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$185)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$200)</f>
         <v/>
       </c>
     </row>
@@ -23610,7 +25440,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$185)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -23628,7 +25458,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$185)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$200)</f>
         <v/>
       </c>
     </row>
@@ -23639,7 +25469,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$185,Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$200,Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
     </row>
@@ -23672,7 +25502,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$185="bezahlt")*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$200="bezahlt")*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
     </row>
@@ -23701,7 +25531,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$185,"*verkauft",Artikelstamm!$AH$3:$AH$185,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$200,"*verkauft",Artikelstamm!$AH$3:$AH$200,"")</f>
         <v/>
       </c>
     </row>
@@ -23712,7 +25542,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$185,"*verkauft",Artikelstamm!$AI$3:$AI$185,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$200,"*verkauft",Artikelstamm!$AI$3:$AI$200,"offen")</f>
         <v/>
       </c>
     </row>
@@ -23723,7 +25553,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$185,"reserviert",Artikelstamm!$AK$3:$AK$185,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$200,"reserviert",Artikelstamm!$AK$3:$AK$200,"")</f>
         <v/>
       </c>
     </row>
@@ -23734,7 +25564,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$185,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$200,"")</f>
         <v/>
       </c>
     </row>
@@ -23745,7 +25575,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$185,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$200,"")</f>
         <v/>
       </c>
     </row>
@@ -23785,15 +25615,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$185,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$200,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$185=$A30)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$200=$A30)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$185,$A30,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$200,$A30,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -23804,15 +25634,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$185,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$200,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$185=$A31)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$200=$A31)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$185,$A31,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$200,$A31,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -23823,15 +25653,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$185,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$200,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$185=$A32)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$200=$A32)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$185,$A32,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$200,$A32,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -23890,15 +25720,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A37)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A37)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A37,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A37,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -23909,15 +25739,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A38)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A38)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A38,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A38,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -23928,15 +25758,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A39)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A39)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A39,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A39,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -23947,15 +25777,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A40)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A40)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A40,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A40,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -23966,15 +25796,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A41)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A41)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A41,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A41,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -23985,15 +25815,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A42)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A42)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A42,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A42,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24004,15 +25834,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A43)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A43)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A43,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A43,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24023,15 +25853,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A44)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A44)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A44,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A44,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24042,15 +25872,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A45)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A45)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A45,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A45,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24061,15 +25891,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A46)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A46)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A46,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A46,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24080,15 +25910,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A47)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A47)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A47,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A47,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24099,15 +25929,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A48)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A48)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A48,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A48,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24118,15 +25948,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A49)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A49)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A49,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A49,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24137,15 +25967,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$185,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$185=$A50)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A50)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$185,$A50,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A50,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24204,15 +26034,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A55)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A55)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A55,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A55,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24223,15 +26053,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A56)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A56)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A56,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A56,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24242,15 +26072,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A57)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A57)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A57,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A57,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24261,15 +26091,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A58)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A58)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A58,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A58,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24280,15 +26110,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A59)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A59)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A59,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A59,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24299,15 +26129,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A60)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A60)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A60,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A60,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24318,15 +26148,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A61)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A61)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A61,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A61,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24337,15 +26167,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A62)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A62)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A62,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A62,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24356,15 +26186,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A63)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A63)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A63,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A63,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24375,15 +26205,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A64)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A64)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A64,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A64,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24394,15 +26224,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A65)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A65)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A65,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A65,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24413,15 +26243,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A66)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A66)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A66,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A66,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24432,15 +26262,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A67)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A67)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A67,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A67,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24451,15 +26281,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A68)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A68)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A68,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A68,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24470,15 +26300,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A69)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A69)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A69,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A69,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24489,15 +26319,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A70)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A70)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A70,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A70,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24508,15 +26338,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A71)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A71)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A71,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A71,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24527,15 +26357,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A72)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A72)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A72,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A72,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24546,15 +26376,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$185,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$185=$A73)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A73)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$185,$A73,Artikelstamm!$U$3:$U$185)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A73,Artikelstamm!$U$3:$U$200)</f>
         <v/>
       </c>
     </row>
@@ -24608,11 +26438,11 @@
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A78)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A78)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
     </row>
@@ -24623,11 +26453,11 @@
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A79)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A79)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
     </row>
@@ -24638,11 +26468,11 @@
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A80)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A80)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
     </row>
@@ -24653,11 +26483,11 @@
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A81)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A81)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
     </row>
@@ -24668,11 +26498,11 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A82)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A82)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
     </row>
@@ -24683,11 +26513,11 @@
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$185,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$185=$A83)*Artikelstamm!$K$3:$K$185*Artikelstamm!$AD$3:$AD$185)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A83)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$207</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM200"/>
+  <dimension ref="A1:AM207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23701,7 +23701,11 @@
         </is>
       </c>
       <c r="B188" s="15" t="n"/>
-      <c r="C188" s="15" t="n"/>
+      <c r="C188" s="15" t="inlineStr">
+        <is>
+          <t>NU05-05</t>
+        </is>
+      </c>
       <c r="D188" s="15" t="inlineStr">
         <is>
           <t>NU04</t>
@@ -23733,7 +23737,7 @@
         </is>
       </c>
       <c r="J188" s="17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K188" s="17" t="n"/>
       <c r="L188" s="18">
@@ -23811,10 +23815,14 @@
       <c r="AK188" s="19" t="n"/>
       <c r="AL188" s="16" t="inlineStr">
         <is>
-          <t>3 Regale – abgebildet ist eines davon.</t>
-        </is>
-      </c>
-      <c r="AM188" s="22" t="n"/>
+          <t>4 Regale insgesamt: 3 im Schlafraum 5 und 1 im Treppenraum 1 (dort mit NU05-05 beschriftet).</t>
+        </is>
+      </c>
+      <c r="AM188" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: NU05-05.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="30" customHeight="1">
       <c r="A189" s="15" t="inlineStr">
@@ -23831,12 +23839,12 @@
       </c>
       <c r="E189" s="15" t="inlineStr">
         <is>
-          <t>Schalenstuhl mit Sitzpolster und Holzbeinen</t>
+          <t>Schalenstuhl weiß mit Sitzpolster und Holzbeinen</t>
         </is>
       </c>
       <c r="F189" s="16" t="inlineStr">
         <is>
-          <t>Schalenstuhl mit grauer Kunststoffschale, hellem Sitzpolster und konischen Beinen aus massivem Holz.</t>
+          <t>Schalenstuhl mit weißer Schale und fest verbundenem Sitzpolster, konische Beine aus braunem Massivholz.</t>
         </is>
       </c>
       <c r="G189" s="15" t="inlineStr">
@@ -23932,11 +23940,7 @@
           <t>4 Stühle – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM189" s="22" t="inlineStr">
-        <is>
-          <t>Farbe klaeren: auf dem Erfassungsblatt steht weiss, die Schale wirkt auf dem Foto grau-beige.</t>
-        </is>
-      </c>
+      <c r="AM189" s="22" t="n"/>
     </row>
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="15" t="inlineStr">
@@ -24531,7 +24535,7 @@
       <c r="AK194" s="19" t="n"/>
       <c r="AL194" s="16" t="inlineStr">
         <is>
-          <t>1 Bällebad einschließlich der Bälle.</t>
+          <t>1 Bällebad einschließlich der Bälle, vom Haus bestätigt.</t>
         </is>
       </c>
       <c r="AM194" s="22" t="n"/>
@@ -24674,7 +24678,7 @@
       </c>
       <c r="F196" s="16" t="inlineStr">
         <is>
-          <t>Kinderwerkbank aus Holz mit Lochplatte, drei Werkzeugkästen, Tafellackfläche oben, Zollstockaufdruck an der Kante und Ablage unten.</t>
+          <t>Kinderwerkbank aus Holz mit Lochplatte, drei Werkzeugkästen, Tafellackfläche oben, Zollstockaufdruck an der Kante und Ablage unten. Einschließlich der Wandaufhängung.</t>
         </is>
       </c>
       <c r="G196" s="15" t="inlineStr">
@@ -24767,14 +24771,10 @@
       <c r="AK196" s="19" t="n"/>
       <c r="AL196" s="16" t="inlineStr">
         <is>
-          <t>1 Werkbank. Werkzeug, Helm und Zubehör gehören nicht dazu.</t>
-        </is>
-      </c>
-      <c r="AM196" s="22" t="inlineStr">
-        <is>
-          <t>Stueckzahl auf dem Erfassungsblatt nicht eingetragen, als 1 angenommen - bitte bestaetigen.</t>
-        </is>
-      </c>
+          <t>1 Werkbank einschließlich Wandaufhängung. Werkzeug, Helm und Zubehör gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM196" s="22" t="n"/>
     </row>
     <row r="197" ht="30" customHeight="1">
       <c r="A197" s="15" t="inlineStr">
@@ -25256,8 +25256,838 @@
       </c>
       <c r="AM200" s="22" t="n"/>
     </row>
+    <row r="201" ht="30" customHeight="1">
+      <c r="A201" s="15" t="inlineStr">
+        <is>
+          <t>NU05-01</t>
+        </is>
+      </c>
+      <c r="B201" s="15" t="n"/>
+      <c r="C201" s="15" t="n"/>
+      <c r="D201" s="15" t="inlineStr">
+        <is>
+          <t>NU05</t>
+        </is>
+      </c>
+      <c r="E201" s="15" t="inlineStr">
+        <is>
+          <t>Mitwachsender Treppenhochstuhl, weiß</t>
+        </is>
+      </c>
+      <c r="F201" s="16" t="inlineStr">
+        <is>
+          <t>Treppenhochstuhl aus Buche mit weißen Sitz- und Rückenplatten, Sitz und Fußbrett in der Höhe verstellbar. Die Seitenwangen tragen Lochreihen für die Verstellung.</t>
+        </is>
+      </c>
+      <c r="G201" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H201" s="15" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="I201" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J201" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K201" s="17" t="n"/>
+      <c r="L201" s="18">
+        <f>J201-IF(K201="",0,K201)</f>
+        <v/>
+      </c>
+      <c r="M201" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N201" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O201" s="19" t="n"/>
+      <c r="P201" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q201" s="19" t="n"/>
+      <c r="R201" s="20" t="n"/>
+      <c r="S201" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T201" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U201" s="21">
+        <f>L201*S201</f>
+        <v/>
+      </c>
+      <c r="V201" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W201" s="15" t="inlineStr">
+        <is>
+          <t>F-213</t>
+        </is>
+      </c>
+      <c r="X201" s="19" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="Y201" s="19" t="n"/>
+      <c r="Z201" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA201" s="19" t="n"/>
+      <c r="AB201" s="19" t="n"/>
+      <c r="AC201" s="19" t="n"/>
+      <c r="AD201" s="20" t="n"/>
+      <c r="AE201" s="21">
+        <f>IF(K201="","",K201*AD201)</f>
+        <v/>
+      </c>
+      <c r="AF201" s="19" t="n"/>
+      <c r="AG201" s="19" t="n"/>
+      <c r="AH201" s="19" t="n"/>
+      <c r="AI201" s="19" t="n"/>
+      <c r="AJ201" s="19" t="n"/>
+      <c r="AK201" s="19" t="n"/>
+      <c r="AL201" s="16" t="inlineStr">
+        <is>
+          <t>6 Stühle – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AM201" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: NICHT VEROEFFENTLICHEN, bis die Marke geklaert ist. Auf dem Erfassungsblatt steht "Tripptrapp". Der Stokke Tripp Trapp hat in den Seitenwangen durchgehende Nuten, dieser Stuhl hat Lochreihen - das spricht gegen ein Original. Ein Stokke bringt gebraucht 100-150 EUR, ein Nachbau 25-40 EUR; bei 6 Stueck sind das 150 bis 900 EUR. Marke steht meist auf der Seitenwange oder unter dem Sitz - Nahaufnahme anfordern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="30" customHeight="1">
+      <c r="A202" s="15" t="inlineStr">
+        <is>
+          <t>NU05-02</t>
+        </is>
+      </c>
+      <c r="B202" s="15" t="n"/>
+      <c r="C202" s="15" t="n"/>
+      <c r="D202" s="15" t="inlineStr">
+        <is>
+          <t>NU05</t>
+        </is>
+      </c>
+      <c r="E202" s="15" t="inlineStr">
+        <is>
+          <t>Juniorstuhl Holz weiß mit Kreuzlehne</t>
+        </is>
+      </c>
+      <c r="F202" s="16" t="inlineStr">
+        <is>
+          <t>Juniorstuhl aus Massivholz, weiß lackiert, Rückenlehne mit gekreuzten Streben, Fußstütze als Querstrebe. Lack an Kanten und Sitzfläche abgestoßen.</t>
+        </is>
+      </c>
+      <c r="G202" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H202" s="15" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="I202" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J202" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K202" s="17" t="n"/>
+      <c r="L202" s="18">
+        <f>J202-IF(K202="",0,K202)</f>
+        <v/>
+      </c>
+      <c r="M202" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N202" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O202" s="19" t="n"/>
+      <c r="P202" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q202" s="19" t="n"/>
+      <c r="R202" s="20" t="n"/>
+      <c r="S202" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T202" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U202" s="21">
+        <f>L202*S202</f>
+        <v/>
+      </c>
+      <c r="V202" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W202" s="15" t="inlineStr">
+        <is>
+          <t>F-214</t>
+        </is>
+      </c>
+      <c r="X202" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y202" s="19" t="n"/>
+      <c r="Z202" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA202" s="19" t="n"/>
+      <c r="AB202" s="19" t="n"/>
+      <c r="AC202" s="19" t="n"/>
+      <c r="AD202" s="20" t="n"/>
+      <c r="AE202" s="21">
+        <f>IF(K202="","",K202*AD202)</f>
+        <v/>
+      </c>
+      <c r="AF202" s="19" t="n"/>
+      <c r="AG202" s="19" t="n"/>
+      <c r="AH202" s="19" t="n"/>
+      <c r="AI202" s="19" t="n"/>
+      <c r="AJ202" s="19" t="n"/>
+      <c r="AK202" s="19" t="n"/>
+      <c r="AL202" s="16" t="inlineStr">
+        <is>
+          <t>3 Stühle – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AM202" s="22" t="n"/>
+    </row>
+    <row r="203" ht="30" customHeight="1">
+      <c r="A203" s="15" t="inlineStr">
+        <is>
+          <t>NU05-03</t>
+        </is>
+      </c>
+      <c r="B203" s="15" t="n"/>
+      <c r="C203" s="15" t="n"/>
+      <c r="D203" s="15" t="inlineStr">
+        <is>
+          <t>NU05</t>
+        </is>
+      </c>
+      <c r="E203" s="15" t="inlineStr">
+        <is>
+          <t>Kindertisch weiß groß mit Holzbeinen</t>
+        </is>
+      </c>
+      <c r="F203" s="16" t="inlineStr">
+        <is>
+          <t>Großer Kindertisch: weiße Platte mit abgerundeten Ecken und Multiplex-Kante auf konischen Beinen aus Buche.</t>
+        </is>
+      </c>
+      <c r="G203" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H203" s="15" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="I203" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J203" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K203" s="17" t="n"/>
+      <c r="L203" s="18">
+        <f>J203-IF(K203="",0,K203)</f>
+        <v/>
+      </c>
+      <c r="M203" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N203" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O203" s="19" t="n"/>
+      <c r="P203" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q203" s="19" t="n"/>
+      <c r="R203" s="20" t="n"/>
+      <c r="S203" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T203" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U203" s="21">
+        <f>L203*S203</f>
+        <v/>
+      </c>
+      <c r="V203" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W203" s="15" t="inlineStr">
+        <is>
+          <t>F-215</t>
+        </is>
+      </c>
+      <c r="X203" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y203" s="19" t="n"/>
+      <c r="Z203" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA203" s="19" t="n"/>
+      <c r="AB203" s="19" t="n"/>
+      <c r="AC203" s="19" t="n"/>
+      <c r="AD203" s="20" t="n"/>
+      <c r="AE203" s="21">
+        <f>IF(K203="","",K203*AD203)</f>
+        <v/>
+      </c>
+      <c r="AF203" s="19" t="n"/>
+      <c r="AG203" s="19" t="n"/>
+      <c r="AH203" s="19" t="n"/>
+      <c r="AI203" s="19" t="n"/>
+      <c r="AJ203" s="19" t="n"/>
+      <c r="AK203" s="19" t="n"/>
+      <c r="AL203" s="16" t="inlineStr">
+        <is>
+          <t>2 Tische – abgebildet ist einer davon. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM203" s="22" t="n"/>
+    </row>
+    <row r="204" ht="30" customHeight="1">
+      <c r="A204" s="15" t="inlineStr">
+        <is>
+          <t>NU05-04</t>
+        </is>
+      </c>
+      <c r="B204" s="15" t="n"/>
+      <c r="C204" s="15" t="n"/>
+      <c r="D204" s="15" t="inlineStr">
+        <is>
+          <t>NU05</t>
+        </is>
+      </c>
+      <c r="E204" s="15" t="inlineStr">
+        <is>
+          <t>Regal weiß hoch, vier Böden</t>
+        </is>
+      </c>
+      <c r="F204" s="16" t="inlineStr">
+        <is>
+          <t>Hohes weißes Regal mit vier Einlegeböden, Bohrreihen zum Verstellen.</t>
+        </is>
+      </c>
+      <c r="G204" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H204" s="15" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="I204" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J204" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" s="17" t="n"/>
+      <c r="L204" s="18">
+        <f>J204-IF(K204="",0,K204)</f>
+        <v/>
+      </c>
+      <c r="M204" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N204" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O204" s="19" t="n"/>
+      <c r="P204" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q204" s="19" t="n"/>
+      <c r="R204" s="20" t="n"/>
+      <c r="S204" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T204" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U204" s="21">
+        <f>L204*S204</f>
+        <v/>
+      </c>
+      <c r="V204" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W204" s="15" t="inlineStr">
+        <is>
+          <t>F-216</t>
+        </is>
+      </c>
+      <c r="X204" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y204" s="19" t="n"/>
+      <c r="Z204" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA204" s="19" t="n"/>
+      <c r="AB204" s="19" t="n"/>
+      <c r="AC204" s="19" t="n"/>
+      <c r="AD204" s="20" t="n"/>
+      <c r="AE204" s="21">
+        <f>IF(K204="","",K204*AD204)</f>
+        <v/>
+      </c>
+      <c r="AF204" s="19" t="n"/>
+      <c r="AG204" s="19" t="n"/>
+      <c r="AH204" s="19" t="n"/>
+      <c r="AI204" s="19" t="n"/>
+      <c r="AJ204" s="19" t="n"/>
+      <c r="AK204" s="19" t="n"/>
+      <c r="AL204" s="16" t="inlineStr">
+        <is>
+          <t>1 Regal.</t>
+        </is>
+      </c>
+      <c r="AM204" s="22" t="n"/>
+    </row>
+    <row r="205" ht="30" customHeight="1">
+      <c r="A205" s="15" t="inlineStr">
+        <is>
+          <t>NU05-06</t>
+        </is>
+      </c>
+      <c r="B205" s="15" t="n"/>
+      <c r="C205" s="15" t="n"/>
+      <c r="D205" s="15" t="inlineStr">
+        <is>
+          <t>NU05</t>
+        </is>
+      </c>
+      <c r="E205" s="15" t="inlineStr">
+        <is>
+          <t>Regal weiß mit zwei Schubladen und zwei Böden</t>
+        </is>
+      </c>
+      <c r="F205" s="16" t="inlineStr">
+        <is>
+          <t>Weißes Regal mit zwei Einlegeböden oben und zwei großen Schubladen mit Griffmulden unten, Front der Schubladen dunkel.</t>
+        </is>
+      </c>
+      <c r="G205" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H205" s="15" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="I205" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J205" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" s="17" t="n"/>
+      <c r="L205" s="18">
+        <f>J205-IF(K205="",0,K205)</f>
+        <v/>
+      </c>
+      <c r="M205" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N205" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O205" s="19" t="n"/>
+      <c r="P205" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q205" s="19" t="n"/>
+      <c r="R205" s="20" t="n"/>
+      <c r="S205" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T205" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U205" s="21">
+        <f>L205*S205</f>
+        <v/>
+      </c>
+      <c r="V205" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W205" s="15" t="inlineStr">
+        <is>
+          <t>F-218</t>
+        </is>
+      </c>
+      <c r="X205" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y205" s="19" t="n"/>
+      <c r="Z205" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA205" s="19" t="n"/>
+      <c r="AB205" s="19" t="n"/>
+      <c r="AC205" s="19" t="n"/>
+      <c r="AD205" s="20" t="n"/>
+      <c r="AE205" s="21">
+        <f>IF(K205="","",K205*AD205)</f>
+        <v/>
+      </c>
+      <c r="AF205" s="19" t="n"/>
+      <c r="AG205" s="19" t="n"/>
+      <c r="AH205" s="19" t="n"/>
+      <c r="AI205" s="19" t="n"/>
+      <c r="AJ205" s="19" t="n"/>
+      <c r="AK205" s="19" t="n"/>
+      <c r="AL205" s="16" t="inlineStr">
+        <is>
+          <t>1 Regal. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM205" s="22" t="n"/>
+    </row>
+    <row r="206" ht="30" customHeight="1">
+      <c r="A206" s="15" t="inlineStr">
+        <is>
+          <t>NU05-07</t>
+        </is>
+      </c>
+      <c r="B206" s="15" t="n"/>
+      <c r="C206" s="15" t="n"/>
+      <c r="D206" s="15" t="inlineStr">
+        <is>
+          <t>NU05</t>
+        </is>
+      </c>
+      <c r="E206" s="15" t="inlineStr">
+        <is>
+          <t>Mal- und Trockengestell fahrbar</t>
+        </is>
+      </c>
+      <c r="F206" s="16" t="inlineStr">
+        <is>
+          <t>Fahrbares Gestell aus Holz mit acht herausziehbaren Drahtgitter-Einschüben zum Trocknen von Bildern, Griffstange oben, auf Rollen.</t>
+        </is>
+      </c>
+      <c r="G206" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H206" s="15" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="I206" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J206" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" s="17" t="n"/>
+      <c r="L206" s="18">
+        <f>J206-IF(K206="",0,K206)</f>
+        <v/>
+      </c>
+      <c r="M206" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N206" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O206" s="19" t="n"/>
+      <c r="P206" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q206" s="19" t="n"/>
+      <c r="R206" s="20" t="n"/>
+      <c r="S206" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T206" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U206" s="21">
+        <f>L206*S206</f>
+        <v/>
+      </c>
+      <c r="V206" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W206" s="15" t="inlineStr">
+        <is>
+          <t>F-219</t>
+        </is>
+      </c>
+      <c r="X206" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y206" s="19" t="n"/>
+      <c r="Z206" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA206" s="19" t="n"/>
+      <c r="AB206" s="19" t="n"/>
+      <c r="AC206" s="19" t="n"/>
+      <c r="AD206" s="20" t="n"/>
+      <c r="AE206" s="21">
+        <f>IF(K206="","",K206*AD206)</f>
+        <v/>
+      </c>
+      <c r="AF206" s="19" t="n"/>
+      <c r="AG206" s="19" t="n"/>
+      <c r="AH206" s="19" t="n"/>
+      <c r="AI206" s="19" t="n"/>
+      <c r="AJ206" s="19" t="n"/>
+      <c r="AK206" s="19" t="n"/>
+      <c r="AL206" s="16" t="inlineStr">
+        <is>
+          <t>1 Gestell mit acht Einschüben.</t>
+        </is>
+      </c>
+      <c r="AM206" s="22" t="n"/>
+    </row>
+    <row r="207" ht="30" customHeight="1">
+      <c r="A207" s="15" t="inlineStr">
+        <is>
+          <t>NU05-08</t>
+        </is>
+      </c>
+      <c r="B207" s="15" t="n"/>
+      <c r="C207" s="15" t="n"/>
+      <c r="D207" s="15" t="inlineStr">
+        <is>
+          <t>NU05</t>
+        </is>
+      </c>
+      <c r="E207" s="15" t="inlineStr">
+        <is>
+          <t>Maltafel Holz mit Kreidetafel und Farbablage</t>
+        </is>
+      </c>
+      <c r="F207" s="16" t="inlineStr">
+        <is>
+          <t>Standtafel aus Holz mit schwarzer Kreidetafel, Ablage mit Aussparungen für Farbbecher und Schwamm, Papierrollenhalter oben. Farbspuren am Rahmen.</t>
+        </is>
+      </c>
+      <c r="G207" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H207" s="15" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="I207" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J207" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" s="17" t="n"/>
+      <c r="L207" s="18">
+        <f>J207-IF(K207="",0,K207)</f>
+        <v/>
+      </c>
+      <c r="M207" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N207" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O207" s="19" t="n"/>
+      <c r="P207" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q207" s="19" t="n"/>
+      <c r="R207" s="20" t="n"/>
+      <c r="S207" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T207" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U207" s="21">
+        <f>L207*S207</f>
+        <v/>
+      </c>
+      <c r="V207" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W207" s="15" t="inlineStr">
+        <is>
+          <t>F-220</t>
+        </is>
+      </c>
+      <c r="X207" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y207" s="19" t="n"/>
+      <c r="Z207" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA207" s="19" t="n"/>
+      <c r="AB207" s="19" t="n"/>
+      <c r="AC207" s="19" t="n"/>
+      <c r="AD207" s="20" t="n"/>
+      <c r="AE207" s="21">
+        <f>IF(K207="","",K207*AD207)</f>
+        <v/>
+      </c>
+      <c r="AF207" s="19" t="n"/>
+      <c r="AG207" s="19" t="n"/>
+      <c r="AH207" s="19" t="n"/>
+      <c r="AI207" s="19" t="n"/>
+      <c r="AJ207" s="19" t="n"/>
+      <c r="AK207" s="19" t="n"/>
+      <c r="AL207" s="16" t="inlineStr">
+        <is>
+          <t>1 Tafel. Schwamm und Becher gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM207" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AM200"/>
+  <autoFilter ref="A2:AM207"/>
   <mergeCells count="7">
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="S1:U1"/>
@@ -25267,7 +26097,7 @@
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AD1:AG1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z200">
+  <conditionalFormatting sqref="Z3:Z207">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -25278,12 +26108,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I200">
+  <conditionalFormatting sqref="I3:I207">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P200">
+  <conditionalFormatting sqref="P3:P207">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -25336,7 +26166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -25374,7 +26204,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$200)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$207)</f>
         <v/>
       </c>
     </row>
@@ -25385,7 +26215,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$200,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$207,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -25396,7 +26226,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$200,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$207,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -25407,7 +26237,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$200,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$207,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -25418,7 +26248,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$200,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$207,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -25429,7 +26259,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$200)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$207)</f>
         <v/>
       </c>
     </row>
@@ -25440,7 +26270,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$200)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25458,7 +26288,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$200)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$207)</f>
         <v/>
       </c>
     </row>
@@ -25469,7 +26299,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$200,Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$207,Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
     </row>
@@ -25502,7 +26332,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$200="bezahlt")*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$207="bezahlt")*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
     </row>
@@ -25531,7 +26361,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$200,"*verkauft",Artikelstamm!$AH$3:$AH$200,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$207,"*verkauft",Artikelstamm!$AH$3:$AH$207,"")</f>
         <v/>
       </c>
     </row>
@@ -25542,7 +26372,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$200,"*verkauft",Artikelstamm!$AI$3:$AI$200,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$207,"*verkauft",Artikelstamm!$AI$3:$AI$207,"offen")</f>
         <v/>
       </c>
     </row>
@@ -25553,7 +26383,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$200,"reserviert",Artikelstamm!$AK$3:$AK$200,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$207,"reserviert",Artikelstamm!$AK$3:$AK$207,"")</f>
         <v/>
       </c>
     </row>
@@ -25564,7 +26394,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$200,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$207,"")</f>
         <v/>
       </c>
     </row>
@@ -25575,7 +26405,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$200,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$207,"")</f>
         <v/>
       </c>
     </row>
@@ -25615,15 +26445,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$200,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$207,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$200=$A30)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$207=$A30)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$200,$A30,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$207,$A30,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25634,15 +26464,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$200,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$207,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$200=$A31)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$207=$A31)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$200,$A31,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$207,$A31,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25653,15 +26483,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$200,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$207,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$200=$A32)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$207=$A32)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$200,$A32,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$207,$A32,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25720,15 +26550,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A37)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A37)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A37,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A37,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25739,15 +26569,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A38)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A38)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A38,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A38,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25758,15 +26588,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A39)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A39)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A39,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A39,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25777,15 +26607,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A40)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A40)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A40,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A40,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25796,15 +26626,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A41)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A41)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A41,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A41,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25815,15 +26645,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A42)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A42)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A42,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A42,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25834,15 +26664,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A43)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A43)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A43,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A43,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25853,15 +26683,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A44)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A44)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A44,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A44,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25872,15 +26702,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A45)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A45)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A45,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A45,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25891,15 +26721,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A46)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A46)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A46,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A46,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25910,15 +26740,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A47)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A47)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A47,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A47,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25929,15 +26759,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A48)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A48)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A48,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A48,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25948,15 +26778,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A49)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A49)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A49,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A49,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -25967,15 +26797,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$200,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$200=$A50)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A50)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$200,$A50,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A50,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26034,15 +26864,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A55)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A55)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A55,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A55,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26053,15 +26883,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A56)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A56)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A56,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A56,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26072,15 +26902,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A57)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A57)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A57,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A57,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26091,15 +26921,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A58)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A58)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A58,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A58,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26110,15 +26940,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A59)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A59)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A59,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A59,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26129,15 +26959,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A60)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A60)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A60,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A60,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26148,15 +26978,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A61)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A61)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A61,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A61,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26167,15 +26997,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A62)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A62)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A62,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A62,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26186,15 +27016,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A63)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A63)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A63,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A63,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26205,15 +27035,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A64)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A64)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A64,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A64,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26224,15 +27054,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A65)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A65)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A65,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A65,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26243,15 +27073,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A66)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A66)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A66,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A66,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26262,15 +27092,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A67)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A67)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A67,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A67,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26281,15 +27111,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A68)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A68)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A68,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A68,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26300,15 +27130,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A69)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A69)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A69,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A69,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26319,15 +27149,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A70)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A70)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A70,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A70,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
@@ -26338,201 +27168,220 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A71)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A71)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A71,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A71,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>Treppenraum 1</t>
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A72)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A72)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A72,Artikelstamm!$U$3:$U$200)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A72,Artikelstamm!$U$3:$U$207)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B73" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A73)</f>
+        <v/>
+      </c>
+      <c r="C73" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A73)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <v/>
+      </c>
+      <c r="D73" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A73,Artikelstamm!$U$3:$U$207)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$200,$A73)</f>
-        <v/>
-      </c>
-      <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$200=$A73)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
-        <v/>
-      </c>
-      <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$200,$A73,Artikelstamm!$U$3:$U$200)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="28" t="inlineStr">
+      <c r="B74" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A74)</f>
+        <v/>
+      </c>
+      <c r="C74" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A74)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <v/>
+      </c>
+      <c r="D74" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A74,Artikelstamm!$U$3:$U$207)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B74" s="35">
-        <f>SUM(B55:B73)</f>
-        <v/>
-      </c>
-      <c r="C74" s="36">
-        <f>SUM(C55:C73)</f>
-        <v/>
-      </c>
-      <c r="D74" s="36">
-        <f>SUM(D55:D73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="25" t="inlineStr">
+      <c r="B75" s="35">
+        <f>SUM(B55:B74)</f>
+        <v/>
+      </c>
+      <c r="C75" s="36">
+        <f>SUM(C55:C74)</f>
+        <v/>
+      </c>
+      <c r="D75" s="36">
+        <f>SUM(D55:D74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="32" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B77" s="32" t="inlineStr">
+      <c r="B78" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C77" s="32" t="inlineStr">
+      <c r="C78" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A78)</f>
-        <v/>
-      </c>
-      <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A78)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
-        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A79)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A79)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A80)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A80)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A81)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A81)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A82)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A82)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B83" s="33">
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A83)</f>
+        <v/>
+      </c>
+      <c r="C83" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A83)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$200,$A83)</f>
-        <v/>
-      </c>
-      <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$200=$A83)*Artikelstamm!$K$3:$K$200*Artikelstamm!$AD$3:$AD$200)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="28" t="inlineStr">
+      <c r="B84" s="33">
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A84)</f>
+        <v/>
+      </c>
+      <c r="C84" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A84)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B84" s="35">
-        <f>SUM(B78:B83)</f>
-        <v/>
-      </c>
-      <c r="C84" s="36">
-        <f>SUM(C78:C83)</f>
+      <c r="B85" s="35">
+        <f>SUM(B79:B84)</f>
+        <v/>
+      </c>
+      <c r="C85" s="36">
+        <f>SUM(C79:C84)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$214</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM207"/>
+  <dimension ref="A1:AM214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -26086,8 +26086,854 @@
       </c>
       <c r="AM207" s="22" t="n"/>
     </row>
+    <row r="208" ht="30" customHeight="1">
+      <c r="A208" s="15" t="inlineStr">
+        <is>
+          <t>NU06-01</t>
+        </is>
+      </c>
+      <c r="B208" s="15" t="n"/>
+      <c r="C208" s="15" t="n"/>
+      <c r="D208" s="15" t="inlineStr">
+        <is>
+          <t>NU06</t>
+        </is>
+      </c>
+      <c r="E208" s="15" t="inlineStr">
+        <is>
+          <t>Garderobenwand weiß, 13 Plätze</t>
+        </is>
+      </c>
+      <c r="F208" s="16" t="inlineStr">
+        <is>
+          <t>Lange Garderobenwand in Weiß: oben ein durchgehendes Ablagefach, darunter eine Leiste mit 13 Doppelhaken, unten eine Sitzbank mit offenen Schuhfächern. Schreinerarbeit.</t>
+        </is>
+      </c>
+      <c r="G208" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H208" s="15" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="I208" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J208" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" s="17" t="n"/>
+      <c r="L208" s="18">
+        <f>J208-IF(K208="",0,K208)</f>
+        <v/>
+      </c>
+      <c r="M208" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N208" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O208" s="19" t="n"/>
+      <c r="P208" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q208" s="19" t="n"/>
+      <c r="R208" s="20" t="n"/>
+      <c r="S208" s="20" t="n">
+        <v>250</v>
+      </c>
+      <c r="T208" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U208" s="21">
+        <f>L208*S208</f>
+        <v/>
+      </c>
+      <c r="V208" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W208" s="15" t="inlineStr">
+        <is>
+          <t>F-223</t>
+        </is>
+      </c>
+      <c r="X208" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y208" s="19" t="n"/>
+      <c r="Z208" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA208" s="19" t="n"/>
+      <c r="AB208" s="19" t="n"/>
+      <c r="AC208" s="19" t="n"/>
+      <c r="AD208" s="20" t="n"/>
+      <c r="AE208" s="21">
+        <f>IF(K208="","",K208*AD208)</f>
+        <v/>
+      </c>
+      <c r="AF208" s="19" t="n"/>
+      <c r="AG208" s="19" t="n"/>
+      <c r="AH208" s="19" t="n"/>
+      <c r="AI208" s="19" t="n"/>
+      <c r="AJ208" s="19" t="n"/>
+      <c r="AK208" s="19" t="n"/>
+      <c r="AL208" s="16" t="inlineStr">
+        <is>
+          <t>1 Garderobenwand mit 13 Plätzen. Die Stoffkörbe gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM208" s="22" t="inlineStr">
+        <is>
+          <t>Foto zeigt einen grauen Balken: dort hingen Fotokarten der Kinder mit Namen. Neues Foto ohne die Karten waere besser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="30" customHeight="1">
+      <c r="A209" s="15" t="inlineStr">
+        <is>
+          <t>NU06-02</t>
+        </is>
+      </c>
+      <c r="B209" s="15" t="n"/>
+      <c r="C209" s="15" t="n"/>
+      <c r="D209" s="15" t="inlineStr">
+        <is>
+          <t>NU06</t>
+        </is>
+      </c>
+      <c r="E209" s="15" t="inlineStr">
+        <is>
+          <t>Garderobenwand weiß, 9 Plätze</t>
+        </is>
+      </c>
+      <c r="F209" s="16" t="inlineStr">
+        <is>
+          <t>Garderobenwand in Weiß: oben ein durchgehendes Ablagefach, darunter eine Leiste mit neun Doppelhaken, unten eine Sitzbank mit offenen Schuhfächern. Schreinerarbeit.</t>
+        </is>
+      </c>
+      <c r="G209" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H209" s="15" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="I209" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J209" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K209" s="17" t="n"/>
+      <c r="L209" s="18">
+        <f>J209-IF(K209="",0,K209)</f>
+        <v/>
+      </c>
+      <c r="M209" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N209" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O209" s="19" t="n"/>
+      <c r="P209" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q209" s="19" t="n"/>
+      <c r="R209" s="20" t="n"/>
+      <c r="S209" s="20" t="n">
+        <v>180</v>
+      </c>
+      <c r="T209" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U209" s="21">
+        <f>L209*S209</f>
+        <v/>
+      </c>
+      <c r="V209" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W209" s="15" t="inlineStr">
+        <is>
+          <t>F-224</t>
+        </is>
+      </c>
+      <c r="X209" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y209" s="19" t="n"/>
+      <c r="Z209" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA209" s="19" t="n"/>
+      <c r="AB209" s="19" t="n"/>
+      <c r="AC209" s="19" t="n"/>
+      <c r="AD209" s="20" t="n"/>
+      <c r="AE209" s="21">
+        <f>IF(K209="","",K209*AD209)</f>
+        <v/>
+      </c>
+      <c r="AF209" s="19" t="n"/>
+      <c r="AG209" s="19" t="n"/>
+      <c r="AH209" s="19" t="n"/>
+      <c r="AI209" s="19" t="n"/>
+      <c r="AJ209" s="19" t="n"/>
+      <c r="AK209" s="19" t="n"/>
+      <c r="AL209" s="16" t="inlineStr">
+        <is>
+          <t>6 Garderobenwände mit je 9 Plätzen – abgebildet ist eine davon. Die Stoffkörbe gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM209" s="22" t="n"/>
+    </row>
+    <row r="210" ht="30" customHeight="1">
+      <c r="A210" s="15" t="inlineStr">
+        <is>
+          <t>NU06-03</t>
+        </is>
+      </c>
+      <c r="B210" s="15" t="n"/>
+      <c r="C210" s="15" t="n"/>
+      <c r="D210" s="15" t="inlineStr">
+        <is>
+          <t>NU06</t>
+        </is>
+      </c>
+      <c r="E210" s="15" t="inlineStr">
+        <is>
+          <t>Hängegarderobe weiß mit Wannen</t>
+        </is>
+      </c>
+      <c r="F210" s="16" t="inlineStr">
+        <is>
+          <t>Wandelement in Weiß mit sechs eingeschobenen Kunststoffwannen, darunter drei rote Doppelhaken.</t>
+        </is>
+      </c>
+      <c r="G210" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H210" s="15" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="I210" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J210" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" s="17" t="n"/>
+      <c r="L210" s="18">
+        <f>J210-IF(K210="",0,K210)</f>
+        <v/>
+      </c>
+      <c r="M210" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N210" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O210" s="19" t="n"/>
+      <c r="P210" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q210" s="19" t="n"/>
+      <c r="R210" s="20" t="n"/>
+      <c r="S210" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T210" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U210" s="21">
+        <f>L210*S210</f>
+        <v/>
+      </c>
+      <c r="V210" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W210" s="15" t="inlineStr">
+        <is>
+          <t>F-225</t>
+        </is>
+      </c>
+      <c r="X210" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y210" s="19" t="n"/>
+      <c r="Z210" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA210" s="19" t="n"/>
+      <c r="AB210" s="19" t="n"/>
+      <c r="AC210" s="19" t="n"/>
+      <c r="AD210" s="20" t="n"/>
+      <c r="AE210" s="21">
+        <f>IF(K210="","",K210*AD210)</f>
+        <v/>
+      </c>
+      <c r="AF210" s="19" t="n"/>
+      <c r="AG210" s="19" t="n"/>
+      <c r="AH210" s="19" t="n"/>
+      <c r="AI210" s="19" t="n"/>
+      <c r="AJ210" s="19" t="n"/>
+      <c r="AK210" s="19" t="n"/>
+      <c r="AL210" s="16" t="inlineStr">
+        <is>
+          <t>3 Elemente einschließlich der Wannen – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AM210" s="22" t="inlineStr">
+        <is>
+          <t>Foto zeigt zwei graue Balken: dort standen Vornamen auf den Etiketten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="30" customHeight="1">
+      <c r="A211" s="15" t="inlineStr">
+        <is>
+          <t>NU06-04</t>
+        </is>
+      </c>
+      <c r="B211" s="15" t="n"/>
+      <c r="C211" s="15" t="n"/>
+      <c r="D211" s="15" t="inlineStr">
+        <is>
+          <t>NU06</t>
+        </is>
+      </c>
+      <c r="E211" s="15" t="inlineStr">
+        <is>
+          <t>Holzregal weiß, sechs Fächer</t>
+        </is>
+      </c>
+      <c r="F211" s="16" t="inlineStr">
+        <is>
+          <t>Regal aus Holz, weiß gestrichen, sechs Fächer in zwei Reihen. Farbe an Kanten und Fachböden großflächig abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="G211" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H211" s="15" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="I211" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J211" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K211" s="17" t="n"/>
+      <c r="L211" s="18">
+        <f>J211-IF(K211="",0,K211)</f>
+        <v/>
+      </c>
+      <c r="M211" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N211" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O211" s="19" t="n"/>
+      <c r="P211" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q211" s="19" t="n"/>
+      <c r="R211" s="20" t="n"/>
+      <c r="S211" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T211" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U211" s="21">
+        <f>L211*S211</f>
+        <v/>
+      </c>
+      <c r="V211" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W211" s="15" t="inlineStr">
+        <is>
+          <t>F-226</t>
+        </is>
+      </c>
+      <c r="X211" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y211" s="19" t="n"/>
+      <c r="Z211" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA211" s="19" t="n"/>
+      <c r="AB211" s="19" t="n"/>
+      <c r="AC211" s="19" t="n"/>
+      <c r="AD211" s="20" t="n"/>
+      <c r="AE211" s="21">
+        <f>IF(K211="","",K211*AD211)</f>
+        <v/>
+      </c>
+      <c r="AF211" s="19" t="n"/>
+      <c r="AG211" s="19" t="n"/>
+      <c r="AH211" s="19" t="n"/>
+      <c r="AI211" s="19" t="n"/>
+      <c r="AJ211" s="19" t="n"/>
+      <c r="AK211" s="19" t="n"/>
+      <c r="AL211" s="16" t="inlineStr">
+        <is>
+          <t>2 Regale – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AM211" s="22" t="n"/>
+    </row>
+    <row r="212" ht="30" customHeight="1">
+      <c r="A212" s="15" t="inlineStr">
+        <is>
+          <t>NU06-05</t>
+        </is>
+      </c>
+      <c r="B212" s="15" t="n"/>
+      <c r="C212" s="15" t="n"/>
+      <c r="D212" s="15" t="inlineStr">
+        <is>
+          <t>NU06</t>
+        </is>
+      </c>
+      <c r="E212" s="15" t="inlineStr">
+        <is>
+          <t>Bauknecht Kühl-Gefrierkombination, Standgerät</t>
+        </is>
+      </c>
+      <c r="F212" s="16" t="inlineStr">
+        <is>
+          <t>Standgerät von Bauknecht in Edelstahloptik: Kühlteil oben mit Glasböden, Gemüsefach und Innenbeleuchtung, Gefrierteil unten. No Frost.</t>
+        </is>
+      </c>
+      <c r="G212" s="15" t="inlineStr">
+        <is>
+          <t>Technik</t>
+        </is>
+      </c>
+      <c r="H212" s="15" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="I212" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J212" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K212" s="17" t="n"/>
+      <c r="L212" s="18">
+        <f>J212-IF(K212="",0,K212)</f>
+        <v/>
+      </c>
+      <c r="M212" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N212" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O212" s="19" t="n"/>
+      <c r="P212" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q212" s="19" t="n"/>
+      <c r="R212" s="20" t="n"/>
+      <c r="S212" s="20" t="n">
+        <v>220</v>
+      </c>
+      <c r="T212" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U212" s="21">
+        <f>L212*S212</f>
+        <v/>
+      </c>
+      <c r="V212" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W212" s="15" t="inlineStr">
+        <is>
+          <t>F-227</t>
+        </is>
+      </c>
+      <c r="X212" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y212" s="19" t="n"/>
+      <c r="Z212" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA212" s="19" t="inlineStr">
+        <is>
+          <t>Bauknecht</t>
+        </is>
+      </c>
+      <c r="AB212" s="19" t="n"/>
+      <c r="AC212" s="19" t="n"/>
+      <c r="AD212" s="20" t="n"/>
+      <c r="AE212" s="21">
+        <f>IF(K212="","",K212*AD212)</f>
+        <v/>
+      </c>
+      <c r="AF212" s="19" t="n"/>
+      <c r="AG212" s="19" t="n"/>
+      <c r="AH212" s="19" t="n"/>
+      <c r="AI212" s="19" t="n"/>
+      <c r="AJ212" s="19" t="n"/>
+      <c r="AK212" s="19" t="n"/>
+      <c r="AL212" s="16" t="inlineStr">
+        <is>
+          <t>1 Gerät. Der Innenraum ist auf Foto F-228 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AM212" s="22" t="inlineStr">
+        <is>
+          <t>Foto zeigt einen grauen Balken: in der Tuer spiegelte sich eine Person. Neues Foto aus anderem Winkel waere besser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="30" customHeight="1">
+      <c r="A213" s="15" t="inlineStr">
+        <is>
+          <t>NU06-06</t>
+        </is>
+      </c>
+      <c r="B213" s="15" t="n"/>
+      <c r="C213" s="15" t="n"/>
+      <c r="D213" s="15" t="inlineStr">
+        <is>
+          <t>NU06</t>
+        </is>
+      </c>
+      <c r="E213" s="15" t="inlineStr">
+        <is>
+          <t>Schwerlastregal verzinkt, vier Böden</t>
+        </is>
+      </c>
+      <c r="F213" s="16" t="inlineStr">
+        <is>
+          <t>Steckregal aus verzinktem Stahl mit vier Holzböden, höhenverstellbar.</t>
+        </is>
+      </c>
+      <c r="G213" s="15" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="H213" s="15" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="I213" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J213" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K213" s="17" t="n"/>
+      <c r="L213" s="18">
+        <f>J213-IF(K213="",0,K213)</f>
+        <v/>
+      </c>
+      <c r="M213" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N213" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O213" s="19" t="n"/>
+      <c r="P213" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q213" s="19" t="n"/>
+      <c r="R213" s="20" t="n"/>
+      <c r="S213" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T213" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U213" s="21">
+        <f>L213*S213</f>
+        <v/>
+      </c>
+      <c r="V213" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W213" s="15" t="inlineStr">
+        <is>
+          <t>F-229</t>
+        </is>
+      </c>
+      <c r="X213" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y213" s="19" t="n"/>
+      <c r="Z213" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA213" s="19" t="n"/>
+      <c r="AB213" s="19" t="n"/>
+      <c r="AC213" s="19" t="n"/>
+      <c r="AD213" s="20" t="n"/>
+      <c r="AE213" s="21">
+        <f>IF(K213="","",K213*AD213)</f>
+        <v/>
+      </c>
+      <c r="AF213" s="19" t="n"/>
+      <c r="AG213" s="19" t="n"/>
+      <c r="AH213" s="19" t="n"/>
+      <c r="AI213" s="19" t="n"/>
+      <c r="AJ213" s="19" t="n"/>
+      <c r="AK213" s="19" t="n"/>
+      <c r="AL213" s="16" t="inlineStr">
+        <is>
+          <t>2 Regale – abgebildet ist eines davon. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM213" s="22" t="n"/>
+    </row>
+    <row r="214" ht="30" customHeight="1">
+      <c r="A214" s="15" t="inlineStr">
+        <is>
+          <t>NU06-07</t>
+        </is>
+      </c>
+      <c r="B214" s="15" t="n"/>
+      <c r="C214" s="15" t="n"/>
+      <c r="D214" s="15" t="inlineStr">
+        <is>
+          <t>NU06</t>
+        </is>
+      </c>
+      <c r="E214" s="15" t="inlineStr">
+        <is>
+          <t>Bild Paris bei Nacht, groß gerahmt</t>
+        </is>
+      </c>
+      <c r="F214" s="16" t="inlineStr">
+        <is>
+          <t>Großformatiges Bild von Paris bei Nacht mit beleuchtetem Eiffelturm, schwarz-weiß mit goldenen Lichtern, in silberfarbenem Aluminiumrahmen. Aufdruck am unteren Rand: „Paris" Scanpix/age fotostock, Jean-Marc Charles, gedruckt für IKEA.</t>
+        </is>
+      </c>
+      <c r="G214" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H214" s="15" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="I214" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J214" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" s="17" t="n"/>
+      <c r="L214" s="18">
+        <f>J214-IF(K214="",0,K214)</f>
+        <v/>
+      </c>
+      <c r="M214" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N214" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O214" s="19" t="n"/>
+      <c r="P214" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q214" s="19" t="n"/>
+      <c r="R214" s="20" t="n"/>
+      <c r="S214" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T214" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U214" s="21">
+        <f>L214*S214</f>
+        <v/>
+      </c>
+      <c r="V214" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W214" s="15" t="inlineStr">
+        <is>
+          <t>F-230</t>
+        </is>
+      </c>
+      <c r="X214" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y214" s="19" t="n"/>
+      <c r="Z214" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA214" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB214" s="19" t="n"/>
+      <c r="AC214" s="19" t="n"/>
+      <c r="AD214" s="20" t="n"/>
+      <c r="AE214" s="21">
+        <f>IF(K214="","",K214*AD214)</f>
+        <v/>
+      </c>
+      <c r="AF214" s="19" t="n"/>
+      <c r="AG214" s="19" t="n"/>
+      <c r="AH214" s="19" t="n"/>
+      <c r="AI214" s="19" t="n"/>
+      <c r="AJ214" s="19" t="n"/>
+      <c r="AK214" s="19" t="n"/>
+      <c r="AL214" s="16" t="inlineStr">
+        <is>
+          <t>1 Bild.</t>
+        </is>
+      </c>
+      <c r="AM214" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AM207"/>
+  <autoFilter ref="A2:AM214"/>
   <mergeCells count="7">
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="S1:U1"/>
@@ -26097,7 +26943,7 @@
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AD1:AG1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z207">
+  <conditionalFormatting sqref="Z3:Z214">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -26108,12 +26954,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I207">
+  <conditionalFormatting sqref="I3:I214">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P207">
+  <conditionalFormatting sqref="P3:P214">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -26166,7 +27012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -26204,7 +27050,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$207)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$214)</f>
         <v/>
       </c>
     </row>
@@ -26215,7 +27061,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$207,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$214,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -26226,7 +27072,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$207,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$214,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -26237,7 +27083,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$207,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$214,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -26248,7 +27094,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$207,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$214,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -26259,7 +27105,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$207)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$214)</f>
         <v/>
       </c>
     </row>
@@ -26270,7 +27116,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$207)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26288,7 +27134,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$207)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$214)</f>
         <v/>
       </c>
     </row>
@@ -26299,7 +27145,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$207,Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$214,Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
     </row>
@@ -26332,7 +27178,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$207="bezahlt")*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$214="bezahlt")*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
     </row>
@@ -26361,7 +27207,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$207,"*verkauft",Artikelstamm!$AH$3:$AH$207,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$214,"*verkauft",Artikelstamm!$AH$3:$AH$214,"")</f>
         <v/>
       </c>
     </row>
@@ -26372,7 +27218,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$207,"*verkauft",Artikelstamm!$AI$3:$AI$207,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$214,"*verkauft",Artikelstamm!$AI$3:$AI$214,"offen")</f>
         <v/>
       </c>
     </row>
@@ -26383,7 +27229,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$207,"reserviert",Artikelstamm!$AK$3:$AK$207,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$214,"reserviert",Artikelstamm!$AK$3:$AK$214,"")</f>
         <v/>
       </c>
     </row>
@@ -26394,7 +27240,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$207,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$214,"")</f>
         <v/>
       </c>
     </row>
@@ -26405,7 +27251,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$207,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$214,"")</f>
         <v/>
       </c>
     </row>
@@ -26445,15 +27291,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$207,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$214,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$207=$A30)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$214=$A30)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$207,$A30,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$214,$A30,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26464,15 +27310,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$207,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$214,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$207=$A31)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$214=$A31)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$207,$A31,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$214,$A31,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26483,15 +27329,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$207,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$214,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$207=$A32)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$214=$A32)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$207,$A32,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$214,$A32,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26550,15 +27396,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A37)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A37)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A37,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A37,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26569,15 +27415,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A38)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A38)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A38,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A38,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26588,15 +27434,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A39)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A39)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A39,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A39,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26607,15 +27453,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A40)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A40)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A40,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A40,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26626,15 +27472,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A41)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A41)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A41,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A41,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26645,15 +27491,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A42)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A42)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A42,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A42,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26664,15 +27510,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A43)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A43)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A43,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A43,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26683,15 +27529,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A44)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A44)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A44,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A44,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26702,15 +27548,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A45)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A45)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A45,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A45,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26721,15 +27567,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A46)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A46)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A46,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A46,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26740,15 +27586,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A47)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A47)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A47,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A47,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26759,15 +27605,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A48)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A48)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A48,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A48,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26778,15 +27624,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A49)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A49)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A49,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A49,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26797,15 +27643,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$207,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$207=$A50)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A50)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$207,$A50,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A50,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26864,15 +27710,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A55)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A55)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A55,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A55,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26883,15 +27729,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A56)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A56)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A56,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A56,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26902,15 +27748,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A57)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A57)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A57,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A57,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26921,15 +27767,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A58)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A58)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A58,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A58,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26940,15 +27786,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A59)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A59)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A59,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A59,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26959,15 +27805,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A60)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A60)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A60,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A60,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26978,15 +27824,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A61)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A61)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A61,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A61,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -26997,15 +27843,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A62)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A62)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A62,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A62,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27016,15 +27862,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A63)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A63)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A63,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A63,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27035,15 +27881,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A64)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A64)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A64,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A64,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27054,15 +27900,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A65)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A65)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A65,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A65,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27073,15 +27919,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A66)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A66)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A66,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A66,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27092,15 +27938,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A67)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A67)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A67,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A67,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27111,15 +27957,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A68)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A68)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A68,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A68,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27130,15 +27976,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A69)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A69)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A69,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A69,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27149,15 +27995,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A70)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A70)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A70,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A70,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27168,15 +28014,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A71)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A71)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A71,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A71,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
@@ -27187,201 +28033,220 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A72)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A72)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A72,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A72,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A73)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A73)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A73,Artikelstamm!$U$3:$U$207)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A73,Artikelstamm!$U$3:$U$214)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B74" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A74)</f>
+        <v/>
+      </c>
+      <c r="C74" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A74)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <v/>
+      </c>
+      <c r="D74" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A74,Artikelstamm!$U$3:$U$214)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$207,$A74)</f>
-        <v/>
-      </c>
-      <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$207=$A74)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
-        <v/>
-      </c>
-      <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$207,$A74,Artikelstamm!$U$3:$U$207)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+      <c r="B75" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A75)</f>
+        <v/>
+      </c>
+      <c r="C75" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A75)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <v/>
+      </c>
+      <c r="D75" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A75,Artikelstamm!$U$3:$U$214)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B75" s="35">
-        <f>SUM(B55:B74)</f>
-        <v/>
-      </c>
-      <c r="C75" s="36">
-        <f>SUM(C55:C74)</f>
-        <v/>
-      </c>
-      <c r="D75" s="36">
-        <f>SUM(D55:D74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="25" t="inlineStr">
+      <c r="B76" s="35">
+        <f>SUM(B55:B75)</f>
+        <v/>
+      </c>
+      <c r="C76" s="36">
+        <f>SUM(C55:C75)</f>
+        <v/>
+      </c>
+      <c r="D76" s="36">
+        <f>SUM(D55:D75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="32" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B78" s="32" t="inlineStr">
+      <c r="B79" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C78" s="32" t="inlineStr">
+      <c r="C79" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A79)</f>
-        <v/>
-      </c>
-      <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A79)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
-        <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A80)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A80)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A81)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A81)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A82)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A82)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A83)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A83)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B84" s="33">
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A84)</f>
+        <v/>
+      </c>
+      <c r="C84" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A84)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$207,$A84)</f>
-        <v/>
-      </c>
-      <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$207=$A84)*Artikelstamm!$K$3:$K$207*Artikelstamm!$AD$3:$AD$207)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="28" t="inlineStr">
+      <c r="B85" s="33">
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A85)</f>
+        <v/>
+      </c>
+      <c r="C85" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A85)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B85" s="35">
-        <f>SUM(B79:B84)</f>
-        <v/>
-      </c>
-      <c r="C85" s="36">
-        <f>SUM(C79:C84)</f>
+      <c r="B86" s="35">
+        <f>SUM(B80:B85)</f>
+        <v/>
+      </c>
+      <c r="C86" s="36">
+        <f>SUM(C80:C85)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$221</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM214"/>
+  <dimension ref="A1:AM221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22591,7 +22591,7 @@
       <c r="AK178" s="19" t="n"/>
       <c r="AL178" s="16" t="inlineStr">
         <is>
-          <t>1 Küche aus 5 Modulen, vom Haus bestätigt.</t>
+          <t>1 Küche aus 5 Modulen, vom Haus bestätigt. Eine zweite Wesco-Küche steht unter NU07-03.</t>
         </is>
       </c>
       <c r="AM178" s="22" t="inlineStr">
@@ -23703,7 +23703,7 @@
       <c r="B188" s="15" t="n"/>
       <c r="C188" s="15" t="inlineStr">
         <is>
-          <t>NU05-05</t>
+          <t>NU05-05, NU07-06</t>
         </is>
       </c>
       <c r="D188" s="15" t="inlineStr">
@@ -23737,7 +23737,7 @@
         </is>
       </c>
       <c r="J188" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K188" s="17" t="n"/>
       <c r="L188" s="18">
@@ -23815,12 +23815,12 @@
       <c r="AK188" s="19" t="n"/>
       <c r="AL188" s="16" t="inlineStr">
         <is>
-          <t>4 Regale insgesamt: 3 im Schlafraum 5 und 1 im Treppenraum 1 (dort mit NU05-05 beschriftet).</t>
+          <t>5 Regale insgesamt: 3 im Schlafraum 5, 1 im Treppenraum 1 (dort NU05-05) und 1 in der Garage (dort NU07-06).</t>
         </is>
       </c>
       <c r="AM188" s="22" t="inlineStr">
         <is>
-          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: NU05-05.</t>
+          <t>Zusammengefasste Position – Post-it-Nummern in den anderen Räumen: NU05-05, NU07-06.</t>
         </is>
       </c>
     </row>
@@ -26932,8 +26932,846 @@
       </c>
       <c r="AM214" s="22" t="n"/>
     </row>
+    <row r="215" ht="30" customHeight="1">
+      <c r="A215" s="15" t="inlineStr">
+        <is>
+          <t>NU07-01</t>
+        </is>
+      </c>
+      <c r="B215" s="15" t="n"/>
+      <c r="C215" s="15" t="n"/>
+      <c r="D215" s="15" t="inlineStr">
+        <is>
+          <t>NU07</t>
+        </is>
+      </c>
+      <c r="E215" s="15" t="inlineStr">
+        <is>
+          <t>Hausbett schwarz mit Dach</t>
+        </is>
+      </c>
+      <c r="F215" s="16" t="inlineStr">
+        <is>
+          <t>Kinderbett in Hausform, dunkelbraun-schwarz lackiert, mit Satteldach, Firstbalken und ausgesägten Sprossenfenstern an beiden Seiten. Matratze liegt auf und kann auf Wunsch mitgenommen werden.</t>
+        </is>
+      </c>
+      <c r="G215" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H215" s="15" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="I215" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J215" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" s="17" t="n"/>
+      <c r="L215" s="18">
+        <f>J215-IF(K215="",0,K215)</f>
+        <v/>
+      </c>
+      <c r="M215" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N215" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O215" s="19" t="n"/>
+      <c r="P215" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q215" s="19" t="n"/>
+      <c r="R215" s="20" t="n"/>
+      <c r="S215" s="20" t="n">
+        <v>180</v>
+      </c>
+      <c r="T215" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U215" s="21">
+        <f>L215*S215</f>
+        <v/>
+      </c>
+      <c r="V215" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W215" s="15" t="inlineStr">
+        <is>
+          <t>F-233</t>
+        </is>
+      </c>
+      <c r="X215" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y215" s="19" t="n"/>
+      <c r="Z215" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA215" s="19" t="n"/>
+      <c r="AB215" s="19" t="n"/>
+      <c r="AC215" s="19" t="n"/>
+      <c r="AD215" s="20" t="n"/>
+      <c r="AE215" s="21">
+        <f>IF(K215="","",K215*AD215)</f>
+        <v/>
+      </c>
+      <c r="AF215" s="19" t="n"/>
+      <c r="AG215" s="19" t="n"/>
+      <c r="AH215" s="19" t="n"/>
+      <c r="AI215" s="19" t="n"/>
+      <c r="AJ215" s="19" t="n"/>
+      <c r="AK215" s="19" t="n"/>
+      <c r="AL215" s="16" t="inlineStr">
+        <is>
+          <t>1 Bett. Bettwäsche und Kissen gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM215" s="22" t="n"/>
+    </row>
+    <row r="216" ht="30" customHeight="1">
+      <c r="A216" s="15" t="inlineStr">
+        <is>
+          <t>NU07-02</t>
+        </is>
+      </c>
+      <c r="B216" s="15" t="n"/>
+      <c r="C216" s="15" t="n"/>
+      <c r="D216" s="15" t="inlineStr">
+        <is>
+          <t>NU07</t>
+        </is>
+      </c>
+      <c r="E216" s="15" t="inlineStr">
+        <is>
+          <t>Kaufladen weiß mit Aufsatz</t>
+        </is>
+      </c>
+      <c r="F216" s="16" t="inlineStr">
+        <is>
+          <t>Kaufladen aus Holz, weiß mit grauer Rückwand: Verkaufstheke mit Ablage unten, Aufsatz mit sechs Fächern und geschwungener Blende.</t>
+        </is>
+      </c>
+      <c r="G216" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H216" s="15" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="I216" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J216" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" s="17" t="n"/>
+      <c r="L216" s="18">
+        <f>J216-IF(K216="",0,K216)</f>
+        <v/>
+      </c>
+      <c r="M216" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N216" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O216" s="19" t="n"/>
+      <c r="P216" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q216" s="19" t="n"/>
+      <c r="R216" s="20" t="n"/>
+      <c r="S216" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T216" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U216" s="21">
+        <f>L216*S216</f>
+        <v/>
+      </c>
+      <c r="V216" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W216" s="15" t="inlineStr">
+        <is>
+          <t>F-234</t>
+        </is>
+      </c>
+      <c r="X216" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y216" s="19" t="n"/>
+      <c r="Z216" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA216" s="19" t="n"/>
+      <c r="AB216" s="19" t="n"/>
+      <c r="AC216" s="19" t="n"/>
+      <c r="AD216" s="20" t="n"/>
+      <c r="AE216" s="21">
+        <f>IF(K216="","",K216*AD216)</f>
+        <v/>
+      </c>
+      <c r="AF216" s="19" t="n"/>
+      <c r="AG216" s="19" t="n"/>
+      <c r="AH216" s="19" t="n"/>
+      <c r="AI216" s="19" t="n"/>
+      <c r="AJ216" s="19" t="n"/>
+      <c r="AK216" s="19" t="n"/>
+      <c r="AL216" s="16" t="inlineStr">
+        <is>
+          <t>1 Kaufladen. Spiellebensmittel, Kasse und Telefon gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM216" s="22" t="n"/>
+    </row>
+    <row r="217" ht="30" customHeight="1">
+      <c r="A217" s="15" t="inlineStr">
+        <is>
+          <t>NU07-03</t>
+        </is>
+      </c>
+      <c r="B217" s="15" t="n"/>
+      <c r="C217" s="15" t="n"/>
+      <c r="D217" s="15" t="inlineStr">
+        <is>
+          <t>NU07</t>
+        </is>
+      </c>
+      <c r="E217" s="15" t="inlineStr">
+        <is>
+          <t>Wesco Spielküche, mehrteilig</t>
+        </is>
+      </c>
+      <c r="F217" s="16" t="inlineStr">
+        <is>
+          <t>Zweite Spielküche von Wesco aus Birke-Multiplex: Mikrowellenmodul und Hängeschrank für die Wand, dazu Unterschränke mit Kochfeld, Spülbecken und Herdplatte. Weiße Klappen mit Holzgriffen, Module stehen frei.</t>
+        </is>
+      </c>
+      <c r="G217" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H217" s="15" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="I217" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J217" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" s="17" t="n"/>
+      <c r="L217" s="18">
+        <f>J217-IF(K217="",0,K217)</f>
+        <v/>
+      </c>
+      <c r="M217" s="15" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N217" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O217" s="19" t="n"/>
+      <c r="P217" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q217" s="19" t="n"/>
+      <c r="R217" s="20" t="n"/>
+      <c r="S217" s="20" t="n">
+        <v>650</v>
+      </c>
+      <c r="T217" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U217" s="21">
+        <f>L217*S217</f>
+        <v/>
+      </c>
+      <c r="V217" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W217" s="15" t="inlineStr">
+        <is>
+          <t>F-236</t>
+        </is>
+      </c>
+      <c r="X217" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y217" s="19" t="n"/>
+      <c r="Z217" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA217" s="19" t="inlineStr">
+        <is>
+          <t>Wesco</t>
+        </is>
+      </c>
+      <c r="AB217" s="19" t="n"/>
+      <c r="AC217" s="19" t="n"/>
+      <c r="AD217" s="20" t="n"/>
+      <c r="AE217" s="21">
+        <f>IF(K217="","",K217*AD217)</f>
+        <v/>
+      </c>
+      <c r="AF217" s="19" t="n"/>
+      <c r="AG217" s="19" t="n"/>
+      <c r="AH217" s="19" t="n"/>
+      <c r="AI217" s="19" t="n"/>
+      <c r="AJ217" s="19" t="n"/>
+      <c r="AK217" s="19" t="n"/>
+      <c r="AL217" s="16" t="inlineStr">
+        <is>
+          <t>1 Küche aus mehreren Modulen. Eine zweite Wesco-Küche steht unter NU03-03.</t>
+        </is>
+      </c>
+      <c r="AM217" s="22" t="inlineStr">
+        <is>
+          <t>Zu klaeren: ist diese Kueche baugleich mit NU03-03? Wenn ja, zu einer Position mit 2 Stueck zusammenfassen. Modulzahl hier noch nicht gezaehlt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="30" customHeight="1">
+      <c r="A218" s="15" t="inlineStr">
+        <is>
+          <t>NU07-04</t>
+        </is>
+      </c>
+      <c r="B218" s="15" t="n"/>
+      <c r="C218" s="15" t="n"/>
+      <c r="D218" s="15" t="inlineStr">
+        <is>
+          <t>NU07</t>
+        </is>
+      </c>
+      <c r="E218" s="15" t="inlineStr">
+        <is>
+          <t>howa Kinderspielgrill</t>
+        </is>
+      </c>
+      <c r="F218" s="16" t="inlineStr">
+        <is>
+          <t>Spielgrill aus Holz von howa: Rollklappe in Alu-Optik, Grillrost, zwei Drehknöpfe mit Digitalanzeige, seitliche Kochstelle und Ablageboden. Farbe an Kanten abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="G218" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H218" s="15" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="I218" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J218" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" s="17" t="n"/>
+      <c r="L218" s="18">
+        <f>J218-IF(K218="",0,K218)</f>
+        <v/>
+      </c>
+      <c r="M218" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N218" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O218" s="19" t="n"/>
+      <c r="P218" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q218" s="19" t="n"/>
+      <c r="R218" s="20" t="n"/>
+      <c r="S218" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T218" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U218" s="21">
+        <f>L218*S218</f>
+        <v/>
+      </c>
+      <c r="V218" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W218" s="15" t="inlineStr">
+        <is>
+          <t>F-237</t>
+        </is>
+      </c>
+      <c r="X218" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y218" s="19" t="n"/>
+      <c r="Z218" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA218" s="19" t="inlineStr">
+        <is>
+          <t>howa</t>
+        </is>
+      </c>
+      <c r="AB218" s="19" t="n"/>
+      <c r="AC218" s="19" t="n"/>
+      <c r="AD218" s="20" t="n"/>
+      <c r="AE218" s="21">
+        <f>IF(K218="","",K218*AD218)</f>
+        <v/>
+      </c>
+      <c r="AF218" s="19" t="n"/>
+      <c r="AG218" s="19" t="n"/>
+      <c r="AH218" s="19" t="n"/>
+      <c r="AI218" s="19" t="n"/>
+      <c r="AJ218" s="19" t="n"/>
+      <c r="AK218" s="19" t="n"/>
+      <c r="AL218" s="16" t="inlineStr">
+        <is>
+          <t>1 Grill.</t>
+        </is>
+      </c>
+      <c r="AM218" s="22" t="n"/>
+    </row>
+    <row r="219" ht="30" customHeight="1">
+      <c r="A219" s="15" t="inlineStr">
+        <is>
+          <t>NU07-05</t>
+        </is>
+      </c>
+      <c r="B219" s="15" t="n"/>
+      <c r="C219" s="15" t="n"/>
+      <c r="D219" s="15" t="inlineStr">
+        <is>
+          <t>NU07</t>
+        </is>
+      </c>
+      <c r="E219" s="15" t="inlineStr">
+        <is>
+          <t>Kinderkleiderschrank Birke mit zwei Türen</t>
+        </is>
+      </c>
+      <c r="F219" s="16" t="inlineStr">
+        <is>
+          <t>Kleiderschrank aus Birke-Multiplex mit zwei weißen Türen und Griffmulden. Innen links eine Kleiderstange, rechts zwei Einlegeböden mit Durchgriff.</t>
+        </is>
+      </c>
+      <c r="G219" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H219" s="15" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="I219" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J219" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" s="17" t="n"/>
+      <c r="L219" s="18">
+        <f>J219-IF(K219="",0,K219)</f>
+        <v/>
+      </c>
+      <c r="M219" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N219" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O219" s="19" t="n"/>
+      <c r="P219" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q219" s="19" t="n"/>
+      <c r="R219" s="20" t="n"/>
+      <c r="S219" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="T219" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U219" s="21">
+        <f>L219*S219</f>
+        <v/>
+      </c>
+      <c r="V219" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W219" s="15" t="inlineStr">
+        <is>
+          <t>F-238</t>
+        </is>
+      </c>
+      <c r="X219" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y219" s="19" t="n"/>
+      <c r="Z219" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA219" s="19" t="n"/>
+      <c r="AB219" s="19" t="n"/>
+      <c r="AC219" s="19" t="n"/>
+      <c r="AD219" s="20" t="n"/>
+      <c r="AE219" s="21">
+        <f>IF(K219="","",K219*AD219)</f>
+        <v/>
+      </c>
+      <c r="AF219" s="19" t="n"/>
+      <c r="AG219" s="19" t="n"/>
+      <c r="AH219" s="19" t="n"/>
+      <c r="AI219" s="19" t="n"/>
+      <c r="AJ219" s="19" t="n"/>
+      <c r="AK219" s="19" t="n"/>
+      <c r="AL219" s="16" t="inlineStr">
+        <is>
+          <t>1 Schrank. Der Innenraum ist auf Foto F-239 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AM219" s="22" t="n"/>
+    </row>
+    <row r="220" ht="30" customHeight="1">
+      <c r="A220" s="15" t="inlineStr">
+        <is>
+          <t>NU07-07</t>
+        </is>
+      </c>
+      <c r="B220" s="15" t="n"/>
+      <c r="C220" s="15" t="n"/>
+      <c r="D220" s="15" t="inlineStr">
+        <is>
+          <t>NU07</t>
+        </is>
+      </c>
+      <c r="E220" s="15" t="inlineStr">
+        <is>
+          <t>Aufbewahrungsregal weiß mit zehn Einschüben</t>
+        </is>
+      </c>
+      <c r="F220" s="16" t="inlineStr">
+        <is>
+          <t>Schmales hohes Regal in Weiß mit zehn Einschubschienen, für flache Kästen oder Papier.</t>
+        </is>
+      </c>
+      <c r="G220" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H220" s="15" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="I220" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J220" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" s="17" t="n"/>
+      <c r="L220" s="18">
+        <f>J220-IF(K220="",0,K220)</f>
+        <v/>
+      </c>
+      <c r="M220" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N220" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O220" s="19" t="n"/>
+      <c r="P220" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q220" s="19" t="n"/>
+      <c r="R220" s="20" t="n"/>
+      <c r="S220" s="20" t="n">
+        <v>75</v>
+      </c>
+      <c r="T220" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U220" s="21">
+        <f>L220*S220</f>
+        <v/>
+      </c>
+      <c r="V220" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W220" s="15" t="inlineStr">
+        <is>
+          <t>F-241</t>
+        </is>
+      </c>
+      <c r="X220" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y220" s="19" t="n"/>
+      <c r="Z220" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA220" s="19" t="n"/>
+      <c r="AB220" s="19" t="n"/>
+      <c r="AC220" s="19" t="n"/>
+      <c r="AD220" s="20" t="n"/>
+      <c r="AE220" s="21">
+        <f>IF(K220="","",K220*AD220)</f>
+        <v/>
+      </c>
+      <c r="AF220" s="19" t="n"/>
+      <c r="AG220" s="19" t="n"/>
+      <c r="AH220" s="19" t="n"/>
+      <c r="AI220" s="19" t="n"/>
+      <c r="AJ220" s="19" t="n"/>
+      <c r="AK220" s="19" t="n"/>
+      <c r="AL220" s="16" t="inlineStr">
+        <is>
+          <t>1 Regal. Die Einschubkästen gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM220" s="22" t="n"/>
+    </row>
+    <row r="221" ht="30" customHeight="1">
+      <c r="A221" s="15" t="inlineStr">
+        <is>
+          <t>NU07-08</t>
+        </is>
+      </c>
+      <c r="B221" s="15" t="n"/>
+      <c r="C221" s="15" t="n"/>
+      <c r="D221" s="15" t="inlineStr">
+        <is>
+          <t>NU07</t>
+        </is>
+      </c>
+      <c r="E221" s="15" t="inlineStr">
+        <is>
+          <t>Sitzgruppe: Tisch und zwei Truhenbänke</t>
+        </is>
+      </c>
+      <c r="F221" s="16" t="inlineStr">
+        <is>
+          <t>Sitzgruppe aus einem Kindertisch und zwei Sitzbänken mit Rückenlehne. Die Sitzflächen lassen sich anheben und geben je einen Stauraum frei, gedämpft über eine Gasdruckfeder. Weiße Platten auf Beinen aus Buche.</t>
+        </is>
+      </c>
+      <c r="G221" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H221" s="15" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="I221" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J221" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" s="17" t="n"/>
+      <c r="L221" s="18">
+        <f>J221-IF(K221="",0,K221)</f>
+        <v/>
+      </c>
+      <c r="M221" s="15" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N221" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O221" s="19" t="n"/>
+      <c r="P221" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q221" s="19" t="n"/>
+      <c r="R221" s="20" t="n"/>
+      <c r="S221" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="T221" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U221" s="21">
+        <f>L221*S221</f>
+        <v/>
+      </c>
+      <c r="V221" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W221" s="15" t="inlineStr">
+        <is>
+          <t>F-242</t>
+        </is>
+      </c>
+      <c r="X221" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y221" s="19" t="n"/>
+      <c r="Z221" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA221" s="19" t="n"/>
+      <c r="AB221" s="19" t="n"/>
+      <c r="AC221" s="19" t="n"/>
+      <c r="AD221" s="20" t="n"/>
+      <c r="AE221" s="21">
+        <f>IF(K221="","",K221*AD221)</f>
+        <v/>
+      </c>
+      <c r="AF221" s="19" t="n"/>
+      <c r="AG221" s="19" t="n"/>
+      <c r="AH221" s="19" t="n"/>
+      <c r="AI221" s="19" t="n"/>
+      <c r="AJ221" s="19" t="n"/>
+      <c r="AK221" s="19" t="n"/>
+      <c r="AL221" s="16" t="inlineStr">
+        <is>
+          <t>1 Sitzgruppe aus drei Teilen: ein Tisch und zwei Truhenbänke. Der Stauraum unter der Sitzfläche ist auf Foto F-243 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AM221" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AM214"/>
+  <autoFilter ref="A2:AM221"/>
   <mergeCells count="7">
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="S1:U1"/>
@@ -26943,7 +27781,7 @@
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AD1:AG1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z214">
+  <conditionalFormatting sqref="Z3:Z221">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -26954,12 +27792,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I214">
+  <conditionalFormatting sqref="I3:I221">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P214">
+  <conditionalFormatting sqref="P3:P221">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -27012,7 +27850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -27050,7 +27888,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$214)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$221)</f>
         <v/>
       </c>
     </row>
@@ -27061,7 +27899,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$214,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$221,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -27072,7 +27910,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$214,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$221,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -27083,7 +27921,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$214,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$221,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -27094,7 +27932,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$214,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$221,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -27105,7 +27943,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$214)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$221)</f>
         <v/>
       </c>
     </row>
@@ -27116,7 +27954,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$214)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27134,7 +27972,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$214)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$221)</f>
         <v/>
       </c>
     </row>
@@ -27145,7 +27983,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$214,Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$221,Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
     </row>
@@ -27178,7 +28016,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$214="bezahlt")*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$221="bezahlt")*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
     </row>
@@ -27207,7 +28045,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$214,"*verkauft",Artikelstamm!$AH$3:$AH$214,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$221,"*verkauft",Artikelstamm!$AH$3:$AH$221,"")</f>
         <v/>
       </c>
     </row>
@@ -27218,7 +28056,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$214,"*verkauft",Artikelstamm!$AI$3:$AI$214,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$221,"*verkauft",Artikelstamm!$AI$3:$AI$221,"offen")</f>
         <v/>
       </c>
     </row>
@@ -27229,7 +28067,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$214,"reserviert",Artikelstamm!$AK$3:$AK$214,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$221,"reserviert",Artikelstamm!$AK$3:$AK$221,"")</f>
         <v/>
       </c>
     </row>
@@ -27240,7 +28078,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$214,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$221,"")</f>
         <v/>
       </c>
     </row>
@@ -27251,7 +28089,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$214,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$221,"")</f>
         <v/>
       </c>
     </row>
@@ -27291,15 +28129,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$214,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$221,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$214=$A30)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$221=$A30)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$214,$A30,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$221,$A30,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27310,15 +28148,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$214,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$221,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$214=$A31)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$221=$A31)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$214,$A31,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$221,$A31,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27329,15 +28167,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$214,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$221,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$214=$A32)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$221=$A32)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$214,$A32,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$221,$A32,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27396,15 +28234,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A37)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A37)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A37,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A37,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27415,15 +28253,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A38)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A38)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A38,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A38,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27434,15 +28272,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A39)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A39)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A39,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A39,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27453,15 +28291,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A40)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A40)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A40,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A40,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27472,15 +28310,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A41)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A41)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A41,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A41,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27491,15 +28329,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A42)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A42)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A42,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A42,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27510,15 +28348,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A43)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A43)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A43,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A43,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27529,15 +28367,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A44)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A44)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A44,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A44,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27548,15 +28386,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A45)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A45)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A45,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A45,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27567,15 +28405,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A46)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A46)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A46,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A46,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27586,15 +28424,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A47)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A47)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A47,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A47,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27605,15 +28443,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A48)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A48)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A48,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A48,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27624,15 +28462,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A49)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A49)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A49,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A49,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27643,15 +28481,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$214,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$214=$A50)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A50)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$214,$A50,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A50,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27710,15 +28548,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A55)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A55)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A55,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A55,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27729,15 +28567,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A56)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A56)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A56,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A56,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27748,15 +28586,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A57)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A57)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A57,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A57,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27767,15 +28605,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A58)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A58)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A58,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A58,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27786,15 +28624,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A59)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A59)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A59,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A59,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
@@ -27805,448 +28643,467 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A60)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A60)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A60,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A60,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="26" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A61)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A61)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A61,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A61,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum</t>
+          <t>Gartenanlage</t>
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A62)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A62)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A62,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A62,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A63)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A63)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A63,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A63,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum 2</t>
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A64)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A64)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A64,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A64,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A65)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A65)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A65,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A65,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="26" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Gruppenraum 5</t>
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A66)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A66)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A66,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A66,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="26" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A67)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A67)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A67,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A67,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A68)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A68)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A68,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A68,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum 4</t>
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A69)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A69)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A69,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A69,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="26" t="inlineStr">
         <is>
-          <t>Speisesaal</t>
+          <t>Schlafraum 5</t>
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A70)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A70)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A70,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A70,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="26" t="inlineStr">
         <is>
-          <t>Terrasse</t>
+          <t>Speisesaal</t>
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A71)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A71)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A71,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A71,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="26" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Terrasse</t>
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A72)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A72)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A72,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A72,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="26" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Treppenraum 1</t>
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A73)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A73)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A73,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A73,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A74)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A74)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A74,Artikelstamm!$U$3:$U$214)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A74,Artikelstamm!$U$3:$U$221)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B75" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A75)</f>
+        <v/>
+      </c>
+      <c r="C75" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A75)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <v/>
+      </c>
+      <c r="D75" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A75,Artikelstamm!$U$3:$U$221)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$214,$A75)</f>
-        <v/>
-      </c>
-      <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$214=$A75)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
-        <v/>
-      </c>
-      <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$214,$A75,Artikelstamm!$U$3:$U$214)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="28" t="inlineStr">
+      <c r="B76" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A76)</f>
+        <v/>
+      </c>
+      <c r="C76" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A76)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <v/>
+      </c>
+      <c r="D76" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A76,Artikelstamm!$U$3:$U$221)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B76" s="35">
-        <f>SUM(B55:B75)</f>
-        <v/>
-      </c>
-      <c r="C76" s="36">
-        <f>SUM(C55:C75)</f>
-        <v/>
-      </c>
-      <c r="D76" s="36">
-        <f>SUM(D55:D75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="25" t="inlineStr">
+      <c r="B77" s="35">
+        <f>SUM(B55:B76)</f>
+        <v/>
+      </c>
+      <c r="C77" s="36">
+        <f>SUM(C55:C76)</f>
+        <v/>
+      </c>
+      <c r="D77" s="36">
+        <f>SUM(D55:D76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="32" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B79" s="32" t="inlineStr">
+      <c r="B80" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C79" s="32" t="inlineStr">
+      <c r="C80" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A80)</f>
-        <v/>
-      </c>
-      <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A80)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
-        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A81)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A81)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A82)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A82)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A83)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A83)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A84)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A84)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B85" s="33">
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A85)</f>
+        <v/>
+      </c>
+      <c r="C85" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A85)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$214,$A85)</f>
-        <v/>
-      </c>
-      <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$214=$A85)*Artikelstamm!$K$3:$K$214*Artikelstamm!$AD$3:$AD$214)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="28" t="inlineStr">
+      <c r="B86" s="33">
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A86)</f>
+        <v/>
+      </c>
+      <c r="C86" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A86)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B86" s="35">
-        <f>SUM(B80:B85)</f>
-        <v/>
-      </c>
-      <c r="C86" s="36">
-        <f>SUM(C80:C85)</f>
+      <c r="B87" s="35">
+        <f>SUM(B81:B86)</f>
+        <v/>
+      </c>
+      <c r="C87" s="36">
+        <f>SUM(C81:C86)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM221"/>
+  <dimension ref="A1:AM231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14248,7 +14248,7 @@
       <c r="O110" s="19" t="n"/>
       <c r="P110" s="19" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>entfällt</t>
         </is>
       </c>
       <c r="Q110" s="19" t="n"/>
@@ -14305,7 +14305,11 @@
           <t>3 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM110" s="22" t="n"/>
+      <c r="AM110" s="22" t="inlineStr">
+        <is>
+          <t>Auf dem Erfassungsblatt NE01 durchgestrichen – entfaellt.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="15" t="inlineStr">
@@ -22591,7 +22595,7 @@
       <c r="AK178" s="19" t="n"/>
       <c r="AL178" s="16" t="inlineStr">
         <is>
-          <t>1 Küche aus 5 Modulen, vom Haus bestätigt. Eine zweite Wesco-Küche steht unter NU07-03.</t>
+          <t>1 Küche aus 5 Modulen, vom Haus bestätigt. Eine zweite, anders zusammengesetzte Wesco-Küche steht unter NU07-03.</t>
         </is>
       </c>
       <c r="AM178" s="22" t="inlineStr">
@@ -27285,12 +27289,12 @@
       <c r="AK217" s="19" t="n"/>
       <c r="AL217" s="16" t="inlineStr">
         <is>
-          <t>1 Küche aus mehreren Modulen. Eine zweite Wesco-Küche steht unter NU03-03.</t>
+          <t>1 Küche aus mehreren Modulen, mit Mikrowellenmodul und Hängeschrank. Eine zweite, anders zusammengesetzte Wesco-Küche steht unter NU03-03.</t>
         </is>
       </c>
       <c r="AM217" s="22" t="inlineStr">
         <is>
-          <t>Zu klaeren: ist diese Kueche baugleich mit NU03-03? Wenn ja, zu einer Position mit 2 Stueck zusammenfassen. Modulzahl hier noch nicht gezaehlt.</t>
+          <t>Nicht baugleich mit NU03-03, vom Haus bestaetigt – bleibt getrennt.</t>
         </is>
       </c>
     </row>
@@ -27770,8 +27774,1188 @@
       </c>
       <c r="AM221" s="22" t="n"/>
     </row>
+    <row r="222" ht="30" customHeight="1">
+      <c r="A222" s="15" t="inlineStr">
+        <is>
+          <t>NE01-17</t>
+        </is>
+      </c>
+      <c r="B222" s="15" t="n"/>
+      <c r="C222" s="15" t="n"/>
+      <c r="D222" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E222" s="15" t="inlineStr">
+        <is>
+          <t>Wandregal Berg, grau mit Holzablagen</t>
+        </is>
+      </c>
+      <c r="F222" s="16" t="inlineStr">
+        <is>
+          <t>Wandregal in Bergform, grau lackiert mit gelber Gipfellinie, mit mehreren Ablagebrettern aus Buche. Im Haus als Regal für Hörfiguren genutzt.</t>
+        </is>
+      </c>
+      <c r="G222" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H222" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I222" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J222" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K222" s="17" t="n"/>
+      <c r="L222" s="18">
+        <f>J222-IF(K222="",0,K222)</f>
+        <v/>
+      </c>
+      <c r="M222" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N222" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O222" s="19" t="n"/>
+      <c r="P222" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q222" s="19" t="n"/>
+      <c r="R222" s="20" t="n"/>
+      <c r="S222" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T222" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U222" s="21">
+        <f>L222*S222</f>
+        <v/>
+      </c>
+      <c r="V222" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W222" s="15" t="inlineStr">
+        <is>
+          <t>F-246</t>
+        </is>
+      </c>
+      <c r="X222" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y222" s="19" t="n"/>
+      <c r="Z222" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA222" s="19" t="n"/>
+      <c r="AB222" s="19" t="n"/>
+      <c r="AC222" s="19" t="n"/>
+      <c r="AD222" s="20" t="n"/>
+      <c r="AE222" s="21">
+        <f>IF(K222="","",K222*AD222)</f>
+        <v/>
+      </c>
+      <c r="AF222" s="19" t="n"/>
+      <c r="AG222" s="19" t="n"/>
+      <c r="AH222" s="19" t="n"/>
+      <c r="AI222" s="19" t="n"/>
+      <c r="AJ222" s="19" t="n"/>
+      <c r="AK222" s="19" t="n"/>
+      <c r="AL222" s="16" t="inlineStr">
+        <is>
+          <t>2 Regale, beide abgebildet. Figuren und Abspielgerät gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM222" s="22" t="n"/>
+    </row>
+    <row r="223" ht="30" customHeight="1">
+      <c r="A223" s="15" t="inlineStr">
+        <is>
+          <t>NE01-18</t>
+        </is>
+      </c>
+      <c r="B223" s="15" t="n"/>
+      <c r="C223" s="15" t="n"/>
+      <c r="D223" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E223" s="15" t="inlineStr">
+        <is>
+          <t>Highboard weiß auf schwarzem Metallgestell</t>
+        </is>
+      </c>
+      <c r="F223" s="16" t="inlineStr">
+        <is>
+          <t>Highboard mit weißen Fronten: zwei Türen oben, zwei breite Schubladen unten, flache schwarze Griffleisten, auf einem schwarzen Metallkufengestell.</t>
+        </is>
+      </c>
+      <c r="G223" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H223" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I223" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J223" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K223" s="17" t="n"/>
+      <c r="L223" s="18">
+        <f>J223-IF(K223="",0,K223)</f>
+        <v/>
+      </c>
+      <c r="M223" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N223" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O223" s="19" t="n"/>
+      <c r="P223" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q223" s="19" t="n"/>
+      <c r="R223" s="20" t="n"/>
+      <c r="S223" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="T223" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U223" s="21">
+        <f>L223*S223</f>
+        <v/>
+      </c>
+      <c r="V223" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W223" s="15" t="inlineStr">
+        <is>
+          <t>F-247</t>
+        </is>
+      </c>
+      <c r="X223" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y223" s="19" t="n"/>
+      <c r="Z223" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA223" s="19" t="n"/>
+      <c r="AB223" s="19" t="n"/>
+      <c r="AC223" s="19" t="n"/>
+      <c r="AD223" s="20" t="n"/>
+      <c r="AE223" s="21">
+        <f>IF(K223="","",K223*AD223)</f>
+        <v/>
+      </c>
+      <c r="AF223" s="19" t="n"/>
+      <c r="AG223" s="19" t="n"/>
+      <c r="AH223" s="19" t="n"/>
+      <c r="AI223" s="19" t="n"/>
+      <c r="AJ223" s="19" t="n"/>
+      <c r="AK223" s="19" t="n"/>
+      <c r="AL223" s="16" t="inlineStr">
+        <is>
+          <t>1 Highboard.</t>
+        </is>
+      </c>
+      <c r="AM223" s="22" t="n"/>
+    </row>
+    <row r="224" ht="30" customHeight="1">
+      <c r="A224" s="15" t="inlineStr">
+        <is>
+          <t>NE01-19</t>
+        </is>
+      </c>
+      <c r="B224" s="15" t="n"/>
+      <c r="C224" s="15" t="n"/>
+      <c r="D224" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E224" s="15" t="inlineStr">
+        <is>
+          <t>Stoff-Alpaka groß</t>
+        </is>
+      </c>
+      <c r="F224" s="16" t="inlineStr">
+        <is>
+          <t>Großes Stofftier in Alpakaform, beiger Bouclé-Bezug, standfest. Etwa einen Meter hoch.</t>
+        </is>
+      </c>
+      <c r="G224" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H224" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I224" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J224" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" s="17" t="n"/>
+      <c r="L224" s="18">
+        <f>J224-IF(K224="",0,K224)</f>
+        <v/>
+      </c>
+      <c r="M224" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N224" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O224" s="19" t="n"/>
+      <c r="P224" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q224" s="19" t="n"/>
+      <c r="R224" s="20" t="n"/>
+      <c r="S224" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="T224" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U224" s="21">
+        <f>L224*S224</f>
+        <v/>
+      </c>
+      <c r="V224" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W224" s="15" t="inlineStr">
+        <is>
+          <t>F-248</t>
+        </is>
+      </c>
+      <c r="X224" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y224" s="19" t="n"/>
+      <c r="Z224" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA224" s="19" t="n"/>
+      <c r="AB224" s="19" t="n"/>
+      <c r="AC224" s="19" t="n"/>
+      <c r="AD224" s="20" t="n"/>
+      <c r="AE224" s="21">
+        <f>IF(K224="","",K224*AD224)</f>
+        <v/>
+      </c>
+      <c r="AF224" s="19" t="n"/>
+      <c r="AG224" s="19" t="n"/>
+      <c r="AH224" s="19" t="n"/>
+      <c r="AI224" s="19" t="n"/>
+      <c r="AJ224" s="19" t="n"/>
+      <c r="AK224" s="19" t="n"/>
+      <c r="AL224" s="16" t="inlineStr">
+        <is>
+          <t>1 Stück.</t>
+        </is>
+      </c>
+      <c r="AM224" s="22" t="n"/>
+    </row>
+    <row r="225" ht="30" customHeight="1">
+      <c r="A225" s="15" t="inlineStr">
+        <is>
+          <t>NE01-20</t>
+        </is>
+      </c>
+      <c r="B225" s="15" t="n"/>
+      <c r="C225" s="15" t="n"/>
+      <c r="D225" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E225" s="15" t="inlineStr">
+        <is>
+          <t>Kinder-Ohrensessel rot, Kunstleder</t>
+        </is>
+      </c>
+      <c r="F225" s="16" t="inlineStr">
+        <is>
+          <t>Ohrensessel in Kindergröße, roter Kunstlederbezug, geschwungene schwarze Holzbeine. An einer Armlehne ist der Bezug aufgerissen.</t>
+        </is>
+      </c>
+      <c r="G225" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H225" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I225" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J225" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K225" s="17" t="n"/>
+      <c r="L225" s="18">
+        <f>J225-IF(K225="",0,K225)</f>
+        <v/>
+      </c>
+      <c r="M225" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N225" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O225" s="19" t="n"/>
+      <c r="P225" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q225" s="19" t="n"/>
+      <c r="R225" s="20" t="n"/>
+      <c r="S225" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="T225" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U225" s="21">
+        <f>L225*S225</f>
+        <v/>
+      </c>
+      <c r="V225" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W225" s="15" t="inlineStr">
+        <is>
+          <t>F-249</t>
+        </is>
+      </c>
+      <c r="X225" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y225" s="19" t="n"/>
+      <c r="Z225" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA225" s="19" t="n"/>
+      <c r="AB225" s="19" t="n"/>
+      <c r="AC225" s="19" t="n"/>
+      <c r="AD225" s="20" t="n"/>
+      <c r="AE225" s="21">
+        <f>IF(K225="","",K225*AD225)</f>
+        <v/>
+      </c>
+      <c r="AF225" s="19" t="n"/>
+      <c r="AG225" s="19" t="n"/>
+      <c r="AH225" s="19" t="n"/>
+      <c r="AI225" s="19" t="n"/>
+      <c r="AJ225" s="19" t="n"/>
+      <c r="AK225" s="19" t="n"/>
+      <c r="AL225" s="16" t="inlineStr">
+        <is>
+          <t>2 Sessel – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AM225" s="22" t="n"/>
+    </row>
+    <row r="226" ht="30" customHeight="1">
+      <c r="A226" s="15" t="inlineStr">
+        <is>
+          <t>NE01-21</t>
+        </is>
+      </c>
+      <c r="B226" s="15" t="n"/>
+      <c r="C226" s="15" t="n"/>
+      <c r="D226" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E226" s="15" t="inlineStr">
+        <is>
+          <t>Wandregal weiß mit drei Wannen</t>
+        </is>
+      </c>
+      <c r="F226" s="16" t="inlineStr">
+        <is>
+          <t>Weißes Wandelement mit drei Fächern und eingeschobenen Kunststoffwannen.</t>
+        </is>
+      </c>
+      <c r="G226" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H226" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I226" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J226" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K226" s="17" t="n"/>
+      <c r="L226" s="18">
+        <f>J226-IF(K226="",0,K226)</f>
+        <v/>
+      </c>
+      <c r="M226" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N226" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O226" s="19" t="n"/>
+      <c r="P226" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q226" s="19" t="n"/>
+      <c r="R226" s="20" t="n"/>
+      <c r="S226" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T226" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U226" s="21">
+        <f>L226*S226</f>
+        <v/>
+      </c>
+      <c r="V226" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W226" s="15" t="inlineStr">
+        <is>
+          <t>F-250</t>
+        </is>
+      </c>
+      <c r="X226" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y226" s="19" t="n"/>
+      <c r="Z226" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA226" s="19" t="n"/>
+      <c r="AB226" s="19" t="n"/>
+      <c r="AC226" s="19" t="n"/>
+      <c r="AD226" s="20" t="n"/>
+      <c r="AE226" s="21">
+        <f>IF(K226="","",K226*AD226)</f>
+        <v/>
+      </c>
+      <c r="AF226" s="19" t="n"/>
+      <c r="AG226" s="19" t="n"/>
+      <c r="AH226" s="19" t="n"/>
+      <c r="AI226" s="19" t="n"/>
+      <c r="AJ226" s="19" t="n"/>
+      <c r="AK226" s="19" t="n"/>
+      <c r="AL226" s="16" t="inlineStr">
+        <is>
+          <t>12 Regale einschließlich der Wannen – abgebildet ist eines davon. Die Hundehaken darunter sind eigene Positionen (NE01-22 und NE01-23).</t>
+        </is>
+      </c>
+      <c r="AM226" s="22" t="n"/>
+    </row>
+    <row r="227" ht="30" customHeight="1">
+      <c r="A227" s="15" t="inlineStr">
+        <is>
+          <t>NE01-22</t>
+        </is>
+      </c>
+      <c r="B227" s="15" t="n"/>
+      <c r="C227" s="15" t="n"/>
+      <c r="D227" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E227" s="15" t="inlineStr">
+        <is>
+          <t>Wandhaken Hund, schwarz</t>
+        </is>
+      </c>
+      <c r="F227" s="16" t="inlineStr">
+        <is>
+          <t>Wandhaken in Form eines Hunde-Hinterteils mit aufgestelltem Schwanz, schwarz, mit einer Schraube befestigt.</t>
+        </is>
+      </c>
+      <c r="G227" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H227" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I227" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J227" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="K227" s="17" t="n"/>
+      <c r="L227" s="18">
+        <f>J227-IF(K227="",0,K227)</f>
+        <v/>
+      </c>
+      <c r="M227" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N227" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O227" s="19" t="n"/>
+      <c r="P227" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q227" s="19" t="n"/>
+      <c r="R227" s="20" t="n"/>
+      <c r="S227" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T227" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U227" s="21">
+        <f>L227*S227</f>
+        <v/>
+      </c>
+      <c r="V227" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W227" s="15" t="inlineStr">
+        <is>
+          <t>F-251</t>
+        </is>
+      </c>
+      <c r="X227" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y227" s="19" t="n"/>
+      <c r="Z227" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA227" s="19" t="n"/>
+      <c r="AB227" s="19" t="n"/>
+      <c r="AC227" s="19" t="n"/>
+      <c r="AD227" s="20" t="n"/>
+      <c r="AE227" s="21">
+        <f>IF(K227="","",K227*AD227)</f>
+        <v/>
+      </c>
+      <c r="AF227" s="19" t="n"/>
+      <c r="AG227" s="19" t="n"/>
+      <c r="AH227" s="19" t="n"/>
+      <c r="AI227" s="19" t="n"/>
+      <c r="AJ227" s="19" t="n"/>
+      <c r="AK227" s="19" t="n"/>
+      <c r="AL227" s="16" t="inlineStr">
+        <is>
+          <t>21 Haken – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AM227" s="22" t="n"/>
+    </row>
+    <row r="228" ht="30" customHeight="1">
+      <c r="A228" s="15" t="inlineStr">
+        <is>
+          <t>NE01-23</t>
+        </is>
+      </c>
+      <c r="B228" s="15" t="n"/>
+      <c r="C228" s="15" t="n"/>
+      <c r="D228" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E228" s="15" t="inlineStr">
+        <is>
+          <t>Wandhaken Hund, grün</t>
+        </is>
+      </c>
+      <c r="F228" s="16" t="inlineStr">
+        <is>
+          <t>Wandhaken in Form eines Hunde-Hinterteils mit aufgestelltem Schwanz, hellgrün, mit einer Schraube befestigt.</t>
+        </is>
+      </c>
+      <c r="G228" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H228" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I228" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J228" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="K228" s="17" t="n"/>
+      <c r="L228" s="18">
+        <f>J228-IF(K228="",0,K228)</f>
+        <v/>
+      </c>
+      <c r="M228" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N228" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O228" s="19" t="n"/>
+      <c r="P228" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q228" s="19" t="n"/>
+      <c r="R228" s="20" t="n"/>
+      <c r="S228" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="T228" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U228" s="21">
+        <f>L228*S228</f>
+        <v/>
+      </c>
+      <c r="V228" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W228" s="15" t="inlineStr">
+        <is>
+          <t>F-252</t>
+        </is>
+      </c>
+      <c r="X228" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y228" s="19" t="n"/>
+      <c r="Z228" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA228" s="19" t="n"/>
+      <c r="AB228" s="19" t="n"/>
+      <c r="AC228" s="19" t="n"/>
+      <c r="AD228" s="20" t="n"/>
+      <c r="AE228" s="21">
+        <f>IF(K228="","",K228*AD228)</f>
+        <v/>
+      </c>
+      <c r="AF228" s="19" t="n"/>
+      <c r="AG228" s="19" t="n"/>
+      <c r="AH228" s="19" t="n"/>
+      <c r="AI228" s="19" t="n"/>
+      <c r="AJ228" s="19" t="n"/>
+      <c r="AK228" s="19" t="n"/>
+      <c r="AL228" s="16" t="inlineStr">
+        <is>
+          <t>11 Haken – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AM228" s="22" t="n"/>
+    </row>
+    <row r="229" ht="30" customHeight="1">
+      <c r="A229" s="15" t="inlineStr">
+        <is>
+          <t>NE01-24</t>
+        </is>
+      </c>
+      <c r="B229" s="15" t="n"/>
+      <c r="C229" s="15" t="n"/>
+      <c r="D229" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E229" s="15" t="inlineStr">
+        <is>
+          <t>Truhenbank Kindergröße, Buche mit weiß</t>
+        </is>
+      </c>
+      <c r="F229" s="16" t="inlineStr">
+        <is>
+          <t>Sitzbank in Kindergröße: Gestell und Sprossenlehne aus Buche massiv, Sitzfläche und Korpus weiß. Unter der Sitzfläche ein Stauraum. Sitzfläche stark verschmutzt und abgestoßen.</t>
+        </is>
+      </c>
+      <c r="G229" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H229" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I229" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J229" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K229" s="17" t="n"/>
+      <c r="L229" s="18">
+        <f>J229-IF(K229="",0,K229)</f>
+        <v/>
+      </c>
+      <c r="M229" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N229" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O229" s="19" t="n"/>
+      <c r="P229" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q229" s="19" t="n"/>
+      <c r="R229" s="20" t="n"/>
+      <c r="S229" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T229" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U229" s="21">
+        <f>L229*S229</f>
+        <v/>
+      </c>
+      <c r="V229" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W229" s="15" t="inlineStr">
+        <is>
+          <t>F-253</t>
+        </is>
+      </c>
+      <c r="X229" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y229" s="19" t="n"/>
+      <c r="Z229" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA229" s="19" t="n"/>
+      <c r="AB229" s="19" t="n"/>
+      <c r="AC229" s="19" t="n"/>
+      <c r="AD229" s="20" t="n"/>
+      <c r="AE229" s="21">
+        <f>IF(K229="","",K229*AD229)</f>
+        <v/>
+      </c>
+      <c r="AF229" s="19" t="n"/>
+      <c r="AG229" s="19" t="n"/>
+      <c r="AH229" s="19" t="n"/>
+      <c r="AI229" s="19" t="n"/>
+      <c r="AJ229" s="19" t="n"/>
+      <c r="AK229" s="19" t="n"/>
+      <c r="AL229" s="16" t="inlineStr">
+        <is>
+          <t>3 Bänke – abgebildet sind zwei davon.</t>
+        </is>
+      </c>
+      <c r="AM229" s="22" t="n"/>
+    </row>
+    <row r="230" ht="30" customHeight="1">
+      <c r="A230" s="15" t="inlineStr">
+        <is>
+          <t>NE01-25</t>
+        </is>
+      </c>
+      <c r="B230" s="15" t="n"/>
+      <c r="C230" s="15" t="n"/>
+      <c r="D230" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E230" s="15" t="inlineStr">
+        <is>
+          <t>Truhenbank Kindergröße, ganz weiß</t>
+        </is>
+      </c>
+      <c r="F230" s="16" t="inlineStr">
+        <is>
+          <t>Sitzbank in Kindergröße, komplett weiß lackiert, mit Sprossenlehne und Stauraum unter der Sitzfläche. Lack an Kanten abgeplatzt, Sitzfläche zerkratzt.</t>
+        </is>
+      </c>
+      <c r="G230" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H230" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I230" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J230" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K230" s="17" t="n"/>
+      <c r="L230" s="18">
+        <f>J230-IF(K230="",0,K230)</f>
+        <v/>
+      </c>
+      <c r="M230" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N230" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O230" s="19" t="n"/>
+      <c r="P230" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q230" s="19" t="n"/>
+      <c r="R230" s="20" t="n"/>
+      <c r="S230" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T230" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U230" s="21">
+        <f>L230*S230</f>
+        <v/>
+      </c>
+      <c r="V230" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W230" s="15" t="inlineStr">
+        <is>
+          <t>F-254</t>
+        </is>
+      </c>
+      <c r="X230" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y230" s="19" t="n"/>
+      <c r="Z230" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA230" s="19" t="n"/>
+      <c r="AB230" s="19" t="n"/>
+      <c r="AC230" s="19" t="n"/>
+      <c r="AD230" s="20" t="n"/>
+      <c r="AE230" s="21">
+        <f>IF(K230="","",K230*AD230)</f>
+        <v/>
+      </c>
+      <c r="AF230" s="19" t="n"/>
+      <c r="AG230" s="19" t="n"/>
+      <c r="AH230" s="19" t="n"/>
+      <c r="AI230" s="19" t="n"/>
+      <c r="AJ230" s="19" t="n"/>
+      <c r="AK230" s="19" t="n"/>
+      <c r="AL230" s="16" t="inlineStr">
+        <is>
+          <t>3 Bänke – abgebildet ist eine davon.</t>
+        </is>
+      </c>
+      <c r="AM230" s="22" t="n"/>
+    </row>
+    <row r="231" ht="30" customHeight="1">
+      <c r="A231" s="15" t="inlineStr">
+        <is>
+          <t>NE01-26</t>
+        </is>
+      </c>
+      <c r="B231" s="15" t="n"/>
+      <c r="C231" s="15" t="n"/>
+      <c r="D231" s="15" t="inlineStr">
+        <is>
+          <t>NE01</t>
+        </is>
+      </c>
+      <c r="E231" s="15" t="inlineStr">
+        <is>
+          <t>Sitzbank weiß mit Stauraum, lang</t>
+        </is>
+      </c>
+      <c r="F231" s="16" t="inlineStr">
+        <is>
+          <t>Lange Sitzbank in Weiß mit niedrigen Armlehnen und aufklappbarer Sitzfläche, darunter Stauraum mit Griffmulde. Lack großflächig zerkratzt.</t>
+        </is>
+      </c>
+      <c r="G231" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H231" s="15" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="I231" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J231" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K231" s="17" t="n"/>
+      <c r="L231" s="18">
+        <f>J231-IF(K231="",0,K231)</f>
+        <v/>
+      </c>
+      <c r="M231" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N231" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O231" s="19" t="n"/>
+      <c r="P231" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q231" s="19" t="n"/>
+      <c r="R231" s="20" t="n"/>
+      <c r="S231" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T231" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U231" s="21">
+        <f>L231*S231</f>
+        <v/>
+      </c>
+      <c r="V231" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W231" s="15" t="inlineStr">
+        <is>
+          <t>F-255</t>
+        </is>
+      </c>
+      <c r="X231" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y231" s="19" t="n"/>
+      <c r="Z231" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA231" s="19" t="n"/>
+      <c r="AB231" s="19" t="n"/>
+      <c r="AC231" s="19" t="n"/>
+      <c r="AD231" s="20" t="n"/>
+      <c r="AE231" s="21">
+        <f>IF(K231="","",K231*AD231)</f>
+        <v/>
+      </c>
+      <c r="AF231" s="19" t="n"/>
+      <c r="AG231" s="19" t="n"/>
+      <c r="AH231" s="19" t="n"/>
+      <c r="AI231" s="19" t="n"/>
+      <c r="AJ231" s="19" t="n"/>
+      <c r="AK231" s="19" t="n"/>
+      <c r="AL231" s="16" t="inlineStr">
+        <is>
+          <t>7 Bänke – abgebildet ist eine davon.</t>
+        </is>
+      </c>
+      <c r="AM231" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AM221"/>
+  <autoFilter ref="A2:AM231"/>
   <mergeCells count="7">
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="S1:U1"/>
@@ -27781,7 +28965,7 @@
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AD1:AG1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z221">
+  <conditionalFormatting sqref="Z3:Z231">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -27792,12 +28976,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I221">
+  <conditionalFormatting sqref="I3:I231">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P221">
+  <conditionalFormatting sqref="P3:P231">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -27888,7 +29072,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$221)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$231)</f>
         <v/>
       </c>
     </row>
@@ -27899,7 +29083,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$221,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$231,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -27910,7 +29094,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$221,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$231,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -27921,7 +29105,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$221,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$231,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -27932,7 +29116,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$221,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$231,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -27943,7 +29127,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$221)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$231)</f>
         <v/>
       </c>
     </row>
@@ -27954,7 +29138,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$221)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -27972,7 +29156,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$221)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$231)</f>
         <v/>
       </c>
     </row>
@@ -27983,7 +29167,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$221,Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$231,Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
     </row>
@@ -28016,7 +29200,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$221="bezahlt")*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$231="bezahlt")*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
     </row>
@@ -28045,7 +29229,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$221,"*verkauft",Artikelstamm!$AH$3:$AH$221,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$231,"*verkauft",Artikelstamm!$AH$3:$AH$231,"")</f>
         <v/>
       </c>
     </row>
@@ -28056,7 +29240,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$221,"*verkauft",Artikelstamm!$AI$3:$AI$221,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$231,"*verkauft",Artikelstamm!$AI$3:$AI$231,"offen")</f>
         <v/>
       </c>
     </row>
@@ -28067,7 +29251,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$221,"reserviert",Artikelstamm!$AK$3:$AK$221,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$231,"reserviert",Artikelstamm!$AK$3:$AK$231,"")</f>
         <v/>
       </c>
     </row>
@@ -28078,7 +29262,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$221,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$231,"")</f>
         <v/>
       </c>
     </row>
@@ -28089,7 +29273,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$221,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$231,"")</f>
         <v/>
       </c>
     </row>
@@ -28129,15 +29313,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$221,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$231,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$221=$A30)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$231=$A30)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$221,$A30,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$231,$A30,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28148,15 +29332,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$221,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$231,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$221=$A31)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$231=$A31)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$221,$A31,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$231,$A31,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28167,15 +29351,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$221,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$231,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$221=$A32)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$231=$A32)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$221,$A32,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$231,$A32,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28234,15 +29418,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A37)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A37)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A37,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A37,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28253,15 +29437,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A38)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A38)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A38,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A38,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28272,15 +29456,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A39)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A39)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A39,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A39,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28291,15 +29475,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A40)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A40)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A40,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A40,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28310,15 +29494,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A41)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A41)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A41,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A41,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28329,15 +29513,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A42)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A42)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A42,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A42,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28348,15 +29532,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A43)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A43)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A43,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A43,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28367,15 +29551,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A44)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A44)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A44,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A44,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28386,15 +29570,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A45)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A45)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A45,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A45,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28405,15 +29589,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A46)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A46)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A46,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A46,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28424,15 +29608,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A47)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A47)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A47,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A47,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28443,15 +29627,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A48)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A48)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A48,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A48,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28462,15 +29646,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A49)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A49)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A49,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A49,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28481,15 +29665,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$221,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$221=$A50)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A50)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$221,$A50,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A50,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28548,15 +29732,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A55)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A55)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A55,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A55,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28567,15 +29751,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A56)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A56)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A56,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A56,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28586,15 +29770,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A57)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A57)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A57,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A57,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28605,15 +29789,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A58)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A58)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A58,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A58,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28624,15 +29808,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A59)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A59)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A59,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A59,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28643,15 +29827,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A60)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A60)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A60,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A60,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28662,15 +29846,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A61)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A61)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A61,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A61,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28681,15 +29865,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A62)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A62)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A62,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A62,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28700,15 +29884,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A63)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A63)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A63,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A63,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28719,15 +29903,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A64)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A64)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A64,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A64,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28738,15 +29922,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A65)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A65)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A65,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A65,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28757,15 +29941,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A66)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A66)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A66,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A66,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28776,15 +29960,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A67)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A67)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A67,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A67,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28795,15 +29979,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A68)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A68)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A68,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A68,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28814,15 +29998,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A69)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A69)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A69,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A69,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28833,15 +30017,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A70)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A70)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A70,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A70,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28852,15 +30036,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A71)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A71)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A71,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A71,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28871,15 +30055,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A72)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A72)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A72,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A72,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28890,15 +30074,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A73)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A73)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A73,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A73,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28909,15 +30093,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A74)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A74)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A74,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A74,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28928,15 +30112,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A75)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A75)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A75,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A75,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -28947,15 +30131,15 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$221,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$221=$A76)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A76)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$221,$A76,Artikelstamm!$U$3:$U$221)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A76,Artikelstamm!$U$3:$U$231)</f>
         <v/>
       </c>
     </row>
@@ -29009,11 +30193,11 @@
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A81)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A81)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
     </row>
@@ -29024,11 +30208,11 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A82)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A82)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
     </row>
@@ -29039,11 +30223,11 @@
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A83)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A83)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
     </row>
@@ -29054,11 +30238,11 @@
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A84)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A84)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
     </row>
@@ -29069,11 +30253,11 @@
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A85)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A85)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
     </row>
@@ -29084,11 +30268,11 @@
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$221,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$221=$A86)*Artikelstamm!$K$3:$K$221*Artikelstamm!$AD$3:$AD$221)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A86)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$235</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM231"/>
+  <dimension ref="A1:AM235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28954,8 +28954,484 @@
       </c>
       <c r="AM231" s="22" t="n"/>
     </row>
+    <row r="232" ht="30" customHeight="1">
+      <c r="A232" s="15" t="inlineStr">
+        <is>
+          <t>BA01-01</t>
+        </is>
+      </c>
+      <c r="B232" s="15" t="n"/>
+      <c r="C232" s="15" t="n"/>
+      <c r="D232" s="15" t="inlineStr">
+        <is>
+          <t>BA01</t>
+        </is>
+      </c>
+      <c r="E232" s="15" t="inlineStr">
+        <is>
+          <t>Gemälde Mona Lisa, Pop-Art</t>
+        </is>
+      </c>
+      <c r="F232" s="16" t="inlineStr">
+        <is>
+          <t>Acryl auf Leinwand im Hochformat: Mona Lisa als flächige Schablonenmalerei in Grau und Creme, darüber grüne Farbläufe vom oberen Rand. Eigenarbeit einer Privatperson, nicht signiert. Großes Format.</t>
+        </is>
+      </c>
+      <c r="G232" s="15" t="inlineStr">
+        <is>
+          <t>Kunst</t>
+        </is>
+      </c>
+      <c r="H232" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I232" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J232" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K232" s="17" t="n"/>
+      <c r="L232" s="18">
+        <f>J232-IF(K232="",0,K232)</f>
+        <v/>
+      </c>
+      <c r="M232" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N232" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O232" s="19" t="n"/>
+      <c r="P232" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q232" s="19" t="n"/>
+      <c r="R232" s="20" t="n"/>
+      <c r="S232" s="20" t="n">
+        <v>250</v>
+      </c>
+      <c r="T232" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U232" s="21">
+        <f>L232*S232</f>
+        <v/>
+      </c>
+      <c r="V232" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W232" s="15" t="inlineStr">
+        <is>
+          <t>F-258</t>
+        </is>
+      </c>
+      <c r="X232" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y232" s="19" t="n"/>
+      <c r="Z232" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA232" s="19" t="n"/>
+      <c r="AB232" s="19" t="n"/>
+      <c r="AC232" s="19" t="n"/>
+      <c r="AD232" s="20" t="n"/>
+      <c r="AE232" s="21">
+        <f>IF(K232="","",K232*AD232)</f>
+        <v/>
+      </c>
+      <c r="AF232" s="19" t="n"/>
+      <c r="AG232" s="19" t="n"/>
+      <c r="AH232" s="19" t="n"/>
+      <c r="AI232" s="19" t="n"/>
+      <c r="AJ232" s="19" t="n"/>
+      <c r="AK232" s="19" t="n"/>
+      <c r="AL232" s="16" t="inlineStr">
+        <is>
+          <t>1 Bild.</t>
+        </is>
+      </c>
+      <c r="AM232" s="22" t="inlineStr">
+        <is>
+          <t>Preis unbestaetigt: stilistisch verwandt mit NU01-06 (Marilyn mit Bollenhut, 650 EUR) von derselben Hand. Bitte pruefen, ob 250 EUR passt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="30" customHeight="1">
+      <c r="A233" s="15" t="inlineStr">
+        <is>
+          <t>BA01-02</t>
+        </is>
+      </c>
+      <c r="B233" s="15" t="n"/>
+      <c r="C233" s="15" t="n"/>
+      <c r="D233" s="15" t="inlineStr">
+        <is>
+          <t>BA01</t>
+        </is>
+      </c>
+      <c r="E233" s="15" t="inlineStr">
+        <is>
+          <t>Acrylbild abstrakt, Neonfarben</t>
+        </is>
+      </c>
+      <c r="F233" s="16" t="inlineStr">
+        <is>
+          <t>Acryl auf Leinwand: abstrakte Komposition mit breiten Pinselzügen in Grün und Blau, darüber Schleudertechnik in Neongelb, Neonrot und Pink. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="G233" s="15" t="inlineStr">
+        <is>
+          <t>Kunst</t>
+        </is>
+      </c>
+      <c r="H233" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I233" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J233" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K233" s="17" t="n"/>
+      <c r="L233" s="18">
+        <f>J233-IF(K233="",0,K233)</f>
+        <v/>
+      </c>
+      <c r="M233" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N233" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O233" s="19" t="n"/>
+      <c r="P233" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q233" s="19" t="n"/>
+      <c r="R233" s="20" t="n"/>
+      <c r="S233" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T233" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U233" s="21">
+        <f>L233*S233</f>
+        <v/>
+      </c>
+      <c r="V233" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W233" s="15" t="inlineStr">
+        <is>
+          <t>F-259</t>
+        </is>
+      </c>
+      <c r="X233" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y233" s="19" t="n"/>
+      <c r="Z233" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA233" s="19" t="n"/>
+      <c r="AB233" s="19" t="n"/>
+      <c r="AC233" s="19" t="n"/>
+      <c r="AD233" s="20" t="n"/>
+      <c r="AE233" s="21">
+        <f>IF(K233="","",K233*AD233)</f>
+        <v/>
+      </c>
+      <c r="AF233" s="19" t="n"/>
+      <c r="AG233" s="19" t="n"/>
+      <c r="AH233" s="19" t="n"/>
+      <c r="AI233" s="19" t="n"/>
+      <c r="AJ233" s="19" t="n"/>
+      <c r="AK233" s="19" t="n"/>
+      <c r="AL233" s="16" t="inlineStr">
+        <is>
+          <t>1 Bild.</t>
+        </is>
+      </c>
+      <c r="AM233" s="22" t="n"/>
+    </row>
+    <row r="234" ht="30" customHeight="1">
+      <c r="A234" s="15" t="inlineStr">
+        <is>
+          <t>BA01-03</t>
+        </is>
+      </c>
+      <c r="B234" s="15" t="n"/>
+      <c r="C234" s="15" t="n"/>
+      <c r="D234" s="15" t="inlineStr">
+        <is>
+          <t>BA01</t>
+        </is>
+      </c>
+      <c r="E234" s="15" t="inlineStr">
+        <is>
+          <t>Tannen-Dekoration</t>
+        </is>
+      </c>
+      <c r="F234" s="16" t="inlineStr">
+        <is>
+          <t>Dekoration in Tannenform.</t>
+        </is>
+      </c>
+      <c r="G234" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H234" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I234" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J234" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K234" s="17" t="n"/>
+      <c r="L234" s="18">
+        <f>J234-IF(K234="",0,K234)</f>
+        <v/>
+      </c>
+      <c r="M234" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N234" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O234" s="19" t="n"/>
+      <c r="P234" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q234" s="19" t="n"/>
+      <c r="R234" s="20" t="n"/>
+      <c r="S234" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T234" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U234" s="21">
+        <f>L234*S234</f>
+        <v/>
+      </c>
+      <c r="V234" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W234" s="15" t="n"/>
+      <c r="X234" s="19" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="Y234" s="19" t="n"/>
+      <c r="Z234" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA234" s="19" t="n"/>
+      <c r="AB234" s="19" t="n"/>
+      <c r="AC234" s="19" t="n"/>
+      <c r="AD234" s="20" t="n"/>
+      <c r="AE234" s="21">
+        <f>IF(K234="","",K234*AD234)</f>
+        <v/>
+      </c>
+      <c r="AF234" s="19" t="n"/>
+      <c r="AG234" s="19" t="n"/>
+      <c r="AH234" s="19" t="n"/>
+      <c r="AI234" s="19" t="n"/>
+      <c r="AJ234" s="19" t="n"/>
+      <c r="AK234" s="19" t="n"/>
+      <c r="AL234" s="16" t="inlineStr">
+        <is>
+          <t>1 Stück.</t>
+        </is>
+      </c>
+      <c r="AM234" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: Foto fehlt - IMG_2291 ist nicht angekommen. Beschreibung und Preis sind daher vorlaeufig. Moeglicherweise dieselben Stuecke wie NE01-15 (Deko-Tannenbaum schwarz, 3 Stueck), die dort durchgestrichen wurden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="30" customHeight="1">
+      <c r="A235" s="15" t="inlineStr">
+        <is>
+          <t>BA01-04</t>
+        </is>
+      </c>
+      <c r="B235" s="15" t="n"/>
+      <c r="C235" s="15" t="n"/>
+      <c r="D235" s="15" t="inlineStr">
+        <is>
+          <t>BA01</t>
+        </is>
+      </c>
+      <c r="E235" s="15" t="inlineStr">
+        <is>
+          <t>Leuchtbuchstabe K, schwarz</t>
+        </is>
+      </c>
+      <c r="F235" s="16" t="inlineStr">
+        <is>
+          <t>Buchstabe K aus schwarz beschichtetem Metall mit sechs runden Leuchtmitteln auf der Front, zum Aufstellen.</t>
+        </is>
+      </c>
+      <c r="G235" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H235" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I235" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J235" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K235" s="17" t="n"/>
+      <c r="L235" s="18">
+        <f>J235-IF(K235="",0,K235)</f>
+        <v/>
+      </c>
+      <c r="M235" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N235" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O235" s="19" t="n"/>
+      <c r="P235" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q235" s="19" t="n"/>
+      <c r="R235" s="20" t="n"/>
+      <c r="S235" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T235" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U235" s="21">
+        <f>L235*S235</f>
+        <v/>
+      </c>
+      <c r="V235" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W235" s="15" t="inlineStr">
+        <is>
+          <t>F-260</t>
+        </is>
+      </c>
+      <c r="X235" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y235" s="19" t="n"/>
+      <c r="Z235" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA235" s="19" t="n"/>
+      <c r="AB235" s="19" t="n"/>
+      <c r="AC235" s="19" t="n"/>
+      <c r="AD235" s="20" t="n"/>
+      <c r="AE235" s="21">
+        <f>IF(K235="","",K235*AD235)</f>
+        <v/>
+      </c>
+      <c r="AF235" s="19" t="n"/>
+      <c r="AG235" s="19" t="n"/>
+      <c r="AH235" s="19" t="n"/>
+      <c r="AI235" s="19" t="n"/>
+      <c r="AJ235" s="19" t="n"/>
+      <c r="AK235" s="19" t="n"/>
+      <c r="AL235" s="16" t="inlineStr">
+        <is>
+          <t>1 Stück.</t>
+        </is>
+      </c>
+      <c r="AM235" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AM231"/>
+  <autoFilter ref="A2:AM235"/>
   <mergeCells count="7">
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="S1:U1"/>
@@ -28965,7 +29441,7 @@
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AD1:AG1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z231">
+  <conditionalFormatting sqref="Z3:Z235">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -28976,12 +29452,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I231">
+  <conditionalFormatting sqref="I3:I235">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P231">
+  <conditionalFormatting sqref="P3:P235">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -29072,7 +29548,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$231)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$235)</f>
         <v/>
       </c>
     </row>
@@ -29083,7 +29559,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$231,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$235,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -29094,7 +29570,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$231,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$235,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -29105,7 +29581,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$231,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$235,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -29116,7 +29592,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$231,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$235,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -29127,7 +29603,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$231)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$235)</f>
         <v/>
       </c>
     </row>
@@ -29138,7 +29614,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$231)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29156,7 +29632,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$231)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$235)</f>
         <v/>
       </c>
     </row>
@@ -29167,7 +29643,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$231,Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$235,Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
     </row>
@@ -29200,7 +29676,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$231="bezahlt")*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$235="bezahlt")*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
     </row>
@@ -29229,7 +29705,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$231,"*verkauft",Artikelstamm!$AH$3:$AH$231,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$235,"*verkauft",Artikelstamm!$AH$3:$AH$235,"")</f>
         <v/>
       </c>
     </row>
@@ -29240,7 +29716,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$231,"*verkauft",Artikelstamm!$AI$3:$AI$231,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$235,"*verkauft",Artikelstamm!$AI$3:$AI$235,"offen")</f>
         <v/>
       </c>
     </row>
@@ -29251,7 +29727,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$231,"reserviert",Artikelstamm!$AK$3:$AK$231,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$235,"reserviert",Artikelstamm!$AK$3:$AK$235,"")</f>
         <v/>
       </c>
     </row>
@@ -29262,7 +29738,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$231,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$235,"")</f>
         <v/>
       </c>
     </row>
@@ -29273,7 +29749,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$231,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$235,"")</f>
         <v/>
       </c>
     </row>
@@ -29313,15 +29789,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$231,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$235,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$231=$A30)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$235=$A30)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$231,$A30,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$235,$A30,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29332,15 +29808,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$231,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$235,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$231=$A31)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$235=$A31)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$231,$A31,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$235,$A31,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29351,15 +29827,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$231,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$235,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$231=$A32)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$235=$A32)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$231,$A32,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$235,$A32,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29418,15 +29894,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A37)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A37)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A37,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A37,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29437,15 +29913,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A38)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A38)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A38,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A38,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29456,15 +29932,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A39)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A39)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A39,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A39,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29475,15 +29951,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A40)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A40)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A40,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A40,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29494,15 +29970,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A41)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A41)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A41,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A41,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29513,15 +29989,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A42)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A42)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A42,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A42,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29532,15 +30008,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A43)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A43)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A43,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A43,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29551,15 +30027,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A44)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A44)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A44,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A44,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29570,15 +30046,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A45)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A45)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A45,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A45,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29589,15 +30065,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A46)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A46)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A46,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A46,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29608,15 +30084,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A47)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A47)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A47,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A47,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29627,15 +30103,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A48)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A48)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A48,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A48,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29646,15 +30122,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A49)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A49)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A49,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A49,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29665,15 +30141,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$231,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$231=$A50)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A50)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$231,$A50,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A50,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29732,15 +30208,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A55)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A55)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A55,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A55,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29751,15 +30227,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A56)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A56)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A56,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A56,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29770,15 +30246,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A57)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A57)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A57,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A57,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29789,15 +30265,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A58)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A58)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A58,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A58,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29808,15 +30284,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A59)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A59)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A59,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A59,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29827,15 +30303,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A60)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A60)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A60,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A60,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29846,15 +30322,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A61)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A61)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A61,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A61,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29865,15 +30341,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A62)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A62)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A62,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A62,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29884,15 +30360,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A63)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A63)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A63,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A63,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29903,15 +30379,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A64)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A64)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A64,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A64,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29922,15 +30398,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A65)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A65)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A65,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A65,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29941,15 +30417,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A66)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A66)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A66,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A66,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29960,15 +30436,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A67)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A67)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A67,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A67,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29979,15 +30455,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A68)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A68)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A68,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A68,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -29998,15 +30474,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A69)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A69)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A69,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A69,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -30017,15 +30493,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A70)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A70)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A70,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A70,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -30036,15 +30512,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A71)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A71)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A71,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A71,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -30055,15 +30531,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A72)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A72)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A72,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A72,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -30074,15 +30550,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A73)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A73)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A73,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A73,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -30093,15 +30569,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A74)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A74)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A74,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A74,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -30112,15 +30588,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A75)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A75)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A75,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A75,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -30131,15 +30607,15 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$231,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$231=$A76)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A76)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$231,$A76,Artikelstamm!$U$3:$U$231)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A76,Artikelstamm!$U$3:$U$235)</f>
         <v/>
       </c>
     </row>
@@ -30193,11 +30669,11 @@
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A81)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A81)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
     </row>
@@ -30208,11 +30684,11 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A82)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A82)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
     </row>
@@ -30223,11 +30699,11 @@
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A83)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A83)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
     </row>
@@ -30238,11 +30714,11 @@
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A84)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A84)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
     </row>
@@ -30253,11 +30729,11 @@
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A85)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A85)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
     </row>
@@ -30268,11 +30744,11 @@
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$231,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$231=$A86)*Artikelstamm!$K$3:$K$231*Artikelstamm!$AD$3:$AD$231)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A86)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -14307,7 +14307,7 @@
       </c>
       <c r="AM110" s="22" t="inlineStr">
         <is>
-          <t>Auf dem Erfassungsblatt NE01 durchgestrichen – entfaellt.</t>
+          <t>Auf dem Erfassungsblatt NE01 durchgestrichen - die Stuecke stehen jetzt im Flur 1 und werden dort als BA01-03 gefuehrt.</t>
         </is>
       </c>
     </row>
@@ -29209,12 +29209,12 @@
       </c>
       <c r="E234" s="15" t="inlineStr">
         <is>
-          <t>Tannen-Dekoration</t>
+          <t>Deko-Tannen Metall auf Holzsockel</t>
         </is>
       </c>
       <c r="F234" s="16" t="inlineStr">
         <is>
-          <t>Dekoration in Tannenform.</t>
+          <t>Stilisierte Tannen aus schwarz mattiertem Metall, auf ovalen Sockeln aus Massivholz. Skandinavischer Stil, standfest.</t>
         </is>
       </c>
       <c r="G234" s="15" t="inlineStr">
@@ -29233,7 +29233,7 @@
         </is>
       </c>
       <c r="J234" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K234" s="17" t="n"/>
       <c r="L234" s="18">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="N234" s="15" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="O234" s="19" t="n"/>
@@ -29272,13 +29272,17 @@
       </c>
       <c r="V234" s="15" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
-        </is>
-      </c>
-      <c r="W234" s="15" t="n"/>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W234" s="15" t="inlineStr">
+        <is>
+          <t>F-262</t>
+        </is>
+      </c>
       <c r="X234" s="19" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="Y234" s="19" t="n"/>
@@ -29303,12 +29307,12 @@
       <c r="AK234" s="19" t="n"/>
       <c r="AL234" s="16" t="inlineStr">
         <is>
-          <t>1 Stück.</t>
+          <t>3 Sockel, unterschiedlich bestückt: einer mit einem großen Baum, zwei mit je drei Bäumen. Alle drei sind abgebildet.</t>
         </is>
       </c>
       <c r="AM234" s="22" t="inlineStr">
         <is>
-          <t>OFFEN: Foto fehlt - IMG_2291 ist nicht angekommen. Beschreibung und Preis sind daher vorlaeufig. Moeglicherweise dieselben Stuecke wie NE01-15 (Deko-Tannenbaum schwarz, 3 Stueck), die dort durchgestrichen wurden.</t>
+          <t>Bisher unter NE01-15 gefuehrt; dort durchgestrichen, weil sie in den Flur 1 umgezogen sind.</t>
         </is>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$235</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$243</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM235"/>
+  <dimension ref="A1:AM243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -29323,7 +29323,11 @@
         </is>
       </c>
       <c r="B235" s="15" t="n"/>
-      <c r="C235" s="15" t="n"/>
+      <c r="C235" s="15" t="inlineStr">
+        <is>
+          <t>BA02-07</t>
+        </is>
+      </c>
       <c r="D235" s="15" t="inlineStr">
         <is>
           <t>BA01</t>
@@ -29355,7 +29359,7 @@
         </is>
       </c>
       <c r="J235" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K235" s="17" t="n"/>
       <c r="L235" s="18">
@@ -29429,13 +29433,961 @@
       <c r="AK235" s="19" t="n"/>
       <c r="AL235" s="16" t="inlineStr">
         <is>
-          <t>1 Stück.</t>
-        </is>
-      </c>
-      <c r="AM235" s="22" t="n"/>
+          <t>2 Buchstaben: einer im Flur 1 (BA01-04) und einer im Flur 2 (dort mit BA02-07 beschriftet).</t>
+        </is>
+      </c>
+      <c r="AM235" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA02-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="30" customHeight="1">
+      <c r="A236" s="15" t="inlineStr">
+        <is>
+          <t>BA02-01</t>
+        </is>
+      </c>
+      <c r="B236" s="15" t="n"/>
+      <c r="C236" s="15" t="n"/>
+      <c r="D236" s="15" t="inlineStr">
+        <is>
+          <t>BA02</t>
+        </is>
+      </c>
+      <c r="E236" s="15" t="inlineStr">
+        <is>
+          <t>Kindergarderobe weiß</t>
+        </is>
+      </c>
+      <c r="F236" s="16" t="inlineStr">
+        <is>
+          <t>Kindergarderobe in Weiß.</t>
+        </is>
+      </c>
+      <c r="G236" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H236" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I236" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J236" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K236" s="17" t="n"/>
+      <c r="L236" s="18">
+        <f>J236-IF(K236="",0,K236)</f>
+        <v/>
+      </c>
+      <c r="M236" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N236" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O236" s="19" t="n"/>
+      <c r="P236" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q236" s="19" t="n"/>
+      <c r="R236" s="20" t="n"/>
+      <c r="S236" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T236" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U236" s="21">
+        <f>L236*S236</f>
+        <v/>
+      </c>
+      <c r="V236" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W236" s="15" t="n"/>
+      <c r="X236" s="19" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="Y236" s="19" t="n"/>
+      <c r="Z236" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA236" s="19" t="n"/>
+      <c r="AB236" s="19" t="n"/>
+      <c r="AC236" s="19" t="n"/>
+      <c r="AD236" s="20" t="n"/>
+      <c r="AE236" s="21">
+        <f>IF(K236="","",K236*AD236)</f>
+        <v/>
+      </c>
+      <c r="AF236" s="19" t="n"/>
+      <c r="AG236" s="19" t="n"/>
+      <c r="AH236" s="19" t="n"/>
+      <c r="AI236" s="19" t="n"/>
+      <c r="AJ236" s="19" t="n"/>
+      <c r="AK236" s="19" t="n"/>
+      <c r="AL236" s="16" t="inlineStr">
+        <is>
+          <t>5 Stück.</t>
+        </is>
+      </c>
+      <c r="AM236" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: Foto fehlt - zu BA02-01 ist kein Bild angekommen. Beschreibung und Preis sind daher vorlaeufig. Moeglicherweise baugleich mit einer der bereits erfassten Garderoben (NU01-14, NU01-19, NU06-01/-02) - dann zusammenfassen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="30" customHeight="1">
+      <c r="A237" s="15" t="inlineStr">
+        <is>
+          <t>BA02-02</t>
+        </is>
+      </c>
+      <c r="B237" s="15" t="n"/>
+      <c r="C237" s="15" t="n"/>
+      <c r="D237" s="15" t="inlineStr">
+        <is>
+          <t>BA02</t>
+        </is>
+      </c>
+      <c r="E237" s="15" t="inlineStr">
+        <is>
+          <t>Rutscherauto rot</t>
+        </is>
+      </c>
+      <c r="F237" s="16" t="inlineStr">
+        <is>
+          <t>Rutscherauto in Sportwagenform, roter Kunststoffkorpus mit schwarzer Sitzfläche in Rautensteppung, verchromte Felgen, Lehne hinten zum Schieben.</t>
+        </is>
+      </c>
+      <c r="G237" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H237" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I237" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J237" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K237" s="17" t="n"/>
+      <c r="L237" s="18">
+        <f>J237-IF(K237="",0,K237)</f>
+        <v/>
+      </c>
+      <c r="M237" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N237" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O237" s="19" t="n"/>
+      <c r="P237" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q237" s="19" t="n"/>
+      <c r="R237" s="20" t="n"/>
+      <c r="S237" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T237" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U237" s="21">
+        <f>L237*S237</f>
+        <v/>
+      </c>
+      <c r="V237" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W237" s="15" t="inlineStr">
+        <is>
+          <t>F-263</t>
+        </is>
+      </c>
+      <c r="X237" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y237" s="19" t="n"/>
+      <c r="Z237" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA237" s="19" t="n"/>
+      <c r="AB237" s="19" t="n"/>
+      <c r="AC237" s="19" t="n"/>
+      <c r="AD237" s="20" t="n"/>
+      <c r="AE237" s="21">
+        <f>IF(K237="","",K237*AD237)</f>
+        <v/>
+      </c>
+      <c r="AF237" s="19" t="n"/>
+      <c r="AG237" s="19" t="n"/>
+      <c r="AH237" s="19" t="n"/>
+      <c r="AI237" s="19" t="n"/>
+      <c r="AJ237" s="19" t="n"/>
+      <c r="AK237" s="19" t="n"/>
+      <c r="AL237" s="16" t="inlineStr">
+        <is>
+          <t>1 Fahrzeug.</t>
+        </is>
+      </c>
+      <c r="AM237" s="22" t="n"/>
+    </row>
+    <row r="238" ht="30" customHeight="1">
+      <c r="A238" s="15" t="inlineStr">
+        <is>
+          <t>BA02-03</t>
+        </is>
+      </c>
+      <c r="B238" s="15" t="n"/>
+      <c r="C238" s="15" t="n"/>
+      <c r="D238" s="15" t="inlineStr">
+        <is>
+          <t>BA02</t>
+        </is>
+      </c>
+      <c r="E238" s="15" t="inlineStr">
+        <is>
+          <t>Bilder Schwarzwald, gerahmt</t>
+        </is>
+      </c>
+      <c r="F238" s="16" t="inlineStr">
+        <is>
+          <t>Schwarz gerahmte Zeichnungen hinter Glas in schlichter Strichtechnik: Bergkette, Mädchen mit Bollenhut und Tannenwald. Motivgruppe Schwarzwald.</t>
+        </is>
+      </c>
+      <c r="G238" s="15" t="inlineStr">
+        <is>
+          <t>Kunst</t>
+        </is>
+      </c>
+      <c r="H238" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I238" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J238" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K238" s="17" t="n"/>
+      <c r="L238" s="18">
+        <f>J238-IF(K238="",0,K238)</f>
+        <v/>
+      </c>
+      <c r="M238" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N238" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O238" s="19" t="n"/>
+      <c r="P238" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q238" s="19" t="n"/>
+      <c r="R238" s="20" t="n"/>
+      <c r="S238" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T238" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U238" s="21">
+        <f>L238*S238</f>
+        <v/>
+      </c>
+      <c r="V238" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W238" s="15" t="inlineStr">
+        <is>
+          <t>F-264</t>
+        </is>
+      </c>
+      <c r="X238" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y238" s="19" t="n"/>
+      <c r="Z238" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA238" s="19" t="n"/>
+      <c r="AB238" s="19" t="n"/>
+      <c r="AC238" s="19" t="n"/>
+      <c r="AD238" s="20" t="n"/>
+      <c r="AE238" s="21">
+        <f>IF(K238="","",K238*AD238)</f>
+        <v/>
+      </c>
+      <c r="AF238" s="19" t="n"/>
+      <c r="AG238" s="19" t="n"/>
+      <c r="AH238" s="19" t="n"/>
+      <c r="AI238" s="19" t="n"/>
+      <c r="AJ238" s="19" t="n"/>
+      <c r="AK238" s="19" t="n"/>
+      <c r="AL238" s="16" t="inlineStr">
+        <is>
+          <t>3 Bilder, alle abgebildet.</t>
+        </is>
+      </c>
+      <c r="AM238" s="22" t="n"/>
+    </row>
+    <row r="239" ht="30" customHeight="1">
+      <c r="A239" s="15" t="inlineStr">
+        <is>
+          <t>BA02-04</t>
+        </is>
+      </c>
+      <c r="B239" s="15" t="n"/>
+      <c r="C239" s="15" t="n"/>
+      <c r="D239" s="15" t="inlineStr">
+        <is>
+          <t>BA02</t>
+        </is>
+      </c>
+      <c r="E239" s="15" t="inlineStr">
+        <is>
+          <t>Kinder-Ohrensessel grau, Kunstleder</t>
+        </is>
+      </c>
+      <c r="F239" s="16" t="inlineStr">
+        <is>
+          <t>Ohrensessel in Kindergröße, hellgrauer Kunstlederbezug, geschwungene schwarze Holzbeine.</t>
+        </is>
+      </c>
+      <c r="G239" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H239" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I239" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J239" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K239" s="17" t="n"/>
+      <c r="L239" s="18">
+        <f>J239-IF(K239="",0,K239)</f>
+        <v/>
+      </c>
+      <c r="M239" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N239" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O239" s="19" t="n"/>
+      <c r="P239" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q239" s="19" t="n"/>
+      <c r="R239" s="20" t="n"/>
+      <c r="S239" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="T239" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U239" s="21">
+        <f>L239*S239</f>
+        <v/>
+      </c>
+      <c r="V239" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W239" s="15" t="inlineStr">
+        <is>
+          <t>F-265</t>
+        </is>
+      </c>
+      <c r="X239" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y239" s="19" t="n"/>
+      <c r="Z239" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA239" s="19" t="n"/>
+      <c r="AB239" s="19" t="n"/>
+      <c r="AC239" s="19" t="n"/>
+      <c r="AD239" s="20" t="n"/>
+      <c r="AE239" s="21">
+        <f>IF(K239="","",K239*AD239)</f>
+        <v/>
+      </c>
+      <c r="AF239" s="19" t="n"/>
+      <c r="AG239" s="19" t="n"/>
+      <c r="AH239" s="19" t="n"/>
+      <c r="AI239" s="19" t="n"/>
+      <c r="AJ239" s="19" t="n"/>
+      <c r="AK239" s="19" t="n"/>
+      <c r="AL239" s="16" t="inlineStr">
+        <is>
+          <t>1 Sessel. Baugleich in Rot gibt es zwei Stück unter NE01-20.</t>
+        </is>
+      </c>
+      <c r="AM239" s="22" t="n"/>
+    </row>
+    <row r="240" ht="30" customHeight="1">
+      <c r="A240" s="15" t="inlineStr">
+        <is>
+          <t>BA02-05</t>
+        </is>
+      </c>
+      <c r="B240" s="15" t="n"/>
+      <c r="C240" s="15" t="n"/>
+      <c r="D240" s="15" t="inlineStr">
+        <is>
+          <t>BA02</t>
+        </is>
+      </c>
+      <c r="E240" s="15" t="inlineStr">
+        <is>
+          <t>Ablagepult Holz auf Metallgestell</t>
+        </is>
+      </c>
+      <c r="F240" s="16" t="inlineStr">
+        <is>
+          <t>Pult mit geneigter Platte aus dunklem Holz mit schwarzer Auflage, auf einem C-förmigen schwarzen Metallgestell. Untergreifbar, im Haus als Stehpult für die Anwesenheitsliste genutzt.</t>
+        </is>
+      </c>
+      <c r="G240" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H240" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I240" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J240" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K240" s="17" t="n"/>
+      <c r="L240" s="18">
+        <f>J240-IF(K240="",0,K240)</f>
+        <v/>
+      </c>
+      <c r="M240" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N240" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O240" s="19" t="n"/>
+      <c r="P240" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q240" s="19" t="n"/>
+      <c r="R240" s="20" t="n"/>
+      <c r="S240" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T240" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U240" s="21">
+        <f>L240*S240</f>
+        <v/>
+      </c>
+      <c r="V240" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W240" s="15" t="inlineStr">
+        <is>
+          <t>F-266</t>
+        </is>
+      </c>
+      <c r="X240" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y240" s="19" t="n"/>
+      <c r="Z240" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA240" s="19" t="n"/>
+      <c r="AB240" s="19" t="n"/>
+      <c r="AC240" s="19" t="n"/>
+      <c r="AD240" s="20" t="n"/>
+      <c r="AE240" s="21">
+        <f>IF(K240="","",K240*AD240)</f>
+        <v/>
+      </c>
+      <c r="AF240" s="19" t="n"/>
+      <c r="AG240" s="19" t="n"/>
+      <c r="AH240" s="19" t="n"/>
+      <c r="AI240" s="19" t="n"/>
+      <c r="AJ240" s="19" t="n"/>
+      <c r="AK240" s="19" t="n"/>
+      <c r="AL240" s="16" t="inlineStr">
+        <is>
+          <t>1 Pult. Die Liste gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM240" s="22" t="n"/>
+    </row>
+    <row r="241" ht="30" customHeight="1">
+      <c r="A241" s="15" t="inlineStr">
+        <is>
+          <t>BA02-06</t>
+        </is>
+      </c>
+      <c r="B241" s="15" t="n"/>
+      <c r="C241" s="15" t="n"/>
+      <c r="D241" s="15" t="inlineStr">
+        <is>
+          <t>BA02</t>
+        </is>
+      </c>
+      <c r="E241" s="15" t="inlineStr">
+        <is>
+          <t>Truhenbank weiß mit Fellauflage</t>
+        </is>
+      </c>
+      <c r="F241" s="16" t="inlineStr">
+        <is>
+          <t>Sitzbank in Weiß mit geschwungenen Seitenteilen, Rückenbrett und aufklappbarer Sitzfläche mit Beschlägen. Darunter ein großer Stauraum. Eine weiße Fellauflage liegt auf der Sitzfläche.</t>
+        </is>
+      </c>
+      <c r="G241" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H241" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I241" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J241" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K241" s="17" t="n"/>
+      <c r="L241" s="18">
+        <f>J241-IF(K241="",0,K241)</f>
+        <v/>
+      </c>
+      <c r="M241" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N241" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O241" s="19" t="n"/>
+      <c r="P241" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q241" s="19" t="n"/>
+      <c r="R241" s="20" t="n"/>
+      <c r="S241" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T241" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U241" s="21">
+        <f>L241*S241</f>
+        <v/>
+      </c>
+      <c r="V241" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W241" s="15" t="inlineStr">
+        <is>
+          <t>F-267</t>
+        </is>
+      </c>
+      <c r="X241" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y241" s="19" t="n"/>
+      <c r="Z241" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA241" s="19" t="n"/>
+      <c r="AB241" s="19" t="n"/>
+      <c r="AC241" s="19" t="n"/>
+      <c r="AD241" s="20" t="n"/>
+      <c r="AE241" s="21">
+        <f>IF(K241="","",K241*AD241)</f>
+        <v/>
+      </c>
+      <c r="AF241" s="19" t="n"/>
+      <c r="AG241" s="19" t="n"/>
+      <c r="AH241" s="19" t="n"/>
+      <c r="AI241" s="19" t="n"/>
+      <c r="AJ241" s="19" t="n"/>
+      <c r="AK241" s="19" t="n"/>
+      <c r="AL241" s="16" t="inlineStr">
+        <is>
+          <t>1 Bank einschließlich der Fellauflage. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AM241" s="22" t="n"/>
+    </row>
+    <row r="242" ht="30" customHeight="1">
+      <c r="A242" s="15" t="inlineStr">
+        <is>
+          <t>BA02-08</t>
+        </is>
+      </c>
+      <c r="B242" s="15" t="n"/>
+      <c r="C242" s="15" t="n"/>
+      <c r="D242" s="15" t="inlineStr">
+        <is>
+          <t>BA02</t>
+        </is>
+      </c>
+      <c r="E242" s="15" t="inlineStr">
+        <is>
+          <t>Kinderschrank weiß mit Handabdrücken</t>
+        </is>
+      </c>
+      <c r="F242" s="16" t="inlineStr">
+        <is>
+          <t>Hoher Schrank in Weiß mit Türen und Schubladen, Griffmulden. Auf den Fronten kleben Aufkleber mit Kinderhandabdrücken in Schwarz und Rot; sie lassen sich abziehen.</t>
+        </is>
+      </c>
+      <c r="G242" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H242" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I242" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J242" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K242" s="17" t="n"/>
+      <c r="L242" s="18">
+        <f>J242-IF(K242="",0,K242)</f>
+        <v/>
+      </c>
+      <c r="M242" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N242" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O242" s="19" t="n"/>
+      <c r="P242" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q242" s="19" t="n"/>
+      <c r="R242" s="20" t="n"/>
+      <c r="S242" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T242" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U242" s="21">
+        <f>L242*S242</f>
+        <v/>
+      </c>
+      <c r="V242" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W242" s="15" t="inlineStr">
+        <is>
+          <t>F-269</t>
+        </is>
+      </c>
+      <c r="X242" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y242" s="19" t="n"/>
+      <c r="Z242" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA242" s="19" t="n"/>
+      <c r="AB242" s="19" t="n"/>
+      <c r="AC242" s="19" t="n"/>
+      <c r="AD242" s="20" t="n"/>
+      <c r="AE242" s="21">
+        <f>IF(K242="","",K242*AD242)</f>
+        <v/>
+      </c>
+      <c r="AF242" s="19" t="n"/>
+      <c r="AG242" s="19" t="n"/>
+      <c r="AH242" s="19" t="n"/>
+      <c r="AI242" s="19" t="n"/>
+      <c r="AJ242" s="19" t="n"/>
+      <c r="AK242" s="19" t="n"/>
+      <c r="AL242" s="16" t="inlineStr">
+        <is>
+          <t>2 Schränke – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AM242" s="22" t="n"/>
+    </row>
+    <row r="243" ht="30" customHeight="1">
+      <c r="A243" s="15" t="inlineStr">
+        <is>
+          <t>BA02-09</t>
+        </is>
+      </c>
+      <c r="B243" s="15" t="n"/>
+      <c r="C243" s="15" t="n"/>
+      <c r="D243" s="15" t="inlineStr">
+        <is>
+          <t>BA02</t>
+        </is>
+      </c>
+      <c r="E243" s="15" t="inlineStr">
+        <is>
+          <t>Deko-Häuser Keramik</t>
+        </is>
+      </c>
+      <c r="F243" s="16" t="inlineStr">
+        <is>
+          <t>Drei Häuschen aus Keramik mit ausgestanzten Fenstern, zum Beleuchten mit einem Teelicht: eines craquelé-grau, eines cremeweiß glasiert, eines dunkelgrau mit rundem Fenster.</t>
+        </is>
+      </c>
+      <c r="G243" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H243" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I243" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J243" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K243" s="17" t="n"/>
+      <c r="L243" s="18">
+        <f>J243-IF(K243="",0,K243)</f>
+        <v/>
+      </c>
+      <c r="M243" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N243" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O243" s="19" t="n"/>
+      <c r="P243" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q243" s="19" t="n"/>
+      <c r="R243" s="20" t="n"/>
+      <c r="S243" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T243" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U243" s="21">
+        <f>L243*S243</f>
+        <v/>
+      </c>
+      <c r="V243" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W243" s="15" t="inlineStr">
+        <is>
+          <t>F-270</t>
+        </is>
+      </c>
+      <c r="X243" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y243" s="19" t="n"/>
+      <c r="Z243" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA243" s="19" t="n"/>
+      <c r="AB243" s="19" t="n"/>
+      <c r="AC243" s="19" t="n"/>
+      <c r="AD243" s="20" t="n"/>
+      <c r="AE243" s="21">
+        <f>IF(K243="","",K243*AD243)</f>
+        <v/>
+      </c>
+      <c r="AF243" s="19" t="n"/>
+      <c r="AG243" s="19" t="n"/>
+      <c r="AH243" s="19" t="n"/>
+      <c r="AI243" s="19" t="n"/>
+      <c r="AJ243" s="19" t="n"/>
+      <c r="AK243" s="19" t="n"/>
+      <c r="AL243" s="16" t="inlineStr">
+        <is>
+          <t>3 Häuschen, alle abgebildet.</t>
+        </is>
+      </c>
+      <c r="AM243" s="22" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AM235"/>
+  <autoFilter ref="A2:AM243"/>
   <mergeCells count="7">
     <mergeCell ref="AH1:AK1"/>
     <mergeCell ref="S1:U1"/>
@@ -29445,7 +30397,7 @@
     <mergeCell ref="AL1:AM1"/>
     <mergeCell ref="AD1:AG1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z235">
+  <conditionalFormatting sqref="Z3:Z243">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -29456,12 +30408,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I235">
+  <conditionalFormatting sqref="I3:I243">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P235">
+  <conditionalFormatting sqref="P3:P243">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -29514,7 +30466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -29552,7 +30504,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$235)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$243)</f>
         <v/>
       </c>
     </row>
@@ -29563,7 +30515,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$235,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -29574,7 +30526,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$235,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -29585,7 +30537,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$235,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -29596,7 +30548,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$235,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -29607,7 +30559,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$235)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$243)</f>
         <v/>
       </c>
     </row>
@@ -29618,7 +30570,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$235)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -29636,7 +30588,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$235)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$243)</f>
         <v/>
       </c>
     </row>
@@ -29647,7 +30599,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$235,Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$243,Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
     </row>
@@ -29680,7 +30632,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$235="bezahlt")*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$243="bezahlt")*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
     </row>
@@ -29709,7 +30661,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$235,"*verkauft",Artikelstamm!$AH$3:$AH$235,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"*verkauft",Artikelstamm!$AH$3:$AH$243,"")</f>
         <v/>
       </c>
     </row>
@@ -29720,7 +30672,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$235,"*verkauft",Artikelstamm!$AI$3:$AI$235,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"*verkauft",Artikelstamm!$AI$3:$AI$243,"offen")</f>
         <v/>
       </c>
     </row>
@@ -29731,7 +30683,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$235,"reserviert",Artikelstamm!$AK$3:$AK$235,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"reserviert",Artikelstamm!$AK$3:$AK$243,"")</f>
         <v/>
       </c>
     </row>
@@ -29742,7 +30694,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$235,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$243,"")</f>
         <v/>
       </c>
     </row>
@@ -29753,7 +30705,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$235,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$243,"")</f>
         <v/>
       </c>
     </row>
@@ -29793,15 +30745,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$235,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$235=$A30)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A30)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$235,$A30,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A30,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -29812,15 +30764,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$235,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$235=$A31)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A31)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$235,$A31,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A31,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -29831,15 +30783,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$235,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$235=$A32)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A32)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$235,$A32,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A32,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -29898,15 +30850,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A37)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A37)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A37,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A37,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -29917,15 +30869,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A38)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A38)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A38,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A38,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -29936,15 +30888,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A39)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A39)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A39,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A39,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -29955,15 +30907,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A40)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A40)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A40,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A40,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -29974,15 +30926,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A41)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A41)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A41,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A41,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -29993,15 +30945,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A42)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A42)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A42,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A42,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30012,15 +30964,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A43)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A43)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A43,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A43,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30031,15 +30983,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A44)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A44)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A44,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A44,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30050,15 +31002,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A45)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A45)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A45,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A45,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30069,15 +31021,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A46)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A46)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A46,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A46,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30088,15 +31040,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A47)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A47)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A47,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A47,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30107,15 +31059,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A48)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A48)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A48,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A48,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30126,15 +31078,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A49)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A49)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A49,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A49,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30145,15 +31097,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$235,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$235=$A50)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A50)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$235,$A50,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A50,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30212,15 +31164,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A55)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A55)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A55,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A55,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30231,15 +31183,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A56)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A56)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A56,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A56,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30250,15 +31202,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A57)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A57)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A57,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A57,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30269,15 +31221,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A58)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A58)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A58,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A58,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30288,15 +31240,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A59)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A59)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A59,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A59,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30307,467 +31259,486 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A60)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A60)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A60,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A60,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="26" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Flur 2</t>
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A61)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A61)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A61,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A61,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="26" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A62)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A62)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A62,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A62,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum</t>
+          <t>Gartenanlage</t>
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A63)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A63)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A63,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A63,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A64)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A64)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A64,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A64,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum 2</t>
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A65)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A65)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A65,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A65,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A66)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A66)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A66,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A66,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="26" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Gruppenraum 5</t>
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A67)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A67)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A67,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A67,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="26" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A68)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A68)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A68,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A68,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A69)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A69)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A69,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A69,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum 4</t>
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A70)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A70)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A70,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A70,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="26" t="inlineStr">
         <is>
-          <t>Speisesaal</t>
+          <t>Schlafraum 5</t>
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A71)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A71)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A71,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A71,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="26" t="inlineStr">
         <is>
-          <t>Terrasse</t>
+          <t>Speisesaal</t>
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A72)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A72)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A72,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A72,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="26" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Terrasse</t>
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A73)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A73)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A73,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A73,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="26" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Treppenraum 1</t>
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A74)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A74)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A74,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A74,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A75)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A75)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A75,Artikelstamm!$U$3:$U$235)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A75,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B76" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A76)</f>
+        <v/>
+      </c>
+      <c r="C76" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A76)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <v/>
+      </c>
+      <c r="D76" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A76,Artikelstamm!$U$3:$U$243)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$235,$A76)</f>
-        <v/>
-      </c>
-      <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$235=$A76)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
-        <v/>
-      </c>
-      <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$235,$A76,Artikelstamm!$U$3:$U$235)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="28" t="inlineStr">
+      <c r="B77" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A77)</f>
+        <v/>
+      </c>
+      <c r="C77" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A77)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <v/>
+      </c>
+      <c r="D77" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A77,Artikelstamm!$U$3:$U$243)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B77" s="35">
-        <f>SUM(B55:B76)</f>
-        <v/>
-      </c>
-      <c r="C77" s="36">
-        <f>SUM(C55:C76)</f>
-        <v/>
-      </c>
-      <c r="D77" s="36">
-        <f>SUM(D55:D76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="25" t="inlineStr">
+      <c r="B78" s="35">
+        <f>SUM(B55:B77)</f>
+        <v/>
+      </c>
+      <c r="C78" s="36">
+        <f>SUM(C55:C77)</f>
+        <v/>
+      </c>
+      <c r="D78" s="36">
+        <f>SUM(D55:D77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="32" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B80" s="32" t="inlineStr">
+      <c r="B81" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C80" s="32" t="inlineStr">
+      <c r="C81" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A81)</f>
-        <v/>
-      </c>
-      <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A81)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
-        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A82)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A82)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A83)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A83)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A84)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A84)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A85)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A85)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B86" s="33">
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A86)</f>
+        <v/>
+      </c>
+      <c r="C86" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A86)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$235,$A86)</f>
-        <v/>
-      </c>
-      <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$235=$A86)*Artikelstamm!$K$3:$K$235*Artikelstamm!$AD$3:$AD$235)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="28" t="inlineStr">
+      <c r="B87" s="33">
+        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A87)</f>
+        <v/>
+      </c>
+      <c r="C87" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A87)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B87" s="35">
-        <f>SUM(B81:B86)</f>
-        <v/>
-      </c>
-      <c r="C87" s="36">
-        <f>SUM(C81:C86)</f>
+      <c r="B88" s="35">
+        <f>SUM(B82:B87)</f>
+        <v/>
+      </c>
+      <c r="C88" s="36">
+        <f>SUM(C82:C87)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AM$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM243"/>
+  <dimension ref="A1:AN242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1050,17 +1050,18 @@
     <col width="12" customWidth="1" min="26" max="26"/>
     <col width="14" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
-    <col width="22" customWidth="1" min="29" max="29"/>
-    <col width="17" customWidth="1" min="30" max="30"/>
-    <col width="14" customWidth="1" min="31" max="31"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="17" customWidth="1" min="31" max="31"/>
     <col width="14" customWidth="1" min="32" max="32"/>
-    <col width="24" customWidth="1" min="33" max="33"/>
-    <col width="14" customWidth="1" min="34" max="34"/>
-    <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="13" customWidth="1" min="36" max="36"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="24" customWidth="1" min="34" max="34"/>
+    <col width="14" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
     <col width="13" customWidth="1" min="37" max="37"/>
-    <col width="40" customWidth="1" min="38" max="38"/>
-    <col width="32" customWidth="1" min="39" max="39"/>
+    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="40" customWidth="1" min="39" max="39"/>
+    <col width="32" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1084,17 +1085,17 @@
           <t>VERMARKTUNG</t>
         </is>
       </c>
-      <c r="AD1" s="10" t="inlineStr">
+      <c r="AE1" s="10" t="inlineStr">
         <is>
           <t>VERKAUF</t>
         </is>
       </c>
-      <c r="AH1" s="9" t="inlineStr">
+      <c r="AI1" s="9" t="inlineStr">
         <is>
           <t>KAUFMÄNNISCH</t>
         </is>
       </c>
-      <c r="AL1" s="12" t="inlineStr">
+      <c r="AM1" s="12" t="inlineStr">
         <is>
           <t>NOTIZEN</t>
         </is>
@@ -1238,60 +1239,65 @@
       </c>
       <c r="AB2" s="14" t="inlineStr">
         <is>
+          <t>Bündel</t>
+        </is>
+      </c>
+      <c r="AC2" s="14" t="inlineStr">
+        <is>
           <t>Kanal</t>
         </is>
       </c>
-      <c r="AC2" s="14" t="inlineStr">
+      <c r="AD2" s="14" t="inlineStr">
         <is>
           <t>Reserviert_für</t>
         </is>
       </c>
-      <c r="AD2" s="14" t="inlineStr">
+      <c r="AE2" s="14" t="inlineStr">
         <is>
           <t>Verkaufspreis_netto</t>
         </is>
       </c>
-      <c r="AE2" s="13" t="inlineStr">
+      <c r="AF2" s="13" t="inlineStr">
         <is>
           <t>Umsatz_netto</t>
         </is>
       </c>
-      <c r="AF2" s="14" t="inlineStr">
+      <c r="AG2" s="14" t="inlineStr">
         <is>
           <t>Verkaufsdatum</t>
         </is>
       </c>
-      <c r="AG2" s="14" t="inlineStr">
+      <c r="AH2" s="14" t="inlineStr">
         <is>
           <t>Käufer</t>
         </is>
       </c>
-      <c r="AH2" s="14" t="inlineStr">
+      <c r="AI2" s="14" t="inlineStr">
         <is>
           <t>Rechnungsnr</t>
         </is>
       </c>
-      <c r="AI2" s="14" t="inlineStr">
+      <c r="AJ2" s="14" t="inlineStr">
         <is>
           <t>Zahlung</t>
         </is>
       </c>
-      <c r="AJ2" s="14" t="inlineStr">
+      <c r="AK2" s="14" t="inlineStr">
         <is>
           <t>Zahlart</t>
         </is>
       </c>
-      <c r="AK2" s="14" t="inlineStr">
+      <c r="AL2" s="14" t="inlineStr">
         <is>
           <t>Abholtermin</t>
         </is>
       </c>
-      <c r="AL2" s="13" t="inlineStr">
+      <c r="AM2" s="13" t="inlineStr">
         <is>
           <t>Mengenhinweis</t>
         </is>
       </c>
-      <c r="AM2" s="14" t="inlineStr">
+      <c r="AN2" s="14" t="inlineStr">
         <is>
           <t>Bemerkung</t>
         </is>
@@ -1401,23 +1407,24 @@
       <c r="AA3" s="19" t="n"/>
       <c r="AB3" s="19" t="n"/>
       <c r="AC3" s="19" t="n"/>
-      <c r="AD3" s="20" t="n"/>
-      <c r="AE3" s="21">
-        <f>IF(K3="","",K3*AD3)</f>
-        <v/>
-      </c>
-      <c r="AF3" s="19" t="n"/>
+      <c r="AD3" s="19" t="n"/>
+      <c r="AE3" s="20" t="n"/>
+      <c r="AF3" s="21">
+        <f>IF(K3="","",K3*AE3)</f>
+        <v/>
+      </c>
       <c r="AG3" s="19" t="n"/>
       <c r="AH3" s="19" t="n"/>
       <c r="AI3" s="19" t="n"/>
       <c r="AJ3" s="19" t="n"/>
       <c r="AK3" s="19" t="n"/>
-      <c r="AL3" s="16" t="inlineStr">
+      <c r="AL3" s="19" t="n"/>
+      <c r="AM3" s="16" t="inlineStr">
         <is>
           <t>1 Regal mit 6 Körben im Bild</t>
         </is>
       </c>
-      <c r="AM3" s="22" t="n"/>
+      <c r="AN3" s="22" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
@@ -1523,23 +1530,24 @@
       <c r="AA4" s="19" t="n"/>
       <c r="AB4" s="19" t="n"/>
       <c r="AC4" s="19" t="n"/>
-      <c r="AD4" s="20" t="n"/>
-      <c r="AE4" s="21">
-        <f>IF(K4="","",K4*AD4)</f>
-        <v/>
-      </c>
-      <c r="AF4" s="19" t="n"/>
+      <c r="AD4" s="19" t="n"/>
+      <c r="AE4" s="20" t="n"/>
+      <c r="AF4" s="21">
+        <f>IF(K4="","",K4*AE4)</f>
+        <v/>
+      </c>
       <c r="AG4" s="19" t="n"/>
       <c r="AH4" s="19" t="n"/>
       <c r="AI4" s="19" t="n"/>
       <c r="AJ4" s="19" t="n"/>
       <c r="AK4" s="19" t="n"/>
-      <c r="AL4" s="16" t="inlineStr">
+      <c r="AL4" s="19" t="n"/>
+      <c r="AM4" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM4" s="22" t="n"/>
+      <c r="AN4" s="22" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
@@ -1649,23 +1657,24 @@
       <c r="AA5" s="19" t="n"/>
       <c r="AB5" s="19" t="n"/>
       <c r="AC5" s="19" t="n"/>
-      <c r="AD5" s="20" t="n"/>
-      <c r="AE5" s="21">
-        <f>IF(K5="","",K5*AD5)</f>
-        <v/>
-      </c>
-      <c r="AF5" s="19" t="n"/>
+      <c r="AD5" s="19" t="n"/>
+      <c r="AE5" s="20" t="n"/>
+      <c r="AF5" s="21">
+        <f>IF(K5="","",K5*AE5)</f>
+        <v/>
+      </c>
       <c r="AG5" s="19" t="n"/>
       <c r="AH5" s="19" t="n"/>
       <c r="AI5" s="19" t="n"/>
       <c r="AJ5" s="19" t="n"/>
       <c r="AK5" s="19" t="n"/>
-      <c r="AL5" s="16" t="inlineStr">
+      <c r="AL5" s="19" t="n"/>
+      <c r="AM5" s="16" t="inlineStr">
         <is>
           <t>mehrere Schrankfächer - Menge bitte vor Ort festlegen</t>
         </is>
       </c>
-      <c r="AM5" s="22" t="n"/>
+      <c r="AN5" s="22" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
@@ -1771,23 +1780,24 @@
       <c r="AA6" s="19" t="n"/>
       <c r="AB6" s="19" t="n"/>
       <c r="AC6" s="19" t="n"/>
-      <c r="AD6" s="20" t="n"/>
-      <c r="AE6" s="21">
-        <f>IF(K6="","",K6*AD6)</f>
-        <v/>
-      </c>
-      <c r="AF6" s="19" t="n"/>
+      <c r="AD6" s="19" t="n"/>
+      <c r="AE6" s="20" t="n"/>
+      <c r="AF6" s="21">
+        <f>IF(K6="","",K6*AE6)</f>
+        <v/>
+      </c>
       <c r="AG6" s="19" t="n"/>
       <c r="AH6" s="19" t="n"/>
       <c r="AI6" s="19" t="n"/>
       <c r="AJ6" s="19" t="n"/>
       <c r="AK6" s="19" t="n"/>
-      <c r="AL6" s="16" t="inlineStr">
+      <c r="AL6" s="19" t="n"/>
+      <c r="AM6" s="16" t="inlineStr">
         <is>
           <t>1 Sortierkasten im Bild</t>
         </is>
       </c>
-      <c r="AM6" s="22" t="n"/>
+      <c r="AN6" s="22" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
@@ -1893,23 +1903,24 @@
       <c r="AA7" s="19" t="n"/>
       <c r="AB7" s="19" t="n"/>
       <c r="AC7" s="19" t="n"/>
-      <c r="AD7" s="20" t="n"/>
-      <c r="AE7" s="21">
-        <f>IF(K7="","",K7*AD7)</f>
-        <v/>
-      </c>
-      <c r="AF7" s="19" t="n"/>
+      <c r="AD7" s="19" t="n"/>
+      <c r="AE7" s="20" t="n"/>
+      <c r="AF7" s="21">
+        <f>IF(K7="","",K7*AE7)</f>
+        <v/>
+      </c>
       <c r="AG7" s="19" t="n"/>
       <c r="AH7" s="19" t="n"/>
       <c r="AI7" s="19" t="n"/>
       <c r="AJ7" s="19" t="n"/>
       <c r="AK7" s="19" t="n"/>
-      <c r="AL7" s="16" t="inlineStr">
+      <c r="AL7" s="19" t="n"/>
+      <c r="AM7" s="16" t="inlineStr">
         <is>
           <t>2 Regalböden im Bild</t>
         </is>
       </c>
-      <c r="AM7" s="22" t="n"/>
+      <c r="AN7" s="22" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
@@ -2015,23 +2026,24 @@
       <c r="AA8" s="19" t="n"/>
       <c r="AB8" s="19" t="n"/>
       <c r="AC8" s="19" t="n"/>
-      <c r="AD8" s="20" t="n"/>
-      <c r="AE8" s="21">
-        <f>IF(K8="","",K8*AD8)</f>
-        <v/>
-      </c>
-      <c r="AF8" s="19" t="n"/>
+      <c r="AD8" s="19" t="n"/>
+      <c r="AE8" s="20" t="n"/>
+      <c r="AF8" s="21">
+        <f>IF(K8="","",K8*AE8)</f>
+        <v/>
+      </c>
       <c r="AG8" s="19" t="n"/>
       <c r="AH8" s="19" t="n"/>
       <c r="AI8" s="19" t="n"/>
       <c r="AJ8" s="19" t="n"/>
       <c r="AK8" s="19" t="n"/>
-      <c r="AL8" s="16" t="inlineStr">
+      <c r="AL8" s="19" t="n"/>
+      <c r="AM8" s="16" t="inlineStr">
         <is>
           <t>1 Schrank inkl. Restbestand Papier</t>
         </is>
       </c>
-      <c r="AM8" s="22" t="n"/>
+      <c r="AN8" s="22" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
@@ -2137,23 +2149,24 @@
       <c r="AA9" s="19" t="n"/>
       <c r="AB9" s="19" t="n"/>
       <c r="AC9" s="19" t="n"/>
-      <c r="AD9" s="20" t="n"/>
-      <c r="AE9" s="21">
-        <f>IF(K9="","",K9*AD9)</f>
-        <v/>
-      </c>
-      <c r="AF9" s="19" t="n"/>
+      <c r="AD9" s="19" t="n"/>
+      <c r="AE9" s="20" t="n"/>
+      <c r="AF9" s="21">
+        <f>IF(K9="","",K9*AE9)</f>
+        <v/>
+      </c>
       <c r="AG9" s="19" t="n"/>
       <c r="AH9" s="19" t="n"/>
       <c r="AI9" s="19" t="n"/>
       <c r="AJ9" s="19" t="n"/>
       <c r="AK9" s="19" t="n"/>
-      <c r="AL9" s="16" t="inlineStr">
+      <c r="AL9" s="19" t="n"/>
+      <c r="AM9" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM9" s="22" t="n"/>
+      <c r="AN9" s="22" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
@@ -2259,23 +2272,24 @@
       <c r="AA10" s="19" t="n"/>
       <c r="AB10" s="19" t="n"/>
       <c r="AC10" s="19" t="n"/>
-      <c r="AD10" s="20" t="n"/>
-      <c r="AE10" s="21">
-        <f>IF(K10="","",K10*AD10)</f>
-        <v/>
-      </c>
-      <c r="AF10" s="19" t="n"/>
+      <c r="AD10" s="19" t="n"/>
+      <c r="AE10" s="20" t="n"/>
+      <c r="AF10" s="21">
+        <f>IF(K10="","",K10*AE10)</f>
+        <v/>
+      </c>
       <c r="AG10" s="19" t="n"/>
       <c r="AH10" s="19" t="n"/>
       <c r="AI10" s="19" t="n"/>
       <c r="AJ10" s="19" t="n"/>
       <c r="AK10" s="19" t="n"/>
-      <c r="AL10" s="16" t="inlineStr">
+      <c r="AL10" s="19" t="n"/>
+      <c r="AM10" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AM10" s="22" t="n"/>
+      <c r="AN10" s="22" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
@@ -2381,23 +2395,24 @@
       <c r="AA11" s="19" t="n"/>
       <c r="AB11" s="19" t="n"/>
       <c r="AC11" s="19" t="n"/>
-      <c r="AD11" s="20" t="n"/>
-      <c r="AE11" s="21">
-        <f>IF(K11="","",K11*AD11)</f>
-        <v/>
-      </c>
-      <c r="AF11" s="19" t="n"/>
+      <c r="AD11" s="19" t="n"/>
+      <c r="AE11" s="20" t="n"/>
+      <c r="AF11" s="21">
+        <f>IF(K11="","",K11*AE11)</f>
+        <v/>
+      </c>
       <c r="AG11" s="19" t="n"/>
       <c r="AH11" s="19" t="n"/>
       <c r="AI11" s="19" t="n"/>
       <c r="AJ11" s="19" t="n"/>
       <c r="AK11" s="19" t="n"/>
-      <c r="AL11" s="16" t="inlineStr">
+      <c r="AL11" s="19" t="n"/>
+      <c r="AM11" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM11" s="22" t="n"/>
+      <c r="AN11" s="22" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
@@ -2511,23 +2526,24 @@
       </c>
       <c r="AB12" s="19" t="n"/>
       <c r="AC12" s="19" t="n"/>
-      <c r="AD12" s="20" t="n"/>
-      <c r="AE12" s="21">
-        <f>IF(K12="","",K12*AD12)</f>
-        <v/>
-      </c>
-      <c r="AF12" s="19" t="n"/>
+      <c r="AD12" s="19" t="n"/>
+      <c r="AE12" s="20" t="n"/>
+      <c r="AF12" s="21">
+        <f>IF(K12="","",K12*AE12)</f>
+        <v/>
+      </c>
       <c r="AG12" s="19" t="n"/>
       <c r="AH12" s="19" t="n"/>
       <c r="AI12" s="19" t="n"/>
       <c r="AJ12" s="19" t="n"/>
       <c r="AK12" s="19" t="n"/>
-      <c r="AL12" s="16" t="inlineStr">
+      <c r="AL12" s="19" t="n"/>
+      <c r="AM12" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AM12" s="22" t="n"/>
+      <c r="AN12" s="22" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
@@ -2637,23 +2653,24 @@
       </c>
       <c r="AB13" s="19" t="n"/>
       <c r="AC13" s="19" t="n"/>
-      <c r="AD13" s="20" t="n"/>
-      <c r="AE13" s="21">
-        <f>IF(K13="","",K13*AD13)</f>
-        <v/>
-      </c>
-      <c r="AF13" s="19" t="n"/>
+      <c r="AD13" s="19" t="n"/>
+      <c r="AE13" s="20" t="n"/>
+      <c r="AF13" s="21">
+        <f>IF(K13="","",K13*AE13)</f>
+        <v/>
+      </c>
       <c r="AG13" s="19" t="n"/>
       <c r="AH13" s="19" t="n"/>
       <c r="AI13" s="19" t="n"/>
       <c r="AJ13" s="19" t="n"/>
       <c r="AK13" s="19" t="n"/>
-      <c r="AL13" s="16" t="inlineStr">
+      <c r="AL13" s="19" t="n"/>
+      <c r="AM13" s="16" t="inlineStr">
         <is>
           <t>mindestens 6 Stück erkennbar - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AM13" s="22" t="n"/>
+      <c r="AN13" s="22" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -2759,23 +2776,24 @@
       <c r="AA14" s="19" t="n"/>
       <c r="AB14" s="19" t="n"/>
       <c r="AC14" s="19" t="n"/>
-      <c r="AD14" s="20" t="n"/>
-      <c r="AE14" s="21">
-        <f>IF(K14="","",K14*AD14)</f>
-        <v/>
-      </c>
-      <c r="AF14" s="19" t="n"/>
+      <c r="AD14" s="19" t="n"/>
+      <c r="AE14" s="20" t="n"/>
+      <c r="AF14" s="21">
+        <f>IF(K14="","",K14*AE14)</f>
+        <v/>
+      </c>
       <c r="AG14" s="19" t="n"/>
       <c r="AH14" s="19" t="n"/>
       <c r="AI14" s="19" t="n"/>
       <c r="AJ14" s="19" t="n"/>
       <c r="AK14" s="19" t="n"/>
-      <c r="AL14" s="16" t="inlineStr">
+      <c r="AL14" s="19" t="n"/>
+      <c r="AM14" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AM14" s="22" t="n"/>
+      <c r="AN14" s="22" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
@@ -2881,23 +2899,24 @@
       <c r="AA15" s="19" t="n"/>
       <c r="AB15" s="19" t="n"/>
       <c r="AC15" s="19" t="n"/>
-      <c r="AD15" s="20" t="n"/>
-      <c r="AE15" s="21">
-        <f>IF(K15="","",K15*AD15)</f>
-        <v/>
-      </c>
-      <c r="AF15" s="19" t="n"/>
+      <c r="AD15" s="19" t="n"/>
+      <c r="AE15" s="20" t="n"/>
+      <c r="AF15" s="21">
+        <f>IF(K15="","",K15*AE15)</f>
+        <v/>
+      </c>
       <c r="AG15" s="19" t="n"/>
       <c r="AH15" s="19" t="n"/>
       <c r="AI15" s="19" t="n"/>
       <c r="AJ15" s="19" t="n"/>
       <c r="AK15" s="19" t="n"/>
-      <c r="AL15" s="16" t="inlineStr">
+      <c r="AL15" s="19" t="n"/>
+      <c r="AM15" s="16" t="inlineStr">
         <is>
           <t>1 Sofa im Bild</t>
         </is>
       </c>
-      <c r="AM15" s="22" t="n"/>
+      <c r="AN15" s="22" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
@@ -3004,23 +3023,24 @@
       <c r="AA16" s="19" t="n"/>
       <c r="AB16" s="19" t="n"/>
       <c r="AC16" s="19" t="n"/>
-      <c r="AD16" s="20" t="n"/>
-      <c r="AE16" s="21">
-        <f>IF(K16="","",K16*AD16)</f>
-        <v/>
-      </c>
-      <c r="AF16" s="19" t="n"/>
+      <c r="AD16" s="19" t="n"/>
+      <c r="AE16" s="20" t="n"/>
+      <c r="AF16" s="21">
+        <f>IF(K16="","",K16*AE16)</f>
+        <v/>
+      </c>
       <c r="AG16" s="19" t="n"/>
       <c r="AH16" s="19" t="n"/>
       <c r="AI16" s="19" t="n"/>
       <c r="AJ16" s="19" t="n"/>
       <c r="AK16" s="19" t="n"/>
-      <c r="AL16" s="16" t="inlineStr">
+      <c r="AL16" s="19" t="n"/>
+      <c r="AM16" s="16" t="inlineStr">
         <is>
           <t>1 Sessel im Bild</t>
         </is>
       </c>
-      <c r="AM16" s="22" t="n"/>
+      <c r="AN16" s="22" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -3127,23 +3147,24 @@
       <c r="AA17" s="19" t="n"/>
       <c r="AB17" s="19" t="n"/>
       <c r="AC17" s="19" t="n"/>
-      <c r="AD17" s="20" t="n"/>
-      <c r="AE17" s="21">
-        <f>IF(K17="","",K17*AD17)</f>
-        <v/>
-      </c>
-      <c r="AF17" s="19" t="n"/>
+      <c r="AD17" s="19" t="n"/>
+      <c r="AE17" s="20" t="n"/>
+      <c r="AF17" s="21">
+        <f>IF(K17="","",K17*AE17)</f>
+        <v/>
+      </c>
       <c r="AG17" s="19" t="n"/>
       <c r="AH17" s="19" t="n"/>
       <c r="AI17" s="19" t="n"/>
       <c r="AJ17" s="19" t="n"/>
       <c r="AK17" s="19" t="n"/>
-      <c r="AL17" s="16" t="inlineStr">
+      <c r="AL17" s="19" t="n"/>
+      <c r="AM17" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM17" s="22" t="n"/>
+      <c r="AN17" s="22" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
@@ -3249,23 +3270,24 @@
       <c r="AA18" s="19" t="n"/>
       <c r="AB18" s="19" t="n"/>
       <c r="AC18" s="19" t="n"/>
-      <c r="AD18" s="20" t="n"/>
-      <c r="AE18" s="21">
-        <f>IF(K18="","",K18*AD18)</f>
-        <v/>
-      </c>
-      <c r="AF18" s="19" t="n"/>
+      <c r="AD18" s="19" t="n"/>
+      <c r="AE18" s="20" t="n"/>
+      <c r="AF18" s="21">
+        <f>IF(K18="","",K18*AE18)</f>
+        <v/>
+      </c>
       <c r="AG18" s="19" t="n"/>
       <c r="AH18" s="19" t="n"/>
       <c r="AI18" s="19" t="n"/>
       <c r="AJ18" s="19" t="n"/>
       <c r="AK18" s="19" t="n"/>
-      <c r="AL18" s="16" t="inlineStr">
+      <c r="AL18" s="19" t="n"/>
+      <c r="AM18" s="16" t="inlineStr">
         <is>
           <t>2 Sessel im Bild</t>
         </is>
       </c>
-      <c r="AM18" s="22" t="n"/>
+      <c r="AN18" s="22" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
@@ -3371,23 +3393,24 @@
       <c r="AA19" s="19" t="n"/>
       <c r="AB19" s="19" t="n"/>
       <c r="AC19" s="19" t="n"/>
-      <c r="AD19" s="20" t="n"/>
-      <c r="AE19" s="21">
-        <f>IF(K19="","",K19*AD19)</f>
-        <v/>
-      </c>
-      <c r="AF19" s="19" t="n"/>
+      <c r="AD19" s="19" t="n"/>
+      <c r="AE19" s="20" t="n"/>
+      <c r="AF19" s="21">
+        <f>IF(K19="","",K19*AE19)</f>
+        <v/>
+      </c>
       <c r="AG19" s="19" t="n"/>
       <c r="AH19" s="19" t="n"/>
       <c r="AI19" s="19" t="n"/>
       <c r="AJ19" s="19" t="n"/>
       <c r="AK19" s="19" t="n"/>
-      <c r="AL19" s="16" t="inlineStr">
+      <c r="AL19" s="19" t="n"/>
+      <c r="AM19" s="16" t="inlineStr">
         <is>
           <t>2 Hocker im Bild</t>
         </is>
       </c>
-      <c r="AM19" s="22" t="n"/>
+      <c r="AN19" s="22" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
@@ -3493,23 +3516,24 @@
       <c r="AA20" s="19" t="n"/>
       <c r="AB20" s="19" t="n"/>
       <c r="AC20" s="19" t="n"/>
-      <c r="AD20" s="20" t="n"/>
-      <c r="AE20" s="21">
-        <f>IF(K20="","",K20*AD20)</f>
-        <v/>
-      </c>
-      <c r="AF20" s="19" t="n"/>
+      <c r="AD20" s="19" t="n"/>
+      <c r="AE20" s="20" t="n"/>
+      <c r="AF20" s="21">
+        <f>IF(K20="","",K20*AE20)</f>
+        <v/>
+      </c>
       <c r="AG20" s="19" t="n"/>
       <c r="AH20" s="19" t="n"/>
       <c r="AI20" s="19" t="n"/>
       <c r="AJ20" s="19" t="n"/>
       <c r="AK20" s="19" t="n"/>
-      <c r="AL20" s="16" t="inlineStr">
+      <c r="AL20" s="19" t="n"/>
+      <c r="AM20" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AM20" s="22" t="n"/>
+      <c r="AN20" s="22" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
@@ -3615,23 +3639,24 @@
       <c r="AA21" s="19" t="n"/>
       <c r="AB21" s="19" t="n"/>
       <c r="AC21" s="19" t="n"/>
-      <c r="AD21" s="20" t="n"/>
-      <c r="AE21" s="21">
-        <f>IF(K21="","",K21*AD21)</f>
-        <v/>
-      </c>
-      <c r="AF21" s="19" t="n"/>
+      <c r="AD21" s="19" t="n"/>
+      <c r="AE21" s="20" t="n"/>
+      <c r="AF21" s="21">
+        <f>IF(K21="","",K21*AE21)</f>
+        <v/>
+      </c>
       <c r="AG21" s="19" t="n"/>
       <c r="AH21" s="19" t="n"/>
       <c r="AI21" s="19" t="n"/>
       <c r="AJ21" s="19" t="n"/>
       <c r="AK21" s="19" t="n"/>
-      <c r="AL21" s="16" t="inlineStr">
+      <c r="AL21" s="19" t="n"/>
+      <c r="AM21" s="16" t="inlineStr">
         <is>
           <t>1 Leuchte im Bild</t>
         </is>
       </c>
-      <c r="AM21" s="22" t="n"/>
+      <c r="AN21" s="22" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
@@ -3737,23 +3762,24 @@
       <c r="AA22" s="19" t="n"/>
       <c r="AB22" s="19" t="n"/>
       <c r="AC22" s="19" t="n"/>
-      <c r="AD22" s="20" t="n"/>
-      <c r="AE22" s="21">
-        <f>IF(K22="","",K22*AD22)</f>
-        <v/>
-      </c>
-      <c r="AF22" s="19" t="n"/>
+      <c r="AD22" s="19" t="n"/>
+      <c r="AE22" s="20" t="n"/>
+      <c r="AF22" s="21">
+        <f>IF(K22="","",K22*AE22)</f>
+        <v/>
+      </c>
       <c r="AG22" s="19" t="n"/>
       <c r="AH22" s="19" t="n"/>
       <c r="AI22" s="19" t="n"/>
       <c r="AJ22" s="19" t="n"/>
       <c r="AK22" s="19" t="n"/>
-      <c r="AL22" s="16" t="inlineStr">
+      <c r="AL22" s="19" t="n"/>
+      <c r="AM22" s="16" t="inlineStr">
         <is>
           <t>1 Mobile im Bild</t>
         </is>
       </c>
-      <c r="AM22" s="22" t="n"/>
+      <c r="AN22" s="22" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
@@ -3859,23 +3885,24 @@
       <c r="AA23" s="19" t="n"/>
       <c r="AB23" s="19" t="n"/>
       <c r="AC23" s="19" t="n"/>
-      <c r="AD23" s="20" t="n"/>
-      <c r="AE23" s="21">
-        <f>IF(K23="","",K23*AD23)</f>
-        <v/>
-      </c>
-      <c r="AF23" s="19" t="n"/>
+      <c r="AD23" s="19" t="n"/>
+      <c r="AE23" s="20" t="n"/>
+      <c r="AF23" s="21">
+        <f>IF(K23="","",K23*AE23)</f>
+        <v/>
+      </c>
       <c r="AG23" s="19" t="n"/>
       <c r="AH23" s="19" t="n"/>
       <c r="AI23" s="19" t="n"/>
       <c r="AJ23" s="19" t="n"/>
       <c r="AK23" s="19" t="n"/>
-      <c r="AL23" s="16" t="inlineStr">
+      <c r="AL23" s="19" t="n"/>
+      <c r="AM23" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM23" s="22" t="n"/>
+      <c r="AN23" s="22" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
@@ -3981,23 +4008,24 @@
       <c r="AA24" s="19" t="n"/>
       <c r="AB24" s="19" t="n"/>
       <c r="AC24" s="19" t="n"/>
-      <c r="AD24" s="20" t="n"/>
-      <c r="AE24" s="21">
-        <f>IF(K24="","",K24*AD24)</f>
-        <v/>
-      </c>
-      <c r="AF24" s="19" t="n"/>
+      <c r="AD24" s="19" t="n"/>
+      <c r="AE24" s="20" t="n"/>
+      <c r="AF24" s="21">
+        <f>IF(K24="","",K24*AE24)</f>
+        <v/>
+      </c>
       <c r="AG24" s="19" t="n"/>
       <c r="AH24" s="19" t="n"/>
       <c r="AI24" s="19" t="n"/>
       <c r="AJ24" s="19" t="n"/>
       <c r="AK24" s="19" t="n"/>
-      <c r="AL24" s="16" t="inlineStr">
+      <c r="AL24" s="19" t="n"/>
+      <c r="AM24" s="16" t="inlineStr">
         <is>
           <t>3 Rahmen im Bild</t>
         </is>
       </c>
-      <c r="AM24" s="22" t="n"/>
+      <c r="AN24" s="22" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="15" t="inlineStr">
@@ -4103,23 +4131,24 @@
       <c r="AA25" s="19" t="n"/>
       <c r="AB25" s="19" t="n"/>
       <c r="AC25" s="19" t="n"/>
-      <c r="AD25" s="20" t="n"/>
-      <c r="AE25" s="21">
-        <f>IF(K25="","",K25*AD25)</f>
-        <v/>
-      </c>
-      <c r="AF25" s="19" t="n"/>
+      <c r="AD25" s="19" t="n"/>
+      <c r="AE25" s="20" t="n"/>
+      <c r="AF25" s="21">
+        <f>IF(K25="","",K25*AE25)</f>
+        <v/>
+      </c>
       <c r="AG25" s="19" t="n"/>
       <c r="AH25" s="19" t="n"/>
       <c r="AI25" s="19" t="n"/>
       <c r="AJ25" s="19" t="n"/>
       <c r="AK25" s="19" t="n"/>
-      <c r="AL25" s="16" t="inlineStr">
+      <c r="AL25" s="19" t="n"/>
+      <c r="AM25" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM25" s="22" t="n"/>
+      <c r="AN25" s="22" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="15" t="inlineStr">
@@ -4225,23 +4254,24 @@
       <c r="AA26" s="19" t="n"/>
       <c r="AB26" s="19" t="n"/>
       <c r="AC26" s="19" t="n"/>
-      <c r="AD26" s="20" t="n"/>
-      <c r="AE26" s="21">
-        <f>IF(K26="","",K26*AD26)</f>
-        <v/>
-      </c>
-      <c r="AF26" s="19" t="n"/>
+      <c r="AD26" s="19" t="n"/>
+      <c r="AE26" s="20" t="n"/>
+      <c r="AF26" s="21">
+        <f>IF(K26="","",K26*AE26)</f>
+        <v/>
+      </c>
       <c r="AG26" s="19" t="n"/>
       <c r="AH26" s="19" t="n"/>
       <c r="AI26" s="19" t="n"/>
       <c r="AJ26" s="19" t="n"/>
       <c r="AK26" s="19" t="n"/>
-      <c r="AL26" s="16" t="inlineStr">
+      <c r="AL26" s="19" t="n"/>
+      <c r="AM26" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM26" s="22" t="n"/>
+      <c r="AN26" s="22" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
@@ -4347,23 +4377,24 @@
       <c r="AA27" s="19" t="n"/>
       <c r="AB27" s="19" t="n"/>
       <c r="AC27" s="19" t="n"/>
-      <c r="AD27" s="20" t="n"/>
-      <c r="AE27" s="21">
-        <f>IF(K27="","",K27*AD27)</f>
-        <v/>
-      </c>
-      <c r="AF27" s="19" t="n"/>
+      <c r="AD27" s="19" t="n"/>
+      <c r="AE27" s="20" t="n"/>
+      <c r="AF27" s="21">
+        <f>IF(K27="","",K27*AE27)</f>
+        <v/>
+      </c>
       <c r="AG27" s="19" t="n"/>
       <c r="AH27" s="19" t="n"/>
       <c r="AI27" s="19" t="n"/>
       <c r="AJ27" s="19" t="n"/>
       <c r="AK27" s="19" t="n"/>
-      <c r="AL27" s="16" t="inlineStr">
+      <c r="AL27" s="19" t="n"/>
+      <c r="AM27" s="16" t="inlineStr">
         <is>
           <t>1 Sofa im Bild</t>
         </is>
       </c>
-      <c r="AM27" s="22" t="n"/>
+      <c r="AN27" s="22" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="15" t="inlineStr">
@@ -4469,23 +4500,24 @@
       <c r="AA28" s="19" t="n"/>
       <c r="AB28" s="19" t="n"/>
       <c r="AC28" s="19" t="n"/>
-      <c r="AD28" s="20" t="n"/>
-      <c r="AE28" s="21">
-        <f>IF(K28="","",K28*AD28)</f>
-        <v/>
-      </c>
-      <c r="AF28" s="19" t="n"/>
+      <c r="AD28" s="19" t="n"/>
+      <c r="AE28" s="20" t="n"/>
+      <c r="AF28" s="21">
+        <f>IF(K28="","",K28*AE28)</f>
+        <v/>
+      </c>
       <c r="AG28" s="19" t="n"/>
       <c r="AH28" s="19" t="n"/>
       <c r="AI28" s="19" t="n"/>
       <c r="AJ28" s="19" t="n"/>
       <c r="AK28" s="19" t="n"/>
-      <c r="AL28" s="16" t="inlineStr">
+      <c r="AL28" s="19" t="n"/>
+      <c r="AM28" s="16" t="inlineStr">
         <is>
           <t>1 Leuchte im Bild</t>
         </is>
       </c>
-      <c r="AM28" s="22" t="n"/>
+      <c r="AN28" s="22" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="15" t="inlineStr">
@@ -4591,23 +4623,24 @@
       <c r="AA29" s="19" t="n"/>
       <c r="AB29" s="19" t="n"/>
       <c r="AC29" s="19" t="n"/>
-      <c r="AD29" s="20" t="n"/>
-      <c r="AE29" s="21">
-        <f>IF(K29="","",K29*AD29)</f>
-        <v/>
-      </c>
-      <c r="AF29" s="19" t="n"/>
+      <c r="AD29" s="19" t="n"/>
+      <c r="AE29" s="20" t="n"/>
+      <c r="AF29" s="21">
+        <f>IF(K29="","",K29*AE29)</f>
+        <v/>
+      </c>
       <c r="AG29" s="19" t="n"/>
       <c r="AH29" s="19" t="n"/>
       <c r="AI29" s="19" t="n"/>
       <c r="AJ29" s="19" t="n"/>
       <c r="AK29" s="19" t="n"/>
-      <c r="AL29" s="16" t="inlineStr">
+      <c r="AL29" s="19" t="n"/>
+      <c r="AM29" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AM29" s="22" t="n"/>
+      <c r="AN29" s="22" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="15" t="inlineStr">
@@ -4713,23 +4746,24 @@
       <c r="AA30" s="19" t="n"/>
       <c r="AB30" s="19" t="n"/>
       <c r="AC30" s="19" t="n"/>
-      <c r="AD30" s="20" t="n"/>
-      <c r="AE30" s="21">
-        <f>IF(K30="","",K30*AD30)</f>
-        <v/>
-      </c>
-      <c r="AF30" s="19" t="n"/>
+      <c r="AD30" s="19" t="n"/>
+      <c r="AE30" s="20" t="n"/>
+      <c r="AF30" s="21">
+        <f>IF(K30="","",K30*AE30)</f>
+        <v/>
+      </c>
       <c r="AG30" s="19" t="n"/>
       <c r="AH30" s="19" t="n"/>
       <c r="AI30" s="19" t="n"/>
       <c r="AJ30" s="19" t="n"/>
       <c r="AK30" s="19" t="n"/>
-      <c r="AL30" s="16" t="inlineStr">
+      <c r="AL30" s="19" t="n"/>
+      <c r="AM30" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM30" s="22" t="n"/>
+      <c r="AN30" s="22" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="15" t="inlineStr">
@@ -4835,23 +4869,24 @@
       <c r="AA31" s="19" t="n"/>
       <c r="AB31" s="19" t="n"/>
       <c r="AC31" s="19" t="n"/>
-      <c r="AD31" s="20" t="n"/>
-      <c r="AE31" s="21">
-        <f>IF(K31="","",K31*AD31)</f>
-        <v/>
-      </c>
-      <c r="AF31" s="19" t="n"/>
+      <c r="AD31" s="19" t="n"/>
+      <c r="AE31" s="20" t="n"/>
+      <c r="AF31" s="21">
+        <f>IF(K31="","",K31*AE31)</f>
+        <v/>
+      </c>
       <c r="AG31" s="19" t="n"/>
       <c r="AH31" s="19" t="n"/>
       <c r="AI31" s="19" t="n"/>
       <c r="AJ31" s="19" t="n"/>
       <c r="AK31" s="19" t="n"/>
-      <c r="AL31" s="16" t="inlineStr">
+      <c r="AL31" s="19" t="n"/>
+      <c r="AM31" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AM31" s="22" t="n"/>
+      <c r="AN31" s="22" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -4957,23 +4992,24 @@
       <c r="AA32" s="19" t="n"/>
       <c r="AB32" s="19" t="n"/>
       <c r="AC32" s="19" t="n"/>
-      <c r="AD32" s="20" t="n"/>
-      <c r="AE32" s="21">
-        <f>IF(K32="","",K32*AD32)</f>
-        <v/>
-      </c>
-      <c r="AF32" s="19" t="n"/>
+      <c r="AD32" s="19" t="n"/>
+      <c r="AE32" s="20" t="n"/>
+      <c r="AF32" s="21">
+        <f>IF(K32="","",K32*AE32)</f>
+        <v/>
+      </c>
       <c r="AG32" s="19" t="n"/>
       <c r="AH32" s="19" t="n"/>
       <c r="AI32" s="19" t="n"/>
       <c r="AJ32" s="19" t="n"/>
       <c r="AK32" s="19" t="n"/>
-      <c r="AL32" s="16" t="inlineStr">
+      <c r="AL32" s="19" t="n"/>
+      <c r="AM32" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AM32" s="22" t="n"/>
+      <c r="AN32" s="22" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="15" t="inlineStr">
@@ -5079,23 +5115,24 @@
       <c r="AA33" s="19" t="n"/>
       <c r="AB33" s="19" t="n"/>
       <c r="AC33" s="19" t="n"/>
-      <c r="AD33" s="20" t="n"/>
-      <c r="AE33" s="21">
-        <f>IF(K33="","",K33*AD33)</f>
-        <v/>
-      </c>
-      <c r="AF33" s="19" t="n"/>
+      <c r="AD33" s="19" t="n"/>
+      <c r="AE33" s="20" t="n"/>
+      <c r="AF33" s="21">
+        <f>IF(K33="","",K33*AE33)</f>
+        <v/>
+      </c>
       <c r="AG33" s="19" t="n"/>
       <c r="AH33" s="19" t="n"/>
       <c r="AI33" s="19" t="n"/>
       <c r="AJ33" s="19" t="n"/>
       <c r="AK33" s="19" t="n"/>
-      <c r="AL33" s="16" t="inlineStr">
+      <c r="AL33" s="19" t="n"/>
+      <c r="AM33" s="16" t="inlineStr">
         <is>
           <t>1 Kübel im Bild (Bepflanzung enthalten)</t>
         </is>
       </c>
-      <c r="AM33" s="22" t="n"/>
+      <c r="AN33" s="22" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="15" t="inlineStr">
@@ -5213,23 +5250,24 @@
       </c>
       <c r="AB34" s="19" t="n"/>
       <c r="AC34" s="19" t="n"/>
-      <c r="AD34" s="20" t="n"/>
-      <c r="AE34" s="21">
-        <f>IF(K34="","",K34*AD34)</f>
-        <v/>
-      </c>
-      <c r="AF34" s="19" t="n"/>
+      <c r="AD34" s="19" t="n"/>
+      <c r="AE34" s="20" t="n"/>
+      <c r="AF34" s="21">
+        <f>IF(K34="","",K34*AE34)</f>
+        <v/>
+      </c>
       <c r="AG34" s="19" t="n"/>
       <c r="AH34" s="19" t="n"/>
       <c r="AI34" s="19" t="n"/>
       <c r="AJ34" s="19" t="n"/>
       <c r="AK34" s="19" t="n"/>
-      <c r="AL34" s="16" t="inlineStr">
+      <c r="AL34" s="19" t="n"/>
+      <c r="AM34" s="16" t="inlineStr">
         <is>
           <t>2 Teppiche insgesamt: einer im Gruppenraum (BU04-03) und einer im Gruppenraum 5 (dort mit NU02-10 beschriftet).</t>
         </is>
       </c>
-      <c r="AM34" s="22" t="inlineStr">
+      <c r="AN34" s="22" t="inlineStr">
         <is>
           <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: NU02-10.</t>
         </is>
@@ -5347,23 +5385,24 @@
       </c>
       <c r="AB35" s="19" t="n"/>
       <c r="AC35" s="19" t="n"/>
-      <c r="AD35" s="20" t="n"/>
-      <c r="AE35" s="21">
-        <f>IF(K35="","",K35*AD35)</f>
-        <v/>
-      </c>
-      <c r="AF35" s="19" t="n"/>
+      <c r="AD35" s="19" t="n"/>
+      <c r="AE35" s="20" t="n"/>
+      <c r="AF35" s="21">
+        <f>IF(K35="","",K35*AE35)</f>
+        <v/>
+      </c>
       <c r="AG35" s="19" t="n"/>
       <c r="AH35" s="19" t="n"/>
       <c r="AI35" s="19" t="n"/>
       <c r="AJ35" s="19" t="n"/>
       <c r="AK35" s="19" t="n"/>
-      <c r="AL35" s="16" t="inlineStr">
+      <c r="AL35" s="19" t="n"/>
+      <c r="AM35" s="16" t="inlineStr">
         <is>
           <t>4 Regale insgesamt: 2 im Gruppenraum (BU04-04) und 2 im Gruppenraum 5 (dort mit NU02-06 beschriftet).</t>
         </is>
       </c>
-      <c r="AM35" s="22" t="inlineStr">
+      <c r="AN35" s="22" t="inlineStr">
         <is>
           <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: NU02-06.</t>
         </is>
@@ -5473,23 +5512,24 @@
       <c r="AA36" s="19" t="n"/>
       <c r="AB36" s="19" t="n"/>
       <c r="AC36" s="19" t="n"/>
-      <c r="AD36" s="20" t="n"/>
-      <c r="AE36" s="21">
-        <f>IF(K36="","",K36*AD36)</f>
-        <v/>
-      </c>
-      <c r="AF36" s="19" t="n"/>
+      <c r="AD36" s="19" t="n"/>
+      <c r="AE36" s="20" t="n"/>
+      <c r="AF36" s="21">
+        <f>IF(K36="","",K36*AE36)</f>
+        <v/>
+      </c>
       <c r="AG36" s="19" t="n"/>
       <c r="AH36" s="19" t="n"/>
       <c r="AI36" s="19" t="n"/>
       <c r="AJ36" s="19" t="n"/>
       <c r="AK36" s="19" t="n"/>
-      <c r="AL36" s="16" t="inlineStr">
+      <c r="AL36" s="19" t="n"/>
+      <c r="AM36" s="16" t="inlineStr">
         <is>
           <t>1 Set im Bild</t>
         </is>
       </c>
-      <c r="AM36" s="22" t="n"/>
+      <c r="AN36" s="22" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
@@ -5595,23 +5635,24 @@
       <c r="AA37" s="19" t="n"/>
       <c r="AB37" s="19" t="n"/>
       <c r="AC37" s="19" t="n"/>
-      <c r="AD37" s="20" t="n"/>
-      <c r="AE37" s="21">
-        <f>IF(K37="","",K37*AD37)</f>
-        <v/>
-      </c>
-      <c r="AF37" s="19" t="n"/>
+      <c r="AD37" s="19" t="n"/>
+      <c r="AE37" s="20" t="n"/>
+      <c r="AF37" s="21">
+        <f>IF(K37="","",K37*AE37)</f>
+        <v/>
+      </c>
       <c r="AG37" s="19" t="n"/>
       <c r="AH37" s="19" t="n"/>
       <c r="AI37" s="19" t="n"/>
       <c r="AJ37" s="19" t="n"/>
       <c r="AK37" s="19" t="n"/>
-      <c r="AL37" s="16" t="inlineStr">
+      <c r="AL37" s="19" t="n"/>
+      <c r="AM37" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM37" s="22" t="n"/>
+      <c r="AN37" s="22" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="15" t="inlineStr">
@@ -5717,23 +5758,24 @@
       <c r="AA38" s="19" t="n"/>
       <c r="AB38" s="19" t="n"/>
       <c r="AC38" s="19" t="n"/>
-      <c r="AD38" s="20" t="n"/>
-      <c r="AE38" s="21">
-        <f>IF(K38="","",K38*AD38)</f>
-        <v/>
-      </c>
-      <c r="AF38" s="19" t="n"/>
+      <c r="AD38" s="19" t="n"/>
+      <c r="AE38" s="20" t="n"/>
+      <c r="AF38" s="21">
+        <f>IF(K38="","",K38*AE38)</f>
+        <v/>
+      </c>
       <c r="AG38" s="19" t="n"/>
       <c r="AH38" s="19" t="n"/>
       <c r="AI38" s="19" t="n"/>
       <c r="AJ38" s="19" t="n"/>
       <c r="AK38" s="19" t="n"/>
-      <c r="AL38" s="16" t="inlineStr">
+      <c r="AL38" s="19" t="n"/>
+      <c r="AM38" s="16" t="inlineStr">
         <is>
           <t>mehrere Kisten im Bild</t>
         </is>
       </c>
-      <c r="AM38" s="22" t="n"/>
+      <c r="AN38" s="22" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="15" t="inlineStr">
@@ -5839,23 +5881,24 @@
       <c r="AA39" s="19" t="n"/>
       <c r="AB39" s="19" t="n"/>
       <c r="AC39" s="19" t="n"/>
-      <c r="AD39" s="20" t="n"/>
-      <c r="AE39" s="21">
-        <f>IF(K39="","",K39*AD39)</f>
-        <v/>
-      </c>
-      <c r="AF39" s="19" t="n"/>
+      <c r="AD39" s="19" t="n"/>
+      <c r="AE39" s="20" t="n"/>
+      <c r="AF39" s="21">
+        <f>IF(K39="","",K39*AE39)</f>
+        <v/>
+      </c>
       <c r="AG39" s="19" t="n"/>
       <c r="AH39" s="19" t="n"/>
       <c r="AI39" s="19" t="n"/>
       <c r="AJ39" s="19" t="n"/>
       <c r="AK39" s="19" t="n"/>
-      <c r="AL39" s="16" t="inlineStr">
+      <c r="AL39" s="19" t="n"/>
+      <c r="AM39" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM39" s="22" t="n"/>
+      <c r="AN39" s="22" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="15" t="inlineStr">
@@ -5961,23 +6004,24 @@
       <c r="AA40" s="19" t="n"/>
       <c r="AB40" s="19" t="n"/>
       <c r="AC40" s="19" t="n"/>
-      <c r="AD40" s="20" t="n"/>
-      <c r="AE40" s="21">
-        <f>IF(K40="","",K40*AD40)</f>
-        <v/>
-      </c>
-      <c r="AF40" s="19" t="n"/>
+      <c r="AD40" s="19" t="n"/>
+      <c r="AE40" s="20" t="n"/>
+      <c r="AF40" s="21">
+        <f>IF(K40="","",K40*AE40)</f>
+        <v/>
+      </c>
       <c r="AG40" s="19" t="n"/>
       <c r="AH40" s="19" t="n"/>
       <c r="AI40" s="19" t="n"/>
       <c r="AJ40" s="19" t="n"/>
       <c r="AK40" s="19" t="n"/>
-      <c r="AL40" s="16" t="inlineStr">
+      <c r="AL40" s="19" t="n"/>
+      <c r="AM40" s="16" t="inlineStr">
         <is>
           <t>1 Liege im Bild</t>
         </is>
       </c>
-      <c r="AM40" s="22" t="n"/>
+      <c r="AN40" s="22" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="15" t="inlineStr">
@@ -6079,23 +6123,24 @@
       <c r="AA41" s="19" t="n"/>
       <c r="AB41" s="19" t="n"/>
       <c r="AC41" s="19" t="n"/>
-      <c r="AD41" s="20" t="n"/>
-      <c r="AE41" s="21">
-        <f>IF(K41="","",K41*AD41)</f>
-        <v/>
-      </c>
-      <c r="AF41" s="19" t="n"/>
+      <c r="AD41" s="19" t="n"/>
+      <c r="AE41" s="20" t="n"/>
+      <c r="AF41" s="21">
+        <f>IF(K41="","",K41*AE41)</f>
+        <v/>
+      </c>
       <c r="AG41" s="19" t="n"/>
       <c r="AH41" s="19" t="n"/>
       <c r="AI41" s="19" t="n"/>
       <c r="AJ41" s="19" t="n"/>
       <c r="AK41" s="19" t="n"/>
-      <c r="AL41" s="16" t="inlineStr">
+      <c r="AL41" s="19" t="n"/>
+      <c r="AM41" s="16" t="inlineStr">
         <is>
           <t>1 Einheit aus 3 Modulen im Bild</t>
         </is>
       </c>
-      <c r="AM41" s="22" t="n"/>
+      <c r="AN41" s="22" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="15" t="inlineStr">
@@ -6197,23 +6242,24 @@
       <c r="AA42" s="19" t="n"/>
       <c r="AB42" s="19" t="n"/>
       <c r="AC42" s="19" t="n"/>
-      <c r="AD42" s="20" t="n"/>
-      <c r="AE42" s="21">
-        <f>IF(K42="","",K42*AD42)</f>
-        <v/>
-      </c>
-      <c r="AF42" s="19" t="n"/>
+      <c r="AD42" s="19" t="n"/>
+      <c r="AE42" s="20" t="n"/>
+      <c r="AF42" s="21">
+        <f>IF(K42="","",K42*AE42)</f>
+        <v/>
+      </c>
       <c r="AG42" s="19" t="n"/>
       <c r="AH42" s="19" t="n"/>
       <c r="AI42" s="19" t="n"/>
       <c r="AJ42" s="19" t="n"/>
       <c r="AK42" s="19" t="n"/>
-      <c r="AL42" s="16" t="inlineStr">
+      <c r="AL42" s="19" t="n"/>
+      <c r="AM42" s="16" t="inlineStr">
         <is>
           <t>3 Teile im Bild</t>
         </is>
       </c>
-      <c r="AM42" s="22" t="n"/>
+      <c r="AN42" s="22" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
@@ -6315,23 +6361,24 @@
       <c r="AA43" s="19" t="n"/>
       <c r="AB43" s="19" t="n"/>
       <c r="AC43" s="19" t="n"/>
-      <c r="AD43" s="20" t="n"/>
-      <c r="AE43" s="21">
-        <f>IF(K43="","",K43*AD43)</f>
-        <v/>
-      </c>
-      <c r="AF43" s="19" t="n"/>
+      <c r="AD43" s="19" t="n"/>
+      <c r="AE43" s="20" t="n"/>
+      <c r="AF43" s="21">
+        <f>IF(K43="","",K43*AE43)</f>
+        <v/>
+      </c>
       <c r="AG43" s="19" t="n"/>
       <c r="AH43" s="19" t="n"/>
       <c r="AI43" s="19" t="n"/>
       <c r="AJ43" s="19" t="n"/>
       <c r="AK43" s="19" t="n"/>
-      <c r="AL43" s="16" t="inlineStr">
+      <c r="AL43" s="19" t="n"/>
+      <c r="AM43" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM43" s="22" t="n"/>
+      <c r="AN43" s="22" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
@@ -6433,23 +6480,24 @@
       <c r="AA44" s="19" t="n"/>
       <c r="AB44" s="19" t="n"/>
       <c r="AC44" s="19" t="n"/>
-      <c r="AD44" s="20" t="n"/>
-      <c r="AE44" s="21">
-        <f>IF(K44="","",K44*AD44)</f>
-        <v/>
-      </c>
-      <c r="AF44" s="19" t="n"/>
+      <c r="AD44" s="19" t="n"/>
+      <c r="AE44" s="20" t="n"/>
+      <c r="AF44" s="21">
+        <f>IF(K44="","",K44*AE44)</f>
+        <v/>
+      </c>
       <c r="AG44" s="19" t="n"/>
       <c r="AH44" s="19" t="n"/>
       <c r="AI44" s="19" t="n"/>
       <c r="AJ44" s="19" t="n"/>
       <c r="AK44" s="19" t="n"/>
-      <c r="AL44" s="16" t="inlineStr">
+      <c r="AL44" s="19" t="n"/>
+      <c r="AM44" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM44" s="22" t="n"/>
+      <c r="AN44" s="22" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="15" t="inlineStr">
@@ -6551,23 +6599,24 @@
       <c r="AA45" s="19" t="n"/>
       <c r="AB45" s="19" t="n"/>
       <c r="AC45" s="19" t="n"/>
-      <c r="AD45" s="20" t="n"/>
-      <c r="AE45" s="21">
-        <f>IF(K45="","",K45*AD45)</f>
-        <v/>
-      </c>
-      <c r="AF45" s="19" t="n"/>
+      <c r="AD45" s="19" t="n"/>
+      <c r="AE45" s="20" t="n"/>
+      <c r="AF45" s="21">
+        <f>IF(K45="","",K45*AE45)</f>
+        <v/>
+      </c>
       <c r="AG45" s="19" t="n"/>
       <c r="AH45" s="19" t="n"/>
       <c r="AI45" s="19" t="n"/>
       <c r="AJ45" s="19" t="n"/>
       <c r="AK45" s="19" t="n"/>
-      <c r="AL45" s="16" t="inlineStr">
+      <c r="AL45" s="19" t="n"/>
+      <c r="AM45" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM45" s="22" t="n"/>
+      <c r="AN45" s="22" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="15" t="inlineStr">
@@ -6669,23 +6718,24 @@
       <c r="AA46" s="19" t="n"/>
       <c r="AB46" s="19" t="n"/>
       <c r="AC46" s="19" t="n"/>
-      <c r="AD46" s="20" t="n"/>
-      <c r="AE46" s="21">
-        <f>IF(K46="","",K46*AD46)</f>
-        <v/>
-      </c>
-      <c r="AF46" s="19" t="n"/>
+      <c r="AD46" s="19" t="n"/>
+      <c r="AE46" s="20" t="n"/>
+      <c r="AF46" s="21">
+        <f>IF(K46="","",K46*AE46)</f>
+        <v/>
+      </c>
       <c r="AG46" s="19" t="n"/>
       <c r="AH46" s="19" t="n"/>
       <c r="AI46" s="19" t="n"/>
       <c r="AJ46" s="19" t="n"/>
       <c r="AK46" s="19" t="n"/>
-      <c r="AL46" s="16" t="inlineStr">
+      <c r="AL46" s="19" t="n"/>
+      <c r="AM46" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM46" s="22" t="n"/>
+      <c r="AN46" s="22" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="15" t="inlineStr">
@@ -6787,23 +6837,24 @@
       <c r="AA47" s="19" t="n"/>
       <c r="AB47" s="19" t="n"/>
       <c r="AC47" s="19" t="n"/>
-      <c r="AD47" s="20" t="n"/>
-      <c r="AE47" s="21">
-        <f>IF(K47="","",K47*AD47)</f>
-        <v/>
-      </c>
-      <c r="AF47" s="19" t="n"/>
+      <c r="AD47" s="19" t="n"/>
+      <c r="AE47" s="20" t="n"/>
+      <c r="AF47" s="21">
+        <f>IF(K47="","",K47*AE47)</f>
+        <v/>
+      </c>
       <c r="AG47" s="19" t="n"/>
       <c r="AH47" s="19" t="n"/>
       <c r="AI47" s="19" t="n"/>
       <c r="AJ47" s="19" t="n"/>
       <c r="AK47" s="19" t="n"/>
-      <c r="AL47" s="16" t="inlineStr">
+      <c r="AL47" s="19" t="n"/>
+      <c r="AM47" s="16" t="inlineStr">
         <is>
           <t>3 Regale im Bild erkennbar</t>
         </is>
       </c>
-      <c r="AM47" s="22" t="n"/>
+      <c r="AN47" s="22" t="n"/>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="15" t="inlineStr">
@@ -6905,23 +6956,24 @@
       <c r="AA48" s="19" t="n"/>
       <c r="AB48" s="19" t="n"/>
       <c r="AC48" s="19" t="n"/>
-      <c r="AD48" s="20" t="n"/>
-      <c r="AE48" s="21">
-        <f>IF(K48="","",K48*AD48)</f>
-        <v/>
-      </c>
-      <c r="AF48" s="19" t="n"/>
+      <c r="AD48" s="19" t="n"/>
+      <c r="AE48" s="20" t="n"/>
+      <c r="AF48" s="21">
+        <f>IF(K48="","",K48*AE48)</f>
+        <v/>
+      </c>
       <c r="AG48" s="19" t="n"/>
       <c r="AH48" s="19" t="n"/>
       <c r="AI48" s="19" t="n"/>
       <c r="AJ48" s="19" t="n"/>
       <c r="AK48" s="19" t="n"/>
-      <c r="AL48" s="16" t="inlineStr">
+      <c r="AL48" s="19" t="n"/>
+      <c r="AM48" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM48" s="22" t="n"/>
+      <c r="AN48" s="22" t="n"/>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="15" t="inlineStr">
@@ -7023,23 +7075,24 @@
       <c r="AA49" s="19" t="n"/>
       <c r="AB49" s="19" t="n"/>
       <c r="AC49" s="19" t="n"/>
-      <c r="AD49" s="20" t="n"/>
-      <c r="AE49" s="21">
-        <f>IF(K49="","",K49*AD49)</f>
-        <v/>
-      </c>
-      <c r="AF49" s="19" t="n"/>
+      <c r="AD49" s="19" t="n"/>
+      <c r="AE49" s="20" t="n"/>
+      <c r="AF49" s="21">
+        <f>IF(K49="","",K49*AE49)</f>
+        <v/>
+      </c>
       <c r="AG49" s="19" t="n"/>
       <c r="AH49" s="19" t="n"/>
       <c r="AI49" s="19" t="n"/>
       <c r="AJ49" s="19" t="n"/>
       <c r="AK49" s="19" t="n"/>
-      <c r="AL49" s="16" t="inlineStr">
+      <c r="AL49" s="19" t="n"/>
+      <c r="AM49" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM49" s="22" t="n"/>
+      <c r="AN49" s="22" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="15" t="inlineStr">
@@ -7141,23 +7194,24 @@
       <c r="AA50" s="19" t="n"/>
       <c r="AB50" s="19" t="n"/>
       <c r="AC50" s="19" t="n"/>
-      <c r="AD50" s="20" t="n"/>
-      <c r="AE50" s="21">
-        <f>IF(K50="","",K50*AD50)</f>
-        <v/>
-      </c>
-      <c r="AF50" s="19" t="n"/>
+      <c r="AD50" s="19" t="n"/>
+      <c r="AE50" s="20" t="n"/>
+      <c r="AF50" s="21">
+        <f>IF(K50="","",K50*AE50)</f>
+        <v/>
+      </c>
       <c r="AG50" s="19" t="n"/>
       <c r="AH50" s="19" t="n"/>
       <c r="AI50" s="19" t="n"/>
       <c r="AJ50" s="19" t="n"/>
       <c r="AK50" s="19" t="n"/>
-      <c r="AL50" s="16" t="inlineStr">
+      <c r="AL50" s="19" t="n"/>
+      <c r="AM50" s="16" t="inlineStr">
         <is>
           <t>2 Bilder im Bild</t>
         </is>
       </c>
-      <c r="AM50" s="22" t="n"/>
+      <c r="AN50" s="22" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="15" t="inlineStr">
@@ -7259,23 +7313,24 @@
       <c r="AA51" s="19" t="n"/>
       <c r="AB51" s="19" t="n"/>
       <c r="AC51" s="19" t="n"/>
-      <c r="AD51" s="20" t="n"/>
-      <c r="AE51" s="21">
-        <f>IF(K51="","",K51*AD51)</f>
-        <v/>
-      </c>
-      <c r="AF51" s="19" t="n"/>
+      <c r="AD51" s="19" t="n"/>
+      <c r="AE51" s="20" t="n"/>
+      <c r="AF51" s="21">
+        <f>IF(K51="","",K51*AE51)</f>
+        <v/>
+      </c>
       <c r="AG51" s="19" t="n"/>
       <c r="AH51" s="19" t="n"/>
       <c r="AI51" s="19" t="n"/>
       <c r="AJ51" s="19" t="n"/>
       <c r="AK51" s="19" t="n"/>
-      <c r="AL51" s="16" t="inlineStr">
+      <c r="AL51" s="19" t="n"/>
+      <c r="AM51" s="16" t="inlineStr">
         <is>
           <t>1 Set im Bild</t>
         </is>
       </c>
-      <c r="AM51" s="22" t="n"/>
+      <c r="AN51" s="22" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="15" t="inlineStr">
@@ -7377,23 +7432,24 @@
       <c r="AA52" s="19" t="n"/>
       <c r="AB52" s="19" t="n"/>
       <c r="AC52" s="19" t="n"/>
-      <c r="AD52" s="20" t="n"/>
-      <c r="AE52" s="21">
-        <f>IF(K52="","",K52*AD52)</f>
-        <v/>
-      </c>
-      <c r="AF52" s="19" t="n"/>
+      <c r="AD52" s="19" t="n"/>
+      <c r="AE52" s="20" t="n"/>
+      <c r="AF52" s="21">
+        <f>IF(K52="","",K52*AE52)</f>
+        <v/>
+      </c>
       <c r="AG52" s="19" t="n"/>
       <c r="AH52" s="19" t="n"/>
       <c r="AI52" s="19" t="n"/>
       <c r="AJ52" s="19" t="n"/>
       <c r="AK52" s="19" t="n"/>
-      <c r="AL52" s="16" t="inlineStr">
+      <c r="AL52" s="19" t="n"/>
+      <c r="AM52" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AM52" s="22" t="n"/>
+      <c r="AN52" s="22" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="15" t="inlineStr">
@@ -7495,23 +7551,24 @@
       <c r="AA53" s="19" t="n"/>
       <c r="AB53" s="19" t="n"/>
       <c r="AC53" s="19" t="n"/>
-      <c r="AD53" s="20" t="n"/>
-      <c r="AE53" s="21">
-        <f>IF(K53="","",K53*AD53)</f>
-        <v/>
-      </c>
-      <c r="AF53" s="19" t="n"/>
+      <c r="AD53" s="19" t="n"/>
+      <c r="AE53" s="20" t="n"/>
+      <c r="AF53" s="21">
+        <f>IF(K53="","",K53*AE53)</f>
+        <v/>
+      </c>
       <c r="AG53" s="19" t="n"/>
       <c r="AH53" s="19" t="n"/>
       <c r="AI53" s="19" t="n"/>
       <c r="AJ53" s="19" t="n"/>
       <c r="AK53" s="19" t="n"/>
-      <c r="AL53" s="16" t="inlineStr">
+      <c r="AL53" s="19" t="n"/>
+      <c r="AM53" s="16" t="inlineStr">
         <is>
           <t>ca. 6 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AM53" s="22" t="n"/>
+      <c r="AN53" s="22" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="15" t="inlineStr">
@@ -7613,23 +7670,24 @@
       <c r="AA54" s="19" t="n"/>
       <c r="AB54" s="19" t="n"/>
       <c r="AC54" s="19" t="n"/>
-      <c r="AD54" s="20" t="n"/>
-      <c r="AE54" s="21">
-        <f>IF(K54="","",K54*AD54)</f>
-        <v/>
-      </c>
-      <c r="AF54" s="19" t="n"/>
+      <c r="AD54" s="19" t="n"/>
+      <c r="AE54" s="20" t="n"/>
+      <c r="AF54" s="21">
+        <f>IF(K54="","",K54*AE54)</f>
+        <v/>
+      </c>
       <c r="AG54" s="19" t="n"/>
       <c r="AH54" s="19" t="n"/>
       <c r="AI54" s="19" t="n"/>
       <c r="AJ54" s="19" t="n"/>
       <c r="AK54" s="19" t="n"/>
-      <c r="AL54" s="16" t="inlineStr">
+      <c r="AL54" s="19" t="n"/>
+      <c r="AM54" s="16" t="inlineStr">
         <is>
           <t>ca. 8 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AM54" s="22" t="n"/>
+      <c r="AN54" s="22" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="15" t="inlineStr">
@@ -7731,23 +7789,24 @@
       <c r="AA55" s="19" t="n"/>
       <c r="AB55" s="19" t="n"/>
       <c r="AC55" s="19" t="n"/>
-      <c r="AD55" s="20" t="n"/>
-      <c r="AE55" s="21">
-        <f>IF(K55="","",K55*AD55)</f>
-        <v/>
-      </c>
-      <c r="AF55" s="19" t="n"/>
+      <c r="AD55" s="19" t="n"/>
+      <c r="AE55" s="20" t="n"/>
+      <c r="AF55" s="21">
+        <f>IF(K55="","",K55*AE55)</f>
+        <v/>
+      </c>
       <c r="AG55" s="19" t="n"/>
       <c r="AH55" s="19" t="n"/>
       <c r="AI55" s="19" t="n"/>
       <c r="AJ55" s="19" t="n"/>
       <c r="AK55" s="19" t="n"/>
-      <c r="AL55" s="16" t="inlineStr">
+      <c r="AL55" s="19" t="n"/>
+      <c r="AM55" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM55" s="22" t="n"/>
+      <c r="AN55" s="22" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="15" t="inlineStr">
@@ -7849,23 +7908,24 @@
       <c r="AA56" s="19" t="n"/>
       <c r="AB56" s="19" t="n"/>
       <c r="AC56" s="19" t="n"/>
-      <c r="AD56" s="20" t="n"/>
-      <c r="AE56" s="21">
-        <f>IF(K56="","",K56*AD56)</f>
-        <v/>
-      </c>
-      <c r="AF56" s="19" t="n"/>
+      <c r="AD56" s="19" t="n"/>
+      <c r="AE56" s="20" t="n"/>
+      <c r="AF56" s="21">
+        <f>IF(K56="","",K56*AE56)</f>
+        <v/>
+      </c>
       <c r="AG56" s="19" t="n"/>
       <c r="AH56" s="19" t="n"/>
       <c r="AI56" s="19" t="n"/>
       <c r="AJ56" s="19" t="n"/>
       <c r="AK56" s="19" t="n"/>
-      <c r="AL56" s="16" t="inlineStr">
+      <c r="AL56" s="19" t="n"/>
+      <c r="AM56" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM56" s="22" t="n"/>
+      <c r="AN56" s="22" t="n"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="15" t="inlineStr">
@@ -7967,23 +8027,24 @@
       <c r="AA57" s="19" t="n"/>
       <c r="AB57" s="19" t="n"/>
       <c r="AC57" s="19" t="n"/>
-      <c r="AD57" s="20" t="n"/>
-      <c r="AE57" s="21">
-        <f>IF(K57="","",K57*AD57)</f>
-        <v/>
-      </c>
-      <c r="AF57" s="19" t="n"/>
+      <c r="AD57" s="19" t="n"/>
+      <c r="AE57" s="20" t="n"/>
+      <c r="AF57" s="21">
+        <f>IF(K57="","",K57*AE57)</f>
+        <v/>
+      </c>
       <c r="AG57" s="19" t="n"/>
       <c r="AH57" s="19" t="n"/>
       <c r="AI57" s="19" t="n"/>
       <c r="AJ57" s="19" t="n"/>
       <c r="AK57" s="19" t="n"/>
-      <c r="AL57" s="16" t="inlineStr">
+      <c r="AL57" s="19" t="n"/>
+      <c r="AM57" s="16" t="inlineStr">
         <is>
           <t>1 Schrank im Bild (Bücher nicht enthalten)</t>
         </is>
       </c>
-      <c r="AM57" s="22" t="n"/>
+      <c r="AN57" s="22" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="15" t="inlineStr">
@@ -8085,23 +8146,24 @@
       <c r="AA58" s="19" t="n"/>
       <c r="AB58" s="19" t="n"/>
       <c r="AC58" s="19" t="n"/>
-      <c r="AD58" s="20" t="n"/>
-      <c r="AE58" s="21">
-        <f>IF(K58="","",K58*AD58)</f>
-        <v/>
-      </c>
-      <c r="AF58" s="19" t="n"/>
+      <c r="AD58" s="19" t="n"/>
+      <c r="AE58" s="20" t="n"/>
+      <c r="AF58" s="21">
+        <f>IF(K58="","",K58*AE58)</f>
+        <v/>
+      </c>
       <c r="AG58" s="19" t="n"/>
       <c r="AH58" s="19" t="n"/>
       <c r="AI58" s="19" t="n"/>
       <c r="AJ58" s="19" t="n"/>
       <c r="AK58" s="19" t="n"/>
-      <c r="AL58" s="16" t="inlineStr">
+      <c r="AL58" s="19" t="n"/>
+      <c r="AM58" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM58" s="22" t="n"/>
+      <c r="AN58" s="22" t="n"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="15" t="inlineStr">
@@ -8203,23 +8265,24 @@
       <c r="AA59" s="19" t="n"/>
       <c r="AB59" s="19" t="n"/>
       <c r="AC59" s="19" t="n"/>
-      <c r="AD59" s="20" t="n"/>
-      <c r="AE59" s="21">
-        <f>IF(K59="","",K59*AD59)</f>
-        <v/>
-      </c>
-      <c r="AF59" s="19" t="n"/>
+      <c r="AD59" s="19" t="n"/>
+      <c r="AE59" s="20" t="n"/>
+      <c r="AF59" s="21">
+        <f>IF(K59="","",K59*AE59)</f>
+        <v/>
+      </c>
       <c r="AG59" s="19" t="n"/>
       <c r="AH59" s="19" t="n"/>
       <c r="AI59" s="19" t="n"/>
       <c r="AJ59" s="19" t="n"/>
       <c r="AK59" s="19" t="n"/>
-      <c r="AL59" s="16" t="inlineStr">
+      <c r="AL59" s="19" t="n"/>
+      <c r="AM59" s="16" t="inlineStr">
         <is>
           <t>2 Regale im Bild</t>
         </is>
       </c>
-      <c r="AM59" s="22" t="n"/>
+      <c r="AN59" s="22" t="n"/>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="15" t="inlineStr">
@@ -8321,23 +8384,24 @@
       <c r="AA60" s="19" t="n"/>
       <c r="AB60" s="19" t="n"/>
       <c r="AC60" s="19" t="n"/>
-      <c r="AD60" s="20" t="n"/>
-      <c r="AE60" s="21">
-        <f>IF(K60="","",K60*AD60)</f>
-        <v/>
-      </c>
-      <c r="AF60" s="19" t="n"/>
+      <c r="AD60" s="19" t="n"/>
+      <c r="AE60" s="20" t="n"/>
+      <c r="AF60" s="21">
+        <f>IF(K60="","",K60*AE60)</f>
+        <v/>
+      </c>
       <c r="AG60" s="19" t="n"/>
       <c r="AH60" s="19" t="n"/>
       <c r="AI60" s="19" t="n"/>
       <c r="AJ60" s="19" t="n"/>
       <c r="AK60" s="19" t="n"/>
-      <c r="AL60" s="16" t="inlineStr">
+      <c r="AL60" s="19" t="n"/>
+      <c r="AM60" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM60" s="22" t="n"/>
+      <c r="AN60" s="22" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="15" t="inlineStr">
@@ -8439,23 +8503,24 @@
       <c r="AA61" s="19" t="n"/>
       <c r="AB61" s="19" t="n"/>
       <c r="AC61" s="19" t="n"/>
-      <c r="AD61" s="20" t="n"/>
-      <c r="AE61" s="21">
-        <f>IF(K61="","",K61*AD61)</f>
-        <v/>
-      </c>
-      <c r="AF61" s="19" t="n"/>
+      <c r="AD61" s="19" t="n"/>
+      <c r="AE61" s="20" t="n"/>
+      <c r="AF61" s="21">
+        <f>IF(K61="","",K61*AE61)</f>
+        <v/>
+      </c>
       <c r="AG61" s="19" t="n"/>
       <c r="AH61" s="19" t="n"/>
       <c r="AI61" s="19" t="n"/>
       <c r="AJ61" s="19" t="n"/>
       <c r="AK61" s="19" t="n"/>
-      <c r="AL61" s="16" t="inlineStr">
+      <c r="AL61" s="19" t="n"/>
+      <c r="AM61" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM61" s="22" t="n"/>
+      <c r="AN61" s="22" t="n"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="15" t="inlineStr">
@@ -8557,23 +8622,24 @@
       <c r="AA62" s="19" t="n"/>
       <c r="AB62" s="19" t="n"/>
       <c r="AC62" s="19" t="n"/>
-      <c r="AD62" s="20" t="n"/>
-      <c r="AE62" s="21">
-        <f>IF(K62="","",K62*AD62)</f>
-        <v/>
-      </c>
-      <c r="AF62" s="19" t="n"/>
+      <c r="AD62" s="19" t="n"/>
+      <c r="AE62" s="20" t="n"/>
+      <c r="AF62" s="21">
+        <f>IF(K62="","",K62*AE62)</f>
+        <v/>
+      </c>
       <c r="AG62" s="19" t="n"/>
       <c r="AH62" s="19" t="n"/>
       <c r="AI62" s="19" t="n"/>
       <c r="AJ62" s="19" t="n"/>
       <c r="AK62" s="19" t="n"/>
-      <c r="AL62" s="16" t="inlineStr">
+      <c r="AL62" s="19" t="n"/>
+      <c r="AM62" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM62" s="22" t="n"/>
+      <c r="AN62" s="22" t="n"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="15" t="inlineStr">
@@ -8675,23 +8741,24 @@
       <c r="AA63" s="19" t="n"/>
       <c r="AB63" s="19" t="n"/>
       <c r="AC63" s="19" t="n"/>
-      <c r="AD63" s="20" t="n"/>
-      <c r="AE63" s="21">
-        <f>IF(K63="","",K63*AD63)</f>
-        <v/>
-      </c>
-      <c r="AF63" s="19" t="n"/>
+      <c r="AD63" s="19" t="n"/>
+      <c r="AE63" s="20" t="n"/>
+      <c r="AF63" s="21">
+        <f>IF(K63="","",K63*AE63)</f>
+        <v/>
+      </c>
       <c r="AG63" s="19" t="n"/>
       <c r="AH63" s="19" t="n"/>
       <c r="AI63" s="19" t="n"/>
       <c r="AJ63" s="19" t="n"/>
       <c r="AK63" s="19" t="n"/>
-      <c r="AL63" s="16" t="inlineStr">
+      <c r="AL63" s="19" t="n"/>
+      <c r="AM63" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM63" s="22" t="n"/>
+      <c r="AN63" s="22" t="n"/>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="15" t="inlineStr">
@@ -8793,23 +8860,24 @@
       <c r="AA64" s="19" t="n"/>
       <c r="AB64" s="19" t="n"/>
       <c r="AC64" s="19" t="n"/>
-      <c r="AD64" s="20" t="n"/>
-      <c r="AE64" s="21">
-        <f>IF(K64="","",K64*AD64)</f>
-        <v/>
-      </c>
-      <c r="AF64" s="19" t="n"/>
+      <c r="AD64" s="19" t="n"/>
+      <c r="AE64" s="20" t="n"/>
+      <c r="AF64" s="21">
+        <f>IF(K64="","",K64*AE64)</f>
+        <v/>
+      </c>
       <c r="AG64" s="19" t="n"/>
       <c r="AH64" s="19" t="n"/>
       <c r="AI64" s="19" t="n"/>
       <c r="AJ64" s="19" t="n"/>
       <c r="AK64" s="19" t="n"/>
-      <c r="AL64" s="16" t="inlineStr">
+      <c r="AL64" s="19" t="n"/>
+      <c r="AM64" s="16" t="inlineStr">
         <is>
           <t>ca. 8 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AM64" s="22" t="n"/>
+      <c r="AN64" s="22" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
@@ -8911,23 +8979,24 @@
       <c r="AA65" s="19" t="n"/>
       <c r="AB65" s="19" t="n"/>
       <c r="AC65" s="19" t="n"/>
-      <c r="AD65" s="20" t="n"/>
-      <c r="AE65" s="21">
-        <f>IF(K65="","",K65*AD65)</f>
-        <v/>
-      </c>
-      <c r="AF65" s="19" t="n"/>
+      <c r="AD65" s="19" t="n"/>
+      <c r="AE65" s="20" t="n"/>
+      <c r="AF65" s="21">
+        <f>IF(K65="","",K65*AE65)</f>
+        <v/>
+      </c>
       <c r="AG65" s="19" t="n"/>
       <c r="AH65" s="19" t="n"/>
       <c r="AI65" s="19" t="n"/>
       <c r="AJ65" s="19" t="n"/>
       <c r="AK65" s="19" t="n"/>
-      <c r="AL65" s="16" t="inlineStr">
+      <c r="AL65" s="19" t="n"/>
+      <c r="AM65" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM65" s="22" t="n"/>
+      <c r="AN65" s="22" t="n"/>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="15" t="inlineStr">
@@ -9029,23 +9098,24 @@
       <c r="AA66" s="19" t="n"/>
       <c r="AB66" s="19" t="n"/>
       <c r="AC66" s="19" t="n"/>
-      <c r="AD66" s="20" t="n"/>
-      <c r="AE66" s="21">
-        <f>IF(K66="","",K66*AD66)</f>
-        <v/>
-      </c>
-      <c r="AF66" s="19" t="n"/>
+      <c r="AD66" s="19" t="n"/>
+      <c r="AE66" s="20" t="n"/>
+      <c r="AF66" s="21">
+        <f>IF(K66="","",K66*AE66)</f>
+        <v/>
+      </c>
       <c r="AG66" s="19" t="n"/>
       <c r="AH66" s="19" t="n"/>
       <c r="AI66" s="19" t="n"/>
       <c r="AJ66" s="19" t="n"/>
       <c r="AK66" s="19" t="n"/>
-      <c r="AL66" s="16" t="inlineStr">
+      <c r="AL66" s="19" t="n"/>
+      <c r="AM66" s="16" t="inlineStr">
         <is>
           <t>2 Schränke im Bild</t>
         </is>
       </c>
-      <c r="AM66" s="22" t="n"/>
+      <c r="AN66" s="22" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="15" t="inlineStr">
@@ -9147,23 +9217,24 @@
       <c r="AA67" s="19" t="n"/>
       <c r="AB67" s="19" t="n"/>
       <c r="AC67" s="19" t="n"/>
-      <c r="AD67" s="20" t="n"/>
-      <c r="AE67" s="21">
-        <f>IF(K67="","",K67*AD67)</f>
-        <v/>
-      </c>
-      <c r="AF67" s="19" t="n"/>
+      <c r="AD67" s="19" t="n"/>
+      <c r="AE67" s="20" t="n"/>
+      <c r="AF67" s="21">
+        <f>IF(K67="","",K67*AE67)</f>
+        <v/>
+      </c>
       <c r="AG67" s="19" t="n"/>
       <c r="AH67" s="19" t="n"/>
       <c r="AI67" s="19" t="n"/>
       <c r="AJ67" s="19" t="n"/>
       <c r="AK67" s="19" t="n"/>
-      <c r="AL67" s="16" t="inlineStr">
+      <c r="AL67" s="19" t="n"/>
+      <c r="AM67" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM67" s="22" t="n"/>
+      <c r="AN67" s="22" t="n"/>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="15" t="inlineStr">
@@ -9265,23 +9336,24 @@
       <c r="AA68" s="19" t="n"/>
       <c r="AB68" s="19" t="n"/>
       <c r="AC68" s="19" t="n"/>
-      <c r="AD68" s="20" t="n"/>
-      <c r="AE68" s="21">
-        <f>IF(K68="","",K68*AD68)</f>
-        <v/>
-      </c>
-      <c r="AF68" s="19" t="n"/>
+      <c r="AD68" s="19" t="n"/>
+      <c r="AE68" s="20" t="n"/>
+      <c r="AF68" s="21">
+        <f>IF(K68="","",K68*AE68)</f>
+        <v/>
+      </c>
       <c r="AG68" s="19" t="n"/>
       <c r="AH68" s="19" t="n"/>
       <c r="AI68" s="19" t="n"/>
       <c r="AJ68" s="19" t="n"/>
       <c r="AK68" s="19" t="n"/>
-      <c r="AL68" s="16" t="inlineStr">
+      <c r="AL68" s="19" t="n"/>
+      <c r="AM68" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM68" s="22" t="n"/>
+      <c r="AN68" s="22" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="15" t="inlineStr">
@@ -9383,23 +9455,24 @@
       <c r="AA69" s="19" t="n"/>
       <c r="AB69" s="19" t="n"/>
       <c r="AC69" s="19" t="n"/>
-      <c r="AD69" s="20" t="n"/>
-      <c r="AE69" s="21">
-        <f>IF(K69="","",K69*AD69)</f>
-        <v/>
-      </c>
-      <c r="AF69" s="19" t="n"/>
+      <c r="AD69" s="19" t="n"/>
+      <c r="AE69" s="20" t="n"/>
+      <c r="AF69" s="21">
+        <f>IF(K69="","",K69*AE69)</f>
+        <v/>
+      </c>
       <c r="AG69" s="19" t="n"/>
       <c r="AH69" s="19" t="n"/>
       <c r="AI69" s="19" t="n"/>
       <c r="AJ69" s="19" t="n"/>
       <c r="AK69" s="19" t="n"/>
-      <c r="AL69" s="16" t="inlineStr">
+      <c r="AL69" s="19" t="n"/>
+      <c r="AM69" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM69" s="22" t="n"/>
+      <c r="AN69" s="22" t="n"/>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="15" t="inlineStr">
@@ -9501,23 +9574,24 @@
       <c r="AA70" s="19" t="n"/>
       <c r="AB70" s="19" t="n"/>
       <c r="AC70" s="19" t="n"/>
-      <c r="AD70" s="20" t="n"/>
-      <c r="AE70" s="21">
-        <f>IF(K70="","",K70*AD70)</f>
-        <v/>
-      </c>
-      <c r="AF70" s="19" t="n"/>
+      <c r="AD70" s="19" t="n"/>
+      <c r="AE70" s="20" t="n"/>
+      <c r="AF70" s="21">
+        <f>IF(K70="","",K70*AE70)</f>
+        <v/>
+      </c>
       <c r="AG70" s="19" t="n"/>
       <c r="AH70" s="19" t="n"/>
       <c r="AI70" s="19" t="n"/>
       <c r="AJ70" s="19" t="n"/>
       <c r="AK70" s="19" t="n"/>
-      <c r="AL70" s="16" t="inlineStr">
+      <c r="AL70" s="19" t="n"/>
+      <c r="AM70" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM70" s="22" t="n"/>
+      <c r="AN70" s="22" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="15" t="inlineStr">
@@ -9619,23 +9693,24 @@
       <c r="AA71" s="19" t="n"/>
       <c r="AB71" s="19" t="n"/>
       <c r="AC71" s="19" t="n"/>
-      <c r="AD71" s="20" t="n"/>
-      <c r="AE71" s="21">
-        <f>IF(K71="","",K71*AD71)</f>
-        <v/>
-      </c>
-      <c r="AF71" s="19" t="n"/>
+      <c r="AD71" s="19" t="n"/>
+      <c r="AE71" s="20" t="n"/>
+      <c r="AF71" s="21">
+        <f>IF(K71="","",K71*AE71)</f>
+        <v/>
+      </c>
       <c r="AG71" s="19" t="n"/>
       <c r="AH71" s="19" t="n"/>
       <c r="AI71" s="19" t="n"/>
       <c r="AJ71" s="19" t="n"/>
       <c r="AK71" s="19" t="n"/>
-      <c r="AL71" s="16" t="inlineStr">
+      <c r="AL71" s="19" t="n"/>
+      <c r="AM71" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild (ohne Treibholz)</t>
         </is>
       </c>
-      <c r="AM71" s="22" t="n"/>
+      <c r="AN71" s="22" t="n"/>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="15" t="inlineStr">
@@ -9737,23 +9812,24 @@
       <c r="AA72" s="19" t="n"/>
       <c r="AB72" s="19" t="n"/>
       <c r="AC72" s="19" t="n"/>
-      <c r="AD72" s="20" t="n"/>
-      <c r="AE72" s="21">
-        <f>IF(K72="","",K72*AD72)</f>
-        <v/>
-      </c>
-      <c r="AF72" s="19" t="n"/>
+      <c r="AD72" s="19" t="n"/>
+      <c r="AE72" s="20" t="n"/>
+      <c r="AF72" s="21">
+        <f>IF(K72="","",K72*AE72)</f>
+        <v/>
+      </c>
       <c r="AG72" s="19" t="n"/>
       <c r="AH72" s="19" t="n"/>
       <c r="AI72" s="19" t="n"/>
       <c r="AJ72" s="19" t="n"/>
       <c r="AK72" s="19" t="n"/>
-      <c r="AL72" s="16" t="inlineStr">
+      <c r="AL72" s="19" t="n"/>
+      <c r="AM72" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM72" s="22" t="n"/>
+      <c r="AN72" s="22" t="n"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="15" t="inlineStr">
@@ -9855,23 +9931,24 @@
       <c r="AA73" s="19" t="n"/>
       <c r="AB73" s="19" t="n"/>
       <c r="AC73" s="19" t="n"/>
-      <c r="AD73" s="20" t="n"/>
-      <c r="AE73" s="21">
-        <f>IF(K73="","",K73*AD73)</f>
-        <v/>
-      </c>
-      <c r="AF73" s="19" t="n"/>
+      <c r="AD73" s="19" t="n"/>
+      <c r="AE73" s="20" t="n"/>
+      <c r="AF73" s="21">
+        <f>IF(K73="","",K73*AE73)</f>
+        <v/>
+      </c>
       <c r="AG73" s="19" t="n"/>
       <c r="AH73" s="19" t="n"/>
       <c r="AI73" s="19" t="n"/>
       <c r="AJ73" s="19" t="n"/>
       <c r="AK73" s="19" t="n"/>
-      <c r="AL73" s="16" t="inlineStr">
+      <c r="AL73" s="19" t="n"/>
+      <c r="AM73" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM73" s="22" t="n"/>
+      <c r="AN73" s="22" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="15" t="inlineStr">
@@ -9973,23 +10050,24 @@
       <c r="AA74" s="19" t="n"/>
       <c r="AB74" s="19" t="n"/>
       <c r="AC74" s="19" t="n"/>
-      <c r="AD74" s="20" t="n"/>
-      <c r="AE74" s="21">
-        <f>IF(K74="","",K74*AD74)</f>
-        <v/>
-      </c>
-      <c r="AF74" s="19" t="n"/>
+      <c r="AD74" s="19" t="n"/>
+      <c r="AE74" s="20" t="n"/>
+      <c r="AF74" s="21">
+        <f>IF(K74="","",K74*AE74)</f>
+        <v/>
+      </c>
       <c r="AG74" s="19" t="n"/>
       <c r="AH74" s="19" t="n"/>
       <c r="AI74" s="19" t="n"/>
       <c r="AJ74" s="19" t="n"/>
       <c r="AK74" s="19" t="n"/>
-      <c r="AL74" s="16" t="inlineStr">
+      <c r="AL74" s="19" t="n"/>
+      <c r="AM74" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM74" s="22" t="n"/>
+      <c r="AN74" s="22" t="n"/>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="15" t="inlineStr">
@@ -10091,23 +10169,24 @@
       <c r="AA75" s="19" t="n"/>
       <c r="AB75" s="19" t="n"/>
       <c r="AC75" s="19" t="n"/>
-      <c r="AD75" s="20" t="n"/>
-      <c r="AE75" s="21">
-        <f>IF(K75="","",K75*AD75)</f>
-        <v/>
-      </c>
-      <c r="AF75" s="19" t="n"/>
+      <c r="AD75" s="19" t="n"/>
+      <c r="AE75" s="20" t="n"/>
+      <c r="AF75" s="21">
+        <f>IF(K75="","",K75*AE75)</f>
+        <v/>
+      </c>
       <c r="AG75" s="19" t="n"/>
       <c r="AH75" s="19" t="n"/>
       <c r="AI75" s="19" t="n"/>
       <c r="AJ75" s="19" t="n"/>
       <c r="AK75" s="19" t="n"/>
-      <c r="AL75" s="16" t="inlineStr">
+      <c r="AL75" s="19" t="n"/>
+      <c r="AM75" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM75" s="22" t="n"/>
+      <c r="AN75" s="22" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="15" t="inlineStr">
@@ -10209,23 +10288,24 @@
       <c r="AA76" s="19" t="n"/>
       <c r="AB76" s="19" t="n"/>
       <c r="AC76" s="19" t="n"/>
-      <c r="AD76" s="20" t="n"/>
-      <c r="AE76" s="21">
-        <f>IF(K76="","",K76*AD76)</f>
-        <v/>
-      </c>
-      <c r="AF76" s="19" t="n"/>
+      <c r="AD76" s="19" t="n"/>
+      <c r="AE76" s="20" t="n"/>
+      <c r="AF76" s="21">
+        <f>IF(K76="","",K76*AE76)</f>
+        <v/>
+      </c>
       <c r="AG76" s="19" t="n"/>
       <c r="AH76" s="19" t="n"/>
       <c r="AI76" s="19" t="n"/>
       <c r="AJ76" s="19" t="n"/>
       <c r="AK76" s="19" t="n"/>
-      <c r="AL76" s="16" t="inlineStr">
+      <c r="AL76" s="19" t="n"/>
+      <c r="AM76" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AM76" s="22" t="n"/>
+      <c r="AN76" s="22" t="n"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="15" t="inlineStr">
@@ -10327,23 +10407,24 @@
       <c r="AA77" s="19" t="n"/>
       <c r="AB77" s="19" t="n"/>
       <c r="AC77" s="19" t="n"/>
-      <c r="AD77" s="20" t="n"/>
-      <c r="AE77" s="21">
-        <f>IF(K77="","",K77*AD77)</f>
-        <v/>
-      </c>
-      <c r="AF77" s="19" t="n"/>
+      <c r="AD77" s="19" t="n"/>
+      <c r="AE77" s="20" t="n"/>
+      <c r="AF77" s="21">
+        <f>IF(K77="","",K77*AE77)</f>
+        <v/>
+      </c>
       <c r="AG77" s="19" t="n"/>
       <c r="AH77" s="19" t="n"/>
       <c r="AI77" s="19" t="n"/>
       <c r="AJ77" s="19" t="n"/>
       <c r="AK77" s="19" t="n"/>
-      <c r="AL77" s="16" t="inlineStr">
+      <c r="AL77" s="19" t="n"/>
+      <c r="AM77" s="16" t="inlineStr">
         <is>
           <t>1 Leuchte im Bild</t>
         </is>
       </c>
-      <c r="AM77" s="22" t="n"/>
+      <c r="AN77" s="22" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="15" t="inlineStr">
@@ -10445,23 +10526,24 @@
       <c r="AA78" s="19" t="n"/>
       <c r="AB78" s="19" t="n"/>
       <c r="AC78" s="19" t="n"/>
-      <c r="AD78" s="20" t="n"/>
-      <c r="AE78" s="21">
-        <f>IF(K78="","",K78*AD78)</f>
-        <v/>
-      </c>
-      <c r="AF78" s="19" t="n"/>
+      <c r="AD78" s="19" t="n"/>
+      <c r="AE78" s="20" t="n"/>
+      <c r="AF78" s="21">
+        <f>IF(K78="","",K78*AE78)</f>
+        <v/>
+      </c>
       <c r="AG78" s="19" t="n"/>
       <c r="AH78" s="19" t="n"/>
       <c r="AI78" s="19" t="n"/>
       <c r="AJ78" s="19" t="n"/>
       <c r="AK78" s="19" t="n"/>
-      <c r="AL78" s="16" t="inlineStr">
+      <c r="AL78" s="19" t="n"/>
+      <c r="AM78" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM78" s="22" t="n"/>
+      <c r="AN78" s="22" t="n"/>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="15" t="inlineStr">
@@ -10563,23 +10645,24 @@
       <c r="AA79" s="19" t="n"/>
       <c r="AB79" s="19" t="n"/>
       <c r="AC79" s="19" t="n"/>
-      <c r="AD79" s="20" t="n"/>
-      <c r="AE79" s="21">
-        <f>IF(K79="","",K79*AD79)</f>
-        <v/>
-      </c>
-      <c r="AF79" s="19" t="n"/>
+      <c r="AD79" s="19" t="n"/>
+      <c r="AE79" s="20" t="n"/>
+      <c r="AF79" s="21">
+        <f>IF(K79="","",K79*AE79)</f>
+        <v/>
+      </c>
       <c r="AG79" s="19" t="n"/>
       <c r="AH79" s="19" t="n"/>
       <c r="AI79" s="19" t="n"/>
       <c r="AJ79" s="19" t="n"/>
       <c r="AK79" s="19" t="n"/>
-      <c r="AL79" s="16" t="inlineStr">
+      <c r="AL79" s="19" t="n"/>
+      <c r="AM79" s="16" t="inlineStr">
         <is>
           <t>1 Sessel im Bild</t>
         </is>
       </c>
-      <c r="AM79" s="22" t="n"/>
+      <c r="AN79" s="22" t="n"/>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
@@ -10681,23 +10764,24 @@
       <c r="AA80" s="19" t="n"/>
       <c r="AB80" s="19" t="n"/>
       <c r="AC80" s="19" t="n"/>
-      <c r="AD80" s="20" t="n"/>
-      <c r="AE80" s="21">
-        <f>IF(K80="","",K80*AD80)</f>
-        <v/>
-      </c>
-      <c r="AF80" s="19" t="n"/>
+      <c r="AD80" s="19" t="n"/>
+      <c r="AE80" s="20" t="n"/>
+      <c r="AF80" s="21">
+        <f>IF(K80="","",K80*AE80)</f>
+        <v/>
+      </c>
       <c r="AG80" s="19" t="n"/>
       <c r="AH80" s="19" t="n"/>
       <c r="AI80" s="19" t="n"/>
       <c r="AJ80" s="19" t="n"/>
       <c r="AK80" s="19" t="n"/>
-      <c r="AL80" s="16" t="inlineStr">
+      <c r="AL80" s="19" t="n"/>
+      <c r="AM80" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM80" s="22" t="n"/>
+      <c r="AN80" s="22" t="n"/>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
@@ -10799,23 +10883,24 @@
       <c r="AA81" s="19" t="n"/>
       <c r="AB81" s="19" t="n"/>
       <c r="AC81" s="19" t="n"/>
-      <c r="AD81" s="20" t="n"/>
-      <c r="AE81" s="21">
-        <f>IF(K81="","",K81*AD81)</f>
-        <v/>
-      </c>
-      <c r="AF81" s="19" t="n"/>
+      <c r="AD81" s="19" t="n"/>
+      <c r="AE81" s="20" t="n"/>
+      <c r="AF81" s="21">
+        <f>IF(K81="","",K81*AE81)</f>
+        <v/>
+      </c>
       <c r="AG81" s="19" t="n"/>
       <c r="AH81" s="19" t="n"/>
       <c r="AI81" s="19" t="n"/>
       <c r="AJ81" s="19" t="n"/>
       <c r="AK81" s="19" t="n"/>
-      <c r="AL81" s="16" t="inlineStr">
+      <c r="AL81" s="19" t="n"/>
+      <c r="AM81" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM81" s="22" t="n"/>
+      <c r="AN81" s="22" t="n"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
@@ -10917,23 +11002,24 @@
       <c r="AA82" s="19" t="n"/>
       <c r="AB82" s="19" t="n"/>
       <c r="AC82" s="19" t="n"/>
-      <c r="AD82" s="20" t="n"/>
-      <c r="AE82" s="21">
-        <f>IF(K82="","",K82*AD82)</f>
-        <v/>
-      </c>
-      <c r="AF82" s="19" t="n"/>
+      <c r="AD82" s="19" t="n"/>
+      <c r="AE82" s="20" t="n"/>
+      <c r="AF82" s="21">
+        <f>IF(K82="","",K82*AE82)</f>
+        <v/>
+      </c>
       <c r="AG82" s="19" t="n"/>
       <c r="AH82" s="19" t="n"/>
       <c r="AI82" s="19" t="n"/>
       <c r="AJ82" s="19" t="n"/>
       <c r="AK82" s="19" t="n"/>
-      <c r="AL82" s="16" t="inlineStr">
+      <c r="AL82" s="19" t="n"/>
+      <c r="AM82" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM82" s="22" t="n"/>
+      <c r="AN82" s="22" t="n"/>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="15" t="inlineStr">
@@ -11035,23 +11121,24 @@
       <c r="AA83" s="19" t="n"/>
       <c r="AB83" s="19" t="n"/>
       <c r="AC83" s="19" t="n"/>
-      <c r="AD83" s="20" t="n"/>
-      <c r="AE83" s="21">
-        <f>IF(K83="","",K83*AD83)</f>
-        <v/>
-      </c>
-      <c r="AF83" s="19" t="n"/>
+      <c r="AD83" s="19" t="n"/>
+      <c r="AE83" s="20" t="n"/>
+      <c r="AF83" s="21">
+        <f>IF(K83="","",K83*AE83)</f>
+        <v/>
+      </c>
       <c r="AG83" s="19" t="n"/>
       <c r="AH83" s="19" t="n"/>
       <c r="AI83" s="19" t="n"/>
       <c r="AJ83" s="19" t="n"/>
       <c r="AK83" s="19" t="n"/>
-      <c r="AL83" s="16" t="inlineStr">
+      <c r="AL83" s="19" t="n"/>
+      <c r="AM83" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM83" s="22" t="n"/>
+      <c r="AN83" s="22" t="n"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="15" t="inlineStr">
@@ -11153,23 +11240,24 @@
       <c r="AA84" s="19" t="n"/>
       <c r="AB84" s="19" t="n"/>
       <c r="AC84" s="19" t="n"/>
-      <c r="AD84" s="20" t="n"/>
-      <c r="AE84" s="21">
-        <f>IF(K84="","",K84*AD84)</f>
-        <v/>
-      </c>
-      <c r="AF84" s="19" t="n"/>
+      <c r="AD84" s="19" t="n"/>
+      <c r="AE84" s="20" t="n"/>
+      <c r="AF84" s="21">
+        <f>IF(K84="","",K84*AE84)</f>
+        <v/>
+      </c>
       <c r="AG84" s="19" t="n"/>
       <c r="AH84" s="19" t="n"/>
       <c r="AI84" s="19" t="n"/>
       <c r="AJ84" s="19" t="n"/>
       <c r="AK84" s="19" t="n"/>
-      <c r="AL84" s="16" t="inlineStr">
+      <c r="AL84" s="19" t="n"/>
+      <c r="AM84" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM84" s="22" t="n"/>
+      <c r="AN84" s="22" t="n"/>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="15" t="inlineStr">
@@ -11271,23 +11359,24 @@
       <c r="AA85" s="19" t="n"/>
       <c r="AB85" s="19" t="n"/>
       <c r="AC85" s="19" t="n"/>
-      <c r="AD85" s="20" t="n"/>
-      <c r="AE85" s="21">
-        <f>IF(K85="","",K85*AD85)</f>
-        <v/>
-      </c>
-      <c r="AF85" s="19" t="n"/>
+      <c r="AD85" s="19" t="n"/>
+      <c r="AE85" s="20" t="n"/>
+      <c r="AF85" s="21">
+        <f>IF(K85="","",K85*AE85)</f>
+        <v/>
+      </c>
       <c r="AG85" s="19" t="n"/>
       <c r="AH85" s="19" t="n"/>
       <c r="AI85" s="19" t="n"/>
       <c r="AJ85" s="19" t="n"/>
       <c r="AK85" s="19" t="n"/>
-      <c r="AL85" s="16" t="inlineStr">
+      <c r="AL85" s="19" t="n"/>
+      <c r="AM85" s="16" t="inlineStr">
         <is>
           <t>1 Stuhl im Bild - vermutlich mehrere vorhanden</t>
         </is>
       </c>
-      <c r="AM85" s="22" t="n"/>
+      <c r="AN85" s="22" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="15" t="inlineStr">
@@ -11389,23 +11478,24 @@
       <c r="AA86" s="19" t="n"/>
       <c r="AB86" s="19" t="n"/>
       <c r="AC86" s="19" t="n"/>
-      <c r="AD86" s="20" t="n"/>
-      <c r="AE86" s="21">
-        <f>IF(K86="","",K86*AD86)</f>
-        <v/>
-      </c>
-      <c r="AF86" s="19" t="n"/>
+      <c r="AD86" s="19" t="n"/>
+      <c r="AE86" s="20" t="n"/>
+      <c r="AF86" s="21">
+        <f>IF(K86="","",K86*AE86)</f>
+        <v/>
+      </c>
       <c r="AG86" s="19" t="n"/>
       <c r="AH86" s="19" t="n"/>
       <c r="AI86" s="19" t="n"/>
       <c r="AJ86" s="19" t="n"/>
       <c r="AK86" s="19" t="n"/>
-      <c r="AL86" s="16" t="inlineStr">
+      <c r="AL86" s="19" t="n"/>
+      <c r="AM86" s="16" t="inlineStr">
         <is>
           <t>1 Box im Bild - bitte prüfen ob 2 oder 3 Boxen gesamt</t>
         </is>
       </c>
-      <c r="AM86" s="22" t="n"/>
+      <c r="AN86" s="22" t="n"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="15" t="inlineStr">
@@ -11507,23 +11597,24 @@
       <c r="AA87" s="19" t="n"/>
       <c r="AB87" s="19" t="n"/>
       <c r="AC87" s="19" t="n"/>
-      <c r="AD87" s="20" t="n"/>
-      <c r="AE87" s="21">
-        <f>IF(K87="","",K87*AD87)</f>
-        <v/>
-      </c>
-      <c r="AF87" s="19" t="n"/>
+      <c r="AD87" s="19" t="n"/>
+      <c r="AE87" s="20" t="n"/>
+      <c r="AF87" s="21">
+        <f>IF(K87="","",K87*AE87)</f>
+        <v/>
+      </c>
       <c r="AG87" s="19" t="n"/>
       <c r="AH87" s="19" t="n"/>
       <c r="AI87" s="19" t="n"/>
       <c r="AJ87" s="19" t="n"/>
       <c r="AK87" s="19" t="n"/>
-      <c r="AL87" s="16" t="inlineStr">
+      <c r="AL87" s="19" t="n"/>
+      <c r="AM87" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM87" s="22" t="n"/>
+      <c r="AN87" s="22" t="n"/>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="15" t="inlineStr">
@@ -11625,23 +11716,24 @@
       <c r="AA88" s="19" t="n"/>
       <c r="AB88" s="19" t="n"/>
       <c r="AC88" s="19" t="n"/>
-      <c r="AD88" s="20" t="n"/>
-      <c r="AE88" s="21">
-        <f>IF(K88="","",K88*AD88)</f>
-        <v/>
-      </c>
-      <c r="AF88" s="19" t="n"/>
+      <c r="AD88" s="19" t="n"/>
+      <c r="AE88" s="20" t="n"/>
+      <c r="AF88" s="21">
+        <f>IF(K88="","",K88*AE88)</f>
+        <v/>
+      </c>
       <c r="AG88" s="19" t="n"/>
       <c r="AH88" s="19" t="n"/>
       <c r="AI88" s="19" t="n"/>
       <c r="AJ88" s="19" t="n"/>
       <c r="AK88" s="19" t="n"/>
-      <c r="AL88" s="16" t="inlineStr">
+      <c r="AL88" s="19" t="n"/>
+      <c r="AM88" s="16" t="inlineStr">
         <is>
           <t>1 Box im Bild</t>
         </is>
       </c>
-      <c r="AM88" s="22" t="n"/>
+      <c r="AN88" s="22" t="n"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="15" t="inlineStr">
@@ -11743,23 +11835,24 @@
       <c r="AA89" s="19" t="n"/>
       <c r="AB89" s="19" t="n"/>
       <c r="AC89" s="19" t="n"/>
-      <c r="AD89" s="20" t="n"/>
-      <c r="AE89" s="21">
-        <f>IF(K89="","",K89*AD89)</f>
-        <v/>
-      </c>
-      <c r="AF89" s="19" t="n"/>
+      <c r="AD89" s="19" t="n"/>
+      <c r="AE89" s="20" t="n"/>
+      <c r="AF89" s="21">
+        <f>IF(K89="","",K89*AE89)</f>
+        <v/>
+      </c>
       <c r="AG89" s="19" t="n"/>
       <c r="AH89" s="19" t="n"/>
       <c r="AI89" s="19" t="n"/>
       <c r="AJ89" s="19" t="n"/>
       <c r="AK89" s="19" t="n"/>
-      <c r="AL89" s="16" t="inlineStr">
+      <c r="AL89" s="19" t="n"/>
+      <c r="AM89" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM89" s="22" t="n"/>
+      <c r="AN89" s="22" t="n"/>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="15" t="inlineStr">
@@ -11861,23 +11954,24 @@
       <c r="AA90" s="19" t="n"/>
       <c r="AB90" s="19" t="n"/>
       <c r="AC90" s="19" t="n"/>
-      <c r="AD90" s="20" t="n"/>
-      <c r="AE90" s="21">
-        <f>IF(K90="","",K90*AD90)</f>
-        <v/>
-      </c>
-      <c r="AF90" s="19" t="n"/>
+      <c r="AD90" s="19" t="n"/>
+      <c r="AE90" s="20" t="n"/>
+      <c r="AF90" s="21">
+        <f>IF(K90="","",K90*AE90)</f>
+        <v/>
+      </c>
       <c r="AG90" s="19" t="n"/>
       <c r="AH90" s="19" t="n"/>
       <c r="AI90" s="19" t="n"/>
       <c r="AJ90" s="19" t="n"/>
       <c r="AK90" s="19" t="n"/>
-      <c r="AL90" s="16" t="inlineStr">
+      <c r="AL90" s="19" t="n"/>
+      <c r="AM90" s="16" t="inlineStr">
         <is>
           <t>4 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM90" s="22" t="n"/>
+      <c r="AN90" s="22" t="n"/>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="15" t="inlineStr">
@@ -11979,23 +12073,24 @@
       <c r="AA91" s="19" t="n"/>
       <c r="AB91" s="19" t="n"/>
       <c r="AC91" s="19" t="n"/>
-      <c r="AD91" s="20" t="n"/>
-      <c r="AE91" s="21">
-        <f>IF(K91="","",K91*AD91)</f>
-        <v/>
-      </c>
-      <c r="AF91" s="19" t="n"/>
+      <c r="AD91" s="19" t="n"/>
+      <c r="AE91" s="20" t="n"/>
+      <c r="AF91" s="21">
+        <f>IF(K91="","",K91*AE91)</f>
+        <v/>
+      </c>
       <c r="AG91" s="19" t="n"/>
       <c r="AH91" s="19" t="n"/>
       <c r="AI91" s="19" t="n"/>
       <c r="AJ91" s="19" t="n"/>
       <c r="AK91" s="19" t="n"/>
-      <c r="AL91" s="16" t="inlineStr">
+      <c r="AL91" s="19" t="n"/>
+      <c r="AM91" s="16" t="inlineStr">
         <is>
           <t>2 Stück gestapelt im Bild</t>
         </is>
       </c>
-      <c r="AM91" s="22" t="n"/>
+      <c r="AN91" s="22" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="15" t="inlineStr">
@@ -12097,23 +12192,24 @@
       <c r="AA92" s="19" t="n"/>
       <c r="AB92" s="19" t="n"/>
       <c r="AC92" s="19" t="n"/>
-      <c r="AD92" s="20" t="n"/>
-      <c r="AE92" s="21">
-        <f>IF(K92="","",K92*AD92)</f>
-        <v/>
-      </c>
-      <c r="AF92" s="19" t="n"/>
+      <c r="AD92" s="19" t="n"/>
+      <c r="AE92" s="20" t="n"/>
+      <c r="AF92" s="21">
+        <f>IF(K92="","",K92*AE92)</f>
+        <v/>
+      </c>
       <c r="AG92" s="19" t="n"/>
       <c r="AH92" s="19" t="n"/>
       <c r="AI92" s="19" t="n"/>
       <c r="AJ92" s="19" t="n"/>
       <c r="AK92" s="19" t="n"/>
-      <c r="AL92" s="16" t="inlineStr">
+      <c r="AL92" s="19" t="n"/>
+      <c r="AM92" s="16" t="inlineStr">
         <is>
           <t>1 Sessel im Bild</t>
         </is>
       </c>
-      <c r="AM92" s="22" t="n"/>
+      <c r="AN92" s="22" t="n"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="15" t="inlineStr">
@@ -12215,23 +12311,24 @@
       <c r="AA93" s="19" t="n"/>
       <c r="AB93" s="19" t="n"/>
       <c r="AC93" s="19" t="n"/>
-      <c r="AD93" s="20" t="n"/>
-      <c r="AE93" s="21">
-        <f>IF(K93="","",K93*AD93)</f>
-        <v/>
-      </c>
-      <c r="AF93" s="19" t="n"/>
+      <c r="AD93" s="19" t="n"/>
+      <c r="AE93" s="20" t="n"/>
+      <c r="AF93" s="21">
+        <f>IF(K93="","",K93*AE93)</f>
+        <v/>
+      </c>
       <c r="AG93" s="19" t="n"/>
       <c r="AH93" s="19" t="n"/>
       <c r="AI93" s="19" t="n"/>
       <c r="AJ93" s="19" t="n"/>
       <c r="AK93" s="19" t="n"/>
-      <c r="AL93" s="16" t="inlineStr">
+      <c r="AL93" s="19" t="n"/>
+      <c r="AM93" s="16" t="inlineStr">
         <is>
           <t>ca. 3 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AM93" s="22" t="n"/>
+      <c r="AN93" s="22" t="n"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="15" t="inlineStr">
@@ -12333,23 +12430,24 @@
       <c r="AA94" s="19" t="n"/>
       <c r="AB94" s="19" t="n"/>
       <c r="AC94" s="19" t="n"/>
-      <c r="AD94" s="20" t="n"/>
-      <c r="AE94" s="21">
-        <f>IF(K94="","",K94*AD94)</f>
-        <v/>
-      </c>
-      <c r="AF94" s="19" t="n"/>
+      <c r="AD94" s="19" t="n"/>
+      <c r="AE94" s="20" t="n"/>
+      <c r="AF94" s="21">
+        <f>IF(K94="","",K94*AE94)</f>
+        <v/>
+      </c>
       <c r="AG94" s="19" t="n"/>
       <c r="AH94" s="19" t="n"/>
       <c r="AI94" s="19" t="n"/>
       <c r="AJ94" s="19" t="n"/>
       <c r="AK94" s="19" t="n"/>
-      <c r="AL94" s="16" t="inlineStr">
+      <c r="AL94" s="19" t="n"/>
+      <c r="AM94" s="16" t="inlineStr">
         <is>
           <t>ca. 6 Stück im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AM94" s="22" t="n"/>
+      <c r="AN94" s="22" t="n"/>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
@@ -12451,23 +12549,24 @@
       <c r="AA95" s="19" t="n"/>
       <c r="AB95" s="19" t="n"/>
       <c r="AC95" s="19" t="n"/>
-      <c r="AD95" s="20" t="n"/>
-      <c r="AE95" s="21">
-        <f>IF(K95="","",K95*AD95)</f>
-        <v/>
-      </c>
-      <c r="AF95" s="19" t="n"/>
+      <c r="AD95" s="19" t="n"/>
+      <c r="AE95" s="20" t="n"/>
+      <c r="AF95" s="21">
+        <f>IF(K95="","",K95*AE95)</f>
+        <v/>
+      </c>
       <c r="AG95" s="19" t="n"/>
       <c r="AH95" s="19" t="n"/>
       <c r="AI95" s="19" t="n"/>
       <c r="AJ95" s="19" t="n"/>
       <c r="AK95" s="19" t="n"/>
-      <c r="AL95" s="16" t="inlineStr">
+      <c r="AL95" s="19" t="n"/>
+      <c r="AM95" s="16" t="inlineStr">
         <is>
           <t>1 Tisch mit 2 Stühlen im Bild</t>
         </is>
       </c>
-      <c r="AM95" s="22" t="n"/>
+      <c r="AN95" s="22" t="n"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="15" t="inlineStr">
@@ -12571,25 +12670,30 @@
         </is>
       </c>
       <c r="AA96" s="19" t="n"/>
-      <c r="AB96" s="19" t="n"/>
+      <c r="AB96" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC96" s="19" t="n"/>
-      <c r="AD96" s="20" t="n"/>
-      <c r="AE96" s="21">
-        <f>IF(K96="","",K96*AD96)</f>
-        <v/>
-      </c>
-      <c r="AF96" s="19" t="n"/>
+      <c r="AD96" s="19" t="n"/>
+      <c r="AE96" s="20" t="n"/>
+      <c r="AF96" s="21">
+        <f>IF(K96="","",K96*AE96)</f>
+        <v/>
+      </c>
       <c r="AG96" s="19" t="n"/>
       <c r="AH96" s="19" t="n"/>
       <c r="AI96" s="19" t="n"/>
       <c r="AJ96" s="19" t="n"/>
       <c r="AK96" s="19" t="n"/>
-      <c r="AL96" s="16" t="inlineStr">
+      <c r="AL96" s="19" t="n"/>
+      <c r="AM96" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM96" s="22" t="n"/>
+      <c r="AN96" s="22" t="n"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="15" t="inlineStr">
@@ -12697,25 +12801,30 @@
         </is>
       </c>
       <c r="AA97" s="19" t="n"/>
-      <c r="AB97" s="19" t="n"/>
+      <c r="AB97" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC97" s="19" t="n"/>
-      <c r="AD97" s="20" t="n"/>
-      <c r="AE97" s="21">
-        <f>IF(K97="","",K97*AD97)</f>
-        <v/>
-      </c>
-      <c r="AF97" s="19" t="n"/>
+      <c r="AD97" s="19" t="n"/>
+      <c r="AE97" s="20" t="n"/>
+      <c r="AF97" s="21">
+        <f>IF(K97="","",K97*AE97)</f>
+        <v/>
+      </c>
       <c r="AG97" s="19" t="n"/>
       <c r="AH97" s="19" t="n"/>
       <c r="AI97" s="19" t="n"/>
       <c r="AJ97" s="19" t="n"/>
       <c r="AK97" s="19" t="n"/>
-      <c r="AL97" s="16" t="inlineStr">
+      <c r="AL97" s="19" t="n"/>
+      <c r="AM97" s="16" t="inlineStr">
         <is>
           <t>5 Rahmen im Bild</t>
         </is>
       </c>
-      <c r="AM97" s="22" t="n"/>
+      <c r="AN97" s="22" t="n"/>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="15" t="inlineStr">
@@ -12823,25 +12932,30 @@
         </is>
       </c>
       <c r="AA98" s="19" t="n"/>
-      <c r="AB98" s="19" t="n"/>
+      <c r="AB98" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC98" s="19" t="n"/>
-      <c r="AD98" s="20" t="n"/>
-      <c r="AE98" s="21">
-        <f>IF(K98="","",K98*AD98)</f>
-        <v/>
-      </c>
-      <c r="AF98" s="19" t="n"/>
+      <c r="AD98" s="19" t="n"/>
+      <c r="AE98" s="20" t="n"/>
+      <c r="AF98" s="21">
+        <f>IF(K98="","",K98*AE98)</f>
+        <v/>
+      </c>
       <c r="AG98" s="19" t="n"/>
       <c r="AH98" s="19" t="n"/>
       <c r="AI98" s="19" t="n"/>
       <c r="AJ98" s="19" t="n"/>
       <c r="AK98" s="19" t="n"/>
-      <c r="AL98" s="16" t="inlineStr">
+      <c r="AL98" s="19" t="n"/>
+      <c r="AM98" s="16" t="inlineStr">
         <is>
           <t>3 Rahmen im Bild</t>
         </is>
       </c>
-      <c r="AM98" s="22" t="n"/>
+      <c r="AN98" s="22" t="n"/>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="15" t="inlineStr">
@@ -12945,25 +13059,30 @@
         </is>
       </c>
       <c r="AA99" s="19" t="n"/>
-      <c r="AB99" s="19" t="n"/>
+      <c r="AB99" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC99" s="19" t="n"/>
-      <c r="AD99" s="20" t="n"/>
-      <c r="AE99" s="21">
-        <f>IF(K99="","",K99*AD99)</f>
-        <v/>
-      </c>
-      <c r="AF99" s="19" t="n"/>
+      <c r="AD99" s="19" t="n"/>
+      <c r="AE99" s="20" t="n"/>
+      <c r="AF99" s="21">
+        <f>IF(K99="","",K99*AE99)</f>
+        <v/>
+      </c>
       <c r="AG99" s="19" t="n"/>
       <c r="AH99" s="19" t="n"/>
       <c r="AI99" s="19" t="n"/>
       <c r="AJ99" s="19" t="n"/>
       <c r="AK99" s="19" t="n"/>
-      <c r="AL99" s="16" t="inlineStr">
+      <c r="AL99" s="19" t="n"/>
+      <c r="AM99" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM99" s="22" t="n"/>
+      <c r="AN99" s="22" t="n"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="15" t="inlineStr">
@@ -13069,23 +13188,24 @@
       <c r="AA100" s="19" t="n"/>
       <c r="AB100" s="19" t="n"/>
       <c r="AC100" s="19" t="n"/>
-      <c r="AD100" s="20" t="n"/>
-      <c r="AE100" s="21">
-        <f>IF(K100="","",K100*AD100)</f>
-        <v/>
-      </c>
-      <c r="AF100" s="19" t="n"/>
+      <c r="AD100" s="19" t="n"/>
+      <c r="AE100" s="20" t="n"/>
+      <c r="AF100" s="21">
+        <f>IF(K100="","",K100*AE100)</f>
+        <v/>
+      </c>
       <c r="AG100" s="19" t="n"/>
       <c r="AH100" s="19" t="n"/>
       <c r="AI100" s="19" t="n"/>
       <c r="AJ100" s="19" t="n"/>
       <c r="AK100" s="19" t="n"/>
-      <c r="AL100" s="16" t="inlineStr">
+      <c r="AL100" s="19" t="n"/>
+      <c r="AM100" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AM100" s="22" t="n"/>
+      <c r="AN100" s="22" t="n"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="15" t="inlineStr">
@@ -13189,25 +13309,30 @@
         </is>
       </c>
       <c r="AA101" s="19" t="n"/>
-      <c r="AB101" s="19" t="n"/>
+      <c r="AB101" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC101" s="19" t="n"/>
-      <c r="AD101" s="20" t="n"/>
-      <c r="AE101" s="21">
-        <f>IF(K101="","",K101*AD101)</f>
-        <v/>
-      </c>
-      <c r="AF101" s="19" t="n"/>
+      <c r="AD101" s="19" t="n"/>
+      <c r="AE101" s="20" t="n"/>
+      <c r="AF101" s="21">
+        <f>IF(K101="","",K101*AE101)</f>
+        <v/>
+      </c>
       <c r="AG101" s="19" t="n"/>
       <c r="AH101" s="19" t="n"/>
       <c r="AI101" s="19" t="n"/>
       <c r="AJ101" s="19" t="n"/>
       <c r="AK101" s="19" t="n"/>
-      <c r="AL101" s="16" t="inlineStr">
+      <c r="AL101" s="19" t="n"/>
+      <c r="AM101" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM101" s="22" t="n"/>
+      <c r="AN101" s="22" t="n"/>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="15" t="inlineStr">
@@ -13311,25 +13436,30 @@
         </is>
       </c>
       <c r="AA102" s="19" t="n"/>
-      <c r="AB102" s="19" t="n"/>
+      <c r="AB102" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC102" s="19" t="n"/>
-      <c r="AD102" s="20" t="n"/>
-      <c r="AE102" s="21">
-        <f>IF(K102="","",K102*AD102)</f>
-        <v/>
-      </c>
-      <c r="AF102" s="19" t="n"/>
+      <c r="AD102" s="19" t="n"/>
+      <c r="AE102" s="20" t="n"/>
+      <c r="AF102" s="21">
+        <f>IF(K102="","",K102*AE102)</f>
+        <v/>
+      </c>
       <c r="AG102" s="19" t="n"/>
       <c r="AH102" s="19" t="n"/>
       <c r="AI102" s="19" t="n"/>
       <c r="AJ102" s="19" t="n"/>
       <c r="AK102" s="19" t="n"/>
-      <c r="AL102" s="16" t="inlineStr">
+      <c r="AL102" s="19" t="n"/>
+      <c r="AM102" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM102" s="22" t="n"/>
+      <c r="AN102" s="22" t="n"/>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="15" t="inlineStr">
@@ -13435,23 +13565,24 @@
       <c r="AA103" s="19" t="n"/>
       <c r="AB103" s="19" t="n"/>
       <c r="AC103" s="19" t="n"/>
-      <c r="AD103" s="20" t="n"/>
-      <c r="AE103" s="21">
-        <f>IF(K103="","",K103*AD103)</f>
-        <v/>
-      </c>
-      <c r="AF103" s="19" t="n"/>
+      <c r="AD103" s="19" t="n"/>
+      <c r="AE103" s="20" t="n"/>
+      <c r="AF103" s="21">
+        <f>IF(K103="","",K103*AE103)</f>
+        <v/>
+      </c>
       <c r="AG103" s="19" t="n"/>
       <c r="AH103" s="19" t="n"/>
       <c r="AI103" s="19" t="n"/>
       <c r="AJ103" s="19" t="n"/>
       <c r="AK103" s="19" t="n"/>
-      <c r="AL103" s="16" t="inlineStr">
+      <c r="AL103" s="19" t="n"/>
+      <c r="AM103" s="16" t="inlineStr">
         <is>
           <t>1 Pflanze im Bild</t>
         </is>
       </c>
-      <c r="AM103" s="22" t="n"/>
+      <c r="AN103" s="22" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="15" t="inlineStr">
@@ -13557,23 +13688,24 @@
       <c r="AA104" s="19" t="n"/>
       <c r="AB104" s="19" t="n"/>
       <c r="AC104" s="19" t="n"/>
-      <c r="AD104" s="20" t="n"/>
-      <c r="AE104" s="21">
-        <f>IF(K104="","",K104*AD104)</f>
-        <v/>
-      </c>
-      <c r="AF104" s="19" t="n"/>
+      <c r="AD104" s="19" t="n"/>
+      <c r="AE104" s="20" t="n"/>
+      <c r="AF104" s="21">
+        <f>IF(K104="","",K104*AE104)</f>
+        <v/>
+      </c>
       <c r="AG104" s="19" t="n"/>
       <c r="AH104" s="19" t="n"/>
       <c r="AI104" s="19" t="n"/>
       <c r="AJ104" s="19" t="n"/>
       <c r="AK104" s="19" t="n"/>
-      <c r="AL104" s="16" t="inlineStr">
+      <c r="AL104" s="19" t="n"/>
+      <c r="AM104" s="16" t="inlineStr">
         <is>
           <t>2 Stück (klein und groß)</t>
         </is>
       </c>
-      <c r="AM104" s="22" t="n"/>
+      <c r="AN104" s="22" t="n"/>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="15" t="inlineStr">
@@ -13679,23 +13811,24 @@
       <c r="AA105" s="19" t="n"/>
       <c r="AB105" s="19" t="n"/>
       <c r="AC105" s="19" t="n"/>
-      <c r="AD105" s="20" t="n"/>
-      <c r="AE105" s="21">
-        <f>IF(K105="","",K105*AD105)</f>
-        <v/>
-      </c>
-      <c r="AF105" s="19" t="n"/>
+      <c r="AD105" s="19" t="n"/>
+      <c r="AE105" s="20" t="n"/>
+      <c r="AF105" s="21">
+        <f>IF(K105="","",K105*AE105)</f>
+        <v/>
+      </c>
       <c r="AG105" s="19" t="n"/>
       <c r="AH105" s="19" t="n"/>
       <c r="AI105" s="19" t="n"/>
       <c r="AJ105" s="19" t="n"/>
       <c r="AK105" s="19" t="n"/>
-      <c r="AL105" s="16" t="inlineStr">
+      <c r="AL105" s="19" t="n"/>
+      <c r="AM105" s="16" t="inlineStr">
         <is>
           <t>2 Stück (zwei Fotos, klein und groß)</t>
         </is>
       </c>
-      <c r="AM105" s="22" t="n"/>
+      <c r="AN105" s="22" t="n"/>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="15" t="inlineStr">
@@ -13799,25 +13932,30 @@
         </is>
       </c>
       <c r="AA106" s="19" t="n"/>
-      <c r="AB106" s="19" t="n"/>
+      <c r="AB106" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC106" s="19" t="n"/>
-      <c r="AD106" s="20" t="n"/>
-      <c r="AE106" s="21">
-        <f>IF(K106="","",K106*AD106)</f>
-        <v/>
-      </c>
-      <c r="AF106" s="19" t="n"/>
+      <c r="AD106" s="19" t="n"/>
+      <c r="AE106" s="20" t="n"/>
+      <c r="AF106" s="21">
+        <f>IF(K106="","",K106*AE106)</f>
+        <v/>
+      </c>
       <c r="AG106" s="19" t="n"/>
       <c r="AH106" s="19" t="n"/>
       <c r="AI106" s="19" t="n"/>
       <c r="AJ106" s="19" t="n"/>
       <c r="AK106" s="19" t="n"/>
-      <c r="AL106" s="16" t="inlineStr">
+      <c r="AL106" s="19" t="n"/>
+      <c r="AM106" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM106" s="22" t="n"/>
+      <c r="AN106" s="22" t="n"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="15" t="inlineStr">
@@ -13921,25 +14059,30 @@
         </is>
       </c>
       <c r="AA107" s="19" t="n"/>
-      <c r="AB107" s="19" t="n"/>
+      <c r="AB107" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC107" s="19" t="n"/>
-      <c r="AD107" s="20" t="n"/>
-      <c r="AE107" s="21">
-        <f>IF(K107="","",K107*AD107)</f>
-        <v/>
-      </c>
-      <c r="AF107" s="19" t="n"/>
+      <c r="AD107" s="19" t="n"/>
+      <c r="AE107" s="20" t="n"/>
+      <c r="AF107" s="21">
+        <f>IF(K107="","",K107*AE107)</f>
+        <v/>
+      </c>
       <c r="AG107" s="19" t="n"/>
       <c r="AH107" s="19" t="n"/>
       <c r="AI107" s="19" t="n"/>
       <c r="AJ107" s="19" t="n"/>
       <c r="AK107" s="19" t="n"/>
-      <c r="AL107" s="16" t="inlineStr">
+      <c r="AL107" s="19" t="n"/>
+      <c r="AM107" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM107" s="22" t="n"/>
+      <c r="AN107" s="22" t="n"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="15" t="inlineStr">
@@ -14043,25 +14186,30 @@
         </is>
       </c>
       <c r="AA108" s="19" t="n"/>
-      <c r="AB108" s="19" t="n"/>
+      <c r="AB108" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC108" s="19" t="n"/>
-      <c r="AD108" s="20" t="n"/>
-      <c r="AE108" s="21">
-        <f>IF(K108="","",K108*AD108)</f>
-        <v/>
-      </c>
-      <c r="AF108" s="19" t="n"/>
+      <c r="AD108" s="19" t="n"/>
+      <c r="AE108" s="20" t="n"/>
+      <c r="AF108" s="21">
+        <f>IF(K108="","",K108*AE108)</f>
+        <v/>
+      </c>
       <c r="AG108" s="19" t="n"/>
       <c r="AH108" s="19" t="n"/>
       <c r="AI108" s="19" t="n"/>
       <c r="AJ108" s="19" t="n"/>
       <c r="AK108" s="19" t="n"/>
-      <c r="AL108" s="16" t="inlineStr">
+      <c r="AL108" s="19" t="n"/>
+      <c r="AM108" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM108" s="22" t="n"/>
+      <c r="AN108" s="22" t="n"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="15" t="inlineStr">
@@ -14165,25 +14313,30 @@
         </is>
       </c>
       <c r="AA109" s="19" t="n"/>
-      <c r="AB109" s="19" t="n"/>
+      <c r="AB109" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC109" s="19" t="n"/>
-      <c r="AD109" s="20" t="n"/>
-      <c r="AE109" s="21">
-        <f>IF(K109="","",K109*AD109)</f>
-        <v/>
-      </c>
-      <c r="AF109" s="19" t="n"/>
+      <c r="AD109" s="19" t="n"/>
+      <c r="AE109" s="20" t="n"/>
+      <c r="AF109" s="21">
+        <f>IF(K109="","",K109*AE109)</f>
+        <v/>
+      </c>
       <c r="AG109" s="19" t="n"/>
       <c r="AH109" s="19" t="n"/>
       <c r="AI109" s="19" t="n"/>
       <c r="AJ109" s="19" t="n"/>
       <c r="AK109" s="19" t="n"/>
-      <c r="AL109" s="16" t="inlineStr">
+      <c r="AL109" s="19" t="n"/>
+      <c r="AM109" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM109" s="22" t="n"/>
+      <c r="AN109" s="22" t="n"/>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="15" t="inlineStr">
@@ -14289,23 +14442,24 @@
       <c r="AA110" s="19" t="n"/>
       <c r="AB110" s="19" t="n"/>
       <c r="AC110" s="19" t="n"/>
-      <c r="AD110" s="20" t="n"/>
-      <c r="AE110" s="21">
-        <f>IF(K110="","",K110*AD110)</f>
-        <v/>
-      </c>
-      <c r="AF110" s="19" t="n"/>
+      <c r="AD110" s="19" t="n"/>
+      <c r="AE110" s="20" t="n"/>
+      <c r="AF110" s="21">
+        <f>IF(K110="","",K110*AE110)</f>
+        <v/>
+      </c>
       <c r="AG110" s="19" t="n"/>
       <c r="AH110" s="19" t="n"/>
       <c r="AI110" s="19" t="n"/>
       <c r="AJ110" s="19" t="n"/>
       <c r="AK110" s="19" t="n"/>
-      <c r="AL110" s="16" t="inlineStr">
+      <c r="AL110" s="19" t="n"/>
+      <c r="AM110" s="16" t="inlineStr">
         <is>
           <t>3 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM110" s="22" t="inlineStr">
+      <c r="AN110" s="22" t="inlineStr">
         <is>
           <t>Auf dem Erfassungsblatt NE01 durchgestrichen - die Stuecke stehen jetzt im Flur 1 und werden dort als BA01-03 gefuehrt.</t>
         </is>
@@ -14415,23 +14569,24 @@
       <c r="AA111" s="19" t="n"/>
       <c r="AB111" s="19" t="n"/>
       <c r="AC111" s="19" t="n"/>
-      <c r="AD111" s="20" t="n"/>
-      <c r="AE111" s="21">
-        <f>IF(K111="","",K111*AD111)</f>
-        <v/>
-      </c>
-      <c r="AF111" s="19" t="n"/>
+      <c r="AD111" s="19" t="n"/>
+      <c r="AE111" s="20" t="n"/>
+      <c r="AF111" s="21">
+        <f>IF(K111="","",K111*AE111)</f>
+        <v/>
+      </c>
       <c r="AG111" s="19" t="n"/>
       <c r="AH111" s="19" t="n"/>
       <c r="AI111" s="19" t="n"/>
       <c r="AJ111" s="19" t="n"/>
       <c r="AK111" s="19" t="n"/>
-      <c r="AL111" s="16" t="inlineStr">
+      <c r="AL111" s="19" t="n"/>
+      <c r="AM111" s="16" t="inlineStr">
         <is>
           <t>2 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM111" s="22" t="n"/>
+      <c r="AN111" s="22" t="n"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="15" t="inlineStr">
@@ -14537,23 +14692,24 @@
       <c r="AA112" s="19" t="n"/>
       <c r="AB112" s="19" t="n"/>
       <c r="AC112" s="19" t="n"/>
-      <c r="AD112" s="20" t="n"/>
-      <c r="AE112" s="21">
-        <f>IF(K112="","",K112*AD112)</f>
-        <v/>
-      </c>
-      <c r="AF112" s="19" t="n"/>
+      <c r="AD112" s="19" t="n"/>
+      <c r="AE112" s="20" t="n"/>
+      <c r="AF112" s="21">
+        <f>IF(K112="","",K112*AE112)</f>
+        <v/>
+      </c>
       <c r="AG112" s="19" t="n"/>
       <c r="AH112" s="19" t="n"/>
       <c r="AI112" s="19" t="n"/>
       <c r="AJ112" s="19" t="n"/>
       <c r="AK112" s="19" t="n"/>
-      <c r="AL112" s="16" t="inlineStr">
+      <c r="AL112" s="19" t="n"/>
+      <c r="AM112" s="16" t="inlineStr">
         <is>
           <t>mindestens 4 Tische im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AM112" s="22" t="n"/>
+      <c r="AN112" s="22" t="n"/>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="15" t="inlineStr">
@@ -14659,23 +14815,24 @@
       <c r="AA113" s="19" t="n"/>
       <c r="AB113" s="19" t="n"/>
       <c r="AC113" s="19" t="n"/>
-      <c r="AD113" s="20" t="n"/>
-      <c r="AE113" s="21">
-        <f>IF(K113="","",K113*AD113)</f>
-        <v/>
-      </c>
-      <c r="AF113" s="19" t="n"/>
+      <c r="AD113" s="19" t="n"/>
+      <c r="AE113" s="20" t="n"/>
+      <c r="AF113" s="21">
+        <f>IF(K113="","",K113*AE113)</f>
+        <v/>
+      </c>
       <c r="AG113" s="19" t="n"/>
       <c r="AH113" s="19" t="n"/>
       <c r="AI113" s="19" t="n"/>
       <c r="AJ113" s="19" t="n"/>
       <c r="AK113" s="19" t="n"/>
-      <c r="AL113" s="16" t="inlineStr">
+      <c r="AL113" s="19" t="n"/>
+      <c r="AM113" s="16" t="inlineStr">
         <is>
           <t>2 Bänke im Bild erkennbar</t>
         </is>
       </c>
-      <c r="AM113" s="22" t="n"/>
+      <c r="AN113" s="22" t="n"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="15" t="inlineStr">
@@ -14779,25 +14936,30 @@
         </is>
       </c>
       <c r="AA114" s="19" t="n"/>
-      <c r="AB114" s="19" t="n"/>
+      <c r="AB114" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC114" s="19" t="n"/>
-      <c r="AD114" s="20" t="n"/>
-      <c r="AE114" s="21">
-        <f>IF(K114="","",K114*AD114)</f>
-        <v/>
-      </c>
-      <c r="AF114" s="19" t="n"/>
+      <c r="AD114" s="19" t="n"/>
+      <c r="AE114" s="20" t="n"/>
+      <c r="AF114" s="21">
+        <f>IF(K114="","",K114*AE114)</f>
+        <v/>
+      </c>
       <c r="AG114" s="19" t="n"/>
       <c r="AH114" s="19" t="n"/>
       <c r="AI114" s="19" t="n"/>
       <c r="AJ114" s="19" t="n"/>
       <c r="AK114" s="19" t="n"/>
-      <c r="AL114" s="16" t="inlineStr">
+      <c r="AL114" s="19" t="n"/>
+      <c r="AM114" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM114" s="22" t="n"/>
+      <c r="AN114" s="22" t="n"/>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="15" t="inlineStr">
@@ -14907,23 +15069,24 @@
       </c>
       <c r="AB115" s="19" t="n"/>
       <c r="AC115" s="19" t="n"/>
-      <c r="AD115" s="20" t="n"/>
-      <c r="AE115" s="21">
-        <f>IF(K115="","",K115*AD115)</f>
-        <v/>
-      </c>
-      <c r="AF115" s="19" t="n"/>
+      <c r="AD115" s="19" t="n"/>
+      <c r="AE115" s="20" t="n"/>
+      <c r="AF115" s="21">
+        <f>IF(K115="","",K115*AE115)</f>
+        <v/>
+      </c>
       <c r="AG115" s="19" t="n"/>
       <c r="AH115" s="19" t="n"/>
       <c r="AI115" s="19" t="n"/>
       <c r="AJ115" s="19" t="n"/>
       <c r="AK115" s="19" t="n"/>
-      <c r="AL115" s="16" t="inlineStr">
+      <c r="AL115" s="19" t="n"/>
+      <c r="AM115" s="16" t="inlineStr">
         <is>
           <t>2 Elemente im Bild - bitte prüfen ob 3</t>
         </is>
       </c>
-      <c r="AM115" s="22" t="n"/>
+      <c r="AN115" s="22" t="n"/>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="15" t="inlineStr">
@@ -15027,25 +15190,30 @@
         </is>
       </c>
       <c r="AA116" s="19" t="n"/>
-      <c r="AB116" s="19" t="n"/>
+      <c r="AB116" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC116" s="19" t="n"/>
-      <c r="AD116" s="20" t="n"/>
-      <c r="AE116" s="21">
-        <f>IF(K116="","",K116*AD116)</f>
-        <v/>
-      </c>
-      <c r="AF116" s="19" t="n"/>
+      <c r="AD116" s="19" t="n"/>
+      <c r="AE116" s="20" t="n"/>
+      <c r="AF116" s="21">
+        <f>IF(K116="","",K116*AE116)</f>
+        <v/>
+      </c>
       <c r="AG116" s="19" t="n"/>
       <c r="AH116" s="19" t="n"/>
       <c r="AI116" s="19" t="n"/>
       <c r="AJ116" s="19" t="n"/>
       <c r="AK116" s="19" t="n"/>
-      <c r="AL116" s="16" t="inlineStr">
+      <c r="AL116" s="19" t="n"/>
+      <c r="AM116" s="16" t="inlineStr">
         <is>
           <t>5 Uhren im Bild - bitte nachzählen</t>
         </is>
       </c>
-      <c r="AM116" s="22" t="n"/>
+      <c r="AN116" s="22" t="n"/>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="15" t="inlineStr">
@@ -15155,23 +15323,24 @@
       <c r="AA117" s="19" t="n"/>
       <c r="AB117" s="19" t="n"/>
       <c r="AC117" s="19" t="n"/>
-      <c r="AD117" s="20" t="n"/>
-      <c r="AE117" s="21">
-        <f>IF(K117="","",K117*AD117)</f>
-        <v/>
-      </c>
-      <c r="AF117" s="19" t="n"/>
+      <c r="AD117" s="19" t="n"/>
+      <c r="AE117" s="20" t="n"/>
+      <c r="AF117" s="21">
+        <f>IF(K117="","",K117*AE117)</f>
+        <v/>
+      </c>
       <c r="AG117" s="19" t="n"/>
       <c r="AH117" s="19" t="n"/>
       <c r="AI117" s="19" t="n"/>
       <c r="AJ117" s="19" t="n"/>
       <c r="AK117" s="19" t="n"/>
-      <c r="AL117" s="16" t="inlineStr">
+      <c r="AL117" s="19" t="n"/>
+      <c r="AM117" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild (Inhalt nicht enthalten)</t>
         </is>
       </c>
-      <c r="AM117" s="22" t="n"/>
+      <c r="AN117" s="22" t="n"/>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="15" t="inlineStr">
@@ -15275,25 +15444,30 @@
         </is>
       </c>
       <c r="AA118" s="19" t="n"/>
-      <c r="AB118" s="19" t="n"/>
+      <c r="AB118" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC118" s="19" t="n"/>
-      <c r="AD118" s="20" t="n"/>
-      <c r="AE118" s="21">
-        <f>IF(K118="","",K118*AD118)</f>
-        <v/>
-      </c>
-      <c r="AF118" s="19" t="n"/>
+      <c r="AD118" s="19" t="n"/>
+      <c r="AE118" s="20" t="n"/>
+      <c r="AF118" s="21">
+        <f>IF(K118="","",K118*AE118)</f>
+        <v/>
+      </c>
       <c r="AG118" s="19" t="n"/>
       <c r="AH118" s="19" t="n"/>
       <c r="AI118" s="19" t="n"/>
       <c r="AJ118" s="19" t="n"/>
       <c r="AK118" s="19" t="n"/>
-      <c r="AL118" s="16" t="inlineStr">
+      <c r="AL118" s="19" t="n"/>
+      <c r="AM118" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM118" s="22" t="n"/>
+      <c r="AN118" s="22" t="n"/>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="15" t="inlineStr">
@@ -15397,25 +15571,30 @@
         </is>
       </c>
       <c r="AA119" s="19" t="n"/>
-      <c r="AB119" s="19" t="n"/>
+      <c r="AB119" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC119" s="19" t="n"/>
-      <c r="AD119" s="20" t="n"/>
-      <c r="AE119" s="21">
-        <f>IF(K119="","",K119*AD119)</f>
-        <v/>
-      </c>
-      <c r="AF119" s="19" t="n"/>
+      <c r="AD119" s="19" t="n"/>
+      <c r="AE119" s="20" t="n"/>
+      <c r="AF119" s="21">
+        <f>IF(K119="","",K119*AE119)</f>
+        <v/>
+      </c>
       <c r="AG119" s="19" t="n"/>
       <c r="AH119" s="19" t="n"/>
       <c r="AI119" s="19" t="n"/>
       <c r="AJ119" s="19" t="n"/>
       <c r="AK119" s="19" t="n"/>
-      <c r="AL119" s="16" t="inlineStr">
+      <c r="AL119" s="19" t="n"/>
+      <c r="AM119" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM119" s="22" t="n"/>
+      <c r="AN119" s="22" t="n"/>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="15" t="inlineStr">
@@ -15519,25 +15698,30 @@
         </is>
       </c>
       <c r="AA120" s="19" t="n"/>
-      <c r="AB120" s="19" t="n"/>
+      <c r="AB120" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC120" s="19" t="n"/>
-      <c r="AD120" s="20" t="n"/>
-      <c r="AE120" s="21">
-        <f>IF(K120="","",K120*AD120)</f>
-        <v/>
-      </c>
-      <c r="AF120" s="19" t="n"/>
+      <c r="AD120" s="19" t="n"/>
+      <c r="AE120" s="20" t="n"/>
+      <c r="AF120" s="21">
+        <f>IF(K120="","",K120*AE120)</f>
+        <v/>
+      </c>
       <c r="AG120" s="19" t="n"/>
       <c r="AH120" s="19" t="n"/>
       <c r="AI120" s="19" t="n"/>
       <c r="AJ120" s="19" t="n"/>
       <c r="AK120" s="19" t="n"/>
-      <c r="AL120" s="16" t="inlineStr">
+      <c r="AL120" s="19" t="n"/>
+      <c r="AM120" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM120" s="22" t="n"/>
+      <c r="AN120" s="22" t="n"/>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="15" t="inlineStr">
@@ -15645,25 +15829,30 @@
         </is>
       </c>
       <c r="AA121" s="19" t="n"/>
-      <c r="AB121" s="19" t="n"/>
+      <c r="AB121" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC121" s="19" t="n"/>
-      <c r="AD121" s="20" t="n"/>
-      <c r="AE121" s="21">
-        <f>IF(K121="","",K121*AD121)</f>
-        <v/>
-      </c>
-      <c r="AF121" s="19" t="n"/>
+      <c r="AD121" s="19" t="n"/>
+      <c r="AE121" s="20" t="n"/>
+      <c r="AF121" s="21">
+        <f>IF(K121="","",K121*AE121)</f>
+        <v/>
+      </c>
       <c r="AG121" s="19" t="n"/>
       <c r="AH121" s="19" t="n"/>
       <c r="AI121" s="19" t="n"/>
       <c r="AJ121" s="19" t="n"/>
       <c r="AK121" s="19" t="n"/>
-      <c r="AL121" s="16" t="inlineStr">
+      <c r="AL121" s="19" t="n"/>
+      <c r="AM121" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM121" s="22" t="n"/>
+      <c r="AN121" s="22" t="n"/>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="15" t="inlineStr">
@@ -15771,25 +15960,30 @@
         </is>
       </c>
       <c r="AA122" s="19" t="n"/>
-      <c r="AB122" s="19" t="n"/>
+      <c r="AB122" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC122" s="19" t="n"/>
-      <c r="AD122" s="20" t="n"/>
-      <c r="AE122" s="21">
-        <f>IF(K122="","",K122*AD122)</f>
-        <v/>
-      </c>
-      <c r="AF122" s="19" t="n"/>
+      <c r="AD122" s="19" t="n"/>
+      <c r="AE122" s="20" t="n"/>
+      <c r="AF122" s="21">
+        <f>IF(K122="","",K122*AE122)</f>
+        <v/>
+      </c>
       <c r="AG122" s="19" t="n"/>
       <c r="AH122" s="19" t="n"/>
       <c r="AI122" s="19" t="n"/>
       <c r="AJ122" s="19" t="n"/>
       <c r="AK122" s="19" t="n"/>
-      <c r="AL122" s="16" t="inlineStr">
+      <c r="AL122" s="19" t="n"/>
+      <c r="AM122" s="16" t="inlineStr">
         <is>
           <t>5 Rahmen im Bild</t>
         </is>
       </c>
-      <c r="AM122" s="22" t="n"/>
+      <c r="AN122" s="22" t="n"/>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="15" t="inlineStr">
@@ -15897,25 +16091,30 @@
         </is>
       </c>
       <c r="AA123" s="19" t="n"/>
-      <c r="AB123" s="19" t="n"/>
+      <c r="AB123" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC123" s="19" t="n"/>
-      <c r="AD123" s="20" t="n"/>
-      <c r="AE123" s="21">
-        <f>IF(K123="","",K123*AD123)</f>
-        <v/>
-      </c>
-      <c r="AF123" s="19" t="n"/>
+      <c r="AD123" s="19" t="n"/>
+      <c r="AE123" s="20" t="n"/>
+      <c r="AF123" s="21">
+        <f>IF(K123="","",K123*AE123)</f>
+        <v/>
+      </c>
       <c r="AG123" s="19" t="n"/>
       <c r="AH123" s="19" t="n"/>
       <c r="AI123" s="19" t="n"/>
       <c r="AJ123" s="19" t="n"/>
       <c r="AK123" s="19" t="n"/>
-      <c r="AL123" s="16" t="inlineStr">
+      <c r="AL123" s="19" t="n"/>
+      <c r="AM123" s="16" t="inlineStr">
         <is>
           <t>4 Rahmen im Bild, ggf. mehr</t>
         </is>
       </c>
-      <c r="AM123" s="22" t="n"/>
+      <c r="AN123" s="22" t="n"/>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="15" t="inlineStr">
@@ -16019,25 +16218,30 @@
         </is>
       </c>
       <c r="AA124" s="19" t="n"/>
-      <c r="AB124" s="19" t="n"/>
+      <c r="AB124" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC124" s="19" t="n"/>
-      <c r="AD124" s="20" t="n"/>
-      <c r="AE124" s="21">
-        <f>IF(K124="","",K124*AD124)</f>
-        <v/>
-      </c>
-      <c r="AF124" s="19" t="n"/>
+      <c r="AD124" s="19" t="n"/>
+      <c r="AE124" s="20" t="n"/>
+      <c r="AF124" s="21">
+        <f>IF(K124="","",K124*AE124)</f>
+        <v/>
+      </c>
       <c r="AG124" s="19" t="n"/>
       <c r="AH124" s="19" t="n"/>
       <c r="AI124" s="19" t="n"/>
       <c r="AJ124" s="19" t="n"/>
       <c r="AK124" s="19" t="n"/>
-      <c r="AL124" s="16" t="inlineStr">
+      <c r="AL124" s="19" t="n"/>
+      <c r="AM124" s="16" t="inlineStr">
         <is>
           <t>1 Bild im Bild</t>
         </is>
       </c>
-      <c r="AM124" s="22" t="n"/>
+      <c r="AN124" s="22" t="n"/>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="15" t="inlineStr">
@@ -16143,23 +16347,24 @@
       <c r="AA125" s="19" t="n"/>
       <c r="AB125" s="19" t="n"/>
       <c r="AC125" s="19" t="n"/>
-      <c r="AD125" s="20" t="n"/>
-      <c r="AE125" s="21">
-        <f>IF(K125="","",K125*AD125)</f>
-        <v/>
-      </c>
-      <c r="AF125" s="19" t="n"/>
+      <c r="AD125" s="19" t="n"/>
+      <c r="AE125" s="20" t="n"/>
+      <c r="AF125" s="21">
+        <f>IF(K125="","",K125*AE125)</f>
+        <v/>
+      </c>
       <c r="AG125" s="19" t="n"/>
       <c r="AH125" s="19" t="n"/>
       <c r="AI125" s="19" t="n"/>
       <c r="AJ125" s="19" t="n"/>
       <c r="AK125" s="19" t="n"/>
-      <c r="AL125" s="16" t="inlineStr">
+      <c r="AL125" s="19" t="n"/>
+      <c r="AM125" s="16" t="inlineStr">
         <is>
           <t>4 Rahmen erkennbar</t>
         </is>
       </c>
-      <c r="AM125" s="22" t="n"/>
+      <c r="AN125" s="22" t="n"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="15" t="inlineStr">
@@ -16265,23 +16470,24 @@
       </c>
       <c r="AB126" s="19" t="n"/>
       <c r="AC126" s="19" t="n"/>
-      <c r="AD126" s="20" t="n"/>
-      <c r="AE126" s="21">
-        <f>IF(K126="","",K126*AD126)</f>
-        <v/>
-      </c>
-      <c r="AF126" s="19" t="n"/>
+      <c r="AD126" s="19" t="n"/>
+      <c r="AE126" s="20" t="n"/>
+      <c r="AF126" s="21">
+        <f>IF(K126="","",K126*AE126)</f>
+        <v/>
+      </c>
       <c r="AG126" s="19" t="n"/>
       <c r="AH126" s="19" t="n"/>
       <c r="AI126" s="19" t="n"/>
       <c r="AJ126" s="19" t="n"/>
       <c r="AK126" s="19" t="n"/>
-      <c r="AL126" s="16" t="inlineStr">
+      <c r="AL126" s="19" t="n"/>
+      <c r="AM126" s="16" t="inlineStr">
         <is>
           <t>15 Läufer laut Angabe im Haus – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM126" s="22" t="n"/>
+      <c r="AN126" s="22" t="n"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="15" t="inlineStr">
@@ -16387,23 +16593,24 @@
       <c r="AA127" s="19" t="n"/>
       <c r="AB127" s="19" t="n"/>
       <c r="AC127" s="19" t="n"/>
-      <c r="AD127" s="20" t="n"/>
-      <c r="AE127" s="21">
-        <f>IF(K127="","",K127*AD127)</f>
-        <v/>
-      </c>
-      <c r="AF127" s="19" t="n"/>
+      <c r="AD127" s="19" t="n"/>
+      <c r="AE127" s="20" t="n"/>
+      <c r="AF127" s="21">
+        <f>IF(K127="","",K127*AE127)</f>
+        <v/>
+      </c>
       <c r="AG127" s="19" t="n"/>
       <c r="AH127" s="19" t="n"/>
       <c r="AI127" s="19" t="n"/>
       <c r="AJ127" s="19" t="n"/>
       <c r="AK127" s="19" t="n"/>
-      <c r="AL127" s="16" t="inlineStr">
+      <c r="AL127" s="19" t="n"/>
+      <c r="AM127" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM127" s="22" t="n"/>
+      <c r="AN127" s="22" t="n"/>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="15" t="inlineStr">
@@ -16509,23 +16716,24 @@
       <c r="AA128" s="19" t="n"/>
       <c r="AB128" s="19" t="n"/>
       <c r="AC128" s="19" t="n"/>
-      <c r="AD128" s="20" t="n"/>
-      <c r="AE128" s="21">
-        <f>IF(K128="","",K128*AD128)</f>
-        <v/>
-      </c>
-      <c r="AF128" s="19" t="n"/>
+      <c r="AD128" s="19" t="n"/>
+      <c r="AE128" s="20" t="n"/>
+      <c r="AF128" s="21">
+        <f>IF(K128="","",K128*AE128)</f>
+        <v/>
+      </c>
       <c r="AG128" s="19" t="n"/>
       <c r="AH128" s="19" t="n"/>
       <c r="AI128" s="19" t="n"/>
       <c r="AJ128" s="19" t="n"/>
       <c r="AK128" s="19" t="n"/>
-      <c r="AL128" s="16" t="inlineStr">
+      <c r="AL128" s="19" t="n"/>
+      <c r="AM128" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM128" s="22" t="n"/>
+      <c r="AN128" s="22" t="n"/>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="15" t="inlineStr">
@@ -16631,23 +16839,24 @@
       <c r="AA129" s="19" t="n"/>
       <c r="AB129" s="19" t="n"/>
       <c r="AC129" s="19" t="n"/>
-      <c r="AD129" s="20" t="n"/>
-      <c r="AE129" s="21">
-        <f>IF(K129="","",K129*AD129)</f>
-        <v/>
-      </c>
-      <c r="AF129" s="19" t="n"/>
+      <c r="AD129" s="19" t="n"/>
+      <c r="AE129" s="20" t="n"/>
+      <c r="AF129" s="21">
+        <f>IF(K129="","",K129*AE129)</f>
+        <v/>
+      </c>
       <c r="AG129" s="19" t="n"/>
       <c r="AH129" s="19" t="n"/>
       <c r="AI129" s="19" t="n"/>
       <c r="AJ129" s="19" t="n"/>
       <c r="AK129" s="19" t="n"/>
-      <c r="AL129" s="16" t="inlineStr">
+      <c r="AL129" s="19" t="n"/>
+      <c r="AM129" s="16" t="inlineStr">
         <is>
           <t>3 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM129" s="22" t="n"/>
+      <c r="AN129" s="22" t="n"/>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="15" t="inlineStr">
@@ -16753,23 +16962,24 @@
       <c r="AA130" s="19" t="n"/>
       <c r="AB130" s="19" t="n"/>
       <c r="AC130" s="19" t="n"/>
-      <c r="AD130" s="20" t="n"/>
-      <c r="AE130" s="21">
-        <f>IF(K130="","",K130*AD130)</f>
-        <v/>
-      </c>
-      <c r="AF130" s="19" t="n"/>
+      <c r="AD130" s="19" t="n"/>
+      <c r="AE130" s="20" t="n"/>
+      <c r="AF130" s="21">
+        <f>IF(K130="","",K130*AE130)</f>
+        <v/>
+      </c>
       <c r="AG130" s="19" t="n"/>
       <c r="AH130" s="19" t="n"/>
       <c r="AI130" s="19" t="n"/>
       <c r="AJ130" s="19" t="n"/>
       <c r="AK130" s="19" t="n"/>
-      <c r="AL130" s="16" t="inlineStr">
+      <c r="AL130" s="19" t="n"/>
+      <c r="AM130" s="16" t="inlineStr">
         <is>
           <t>1 große Einheit im Bild</t>
         </is>
       </c>
-      <c r="AM130" s="22" t="n"/>
+      <c r="AN130" s="22" t="n"/>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="15" t="inlineStr">
@@ -16875,23 +17085,24 @@
       <c r="AA131" s="19" t="n"/>
       <c r="AB131" s="19" t="n"/>
       <c r="AC131" s="19" t="n"/>
-      <c r="AD131" s="20" t="n"/>
-      <c r="AE131" s="21">
-        <f>IF(K131="","",K131*AD131)</f>
-        <v/>
-      </c>
-      <c r="AF131" s="19" t="n"/>
+      <c r="AD131" s="19" t="n"/>
+      <c r="AE131" s="20" t="n"/>
+      <c r="AF131" s="21">
+        <f>IF(K131="","",K131*AE131)</f>
+        <v/>
+      </c>
       <c r="AG131" s="19" t="n"/>
       <c r="AH131" s="19" t="n"/>
       <c r="AI131" s="19" t="n"/>
       <c r="AJ131" s="19" t="n"/>
       <c r="AK131" s="19" t="n"/>
-      <c r="AL131" s="16" t="inlineStr">
+      <c r="AL131" s="19" t="n"/>
+      <c r="AM131" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Vordergrund, weitere im Hintergrund</t>
         </is>
       </c>
-      <c r="AM131" s="22" t="n"/>
+      <c r="AN131" s="22" t="n"/>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="15" t="inlineStr">
@@ -16997,23 +17208,24 @@
       <c r="AA132" s="19" t="n"/>
       <c r="AB132" s="19" t="n"/>
       <c r="AC132" s="19" t="n"/>
-      <c r="AD132" s="20" t="n"/>
-      <c r="AE132" s="21">
-        <f>IF(K132="","",K132*AD132)</f>
-        <v/>
-      </c>
-      <c r="AF132" s="19" t="n"/>
+      <c r="AD132" s="19" t="n"/>
+      <c r="AE132" s="20" t="n"/>
+      <c r="AF132" s="21">
+        <f>IF(K132="","",K132*AE132)</f>
+        <v/>
+      </c>
       <c r="AG132" s="19" t="n"/>
       <c r="AH132" s="19" t="n"/>
       <c r="AI132" s="19" t="n"/>
       <c r="AJ132" s="19" t="n"/>
       <c r="AK132" s="19" t="n"/>
-      <c r="AL132" s="16" t="inlineStr">
+      <c r="AL132" s="19" t="n"/>
+      <c r="AM132" s="16" t="inlineStr">
         <is>
           <t>1 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM132" s="22" t="n"/>
+      <c r="AN132" s="22" t="n"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="15" t="inlineStr">
@@ -17127,23 +17339,24 @@
       </c>
       <c r="AB133" s="19" t="n"/>
       <c r="AC133" s="19" t="n"/>
-      <c r="AD133" s="20" t="n"/>
-      <c r="AE133" s="21">
-        <f>IF(K133="","",K133*AD133)</f>
-        <v/>
-      </c>
-      <c r="AF133" s="19" t="n"/>
+      <c r="AD133" s="19" t="n"/>
+      <c r="AE133" s="20" t="n"/>
+      <c r="AF133" s="21">
+        <f>IF(K133="","",K133*AE133)</f>
+        <v/>
+      </c>
       <c r="AG133" s="19" t="n"/>
       <c r="AH133" s="19" t="n"/>
       <c r="AI133" s="19" t="n"/>
       <c r="AJ133" s="19" t="n"/>
       <c r="AK133" s="19" t="n"/>
-      <c r="AL133" s="16" t="inlineStr">
+      <c r="AL133" s="19" t="n"/>
+      <c r="AM133" s="16" t="inlineStr">
         <is>
           <t>2 Teppiche, Maße vom Erfassungsblatt.</t>
         </is>
       </c>
-      <c r="AM133" s="22" t="n"/>
+      <c r="AN133" s="22" t="n"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="15" t="inlineStr">
@@ -17257,23 +17470,24 @@
       </c>
       <c r="AB134" s="19" t="n"/>
       <c r="AC134" s="19" t="n"/>
-      <c r="AD134" s="20" t="n"/>
-      <c r="AE134" s="21">
-        <f>IF(K134="","",K134*AD134)</f>
-        <v/>
-      </c>
-      <c r="AF134" s="19" t="n"/>
+      <c r="AD134" s="19" t="n"/>
+      <c r="AE134" s="20" t="n"/>
+      <c r="AF134" s="21">
+        <f>IF(K134="","",K134*AE134)</f>
+        <v/>
+      </c>
       <c r="AG134" s="19" t="n"/>
       <c r="AH134" s="19" t="n"/>
       <c r="AI134" s="19" t="n"/>
       <c r="AJ134" s="19" t="n"/>
       <c r="AK134" s="19" t="n"/>
-      <c r="AL134" s="16" t="inlineStr">
+      <c r="AL134" s="19" t="n"/>
+      <c r="AM134" s="16" t="inlineStr">
         <is>
           <t>2 Teppiche, Maße vom Erfassungsblatt.</t>
         </is>
       </c>
-      <c r="AM134" s="22" t="n"/>
+      <c r="AN134" s="22" t="n"/>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="15" t="inlineStr">
@@ -17384,23 +17598,24 @@
       </c>
       <c r="AB135" s="19" t="n"/>
       <c r="AC135" s="19" t="n"/>
-      <c r="AD135" s="20" t="n"/>
-      <c r="AE135" s="21">
-        <f>IF(K135="","",K135*AD135)</f>
-        <v/>
-      </c>
-      <c r="AF135" s="19" t="n"/>
+      <c r="AD135" s="19" t="n"/>
+      <c r="AE135" s="20" t="n"/>
+      <c r="AF135" s="21">
+        <f>IF(K135="","",K135*AE135)</f>
+        <v/>
+      </c>
       <c r="AG135" s="19" t="n"/>
       <c r="AH135" s="19" t="n"/>
       <c r="AI135" s="19" t="n"/>
       <c r="AJ135" s="19" t="n"/>
       <c r="AK135" s="19" t="n"/>
-      <c r="AL135" s="16" t="inlineStr">
+      <c r="AL135" s="19" t="n"/>
+      <c r="AM135" s="16" t="inlineStr">
         <is>
           <t>1 Box im Bild</t>
         </is>
       </c>
-      <c r="AM135" s="22" t="n"/>
+      <c r="AN135" s="22" t="n"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="15" t="inlineStr">
@@ -17506,23 +17721,24 @@
       <c r="AA136" s="19" t="n"/>
       <c r="AB136" s="19" t="n"/>
       <c r="AC136" s="19" t="n"/>
-      <c r="AD136" s="20" t="n"/>
-      <c r="AE136" s="21">
-        <f>IF(K136="","",K136*AD136)</f>
-        <v/>
-      </c>
-      <c r="AF136" s="19" t="n"/>
+      <c r="AD136" s="19" t="n"/>
+      <c r="AE136" s="20" t="n"/>
+      <c r="AF136" s="21">
+        <f>IF(K136="","",K136*AE136)</f>
+        <v/>
+      </c>
       <c r="AG136" s="19" t="n"/>
       <c r="AH136" s="19" t="n"/>
       <c r="AI136" s="19" t="n"/>
       <c r="AJ136" s="19" t="n"/>
       <c r="AK136" s="19" t="n"/>
-      <c r="AL136" s="16" t="inlineStr">
+      <c r="AL136" s="19" t="n"/>
+      <c r="AM136" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AM136" s="22" t="n"/>
+      <c r="AN136" s="22" t="n"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="15" t="inlineStr">
@@ -17628,23 +17844,24 @@
       <c r="AA137" s="19" t="n"/>
       <c r="AB137" s="19" t="n"/>
       <c r="AC137" s="19" t="n"/>
-      <c r="AD137" s="20" t="n"/>
-      <c r="AE137" s="21">
-        <f>IF(K137="","",K137*AD137)</f>
-        <v/>
-      </c>
-      <c r="AF137" s="19" t="n"/>
+      <c r="AD137" s="19" t="n"/>
+      <c r="AE137" s="20" t="n"/>
+      <c r="AF137" s="21">
+        <f>IF(K137="","",K137*AE137)</f>
+        <v/>
+      </c>
       <c r="AG137" s="19" t="n"/>
       <c r="AH137" s="19" t="n"/>
       <c r="AI137" s="19" t="n"/>
       <c r="AJ137" s="19" t="n"/>
       <c r="AK137" s="19" t="n"/>
-      <c r="AL137" s="16" t="inlineStr">
+      <c r="AL137" s="19" t="n"/>
+      <c r="AM137" s="16" t="inlineStr">
         <is>
           <t>4 Stück im Bild</t>
         </is>
       </c>
-      <c r="AM137" s="22" t="n"/>
+      <c r="AN137" s="22" t="n"/>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="15" t="inlineStr">
@@ -17758,23 +17975,24 @@
       </c>
       <c r="AB138" s="19" t="n"/>
       <c r="AC138" s="19" t="n"/>
-      <c r="AD138" s="20" t="n"/>
-      <c r="AE138" s="21">
-        <f>IF(K138="","",K138*AD138)</f>
-        <v/>
-      </c>
-      <c r="AF138" s="19" t="n"/>
+      <c r="AD138" s="19" t="n"/>
+      <c r="AE138" s="20" t="n"/>
+      <c r="AF138" s="21">
+        <f>IF(K138="","",K138*AE138)</f>
+        <v/>
+      </c>
       <c r="AG138" s="19" t="n"/>
       <c r="AH138" s="19" t="n"/>
       <c r="AI138" s="19" t="n"/>
       <c r="AJ138" s="19" t="n"/>
       <c r="AK138" s="19" t="n"/>
-      <c r="AL138" s="16" t="inlineStr">
+      <c r="AL138" s="19" t="n"/>
+      <c r="AM138" s="16" t="inlineStr">
         <is>
           <t>1 Grill im Bild</t>
         </is>
       </c>
-      <c r="AM138" s="22" t="n"/>
+      <c r="AN138" s="22" t="n"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="15" t="inlineStr">
@@ -17880,23 +18098,24 @@
       <c r="AA139" s="19" t="n"/>
       <c r="AB139" s="19" t="n"/>
       <c r="AC139" s="19" t="n"/>
-      <c r="AD139" s="20" t="n"/>
-      <c r="AE139" s="21">
-        <f>IF(K139="","",K139*AD139)</f>
-        <v/>
-      </c>
-      <c r="AF139" s="19" t="n"/>
+      <c r="AD139" s="19" t="n"/>
+      <c r="AE139" s="20" t="n"/>
+      <c r="AF139" s="21">
+        <f>IF(K139="","",K139*AE139)</f>
+        <v/>
+      </c>
       <c r="AG139" s="19" t="n"/>
       <c r="AH139" s="19" t="n"/>
       <c r="AI139" s="19" t="n"/>
       <c r="AJ139" s="19" t="n"/>
       <c r="AK139" s="19" t="n"/>
-      <c r="AL139" s="16" t="inlineStr">
+      <c r="AL139" s="19" t="n"/>
+      <c r="AM139" s="16" t="inlineStr">
         <is>
           <t>1 Schirm im Bild</t>
         </is>
       </c>
-      <c r="AM139" s="22" t="n"/>
+      <c r="AN139" s="22" t="n"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="15" t="inlineStr">
@@ -18002,23 +18221,24 @@
       <c r="AA140" s="19" t="n"/>
       <c r="AB140" s="19" t="n"/>
       <c r="AC140" s="19" t="n"/>
-      <c r="AD140" s="20" t="n"/>
-      <c r="AE140" s="21">
-        <f>IF(K140="","",K140*AD140)</f>
-        <v/>
-      </c>
-      <c r="AF140" s="19" t="n"/>
+      <c r="AD140" s="19" t="n"/>
+      <c r="AE140" s="20" t="n"/>
+      <c r="AF140" s="21">
+        <f>IF(K140="","",K140*AE140)</f>
+        <v/>
+      </c>
       <c r="AG140" s="19" t="n"/>
       <c r="AH140" s="19" t="n"/>
       <c r="AI140" s="19" t="n"/>
       <c r="AJ140" s="19" t="n"/>
       <c r="AK140" s="19" t="n"/>
-      <c r="AL140" s="16" t="inlineStr">
+      <c r="AL140" s="19" t="n"/>
+      <c r="AM140" s="16" t="inlineStr">
         <is>
           <t>3 Kübel im Bild</t>
         </is>
       </c>
-      <c r="AM140" s="22" t="n"/>
+      <c r="AN140" s="22" t="n"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="15" t="inlineStr">
@@ -18124,23 +18344,24 @@
       <c r="AA141" s="19" t="n"/>
       <c r="AB141" s="19" t="n"/>
       <c r="AC141" s="19" t="n"/>
-      <c r="AD141" s="20" t="n"/>
-      <c r="AE141" s="21">
-        <f>IF(K141="","",K141*AD141)</f>
-        <v/>
-      </c>
-      <c r="AF141" s="19" t="n"/>
+      <c r="AD141" s="19" t="n"/>
+      <c r="AE141" s="20" t="n"/>
+      <c r="AF141" s="21">
+        <f>IF(K141="","",K141*AE141)</f>
+        <v/>
+      </c>
       <c r="AG141" s="19" t="n"/>
       <c r="AH141" s="19" t="n"/>
       <c r="AI141" s="19" t="n"/>
       <c r="AJ141" s="19" t="n"/>
       <c r="AK141" s="19" t="n"/>
-      <c r="AL141" s="16" t="inlineStr">
+      <c r="AL141" s="19" t="n"/>
+      <c r="AM141" s="16" t="inlineStr">
         <is>
           <t>4 Stück gestapelt im Bild</t>
         </is>
       </c>
-      <c r="AM141" s="22" t="n"/>
+      <c r="AN141" s="22" t="n"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="15" t="inlineStr">
@@ -18246,23 +18467,24 @@
       <c r="AA142" s="19" t="n"/>
       <c r="AB142" s="19" t="n"/>
       <c r="AC142" s="19" t="n"/>
-      <c r="AD142" s="20" t="n"/>
-      <c r="AE142" s="21">
-        <f>IF(K142="","",K142*AD142)</f>
-        <v/>
-      </c>
-      <c r="AF142" s="19" t="n"/>
+      <c r="AD142" s="19" t="n"/>
+      <c r="AE142" s="20" t="n"/>
+      <c r="AF142" s="21">
+        <f>IF(K142="","",K142*AE142)</f>
+        <v/>
+      </c>
       <c r="AG142" s="19" t="n"/>
       <c r="AH142" s="19" t="n"/>
       <c r="AI142" s="19" t="n"/>
       <c r="AJ142" s="19" t="n"/>
       <c r="AK142" s="19" t="n"/>
-      <c r="AL142" s="16" t="inlineStr">
+      <c r="AL142" s="19" t="n"/>
+      <c r="AM142" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AM142" s="22" t="n"/>
+      <c r="AN142" s="22" t="n"/>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="15" t="inlineStr">
@@ -18368,23 +18590,24 @@
       <c r="AA143" s="19" t="n"/>
       <c r="AB143" s="19" t="n"/>
       <c r="AC143" s="19" t="n"/>
-      <c r="AD143" s="20" t="n"/>
-      <c r="AE143" s="21">
-        <f>IF(K143="","",K143*AD143)</f>
-        <v/>
-      </c>
-      <c r="AF143" s="19" t="n"/>
+      <c r="AD143" s="19" t="n"/>
+      <c r="AE143" s="20" t="n"/>
+      <c r="AF143" s="21">
+        <f>IF(K143="","",K143*AE143)</f>
+        <v/>
+      </c>
       <c r="AG143" s="19" t="n"/>
       <c r="AH143" s="19" t="n"/>
       <c r="AI143" s="19" t="n"/>
       <c r="AJ143" s="19" t="n"/>
       <c r="AK143" s="19" t="n"/>
-      <c r="AL143" s="16" t="inlineStr">
+      <c r="AL143" s="19" t="n"/>
+      <c r="AM143" s="16" t="inlineStr">
         <is>
           <t>1 Tisch im Bild</t>
         </is>
       </c>
-      <c r="AM143" s="22" t="n"/>
+      <c r="AN143" s="22" t="n"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="15" t="inlineStr">
@@ -18490,23 +18713,24 @@
       <c r="AA144" s="19" t="n"/>
       <c r="AB144" s="19" t="n"/>
       <c r="AC144" s="19" t="n"/>
-      <c r="AD144" s="20" t="n"/>
-      <c r="AE144" s="21">
-        <f>IF(K144="","",K144*AD144)</f>
-        <v/>
-      </c>
-      <c r="AF144" s="19" t="n"/>
+      <c r="AD144" s="19" t="n"/>
+      <c r="AE144" s="20" t="n"/>
+      <c r="AF144" s="21">
+        <f>IF(K144="","",K144*AE144)</f>
+        <v/>
+      </c>
       <c r="AG144" s="19" t="n"/>
       <c r="AH144" s="19" t="n"/>
       <c r="AI144" s="19" t="n"/>
       <c r="AJ144" s="19" t="n"/>
       <c r="AK144" s="19" t="n"/>
-      <c r="AL144" s="16" t="inlineStr">
+      <c r="AL144" s="19" t="n"/>
+      <c r="AM144" s="16" t="inlineStr">
         <is>
           <t>1 Kübel im Bild</t>
         </is>
       </c>
-      <c r="AM144" s="22" t="n"/>
+      <c r="AN144" s="22" t="n"/>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="15" t="inlineStr">
@@ -18612,23 +18836,24 @@
       <c r="AA145" s="19" t="n"/>
       <c r="AB145" s="19" t="n"/>
       <c r="AC145" s="19" t="n"/>
-      <c r="AD145" s="20" t="n"/>
-      <c r="AE145" s="21">
-        <f>IF(K145="","",K145*AD145)</f>
-        <v/>
-      </c>
-      <c r="AF145" s="19" t="n"/>
+      <c r="AD145" s="19" t="n"/>
+      <c r="AE145" s="20" t="n"/>
+      <c r="AF145" s="21">
+        <f>IF(K145="","",K145*AE145)</f>
+        <v/>
+      </c>
       <c r="AG145" s="19" t="n"/>
       <c r="AH145" s="19" t="n"/>
       <c r="AI145" s="19" t="n"/>
       <c r="AJ145" s="19" t="n"/>
       <c r="AK145" s="19" t="n"/>
-      <c r="AL145" s="16" t="inlineStr">
+      <c r="AL145" s="19" t="n"/>
+      <c r="AM145" s="16" t="inlineStr">
         <is>
           <t>1 Stern im Bild</t>
         </is>
       </c>
-      <c r="AM145" s="22" t="n"/>
+      <c r="AN145" s="22" t="n"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="15" t="inlineStr">
@@ -18730,23 +18955,24 @@
       <c r="AA146" s="19" t="n"/>
       <c r="AB146" s="19" t="n"/>
       <c r="AC146" s="19" t="n"/>
-      <c r="AD146" s="20" t="n"/>
-      <c r="AE146" s="21">
-        <f>IF(K146="","",K146*AD146)</f>
-        <v/>
-      </c>
-      <c r="AF146" s="19" t="n"/>
+      <c r="AD146" s="19" t="n"/>
+      <c r="AE146" s="20" t="n"/>
+      <c r="AF146" s="21">
+        <f>IF(K146="","",K146*AE146)</f>
+        <v/>
+      </c>
       <c r="AG146" s="19" t="n"/>
       <c r="AH146" s="19" t="n"/>
       <c r="AI146" s="19" t="n"/>
       <c r="AJ146" s="19" t="n"/>
       <c r="AK146" s="19" t="n"/>
-      <c r="AL146" s="16" t="inlineStr">
+      <c r="AL146" s="19" t="n"/>
+      <c r="AM146" s="16" t="inlineStr">
         <is>
           <t>1 Vitrine. Die Dekoration darin ist Position NU01-03 und wird getrennt verkauft.</t>
         </is>
       </c>
-      <c r="AM146" s="22" t="inlineStr">
+      <c r="AN146" s="22" t="inlineStr">
         <is>
           <t>Personenfotos in der Vitrine sind im Bild maskiert (so gewollt).</t>
         </is>
@@ -18759,7 +18985,11 @@
         </is>
       </c>
       <c r="B147" s="15" t="n"/>
-      <c r="C147" s="15" t="n"/>
+      <c r="C147" s="15" t="inlineStr">
+        <is>
+          <t>BA02-01</t>
+        </is>
+      </c>
       <c r="D147" s="15" t="inlineStr">
         <is>
           <t>NU01</t>
@@ -18791,7 +19021,7 @@
         </is>
       </c>
       <c r="J147" s="17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K147" s="17" t="n"/>
       <c r="L147" s="18">
@@ -18852,23 +19082,28 @@
       <c r="AA147" s="19" t="n"/>
       <c r="AB147" s="19" t="n"/>
       <c r="AC147" s="19" t="n"/>
-      <c r="AD147" s="20" t="n"/>
-      <c r="AE147" s="21">
-        <f>IF(K147="","",K147*AD147)</f>
-        <v/>
-      </c>
-      <c r="AF147" s="19" t="n"/>
+      <c r="AD147" s="19" t="n"/>
+      <c r="AE147" s="20" t="n"/>
+      <c r="AF147" s="21">
+        <f>IF(K147="","",K147*AE147)</f>
+        <v/>
+      </c>
       <c r="AG147" s="19" t="n"/>
       <c r="AH147" s="19" t="n"/>
       <c r="AI147" s="19" t="n"/>
       <c r="AJ147" s="19" t="n"/>
       <c r="AK147" s="19" t="n"/>
-      <c r="AL147" s="16" t="inlineStr">
-        <is>
-          <t>5 gleiche Einheiten laut Erfassungsblatt – abgebildet ist eine davon.</t>
-        </is>
-      </c>
-      <c r="AM147" s="22" t="n"/>
+      <c r="AL147" s="19" t="n"/>
+      <c r="AM147" s="16" t="inlineStr">
+        <is>
+          <t>10 Garderoben insgesamt: 5 im Flur des Neubaus (NU01-14) und 5 im Flur 2 des Bestandsgebäudes (dort mit BA02-01 beschriftet). Abgebildet ist eine davon, eine zweite auf Foto F-272.</t>
+        </is>
+      </c>
+      <c r="AN147" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA02-01.</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="15" t="inlineStr">
@@ -18970,23 +19205,24 @@
       <c r="AA148" s="19" t="n"/>
       <c r="AB148" s="19" t="n"/>
       <c r="AC148" s="19" t="n"/>
-      <c r="AD148" s="20" t="n"/>
-      <c r="AE148" s="21">
-        <f>IF(K148="","",K148*AD148)</f>
-        <v/>
-      </c>
-      <c r="AF148" s="19" t="n"/>
+      <c r="AD148" s="19" t="n"/>
+      <c r="AE148" s="20" t="n"/>
+      <c r="AF148" s="21">
+        <f>IF(K148="","",K148*AE148)</f>
+        <v/>
+      </c>
       <c r="AG148" s="19" t="n"/>
       <c r="AH148" s="19" t="n"/>
       <c r="AI148" s="19" t="n"/>
       <c r="AJ148" s="19" t="n"/>
       <c r="AK148" s="19" t="n"/>
-      <c r="AL148" s="16" t="inlineStr">
+      <c r="AL148" s="19" t="n"/>
+      <c r="AM148" s="16" t="inlineStr">
         <is>
           <t>4 gleiche Schränke laut Erfassungsblatt – abgebildet ist die Schrankwand im Ganzen.</t>
         </is>
       </c>
-      <c r="AM148" s="22" t="n"/>
+      <c r="AN148" s="22" t="n"/>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="15" t="inlineStr">
@@ -19096,23 +19332,24 @@
       </c>
       <c r="AB149" s="19" t="n"/>
       <c r="AC149" s="19" t="n"/>
-      <c r="AD149" s="20" t="n"/>
-      <c r="AE149" s="21">
-        <f>IF(K149="","",K149*AD149)</f>
-        <v/>
-      </c>
-      <c r="AF149" s="19" t="n"/>
+      <c r="AD149" s="19" t="n"/>
+      <c r="AE149" s="20" t="n"/>
+      <c r="AF149" s="21">
+        <f>IF(K149="","",K149*AE149)</f>
+        <v/>
+      </c>
       <c r="AG149" s="19" t="n"/>
       <c r="AH149" s="19" t="n"/>
       <c r="AI149" s="19" t="n"/>
       <c r="AJ149" s="19" t="n"/>
       <c r="AK149" s="19" t="n"/>
-      <c r="AL149" s="16" t="inlineStr">
+      <c r="AL149" s="19" t="n"/>
+      <c r="AM149" s="16" t="inlineStr">
         <is>
           <t>1 Gerät. Typenschild ist abfotografiert (Foto F-121).</t>
         </is>
       </c>
-      <c r="AM149" s="22" t="n"/>
+      <c r="AN149" s="22" t="n"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="15" t="inlineStr">
@@ -19218,23 +19455,24 @@
       </c>
       <c r="AB150" s="19" t="n"/>
       <c r="AC150" s="19" t="n"/>
-      <c r="AD150" s="20" t="n"/>
-      <c r="AE150" s="21">
-        <f>IF(K150="","",K150*AD150)</f>
-        <v/>
-      </c>
-      <c r="AF150" s="19" t="n"/>
+      <c r="AD150" s="19" t="n"/>
+      <c r="AE150" s="20" t="n"/>
+      <c r="AF150" s="21">
+        <f>IF(K150="","",K150*AE150)</f>
+        <v/>
+      </c>
       <c r="AG150" s="19" t="n"/>
       <c r="AH150" s="19" t="n"/>
       <c r="AI150" s="19" t="n"/>
       <c r="AJ150" s="19" t="n"/>
       <c r="AK150" s="19" t="n"/>
-      <c r="AL150" s="16" t="inlineStr">
+      <c r="AL150" s="19" t="n"/>
+      <c r="AM150" s="16" t="inlineStr">
         <is>
           <t>1 Gerät. Typenschild ist abfotografiert (Foto F-122).</t>
         </is>
       </c>
-      <c r="AM150" s="22" t="n"/>
+      <c r="AN150" s="22" t="n"/>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="15" t="inlineStr">
@@ -19340,23 +19578,24 @@
       </c>
       <c r="AB151" s="19" t="n"/>
       <c r="AC151" s="19" t="n"/>
-      <c r="AD151" s="20" t="n"/>
-      <c r="AE151" s="21">
-        <f>IF(K151="","",K151*AD151)</f>
-        <v/>
-      </c>
-      <c r="AF151" s="19" t="n"/>
+      <c r="AD151" s="19" t="n"/>
+      <c r="AE151" s="20" t="n"/>
+      <c r="AF151" s="21">
+        <f>IF(K151="","",K151*AE151)</f>
+        <v/>
+      </c>
       <c r="AG151" s="19" t="n"/>
       <c r="AH151" s="19" t="n"/>
       <c r="AI151" s="19" t="n"/>
       <c r="AJ151" s="19" t="n"/>
       <c r="AK151" s="19" t="n"/>
-      <c r="AL151" s="16" t="inlineStr">
+      <c r="AL151" s="19" t="n"/>
+      <c r="AM151" s="16" t="inlineStr">
         <is>
           <t>1 Gerät. Typenschild ist abfotografiert (Foto F-124).</t>
         </is>
       </c>
-      <c r="AM151" s="22" t="n"/>
+      <c r="AN151" s="22" t="n"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="15" t="inlineStr">
@@ -19458,23 +19697,24 @@
       <c r="AA152" s="19" t="n"/>
       <c r="AB152" s="19" t="n"/>
       <c r="AC152" s="19" t="n"/>
-      <c r="AD152" s="20" t="n"/>
-      <c r="AE152" s="21">
-        <f>IF(K152="","",K152*AD152)</f>
-        <v/>
-      </c>
-      <c r="AF152" s="19" t="n"/>
+      <c r="AD152" s="19" t="n"/>
+      <c r="AE152" s="20" t="n"/>
+      <c r="AF152" s="21">
+        <f>IF(K152="","",K152*AE152)</f>
+        <v/>
+      </c>
       <c r="AG152" s="19" t="n"/>
       <c r="AH152" s="19" t="n"/>
       <c r="AI152" s="19" t="n"/>
       <c r="AJ152" s="19" t="n"/>
       <c r="AK152" s="19" t="n"/>
-      <c r="AL152" s="16" t="inlineStr">
+      <c r="AL152" s="19" t="n"/>
+      <c r="AM152" s="16" t="inlineStr">
         <is>
           <t>4 gleiche Garderoben, jede aus Wandelement und Sitzbank – abgebildet ist eine davon.</t>
         </is>
       </c>
-      <c r="AM152" s="22" t="n"/>
+      <c r="AN152" s="22" t="n"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="15" t="inlineStr">
@@ -19576,23 +19816,24 @@
       <c r="AA153" s="19" t="n"/>
       <c r="AB153" s="19" t="n"/>
       <c r="AC153" s="19" t="n"/>
-      <c r="AD153" s="20" t="n"/>
-      <c r="AE153" s="21">
-        <f>IF(K153="","",K153*AD153)</f>
-        <v/>
-      </c>
-      <c r="AF153" s="19" t="n"/>
+      <c r="AD153" s="19" t="n"/>
+      <c r="AE153" s="20" t="n"/>
+      <c r="AF153" s="21">
+        <f>IF(K153="","",K153*AE153)</f>
+        <v/>
+      </c>
       <c r="AG153" s="19" t="n"/>
       <c r="AH153" s="19" t="n"/>
       <c r="AI153" s="19" t="n"/>
       <c r="AJ153" s="19" t="n"/>
       <c r="AK153" s="19" t="n"/>
-      <c r="AL153" s="16" t="inlineStr">
+      <c r="AL153" s="19" t="n"/>
+      <c r="AM153" s="16" t="inlineStr">
         <is>
           <t>2 Sessel, beide abgebildet.</t>
         </is>
       </c>
-      <c r="AM153" s="22" t="n"/>
+      <c r="AN153" s="22" t="n"/>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="15" t="inlineStr">
@@ -19698,23 +19939,24 @@
       </c>
       <c r="AB154" s="19" t="n"/>
       <c r="AC154" s="19" t="n"/>
-      <c r="AD154" s="20" t="n"/>
-      <c r="AE154" s="21">
-        <f>IF(K154="","",K154*AD154)</f>
-        <v/>
-      </c>
-      <c r="AF154" s="19" t="n"/>
+      <c r="AD154" s="19" t="n"/>
+      <c r="AE154" s="20" t="n"/>
+      <c r="AF154" s="21">
+        <f>IF(K154="","",K154*AE154)</f>
+        <v/>
+      </c>
       <c r="AG154" s="19" t="n"/>
       <c r="AH154" s="19" t="n"/>
       <c r="AI154" s="19" t="n"/>
       <c r="AJ154" s="19" t="n"/>
       <c r="AK154" s="19" t="n"/>
-      <c r="AL154" s="16" t="inlineStr">
+      <c r="AL154" s="19" t="n"/>
+      <c r="AM154" s="16" t="inlineStr">
         <is>
           <t>1 Leuchte, das große Exemplar.</t>
         </is>
       </c>
-      <c r="AM154" s="22" t="n"/>
+      <c r="AN154" s="22" t="n"/>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="15" t="inlineStr">
@@ -19820,23 +20062,24 @@
       </c>
       <c r="AB155" s="19" t="n"/>
       <c r="AC155" s="19" t="n"/>
-      <c r="AD155" s="20" t="n"/>
-      <c r="AE155" s="21">
-        <f>IF(K155="","",K155*AD155)</f>
-        <v/>
-      </c>
-      <c r="AF155" s="19" t="n"/>
+      <c r="AD155" s="19" t="n"/>
+      <c r="AE155" s="20" t="n"/>
+      <c r="AF155" s="21">
+        <f>IF(K155="","",K155*AE155)</f>
+        <v/>
+      </c>
       <c r="AG155" s="19" t="n"/>
       <c r="AH155" s="19" t="n"/>
       <c r="AI155" s="19" t="n"/>
       <c r="AJ155" s="19" t="n"/>
       <c r="AK155" s="19" t="n"/>
-      <c r="AL155" s="16" t="inlineStr">
+      <c r="AL155" s="19" t="n"/>
+      <c r="AM155" s="16" t="inlineStr">
         <is>
           <t>3 gleiche Leuchten in der kleinen Ausführung – abgebildet ist eine davon.</t>
         </is>
       </c>
-      <c r="AM155" s="22" t="n"/>
+      <c r="AN155" s="22" t="n"/>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="15" t="inlineStr">
@@ -19946,23 +20189,24 @@
       </c>
       <c r="AB156" s="19" t="n"/>
       <c r="AC156" s="19" t="n"/>
-      <c r="AD156" s="20" t="n"/>
-      <c r="AE156" s="21">
-        <f>IF(K156="","",K156*AD156)</f>
-        <v/>
-      </c>
-      <c r="AF156" s="19" t="n"/>
+      <c r="AD156" s="19" t="n"/>
+      <c r="AE156" s="20" t="n"/>
+      <c r="AF156" s="21">
+        <f>IF(K156="","",K156*AE156)</f>
+        <v/>
+      </c>
       <c r="AG156" s="19" t="n"/>
       <c r="AH156" s="19" t="n"/>
       <c r="AI156" s="19" t="n"/>
       <c r="AJ156" s="19" t="n"/>
       <c r="AK156" s="19" t="n"/>
-      <c r="AL156" s="16" t="inlineStr">
+      <c r="AL156" s="19" t="n"/>
+      <c r="AM156" s="16" t="inlineStr">
         <is>
           <t>16 Stühle insgesamt: 10 im Gruppenraum 5 und im Nachbarraum NU03, 6 im Schlafraum 5 (dort mit NU04-12 beschriftet).</t>
         </is>
       </c>
-      <c r="AM156" s="22" t="inlineStr">
+      <c r="AN156" s="22" t="inlineStr">
         <is>
           <t>Zusammengefasste Position ueber drei Raeume. Post-it-Nummer im Schlafraum 5: NU04-12. In NU03 nicht erneut anlegen.</t>
         </is>
@@ -20068,23 +20312,24 @@
       <c r="AA157" s="19" t="n"/>
       <c r="AB157" s="19" t="n"/>
       <c r="AC157" s="19" t="n"/>
-      <c r="AD157" s="20" t="n"/>
-      <c r="AE157" s="21">
-        <f>IF(K157="","",K157*AD157)</f>
-        <v/>
-      </c>
-      <c r="AF157" s="19" t="n"/>
+      <c r="AD157" s="19" t="n"/>
+      <c r="AE157" s="20" t="n"/>
+      <c r="AF157" s="21">
+        <f>IF(K157="","",K157*AE157)</f>
+        <v/>
+      </c>
       <c r="AG157" s="19" t="n"/>
       <c r="AH157" s="19" t="n"/>
       <c r="AI157" s="19" t="n"/>
       <c r="AJ157" s="19" t="n"/>
       <c r="AK157" s="19" t="n"/>
-      <c r="AL157" s="16" t="inlineStr">
+      <c r="AL157" s="19" t="n"/>
+      <c r="AM157" s="16" t="inlineStr">
         <is>
           <t>2 Tische – abgebildet ist einer davon von oben.</t>
         </is>
       </c>
-      <c r="AM157" s="22" t="inlineStr">
+      <c r="AN157" s="22" t="inlineStr">
         <is>
           <t>Gesamtstückzahl über Gruppenraum 5 und den Nachbarraum NU02/NU03 hinweg, so vom Haus gezählt. In NU03 nicht erneut anlegen.</t>
         </is>
@@ -20194,23 +20439,24 @@
       </c>
       <c r="AB158" s="19" t="n"/>
       <c r="AC158" s="19" t="n"/>
-      <c r="AD158" s="20" t="n"/>
-      <c r="AE158" s="21">
-        <f>IF(K158="","",K158*AD158)</f>
-        <v/>
-      </c>
-      <c r="AF158" s="19" t="n"/>
+      <c r="AD158" s="19" t="n"/>
+      <c r="AE158" s="20" t="n"/>
+      <c r="AF158" s="21">
+        <f>IF(K158="","",K158*AE158)</f>
+        <v/>
+      </c>
       <c r="AG158" s="19" t="n"/>
       <c r="AH158" s="19" t="n"/>
       <c r="AI158" s="19" t="n"/>
       <c r="AJ158" s="19" t="n"/>
       <c r="AK158" s="19" t="n"/>
-      <c r="AL158" s="16" t="inlineStr">
+      <c r="AL158" s="19" t="n"/>
+      <c r="AM158" s="16" t="inlineStr">
         <is>
           <t>8 Stück – abgebildet ist einer davon. Das Logo auf der Lehne ist auf Foto F-143 zu sehen.</t>
         </is>
       </c>
-      <c r="AM158" s="22" t="n"/>
+      <c r="AN158" s="22" t="n"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="15" t="inlineStr">
@@ -20312,23 +20558,24 @@
       <c r="AA159" s="19" t="n"/>
       <c r="AB159" s="19" t="n"/>
       <c r="AC159" s="19" t="n"/>
-      <c r="AD159" s="20" t="n"/>
-      <c r="AE159" s="21">
-        <f>IF(K159="","",K159*AD159)</f>
-        <v/>
-      </c>
-      <c r="AF159" s="19" t="n"/>
+      <c r="AD159" s="19" t="n"/>
+      <c r="AE159" s="20" t="n"/>
+      <c r="AF159" s="21">
+        <f>IF(K159="","",K159*AE159)</f>
+        <v/>
+      </c>
       <c r="AG159" s="19" t="n"/>
       <c r="AH159" s="19" t="n"/>
       <c r="AI159" s="19" t="n"/>
       <c r="AJ159" s="19" t="n"/>
       <c r="AK159" s="19" t="n"/>
-      <c r="AL159" s="16" t="inlineStr">
+      <c r="AL159" s="19" t="n"/>
+      <c r="AM159" s="16" t="inlineStr">
         <is>
           <t>4 halbrunde Tische – abgebildet sind zwei zusammengestellt.</t>
         </is>
       </c>
-      <c r="AM159" s="22" t="n"/>
+      <c r="AN159" s="22" t="n"/>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="15" t="inlineStr">
@@ -20430,23 +20677,24 @@
       <c r="AA160" s="19" t="n"/>
       <c r="AB160" s="19" t="n"/>
       <c r="AC160" s="19" t="n"/>
-      <c r="AD160" s="20" t="n"/>
-      <c r="AE160" s="21">
-        <f>IF(K160="","",K160*AD160)</f>
-        <v/>
-      </c>
-      <c r="AF160" s="19" t="n"/>
+      <c r="AD160" s="19" t="n"/>
+      <c r="AE160" s="20" t="n"/>
+      <c r="AF160" s="21">
+        <f>IF(K160="","",K160*AE160)</f>
+        <v/>
+      </c>
       <c r="AG160" s="19" t="n"/>
       <c r="AH160" s="19" t="n"/>
       <c r="AI160" s="19" t="n"/>
       <c r="AJ160" s="19" t="n"/>
       <c r="AK160" s="19" t="n"/>
-      <c r="AL160" s="16" t="inlineStr">
+      <c r="AL160" s="19" t="n"/>
+      <c r="AM160" s="16" t="inlineStr">
         <is>
           <t>2 Tische – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM160" s="22" t="n"/>
+      <c r="AN160" s="22" t="n"/>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="15" t="inlineStr">
@@ -20548,23 +20796,24 @@
       <c r="AA161" s="19" t="n"/>
       <c r="AB161" s="19" t="n"/>
       <c r="AC161" s="19" t="n"/>
-      <c r="AD161" s="20" t="n"/>
-      <c r="AE161" s="21">
-        <f>IF(K161="","",K161*AD161)</f>
-        <v/>
-      </c>
-      <c r="AF161" s="19" t="n"/>
+      <c r="AD161" s="19" t="n"/>
+      <c r="AE161" s="20" t="n"/>
+      <c r="AF161" s="21">
+        <f>IF(K161="","",K161*AE161)</f>
+        <v/>
+      </c>
       <c r="AG161" s="19" t="n"/>
       <c r="AH161" s="19" t="n"/>
       <c r="AI161" s="19" t="n"/>
       <c r="AJ161" s="19" t="n"/>
       <c r="AK161" s="19" t="n"/>
-      <c r="AL161" s="16" t="inlineStr">
+      <c r="AL161" s="19" t="n"/>
+      <c r="AM161" s="16" t="inlineStr">
         <is>
           <t>1 Sessel.</t>
         </is>
       </c>
-      <c r="AM161" s="22" t="n"/>
+      <c r="AN161" s="22" t="n"/>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="15" t="inlineStr">
@@ -20666,23 +20915,24 @@
       <c r="AA162" s="19" t="n"/>
       <c r="AB162" s="19" t="n"/>
       <c r="AC162" s="19" t="n"/>
-      <c r="AD162" s="20" t="n"/>
-      <c r="AE162" s="21">
-        <f>IF(K162="","",K162*AD162)</f>
-        <v/>
-      </c>
-      <c r="AF162" s="19" t="n"/>
+      <c r="AD162" s="19" t="n"/>
+      <c r="AE162" s="20" t="n"/>
+      <c r="AF162" s="21">
+        <f>IF(K162="","",K162*AE162)</f>
+        <v/>
+      </c>
       <c r="AG162" s="19" t="n"/>
       <c r="AH162" s="19" t="n"/>
       <c r="AI162" s="19" t="n"/>
       <c r="AJ162" s="19" t="n"/>
       <c r="AK162" s="19" t="n"/>
-      <c r="AL162" s="16" t="inlineStr">
+      <c r="AL162" s="19" t="n"/>
+      <c r="AM162" s="16" t="inlineStr">
         <is>
           <t>1 Tisch.</t>
         </is>
       </c>
-      <c r="AM162" s="22" t="n"/>
+      <c r="AN162" s="22" t="n"/>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="15" t="inlineStr">
@@ -20784,23 +21034,24 @@
       <c r="AA163" s="19" t="n"/>
       <c r="AB163" s="19" t="n"/>
       <c r="AC163" s="19" t="n"/>
-      <c r="AD163" s="20" t="n"/>
-      <c r="AE163" s="21">
-        <f>IF(K163="","",K163*AD163)</f>
-        <v/>
-      </c>
-      <c r="AF163" s="19" t="n"/>
+      <c r="AD163" s="19" t="n"/>
+      <c r="AE163" s="20" t="n"/>
+      <c r="AF163" s="21">
+        <f>IF(K163="","",K163*AE163)</f>
+        <v/>
+      </c>
       <c r="AG163" s="19" t="n"/>
       <c r="AH163" s="19" t="n"/>
       <c r="AI163" s="19" t="n"/>
       <c r="AJ163" s="19" t="n"/>
       <c r="AK163" s="19" t="n"/>
-      <c r="AL163" s="16" t="inlineStr">
+      <c r="AL163" s="19" t="n"/>
+      <c r="AM163" s="16" t="inlineStr">
         <is>
           <t>1 Tisch.</t>
         </is>
       </c>
-      <c r="AM163" s="22" t="n"/>
+      <c r="AN163" s="22" t="n"/>
     </row>
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="15" t="inlineStr">
@@ -20906,23 +21157,24 @@
       </c>
       <c r="AB164" s="19" t="n"/>
       <c r="AC164" s="19" t="n"/>
-      <c r="AD164" s="20" t="n"/>
-      <c r="AE164" s="21">
-        <f>IF(K164="","",K164*AD164)</f>
-        <v/>
-      </c>
-      <c r="AF164" s="19" t="n"/>
+      <c r="AD164" s="19" t="n"/>
+      <c r="AE164" s="20" t="n"/>
+      <c r="AF164" s="21">
+        <f>IF(K164="","",K164*AE164)</f>
+        <v/>
+      </c>
       <c r="AG164" s="19" t="n"/>
       <c r="AH164" s="19" t="n"/>
       <c r="AI164" s="19" t="n"/>
       <c r="AJ164" s="19" t="n"/>
       <c r="AK164" s="19" t="n"/>
-      <c r="AL164" s="16" t="inlineStr">
+      <c r="AL164" s="19" t="n"/>
+      <c r="AM164" s="16" t="inlineStr">
         <is>
           <t>1 Sitzgruppe, Tisch und Bänke fest verbunden.</t>
         </is>
       </c>
-      <c r="AM164" s="22" t="n"/>
+      <c r="AN164" s="22" t="n"/>
     </row>
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="15" t="inlineStr">
@@ -21028,23 +21280,24 @@
       </c>
       <c r="AB165" s="19" t="n"/>
       <c r="AC165" s="19" t="n"/>
-      <c r="AD165" s="20" t="n"/>
-      <c r="AE165" s="21">
-        <f>IF(K165="","",K165*AD165)</f>
-        <v/>
-      </c>
-      <c r="AF165" s="19" t="n"/>
+      <c r="AD165" s="19" t="n"/>
+      <c r="AE165" s="20" t="n"/>
+      <c r="AF165" s="21">
+        <f>IF(K165="","",K165*AE165)</f>
+        <v/>
+      </c>
       <c r="AG165" s="19" t="n"/>
       <c r="AH165" s="19" t="n"/>
       <c r="AI165" s="19" t="n"/>
       <c r="AJ165" s="19" t="n"/>
       <c r="AK165" s="19" t="n"/>
-      <c r="AL165" s="16" t="inlineStr">
+      <c r="AL165" s="19" t="n"/>
+      <c r="AM165" s="16" t="inlineStr">
         <is>
           <t>1 Set aus einem Tisch und vier Stühlen.</t>
         </is>
       </c>
-      <c r="AM165" s="22" t="n"/>
+      <c r="AN165" s="22" t="n"/>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="15" t="inlineStr">
@@ -21150,23 +21403,24 @@
       </c>
       <c r="AB166" s="19" t="n"/>
       <c r="AC166" s="19" t="n"/>
-      <c r="AD166" s="20" t="n"/>
-      <c r="AE166" s="21">
-        <f>IF(K166="","",K166*AD166)</f>
-        <v/>
-      </c>
-      <c r="AF166" s="19" t="n"/>
+      <c r="AD166" s="19" t="n"/>
+      <c r="AE166" s="20" t="n"/>
+      <c r="AF166" s="21">
+        <f>IF(K166="","",K166*AE166)</f>
+        <v/>
+      </c>
       <c r="AG166" s="19" t="n"/>
       <c r="AH166" s="19" t="n"/>
       <c r="AI166" s="19" t="n"/>
       <c r="AJ166" s="19" t="n"/>
       <c r="AK166" s="19" t="n"/>
-      <c r="AL166" s="16" t="inlineStr">
+      <c r="AL166" s="19" t="n"/>
+      <c r="AM166" s="16" t="inlineStr">
         <is>
           <t>Bisher erfasst: zwei rosa und einer grün. Es gibt sie in weiteren Farben, auch in den Außenanlagen – Stückzahl wird am Ende des Rundgangs zusammengezählt.</t>
         </is>
       </c>
-      <c r="AM166" s="22" t="inlineStr">
+      <c r="AN166" s="22" t="inlineStr">
         <is>
           <t>OFFEN: Stueckzahl und Farben unvollstaendig. Die Nutzerin liefert die restlichen Fotos am Ende des Rundgangs nach; dann wird diese Position auf die Gesamtzahl gebracht und die Post-it-Nummern der anderen Raeume kommen in Weitere_ArtNr.</t>
         </is>
@@ -21272,23 +21526,24 @@
       <c r="AA167" s="19" t="n"/>
       <c r="AB167" s="19" t="n"/>
       <c r="AC167" s="19" t="n"/>
-      <c r="AD167" s="20" t="n"/>
-      <c r="AE167" s="21">
-        <f>IF(K167="","",K167*AD167)</f>
-        <v/>
-      </c>
-      <c r="AF167" s="19" t="n"/>
+      <c r="AD167" s="19" t="n"/>
+      <c r="AE167" s="20" t="n"/>
+      <c r="AF167" s="21">
+        <f>IF(K167="","",K167*AE167)</f>
+        <v/>
+      </c>
       <c r="AG167" s="19" t="n"/>
       <c r="AH167" s="19" t="n"/>
       <c r="AI167" s="19" t="n"/>
       <c r="AJ167" s="19" t="n"/>
       <c r="AK167" s="19" t="n"/>
-      <c r="AL167" s="16" t="inlineStr">
+      <c r="AL167" s="19" t="n"/>
+      <c r="AM167" s="16" t="inlineStr">
         <is>
           <t>1 Stück.</t>
         </is>
       </c>
-      <c r="AM167" s="22" t="n"/>
+      <c r="AN167" s="22" t="n"/>
     </row>
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="15" t="inlineStr">
@@ -21390,23 +21645,24 @@
       <c r="AA168" s="19" t="n"/>
       <c r="AB168" s="19" t="n"/>
       <c r="AC168" s="19" t="n"/>
-      <c r="AD168" s="20" t="n"/>
-      <c r="AE168" s="21">
-        <f>IF(K168="","",K168*AD168)</f>
-        <v/>
-      </c>
-      <c r="AF168" s="19" t="n"/>
+      <c r="AD168" s="19" t="n"/>
+      <c r="AE168" s="20" t="n"/>
+      <c r="AF168" s="21">
+        <f>IF(K168="","",K168*AE168)</f>
+        <v/>
+      </c>
       <c r="AG168" s="19" t="n"/>
       <c r="AH168" s="19" t="n"/>
       <c r="AI168" s="19" t="n"/>
       <c r="AJ168" s="19" t="n"/>
       <c r="AK168" s="19" t="n"/>
-      <c r="AL168" s="16" t="inlineStr">
+      <c r="AL168" s="19" t="n"/>
+      <c r="AM168" s="16" t="inlineStr">
         <is>
           <t>3 Regale – abgebildet sind alle drei übereinander.</t>
         </is>
       </c>
-      <c r="AM168" s="22" t="n"/>
+      <c r="AN168" s="22" t="n"/>
     </row>
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="15" t="inlineStr">
@@ -21508,23 +21764,24 @@
       <c r="AA169" s="19" t="n"/>
       <c r="AB169" s="19" t="n"/>
       <c r="AC169" s="19" t="n"/>
-      <c r="AD169" s="20" t="n"/>
-      <c r="AE169" s="21">
-        <f>IF(K169="","",K169*AD169)</f>
-        <v/>
-      </c>
-      <c r="AF169" s="19" t="n"/>
+      <c r="AD169" s="19" t="n"/>
+      <c r="AE169" s="20" t="n"/>
+      <c r="AF169" s="21">
+        <f>IF(K169="","",K169*AE169)</f>
+        <v/>
+      </c>
       <c r="AG169" s="19" t="n"/>
       <c r="AH169" s="19" t="n"/>
       <c r="AI169" s="19" t="n"/>
       <c r="AJ169" s="19" t="n"/>
       <c r="AK169" s="19" t="n"/>
-      <c r="AL169" s="16" t="inlineStr">
+      <c r="AL169" s="19" t="n"/>
+      <c r="AM169" s="16" t="inlineStr">
         <is>
           <t>2 Regale – abgebildet sind beide.</t>
         </is>
       </c>
-      <c r="AM169" s="22" t="n"/>
+      <c r="AN169" s="22" t="n"/>
     </row>
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="15" t="inlineStr">
@@ -21626,23 +21883,24 @@
       <c r="AA170" s="19" t="n"/>
       <c r="AB170" s="19" t="n"/>
       <c r="AC170" s="19" t="n"/>
-      <c r="AD170" s="20" t="n"/>
-      <c r="AE170" s="21">
-        <f>IF(K170="","",K170*AD170)</f>
-        <v/>
-      </c>
-      <c r="AF170" s="19" t="n"/>
+      <c r="AD170" s="19" t="n"/>
+      <c r="AE170" s="20" t="n"/>
+      <c r="AF170" s="21">
+        <f>IF(K170="","",K170*AE170)</f>
+        <v/>
+      </c>
       <c r="AG170" s="19" t="n"/>
       <c r="AH170" s="19" t="n"/>
       <c r="AI170" s="19" t="n"/>
       <c r="AJ170" s="19" t="n"/>
       <c r="AK170" s="19" t="n"/>
-      <c r="AL170" s="16" t="inlineStr">
+      <c r="AL170" s="19" t="n"/>
+      <c r="AM170" s="16" t="inlineStr">
         <is>
           <t>2 Elefanten, weiß und schwarz. Abgebildet ist der weiße; der schwarze wird nachfotografiert. Ein kleinerer schwarzer folgt als eigene Position.</t>
         </is>
       </c>
-      <c r="AM170" s="22" t="inlineStr">
+      <c r="AN170" s="22" t="inlineStr">
         <is>
           <t>OFFEN: NICHT VEROEFFENTLICHEN, bis die Marke geklaert ist: Form und Signaturplaettchen sprechen fuer einen Vitra Eames Elephant (gebraucht 150-280 EUR je Stueck), ein Nachbau waere 20-40 EUR wert. Nahaufnahme des Plaettchens und der Unterseite steht aus; die Nutzerin liefert sie am Ende des Rundgangs. Der kleinere schwarze wird dann eine eigene Position.</t>
         </is>
@@ -21748,23 +22006,24 @@
       <c r="AA171" s="19" t="n"/>
       <c r="AB171" s="19" t="n"/>
       <c r="AC171" s="19" t="n"/>
-      <c r="AD171" s="20" t="n"/>
-      <c r="AE171" s="21">
-        <f>IF(K171="","",K171*AD171)</f>
-        <v/>
-      </c>
-      <c r="AF171" s="19" t="n"/>
+      <c r="AD171" s="19" t="n"/>
+      <c r="AE171" s="20" t="n"/>
+      <c r="AF171" s="21">
+        <f>IF(K171="","",K171*AE171)</f>
+        <v/>
+      </c>
       <c r="AG171" s="19" t="n"/>
       <c r="AH171" s="19" t="n"/>
       <c r="AI171" s="19" t="n"/>
       <c r="AJ171" s="19" t="n"/>
       <c r="AK171" s="19" t="n"/>
-      <c r="AL171" s="16" t="inlineStr">
+      <c r="AL171" s="19" t="n"/>
+      <c r="AM171" s="16" t="inlineStr">
         <is>
           <t>1 Schrank. Foto F-167 zeigt ihn neben NU02-20, das gibt die Größe.</t>
         </is>
       </c>
-      <c r="AM171" s="22" t="n"/>
+      <c r="AN171" s="22" t="n"/>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="15" t="inlineStr">
@@ -21866,23 +22125,24 @@
       <c r="AA172" s="19" t="n"/>
       <c r="AB172" s="19" t="n"/>
       <c r="AC172" s="19" t="n"/>
-      <c r="AD172" s="20" t="n"/>
-      <c r="AE172" s="21">
-        <f>IF(K172="","",K172*AD172)</f>
-        <v/>
-      </c>
-      <c r="AF172" s="19" t="n"/>
+      <c r="AD172" s="19" t="n"/>
+      <c r="AE172" s="20" t="n"/>
+      <c r="AF172" s="21">
+        <f>IF(K172="","",K172*AE172)</f>
+        <v/>
+      </c>
       <c r="AG172" s="19" t="n"/>
       <c r="AH172" s="19" t="n"/>
       <c r="AI172" s="19" t="n"/>
       <c r="AJ172" s="19" t="n"/>
       <c r="AK172" s="19" t="n"/>
-      <c r="AL172" s="16" t="inlineStr">
+      <c r="AL172" s="19" t="n"/>
+      <c r="AM172" s="16" t="inlineStr">
         <is>
           <t>1 Schrank. Foto F-167 zeigt ihn neben NU02-19, das gibt die Größe.</t>
         </is>
       </c>
-      <c r="AM172" s="22" t="n"/>
+      <c r="AN172" s="22" t="n"/>
     </row>
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="15" t="inlineStr">
@@ -21984,23 +22244,24 @@
       <c r="AA173" s="19" t="n"/>
       <c r="AB173" s="19" t="n"/>
       <c r="AC173" s="19" t="n"/>
-      <c r="AD173" s="20" t="n"/>
-      <c r="AE173" s="21">
-        <f>IF(K173="","",K173*AD173)</f>
-        <v/>
-      </c>
-      <c r="AF173" s="19" t="n"/>
+      <c r="AD173" s="19" t="n"/>
+      <c r="AE173" s="20" t="n"/>
+      <c r="AF173" s="21">
+        <f>IF(K173="","",K173*AE173)</f>
+        <v/>
+      </c>
       <c r="AG173" s="19" t="n"/>
       <c r="AH173" s="19" t="n"/>
       <c r="AI173" s="19" t="n"/>
       <c r="AJ173" s="19" t="n"/>
       <c r="AK173" s="19" t="n"/>
-      <c r="AL173" s="16" t="inlineStr">
+      <c r="AL173" s="19" t="n"/>
+      <c r="AM173" s="16" t="inlineStr">
         <is>
           <t>1 Regal. Der Inhalt gehört nicht dazu.</t>
         </is>
       </c>
-      <c r="AM173" s="22" t="n"/>
+      <c r="AN173" s="22" t="n"/>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="15" t="inlineStr">
@@ -22102,23 +22363,24 @@
       <c r="AA174" s="19" t="n"/>
       <c r="AB174" s="19" t="n"/>
       <c r="AC174" s="19" t="n"/>
-      <c r="AD174" s="20" t="n"/>
-      <c r="AE174" s="21">
-        <f>IF(K174="","",K174*AD174)</f>
-        <v/>
-      </c>
-      <c r="AF174" s="19" t="n"/>
+      <c r="AD174" s="19" t="n"/>
+      <c r="AE174" s="20" t="n"/>
+      <c r="AF174" s="21">
+        <f>IF(K174="","",K174*AE174)</f>
+        <v/>
+      </c>
       <c r="AG174" s="19" t="n"/>
       <c r="AH174" s="19" t="n"/>
       <c r="AI174" s="19" t="n"/>
       <c r="AJ174" s="19" t="n"/>
       <c r="AK174" s="19" t="n"/>
-      <c r="AL174" s="16" t="inlineStr">
+      <c r="AL174" s="19" t="n"/>
+      <c r="AM174" s="16" t="inlineStr">
         <is>
           <t>3 Bilder in unterschiedlichen Formaten: ein großes quadratisches (abgebildet) und zwei kleinere im Querformat, siehe Foto F-170.</t>
         </is>
       </c>
-      <c r="AM174" s="22" t="n"/>
+      <c r="AN174" s="22" t="n"/>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="15" t="inlineStr">
@@ -22220,23 +22482,24 @@
       <c r="AA175" s="19" t="n"/>
       <c r="AB175" s="19" t="n"/>
       <c r="AC175" s="19" t="n"/>
-      <c r="AD175" s="20" t="n"/>
-      <c r="AE175" s="21">
-        <f>IF(K175="","",K175*AD175)</f>
-        <v/>
-      </c>
-      <c r="AF175" s="19" t="n"/>
+      <c r="AD175" s="19" t="n"/>
+      <c r="AE175" s="20" t="n"/>
+      <c r="AF175" s="21">
+        <f>IF(K175="","",K175*AE175)</f>
+        <v/>
+      </c>
       <c r="AG175" s="19" t="n"/>
       <c r="AH175" s="19" t="n"/>
       <c r="AI175" s="19" t="n"/>
       <c r="AJ175" s="19" t="n"/>
       <c r="AK175" s="19" t="n"/>
-      <c r="AL175" s="16" t="inlineStr">
+      <c r="AL175" s="19" t="n"/>
+      <c r="AM175" s="16" t="inlineStr">
         <is>
           <t>1 Tischgruppe aus vier Segmenten.</t>
         </is>
       </c>
-      <c r="AM175" s="22" t="n"/>
+      <c r="AN175" s="22" t="n"/>
     </row>
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="15" t="inlineStr">
@@ -22338,23 +22601,24 @@
       <c r="AA176" s="19" t="n"/>
       <c r="AB176" s="19" t="n"/>
       <c r="AC176" s="19" t="n"/>
-      <c r="AD176" s="20" t="n"/>
-      <c r="AE176" s="21">
-        <f>IF(K176="","",K176*AD176)</f>
-        <v/>
-      </c>
-      <c r="AF176" s="19" t="n"/>
+      <c r="AD176" s="19" t="n"/>
+      <c r="AE176" s="20" t="n"/>
+      <c r="AF176" s="21">
+        <f>IF(K176="","",K176*AE176)</f>
+        <v/>
+      </c>
       <c r="AG176" s="19" t="n"/>
       <c r="AH176" s="19" t="n"/>
       <c r="AI176" s="19" t="n"/>
       <c r="AJ176" s="19" t="n"/>
       <c r="AK176" s="19" t="n"/>
-      <c r="AL176" s="16" t="inlineStr">
+      <c r="AL176" s="19" t="n"/>
+      <c r="AM176" s="16" t="inlineStr">
         <is>
           <t>1 Regal. Der Inhalt (Stiftebecher, Farbkästen, Pinsel) gehört nicht dazu.</t>
         </is>
       </c>
-      <c r="AM176" s="22" t="n"/>
+      <c r="AN176" s="22" t="n"/>
     </row>
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="15" t="inlineStr">
@@ -22456,23 +22720,24 @@
       <c r="AA177" s="19" t="n"/>
       <c r="AB177" s="19" t="n"/>
       <c r="AC177" s="19" t="n"/>
-      <c r="AD177" s="20" t="n"/>
-      <c r="AE177" s="21">
-        <f>IF(K177="","",K177*AD177)</f>
-        <v/>
-      </c>
-      <c r="AF177" s="19" t="n"/>
+      <c r="AD177" s="19" t="n"/>
+      <c r="AE177" s="20" t="n"/>
+      <c r="AF177" s="21">
+        <f>IF(K177="","",K177*AE177)</f>
+        <v/>
+      </c>
       <c r="AG177" s="19" t="n"/>
       <c r="AH177" s="19" t="n"/>
       <c r="AI177" s="19" t="n"/>
       <c r="AJ177" s="19" t="n"/>
       <c r="AK177" s="19" t="n"/>
-      <c r="AL177" s="16" t="inlineStr">
+      <c r="AL177" s="19" t="n"/>
+      <c r="AM177" s="16" t="inlineStr">
         <is>
           <t>4 Betten, alle aufgebaut: 2 im Schlafraum 4 und 2 in einem weiteren Schlafraum.</t>
         </is>
       </c>
-      <c r="AM177" s="22" t="inlineStr">
+      <c r="AN177" s="22" t="inlineStr">
         <is>
           <t>OFFEN: waechst noch. Aus den weiteren Schlafraeumen kommen zusaetzliche Betten dazu - am Ende des Rundgangs auf die Gesamtzahl bringen und die Post-it-Nummern der anderen Raeume in Weitere_ArtNr.</t>
         </is>
@@ -22582,23 +22847,24 @@
       </c>
       <c r="AB178" s="19" t="n"/>
       <c r="AC178" s="19" t="n"/>
-      <c r="AD178" s="20" t="n"/>
-      <c r="AE178" s="21">
-        <f>IF(K178="","",K178*AD178)</f>
-        <v/>
-      </c>
-      <c r="AF178" s="19" t="n"/>
+      <c r="AD178" s="19" t="n"/>
+      <c r="AE178" s="20" t="n"/>
+      <c r="AF178" s="21">
+        <f>IF(K178="","",K178*AE178)</f>
+        <v/>
+      </c>
       <c r="AG178" s="19" t="n"/>
       <c r="AH178" s="19" t="n"/>
       <c r="AI178" s="19" t="n"/>
       <c r="AJ178" s="19" t="n"/>
       <c r="AK178" s="19" t="n"/>
-      <c r="AL178" s="16" t="inlineStr">
+      <c r="AL178" s="19" t="n"/>
+      <c r="AM178" s="16" t="inlineStr">
         <is>
           <t>1 Küche aus 5 Modulen, vom Haus bestätigt. Eine zweite, anders zusammengesetzte Wesco-Küche steht unter NU07-03.</t>
         </is>
       </c>
-      <c r="AM178" s="22" t="inlineStr">
+      <c r="AN178" s="22" t="inlineStr">
         <is>
           <t>Wesco ist institutionelle Qualitaet, neu kostet ein Modul 300-600 EUR. Nach dem Vitra Alcove die wertvollste Position.</t>
         </is>
@@ -22708,23 +22974,24 @@
       </c>
       <c r="AB179" s="19" t="n"/>
       <c r="AC179" s="19" t="n"/>
-      <c r="AD179" s="20" t="n"/>
-      <c r="AE179" s="21">
-        <f>IF(K179="","",K179*AD179)</f>
-        <v/>
-      </c>
-      <c r="AF179" s="19" t="n"/>
+      <c r="AD179" s="19" t="n"/>
+      <c r="AE179" s="20" t="n"/>
+      <c r="AF179" s="21">
+        <f>IF(K179="","",K179*AE179)</f>
+        <v/>
+      </c>
       <c r="AG179" s="19" t="n"/>
       <c r="AH179" s="19" t="n"/>
       <c r="AI179" s="19" t="n"/>
       <c r="AJ179" s="19" t="n"/>
       <c r="AK179" s="19" t="n"/>
-      <c r="AL179" s="16" t="inlineStr">
+      <c r="AL179" s="19" t="n"/>
+      <c r="AM179" s="16" t="inlineStr">
         <is>
           <t>2 Teile: ein Bügelbrett und ein Wäscheständer, beide auf Foto F-178 zu sehen.</t>
         </is>
       </c>
-      <c r="AM179" s="22" t="n"/>
+      <c r="AN179" s="22" t="n"/>
     </row>
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="15" t="inlineStr">
@@ -22830,23 +23097,24 @@
       </c>
       <c r="AB180" s="19" t="n"/>
       <c r="AC180" s="19" t="n"/>
-      <c r="AD180" s="20" t="n"/>
-      <c r="AE180" s="21">
-        <f>IF(K180="","",K180*AD180)</f>
-        <v/>
-      </c>
-      <c r="AF180" s="19" t="n"/>
+      <c r="AD180" s="19" t="n"/>
+      <c r="AE180" s="20" t="n"/>
+      <c r="AF180" s="21">
+        <f>IF(K180="","",K180*AE180)</f>
+        <v/>
+      </c>
       <c r="AG180" s="19" t="n"/>
       <c r="AH180" s="19" t="n"/>
       <c r="AI180" s="19" t="n"/>
       <c r="AJ180" s="19" t="n"/>
       <c r="AK180" s="19" t="n"/>
-      <c r="AL180" s="16" t="inlineStr">
+      <c r="AL180" s="19" t="n"/>
+      <c r="AM180" s="16" t="inlineStr">
         <is>
           <t>1 Sessel.</t>
         </is>
       </c>
-      <c r="AM180" s="22" t="n"/>
+      <c r="AN180" s="22" t="n"/>
     </row>
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="15" t="inlineStr">
@@ -22948,23 +23216,24 @@
       <c r="AA181" s="19" t="n"/>
       <c r="AB181" s="19" t="n"/>
       <c r="AC181" s="19" t="n"/>
-      <c r="AD181" s="20" t="n"/>
-      <c r="AE181" s="21">
-        <f>IF(K181="","",K181*AD181)</f>
-        <v/>
-      </c>
-      <c r="AF181" s="19" t="n"/>
+      <c r="AD181" s="19" t="n"/>
+      <c r="AE181" s="20" t="n"/>
+      <c r="AF181" s="21">
+        <f>IF(K181="","",K181*AE181)</f>
+        <v/>
+      </c>
       <c r="AG181" s="19" t="n"/>
       <c r="AH181" s="19" t="n"/>
       <c r="AI181" s="19" t="n"/>
       <c r="AJ181" s="19" t="n"/>
       <c r="AK181" s="19" t="n"/>
-      <c r="AL181" s="16" t="inlineStr">
+      <c r="AL181" s="19" t="n"/>
+      <c r="AM181" s="16" t="inlineStr">
         <is>
           <t>2 Regale – abgebildet ist eines davon.</t>
         </is>
       </c>
-      <c r="AM181" s="22" t="n"/>
+      <c r="AN181" s="22" t="n"/>
     </row>
     <row r="182" ht="30" customHeight="1">
       <c r="A182" s="15" t="inlineStr">
@@ -23066,23 +23335,24 @@
       <c r="AA182" s="19" t="n"/>
       <c r="AB182" s="19" t="n"/>
       <c r="AC182" s="19" t="n"/>
-      <c r="AD182" s="20" t="n"/>
-      <c r="AE182" s="21">
-        <f>IF(K182="","",K182*AD182)</f>
-        <v/>
-      </c>
-      <c r="AF182" s="19" t="n"/>
+      <c r="AD182" s="19" t="n"/>
+      <c r="AE182" s="20" t="n"/>
+      <c r="AF182" s="21">
+        <f>IF(K182="","",K182*AE182)</f>
+        <v/>
+      </c>
       <c r="AG182" s="19" t="n"/>
       <c r="AH182" s="19" t="n"/>
       <c r="AI182" s="19" t="n"/>
       <c r="AJ182" s="19" t="n"/>
       <c r="AK182" s="19" t="n"/>
-      <c r="AL182" s="16" t="inlineStr">
+      <c r="AL182" s="19" t="n"/>
+      <c r="AM182" s="16" t="inlineStr">
         <is>
           <t>1 Regal. Der Inhalt gehört nicht dazu.</t>
         </is>
       </c>
-      <c r="AM182" s="22" t="n"/>
+      <c r="AN182" s="22" t="n"/>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="15" t="inlineStr">
@@ -23188,23 +23458,24 @@
       </c>
       <c r="AB183" s="19" t="n"/>
       <c r="AC183" s="19" t="n"/>
-      <c r="AD183" s="20" t="n"/>
-      <c r="AE183" s="21">
-        <f>IF(K183="","",K183*AD183)</f>
-        <v/>
-      </c>
-      <c r="AF183" s="19" t="n"/>
+      <c r="AD183" s="19" t="n"/>
+      <c r="AE183" s="20" t="n"/>
+      <c r="AF183" s="21">
+        <f>IF(K183="","",K183*AE183)</f>
+        <v/>
+      </c>
       <c r="AG183" s="19" t="n"/>
       <c r="AH183" s="19" t="n"/>
       <c r="AI183" s="19" t="n"/>
       <c r="AJ183" s="19" t="n"/>
       <c r="AK183" s="19" t="n"/>
-      <c r="AL183" s="16" t="inlineStr">
+      <c r="AL183" s="19" t="n"/>
+      <c r="AM183" s="16" t="inlineStr">
         <is>
           <t>2 Kommoden – abgebildet ist eine davon, die zweite steht rechts daneben.</t>
         </is>
       </c>
-      <c r="AM183" s="22" t="n"/>
+      <c r="AN183" s="22" t="n"/>
     </row>
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="15" t="inlineStr">
@@ -23306,23 +23577,24 @@
       <c r="AA184" s="19" t="n"/>
       <c r="AB184" s="19" t="n"/>
       <c r="AC184" s="19" t="n"/>
-      <c r="AD184" s="20" t="n"/>
-      <c r="AE184" s="21">
-        <f>IF(K184="","",K184*AD184)</f>
-        <v/>
-      </c>
-      <c r="AF184" s="19" t="n"/>
+      <c r="AD184" s="19" t="n"/>
+      <c r="AE184" s="20" t="n"/>
+      <c r="AF184" s="21">
+        <f>IF(K184="","",K184*AE184)</f>
+        <v/>
+      </c>
       <c r="AG184" s="19" t="n"/>
       <c r="AH184" s="19" t="n"/>
       <c r="AI184" s="19" t="n"/>
       <c r="AJ184" s="19" t="n"/>
       <c r="AK184" s="19" t="n"/>
-      <c r="AL184" s="16" t="inlineStr">
+      <c r="AL184" s="19" t="n"/>
+      <c r="AM184" s="16" t="inlineStr">
         <is>
           <t>2 Regale einschließlich der eingehängten Wannen – abgebildet ist eines davon. Der Inhalt der Wannen gehört nicht dazu.</t>
         </is>
       </c>
-      <c r="AM184" s="22" t="n"/>
+      <c r="AN184" s="22" t="n"/>
     </row>
     <row r="185" ht="30" customHeight="1">
       <c r="A185" s="15" t="inlineStr">
@@ -23428,23 +23700,24 @@
       </c>
       <c r="AB185" s="19" t="n"/>
       <c r="AC185" s="19" t="n"/>
-      <c r="AD185" s="20" t="n"/>
-      <c r="AE185" s="21">
-        <f>IF(K185="","",K185*AD185)</f>
-        <v/>
-      </c>
-      <c r="AF185" s="19" t="n"/>
+      <c r="AD185" s="19" t="n"/>
+      <c r="AE185" s="20" t="n"/>
+      <c r="AF185" s="21">
+        <f>IF(K185="","",K185*AE185)</f>
+        <v/>
+      </c>
       <c r="AG185" s="19" t="n"/>
       <c r="AH185" s="19" t="n"/>
       <c r="AI185" s="19" t="n"/>
       <c r="AJ185" s="19" t="n"/>
       <c r="AK185" s="19" t="n"/>
-      <c r="AL185" s="16" t="inlineStr">
+      <c r="AL185" s="19" t="n"/>
+      <c r="AM185" s="16" t="inlineStr">
         <is>
           <t>9 Stühle – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM185" s="22" t="inlineStr">
+      <c r="AN185" s="22" t="inlineStr">
         <is>
           <t>OFFEN: waechst noch. Aus weiteren Raeumen kommen zusaetzliche Hochstuehle dazu - am Ende des Rundgangs auf die Gesamtzahl bringen und die Post-it-Nummern der anderen Raeume in Weitere_ArtNr.</t>
         </is>
@@ -23554,23 +23827,24 @@
       </c>
       <c r="AB186" s="19" t="n"/>
       <c r="AC186" s="19" t="n"/>
-      <c r="AD186" s="20" t="n"/>
-      <c r="AE186" s="21">
-        <f>IF(K186="","",K186*AD186)</f>
-        <v/>
-      </c>
-      <c r="AF186" s="19" t="n"/>
+      <c r="AD186" s="19" t="n"/>
+      <c r="AE186" s="20" t="n"/>
+      <c r="AF186" s="21">
+        <f>IF(K186="","",K186*AE186)</f>
+        <v/>
+      </c>
       <c r="AG186" s="19" t="n"/>
       <c r="AH186" s="19" t="n"/>
       <c r="AI186" s="19" t="n"/>
       <c r="AJ186" s="19" t="n"/>
       <c r="AK186" s="19" t="n"/>
-      <c r="AL186" s="16" t="inlineStr">
+      <c r="AL186" s="19" t="n"/>
+      <c r="AM186" s="16" t="inlineStr">
         <is>
           <t>13 Stühle – abgebildet ist einer davon, das Etikett auf Foto F-189.</t>
         </is>
       </c>
-      <c r="AM186" s="22" t="n"/>
+      <c r="AN186" s="22" t="n"/>
     </row>
     <row r="187" ht="30" customHeight="1">
       <c r="A187" s="15" t="inlineStr">
@@ -23676,23 +23950,24 @@
       </c>
       <c r="AB187" s="19" t="n"/>
       <c r="AC187" s="19" t="n"/>
-      <c r="AD187" s="20" t="n"/>
-      <c r="AE187" s="21">
-        <f>IF(K187="","",K187*AD187)</f>
-        <v/>
-      </c>
-      <c r="AF187" s="19" t="n"/>
+      <c r="AD187" s="19" t="n"/>
+      <c r="AE187" s="20" t="n"/>
+      <c r="AF187" s="21">
+        <f>IF(K187="","",K187*AE187)</f>
+        <v/>
+      </c>
       <c r="AG187" s="19" t="n"/>
       <c r="AH187" s="19" t="n"/>
       <c r="AI187" s="19" t="n"/>
       <c r="AJ187" s="19" t="n"/>
       <c r="AK187" s="19" t="n"/>
-      <c r="AL187" s="16" t="inlineStr">
+      <c r="AL187" s="19" t="n"/>
+      <c r="AM187" s="16" t="inlineStr">
         <is>
           <t>7 Stühle – abgebildet ist einer davon, das Etikett auf Foto F-191.</t>
         </is>
       </c>
-      <c r="AM187" s="22" t="inlineStr">
+      <c r="AN187" s="22" t="inlineStr">
         <is>
           <t>Farbe klaeren: auf dem Erfassungsblatt steht weiss, das Foto wirkt hellgrau-gruen.</t>
         </is>
@@ -23806,23 +24081,24 @@
       </c>
       <c r="AB188" s="19" t="n"/>
       <c r="AC188" s="19" t="n"/>
-      <c r="AD188" s="20" t="n"/>
-      <c r="AE188" s="21">
-        <f>IF(K188="","",K188*AD188)</f>
-        <v/>
-      </c>
-      <c r="AF188" s="19" t="n"/>
+      <c r="AD188" s="19" t="n"/>
+      <c r="AE188" s="20" t="n"/>
+      <c r="AF188" s="21">
+        <f>IF(K188="","",K188*AE188)</f>
+        <v/>
+      </c>
       <c r="AG188" s="19" t="n"/>
       <c r="AH188" s="19" t="n"/>
       <c r="AI188" s="19" t="n"/>
       <c r="AJ188" s="19" t="n"/>
       <c r="AK188" s="19" t="n"/>
-      <c r="AL188" s="16" t="inlineStr">
+      <c r="AL188" s="19" t="n"/>
+      <c r="AM188" s="16" t="inlineStr">
         <is>
           <t>5 Regale insgesamt: 3 im Schlafraum 5, 1 im Treppenraum 1 (dort NU05-05) und 1 in der Garage (dort NU07-06).</t>
         </is>
       </c>
-      <c r="AM188" s="22" t="inlineStr">
+      <c r="AN188" s="22" t="inlineStr">
         <is>
           <t>Zusammengefasste Position – Post-it-Nummern in den anderen Räumen: NU05-05, NU07-06.</t>
         </is>
@@ -23928,23 +24204,24 @@
       <c r="AA189" s="19" t="n"/>
       <c r="AB189" s="19" t="n"/>
       <c r="AC189" s="19" t="n"/>
-      <c r="AD189" s="20" t="n"/>
-      <c r="AE189" s="21">
-        <f>IF(K189="","",K189*AD189)</f>
-        <v/>
-      </c>
-      <c r="AF189" s="19" t="n"/>
+      <c r="AD189" s="19" t="n"/>
+      <c r="AE189" s="20" t="n"/>
+      <c r="AF189" s="21">
+        <f>IF(K189="","",K189*AE189)</f>
+        <v/>
+      </c>
       <c r="AG189" s="19" t="n"/>
       <c r="AH189" s="19" t="n"/>
       <c r="AI189" s="19" t="n"/>
       <c r="AJ189" s="19" t="n"/>
       <c r="AK189" s="19" t="n"/>
-      <c r="AL189" s="16" t="inlineStr">
+      <c r="AL189" s="19" t="n"/>
+      <c r="AM189" s="16" t="inlineStr">
         <is>
           <t>4 Stühle – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM189" s="22" t="n"/>
+      <c r="AN189" s="22" t="n"/>
     </row>
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="15" t="inlineStr">
@@ -24050,23 +24327,24 @@
       </c>
       <c r="AB190" s="19" t="n"/>
       <c r="AC190" s="19" t="n"/>
-      <c r="AD190" s="20" t="n"/>
-      <c r="AE190" s="21">
-        <f>IF(K190="","",K190*AD190)</f>
-        <v/>
-      </c>
-      <c r="AF190" s="19" t="n"/>
+      <c r="AD190" s="19" t="n"/>
+      <c r="AE190" s="20" t="n"/>
+      <c r="AF190" s="21">
+        <f>IF(K190="","",K190*AE190)</f>
+        <v/>
+      </c>
       <c r="AG190" s="19" t="n"/>
       <c r="AH190" s="19" t="n"/>
       <c r="AI190" s="19" t="n"/>
       <c r="AJ190" s="19" t="n"/>
       <c r="AK190" s="19" t="n"/>
-      <c r="AL190" s="16" t="inlineStr">
+      <c r="AL190" s="19" t="n"/>
+      <c r="AM190" s="16" t="inlineStr">
         <is>
           <t>2 Stück – abgebildet ist eines davon, das Etikett auf Foto F-195.</t>
         </is>
       </c>
-      <c r="AM190" s="22" t="n"/>
+      <c r="AN190" s="22" t="n"/>
     </row>
     <row r="191" ht="30" customHeight="1">
       <c r="A191" s="15" t="inlineStr">
@@ -24168,23 +24446,24 @@
       <c r="AA191" s="19" t="n"/>
       <c r="AB191" s="19" t="n"/>
       <c r="AC191" s="19" t="n"/>
-      <c r="AD191" s="20" t="n"/>
-      <c r="AE191" s="21">
-        <f>IF(K191="","",K191*AD191)</f>
-        <v/>
-      </c>
-      <c r="AF191" s="19" t="n"/>
+      <c r="AD191" s="19" t="n"/>
+      <c r="AE191" s="20" t="n"/>
+      <c r="AF191" s="21">
+        <f>IF(K191="","",K191*AE191)</f>
+        <v/>
+      </c>
       <c r="AG191" s="19" t="n"/>
       <c r="AH191" s="19" t="n"/>
       <c r="AI191" s="19" t="n"/>
       <c r="AJ191" s="19" t="n"/>
       <c r="AK191" s="19" t="n"/>
-      <c r="AL191" s="16" t="inlineStr">
+      <c r="AL191" s="19" t="n"/>
+      <c r="AM191" s="16" t="inlineStr">
         <is>
           <t>1 Tisch.</t>
         </is>
       </c>
-      <c r="AM191" s="22" t="n"/>
+      <c r="AN191" s="22" t="n"/>
     </row>
     <row r="192" ht="30" customHeight="1">
       <c r="A192" s="15" t="inlineStr">
@@ -24286,23 +24565,24 @@
       <c r="AA192" s="19" t="n"/>
       <c r="AB192" s="19" t="n"/>
       <c r="AC192" s="19" t="n"/>
-      <c r="AD192" s="20" t="n"/>
-      <c r="AE192" s="21">
-        <f>IF(K192="","",K192*AD192)</f>
-        <v/>
-      </c>
-      <c r="AF192" s="19" t="n"/>
+      <c r="AD192" s="19" t="n"/>
+      <c r="AE192" s="20" t="n"/>
+      <c r="AF192" s="21">
+        <f>IF(K192="","",K192*AE192)</f>
+        <v/>
+      </c>
       <c r="AG192" s="19" t="n"/>
       <c r="AH192" s="19" t="n"/>
       <c r="AI192" s="19" t="n"/>
       <c r="AJ192" s="19" t="n"/>
       <c r="AK192" s="19" t="n"/>
-      <c r="AL192" s="16" t="inlineStr">
+      <c r="AL192" s="19" t="n"/>
+      <c r="AM192" s="16" t="inlineStr">
         <is>
           <t>1 Raumteiler.</t>
         </is>
       </c>
-      <c r="AM192" s="22" t="n"/>
+      <c r="AN192" s="22" t="n"/>
     </row>
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="15" t="inlineStr">
@@ -24408,23 +24688,24 @@
       </c>
       <c r="AB193" s="19" t="n"/>
       <c r="AC193" s="19" t="n"/>
-      <c r="AD193" s="20" t="n"/>
-      <c r="AE193" s="21">
-        <f>IF(K193="","",K193*AD193)</f>
-        <v/>
-      </c>
-      <c r="AF193" s="19" t="n"/>
+      <c r="AD193" s="19" t="n"/>
+      <c r="AE193" s="20" t="n"/>
+      <c r="AF193" s="21">
+        <f>IF(K193="","",K193*AE193)</f>
+        <v/>
+      </c>
       <c r="AG193" s="19" t="n"/>
       <c r="AH193" s="19" t="n"/>
       <c r="AI193" s="19" t="n"/>
       <c r="AJ193" s="19" t="n"/>
       <c r="AK193" s="19" t="n"/>
-      <c r="AL193" s="16" t="inlineStr">
+      <c r="AL193" s="19" t="n"/>
+      <c r="AM193" s="16" t="inlineStr">
         <is>
           <t>1 Regal. Die Bücher gehören nicht dazu.</t>
         </is>
       </c>
-      <c r="AM193" s="22" t="n"/>
+      <c r="AN193" s="22" t="n"/>
     </row>
     <row r="194" ht="30" customHeight="1">
       <c r="A194" s="15" t="inlineStr">
@@ -24526,23 +24807,24 @@
       <c r="AA194" s="19" t="n"/>
       <c r="AB194" s="19" t="n"/>
       <c r="AC194" s="19" t="n"/>
-      <c r="AD194" s="20" t="n"/>
-      <c r="AE194" s="21">
-        <f>IF(K194="","",K194*AD194)</f>
-        <v/>
-      </c>
-      <c r="AF194" s="19" t="n"/>
+      <c r="AD194" s="19" t="n"/>
+      <c r="AE194" s="20" t="n"/>
+      <c r="AF194" s="21">
+        <f>IF(K194="","",K194*AE194)</f>
+        <v/>
+      </c>
       <c r="AG194" s="19" t="n"/>
       <c r="AH194" s="19" t="n"/>
       <c r="AI194" s="19" t="n"/>
       <c r="AJ194" s="19" t="n"/>
       <c r="AK194" s="19" t="n"/>
-      <c r="AL194" s="16" t="inlineStr">
+      <c r="AL194" s="19" t="n"/>
+      <c r="AM194" s="16" t="inlineStr">
         <is>
           <t>1 Bällebad einschließlich der Bälle, vom Haus bestätigt.</t>
         </is>
       </c>
-      <c r="AM194" s="22" t="n"/>
+      <c r="AN194" s="22" t="n"/>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="15" t="inlineStr">
@@ -24644,23 +24926,24 @@
       <c r="AA195" s="19" t="n"/>
       <c r="AB195" s="19" t="n"/>
       <c r="AC195" s="19" t="n"/>
-      <c r="AD195" s="20" t="n"/>
-      <c r="AE195" s="21">
-        <f>IF(K195="","",K195*AD195)</f>
-        <v/>
-      </c>
-      <c r="AF195" s="19" t="n"/>
+      <c r="AD195" s="19" t="n"/>
+      <c r="AE195" s="20" t="n"/>
+      <c r="AF195" s="21">
+        <f>IF(K195="","",K195*AE195)</f>
+        <v/>
+      </c>
       <c r="AG195" s="19" t="n"/>
       <c r="AH195" s="19" t="n"/>
       <c r="AI195" s="19" t="n"/>
       <c r="AJ195" s="19" t="n"/>
       <c r="AK195" s="19" t="n"/>
-      <c r="AL195" s="16" t="inlineStr">
+      <c r="AL195" s="19" t="n"/>
+      <c r="AM195" s="16" t="inlineStr">
         <is>
           <t>2 Einheiten, jeweils Unterteil und Wandaufsatz. Der Inhalt der Wannen gehört nicht dazu.</t>
         </is>
       </c>
-      <c r="AM195" s="22" t="n"/>
+      <c r="AN195" s="22" t="n"/>
     </row>
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="15" t="inlineStr">
@@ -24762,23 +25045,24 @@
       <c r="AA196" s="19" t="n"/>
       <c r="AB196" s="19" t="n"/>
       <c r="AC196" s="19" t="n"/>
-      <c r="AD196" s="20" t="n"/>
-      <c r="AE196" s="21">
-        <f>IF(K196="","",K196*AD196)</f>
-        <v/>
-      </c>
-      <c r="AF196" s="19" t="n"/>
+      <c r="AD196" s="19" t="n"/>
+      <c r="AE196" s="20" t="n"/>
+      <c r="AF196" s="21">
+        <f>IF(K196="","",K196*AE196)</f>
+        <v/>
+      </c>
       <c r="AG196" s="19" t="n"/>
       <c r="AH196" s="19" t="n"/>
       <c r="AI196" s="19" t="n"/>
       <c r="AJ196" s="19" t="n"/>
       <c r="AK196" s="19" t="n"/>
-      <c r="AL196" s="16" t="inlineStr">
+      <c r="AL196" s="19" t="n"/>
+      <c r="AM196" s="16" t="inlineStr">
         <is>
           <t>1 Werkbank einschließlich Wandaufhängung. Werkzeug, Helm und Zubehör gehören nicht dazu.</t>
         </is>
       </c>
-      <c r="AM196" s="22" t="n"/>
+      <c r="AN196" s="22" t="n"/>
     </row>
     <row r="197" ht="30" customHeight="1">
       <c r="A197" s="15" t="inlineStr">
@@ -24884,23 +25168,24 @@
       </c>
       <c r="AB197" s="19" t="n"/>
       <c r="AC197" s="19" t="n"/>
-      <c r="AD197" s="20" t="n"/>
-      <c r="AE197" s="21">
-        <f>IF(K197="","",K197*AD197)</f>
-        <v/>
-      </c>
-      <c r="AF197" s="19" t="n"/>
+      <c r="AD197" s="19" t="n"/>
+      <c r="AE197" s="20" t="n"/>
+      <c r="AF197" s="21">
+        <f>IF(K197="","",K197*AE197)</f>
+        <v/>
+      </c>
       <c r="AG197" s="19" t="n"/>
       <c r="AH197" s="19" t="n"/>
       <c r="AI197" s="19" t="n"/>
       <c r="AJ197" s="19" t="n"/>
       <c r="AK197" s="19" t="n"/>
-      <c r="AL197" s="16" t="inlineStr">
+      <c r="AL197" s="19" t="n"/>
+      <c r="AM197" s="16" t="inlineStr">
         <is>
           <t>2 Schränke – abgebildet ist einer davon, innen auf Foto F-206.</t>
         </is>
       </c>
-      <c r="AM197" s="22" t="n"/>
+      <c r="AN197" s="22" t="n"/>
     </row>
     <row r="198" ht="30" customHeight="1">
       <c r="A198" s="15" t="inlineStr">
@@ -25002,23 +25287,24 @@
       <c r="AA198" s="19" t="n"/>
       <c r="AB198" s="19" t="n"/>
       <c r="AC198" s="19" t="n"/>
-      <c r="AD198" s="20" t="n"/>
-      <c r="AE198" s="21">
-        <f>IF(K198="","",K198*AD198)</f>
-        <v/>
-      </c>
-      <c r="AF198" s="19" t="n"/>
+      <c r="AD198" s="19" t="n"/>
+      <c r="AE198" s="20" t="n"/>
+      <c r="AF198" s="21">
+        <f>IF(K198="","",K198*AE198)</f>
+        <v/>
+      </c>
       <c r="AG198" s="19" t="n"/>
       <c r="AH198" s="19" t="n"/>
       <c r="AI198" s="19" t="n"/>
       <c r="AJ198" s="19" t="n"/>
       <c r="AK198" s="19" t="n"/>
-      <c r="AL198" s="16" t="inlineStr">
+      <c r="AL198" s="19" t="n"/>
+      <c r="AM198" s="16" t="inlineStr">
         <is>
           <t>1 Stuhl.</t>
         </is>
       </c>
-      <c r="AM198" s="22" t="inlineStr">
+      <c r="AN198" s="22" t="inlineStr">
         <is>
           <t>OFFEN: NICHT VEROEFFENTLICHEN, bis die Marke geklaert ist. Die Form ist der Panton Chair von Verner Panton, Original von Vitra - gebraucht 120-250 EUR, ein Nachbau 30-50 EUR. Das Original traegt auf der Unterseite eine eingeformte Vitra-Kennzeichnung. Nahaufnahme der Unterseite anfordern, dann entscheiden.</t>
         </is>
@@ -25124,23 +25410,24 @@
       <c r="AA199" s="19" t="n"/>
       <c r="AB199" s="19" t="n"/>
       <c r="AC199" s="19" t="n"/>
-      <c r="AD199" s="20" t="n"/>
-      <c r="AE199" s="21">
-        <f>IF(K199="","",K199*AD199)</f>
-        <v/>
-      </c>
-      <c r="AF199" s="19" t="n"/>
+      <c r="AD199" s="19" t="n"/>
+      <c r="AE199" s="20" t="n"/>
+      <c r="AF199" s="21">
+        <f>IF(K199="","",K199*AE199)</f>
+        <v/>
+      </c>
       <c r="AG199" s="19" t="n"/>
       <c r="AH199" s="19" t="n"/>
       <c r="AI199" s="19" t="n"/>
       <c r="AJ199" s="19" t="n"/>
       <c r="AK199" s="19" t="n"/>
-      <c r="AL199" s="16" t="inlineStr">
+      <c r="AL199" s="19" t="n"/>
+      <c r="AM199" s="16" t="inlineStr">
         <is>
           <t>1 Tisch mit Platten und Wanne. Der Inhalt gehört nicht dazu.</t>
         </is>
       </c>
-      <c r="AM199" s="22" t="n"/>
+      <c r="AN199" s="22" t="n"/>
     </row>
     <row r="200" ht="30" customHeight="1">
       <c r="A200" s="15" t="inlineStr">
@@ -25242,23 +25529,24 @@
       <c r="AA200" s="19" t="n"/>
       <c r="AB200" s="19" t="n"/>
       <c r="AC200" s="19" t="n"/>
-      <c r="AD200" s="20" t="n"/>
-      <c r="AE200" s="21">
-        <f>IF(K200="","",K200*AD200)</f>
-        <v/>
-      </c>
-      <c r="AF200" s="19" t="n"/>
+      <c r="AD200" s="19" t="n"/>
+      <c r="AE200" s="20" t="n"/>
+      <c r="AF200" s="21">
+        <f>IF(K200="","",K200*AE200)</f>
+        <v/>
+      </c>
       <c r="AG200" s="19" t="n"/>
       <c r="AH200" s="19" t="n"/>
       <c r="AI200" s="19" t="n"/>
       <c r="AJ200" s="19" t="n"/>
       <c r="AK200" s="19" t="n"/>
-      <c r="AL200" s="16" t="inlineStr">
+      <c r="AL200" s="19" t="n"/>
+      <c r="AM200" s="16" t="inlineStr">
         <is>
           <t>3 Regale – abgebildet sind zwei davon.</t>
         </is>
       </c>
-      <c r="AM200" s="22" t="n"/>
+      <c r="AN200" s="22" t="n"/>
     </row>
     <row r="201" ht="30" customHeight="1">
       <c r="A201" s="15" t="inlineStr">
@@ -25360,23 +25648,24 @@
       <c r="AA201" s="19" t="n"/>
       <c r="AB201" s="19" t="n"/>
       <c r="AC201" s="19" t="n"/>
-      <c r="AD201" s="20" t="n"/>
-      <c r="AE201" s="21">
-        <f>IF(K201="","",K201*AD201)</f>
-        <v/>
-      </c>
-      <c r="AF201" s="19" t="n"/>
+      <c r="AD201" s="19" t="n"/>
+      <c r="AE201" s="20" t="n"/>
+      <c r="AF201" s="21">
+        <f>IF(K201="","",K201*AE201)</f>
+        <v/>
+      </c>
       <c r="AG201" s="19" t="n"/>
       <c r="AH201" s="19" t="n"/>
       <c r="AI201" s="19" t="n"/>
       <c r="AJ201" s="19" t="n"/>
       <c r="AK201" s="19" t="n"/>
-      <c r="AL201" s="16" t="inlineStr">
+      <c r="AL201" s="19" t="n"/>
+      <c r="AM201" s="16" t="inlineStr">
         <is>
           <t>6 Stühle – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM201" s="22" t="inlineStr">
+      <c r="AN201" s="22" t="inlineStr">
         <is>
           <t>OFFEN: NICHT VEROEFFENTLICHEN, bis die Marke geklaert ist. Auf dem Erfassungsblatt steht "Tripptrapp". Der Stokke Tripp Trapp hat in den Seitenwangen durchgehende Nuten, dieser Stuhl hat Lochreihen - das spricht gegen ein Original. Ein Stokke bringt gebraucht 100-150 EUR, ein Nachbau 25-40 EUR; bei 6 Stueck sind das 150 bis 900 EUR. Marke steht meist auf der Seitenwange oder unter dem Sitz - Nahaufnahme anfordern.</t>
         </is>
@@ -25482,23 +25771,24 @@
       <c r="AA202" s="19" t="n"/>
       <c r="AB202" s="19" t="n"/>
       <c r="AC202" s="19" t="n"/>
-      <c r="AD202" s="20" t="n"/>
-      <c r="AE202" s="21">
-        <f>IF(K202="","",K202*AD202)</f>
-        <v/>
-      </c>
-      <c r="AF202" s="19" t="n"/>
+      <c r="AD202" s="19" t="n"/>
+      <c r="AE202" s="20" t="n"/>
+      <c r="AF202" s="21">
+        <f>IF(K202="","",K202*AE202)</f>
+        <v/>
+      </c>
       <c r="AG202" s="19" t="n"/>
       <c r="AH202" s="19" t="n"/>
       <c r="AI202" s="19" t="n"/>
       <c r="AJ202" s="19" t="n"/>
       <c r="AK202" s="19" t="n"/>
-      <c r="AL202" s="16" t="inlineStr">
+      <c r="AL202" s="19" t="n"/>
+      <c r="AM202" s="16" t="inlineStr">
         <is>
           <t>3 Stühle – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM202" s="22" t="n"/>
+      <c r="AN202" s="22" t="n"/>
     </row>
     <row r="203" ht="30" customHeight="1">
       <c r="A203" s="15" t="inlineStr">
@@ -25600,23 +25890,24 @@
       <c r="AA203" s="19" t="n"/>
       <c r="AB203" s="19" t="n"/>
       <c r="AC203" s="19" t="n"/>
-      <c r="AD203" s="20" t="n"/>
-      <c r="AE203" s="21">
-        <f>IF(K203="","",K203*AD203)</f>
-        <v/>
-      </c>
-      <c r="AF203" s="19" t="n"/>
+      <c r="AD203" s="19" t="n"/>
+      <c r="AE203" s="20" t="n"/>
+      <c r="AF203" s="21">
+        <f>IF(K203="","",K203*AE203)</f>
+        <v/>
+      </c>
       <c r="AG203" s="19" t="n"/>
       <c r="AH203" s="19" t="n"/>
       <c r="AI203" s="19" t="n"/>
       <c r="AJ203" s="19" t="n"/>
       <c r="AK203" s="19" t="n"/>
-      <c r="AL203" s="16" t="inlineStr">
+      <c r="AL203" s="19" t="n"/>
+      <c r="AM203" s="16" t="inlineStr">
         <is>
           <t>2 Tische – abgebildet ist einer davon. Der Inhalt gehört nicht dazu.</t>
         </is>
       </c>
-      <c r="AM203" s="22" t="n"/>
+      <c r="AN203" s="22" t="n"/>
     </row>
     <row r="204" ht="30" customHeight="1">
       <c r="A204" s="15" t="inlineStr">
@@ -25718,23 +26009,24 @@
       <c r="AA204" s="19" t="n"/>
       <c r="AB204" s="19" t="n"/>
       <c r="AC204" s="19" t="n"/>
-      <c r="AD204" s="20" t="n"/>
-      <c r="AE204" s="21">
-        <f>IF(K204="","",K204*AD204)</f>
-        <v/>
-      </c>
-      <c r="AF204" s="19" t="n"/>
+      <c r="AD204" s="19" t="n"/>
+      <c r="AE204" s="20" t="n"/>
+      <c r="AF204" s="21">
+        <f>IF(K204="","",K204*AE204)</f>
+        <v/>
+      </c>
       <c r="AG204" s="19" t="n"/>
       <c r="AH204" s="19" t="n"/>
       <c r="AI204" s="19" t="n"/>
       <c r="AJ204" s="19" t="n"/>
       <c r="AK204" s="19" t="n"/>
-      <c r="AL204" s="16" t="inlineStr">
+      <c r="AL204" s="19" t="n"/>
+      <c r="AM204" s="16" t="inlineStr">
         <is>
           <t>1 Regal.</t>
         </is>
       </c>
-      <c r="AM204" s="22" t="n"/>
+      <c r="AN204" s="22" t="n"/>
     </row>
     <row r="205" ht="30" customHeight="1">
       <c r="A205" s="15" t="inlineStr">
@@ -25836,23 +26128,24 @@
       <c r="AA205" s="19" t="n"/>
       <c r="AB205" s="19" t="n"/>
       <c r="AC205" s="19" t="n"/>
-      <c r="AD205" s="20" t="n"/>
-      <c r="AE205" s="21">
-        <f>IF(K205="","",K205*AD205)</f>
-        <v/>
-      </c>
-      <c r="AF205" s="19" t="n"/>
+      <c r="AD205" s="19" t="n"/>
+      <c r="AE205" s="20" t="n"/>
+      <c r="AF205" s="21">
+        <f>IF(K205="","",K205*AE205)</f>
+        <v/>
+      </c>
       <c r="AG205" s="19" t="n"/>
       <c r="AH205" s="19" t="n"/>
       <c r="AI205" s="19" t="n"/>
       <c r="AJ205" s="19" t="n"/>
       <c r="AK205" s="19" t="n"/>
-      <c r="AL205" s="16" t="inlineStr">
+      <c r="AL205" s="19" t="n"/>
+      <c r="AM205" s="16" t="inlineStr">
         <is>
           <t>1 Regal. Der Inhalt gehört nicht dazu.</t>
         </is>
       </c>
-      <c r="AM205" s="22" t="n"/>
+      <c r="AN205" s="22" t="n"/>
     </row>
     <row r="206" ht="30" customHeight="1">
       <c r="A206" s="15" t="inlineStr">
@@ -25954,23 +26247,24 @@
       <c r="AA206" s="19" t="n"/>
       <c r="AB206" s="19" t="n"/>
       <c r="AC206" s="19" t="n"/>
-      <c r="AD206" s="20" t="n"/>
-      <c r="AE206" s="21">
-        <f>IF(K206="","",K206*AD206)</f>
-        <v/>
-      </c>
-      <c r="AF206" s="19" t="n"/>
+      <c r="AD206" s="19" t="n"/>
+      <c r="AE206" s="20" t="n"/>
+      <c r="AF206" s="21">
+        <f>IF(K206="","",K206*AE206)</f>
+        <v/>
+      </c>
       <c r="AG206" s="19" t="n"/>
       <c r="AH206" s="19" t="n"/>
       <c r="AI206" s="19" t="n"/>
       <c r="AJ206" s="19" t="n"/>
       <c r="AK206" s="19" t="n"/>
-      <c r="AL206" s="16" t="inlineStr">
+      <c r="AL206" s="19" t="n"/>
+      <c r="AM206" s="16" t="inlineStr">
         <is>
           <t>1 Gestell mit acht Einschüben.</t>
         </is>
       </c>
-      <c r="AM206" s="22" t="n"/>
+      <c r="AN206" s="22" t="n"/>
     </row>
     <row r="207" ht="30" customHeight="1">
       <c r="A207" s="15" t="inlineStr">
@@ -26072,23 +26366,24 @@
       <c r="AA207" s="19" t="n"/>
       <c r="AB207" s="19" t="n"/>
       <c r="AC207" s="19" t="n"/>
-      <c r="AD207" s="20" t="n"/>
-      <c r="AE207" s="21">
-        <f>IF(K207="","",K207*AD207)</f>
-        <v/>
-      </c>
-      <c r="AF207" s="19" t="n"/>
+      <c r="AD207" s="19" t="n"/>
+      <c r="AE207" s="20" t="n"/>
+      <c r="AF207" s="21">
+        <f>IF(K207="","",K207*AE207)</f>
+        <v/>
+      </c>
       <c r="AG207" s="19" t="n"/>
       <c r="AH207" s="19" t="n"/>
       <c r="AI207" s="19" t="n"/>
       <c r="AJ207" s="19" t="n"/>
       <c r="AK207" s="19" t="n"/>
-      <c r="AL207" s="16" t="inlineStr">
+      <c r="AL207" s="19" t="n"/>
+      <c r="AM207" s="16" t="inlineStr">
         <is>
           <t>1 Tafel. Schwamm und Becher gehören nicht dazu.</t>
         </is>
       </c>
-      <c r="AM207" s="22" t="n"/>
+      <c r="AN207" s="22" t="n"/>
     </row>
     <row r="208" ht="30" customHeight="1">
       <c r="A208" s="15" t="inlineStr">
@@ -26190,23 +26485,24 @@
       <c r="AA208" s="19" t="n"/>
       <c r="AB208" s="19" t="n"/>
       <c r="AC208" s="19" t="n"/>
-      <c r="AD208" s="20" t="n"/>
-      <c r="AE208" s="21">
-        <f>IF(K208="","",K208*AD208)</f>
-        <v/>
-      </c>
-      <c r="AF208" s="19" t="n"/>
+      <c r="AD208" s="19" t="n"/>
+      <c r="AE208" s="20" t="n"/>
+      <c r="AF208" s="21">
+        <f>IF(K208="","",K208*AE208)</f>
+        <v/>
+      </c>
       <c r="AG208" s="19" t="n"/>
       <c r="AH208" s="19" t="n"/>
       <c r="AI208" s="19" t="n"/>
       <c r="AJ208" s="19" t="n"/>
       <c r="AK208" s="19" t="n"/>
-      <c r="AL208" s="16" t="inlineStr">
+      <c r="AL208" s="19" t="n"/>
+      <c r="AM208" s="16" t="inlineStr">
         <is>
           <t>1 Garderobenwand mit 13 Plätzen. Die Stoffkörbe gehören nicht dazu.</t>
         </is>
       </c>
-      <c r="AM208" s="22" t="inlineStr">
+      <c r="AN208" s="22" t="inlineStr">
         <is>
           <t>Foto zeigt einen grauen Balken: dort hingen Fotokarten der Kinder mit Namen. Neues Foto ohne die Karten waere besser.</t>
         </is>
@@ -26312,23 +26608,24 @@
       <c r="AA209" s="19" t="n"/>
       <c r="AB209" s="19" t="n"/>
       <c r="AC209" s="19" t="n"/>
-      <c r="AD209" s="20" t="n"/>
-      <c r="AE209" s="21">
-        <f>IF(K209="","",K209*AD209)</f>
-        <v/>
-      </c>
-      <c r="AF209" s="19" t="n"/>
+      <c r="AD209" s="19" t="n"/>
+      <c r="AE209" s="20" t="n"/>
+      <c r="AF209" s="21">
+        <f>IF(K209="","",K209*AE209)</f>
+        <v/>
+      </c>
       <c r="AG209" s="19" t="n"/>
       <c r="AH209" s="19" t="n"/>
       <c r="AI209" s="19" t="n"/>
       <c r="AJ209" s="19" t="n"/>
       <c r="AK209" s="19" t="n"/>
-      <c r="AL209" s="16" t="inlineStr">
+      <c r="AL209" s="19" t="n"/>
+      <c r="AM209" s="16" t="inlineStr">
         <is>
           <t>6 Garderobenwände mit je 9 Plätzen – abgebildet ist eine davon. Die Stoffkörbe gehören nicht dazu.</t>
         </is>
       </c>
-      <c r="AM209" s="22" t="n"/>
+      <c r="AN209" s="22" t="n"/>
     </row>
     <row r="210" ht="30" customHeight="1">
       <c r="A210" s="15" t="inlineStr">
@@ -26430,23 +26727,24 @@
       <c r="AA210" s="19" t="n"/>
       <c r="AB210" s="19" t="n"/>
       <c r="AC210" s="19" t="n"/>
-      <c r="AD210" s="20" t="n"/>
-      <c r="AE210" s="21">
-        <f>IF(K210="","",K210*AD210)</f>
-        <v/>
-      </c>
-      <c r="AF210" s="19" t="n"/>
+      <c r="AD210" s="19" t="n"/>
+      <c r="AE210" s="20" t="n"/>
+      <c r="AF210" s="21">
+        <f>IF(K210="","",K210*AE210)</f>
+        <v/>
+      </c>
       <c r="AG210" s="19" t="n"/>
       <c r="AH210" s="19" t="n"/>
       <c r="AI210" s="19" t="n"/>
       <c r="AJ210" s="19" t="n"/>
       <c r="AK210" s="19" t="n"/>
-      <c r="AL210" s="16" t="inlineStr">
+      <c r="AL210" s="19" t="n"/>
+      <c r="AM210" s="16" t="inlineStr">
         <is>
           <t>3 Elemente einschließlich der Wannen – abgebildet ist eines davon.</t>
         </is>
       </c>
-      <c r="AM210" s="22" t="inlineStr">
+      <c r="AN210" s="22" t="inlineStr">
         <is>
           <t>Foto zeigt zwei graue Balken: dort standen Vornamen auf den Etiketten.</t>
         </is>
@@ -26552,23 +26850,24 @@
       <c r="AA211" s="19" t="n"/>
       <c r="AB211" s="19" t="n"/>
       <c r="AC211" s="19" t="n"/>
-      <c r="AD211" s="20" t="n"/>
-      <c r="AE211" s="21">
-        <f>IF(K211="","",K211*AD211)</f>
-        <v/>
-      </c>
-      <c r="AF211" s="19" t="n"/>
+      <c r="AD211" s="19" t="n"/>
+      <c r="AE211" s="20" t="n"/>
+      <c r="AF211" s="21">
+        <f>IF(K211="","",K211*AE211)</f>
+        <v/>
+      </c>
       <c r="AG211" s="19" t="n"/>
       <c r="AH211" s="19" t="n"/>
       <c r="AI211" s="19" t="n"/>
       <c r="AJ211" s="19" t="n"/>
       <c r="AK211" s="19" t="n"/>
-      <c r="AL211" s="16" t="inlineStr">
+      <c r="AL211" s="19" t="n"/>
+      <c r="AM211" s="16" t="inlineStr">
         <is>
           <t>2 Regale – abgebildet ist eines davon.</t>
         </is>
       </c>
-      <c r="AM211" s="22" t="n"/>
+      <c r="AN211" s="22" t="n"/>
     </row>
     <row r="212" ht="30" customHeight="1">
       <c r="A212" s="15" t="inlineStr">
@@ -26674,23 +26973,24 @@
       </c>
       <c r="AB212" s="19" t="n"/>
       <c r="AC212" s="19" t="n"/>
-      <c r="AD212" s="20" t="n"/>
-      <c r="AE212" s="21">
-        <f>IF(K212="","",K212*AD212)</f>
-        <v/>
-      </c>
-      <c r="AF212" s="19" t="n"/>
+      <c r="AD212" s="19" t="n"/>
+      <c r="AE212" s="20" t="n"/>
+      <c r="AF212" s="21">
+        <f>IF(K212="","",K212*AE212)</f>
+        <v/>
+      </c>
       <c r="AG212" s="19" t="n"/>
       <c r="AH212" s="19" t="n"/>
       <c r="AI212" s="19" t="n"/>
       <c r="AJ212" s="19" t="n"/>
       <c r="AK212" s="19" t="n"/>
-      <c r="AL212" s="16" t="inlineStr">
+      <c r="AL212" s="19" t="n"/>
+      <c r="AM212" s="16" t="inlineStr">
         <is>
           <t>1 Gerät. Der Innenraum ist auf Foto F-228 zu sehen.</t>
         </is>
       </c>
-      <c r="AM212" s="22" t="inlineStr">
+      <c r="AN212" s="22" t="inlineStr">
         <is>
           <t>Foto zeigt einen grauen Balken: in der Tuer spiegelte sich eine Person. Neues Foto aus anderem Winkel waere besser.</t>
         </is>
@@ -26796,23 +27096,24 @@
       <c r="AA213" s="19" t="n"/>
       <c r="AB213" s="19" t="n"/>
       <c r="AC213" s="19" t="n"/>
-      <c r="AD213" s="20" t="n"/>
-      <c r="AE213" s="21">
-        <f>IF(K213="","",K213*AD213)</f>
-        <v/>
-      </c>
-      <c r="AF213" s="19" t="n"/>
+      <c r="AD213" s="19" t="n"/>
+      <c r="AE213" s="20" t="n"/>
+      <c r="AF213" s="21">
+        <f>IF(K213="","",K213*AE213)</f>
+        <v/>
+      </c>
       <c r="AG213" s="19" t="n"/>
       <c r="AH213" s="19" t="n"/>
       <c r="AI213" s="19" t="n"/>
       <c r="AJ213" s="19" t="n"/>
       <c r="AK213" s="19" t="n"/>
-      <c r="AL213" s="16" t="inlineStr">
+      <c r="AL213" s="19" t="n"/>
+      <c r="AM213" s="16" t="inlineStr">
         <is>
           <t>2 Regale – abgebildet ist eines davon. Der Inhalt gehört nicht dazu.</t>
         </is>
       </c>
-      <c r="AM213" s="22" t="n"/>
+      <c r="AN213" s="22" t="n"/>
     </row>
     <row r="214" ht="30" customHeight="1">
       <c r="A214" s="15" t="inlineStr">
@@ -26918,23 +27219,24 @@
       </c>
       <c r="AB214" s="19" t="n"/>
       <c r="AC214" s="19" t="n"/>
-      <c r="AD214" s="20" t="n"/>
-      <c r="AE214" s="21">
-        <f>IF(K214="","",K214*AD214)</f>
-        <v/>
-      </c>
-      <c r="AF214" s="19" t="n"/>
+      <c r="AD214" s="19" t="n"/>
+      <c r="AE214" s="20" t="n"/>
+      <c r="AF214" s="21">
+        <f>IF(K214="","",K214*AE214)</f>
+        <v/>
+      </c>
       <c r="AG214" s="19" t="n"/>
       <c r="AH214" s="19" t="n"/>
       <c r="AI214" s="19" t="n"/>
       <c r="AJ214" s="19" t="n"/>
       <c r="AK214" s="19" t="n"/>
-      <c r="AL214" s="16" t="inlineStr">
+      <c r="AL214" s="19" t="n"/>
+      <c r="AM214" s="16" t="inlineStr">
         <is>
           <t>1 Bild.</t>
         </is>
       </c>
-      <c r="AM214" s="22" t="n"/>
+      <c r="AN214" s="22" t="n"/>
     </row>
     <row r="215" ht="30" customHeight="1">
       <c r="A215" s="15" t="inlineStr">
@@ -27036,23 +27338,24 @@
       <c r="AA215" s="19" t="n"/>
       <c r="AB215" s="19" t="n"/>
       <c r="AC215" s="19" t="n"/>
-      <c r="AD215" s="20" t="n"/>
-      <c r="AE215" s="21">
-        <f>IF(K215="","",K215*AD215)</f>
-        <v/>
-      </c>
-      <c r="AF215" s="19" t="n"/>
+      <c r="AD215" s="19" t="n"/>
+      <c r="AE215" s="20" t="n"/>
+      <c r="AF215" s="21">
+        <f>IF(K215="","",K215*AE215)</f>
+        <v/>
+      </c>
       <c r="AG215" s="19" t="n"/>
       <c r="AH215" s="19" t="n"/>
       <c r="AI215" s="19" t="n"/>
       <c r="AJ215" s="19" t="n"/>
       <c r="AK215" s="19" t="n"/>
-      <c r="AL215" s="16" t="inlineStr">
+      <c r="AL215" s="19" t="n"/>
+      <c r="AM215" s="16" t="inlineStr">
         <is>
           <t>1 Bett. Bettwäsche und Kissen gehören nicht dazu.</t>
         </is>
       </c>
-      <c r="AM215" s="22" t="n"/>
+      <c r="AN215" s="22" t="n"/>
     </row>
     <row r="216" ht="30" customHeight="1">
       <c r="A216" s="15" t="inlineStr">
@@ -27154,23 +27457,24 @@
       <c r="AA216" s="19" t="n"/>
       <c r="AB216" s="19" t="n"/>
       <c r="AC216" s="19" t="n"/>
-      <c r="AD216" s="20" t="n"/>
-      <c r="AE216" s="21">
-        <f>IF(K216="","",K216*AD216)</f>
-        <v/>
-      </c>
-      <c r="AF216" s="19" t="n"/>
+      <c r="AD216" s="19" t="n"/>
+      <c r="AE216" s="20" t="n"/>
+      <c r="AF216" s="21">
+        <f>IF(K216="","",K216*AE216)</f>
+        <v/>
+      </c>
       <c r="AG216" s="19" t="n"/>
       <c r="AH216" s="19" t="n"/>
       <c r="AI216" s="19" t="n"/>
       <c r="AJ216" s="19" t="n"/>
       <c r="AK216" s="19" t="n"/>
-      <c r="AL216" s="16" t="inlineStr">
+      <c r="AL216" s="19" t="n"/>
+      <c r="AM216" s="16" t="inlineStr">
         <is>
           <t>1 Kaufladen. Spiellebensmittel, Kasse und Telefon gehören nicht dazu.</t>
         </is>
       </c>
-      <c r="AM216" s="22" t="n"/>
+      <c r="AN216" s="22" t="n"/>
     </row>
     <row r="217" ht="30" customHeight="1">
       <c r="A217" s="15" t="inlineStr">
@@ -27276,23 +27580,24 @@
       </c>
       <c r="AB217" s="19" t="n"/>
       <c r="AC217" s="19" t="n"/>
-      <c r="AD217" s="20" t="n"/>
-      <c r="AE217" s="21">
-        <f>IF(K217="","",K217*AD217)</f>
-        <v/>
-      </c>
-      <c r="AF217" s="19" t="n"/>
+      <c r="AD217" s="19" t="n"/>
+      <c r="AE217" s="20" t="n"/>
+      <c r="AF217" s="21">
+        <f>IF(K217="","",K217*AE217)</f>
+        <v/>
+      </c>
       <c r="AG217" s="19" t="n"/>
       <c r="AH217" s="19" t="n"/>
       <c r="AI217" s="19" t="n"/>
       <c r="AJ217" s="19" t="n"/>
       <c r="AK217" s="19" t="n"/>
-      <c r="AL217" s="16" t="inlineStr">
+      <c r="AL217" s="19" t="n"/>
+      <c r="AM217" s="16" t="inlineStr">
         <is>
           <t>1 Küche aus mehreren Modulen, mit Mikrowellenmodul und Hängeschrank. Eine zweite, anders zusammengesetzte Wesco-Küche steht unter NU03-03.</t>
         </is>
       </c>
-      <c r="AM217" s="22" t="inlineStr">
+      <c r="AN217" s="22" t="inlineStr">
         <is>
           <t>Nicht baugleich mit NU03-03, vom Haus bestaetigt – bleibt getrennt.</t>
         </is>
@@ -27402,23 +27707,24 @@
       </c>
       <c r="AB218" s="19" t="n"/>
       <c r="AC218" s="19" t="n"/>
-      <c r="AD218" s="20" t="n"/>
-      <c r="AE218" s="21">
-        <f>IF(K218="","",K218*AD218)</f>
-        <v/>
-      </c>
-      <c r="AF218" s="19" t="n"/>
+      <c r="AD218" s="19" t="n"/>
+      <c r="AE218" s="20" t="n"/>
+      <c r="AF218" s="21">
+        <f>IF(K218="","",K218*AE218)</f>
+        <v/>
+      </c>
       <c r="AG218" s="19" t="n"/>
       <c r="AH218" s="19" t="n"/>
       <c r="AI218" s="19" t="n"/>
       <c r="AJ218" s="19" t="n"/>
       <c r="AK218" s="19" t="n"/>
-      <c r="AL218" s="16" t="inlineStr">
+      <c r="AL218" s="19" t="n"/>
+      <c r="AM218" s="16" t="inlineStr">
         <is>
           <t>1 Grill.</t>
         </is>
       </c>
-      <c r="AM218" s="22" t="n"/>
+      <c r="AN218" s="22" t="n"/>
     </row>
     <row r="219" ht="30" customHeight="1">
       <c r="A219" s="15" t="inlineStr">
@@ -27520,23 +27826,24 @@
       <c r="AA219" s="19" t="n"/>
       <c r="AB219" s="19" t="n"/>
       <c r="AC219" s="19" t="n"/>
-      <c r="AD219" s="20" t="n"/>
-      <c r="AE219" s="21">
-        <f>IF(K219="","",K219*AD219)</f>
-        <v/>
-      </c>
-      <c r="AF219" s="19" t="n"/>
+      <c r="AD219" s="19" t="n"/>
+      <c r="AE219" s="20" t="n"/>
+      <c r="AF219" s="21">
+        <f>IF(K219="","",K219*AE219)</f>
+        <v/>
+      </c>
       <c r="AG219" s="19" t="n"/>
       <c r="AH219" s="19" t="n"/>
       <c r="AI219" s="19" t="n"/>
       <c r="AJ219" s="19" t="n"/>
       <c r="AK219" s="19" t="n"/>
-      <c r="AL219" s="16" t="inlineStr">
+      <c r="AL219" s="19" t="n"/>
+      <c r="AM219" s="16" t="inlineStr">
         <is>
           <t>1 Schrank. Der Innenraum ist auf Foto F-239 zu sehen.</t>
         </is>
       </c>
-      <c r="AM219" s="22" t="n"/>
+      <c r="AN219" s="22" t="n"/>
     </row>
     <row r="220" ht="30" customHeight="1">
       <c r="A220" s="15" t="inlineStr">
@@ -27638,23 +27945,24 @@
       <c r="AA220" s="19" t="n"/>
       <c r="AB220" s="19" t="n"/>
       <c r="AC220" s="19" t="n"/>
-      <c r="AD220" s="20" t="n"/>
-      <c r="AE220" s="21">
-        <f>IF(K220="","",K220*AD220)</f>
-        <v/>
-      </c>
-      <c r="AF220" s="19" t="n"/>
+      <c r="AD220" s="19" t="n"/>
+      <c r="AE220" s="20" t="n"/>
+      <c r="AF220" s="21">
+        <f>IF(K220="","",K220*AE220)</f>
+        <v/>
+      </c>
       <c r="AG220" s="19" t="n"/>
       <c r="AH220" s="19" t="n"/>
       <c r="AI220" s="19" t="n"/>
       <c r="AJ220" s="19" t="n"/>
       <c r="AK220" s="19" t="n"/>
-      <c r="AL220" s="16" t="inlineStr">
+      <c r="AL220" s="19" t="n"/>
+      <c r="AM220" s="16" t="inlineStr">
         <is>
           <t>1 Regal. Die Einschubkästen gehören nicht dazu.</t>
         </is>
       </c>
-      <c r="AM220" s="22" t="n"/>
+      <c r="AN220" s="22" t="n"/>
     </row>
     <row r="221" ht="30" customHeight="1">
       <c r="A221" s="15" t="inlineStr">
@@ -27756,23 +28064,24 @@
       <c r="AA221" s="19" t="n"/>
       <c r="AB221" s="19" t="n"/>
       <c r="AC221" s="19" t="n"/>
-      <c r="AD221" s="20" t="n"/>
-      <c r="AE221" s="21">
-        <f>IF(K221="","",K221*AD221)</f>
-        <v/>
-      </c>
-      <c r="AF221" s="19" t="n"/>
+      <c r="AD221" s="19" t="n"/>
+      <c r="AE221" s="20" t="n"/>
+      <c r="AF221" s="21">
+        <f>IF(K221="","",K221*AE221)</f>
+        <v/>
+      </c>
       <c r="AG221" s="19" t="n"/>
       <c r="AH221" s="19" t="n"/>
       <c r="AI221" s="19" t="n"/>
       <c r="AJ221" s="19" t="n"/>
       <c r="AK221" s="19" t="n"/>
-      <c r="AL221" s="16" t="inlineStr">
+      <c r="AL221" s="19" t="n"/>
+      <c r="AM221" s="16" t="inlineStr">
         <is>
           <t>1 Sitzgruppe aus drei Teilen: ein Tisch und zwei Truhenbänke. Der Stauraum unter der Sitzfläche ist auf Foto F-243 zu sehen.</t>
         </is>
       </c>
-      <c r="AM221" s="22" t="n"/>
+      <c r="AN221" s="22" t="n"/>
     </row>
     <row r="222" ht="30" customHeight="1">
       <c r="A222" s="15" t="inlineStr">
@@ -27874,23 +28183,24 @@
       <c r="AA222" s="19" t="n"/>
       <c r="AB222" s="19" t="n"/>
       <c r="AC222" s="19" t="n"/>
-      <c r="AD222" s="20" t="n"/>
-      <c r="AE222" s="21">
-        <f>IF(K222="","",K222*AD222)</f>
-        <v/>
-      </c>
-      <c r="AF222" s="19" t="n"/>
+      <c r="AD222" s="19" t="n"/>
+      <c r="AE222" s="20" t="n"/>
+      <c r="AF222" s="21">
+        <f>IF(K222="","",K222*AE222)</f>
+        <v/>
+      </c>
       <c r="AG222" s="19" t="n"/>
       <c r="AH222" s="19" t="n"/>
       <c r="AI222" s="19" t="n"/>
       <c r="AJ222" s="19" t="n"/>
       <c r="AK222" s="19" t="n"/>
-      <c r="AL222" s="16" t="inlineStr">
+      <c r="AL222" s="19" t="n"/>
+      <c r="AM222" s="16" t="inlineStr">
         <is>
           <t>2 Regale, beide abgebildet. Figuren und Abspielgerät gehören nicht dazu.</t>
         </is>
       </c>
-      <c r="AM222" s="22" t="n"/>
+      <c r="AN222" s="22" t="n"/>
     </row>
     <row r="223" ht="30" customHeight="1">
       <c r="A223" s="15" t="inlineStr">
@@ -27992,23 +28302,24 @@
       <c r="AA223" s="19" t="n"/>
       <c r="AB223" s="19" t="n"/>
       <c r="AC223" s="19" t="n"/>
-      <c r="AD223" s="20" t="n"/>
-      <c r="AE223" s="21">
-        <f>IF(K223="","",K223*AD223)</f>
-        <v/>
-      </c>
-      <c r="AF223" s="19" t="n"/>
+      <c r="AD223" s="19" t="n"/>
+      <c r="AE223" s="20" t="n"/>
+      <c r="AF223" s="21">
+        <f>IF(K223="","",K223*AE223)</f>
+        <v/>
+      </c>
       <c r="AG223" s="19" t="n"/>
       <c r="AH223" s="19" t="n"/>
       <c r="AI223" s="19" t="n"/>
       <c r="AJ223" s="19" t="n"/>
       <c r="AK223" s="19" t="n"/>
-      <c r="AL223" s="16" t="inlineStr">
+      <c r="AL223" s="19" t="n"/>
+      <c r="AM223" s="16" t="inlineStr">
         <is>
           <t>1 Highboard.</t>
         </is>
       </c>
-      <c r="AM223" s="22" t="n"/>
+      <c r="AN223" s="22" t="n"/>
     </row>
     <row r="224" ht="30" customHeight="1">
       <c r="A224" s="15" t="inlineStr">
@@ -28110,23 +28421,24 @@
       <c r="AA224" s="19" t="n"/>
       <c r="AB224" s="19" t="n"/>
       <c r="AC224" s="19" t="n"/>
-      <c r="AD224" s="20" t="n"/>
-      <c r="AE224" s="21">
-        <f>IF(K224="","",K224*AD224)</f>
-        <v/>
-      </c>
-      <c r="AF224" s="19" t="n"/>
+      <c r="AD224" s="19" t="n"/>
+      <c r="AE224" s="20" t="n"/>
+      <c r="AF224" s="21">
+        <f>IF(K224="","",K224*AE224)</f>
+        <v/>
+      </c>
       <c r="AG224" s="19" t="n"/>
       <c r="AH224" s="19" t="n"/>
       <c r="AI224" s="19" t="n"/>
       <c r="AJ224" s="19" t="n"/>
       <c r="AK224" s="19" t="n"/>
-      <c r="AL224" s="16" t="inlineStr">
+      <c r="AL224" s="19" t="n"/>
+      <c r="AM224" s="16" t="inlineStr">
         <is>
           <t>1 Stück.</t>
         </is>
       </c>
-      <c r="AM224" s="22" t="n"/>
+      <c r="AN224" s="22" t="n"/>
     </row>
     <row r="225" ht="30" customHeight="1">
       <c r="A225" s="15" t="inlineStr">
@@ -28228,23 +28540,24 @@
       <c r="AA225" s="19" t="n"/>
       <c r="AB225" s="19" t="n"/>
       <c r="AC225" s="19" t="n"/>
-      <c r="AD225" s="20" t="n"/>
-      <c r="AE225" s="21">
-        <f>IF(K225="","",K225*AD225)</f>
-        <v/>
-      </c>
-      <c r="AF225" s="19" t="n"/>
+      <c r="AD225" s="19" t="n"/>
+      <c r="AE225" s="20" t="n"/>
+      <c r="AF225" s="21">
+        <f>IF(K225="","",K225*AE225)</f>
+        <v/>
+      </c>
       <c r="AG225" s="19" t="n"/>
       <c r="AH225" s="19" t="n"/>
       <c r="AI225" s="19" t="n"/>
       <c r="AJ225" s="19" t="n"/>
       <c r="AK225" s="19" t="n"/>
-      <c r="AL225" s="16" t="inlineStr">
+      <c r="AL225" s="19" t="n"/>
+      <c r="AM225" s="16" t="inlineStr">
         <is>
           <t>2 Sessel – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM225" s="22" t="n"/>
+      <c r="AN225" s="22" t="n"/>
     </row>
     <row r="226" ht="30" customHeight="1">
       <c r="A226" s="15" t="inlineStr">
@@ -28346,23 +28659,24 @@
       <c r="AA226" s="19" t="n"/>
       <c r="AB226" s="19" t="n"/>
       <c r="AC226" s="19" t="n"/>
-      <c r="AD226" s="20" t="n"/>
-      <c r="AE226" s="21">
-        <f>IF(K226="","",K226*AD226)</f>
-        <v/>
-      </c>
-      <c r="AF226" s="19" t="n"/>
+      <c r="AD226" s="19" t="n"/>
+      <c r="AE226" s="20" t="n"/>
+      <c r="AF226" s="21">
+        <f>IF(K226="","",K226*AE226)</f>
+        <v/>
+      </c>
       <c r="AG226" s="19" t="n"/>
       <c r="AH226" s="19" t="n"/>
       <c r="AI226" s="19" t="n"/>
       <c r="AJ226" s="19" t="n"/>
       <c r="AK226" s="19" t="n"/>
-      <c r="AL226" s="16" t="inlineStr">
+      <c r="AL226" s="19" t="n"/>
+      <c r="AM226" s="16" t="inlineStr">
         <is>
           <t>12 Regale einschließlich der Wannen – abgebildet ist eines davon. Die Hundehaken darunter sind eigene Positionen (NE01-22 und NE01-23).</t>
         </is>
       </c>
-      <c r="AM226" s="22" t="n"/>
+      <c r="AN226" s="22" t="n"/>
     </row>
     <row r="227" ht="30" customHeight="1">
       <c r="A227" s="15" t="inlineStr">
@@ -28464,23 +28778,24 @@
       <c r="AA227" s="19" t="n"/>
       <c r="AB227" s="19" t="n"/>
       <c r="AC227" s="19" t="n"/>
-      <c r="AD227" s="20" t="n"/>
-      <c r="AE227" s="21">
-        <f>IF(K227="","",K227*AD227)</f>
-        <v/>
-      </c>
-      <c r="AF227" s="19" t="n"/>
+      <c r="AD227" s="19" t="n"/>
+      <c r="AE227" s="20" t="n"/>
+      <c r="AF227" s="21">
+        <f>IF(K227="","",K227*AE227)</f>
+        <v/>
+      </c>
       <c r="AG227" s="19" t="n"/>
       <c r="AH227" s="19" t="n"/>
       <c r="AI227" s="19" t="n"/>
       <c r="AJ227" s="19" t="n"/>
       <c r="AK227" s="19" t="n"/>
-      <c r="AL227" s="16" t="inlineStr">
+      <c r="AL227" s="19" t="n"/>
+      <c r="AM227" s="16" t="inlineStr">
         <is>
           <t>21 Haken – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM227" s="22" t="n"/>
+      <c r="AN227" s="22" t="n"/>
     </row>
     <row r="228" ht="30" customHeight="1">
       <c r="A228" s="15" t="inlineStr">
@@ -28582,23 +28897,24 @@
       <c r="AA228" s="19" t="n"/>
       <c r="AB228" s="19" t="n"/>
       <c r="AC228" s="19" t="n"/>
-      <c r="AD228" s="20" t="n"/>
-      <c r="AE228" s="21">
-        <f>IF(K228="","",K228*AD228)</f>
-        <v/>
-      </c>
-      <c r="AF228" s="19" t="n"/>
+      <c r="AD228" s="19" t="n"/>
+      <c r="AE228" s="20" t="n"/>
+      <c r="AF228" s="21">
+        <f>IF(K228="","",K228*AE228)</f>
+        <v/>
+      </c>
       <c r="AG228" s="19" t="n"/>
       <c r="AH228" s="19" t="n"/>
       <c r="AI228" s="19" t="n"/>
       <c r="AJ228" s="19" t="n"/>
       <c r="AK228" s="19" t="n"/>
-      <c r="AL228" s="16" t="inlineStr">
+      <c r="AL228" s="19" t="n"/>
+      <c r="AM228" s="16" t="inlineStr">
         <is>
           <t>11 Haken – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AM228" s="22" t="n"/>
+      <c r="AN228" s="22" t="n"/>
     </row>
     <row r="229" ht="30" customHeight="1">
       <c r="A229" s="15" t="inlineStr">
@@ -28700,23 +29016,24 @@
       <c r="AA229" s="19" t="n"/>
       <c r="AB229" s="19" t="n"/>
       <c r="AC229" s="19" t="n"/>
-      <c r="AD229" s="20" t="n"/>
-      <c r="AE229" s="21">
-        <f>IF(K229="","",K229*AD229)</f>
-        <v/>
-      </c>
-      <c r="AF229" s="19" t="n"/>
+      <c r="AD229" s="19" t="n"/>
+      <c r="AE229" s="20" t="n"/>
+      <c r="AF229" s="21">
+        <f>IF(K229="","",K229*AE229)</f>
+        <v/>
+      </c>
       <c r="AG229" s="19" t="n"/>
       <c r="AH229" s="19" t="n"/>
       <c r="AI229" s="19" t="n"/>
       <c r="AJ229" s="19" t="n"/>
       <c r="AK229" s="19" t="n"/>
-      <c r="AL229" s="16" t="inlineStr">
+      <c r="AL229" s="19" t="n"/>
+      <c r="AM229" s="16" t="inlineStr">
         <is>
           <t>3 Bänke – abgebildet sind zwei davon.</t>
         </is>
       </c>
-      <c r="AM229" s="22" t="n"/>
+      <c r="AN229" s="22" t="n"/>
     </row>
     <row r="230" ht="30" customHeight="1">
       <c r="A230" s="15" t="inlineStr">
@@ -28818,23 +29135,24 @@
       <c r="AA230" s="19" t="n"/>
       <c r="AB230" s="19" t="n"/>
       <c r="AC230" s="19" t="n"/>
-      <c r="AD230" s="20" t="n"/>
-      <c r="AE230" s="21">
-        <f>IF(K230="","",K230*AD230)</f>
-        <v/>
-      </c>
-      <c r="AF230" s="19" t="n"/>
+      <c r="AD230" s="19" t="n"/>
+      <c r="AE230" s="20" t="n"/>
+      <c r="AF230" s="21">
+        <f>IF(K230="","",K230*AE230)</f>
+        <v/>
+      </c>
       <c r="AG230" s="19" t="n"/>
       <c r="AH230" s="19" t="n"/>
       <c r="AI230" s="19" t="n"/>
       <c r="AJ230" s="19" t="n"/>
       <c r="AK230" s="19" t="n"/>
-      <c r="AL230" s="16" t="inlineStr">
+      <c r="AL230" s="19" t="n"/>
+      <c r="AM230" s="16" t="inlineStr">
         <is>
           <t>3 Bänke – abgebildet ist eine davon.</t>
         </is>
       </c>
-      <c r="AM230" s="22" t="n"/>
+      <c r="AN230" s="22" t="n"/>
     </row>
     <row r="231" ht="30" customHeight="1">
       <c r="A231" s="15" t="inlineStr">
@@ -28936,23 +29254,24 @@
       <c r="AA231" s="19" t="n"/>
       <c r="AB231" s="19" t="n"/>
       <c r="AC231" s="19" t="n"/>
-      <c r="AD231" s="20" t="n"/>
-      <c r="AE231" s="21">
-        <f>IF(K231="","",K231*AD231)</f>
-        <v/>
-      </c>
-      <c r="AF231" s="19" t="n"/>
+      <c r="AD231" s="19" t="n"/>
+      <c r="AE231" s="20" t="n"/>
+      <c r="AF231" s="21">
+        <f>IF(K231="","",K231*AE231)</f>
+        <v/>
+      </c>
       <c r="AG231" s="19" t="n"/>
       <c r="AH231" s="19" t="n"/>
       <c r="AI231" s="19" t="n"/>
       <c r="AJ231" s="19" t="n"/>
       <c r="AK231" s="19" t="n"/>
-      <c r="AL231" s="16" t="inlineStr">
+      <c r="AL231" s="19" t="n"/>
+      <c r="AM231" s="16" t="inlineStr">
         <is>
           <t>7 Bänke – abgebildet ist eine davon.</t>
         </is>
       </c>
-      <c r="AM231" s="22" t="n"/>
+      <c r="AN231" s="22" t="n"/>
     </row>
     <row r="232" ht="30" customHeight="1">
       <c r="A232" s="15" t="inlineStr">
@@ -29054,23 +29373,24 @@
       <c r="AA232" s="19" t="n"/>
       <c r="AB232" s="19" t="n"/>
       <c r="AC232" s="19" t="n"/>
-      <c r="AD232" s="20" t="n"/>
-      <c r="AE232" s="21">
-        <f>IF(K232="","",K232*AD232)</f>
-        <v/>
-      </c>
-      <c r="AF232" s="19" t="n"/>
+      <c r="AD232" s="19" t="n"/>
+      <c r="AE232" s="20" t="n"/>
+      <c r="AF232" s="21">
+        <f>IF(K232="","",K232*AE232)</f>
+        <v/>
+      </c>
       <c r="AG232" s="19" t="n"/>
       <c r="AH232" s="19" t="n"/>
       <c r="AI232" s="19" t="n"/>
       <c r="AJ232" s="19" t="n"/>
       <c r="AK232" s="19" t="n"/>
-      <c r="AL232" s="16" t="inlineStr">
+      <c r="AL232" s="19" t="n"/>
+      <c r="AM232" s="16" t="inlineStr">
         <is>
           <t>1 Bild.</t>
         </is>
       </c>
-      <c r="AM232" s="22" t="inlineStr">
+      <c r="AN232" s="22" t="inlineStr">
         <is>
           <t>Preis unbestaetigt: stilistisch verwandt mit NU01-06 (Marilyn mit Bollenhut, 650 EUR) von derselben Hand. Bitte pruefen, ob 250 EUR passt.</t>
         </is>
@@ -29176,23 +29496,24 @@
       <c r="AA233" s="19" t="n"/>
       <c r="AB233" s="19" t="n"/>
       <c r="AC233" s="19" t="n"/>
-      <c r="AD233" s="20" t="n"/>
-      <c r="AE233" s="21">
-        <f>IF(K233="","",K233*AD233)</f>
-        <v/>
-      </c>
-      <c r="AF233" s="19" t="n"/>
+      <c r="AD233" s="19" t="n"/>
+      <c r="AE233" s="20" t="n"/>
+      <c r="AF233" s="21">
+        <f>IF(K233="","",K233*AE233)</f>
+        <v/>
+      </c>
       <c r="AG233" s="19" t="n"/>
       <c r="AH233" s="19" t="n"/>
       <c r="AI233" s="19" t="n"/>
       <c r="AJ233" s="19" t="n"/>
       <c r="AK233" s="19" t="n"/>
-      <c r="AL233" s="16" t="inlineStr">
+      <c r="AL233" s="19" t="n"/>
+      <c r="AM233" s="16" t="inlineStr">
         <is>
           <t>1 Bild.</t>
         </is>
       </c>
-      <c r="AM233" s="22" t="n"/>
+      <c r="AN233" s="22" t="n"/>
     </row>
     <row r="234" ht="30" customHeight="1">
       <c r="A234" s="15" t="inlineStr">
@@ -29294,23 +29615,24 @@
       <c r="AA234" s="19" t="n"/>
       <c r="AB234" s="19" t="n"/>
       <c r="AC234" s="19" t="n"/>
-      <c r="AD234" s="20" t="n"/>
-      <c r="AE234" s="21">
-        <f>IF(K234="","",K234*AD234)</f>
-        <v/>
-      </c>
-      <c r="AF234" s="19" t="n"/>
+      <c r="AD234" s="19" t="n"/>
+      <c r="AE234" s="20" t="n"/>
+      <c r="AF234" s="21">
+        <f>IF(K234="","",K234*AE234)</f>
+        <v/>
+      </c>
       <c r="AG234" s="19" t="n"/>
       <c r="AH234" s="19" t="n"/>
       <c r="AI234" s="19" t="n"/>
       <c r="AJ234" s="19" t="n"/>
       <c r="AK234" s="19" t="n"/>
-      <c r="AL234" s="16" t="inlineStr">
+      <c r="AL234" s="19" t="n"/>
+      <c r="AM234" s="16" t="inlineStr">
         <is>
           <t>3 Sockel, unterschiedlich bestückt: einer mit einem großen Baum, zwei mit je drei Bäumen. Alle drei sind abgebildet.</t>
         </is>
       </c>
-      <c r="AM234" s="22" t="inlineStr">
+      <c r="AN234" s="22" t="inlineStr">
         <is>
           <t>Bisher unter NE01-15 gefuehrt; dort durchgestrichen, weil sie in den Flur 1 umgezogen sind.</t>
         </is>
@@ -29420,23 +29742,24 @@
       <c r="AA235" s="19" t="n"/>
       <c r="AB235" s="19" t="n"/>
       <c r="AC235" s="19" t="n"/>
-      <c r="AD235" s="20" t="n"/>
-      <c r="AE235" s="21">
-        <f>IF(K235="","",K235*AD235)</f>
-        <v/>
-      </c>
-      <c r="AF235" s="19" t="n"/>
+      <c r="AD235" s="19" t="n"/>
+      <c r="AE235" s="20" t="n"/>
+      <c r="AF235" s="21">
+        <f>IF(K235="","",K235*AE235)</f>
+        <v/>
+      </c>
       <c r="AG235" s="19" t="n"/>
       <c r="AH235" s="19" t="n"/>
       <c r="AI235" s="19" t="n"/>
       <c r="AJ235" s="19" t="n"/>
       <c r="AK235" s="19" t="n"/>
-      <c r="AL235" s="16" t="inlineStr">
+      <c r="AL235" s="19" t="n"/>
+      <c r="AM235" s="16" t="inlineStr">
         <is>
           <t>2 Buchstaben: einer im Flur 1 (BA01-04) und einer im Flur 2 (dort mit BA02-07 beschriftet).</t>
         </is>
       </c>
-      <c r="AM235" s="22" t="inlineStr">
+      <c r="AN235" s="22" t="inlineStr">
         <is>
           <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA02-07.</t>
         </is>
@@ -29445,7 +29768,7 @@
     <row r="236" ht="30" customHeight="1">
       <c r="A236" s="15" t="inlineStr">
         <is>
-          <t>BA02-01</t>
+          <t>BA02-02</t>
         </is>
       </c>
       <c r="B236" s="15" t="n"/>
@@ -29457,12 +29780,12 @@
       </c>
       <c r="E236" s="15" t="inlineStr">
         <is>
-          <t>Kindergarderobe weiß</t>
+          <t>Rutscherauto rot</t>
         </is>
       </c>
       <c r="F236" s="16" t="inlineStr">
         <is>
-          <t>Kindergarderobe in Weiß.</t>
+          <t>Rutscherauto in Sportwagenform, roter Kunststoffkorpus mit schwarzer Sitzfläche in Rautensteppung, verchromte Felgen, Lehne hinten zum Schieben.</t>
         </is>
       </c>
       <c r="G236" s="15" t="inlineStr">
@@ -29481,7 +29804,7 @@
         </is>
       </c>
       <c r="J236" s="17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K236" s="17" t="n"/>
       <c r="L236" s="18">
@@ -29507,7 +29830,7 @@
       <c r="Q236" s="19" t="n"/>
       <c r="R236" s="20" t="n"/>
       <c r="S236" s="20" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="T236" s="19" t="inlineStr">
         <is>
@@ -29523,10 +29846,14 @@
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="W236" s="15" t="n"/>
+      <c r="W236" s="15" t="inlineStr">
+        <is>
+          <t>F-263</t>
+        </is>
+      </c>
       <c r="X236" s="19" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="Y236" s="19" t="n"/>
@@ -29538,32 +29865,29 @@
       <c r="AA236" s="19" t="n"/>
       <c r="AB236" s="19" t="n"/>
       <c r="AC236" s="19" t="n"/>
-      <c r="AD236" s="20" t="n"/>
-      <c r="AE236" s="21">
-        <f>IF(K236="","",K236*AD236)</f>
-        <v/>
-      </c>
-      <c r="AF236" s="19" t="n"/>
+      <c r="AD236" s="19" t="n"/>
+      <c r="AE236" s="20" t="n"/>
+      <c r="AF236" s="21">
+        <f>IF(K236="","",K236*AE236)</f>
+        <v/>
+      </c>
       <c r="AG236" s="19" t="n"/>
       <c r="AH236" s="19" t="n"/>
       <c r="AI236" s="19" t="n"/>
       <c r="AJ236" s="19" t="n"/>
       <c r="AK236" s="19" t="n"/>
-      <c r="AL236" s="16" t="inlineStr">
-        <is>
-          <t>5 Stück.</t>
-        </is>
-      </c>
-      <c r="AM236" s="22" t="inlineStr">
-        <is>
-          <t>OFFEN: Foto fehlt - zu BA02-01 ist kein Bild angekommen. Beschreibung und Preis sind daher vorlaeufig. Moeglicherweise baugleich mit einer der bereits erfassten Garderoben (NU01-14, NU01-19, NU06-01/-02) - dann zusammenfassen.</t>
-        </is>
-      </c>
+      <c r="AL236" s="19" t="n"/>
+      <c r="AM236" s="16" t="inlineStr">
+        <is>
+          <t>1 Fahrzeug.</t>
+        </is>
+      </c>
+      <c r="AN236" s="22" t="n"/>
     </row>
     <row r="237" ht="30" customHeight="1">
       <c r="A237" s="15" t="inlineStr">
         <is>
-          <t>BA02-02</t>
+          <t>BA02-03</t>
         </is>
       </c>
       <c r="B237" s="15" t="n"/>
@@ -29575,17 +29899,17 @@
       </c>
       <c r="E237" s="15" t="inlineStr">
         <is>
-          <t>Rutscherauto rot</t>
+          <t>Bilder Schwarzwald, gerahmt</t>
         </is>
       </c>
       <c r="F237" s="16" t="inlineStr">
         <is>
-          <t>Rutscherauto in Sportwagenform, roter Kunststoffkorpus mit schwarzer Sitzfläche in Rautensteppung, verchromte Felgen, Lehne hinten zum Schieben.</t>
+          <t>Schwarz gerahmte Zeichnungen hinter Glas in schlichter Strichtechnik: Bergkette, Mädchen mit Bollenhut und Tannenwald. Motivgruppe Schwarzwald.</t>
         </is>
       </c>
       <c r="G237" s="15" t="inlineStr">
         <is>
-          <t>Kita-Ausstattung</t>
+          <t>Kunst</t>
         </is>
       </c>
       <c r="H237" s="15" t="inlineStr">
@@ -29599,7 +29923,7 @@
         </is>
       </c>
       <c r="J237" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K237" s="17" t="n"/>
       <c r="L237" s="18">
@@ -29613,7 +29937,7 @@
       </c>
       <c r="N237" s="15" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="O237" s="19" t="n"/>
@@ -29625,7 +29949,7 @@
       <c r="Q237" s="19" t="n"/>
       <c r="R237" s="20" t="n"/>
       <c r="S237" s="20" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="T237" s="19" t="inlineStr">
         <is>
@@ -29638,12 +29962,12 @@
       </c>
       <c r="V237" s="15" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="W237" s="15" t="inlineStr">
         <is>
-          <t>F-263</t>
+          <t>F-264</t>
         </is>
       </c>
       <c r="X237" s="19" t="inlineStr">
@@ -29658,30 +29982,35 @@
         </is>
       </c>
       <c r="AA237" s="19" t="n"/>
-      <c r="AB237" s="19" t="n"/>
+      <c r="AB237" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
       <c r="AC237" s="19" t="n"/>
-      <c r="AD237" s="20" t="n"/>
-      <c r="AE237" s="21">
-        <f>IF(K237="","",K237*AD237)</f>
-        <v/>
-      </c>
-      <c r="AF237" s="19" t="n"/>
+      <c r="AD237" s="19" t="n"/>
+      <c r="AE237" s="20" t="n"/>
+      <c r="AF237" s="21">
+        <f>IF(K237="","",K237*AE237)</f>
+        <v/>
+      </c>
       <c r="AG237" s="19" t="n"/>
       <c r="AH237" s="19" t="n"/>
       <c r="AI237" s="19" t="n"/>
       <c r="AJ237" s="19" t="n"/>
       <c r="AK237" s="19" t="n"/>
-      <c r="AL237" s="16" t="inlineStr">
-        <is>
-          <t>1 Fahrzeug.</t>
-        </is>
-      </c>
-      <c r="AM237" s="22" t="n"/>
+      <c r="AL237" s="19" t="n"/>
+      <c r="AM237" s="16" t="inlineStr">
+        <is>
+          <t>3 Bilder, alle abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN237" s="22" t="n"/>
     </row>
     <row r="238" ht="30" customHeight="1">
       <c r="A238" s="15" t="inlineStr">
         <is>
-          <t>BA02-03</t>
+          <t>BA02-04</t>
         </is>
       </c>
       <c r="B238" s="15" t="n"/>
@@ -29693,17 +30022,17 @@
       </c>
       <c r="E238" s="15" t="inlineStr">
         <is>
-          <t>Bilder Schwarzwald, gerahmt</t>
+          <t>Kinder-Ohrensessel grau, Kunstleder</t>
         </is>
       </c>
       <c r="F238" s="16" t="inlineStr">
         <is>
-          <t>Schwarz gerahmte Zeichnungen hinter Glas in schlichter Strichtechnik: Bergkette, Mädchen mit Bollenhut und Tannenwald. Motivgruppe Schwarzwald.</t>
+          <t>Ohrensessel in Kindergröße, hellgrauer Kunstlederbezug, geschwungene schwarze Holzbeine.</t>
         </is>
       </c>
       <c r="G238" s="15" t="inlineStr">
         <is>
-          <t>Kunst</t>
+          <t>Möbel</t>
         </is>
       </c>
       <c r="H238" s="15" t="inlineStr">
@@ -29717,7 +30046,7 @@
         </is>
       </c>
       <c r="J238" s="17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K238" s="17" t="n"/>
       <c r="L238" s="18">
@@ -29731,7 +30060,7 @@
       </c>
       <c r="N238" s="15" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="O238" s="19" t="n"/>
@@ -29743,7 +30072,7 @@
       <c r="Q238" s="19" t="n"/>
       <c r="R238" s="20" t="n"/>
       <c r="S238" s="20" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T238" s="19" t="inlineStr">
         <is>
@@ -29756,12 +30085,12 @@
       </c>
       <c r="V238" s="15" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="W238" s="15" t="inlineStr">
         <is>
-          <t>F-264</t>
+          <t>F-265</t>
         </is>
       </c>
       <c r="X238" s="19" t="inlineStr">
@@ -29778,28 +30107,29 @@
       <c r="AA238" s="19" t="n"/>
       <c r="AB238" s="19" t="n"/>
       <c r="AC238" s="19" t="n"/>
-      <c r="AD238" s="20" t="n"/>
-      <c r="AE238" s="21">
-        <f>IF(K238="","",K238*AD238)</f>
-        <v/>
-      </c>
-      <c r="AF238" s="19" t="n"/>
+      <c r="AD238" s="19" t="n"/>
+      <c r="AE238" s="20" t="n"/>
+      <c r="AF238" s="21">
+        <f>IF(K238="","",K238*AE238)</f>
+        <v/>
+      </c>
       <c r="AG238" s="19" t="n"/>
       <c r="AH238" s="19" t="n"/>
       <c r="AI238" s="19" t="n"/>
       <c r="AJ238" s="19" t="n"/>
       <c r="AK238" s="19" t="n"/>
-      <c r="AL238" s="16" t="inlineStr">
-        <is>
-          <t>3 Bilder, alle abgebildet.</t>
-        </is>
-      </c>
-      <c r="AM238" s="22" t="n"/>
+      <c r="AL238" s="19" t="n"/>
+      <c r="AM238" s="16" t="inlineStr">
+        <is>
+          <t>1 Sessel. Baugleich in Rot gibt es zwei Stück unter NE01-20.</t>
+        </is>
+      </c>
+      <c r="AN238" s="22" t="n"/>
     </row>
     <row r="239" ht="30" customHeight="1">
       <c r="A239" s="15" t="inlineStr">
         <is>
-          <t>BA02-04</t>
+          <t>BA02-05</t>
         </is>
       </c>
       <c r="B239" s="15" t="n"/>
@@ -29811,12 +30141,12 @@
       </c>
       <c r="E239" s="15" t="inlineStr">
         <is>
-          <t>Kinder-Ohrensessel grau, Kunstleder</t>
+          <t>Ablagepult Holz auf Metallgestell</t>
         </is>
       </c>
       <c r="F239" s="16" t="inlineStr">
         <is>
-          <t>Ohrensessel in Kindergröße, hellgrauer Kunstlederbezug, geschwungene schwarze Holzbeine.</t>
+          <t>Pult mit geneigter Platte aus dunklem Holz mit schwarzer Auflage, auf einem C-förmigen schwarzen Metallgestell. Untergreifbar, im Haus als Stehpult für die Anwesenheitsliste genutzt.</t>
         </is>
       </c>
       <c r="G239" s="15" t="inlineStr">
@@ -29861,7 +30191,7 @@
       <c r="Q239" s="19" t="n"/>
       <c r="R239" s="20" t="n"/>
       <c r="S239" s="20" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="T239" s="19" t="inlineStr">
         <is>
@@ -29879,7 +30209,7 @@
       </c>
       <c r="W239" s="15" t="inlineStr">
         <is>
-          <t>F-265</t>
+          <t>F-266</t>
         </is>
       </c>
       <c r="X239" s="19" t="inlineStr">
@@ -29896,28 +30226,29 @@
       <c r="AA239" s="19" t="n"/>
       <c r="AB239" s="19" t="n"/>
       <c r="AC239" s="19" t="n"/>
-      <c r="AD239" s="20" t="n"/>
-      <c r="AE239" s="21">
-        <f>IF(K239="","",K239*AD239)</f>
-        <v/>
-      </c>
-      <c r="AF239" s="19" t="n"/>
+      <c r="AD239" s="19" t="n"/>
+      <c r="AE239" s="20" t="n"/>
+      <c r="AF239" s="21">
+        <f>IF(K239="","",K239*AE239)</f>
+        <v/>
+      </c>
       <c r="AG239" s="19" t="n"/>
       <c r="AH239" s="19" t="n"/>
       <c r="AI239" s="19" t="n"/>
       <c r="AJ239" s="19" t="n"/>
       <c r="AK239" s="19" t="n"/>
-      <c r="AL239" s="16" t="inlineStr">
-        <is>
-          <t>1 Sessel. Baugleich in Rot gibt es zwei Stück unter NE01-20.</t>
-        </is>
-      </c>
-      <c r="AM239" s="22" t="n"/>
+      <c r="AL239" s="19" t="n"/>
+      <c r="AM239" s="16" t="inlineStr">
+        <is>
+          <t>1 Pult. Die Liste gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN239" s="22" t="n"/>
     </row>
     <row r="240" ht="30" customHeight="1">
       <c r="A240" s="15" t="inlineStr">
         <is>
-          <t>BA02-05</t>
+          <t>BA02-06</t>
         </is>
       </c>
       <c r="B240" s="15" t="n"/>
@@ -29929,17 +30260,17 @@
       </c>
       <c r="E240" s="15" t="inlineStr">
         <is>
-          <t>Ablagepult Holz auf Metallgestell</t>
+          <t>Truhenbank weiß mit Fellauflage</t>
         </is>
       </c>
       <c r="F240" s="16" t="inlineStr">
         <is>
-          <t>Pult mit geneigter Platte aus dunklem Holz mit schwarzer Auflage, auf einem C-förmigen schwarzen Metallgestell. Untergreifbar, im Haus als Stehpult für die Anwesenheitsliste genutzt.</t>
+          <t>Sitzbank in Weiß mit geschwungenen Seitenteilen, Rückenbrett und aufklappbarer Sitzfläche mit Beschlägen. Darunter ein großer Stauraum. Eine weiße Fellauflage liegt auf der Sitzfläche.</t>
         </is>
       </c>
       <c r="G240" s="15" t="inlineStr">
         <is>
-          <t>Möbel</t>
+          <t>Kita-Ausstattung</t>
         </is>
       </c>
       <c r="H240" s="15" t="inlineStr">
@@ -29997,7 +30328,7 @@
       </c>
       <c r="W240" s="15" t="inlineStr">
         <is>
-          <t>F-266</t>
+          <t>F-267</t>
         </is>
       </c>
       <c r="X240" s="19" t="inlineStr">
@@ -30014,28 +30345,29 @@
       <c r="AA240" s="19" t="n"/>
       <c r="AB240" s="19" t="n"/>
       <c r="AC240" s="19" t="n"/>
-      <c r="AD240" s="20" t="n"/>
-      <c r="AE240" s="21">
-        <f>IF(K240="","",K240*AD240)</f>
-        <v/>
-      </c>
-      <c r="AF240" s="19" t="n"/>
+      <c r="AD240" s="19" t="n"/>
+      <c r="AE240" s="20" t="n"/>
+      <c r="AF240" s="21">
+        <f>IF(K240="","",K240*AE240)</f>
+        <v/>
+      </c>
       <c r="AG240" s="19" t="n"/>
       <c r="AH240" s="19" t="n"/>
       <c r="AI240" s="19" t="n"/>
       <c r="AJ240" s="19" t="n"/>
       <c r="AK240" s="19" t="n"/>
-      <c r="AL240" s="16" t="inlineStr">
-        <is>
-          <t>1 Pult. Die Liste gehört nicht dazu.</t>
-        </is>
-      </c>
-      <c r="AM240" s="22" t="n"/>
+      <c r="AL240" s="19" t="n"/>
+      <c r="AM240" s="16" t="inlineStr">
+        <is>
+          <t>1 Bank einschließlich der Fellauflage. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN240" s="22" t="n"/>
     </row>
     <row r="241" ht="30" customHeight="1">
       <c r="A241" s="15" t="inlineStr">
         <is>
-          <t>BA02-06</t>
+          <t>BA02-08</t>
         </is>
       </c>
       <c r="B241" s="15" t="n"/>
@@ -30047,17 +30379,17 @@
       </c>
       <c r="E241" s="15" t="inlineStr">
         <is>
-          <t>Truhenbank weiß mit Fellauflage</t>
+          <t>Kinderschrank weiß mit Handabdrücken</t>
         </is>
       </c>
       <c r="F241" s="16" t="inlineStr">
         <is>
-          <t>Sitzbank in Weiß mit geschwungenen Seitenteilen, Rückenbrett und aufklappbarer Sitzfläche mit Beschlägen. Darunter ein großer Stauraum. Eine weiße Fellauflage liegt auf der Sitzfläche.</t>
+          <t>Hoher Schrank in Weiß mit Türen und Schubladen, Griffmulden. Auf den Fronten kleben Aufkleber mit Kinderhandabdrücken in Schwarz und Rot; sie lassen sich abziehen.</t>
         </is>
       </c>
       <c r="G241" s="15" t="inlineStr">
         <is>
-          <t>Kita-Ausstattung</t>
+          <t>Möbel</t>
         </is>
       </c>
       <c r="H241" s="15" t="inlineStr">
@@ -30071,7 +30403,7 @@
         </is>
       </c>
       <c r="J241" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K241" s="17" t="n"/>
       <c r="L241" s="18">
@@ -30097,7 +30429,7 @@
       <c r="Q241" s="19" t="n"/>
       <c r="R241" s="20" t="n"/>
       <c r="S241" s="20" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="T241" s="19" t="inlineStr">
         <is>
@@ -30115,7 +30447,7 @@
       </c>
       <c r="W241" s="15" t="inlineStr">
         <is>
-          <t>F-267</t>
+          <t>F-269</t>
         </is>
       </c>
       <c r="X241" s="19" t="inlineStr">
@@ -30132,28 +30464,29 @@
       <c r="AA241" s="19" t="n"/>
       <c r="AB241" s="19" t="n"/>
       <c r="AC241" s="19" t="n"/>
-      <c r="AD241" s="20" t="n"/>
-      <c r="AE241" s="21">
-        <f>IF(K241="","",K241*AD241)</f>
-        <v/>
-      </c>
-      <c r="AF241" s="19" t="n"/>
+      <c r="AD241" s="19" t="n"/>
+      <c r="AE241" s="20" t="n"/>
+      <c r="AF241" s="21">
+        <f>IF(K241="","",K241*AE241)</f>
+        <v/>
+      </c>
       <c r="AG241" s="19" t="n"/>
       <c r="AH241" s="19" t="n"/>
       <c r="AI241" s="19" t="n"/>
       <c r="AJ241" s="19" t="n"/>
       <c r="AK241" s="19" t="n"/>
-      <c r="AL241" s="16" t="inlineStr">
-        <is>
-          <t>1 Bank einschließlich der Fellauflage. Der Inhalt gehört nicht dazu.</t>
-        </is>
-      </c>
-      <c r="AM241" s="22" t="n"/>
+      <c r="AL241" s="19" t="n"/>
+      <c r="AM241" s="16" t="inlineStr">
+        <is>
+          <t>2 Schränke – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AN241" s="22" t="n"/>
     </row>
     <row r="242" ht="30" customHeight="1">
       <c r="A242" s="15" t="inlineStr">
         <is>
-          <t>BA02-08</t>
+          <t>BA02-09</t>
         </is>
       </c>
       <c r="B242" s="15" t="n"/>
@@ -30165,17 +30498,17 @@
       </c>
       <c r="E242" s="15" t="inlineStr">
         <is>
-          <t>Kinderschrank weiß mit Handabdrücken</t>
+          <t>Deko-Häuser Keramik</t>
         </is>
       </c>
       <c r="F242" s="16" t="inlineStr">
         <is>
-          <t>Hoher Schrank in Weiß mit Türen und Schubladen, Griffmulden. Auf den Fronten kleben Aufkleber mit Kinderhandabdrücken in Schwarz und Rot; sie lassen sich abziehen.</t>
+          <t>Drei Häuschen aus Keramik mit ausgestanzten Fenstern, zum Beleuchten mit einem Teelicht: eines craquelé-grau, eines cremeweiß glasiert, eines dunkelgrau mit rundem Fenster.</t>
         </is>
       </c>
       <c r="G242" s="15" t="inlineStr">
         <is>
-          <t>Möbel</t>
+          <t>Deko</t>
         </is>
       </c>
       <c r="H242" s="15" t="inlineStr">
@@ -30185,11 +30518,11 @@
       </c>
       <c r="I242" s="15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J242" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K242" s="17" t="n"/>
       <c r="L242" s="18">
@@ -30203,7 +30536,7 @@
       </c>
       <c r="N242" s="15" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="O242" s="19" t="n"/>
@@ -30215,7 +30548,7 @@
       <c r="Q242" s="19" t="n"/>
       <c r="R242" s="20" t="n"/>
       <c r="S242" s="20" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="T242" s="19" t="inlineStr">
         <is>
@@ -30228,12 +30561,12 @@
       </c>
       <c r="V242" s="15" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="W242" s="15" t="inlineStr">
         <is>
-          <t>F-269</t>
+          <t>F-270</t>
         </is>
       </c>
       <c r="X242" s="19" t="inlineStr">
@@ -30250,154 +30583,37 @@
       <c r="AA242" s="19" t="n"/>
       <c r="AB242" s="19" t="n"/>
       <c r="AC242" s="19" t="n"/>
-      <c r="AD242" s="20" t="n"/>
-      <c r="AE242" s="21">
-        <f>IF(K242="","",K242*AD242)</f>
-        <v/>
-      </c>
-      <c r="AF242" s="19" t="n"/>
+      <c r="AD242" s="19" t="n"/>
+      <c r="AE242" s="20" t="n"/>
+      <c r="AF242" s="21">
+        <f>IF(K242="","",K242*AE242)</f>
+        <v/>
+      </c>
       <c r="AG242" s="19" t="n"/>
       <c r="AH242" s="19" t="n"/>
       <c r="AI242" s="19" t="n"/>
       <c r="AJ242" s="19" t="n"/>
       <c r="AK242" s="19" t="n"/>
-      <c r="AL242" s="16" t="inlineStr">
-        <is>
-          <t>2 Schränke – abgebildet ist einer davon.</t>
-        </is>
-      </c>
-      <c r="AM242" s="22" t="n"/>
-    </row>
-    <row r="243" ht="30" customHeight="1">
-      <c r="A243" s="15" t="inlineStr">
-        <is>
-          <t>BA02-09</t>
-        </is>
-      </c>
-      <c r="B243" s="15" t="n"/>
-      <c r="C243" s="15" t="n"/>
-      <c r="D243" s="15" t="inlineStr">
-        <is>
-          <t>BA02</t>
-        </is>
-      </c>
-      <c r="E243" s="15" t="inlineStr">
-        <is>
-          <t>Deko-Häuser Keramik</t>
-        </is>
-      </c>
-      <c r="F243" s="16" t="inlineStr">
-        <is>
-          <t>Drei Häuschen aus Keramik mit ausgestanzten Fenstern, zum Beleuchten mit einem Teelicht: eines craquelé-grau, eines cremeweiß glasiert, eines dunkelgrau mit rundem Fenster.</t>
-        </is>
-      </c>
-      <c r="G243" s="15" t="inlineStr">
-        <is>
-          <t>Deko</t>
-        </is>
-      </c>
-      <c r="H243" s="15" t="inlineStr">
-        <is>
-          <t>Flur 2</t>
-        </is>
-      </c>
-      <c r="I243" s="15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J243" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="K243" s="17" t="n"/>
-      <c r="L243" s="18">
-        <f>J243-IF(K243="",0,K243)</f>
-        <v/>
-      </c>
-      <c r="M243" s="15" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="N243" s="15" t="inlineStr">
-        <is>
-          <t>gut</t>
-        </is>
-      </c>
-      <c r="O243" s="19" t="n"/>
-      <c r="P243" s="19" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="Q243" s="19" t="n"/>
-      <c r="R243" s="20" t="n"/>
-      <c r="S243" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="T243" s="19" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="U243" s="21">
-        <f>L243*S243</f>
-        <v/>
-      </c>
-      <c r="V243" s="15" t="inlineStr">
-        <is>
-          <t>Versand möglich</t>
-        </is>
-      </c>
-      <c r="W243" s="15" t="inlineStr">
-        <is>
-          <t>F-270</t>
-        </is>
-      </c>
-      <c r="X243" s="19" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="Y243" s="19" t="n"/>
-      <c r="Z243" s="19" t="inlineStr">
-        <is>
-          <t>verfügbar</t>
-        </is>
-      </c>
-      <c r="AA243" s="19" t="n"/>
-      <c r="AB243" s="19" t="n"/>
-      <c r="AC243" s="19" t="n"/>
-      <c r="AD243" s="20" t="n"/>
-      <c r="AE243" s="21">
-        <f>IF(K243="","",K243*AD243)</f>
-        <v/>
-      </c>
-      <c r="AF243" s="19" t="n"/>
-      <c r="AG243" s="19" t="n"/>
-      <c r="AH243" s="19" t="n"/>
-      <c r="AI243" s="19" t="n"/>
-      <c r="AJ243" s="19" t="n"/>
-      <c r="AK243" s="19" t="n"/>
-      <c r="AL243" s="16" t="inlineStr">
+      <c r="AL242" s="19" t="n"/>
+      <c r="AM242" s="16" t="inlineStr">
         <is>
           <t>3 Häuschen, alle abgebildet.</t>
         </is>
       </c>
-      <c r="AM243" s="22" t="n"/>
+      <c r="AN242" s="22" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AM243"/>
+  <autoFilter ref="A2:AN242"/>
   <mergeCells count="7">
-    <mergeCell ref="AH1:AK1"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="V1:AD1"/>
     <mergeCell ref="S1:U1"/>
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="V1:AC1"/>
-    <mergeCell ref="AL1:AM1"/>
-    <mergeCell ref="AD1:AG1"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z243">
+  <conditionalFormatting sqref="Z3:Z242">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -30408,12 +30624,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I243">
+  <conditionalFormatting sqref="I3:I242">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P243">
+  <conditionalFormatting sqref="P3:P242">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -30446,13 +30662,13 @@
     <dataValidation sqref="Z3:Z803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"verfügbar,reserviert,teilverkauft,verkauft,gespendet,entsorgt"</formula1>
     </dataValidation>
-    <dataValidation sqref="AB3:AB803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AC3:AC803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Webkatalog,Kleinanzeigen,eBay,Direkt,Händler,Verkaufstag"</formula1>
     </dataValidation>
-    <dataValidation sqref="AI3:AI803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AJ3:AJ803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"offen,bezahlt,teilbezahlt"</formula1>
     </dataValidation>
-    <dataValidation sqref="AJ3:AJ803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AK3:AK803" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Überweisung,bar,PayPal"</formula1>
     </dataValidation>
   </dataValidations>
@@ -30504,7 +30720,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$243)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$242)</f>
         <v/>
       </c>
     </row>
@@ -30515,7 +30731,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$242,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -30526,7 +30742,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$242,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -30537,7 +30753,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$242,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -30548,7 +30764,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$242,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -30559,7 +30775,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$243)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$242)</f>
         <v/>
       </c>
     </row>
@@ -30570,7 +30786,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$243)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30588,7 +30804,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$243)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$242)</f>
         <v/>
       </c>
     </row>
@@ -30599,7 +30815,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$243,Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$242,Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
     </row>
@@ -30632,7 +30848,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AI$3:$AI$243="bezahlt")*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$242="bezahlt")*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
     </row>
@@ -30661,7 +30877,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"*verkauft",Artikelstamm!$AH$3:$AH$243,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$242,"*verkauft",Artikelstamm!$AI$3:$AI$242,"")</f>
         <v/>
       </c>
     </row>
@@ -30672,7 +30888,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"*verkauft",Artikelstamm!$AI$3:$AI$243,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$242,"*verkauft",Artikelstamm!$AJ$3:$AJ$242,"offen")</f>
         <v/>
       </c>
     </row>
@@ -30683,7 +30899,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"reserviert",Artikelstamm!$AK$3:$AK$243,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$242,"reserviert",Artikelstamm!$AL$3:$AL$242,"")</f>
         <v/>
       </c>
     </row>
@@ -30694,7 +30910,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$243,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$242,"")</f>
         <v/>
       </c>
     </row>
@@ -30705,7 +30921,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$243,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$242,"")</f>
         <v/>
       </c>
     </row>
@@ -30745,15 +30961,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$242,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A30)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$242=$A30)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A30,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$242,$A30,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30764,15 +30980,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$242,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A31)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$242=$A31)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A31,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$242,$A31,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30783,15 +30999,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$242,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A32)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$242=$A32)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A32,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$242,$A32,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30850,15 +31066,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A37)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A37)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A37,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A37,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30869,15 +31085,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A38)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A38)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A38,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A38,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30888,15 +31104,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A39)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A39)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A39,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A39,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30907,15 +31123,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A40)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A40)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A40,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A40,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30926,15 +31142,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A41)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A41)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A41,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A41,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30945,15 +31161,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A42)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A42)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A42,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A42,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30964,15 +31180,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A43)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A43)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A43,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A43,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -30983,15 +31199,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A44)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A44)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A44,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A44,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31002,15 +31218,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A45)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A45)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A45,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A45,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31021,15 +31237,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A46)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A46)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A46,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A46,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31040,15 +31256,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A47)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A47)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A47,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A47,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31059,15 +31275,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A48)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A48)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A48,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A48,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31078,15 +31294,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A49)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A49)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A49,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A49,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31097,15 +31313,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A50)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A50)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A50,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A50,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31164,15 +31380,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A55)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A55)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A55,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A55,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31183,15 +31399,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A56)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A56)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A56,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A56,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31202,15 +31418,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A57)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A57)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A57,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A57,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31221,15 +31437,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A58)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A58)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A58,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A58,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31240,15 +31456,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A59)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A59)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A59,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A59,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31259,15 +31475,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A60)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A60)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A60,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A60,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31278,15 +31494,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A61)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A61)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A61,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A61,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31297,15 +31513,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A62)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A62)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A62,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A62,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31316,15 +31532,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A63)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A63)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A63,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A63,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31335,15 +31551,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A64)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A64)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A64,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A64,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31354,15 +31570,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A65)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A65)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A65,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A65,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31373,15 +31589,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A66)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A66)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A66,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A66,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31392,15 +31608,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A67)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A67)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A67,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A67,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31411,15 +31627,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A68)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A68)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A68,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A68,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31430,15 +31646,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A69)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A69)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A69,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A69,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31449,15 +31665,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A70)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A70)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A70,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A70,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31468,15 +31684,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A71)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A71)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A71,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A71,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31487,15 +31703,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A72)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A72)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A72,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A72,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31506,15 +31722,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A73)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A73)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A73,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A73,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31525,15 +31741,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A74)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A74)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A74,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A74,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31544,15 +31760,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A75)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A75)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A75,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A75,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31563,15 +31779,15 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A76)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A76)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A76,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A76,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31582,15 +31798,15 @@
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A77)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A77)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A77,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A77,Artikelstamm!$U$3:$U$242)</f>
         <v/>
       </c>
     </row>
@@ -31644,11 +31860,11 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A82)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A82)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
     </row>
@@ -31659,11 +31875,11 @@
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A83)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A83)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
     </row>
@@ -31674,11 +31890,11 @@
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A84)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A84)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
     </row>
@@ -31689,11 +31905,11 @@
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A85)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A85)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
     </row>
@@ -31704,11 +31920,11 @@
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A86)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A86)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
     </row>
@@ -31719,11 +31935,11 @@
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AB$3:$AB$243,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AB$3:$AB$243=$A87)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AD$3:$AD$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A87)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$242</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$243</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN242"/>
+  <dimension ref="A1:AN243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="J13" s="17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K13" s="17" t="n"/>
       <c r="L13" s="18">
@@ -2667,7 +2667,7 @@
       <c r="AL13" s="19" t="n"/>
       <c r="AM13" s="16" t="inlineStr">
         <is>
-          <t>mindestens 6 Stück erkennbar - bitte nachzählen</t>
+          <t>4 Stühle – abgebildet sind zwei davon.</t>
         </is>
       </c>
       <c r="AN13" s="22" t="n"/>
@@ -30602,8 +30602,127 @@
       </c>
       <c r="AN242" s="22" t="n"/>
     </row>
+    <row r="243" ht="30" customHeight="1">
+      <c r="A243" s="15" t="inlineStr">
+        <is>
+          <t>BA09-06</t>
+        </is>
+      </c>
+      <c r="B243" s="15" t="n"/>
+      <c r="C243" s="15" t="n"/>
+      <c r="D243" s="15" t="inlineStr">
+        <is>
+          <t>BA09</t>
+        </is>
+      </c>
+      <c r="E243" s="15" t="inlineStr">
+        <is>
+          <t>Sitzhocker rund, drehbar auf Rollen</t>
+        </is>
+      </c>
+      <c r="F243" s="16" t="inlineStr">
+        <is>
+          <t>Runder Sitzhocker mit schwarzem Netzstoffbezug und umlaufendem Reißverschluss, auf einem silberfarbenen Fünffußkreuz mit Rollen, höhenverstellbar.</t>
+        </is>
+      </c>
+      <c r="G243" s="15" t="inlineStr">
+        <is>
+          <t>Büro</t>
+        </is>
+      </c>
+      <c r="H243" s="15" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="I243" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J243" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K243" s="17" t="n"/>
+      <c r="L243" s="18">
+        <f>J243-IF(K243="",0,K243)</f>
+        <v/>
+      </c>
+      <c r="M243" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N243" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O243" s="19" t="n"/>
+      <c r="P243" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q243" s="19" t="n"/>
+      <c r="R243" s="20" t="n"/>
+      <c r="S243" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T243" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U243" s="21">
+        <f>L243*S243</f>
+        <v/>
+      </c>
+      <c r="V243" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W243" s="15" t="inlineStr">
+        <is>
+          <t>F-274</t>
+        </is>
+      </c>
+      <c r="X243" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y243" s="19" t="n"/>
+      <c r="Z243" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA243" s="19" t="n"/>
+      <c r="AB243" s="19" t="n"/>
+      <c r="AC243" s="19" t="n"/>
+      <c r="AD243" s="19" t="n"/>
+      <c r="AE243" s="20" t="n"/>
+      <c r="AF243" s="21">
+        <f>IF(K243="","",K243*AE243)</f>
+        <v/>
+      </c>
+      <c r="AG243" s="19" t="n"/>
+      <c r="AH243" s="19" t="n"/>
+      <c r="AI243" s="19" t="n"/>
+      <c r="AJ243" s="19" t="n"/>
+      <c r="AK243" s="19" t="n"/>
+      <c r="AL243" s="19" t="n"/>
+      <c r="AM243" s="16" t="inlineStr">
+        <is>
+          <t>1 Hocker.</t>
+        </is>
+      </c>
+      <c r="AN243" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN242"/>
+  <autoFilter ref="A2:AN243"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -30613,7 +30732,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z242">
+  <conditionalFormatting sqref="Z3:Z243">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -30624,12 +30743,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I242">
+  <conditionalFormatting sqref="I3:I243">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P242">
+  <conditionalFormatting sqref="P3:P243">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -30720,7 +30839,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$242)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$243)</f>
         <v/>
       </c>
     </row>
@@ -30731,7 +30850,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$242,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -30742,7 +30861,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$242,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -30753,7 +30872,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$242,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -30764,7 +30883,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$242,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -30775,7 +30894,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$242)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$243)</f>
         <v/>
       </c>
     </row>
@@ -30786,7 +30905,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$242)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30804,7 +30923,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$242)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$243)</f>
         <v/>
       </c>
     </row>
@@ -30815,7 +30934,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$242,Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$243,Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
     </row>
@@ -30848,7 +30967,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$242="bezahlt")*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$243="bezahlt")*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
     </row>
@@ -30877,7 +30996,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$242,"*verkauft",Artikelstamm!$AI$3:$AI$242,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"*verkauft",Artikelstamm!$AI$3:$AI$243,"")</f>
         <v/>
       </c>
     </row>
@@ -30888,7 +31007,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$242,"*verkauft",Artikelstamm!$AJ$3:$AJ$242,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"*verkauft",Artikelstamm!$AJ$3:$AJ$243,"offen")</f>
         <v/>
       </c>
     </row>
@@ -30899,7 +31018,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$242,"reserviert",Artikelstamm!$AL$3:$AL$242,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"reserviert",Artikelstamm!$AL$3:$AL$243,"")</f>
         <v/>
       </c>
     </row>
@@ -30910,7 +31029,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$242,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$243,"")</f>
         <v/>
       </c>
     </row>
@@ -30921,7 +31040,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$242,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$243,"")</f>
         <v/>
       </c>
     </row>
@@ -30961,15 +31080,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$242,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$242=$A30)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A30)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$242,$A30,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A30,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30980,15 +31099,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$242,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$242=$A31)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A31)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$242,$A31,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A31,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -30999,15 +31118,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$242,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$242=$A32)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A32)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$242,$A32,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A32,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31066,15 +31185,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A37)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A37)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A37,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A37,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31085,15 +31204,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A38)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A38)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A38,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A38,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31104,15 +31223,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A39)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A39)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A39,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A39,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31123,15 +31242,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A40)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A40)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A40,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A40,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31142,15 +31261,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A41)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A41)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A41,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A41,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31161,15 +31280,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A42)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A42)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A42,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A42,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31180,15 +31299,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A43)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A43)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A43,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A43,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31199,15 +31318,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A44)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A44)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A44,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A44,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31218,15 +31337,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A45)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A45)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A45,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A45,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31237,15 +31356,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A46)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A46)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A46,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A46,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31256,15 +31375,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A47)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A47)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A47,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A47,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31275,15 +31394,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A48)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A48)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A48,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A48,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31294,15 +31413,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A49)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A49)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A49,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A49,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31313,15 +31432,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$242,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$242=$A50)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A50)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$242,$A50,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A50,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31380,15 +31499,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A55)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A55)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A55,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A55,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31399,15 +31518,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A56)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A56)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A56,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A56,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31418,15 +31537,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A57)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A57)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A57,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A57,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31437,15 +31556,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A58)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A58)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A58,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A58,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31456,15 +31575,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A59)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A59)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A59,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A59,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31475,15 +31594,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A60)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A60)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A60,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A60,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31494,15 +31613,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A61)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A61)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A61,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A61,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31513,15 +31632,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A62)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A62)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A62,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A62,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31532,15 +31651,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A63)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A63)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A63,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A63,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31551,15 +31670,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A64)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A64)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A64,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A64,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31570,15 +31689,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A65)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A65)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A65,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A65,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31589,15 +31708,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A66)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A66)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A66,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A66,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31608,15 +31727,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A67)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A67)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A67,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A67,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31627,15 +31746,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A68)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A68)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A68,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A68,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31646,15 +31765,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A69)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A69)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A69,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A69,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31665,15 +31784,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A70)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A70)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A70,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A70,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31684,15 +31803,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A71)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A71)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A71,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A71,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31703,15 +31822,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A72)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A72)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A72,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A72,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31722,15 +31841,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A73)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A73)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A73,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A73,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31741,15 +31860,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A74)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A74)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A74,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A74,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31760,15 +31879,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A75)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A75)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A75,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A75,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31779,15 +31898,15 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A76)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A76)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A76,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A76,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31798,15 +31917,15 @@
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$242,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$242=$A77)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A77)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$242,$A77,Artikelstamm!$U$3:$U$242)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A77,Artikelstamm!$U$3:$U$243)</f>
         <v/>
       </c>
     </row>
@@ -31860,11 +31979,11 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A82)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A82)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
     </row>
@@ -31875,11 +31994,11 @@
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A83)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A83)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
     </row>
@@ -31890,11 +32009,11 @@
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A84)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A84)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
     </row>
@@ -31905,11 +32024,11 @@
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A85)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A85)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
     </row>
@@ -31920,11 +32039,11 @@
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A86)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A86)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
     </row>
@@ -31935,11 +32054,11 @@
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$242,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$242=$A87)*Artikelstamm!$K$3:$K$242*Artikelstamm!$AE$3:$AE$242)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A87)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$243</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$252</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN243"/>
+  <dimension ref="A1:AN252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30721,8 +30721,1087 @@
       </c>
       <c r="AN243" s="22" t="n"/>
     </row>
+    <row r="244" ht="30" customHeight="1">
+      <c r="A244" s="15" t="inlineStr">
+        <is>
+          <t>NE02-01</t>
+        </is>
+      </c>
+      <c r="B244" s="15" t="n"/>
+      <c r="C244" s="15" t="n"/>
+      <c r="D244" s="15" t="inlineStr">
+        <is>
+          <t>NE02</t>
+        </is>
+      </c>
+      <c r="E244" s="15" t="inlineStr">
+        <is>
+          <t>Hirsch Metall, stehend</t>
+        </is>
+      </c>
+      <c r="F244" s="16" t="inlineStr">
+        <is>
+          <t>Figur eines Hirschs aus Metall mit dunkler, teils silbrig durchscheinender Oberfläche, auf länglichem Sockel mit Geweihstück.</t>
+        </is>
+      </c>
+      <c r="G244" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H244" s="15" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="I244" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J244" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K244" s="17" t="n"/>
+      <c r="L244" s="18">
+        <f>J244-IF(K244="",0,K244)</f>
+        <v/>
+      </c>
+      <c r="M244" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N244" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O244" s="19" t="n"/>
+      <c r="P244" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q244" s="19" t="n"/>
+      <c r="R244" s="20" t="n"/>
+      <c r="S244" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T244" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U244" s="21">
+        <f>L244*S244</f>
+        <v/>
+      </c>
+      <c r="V244" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W244" s="15" t="inlineStr">
+        <is>
+          <t>F-276</t>
+        </is>
+      </c>
+      <c r="X244" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y244" s="19" t="n"/>
+      <c r="Z244" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA244" s="19" t="n"/>
+      <c r="AB244" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
+      <c r="AC244" s="19" t="n"/>
+      <c r="AD244" s="19" t="n"/>
+      <c r="AE244" s="20" t="n"/>
+      <c r="AF244" s="21">
+        <f>IF(K244="","",K244*AE244)</f>
+        <v/>
+      </c>
+      <c r="AG244" s="19" t="n"/>
+      <c r="AH244" s="19" t="n"/>
+      <c r="AI244" s="19" t="n"/>
+      <c r="AJ244" s="19" t="n"/>
+      <c r="AK244" s="19" t="n"/>
+      <c r="AL244" s="19" t="n"/>
+      <c r="AM244" s="16" t="inlineStr">
+        <is>
+          <t>1 Figur.</t>
+        </is>
+      </c>
+      <c r="AN244" s="22" t="n"/>
+    </row>
+    <row r="245" ht="30" customHeight="1">
+      <c r="A245" s="15" t="inlineStr">
+        <is>
+          <t>NE02-02</t>
+        </is>
+      </c>
+      <c r="B245" s="15" t="n"/>
+      <c r="C245" s="15" t="n"/>
+      <c r="D245" s="15" t="inlineStr">
+        <is>
+          <t>NE02</t>
+        </is>
+      </c>
+      <c r="E245" s="15" t="inlineStr">
+        <is>
+          <t>Barhocker dunkelgrau, Erwachsenenhöhe</t>
+        </is>
+      </c>
+      <c r="F245" s="16" t="inlineStr">
+        <is>
+          <t>Barhocker mit dunkelgrauer Kunststoffschale auf schwarzem Kufengestell aus Rundstahl, mit Fußstütze.</t>
+        </is>
+      </c>
+      <c r="G245" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H245" s="15" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="I245" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J245" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K245" s="17" t="n"/>
+      <c r="L245" s="18">
+        <f>J245-IF(K245="",0,K245)</f>
+        <v/>
+      </c>
+      <c r="M245" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N245" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O245" s="19" t="n"/>
+      <c r="P245" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q245" s="19" t="n"/>
+      <c r="R245" s="20" t="n"/>
+      <c r="S245" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T245" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U245" s="21">
+        <f>L245*S245</f>
+        <v/>
+      </c>
+      <c r="V245" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W245" s="15" t="inlineStr">
+        <is>
+          <t>F-277</t>
+        </is>
+      </c>
+      <c r="X245" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y245" s="19" t="n"/>
+      <c r="Z245" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA245" s="19" t="n"/>
+      <c r="AB245" s="19" t="n"/>
+      <c r="AC245" s="19" t="n"/>
+      <c r="AD245" s="19" t="n"/>
+      <c r="AE245" s="20" t="n"/>
+      <c r="AF245" s="21">
+        <f>IF(K245="","",K245*AE245)</f>
+        <v/>
+      </c>
+      <c r="AG245" s="19" t="n"/>
+      <c r="AH245" s="19" t="n"/>
+      <c r="AI245" s="19" t="n"/>
+      <c r="AJ245" s="19" t="n"/>
+      <c r="AK245" s="19" t="n"/>
+      <c r="AL245" s="19" t="n"/>
+      <c r="AM245" s="16" t="inlineStr">
+        <is>
+          <t>2 Hocker – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AN245" s="22" t="n"/>
+    </row>
+    <row r="246" ht="30" customHeight="1">
+      <c r="A246" s="15" t="inlineStr">
+        <is>
+          <t>NE02-03</t>
+        </is>
+      </c>
+      <c r="B246" s="15" t="n"/>
+      <c r="C246" s="15" t="n"/>
+      <c r="D246" s="15" t="inlineStr">
+        <is>
+          <t>NE02</t>
+        </is>
+      </c>
+      <c r="E246" s="15" t="inlineStr">
+        <is>
+          <t>Wäschekorb schwarz mit Deckel</t>
+        </is>
+      </c>
+      <c r="F246" s="16" t="inlineStr">
+        <is>
+          <t>Wäschekorb aus Kunststoff in Flechtoptik, schwarz, mit aufklappbarem Deckel.</t>
+        </is>
+      </c>
+      <c r="G246" s="15" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="H246" s="15" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="I246" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J246" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K246" s="17" t="n"/>
+      <c r="L246" s="18">
+        <f>J246-IF(K246="",0,K246)</f>
+        <v/>
+      </c>
+      <c r="M246" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N246" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O246" s="19" t="n"/>
+      <c r="P246" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q246" s="19" t="n"/>
+      <c r="R246" s="20" t="n"/>
+      <c r="S246" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T246" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U246" s="21">
+        <f>L246*S246</f>
+        <v/>
+      </c>
+      <c r="V246" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W246" s="15" t="inlineStr">
+        <is>
+          <t>F-278</t>
+        </is>
+      </c>
+      <c r="X246" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y246" s="19" t="n"/>
+      <c r="Z246" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA246" s="19" t="n"/>
+      <c r="AB246" s="19" t="n"/>
+      <c r="AC246" s="19" t="n"/>
+      <c r="AD246" s="19" t="n"/>
+      <c r="AE246" s="20" t="n"/>
+      <c r="AF246" s="21">
+        <f>IF(K246="","",K246*AE246)</f>
+        <v/>
+      </c>
+      <c r="AG246" s="19" t="n"/>
+      <c r="AH246" s="19" t="n"/>
+      <c r="AI246" s="19" t="n"/>
+      <c r="AJ246" s="19" t="n"/>
+      <c r="AK246" s="19" t="n"/>
+      <c r="AL246" s="19" t="n"/>
+      <c r="AM246" s="16" t="inlineStr">
+        <is>
+          <t>3 Körbe – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AN246" s="22" t="n"/>
+    </row>
+    <row r="247" ht="30" customHeight="1">
+      <c r="A247" s="15" t="inlineStr">
+        <is>
+          <t>NE02-04</t>
+        </is>
+      </c>
+      <c r="B247" s="15" t="n"/>
+      <c r="C247" s="15" t="n"/>
+      <c r="D247" s="15" t="inlineStr">
+        <is>
+          <t>NE02</t>
+        </is>
+      </c>
+      <c r="E247" s="15" t="inlineStr">
+        <is>
+          <t>Mülleimer Kunststoff schwarz, groß</t>
+        </is>
+      </c>
+      <c r="F247" s="16" t="inlineStr">
+        <is>
+          <t>Runder Abfallbehälter aus schwarzem Kunststoff mit aufgesetztem Schwingdeckel.</t>
+        </is>
+      </c>
+      <c r="G247" s="15" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="H247" s="15" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="I247" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J247" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K247" s="17" t="n"/>
+      <c r="L247" s="18">
+        <f>J247-IF(K247="",0,K247)</f>
+        <v/>
+      </c>
+      <c r="M247" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N247" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O247" s="19" t="n"/>
+      <c r="P247" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q247" s="19" t="n"/>
+      <c r="R247" s="20" t="n"/>
+      <c r="S247" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T247" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U247" s="21">
+        <f>L247*S247</f>
+        <v/>
+      </c>
+      <c r="V247" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W247" s="15" t="inlineStr">
+        <is>
+          <t>F-279</t>
+        </is>
+      </c>
+      <c r="X247" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y247" s="19" t="n"/>
+      <c r="Z247" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA247" s="19" t="n"/>
+      <c r="AB247" s="19" t="n"/>
+      <c r="AC247" s="19" t="n"/>
+      <c r="AD247" s="19" t="n"/>
+      <c r="AE247" s="20" t="n"/>
+      <c r="AF247" s="21">
+        <f>IF(K247="","",K247*AE247)</f>
+        <v/>
+      </c>
+      <c r="AG247" s="19" t="n"/>
+      <c r="AH247" s="19" t="n"/>
+      <c r="AI247" s="19" t="n"/>
+      <c r="AJ247" s="19" t="n"/>
+      <c r="AK247" s="19" t="n"/>
+      <c r="AL247" s="19" t="n"/>
+      <c r="AM247" s="16" t="inlineStr">
+        <is>
+          <t>2 Eimer. Der zweite steht in einem anderen Raum und trägt dort kein eigenes Post-it.</t>
+        </is>
+      </c>
+      <c r="AN247" s="22" t="n"/>
+    </row>
+    <row r="248" ht="30" customHeight="1">
+      <c r="A248" s="15" t="inlineStr">
+        <is>
+          <t>NE02-05</t>
+        </is>
+      </c>
+      <c r="B248" s="15" t="n"/>
+      <c r="C248" s="15" t="n"/>
+      <c r="D248" s="15" t="inlineStr">
+        <is>
+          <t>NE02</t>
+        </is>
+      </c>
+      <c r="E248" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Trinkbecher Kinder, bunt</t>
+        </is>
+      </c>
+      <c r="F248" s="16" t="inlineStr">
+        <is>
+          <t>Trinkbecher aus Kunststoff für Kinder, IKEA, in Rot, Blau, Pink, Gelb und Weiß. Stapelbar, spülmaschinenfest.</t>
+        </is>
+      </c>
+      <c r="G248" s="15" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="H248" s="15" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="I248" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J248" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="K248" s="17" t="n"/>
+      <c r="L248" s="18">
+        <f>J248-IF(K248="",0,K248)</f>
+        <v/>
+      </c>
+      <c r="M248" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N248" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O248" s="19" t="n"/>
+      <c r="P248" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q248" s="19" t="n"/>
+      <c r="R248" s="20" t="n"/>
+      <c r="S248" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T248" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U248" s="21">
+        <f>L248*S248</f>
+        <v/>
+      </c>
+      <c r="V248" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W248" s="15" t="inlineStr">
+        <is>
+          <t>F-280</t>
+        </is>
+      </c>
+      <c r="X248" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y248" s="19" t="n"/>
+      <c r="Z248" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA248" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB248" s="19" t="n"/>
+      <c r="AC248" s="19" t="n"/>
+      <c r="AD248" s="19" t="n"/>
+      <c r="AE248" s="20" t="n"/>
+      <c r="AF248" s="21">
+        <f>IF(K248="","",K248*AE248)</f>
+        <v/>
+      </c>
+      <c r="AG248" s="19" t="n"/>
+      <c r="AH248" s="19" t="n"/>
+      <c r="AI248" s="19" t="n"/>
+      <c r="AJ248" s="19" t="n"/>
+      <c r="AK248" s="19" t="n"/>
+      <c r="AL248" s="19" t="n"/>
+      <c r="AM248" s="16" t="inlineStr">
+        <is>
+          <t>39 Becher in gemischten Farben – abgebildet sind alle.</t>
+        </is>
+      </c>
+      <c r="AN248" s="22" t="n"/>
+    </row>
+    <row r="249" ht="30" customHeight="1">
+      <c r="A249" s="15" t="inlineStr">
+        <is>
+          <t>NE02-06</t>
+        </is>
+      </c>
+      <c r="B249" s="15" t="n"/>
+      <c r="C249" s="15" t="n"/>
+      <c r="D249" s="15" t="inlineStr">
+        <is>
+          <t>NE02</t>
+        </is>
+      </c>
+      <c r="E249" s="15" t="inlineStr">
+        <is>
+          <t>Trinkbecher Melamin, grün- und grautöne</t>
+        </is>
+      </c>
+      <c r="F249" s="16" t="inlineStr">
+        <is>
+          <t>Trinkbecher mit facettiertem Fuß in Weiß, Salbeigrün, Graugrün und Mintgrün. Acht der Becher tragen ein Motiv.</t>
+        </is>
+      </c>
+      <c r="G249" s="15" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="H249" s="15" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="I249" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J249" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="K249" s="17" t="n"/>
+      <c r="L249" s="18">
+        <f>J249-IF(K249="",0,K249)</f>
+        <v/>
+      </c>
+      <c r="M249" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N249" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O249" s="19" t="n"/>
+      <c r="P249" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q249" s="19" t="n"/>
+      <c r="R249" s="20" t="n"/>
+      <c r="S249" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T249" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U249" s="21">
+        <f>L249*S249</f>
+        <v/>
+      </c>
+      <c r="V249" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W249" s="15" t="inlineStr">
+        <is>
+          <t>F-281</t>
+        </is>
+      </c>
+      <c r="X249" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y249" s="19" t="n"/>
+      <c r="Z249" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA249" s="19" t="n"/>
+      <c r="AB249" s="19" t="n"/>
+      <c r="AC249" s="19" t="n"/>
+      <c r="AD249" s="19" t="n"/>
+      <c r="AE249" s="20" t="n"/>
+      <c r="AF249" s="21">
+        <f>IF(K249="","",K249*AE249)</f>
+        <v/>
+      </c>
+      <c r="AG249" s="19" t="n"/>
+      <c r="AH249" s="19" t="n"/>
+      <c r="AI249" s="19" t="n"/>
+      <c r="AJ249" s="19" t="n"/>
+      <c r="AK249" s="19" t="n"/>
+      <c r="AL249" s="19" t="n"/>
+      <c r="AM249" s="16" t="inlineStr">
+        <is>
+          <t>17 Becher – abgebildet sind alle. Acht davon mit Motiv.</t>
+        </is>
+      </c>
+      <c r="AN249" s="22" t="n"/>
+    </row>
+    <row r="250" ht="30" customHeight="1">
+      <c r="A250" s="15" t="inlineStr">
+        <is>
+          <t>NE02-07</t>
+        </is>
+      </c>
+      <c r="B250" s="15" t="n"/>
+      <c r="C250" s="15" t="n"/>
+      <c r="D250" s="15" t="inlineStr">
+        <is>
+          <t>NE02</t>
+        </is>
+      </c>
+      <c r="E250" s="15" t="inlineStr">
+        <is>
+          <t>Teller Kunststoff, bunt</t>
+        </is>
+      </c>
+      <c r="F250" s="16" t="inlineStr">
+        <is>
+          <t>Flache Teller aus Kunststoff in kräftigen Farben: elf kleine bunte, drei große sowie weitere mit Tiermotiv.</t>
+        </is>
+      </c>
+      <c r="G250" s="15" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="H250" s="15" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="I250" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J250" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="K250" s="17" t="n"/>
+      <c r="L250" s="18">
+        <f>J250-IF(K250="",0,K250)</f>
+        <v/>
+      </c>
+      <c r="M250" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N250" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O250" s="19" t="n"/>
+      <c r="P250" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q250" s="19" t="n"/>
+      <c r="R250" s="20" t="n"/>
+      <c r="S250" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T250" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U250" s="21">
+        <f>L250*S250</f>
+        <v/>
+      </c>
+      <c r="V250" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W250" s="15" t="inlineStr">
+        <is>
+          <t>F-282</t>
+        </is>
+      </c>
+      <c r="X250" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y250" s="19" t="n"/>
+      <c r="Z250" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA250" s="19" t="n"/>
+      <c r="AB250" s="19" t="n"/>
+      <c r="AC250" s="19" t="n"/>
+      <c r="AD250" s="19" t="n"/>
+      <c r="AE250" s="20" t="n"/>
+      <c r="AF250" s="21">
+        <f>IF(K250="","",K250*AE250)</f>
+        <v/>
+      </c>
+      <c r="AG250" s="19" t="n"/>
+      <c r="AH250" s="19" t="n"/>
+      <c r="AI250" s="19" t="n"/>
+      <c r="AJ250" s="19" t="n"/>
+      <c r="AK250" s="19" t="n"/>
+      <c r="AL250" s="19" t="n"/>
+      <c r="AM250" s="16" t="inlineStr">
+        <is>
+          <t>22 Teller – abgebildet sind alle. Elf kleine bunte, drei große, der Rest mit Motiv.</t>
+        </is>
+      </c>
+      <c r="AN250" s="22" t="n"/>
+    </row>
+    <row r="251" ht="30" customHeight="1">
+      <c r="A251" s="15" t="inlineStr">
+        <is>
+          <t>NE02-08</t>
+        </is>
+      </c>
+      <c r="B251" s="15" t="n"/>
+      <c r="C251" s="15" t="n"/>
+      <c r="D251" s="15" t="inlineStr">
+        <is>
+          <t>NE02</t>
+        </is>
+      </c>
+      <c r="E251" s="15" t="inlineStr">
+        <is>
+          <t>Schriftzug „Sterneküche", schwarz</t>
+        </is>
+      </c>
+      <c r="F251" s="16" t="inlineStr">
+        <is>
+          <t>Großer Wandschriftzug „Sterneküche" in Schreibschrift, schwarz, aus Holz gefräst.</t>
+        </is>
+      </c>
+      <c r="G251" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H251" s="15" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="I251" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J251" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K251" s="17" t="n"/>
+      <c r="L251" s="18">
+        <f>J251-IF(K251="",0,K251)</f>
+        <v/>
+      </c>
+      <c r="M251" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N251" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O251" s="19" t="n"/>
+      <c r="P251" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q251" s="19" t="n"/>
+      <c r="R251" s="20" t="n"/>
+      <c r="S251" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T251" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U251" s="21">
+        <f>L251*S251</f>
+        <v/>
+      </c>
+      <c r="V251" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W251" s="15" t="inlineStr">
+        <is>
+          <t>F-283</t>
+        </is>
+      </c>
+      <c r="X251" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y251" s="19" t="n"/>
+      <c r="Z251" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA251" s="19" t="n"/>
+      <c r="AB251" s="19" t="n"/>
+      <c r="AC251" s="19" t="n"/>
+      <c r="AD251" s="19" t="n"/>
+      <c r="AE251" s="20" t="n"/>
+      <c r="AF251" s="21">
+        <f>IF(K251="","",K251*AE251)</f>
+        <v/>
+      </c>
+      <c r="AG251" s="19" t="n"/>
+      <c r="AH251" s="19" t="n"/>
+      <c r="AI251" s="19" t="n"/>
+      <c r="AJ251" s="19" t="n"/>
+      <c r="AK251" s="19" t="n"/>
+      <c r="AL251" s="19" t="n"/>
+      <c r="AM251" s="16" t="inlineStr">
+        <is>
+          <t>1 Schriftzug.</t>
+        </is>
+      </c>
+      <c r="AN251" s="22" t="n"/>
+    </row>
+    <row r="252" ht="30" customHeight="1">
+      <c r="A252" s="15" t="inlineStr">
+        <is>
+          <t>NE02-09</t>
+        </is>
+      </c>
+      <c r="B252" s="15" t="n"/>
+      <c r="C252" s="15" t="n"/>
+      <c r="D252" s="15" t="inlineStr">
+        <is>
+          <t>NE02</t>
+        </is>
+      </c>
+      <c r="E252" s="15" t="inlineStr">
+        <is>
+          <t>Tablett weiß mit Streifenmuster</t>
+        </is>
+      </c>
+      <c r="F252" s="16" t="inlineStr">
+        <is>
+          <t>Serviertablett aus Kunststoff, weiß mit Griffausschnitten, Boden mit Streifenmuster – eines in Blautönen, eines in Rottönen.</t>
+        </is>
+      </c>
+      <c r="G252" s="15" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="H252" s="15" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="I252" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J252" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K252" s="17" t="n"/>
+      <c r="L252" s="18">
+        <f>J252-IF(K252="",0,K252)</f>
+        <v/>
+      </c>
+      <c r="M252" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N252" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O252" s="19" t="n"/>
+      <c r="P252" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q252" s="19" t="n"/>
+      <c r="R252" s="20" t="n"/>
+      <c r="S252" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T252" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U252" s="21">
+        <f>L252*S252</f>
+        <v/>
+      </c>
+      <c r="V252" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W252" s="15" t="inlineStr">
+        <is>
+          <t>F-284</t>
+        </is>
+      </c>
+      <c r="X252" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y252" s="19" t="n"/>
+      <c r="Z252" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA252" s="19" t="n"/>
+      <c r="AB252" s="19" t="n"/>
+      <c r="AC252" s="19" t="n"/>
+      <c r="AD252" s="19" t="n"/>
+      <c r="AE252" s="20" t="n"/>
+      <c r="AF252" s="21">
+        <f>IF(K252="","",K252*AE252)</f>
+        <v/>
+      </c>
+      <c r="AG252" s="19" t="n"/>
+      <c r="AH252" s="19" t="n"/>
+      <c r="AI252" s="19" t="n"/>
+      <c r="AJ252" s="19" t="n"/>
+      <c r="AK252" s="19" t="n"/>
+      <c r="AL252" s="19" t="n"/>
+      <c r="AM252" s="16" t="inlineStr">
+        <is>
+          <t>2 Tabletts, beide abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN252" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN243"/>
+  <autoFilter ref="A2:AN252"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -30732,7 +31811,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z243">
+  <conditionalFormatting sqref="Z3:Z252">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -30743,12 +31822,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I243">
+  <conditionalFormatting sqref="I3:I252">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P243">
+  <conditionalFormatting sqref="P3:P252">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -30801,7 +31880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -30839,7 +31918,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$243)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$252)</f>
         <v/>
       </c>
     </row>
@@ -30850,7 +31929,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$252,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -30861,7 +31940,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$252,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -30872,7 +31951,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$252,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -30883,7 +31962,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$243,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$252,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -30894,7 +31973,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$243)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$252)</f>
         <v/>
       </c>
     </row>
@@ -30905,7 +31984,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$243)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -30923,7 +32002,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$243)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$252)</f>
         <v/>
       </c>
     </row>
@@ -30934,7 +32013,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$243,Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$252,Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
     </row>
@@ -30967,7 +32046,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$243="bezahlt")*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$252="bezahlt")*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
     </row>
@@ -30996,7 +32075,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"*verkauft",Artikelstamm!$AI$3:$AI$243,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$252,"*verkauft",Artikelstamm!$AI$3:$AI$252,"")</f>
         <v/>
       </c>
     </row>
@@ -31007,7 +32086,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"*verkauft",Artikelstamm!$AJ$3:$AJ$243,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$252,"*verkauft",Artikelstamm!$AJ$3:$AJ$252,"offen")</f>
         <v/>
       </c>
     </row>
@@ -31018,7 +32097,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$243,"reserviert",Artikelstamm!$AL$3:$AL$243,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$252,"reserviert",Artikelstamm!$AL$3:$AL$252,"")</f>
         <v/>
       </c>
     </row>
@@ -31029,7 +32108,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$243,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$252,"")</f>
         <v/>
       </c>
     </row>
@@ -31040,7 +32119,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$243,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$252,"")</f>
         <v/>
       </c>
     </row>
@@ -31080,15 +32159,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$252,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A30)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$252=$A30)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A30,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$252,$A30,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31099,15 +32178,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$252,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A31)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$252=$A31)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A31,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$252,$A31,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31118,15 +32197,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$243,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$252,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$243=$A32)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$252=$A32)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$243,$A32,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$252,$A32,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31185,15 +32264,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A37)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A37)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A37,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A37,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31204,15 +32283,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A38)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A38)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A38,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A38,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31223,15 +32302,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A39)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A39)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A39,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A39,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31242,15 +32321,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A40)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A40)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A40,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A40,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31261,15 +32340,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A41)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A41)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A41,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A41,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31280,15 +32359,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A42)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A42)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A42,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A42,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31299,15 +32378,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A43)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A43)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A43,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A43,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31318,15 +32397,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A44)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A44)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A44,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A44,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31337,15 +32416,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A45)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A45)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A45,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A45,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31356,15 +32435,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A46)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A46)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A46,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A46,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31375,15 +32454,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A47)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A47)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A47,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A47,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31394,15 +32473,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A48)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A48)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A48,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A48,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31413,15 +32492,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A49)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A49)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A49,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A49,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31432,15 +32511,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$243,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$243=$A50)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A50)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$243,$A50,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A50,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31499,15 +32578,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A55)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A55)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A55,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A55,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31518,15 +32597,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A56)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A56)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A56,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A56,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31537,15 +32616,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A57)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A57)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A57,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A57,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31556,15 +32635,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A58)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A58)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A58,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A58,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31575,15 +32654,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A59)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A59)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A59,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A59,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31594,15 +32673,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A60)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A60)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A60,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A60,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31613,15 +32692,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A61)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A61)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A61,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A61,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31632,15 +32711,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A62)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A62)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A62,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A62,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31651,15 +32730,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A63)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A63)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A63,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A63,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31670,15 +32749,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A64)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A64)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A64,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A64,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31689,15 +32768,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A65)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A65)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A65,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A65,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31708,15 +32787,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A66)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A66)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A66,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A66,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
@@ -31727,353 +32806,372 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A67)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A67)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A67,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A67,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="26" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Küche</t>
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A68)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A68)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A68,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A68,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="26" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A69)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A69)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A69,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A69,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A70)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A70)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A70,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A70,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum 4</t>
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A71)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A71)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A71,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A71,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="26" t="inlineStr">
         <is>
-          <t>Speisesaal</t>
+          <t>Schlafraum 5</t>
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A72)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A72)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A72,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A72,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="26" t="inlineStr">
         <is>
-          <t>Terrasse</t>
+          <t>Speisesaal</t>
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A73)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A73)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A73,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A73,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="26" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Terrasse</t>
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A74)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A74)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A74,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A74,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="26" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Treppenraum 1</t>
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A75)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A75)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A75,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A75,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A76)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A76)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A76,Artikelstamm!$U$3:$U$243)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A76,Artikelstamm!$U$3:$U$252)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B77" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A77)</f>
+        <v/>
+      </c>
+      <c r="C77" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A77)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <v/>
+      </c>
+      <c r="D77" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A77,Artikelstamm!$U$3:$U$252)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$243,$A77)</f>
-        <v/>
-      </c>
-      <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$243=$A77)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
-        <v/>
-      </c>
-      <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$243,$A77,Artikelstamm!$U$3:$U$243)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="28" t="inlineStr">
+      <c r="B78" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A78)</f>
+        <v/>
+      </c>
+      <c r="C78" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A78)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <v/>
+      </c>
+      <c r="D78" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A78,Artikelstamm!$U$3:$U$252)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B78" s="35">
-        <f>SUM(B55:B77)</f>
-        <v/>
-      </c>
-      <c r="C78" s="36">
-        <f>SUM(C55:C77)</f>
-        <v/>
-      </c>
-      <c r="D78" s="36">
-        <f>SUM(D55:D77)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="25" t="inlineStr">
+      <c r="B79" s="35">
+        <f>SUM(B55:B78)</f>
+        <v/>
+      </c>
+      <c r="C79" s="36">
+        <f>SUM(C55:C78)</f>
+        <v/>
+      </c>
+      <c r="D79" s="36">
+        <f>SUM(D55:D78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="32" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B81" s="32" t="inlineStr">
+      <c r="B82" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C81" s="32" t="inlineStr">
+      <c r="C82" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A82)</f>
-        <v/>
-      </c>
-      <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A82)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
-        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A83)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A83)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A84)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A84)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A85)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A85)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A86)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A86)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B87" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A87)</f>
+        <v/>
+      </c>
+      <c r="C87" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A87)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$243,$A87)</f>
-        <v/>
-      </c>
-      <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$243=$A87)*Artikelstamm!$K$3:$K$243*Artikelstamm!$AE$3:$AE$243)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="28" t="inlineStr">
+      <c r="B88" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A88)</f>
+        <v/>
+      </c>
+      <c r="C88" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A88)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B88" s="35">
-        <f>SUM(B82:B87)</f>
-        <v/>
-      </c>
-      <c r="C88" s="36">
-        <f>SUM(C82:C87)</f>
+      <c r="B89" s="35">
+        <f>SUM(B83:B88)</f>
+        <v/>
+      </c>
+      <c r="C89" s="36">
+        <f>SUM(C83:C88)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$255</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN252"/>
+  <dimension ref="A1:AN255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3086,7 +3086,7 @@
         </is>
       </c>
       <c r="J17" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" s="17" t="n"/>
       <c r="L17" s="18">
@@ -3161,7 +3161,7 @@
       <c r="AL17" s="19" t="n"/>
       <c r="AM17" s="16" t="inlineStr">
         <is>
-          <t>1 Stück im Bild</t>
+          <t>1 Hocker.</t>
         </is>
       </c>
       <c r="AN17" s="22" t="n"/>
@@ -30609,7 +30609,11 @@
         </is>
       </c>
       <c r="B243" s="15" t="n"/>
-      <c r="C243" s="15" t="n"/>
+      <c r="C243" s="15" t="inlineStr">
+        <is>
+          <t>BA10-12</t>
+        </is>
+      </c>
       <c r="D243" s="15" t="inlineStr">
         <is>
           <t>BA09</t>
@@ -30641,7 +30645,7 @@
         </is>
       </c>
       <c r="J243" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K243" s="17" t="n"/>
       <c r="L243" s="18">
@@ -30716,10 +30720,14 @@
       <c r="AL243" s="19" t="n"/>
       <c r="AM243" s="16" t="inlineStr">
         <is>
-          <t>1 Hocker.</t>
-        </is>
-      </c>
-      <c r="AN243" s="22" t="n"/>
+          <t>2 Hocker: einer im Personalraum (BA09-06) und einer im Ruhe- und Schlafraum (dort mit BA10-12 beschriftet).</t>
+        </is>
+      </c>
+      <c r="AN243" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA10-12.</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="30" customHeight="1">
       <c r="A244" s="15" t="inlineStr">
@@ -31322,7 +31330,11 @@
           <t>39 Becher in gemischten Farben – abgebildet sind alle.</t>
         </is>
       </c>
-      <c r="AN248" s="22" t="n"/>
+      <c r="AN248" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: waechst noch. Aus einer weiteren Kueche kommen Becher und bunte Teller dazu. Am Ende des Rundgangs zu EINEM Geschirr-Konvolut zusammenfassen und im Katalog lassen - so von der Nutzerin gewuenscht.</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="30" customHeight="1">
       <c r="A249" s="15" t="inlineStr">
@@ -31441,7 +31453,11 @@
           <t>17 Becher – abgebildet sind alle. Acht davon mit Motiv.</t>
         </is>
       </c>
-      <c r="AN249" s="22" t="n"/>
+      <c r="AN249" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: waechst noch. Aus einer weiteren Kueche kommen Becher und bunte Teller dazu. Am Ende des Rundgangs zu EINEM Geschirr-Konvolut zusammenfassen und im Katalog lassen - so von der Nutzerin gewuenscht.</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="30" customHeight="1">
       <c r="A250" s="15" t="inlineStr">
@@ -31560,7 +31576,11 @@
           <t>22 Teller – abgebildet sind alle. Elf kleine bunte, drei große, der Rest mit Motiv.</t>
         </is>
       </c>
-      <c r="AN250" s="22" t="n"/>
+      <c r="AN250" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: waechst noch. Aus einer weiteren Kueche kommen Becher und bunte Teller dazu. Am Ende des Rundgangs zu EINEM Geschirr-Konvolut zusammenfassen und im Katalog lassen - so von der Nutzerin gewuenscht.</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="30" customHeight="1">
       <c r="A251" s="15" t="inlineStr">
@@ -31800,8 +31820,365 @@
       </c>
       <c r="AN252" s="22" t="n"/>
     </row>
+    <row r="253" ht="30" customHeight="1">
+      <c r="A253" s="15" t="inlineStr">
+        <is>
+          <t>BA10-09</t>
+        </is>
+      </c>
+      <c r="B253" s="15" t="n"/>
+      <c r="C253" s="15" t="n"/>
+      <c r="D253" s="15" t="inlineStr">
+        <is>
+          <t>BA10</t>
+        </is>
+      </c>
+      <c r="E253" s="15" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Tablettplatte Birke</t>
+        </is>
+      </c>
+      <c r="F253" s="16" t="inlineStr">
+        <is>
+          <t>Runder Beistelltisch: abnehmbare Tablettplatte aus Birke mit umlaufendem Rand, auf einem weißen Gestell aus Rundstahl mit Tragebügel.</t>
+        </is>
+      </c>
+      <c r="G253" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H253" s="15" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="I253" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J253" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K253" s="17" t="n"/>
+      <c r="L253" s="18">
+        <f>J253-IF(K253="",0,K253)</f>
+        <v/>
+      </c>
+      <c r="M253" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N253" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O253" s="19" t="n"/>
+      <c r="P253" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q253" s="19" t="n"/>
+      <c r="R253" s="20" t="n"/>
+      <c r="S253" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T253" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U253" s="21">
+        <f>L253*S253</f>
+        <v/>
+      </c>
+      <c r="V253" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W253" s="15" t="inlineStr">
+        <is>
+          <t>F-286</t>
+        </is>
+      </c>
+      <c r="X253" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y253" s="19" t="n"/>
+      <c r="Z253" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA253" s="19" t="n"/>
+      <c r="AB253" s="19" t="n"/>
+      <c r="AC253" s="19" t="n"/>
+      <c r="AD253" s="19" t="n"/>
+      <c r="AE253" s="20" t="n"/>
+      <c r="AF253" s="21">
+        <f>IF(K253="","",K253*AE253)</f>
+        <v/>
+      </c>
+      <c r="AG253" s="19" t="n"/>
+      <c r="AH253" s="19" t="n"/>
+      <c r="AI253" s="19" t="n"/>
+      <c r="AJ253" s="19" t="n"/>
+      <c r="AK253" s="19" t="n"/>
+      <c r="AL253" s="19" t="n"/>
+      <c r="AM253" s="16" t="inlineStr">
+        <is>
+          <t>1 Tisch. Die Teelichtgläser gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN253" s="22" t="n"/>
+    </row>
+    <row r="254" ht="30" customHeight="1">
+      <c r="A254" s="15" t="inlineStr">
+        <is>
+          <t>BA10-10</t>
+        </is>
+      </c>
+      <c r="B254" s="15" t="n"/>
+      <c r="C254" s="15" t="n"/>
+      <c r="D254" s="15" t="inlineStr">
+        <is>
+          <t>BA10</t>
+        </is>
+      </c>
+      <c r="E254" s="15" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Tablettplatte schwarz</t>
+        </is>
+      </c>
+      <c r="F254" s="16" t="inlineStr">
+        <is>
+          <t>Runder Beistelltisch mit schwarzer Tablettplatte auf drei schlanken, schwarz lackierten Metallbeinen. Platte mit Gebrauchsspuren.</t>
+        </is>
+      </c>
+      <c r="G254" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H254" s="15" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="I254" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J254" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K254" s="17" t="n"/>
+      <c r="L254" s="18">
+        <f>J254-IF(K254="",0,K254)</f>
+        <v/>
+      </c>
+      <c r="M254" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N254" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O254" s="19" t="n"/>
+      <c r="P254" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q254" s="19" t="n"/>
+      <c r="R254" s="20" t="n"/>
+      <c r="S254" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T254" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U254" s="21">
+        <f>L254*S254</f>
+        <v/>
+      </c>
+      <c r="V254" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W254" s="15" t="inlineStr">
+        <is>
+          <t>F-287</t>
+        </is>
+      </c>
+      <c r="X254" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y254" s="19" t="n"/>
+      <c r="Z254" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA254" s="19" t="n"/>
+      <c r="AB254" s="19" t="n"/>
+      <c r="AC254" s="19" t="n"/>
+      <c r="AD254" s="19" t="n"/>
+      <c r="AE254" s="20" t="n"/>
+      <c r="AF254" s="21">
+        <f>IF(K254="","",K254*AE254)</f>
+        <v/>
+      </c>
+      <c r="AG254" s="19" t="n"/>
+      <c r="AH254" s="19" t="n"/>
+      <c r="AI254" s="19" t="n"/>
+      <c r="AJ254" s="19" t="n"/>
+      <c r="AK254" s="19" t="n"/>
+      <c r="AL254" s="19" t="n"/>
+      <c r="AM254" s="16" t="inlineStr">
+        <is>
+          <t>1 Tisch. Die Kerzengläser gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN254" s="22" t="n"/>
+    </row>
+    <row r="255" ht="30" customHeight="1">
+      <c r="A255" s="15" t="inlineStr">
+        <is>
+          <t>BA10-11</t>
+        </is>
+      </c>
+      <c r="B255" s="15" t="n"/>
+      <c r="C255" s="15" t="n"/>
+      <c r="D255" s="15" t="inlineStr">
+        <is>
+          <t>BA10</t>
+        </is>
+      </c>
+      <c r="E255" s="15" t="inlineStr">
+        <is>
+          <t>Tisch rund, zweiteilig, weiß</t>
+        </is>
+      </c>
+      <c r="F255" s="16" t="inlineStr">
+        <is>
+          <t>Runder Tisch aus zwei halbrunden weißen Platten mit Multiplex-Kante, auf höhenverstellbaren Rundfüßen aus Chrom. Die Hälften lassen sich einzeln stellen.</t>
+        </is>
+      </c>
+      <c r="G255" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H255" s="15" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="I255" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J255" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K255" s="17" t="n"/>
+      <c r="L255" s="18">
+        <f>J255-IF(K255="",0,K255)</f>
+        <v/>
+      </c>
+      <c r="M255" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N255" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O255" s="19" t="n"/>
+      <c r="P255" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q255" s="19" t="n"/>
+      <c r="R255" s="20" t="n"/>
+      <c r="S255" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T255" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U255" s="21">
+        <f>L255*S255</f>
+        <v/>
+      </c>
+      <c r="V255" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W255" s="15" t="inlineStr">
+        <is>
+          <t>F-288</t>
+        </is>
+      </c>
+      <c r="X255" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y255" s="19" t="n"/>
+      <c r="Z255" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA255" s="19" t="n"/>
+      <c r="AB255" s="19" t="n"/>
+      <c r="AC255" s="19" t="n"/>
+      <c r="AD255" s="19" t="n"/>
+      <c r="AE255" s="20" t="n"/>
+      <c r="AF255" s="21">
+        <f>IF(K255="","",K255*AE255)</f>
+        <v/>
+      </c>
+      <c r="AG255" s="19" t="n"/>
+      <c r="AH255" s="19" t="n"/>
+      <c r="AI255" s="19" t="n"/>
+      <c r="AJ255" s="19" t="n"/>
+      <c r="AK255" s="19" t="n"/>
+      <c r="AL255" s="19" t="n"/>
+      <c r="AM255" s="16" t="inlineStr">
+        <is>
+          <t>1 Tisch aus zwei halbrunden Platten.</t>
+        </is>
+      </c>
+      <c r="AN255" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN252"/>
+  <autoFilter ref="A2:AN255"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -31811,7 +32188,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z252">
+  <conditionalFormatting sqref="Z3:Z255">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -31822,12 +32199,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I252">
+  <conditionalFormatting sqref="I3:I255">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P252">
+  <conditionalFormatting sqref="P3:P255">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -31918,7 +32295,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$252)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$255)</f>
         <v/>
       </c>
     </row>
@@ -31929,7 +32306,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$252,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$255,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -31940,7 +32317,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$252,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$255,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -31951,7 +32328,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$252,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$255,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -31962,7 +32339,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$252,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$255,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -31973,7 +32350,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$252)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$255)</f>
         <v/>
       </c>
     </row>
@@ -31984,7 +32361,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$252)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32002,7 +32379,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$252)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$255)</f>
         <v/>
       </c>
     </row>
@@ -32013,7 +32390,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$252,Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$255,Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
     </row>
@@ -32046,7 +32423,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$252="bezahlt")*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$255="bezahlt")*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
     </row>
@@ -32075,7 +32452,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$252,"*verkauft",Artikelstamm!$AI$3:$AI$252,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$255,"*verkauft",Artikelstamm!$AI$3:$AI$255,"")</f>
         <v/>
       </c>
     </row>
@@ -32086,7 +32463,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$252,"*verkauft",Artikelstamm!$AJ$3:$AJ$252,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$255,"*verkauft",Artikelstamm!$AJ$3:$AJ$255,"offen")</f>
         <v/>
       </c>
     </row>
@@ -32097,7 +32474,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$252,"reserviert",Artikelstamm!$AL$3:$AL$252,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$255,"reserviert",Artikelstamm!$AL$3:$AL$255,"")</f>
         <v/>
       </c>
     </row>
@@ -32108,7 +32485,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$252,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$255,"")</f>
         <v/>
       </c>
     </row>
@@ -32119,7 +32496,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$252,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$255,"")</f>
         <v/>
       </c>
     </row>
@@ -32159,15 +32536,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$252,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$255,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$252=$A30)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$255=$A30)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$252,$A30,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$255,$A30,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32178,15 +32555,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$252,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$255,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$252=$A31)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$255=$A31)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$252,$A31,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$255,$A31,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32197,15 +32574,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$252,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$255,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$252=$A32)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$255=$A32)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$252,$A32,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$255,$A32,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32264,15 +32641,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A37)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A37)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A37,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A37,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32283,15 +32660,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A38)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A38)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A38,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A38,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32302,15 +32679,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A39)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A39)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A39,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A39,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32321,15 +32698,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A40)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A40)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A40,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A40,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32340,15 +32717,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A41)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A41)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A41,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A41,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32359,15 +32736,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A42)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A42)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A42,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A42,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32378,15 +32755,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A43)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A43)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A43,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A43,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32397,15 +32774,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A44)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A44)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A44,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A44,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32416,15 +32793,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A45)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A45)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A45,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A45,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32435,15 +32812,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A46)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A46)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A46,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A46,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32454,15 +32831,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A47)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A47)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A47,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A47,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32473,15 +32850,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A48)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A48)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A48,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A48,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32492,15 +32869,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A49)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A49)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A49,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A49,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32511,15 +32888,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$252,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$252=$A50)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A50)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$252,$A50,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A50,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32578,15 +32955,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A55)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A55)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A55,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A55,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32597,15 +32974,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A56)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A56)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A56,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A56,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32616,15 +32993,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A57)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A57)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A57,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A57,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32635,15 +33012,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A58)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A58)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A58,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A58,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32654,15 +33031,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A59)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A59)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A59,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A59,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32673,15 +33050,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A60)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A60)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A60,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A60,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32692,15 +33069,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A61)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A61)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A61,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A61,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32711,15 +33088,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A62)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A62)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A62,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A62,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32730,15 +33107,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A63)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A63)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A63,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A63,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32749,15 +33126,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A64)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A64)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A64,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A64,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32768,15 +33145,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A65)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A65)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A65,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A65,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32787,15 +33164,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A66)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A66)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A66,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A66,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32806,15 +33183,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A67)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A67)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A67,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A67,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32825,15 +33202,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A68)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A68)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A68,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A68,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32844,15 +33221,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A69)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A69)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A69,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A69,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32863,15 +33240,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A70)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A70)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A70,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A70,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32882,15 +33259,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A71)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A71)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A71,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A71,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32901,15 +33278,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A72)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A72)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A72,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A72,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32920,15 +33297,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A73)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A73)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A73,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A73,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32939,15 +33316,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A74)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A74)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A74,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A74,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32958,15 +33335,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A75)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A75)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A75,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A75,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32977,15 +33354,15 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A76)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A76)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A76,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A76,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -32996,15 +33373,15 @@
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A77)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A77)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A77,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A77,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -33015,15 +33392,15 @@
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$252,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$252=$A78)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A78)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
       <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$252,$A78,Artikelstamm!$U$3:$U$252)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A78,Artikelstamm!$U$3:$U$255)</f>
         <v/>
       </c>
     </row>
@@ -33077,11 +33454,11 @@
         </is>
       </c>
       <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A83)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A83)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A83)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A83)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
     </row>
@@ -33092,11 +33469,11 @@
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A84)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A84)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
     </row>
@@ -33107,11 +33484,11 @@
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A85)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A85)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
     </row>
@@ -33122,11 +33499,11 @@
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A86)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A86)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
     </row>
@@ -33137,11 +33514,11 @@
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A87)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A87)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
     </row>
@@ -33152,11 +33529,11 @@
         </is>
       </c>
       <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$252,$A88)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A88)</f>
         <v/>
       </c>
       <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$252=$A88)*Artikelstamm!$K$3:$K$252*Artikelstamm!$AE$3:$AE$252)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A88)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$262</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN255"/>
+  <dimension ref="A1:AN262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -32177,8 +32177,853 @@
       </c>
       <c r="AN255" s="22" t="n"/>
     </row>
+    <row r="256" ht="30" customHeight="1">
+      <c r="A256" s="15" t="inlineStr">
+        <is>
+          <t>BA03-01</t>
+        </is>
+      </c>
+      <c r="B256" s="15" t="n"/>
+      <c r="C256" s="15" t="n"/>
+      <c r="D256" s="15" t="inlineStr">
+        <is>
+          <t>BA03</t>
+        </is>
+      </c>
+      <c r="E256" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Avsiktlig Teppich, schwarz-weiß gepunktet</t>
+        </is>
+      </c>
+      <c r="F256" s="16" t="inlineStr">
+        <is>
+          <t>Flachgewebter Teppich in Creme mit schwarzen Punktreihen, IKEA Avsiktlig. Flor 100 % Polypropylen auf Jutekette. Etikett auf der Rückseite vorhanden.</t>
+        </is>
+      </c>
+      <c r="G256" s="15" t="inlineStr">
+        <is>
+          <t>Textilien</t>
+        </is>
+      </c>
+      <c r="H256" s="15" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="I256" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J256" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K256" s="17" t="n"/>
+      <c r="L256" s="18">
+        <f>J256-IF(K256="",0,K256)</f>
+        <v/>
+      </c>
+      <c r="M256" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N256" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O256" s="19" t="inlineStr">
+        <is>
+          <t>133 × 195 cm</t>
+        </is>
+      </c>
+      <c r="P256" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q256" s="19" t="n"/>
+      <c r="R256" s="20" t="n"/>
+      <c r="S256" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T256" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U256" s="21">
+        <f>L256*S256</f>
+        <v/>
+      </c>
+      <c r="V256" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W256" s="15" t="inlineStr">
+        <is>
+          <t>F-291</t>
+        </is>
+      </c>
+      <c r="X256" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y256" s="19" t="n"/>
+      <c r="Z256" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA256" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB256" s="19" t="n"/>
+      <c r="AC256" s="19" t="n"/>
+      <c r="AD256" s="19" t="n"/>
+      <c r="AE256" s="20" t="n"/>
+      <c r="AF256" s="21">
+        <f>IF(K256="","",K256*AE256)</f>
+        <v/>
+      </c>
+      <c r="AG256" s="19" t="n"/>
+      <c r="AH256" s="19" t="n"/>
+      <c r="AI256" s="19" t="n"/>
+      <c r="AJ256" s="19" t="n"/>
+      <c r="AK256" s="19" t="n"/>
+      <c r="AL256" s="19" t="n"/>
+      <c r="AM256" s="16" t="inlineStr">
+        <is>
+          <t>1 Teppich. Das Etikett ist auf Foto F-292 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN256" s="22" t="n"/>
+    </row>
+    <row r="257" ht="30" customHeight="1">
+      <c r="A257" s="15" t="inlineStr">
+        <is>
+          <t>BA03-02</t>
+        </is>
+      </c>
+      <c r="B257" s="15" t="n"/>
+      <c r="C257" s="15" t="n"/>
+      <c r="D257" s="15" t="inlineStr">
+        <is>
+          <t>BA03</t>
+        </is>
+      </c>
+      <c r="E257" s="15" t="inlineStr">
+        <is>
+          <t>Spielküche beige-braun, mehrteilig</t>
+        </is>
+      </c>
+      <c r="F257" s="16" t="inlineStr">
+        <is>
+          <t>Spielküche aus beschichteter Platte in Creme und Taupe mit Holzarbeitsplatten: Mikrowellenmodul mit Digitalanzeige, Unterschränke mit Kochfeld, Backofen mit Sichtfenster und Spüle, dazu ein Wandregal. Abgerundete Ecken, kindgerechte Höhe.</t>
+        </is>
+      </c>
+      <c r="G257" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H257" s="15" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="I257" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J257" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K257" s="17" t="n"/>
+      <c r="L257" s="18">
+        <f>J257-IF(K257="",0,K257)</f>
+        <v/>
+      </c>
+      <c r="M257" s="15" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N257" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O257" s="19" t="n"/>
+      <c r="P257" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q257" s="19" t="n"/>
+      <c r="R257" s="20" t="n"/>
+      <c r="S257" s="20" t="n">
+        <v>250</v>
+      </c>
+      <c r="T257" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U257" s="21">
+        <f>L257*S257</f>
+        <v/>
+      </c>
+      <c r="V257" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W257" s="15" t="inlineStr">
+        <is>
+          <t>F-293</t>
+        </is>
+      </c>
+      <c r="X257" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y257" s="19" t="n"/>
+      <c r="Z257" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA257" s="19" t="n"/>
+      <c r="AB257" s="19" t="n"/>
+      <c r="AC257" s="19" t="n"/>
+      <c r="AD257" s="19" t="n"/>
+      <c r="AE257" s="20" t="n"/>
+      <c r="AF257" s="21">
+        <f>IF(K257="","",K257*AE257)</f>
+        <v/>
+      </c>
+      <c r="AG257" s="19" t="n"/>
+      <c r="AH257" s="19" t="n"/>
+      <c r="AI257" s="19" t="n"/>
+      <c r="AJ257" s="19" t="n"/>
+      <c r="AK257" s="19" t="n"/>
+      <c r="AL257" s="19" t="n"/>
+      <c r="AM257" s="16" t="inlineStr">
+        <is>
+          <t>1 Küche aus mehreren Modulen. Spielgeschirr und Zubehör gehören nicht dazu. Zwei weitere Spielküchen von Wesco stehen unter NU03-03 und NU07-03.</t>
+        </is>
+      </c>
+      <c r="AN257" s="22" t="n"/>
+    </row>
+    <row r="258" ht="30" customHeight="1">
+      <c r="A258" s="15" t="inlineStr">
+        <is>
+          <t>BA03-03</t>
+        </is>
+      </c>
+      <c r="B258" s="15" t="n"/>
+      <c r="C258" s="15" t="n"/>
+      <c r="D258" s="15" t="inlineStr">
+        <is>
+          <t>BA03</t>
+        </is>
+      </c>
+      <c r="E258" s="15" t="inlineStr">
+        <is>
+          <t>Sofa grau, 2-Sitzer</t>
+        </is>
+      </c>
+      <c r="F258" s="16" t="inlineStr">
+        <is>
+          <t>Kleines Zweisitzer-Sofa mit grauem Steppbezug aus Velours und weißem Metallgestell. Bezug abnehmbar.</t>
+        </is>
+      </c>
+      <c r="G258" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H258" s="15" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="I258" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J258" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K258" s="17" t="n"/>
+      <c r="L258" s="18">
+        <f>J258-IF(K258="",0,K258)</f>
+        <v/>
+      </c>
+      <c r="M258" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N258" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O258" s="19" t="n"/>
+      <c r="P258" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q258" s="19" t="n"/>
+      <c r="R258" s="20" t="n"/>
+      <c r="S258" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="T258" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U258" s="21">
+        <f>L258*S258</f>
+        <v/>
+      </c>
+      <c r="V258" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W258" s="15" t="inlineStr">
+        <is>
+          <t>F-294</t>
+        </is>
+      </c>
+      <c r="X258" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y258" s="19" t="n"/>
+      <c r="Z258" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA258" s="19" t="n"/>
+      <c r="AB258" s="19" t="n"/>
+      <c r="AC258" s="19" t="n"/>
+      <c r="AD258" s="19" t="n"/>
+      <c r="AE258" s="20" t="n"/>
+      <c r="AF258" s="21">
+        <f>IF(K258="","",K258*AE258)</f>
+        <v/>
+      </c>
+      <c r="AG258" s="19" t="n"/>
+      <c r="AH258" s="19" t="n"/>
+      <c r="AI258" s="19" t="n"/>
+      <c r="AJ258" s="19" t="n"/>
+      <c r="AK258" s="19" t="n"/>
+      <c r="AL258" s="19" t="n"/>
+      <c r="AM258" s="16" t="inlineStr">
+        <is>
+          <t>1 Sofa. Das Kissen gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN258" s="22" t="n"/>
+    </row>
+    <row r="259" ht="30" customHeight="1">
+      <c r="A259" s="15" t="inlineStr">
+        <is>
+          <t>BA03-05</t>
+        </is>
+      </c>
+      <c r="B259" s="15" t="n"/>
+      <c r="C259" s="15" t="n"/>
+      <c r="D259" s="15" t="inlineStr">
+        <is>
+          <t>BA03</t>
+        </is>
+      </c>
+      <c r="E259" s="15" t="inlineStr">
+        <is>
+          <t>BRIO Puppenwagen rot gepunktet</t>
+        </is>
+      </c>
+      <c r="F259" s="16" t="inlineStr">
+        <is>
+          <t>Kombi-Puppenwagen von BRIO: weißes Metallgestell mit Luftreifen, roter Stoffbezug mit weißen Punkten, schwenkbarer Schiebebügel, Ablagekorb unten. Markenetikett am Verdeck.</t>
+        </is>
+      </c>
+      <c r="G259" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H259" s="15" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="I259" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J259" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K259" s="17" t="n"/>
+      <c r="L259" s="18">
+        <f>J259-IF(K259="",0,K259)</f>
+        <v/>
+      </c>
+      <c r="M259" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N259" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O259" s="19" t="n"/>
+      <c r="P259" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q259" s="19" t="n"/>
+      <c r="R259" s="20" t="n"/>
+      <c r="S259" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T259" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U259" s="21">
+        <f>L259*S259</f>
+        <v/>
+      </c>
+      <c r="V259" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W259" s="15" t="inlineStr">
+        <is>
+          <t>F-296</t>
+        </is>
+      </c>
+      <c r="X259" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y259" s="19" t="n"/>
+      <c r="Z259" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA259" s="19" t="inlineStr">
+        <is>
+          <t>BRIO</t>
+        </is>
+      </c>
+      <c r="AB259" s="19" t="n"/>
+      <c r="AC259" s="19" t="n"/>
+      <c r="AD259" s="19" t="n"/>
+      <c r="AE259" s="20" t="n"/>
+      <c r="AF259" s="21">
+        <f>IF(K259="","",K259*AE259)</f>
+        <v/>
+      </c>
+      <c r="AG259" s="19" t="n"/>
+      <c r="AH259" s="19" t="n"/>
+      <c r="AI259" s="19" t="n"/>
+      <c r="AJ259" s="19" t="n"/>
+      <c r="AK259" s="19" t="n"/>
+      <c r="AL259" s="19" t="n"/>
+      <c r="AM259" s="16" t="inlineStr">
+        <is>
+          <t>1 Puppenwagen. Die Puppe gehört nicht dazu. Das Etikett ist auf Foto F-297 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN259" s="22" t="n"/>
+    </row>
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="15" t="inlineStr">
+        <is>
+          <t>BA03-06</t>
+        </is>
+      </c>
+      <c r="B260" s="15" t="n"/>
+      <c r="C260" s="15" t="n"/>
+      <c r="D260" s="15" t="inlineStr">
+        <is>
+          <t>BA03</t>
+        </is>
+      </c>
+      <c r="E260" s="15" t="inlineStr">
+        <is>
+          <t>Kaufladen weiß mit Aufsatz</t>
+        </is>
+      </c>
+      <c r="F260" s="16" t="inlineStr">
+        <is>
+          <t>Kaufladen aus Holz, weiß mit grauer Rückwand: Verkaufstheke mit Ablage unten, Aufsatz mit mehreren unterschiedlich großen Fächern.</t>
+        </is>
+      </c>
+      <c r="G260" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H260" s="15" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="I260" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J260" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K260" s="17" t="n"/>
+      <c r="L260" s="18">
+        <f>J260-IF(K260="",0,K260)</f>
+        <v/>
+      </c>
+      <c r="M260" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N260" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O260" s="19" t="n"/>
+      <c r="P260" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q260" s="19" t="n"/>
+      <c r="R260" s="20" t="n"/>
+      <c r="S260" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T260" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U260" s="21">
+        <f>L260*S260</f>
+        <v/>
+      </c>
+      <c r="V260" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W260" s="15" t="inlineStr">
+        <is>
+          <t>F-298</t>
+        </is>
+      </c>
+      <c r="X260" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y260" s="19" t="n"/>
+      <c r="Z260" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA260" s="19" t="n"/>
+      <c r="AB260" s="19" t="n"/>
+      <c r="AC260" s="19" t="n"/>
+      <c r="AD260" s="19" t="n"/>
+      <c r="AE260" s="20" t="n"/>
+      <c r="AF260" s="21">
+        <f>IF(K260="","",K260*AE260)</f>
+        <v/>
+      </c>
+      <c r="AG260" s="19" t="n"/>
+      <c r="AH260" s="19" t="n"/>
+      <c r="AI260" s="19" t="n"/>
+      <c r="AJ260" s="19" t="n"/>
+      <c r="AK260" s="19" t="n"/>
+      <c r="AL260" s="19" t="n"/>
+      <c r="AM260" s="16" t="inlineStr">
+        <is>
+          <t>1 Kaufladen. Kasse, Spiellebensmittel und Geschirr gehören nicht dazu. Ein zweiter Kaufladen steht unter NU07-02.</t>
+        </is>
+      </c>
+      <c r="AN260" s="22" t="n"/>
+    </row>
+    <row r="261" ht="30" customHeight="1">
+      <c r="A261" s="15" t="inlineStr">
+        <is>
+          <t>BA03-07</t>
+        </is>
+      </c>
+      <c r="B261" s="15" t="n"/>
+      <c r="C261" s="15" t="n"/>
+      <c r="D261" s="15" t="inlineStr">
+        <is>
+          <t>BA03</t>
+        </is>
+      </c>
+      <c r="E261" s="15" t="inlineStr">
+        <is>
+          <t>Schrank weiß, zwei Türen</t>
+        </is>
+      </c>
+      <c r="F261" s="16" t="inlineStr">
+        <is>
+          <t>Hoher Schrank in Weiß mit zwei Türen und runden Porzellanknöpfen in Rosenform.</t>
+        </is>
+      </c>
+      <c r="G261" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H261" s="15" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="I261" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J261" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K261" s="17" t="n"/>
+      <c r="L261" s="18">
+        <f>J261-IF(K261="",0,K261)</f>
+        <v/>
+      </c>
+      <c r="M261" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N261" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O261" s="19" t="n"/>
+      <c r="P261" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q261" s="19" t="n"/>
+      <c r="R261" s="20" t="n"/>
+      <c r="S261" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="T261" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U261" s="21">
+        <f>L261*S261</f>
+        <v/>
+      </c>
+      <c r="V261" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W261" s="15" t="inlineStr">
+        <is>
+          <t>F-299</t>
+        </is>
+      </c>
+      <c r="X261" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y261" s="19" t="n"/>
+      <c r="Z261" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA261" s="19" t="n"/>
+      <c r="AB261" s="19" t="n"/>
+      <c r="AC261" s="19" t="n"/>
+      <c r="AD261" s="19" t="n"/>
+      <c r="AE261" s="20" t="n"/>
+      <c r="AF261" s="21">
+        <f>IF(K261="","",K261*AE261)</f>
+        <v/>
+      </c>
+      <c r="AG261" s="19" t="n"/>
+      <c r="AH261" s="19" t="n"/>
+      <c r="AI261" s="19" t="n"/>
+      <c r="AJ261" s="19" t="n"/>
+      <c r="AK261" s="19" t="n"/>
+      <c r="AL261" s="19" t="n"/>
+      <c r="AM261" s="16" t="inlineStr">
+        <is>
+          <t>1 Schrank.</t>
+        </is>
+      </c>
+      <c r="AN261" s="22" t="n"/>
+    </row>
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="15" t="inlineStr">
+        <is>
+          <t>BA03-04</t>
+        </is>
+      </c>
+      <c r="B262" s="15" t="n"/>
+      <c r="C262" s="15" t="n"/>
+      <c r="D262" s="15" t="inlineStr">
+        <is>
+          <t>BA03</t>
+        </is>
+      </c>
+      <c r="E262" s="15" t="inlineStr">
+        <is>
+          <t>Wandregal Hausform, schwarz</t>
+        </is>
+      </c>
+      <c r="F262" s="16" t="inlineStr">
+        <is>
+          <t>Wandregale in Hausform aus schwarz lackiertem Holz, zum Aufstellen oder Aufhängen, in unterschiedlichen Größen.</t>
+        </is>
+      </c>
+      <c r="G262" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H262" s="15" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="I262" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J262" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K262" s="17" t="n"/>
+      <c r="L262" s="18">
+        <f>J262-IF(K262="",0,K262)</f>
+        <v/>
+      </c>
+      <c r="M262" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N262" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O262" s="19" t="n"/>
+      <c r="P262" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q262" s="19" t="n"/>
+      <c r="R262" s="20" t="n"/>
+      <c r="S262" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T262" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U262" s="21">
+        <f>L262*S262</f>
+        <v/>
+      </c>
+      <c r="V262" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W262" s="15" t="inlineStr">
+        <is>
+          <t>F-295</t>
+        </is>
+      </c>
+      <c r="X262" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y262" s="19" t="n"/>
+      <c r="Z262" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA262" s="19" t="n"/>
+      <c r="AB262" s="19" t="n"/>
+      <c r="AC262" s="19" t="n"/>
+      <c r="AD262" s="19" t="n"/>
+      <c r="AE262" s="20" t="n"/>
+      <c r="AF262" s="21">
+        <f>IF(K262="","",K262*AE262)</f>
+        <v/>
+      </c>
+      <c r="AG262" s="19" t="n"/>
+      <c r="AH262" s="19" t="n"/>
+      <c r="AI262" s="19" t="n"/>
+      <c r="AJ262" s="19" t="n"/>
+      <c r="AK262" s="19" t="n"/>
+      <c r="AL262" s="19" t="n"/>
+      <c r="AM262" s="16" t="inlineStr">
+        <is>
+          <t>5 Häuser in verschiedenen Größen. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN262" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN255"/>
+  <autoFilter ref="A2:AN262"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -32188,7 +33033,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z255">
+  <conditionalFormatting sqref="Z3:Z262">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -32199,12 +33044,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I255">
+  <conditionalFormatting sqref="I3:I262">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P255">
+  <conditionalFormatting sqref="P3:P262">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -32257,7 +33102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -32295,7 +33140,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$255)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$262)</f>
         <v/>
       </c>
     </row>
@@ -32306,7 +33151,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$255,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$262,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -32317,7 +33162,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$255,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$262,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -32328,7 +33173,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$255,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$262,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -32339,7 +33184,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$255,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$262,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -32350,7 +33195,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$255)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$262)</f>
         <v/>
       </c>
     </row>
@@ -32361,7 +33206,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$255)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32379,7 +33224,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$255)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$262)</f>
         <v/>
       </c>
     </row>
@@ -32390,7 +33235,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$255,Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$262,Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
     </row>
@@ -32423,7 +33268,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$255="bezahlt")*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$262="bezahlt")*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
     </row>
@@ -32452,7 +33297,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$255,"*verkauft",Artikelstamm!$AI$3:$AI$255,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$262,"*verkauft",Artikelstamm!$AI$3:$AI$262,"")</f>
         <v/>
       </c>
     </row>
@@ -32463,7 +33308,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$255,"*verkauft",Artikelstamm!$AJ$3:$AJ$255,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$262,"*verkauft",Artikelstamm!$AJ$3:$AJ$262,"offen")</f>
         <v/>
       </c>
     </row>
@@ -32474,7 +33319,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$255,"reserviert",Artikelstamm!$AL$3:$AL$255,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$262,"reserviert",Artikelstamm!$AL$3:$AL$262,"")</f>
         <v/>
       </c>
     </row>
@@ -32485,7 +33330,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$255,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$262,"")</f>
         <v/>
       </c>
     </row>
@@ -32496,7 +33341,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$255,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$262,"")</f>
         <v/>
       </c>
     </row>
@@ -32536,15 +33381,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$255,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$262,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$255=$A30)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$262=$A30)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$255,$A30,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$262,$A30,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32555,15 +33400,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$255,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$262,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$255=$A31)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$262=$A31)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$255,$A31,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$262,$A31,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32574,15 +33419,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$255,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$262,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$255=$A32)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$262=$A32)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$255,$A32,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$262,$A32,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32641,15 +33486,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A37)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A37)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A37,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A37,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32660,15 +33505,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A38)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A38)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A38,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A38,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32679,15 +33524,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A39)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A39)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A39,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A39,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32698,15 +33543,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A40)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A40)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A40,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A40,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32717,15 +33562,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A41)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A41)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A41,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A41,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32736,15 +33581,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A42)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A42)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A42,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A42,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32755,15 +33600,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A43)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A43)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A43,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A43,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32774,15 +33619,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A44)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A44)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A44,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A44,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32793,15 +33638,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A45)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A45)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A45,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A45,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32812,15 +33657,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A46)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A46)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A46,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A46,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32831,15 +33676,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A47)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A47)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A47,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A47,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32850,15 +33695,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A48)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A48)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A48,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A48,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32869,15 +33714,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A49)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A49)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A49,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A49,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32888,15 +33733,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$255,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$255=$A50)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A50)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$255,$A50,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A50,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32955,15 +33800,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A55)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A55)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A55,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A55,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32974,15 +33819,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A56)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A56)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A56,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A56,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -32993,15 +33838,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A57)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A57)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A57,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A57,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -33012,15 +33857,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A58)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A58)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A58,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A58,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -33031,15 +33876,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A59)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A59)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A59,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A59,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -33050,15 +33895,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A60)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A60)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A60,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A60,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
@@ -33069,486 +33914,505 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A61)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A61)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A61,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A61,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="26" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Galerie</t>
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A62)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A62)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A62,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A62,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="26" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A63)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A63)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A63,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A63,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum</t>
+          <t>Gartenanlage</t>
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A64)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A64)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A64,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A64,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A65)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A65)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A65,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A65,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum 2</t>
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A66)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A66)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A66,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A66,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A67)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A67)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A67,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A67,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="26" t="inlineStr">
         <is>
-          <t>Küche</t>
+          <t>Gruppenraum 5</t>
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A68)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A68)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A68,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A68,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="26" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Küche</t>
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A69)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A69)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A69,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A69,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="26" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A70)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A70)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A70,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A70,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A71)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A71)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A71,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A71,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum 4</t>
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A72)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A72)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A72,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A72,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="26" t="inlineStr">
         <is>
-          <t>Speisesaal</t>
+          <t>Schlafraum 5</t>
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A73)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A73)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A73,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A73,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="26" t="inlineStr">
         <is>
-          <t>Terrasse</t>
+          <t>Speisesaal</t>
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A74)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A74)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A74,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A74,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="26" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Terrasse</t>
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A75)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A75)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A75,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A75,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="26" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Treppenraum 1</t>
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A76)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A76)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A76,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A76,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A77)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A77)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A77,Artikelstamm!$U$3:$U$255)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A77,Artikelstamm!$U$3:$U$262)</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B78" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A78)</f>
+        <v/>
+      </c>
+      <c r="C78" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A78)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <v/>
+      </c>
+      <c r="D78" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A78,Artikelstamm!$U$3:$U$262)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$255,$A78)</f>
-        <v/>
-      </c>
-      <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$255=$A78)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
-        <v/>
-      </c>
-      <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$255,$A78,Artikelstamm!$U$3:$U$255)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="28" t="inlineStr">
+      <c r="B79" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A79)</f>
+        <v/>
+      </c>
+      <c r="C79" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A79)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <v/>
+      </c>
+      <c r="D79" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A79,Artikelstamm!$U$3:$U$262)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B79" s="35">
-        <f>SUM(B55:B78)</f>
-        <v/>
-      </c>
-      <c r="C79" s="36">
-        <f>SUM(C55:C78)</f>
-        <v/>
-      </c>
-      <c r="D79" s="36">
-        <f>SUM(D55:D78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="25" t="inlineStr">
+      <c r="B80" s="35">
+        <f>SUM(B55:B79)</f>
+        <v/>
+      </c>
+      <c r="C80" s="36">
+        <f>SUM(C55:C79)</f>
+        <v/>
+      </c>
+      <c r="D80" s="36">
+        <f>SUM(D55:D79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="32" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B82" s="32" t="inlineStr">
+      <c r="B83" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C82" s="32" t="inlineStr">
+      <c r="C83" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B83" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A83)</f>
-        <v/>
-      </c>
-      <c r="C83" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A83)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
-        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A84)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A84)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A85)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A85)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A86)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A86)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A87)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A87)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B88" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A88)</f>
+        <v/>
+      </c>
+      <c r="C88" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A88)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$255,$A88)</f>
-        <v/>
-      </c>
-      <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$255=$A88)*Artikelstamm!$K$3:$K$255*Artikelstamm!$AE$3:$AE$255)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="28" t="inlineStr">
+      <c r="B89" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A89)</f>
+        <v/>
+      </c>
+      <c r="C89" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A89)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B89" s="35">
-        <f>SUM(B83:B88)</f>
-        <v/>
-      </c>
-      <c r="C89" s="36">
-        <f>SUM(C83:C88)</f>
+      <c r="B90" s="35">
+        <f>SUM(B84:B89)</f>
+        <v/>
+      </c>
+      <c r="C90" s="36">
+        <f>SUM(C84:C89)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$262</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN262"/>
+  <dimension ref="A1:AN267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="J4" s="17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" s="17" t="n"/>
       <c r="L4" s="18">
@@ -1544,7 +1544,7 @@
       <c r="AL4" s="19" t="n"/>
       <c r="AM4" s="16" t="inlineStr">
         <is>
-          <t>1 Stück im Bild</t>
+          <t>4 Kisten – abgebildet ist eine davon.</t>
         </is>
       </c>
       <c r="AN4" s="22" t="n"/>
@@ -23982,7 +23982,7 @@
       <c r="B188" s="15" t="n"/>
       <c r="C188" s="15" t="inlineStr">
         <is>
-          <t>NU05-05, NU07-06</t>
+          <t>NU05-05, NU07-06, BA04-03</t>
         </is>
       </c>
       <c r="D188" s="15" t="inlineStr">
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="J188" s="17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K188" s="17" t="n"/>
       <c r="L188" s="18">
@@ -24095,12 +24095,12 @@
       <c r="AL188" s="19" t="n"/>
       <c r="AM188" s="16" t="inlineStr">
         <is>
-          <t>5 Regale insgesamt: 3 im Schlafraum 5, 1 im Treppenraum 1 (dort NU05-05) und 1 in der Garage (dort NU07-06).</t>
+          <t>8 Regale insgesamt: 3 im Schlafraum 5, 1 im Treppenraum 1 (NU05-05), 1 in der Garage (NU07-06) und 3 im Gruppenraum 4 (BA04-03).</t>
         </is>
       </c>
       <c r="AN188" s="22" t="inlineStr">
         <is>
-          <t>Zusammengefasste Position – Post-it-Nummern in den anderen Räumen: NU05-05, NU07-06.</t>
+          <t>Zusammengefasste Position über vier Räume – Post-it-Nummern: NU05-05, NU07-06, BA04-03.</t>
         </is>
       </c>
     </row>
@@ -24833,7 +24833,11 @@
         </is>
       </c>
       <c r="B195" s="15" t="n"/>
-      <c r="C195" s="15" t="n"/>
+      <c r="C195" s="15" t="inlineStr">
+        <is>
+          <t>BA04-08</t>
+        </is>
+      </c>
       <c r="D195" s="15" t="inlineStr">
         <is>
           <t>NU04</t>
@@ -24865,7 +24869,7 @@
         </is>
       </c>
       <c r="J195" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K195" s="17" t="n"/>
       <c r="L195" s="18">
@@ -24940,10 +24944,14 @@
       <c r="AL195" s="19" t="n"/>
       <c r="AM195" s="16" t="inlineStr">
         <is>
-          <t>2 Einheiten, jeweils Unterteil und Wandaufsatz. Der Inhalt der Wannen gehört nicht dazu.</t>
-        </is>
-      </c>
-      <c r="AN195" s="22" t="n"/>
+          <t>4 Einheiten, jeweils Unterteil und Wandaufsatz: 2 im Schlafraum 5 und 2 im Gruppenraum 4 (dort mit BA04-08 beschriftet). Der Inhalt der Wannen gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN195" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA04-08.</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="15" t="inlineStr">
@@ -33022,8 +33030,611 @@
       </c>
       <c r="AN262" s="22" t="n"/>
     </row>
+    <row r="263" ht="30" customHeight="1">
+      <c r="A263" s="15" t="inlineStr">
+        <is>
+          <t>BA04-04</t>
+        </is>
+      </c>
+      <c r="B263" s="15" t="n"/>
+      <c r="C263" s="15" t="n"/>
+      <c r="D263" s="15" t="inlineStr">
+        <is>
+          <t>BA04</t>
+        </is>
+      </c>
+      <c r="E263" s="15" t="inlineStr">
+        <is>
+          <t>Stapelstuhl Kunststoff, weiß</t>
+        </is>
+      </c>
+      <c r="F263" s="16" t="inlineStr">
+        <is>
+          <t>Stuhl aus weißem Kunststoff in einem Stück, runde Rückenlehne, konische Beine mit Querstrebe, stapelbar. Sitzfläche mit Kratzern.</t>
+        </is>
+      </c>
+      <c r="G263" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H263" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="I263" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J263" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="K263" s="17" t="n"/>
+      <c r="L263" s="18">
+        <f>J263-IF(K263="",0,K263)</f>
+        <v/>
+      </c>
+      <c r="M263" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N263" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O263" s="19" t="n"/>
+      <c r="P263" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q263" s="19" t="n"/>
+      <c r="R263" s="20" t="n"/>
+      <c r="S263" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T263" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U263" s="21">
+        <f>L263*S263</f>
+        <v/>
+      </c>
+      <c r="V263" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W263" s="15" t="inlineStr">
+        <is>
+          <t>F-303</t>
+        </is>
+      </c>
+      <c r="X263" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y263" s="19" t="n"/>
+      <c r="Z263" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA263" s="19" t="n"/>
+      <c r="AB263" s="19" t="n"/>
+      <c r="AC263" s="19" t="n"/>
+      <c r="AD263" s="19" t="n"/>
+      <c r="AE263" s="20" t="n"/>
+      <c r="AF263" s="21">
+        <f>IF(K263="","",K263*AE263)</f>
+        <v/>
+      </c>
+      <c r="AG263" s="19" t="n"/>
+      <c r="AH263" s="19" t="n"/>
+      <c r="AI263" s="19" t="n"/>
+      <c r="AJ263" s="19" t="n"/>
+      <c r="AK263" s="19" t="n"/>
+      <c r="AL263" s="19" t="n"/>
+      <c r="AM263" s="16" t="inlineStr">
+        <is>
+          <t>8 Stühle – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AN263" s="22" t="inlineStr">
+        <is>
+          <t>Groesse klaeren: auf dem Erfassungsblatt stehen sie als Kinderstuehle, die Proportionen im Foto sprechen eher fuer Erwachsenengroesse. Bitte Sitzhoehe messen - davon haengt der Preis ab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="30" customHeight="1">
+      <c r="A264" s="15" t="inlineStr">
+        <is>
+          <t>BA04-05</t>
+        </is>
+      </c>
+      <c r="B264" s="15" t="n"/>
+      <c r="C264" s="15" t="n"/>
+      <c r="D264" s="15" t="inlineStr">
+        <is>
+          <t>BA04</t>
+        </is>
+      </c>
+      <c r="E264" s="15" t="inlineStr">
+        <is>
+          <t>Kinder-Sessel Bugholz mit Polster</t>
+        </is>
+      </c>
+      <c r="F264" s="16" t="inlineStr">
+        <is>
+          <t>Sessel in Kindergröße: Gestell aus gebogenem Schichtholz in Birke, Auflage aus cremefarbenem Stoff mit Nackenkissen. Bezug abnehmbar, Stoff fleckig.</t>
+        </is>
+      </c>
+      <c r="G264" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H264" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="I264" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J264" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K264" s="17" t="n"/>
+      <c r="L264" s="18">
+        <f>J264-IF(K264="",0,K264)</f>
+        <v/>
+      </c>
+      <c r="M264" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N264" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O264" s="19" t="n"/>
+      <c r="P264" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q264" s="19" t="n"/>
+      <c r="R264" s="20" t="n"/>
+      <c r="S264" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T264" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U264" s="21">
+        <f>L264*S264</f>
+        <v/>
+      </c>
+      <c r="V264" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W264" s="15" t="inlineStr">
+        <is>
+          <t>F-304</t>
+        </is>
+      </c>
+      <c r="X264" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y264" s="19" t="n"/>
+      <c r="Z264" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA264" s="19" t="n"/>
+      <c r="AB264" s="19" t="n"/>
+      <c r="AC264" s="19" t="n"/>
+      <c r="AD264" s="19" t="n"/>
+      <c r="AE264" s="20" t="n"/>
+      <c r="AF264" s="21">
+        <f>IF(K264="","",K264*AE264)</f>
+        <v/>
+      </c>
+      <c r="AG264" s="19" t="n"/>
+      <c r="AH264" s="19" t="n"/>
+      <c r="AI264" s="19" t="n"/>
+      <c r="AJ264" s="19" t="n"/>
+      <c r="AK264" s="19" t="n"/>
+      <c r="AL264" s="19" t="n"/>
+      <c r="AM264" s="16" t="inlineStr">
+        <is>
+          <t>1 Sessel.</t>
+        </is>
+      </c>
+      <c r="AN264" s="22" t="n"/>
+    </row>
+    <row r="265" ht="30" customHeight="1">
+      <c r="A265" s="15" t="inlineStr">
+        <is>
+          <t>BA04-06</t>
+        </is>
+      </c>
+      <c r="B265" s="15" t="n"/>
+      <c r="C265" s="15" t="n"/>
+      <c r="D265" s="15" t="inlineStr">
+        <is>
+          <t>BA04</t>
+        </is>
+      </c>
+      <c r="E265" s="15" t="inlineStr">
+        <is>
+          <t>Rollwagen weiß, drei Etagen</t>
+        </is>
+      </c>
+      <c r="F265" s="16" t="inlineStr">
+        <is>
+          <t>Rollwagen aus weiß lackiertem Stahlblech mit drei Wannenböden und vier Rollen.</t>
+        </is>
+      </c>
+      <c r="G265" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H265" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="I265" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J265" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K265" s="17" t="n"/>
+      <c r="L265" s="18">
+        <f>J265-IF(K265="",0,K265)</f>
+        <v/>
+      </c>
+      <c r="M265" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N265" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O265" s="19" t="n"/>
+      <c r="P265" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q265" s="19" t="n"/>
+      <c r="R265" s="20" t="n"/>
+      <c r="S265" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T265" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U265" s="21">
+        <f>L265*S265</f>
+        <v/>
+      </c>
+      <c r="V265" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W265" s="15" t="inlineStr">
+        <is>
+          <t>F-305</t>
+        </is>
+      </c>
+      <c r="X265" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y265" s="19" t="n"/>
+      <c r="Z265" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA265" s="19" t="n"/>
+      <c r="AB265" s="19" t="n"/>
+      <c r="AC265" s="19" t="n"/>
+      <c r="AD265" s="19" t="n"/>
+      <c r="AE265" s="20" t="n"/>
+      <c r="AF265" s="21">
+        <f>IF(K265="","",K265*AE265)</f>
+        <v/>
+      </c>
+      <c r="AG265" s="19" t="n"/>
+      <c r="AH265" s="19" t="n"/>
+      <c r="AI265" s="19" t="n"/>
+      <c r="AJ265" s="19" t="n"/>
+      <c r="AK265" s="19" t="n"/>
+      <c r="AL265" s="19" t="n"/>
+      <c r="AM265" s="16" t="inlineStr">
+        <is>
+          <t>1 Wagen. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN265" s="22" t="n"/>
+    </row>
+    <row r="266" ht="30" customHeight="1">
+      <c r="A266" s="15" t="inlineStr">
+        <is>
+          <t>BA04-07</t>
+        </is>
+      </c>
+      <c r="B266" s="15" t="n"/>
+      <c r="C266" s="15" t="n"/>
+      <c r="D266" s="15" t="inlineStr">
+        <is>
+          <t>BA04</t>
+        </is>
+      </c>
+      <c r="E266" s="15" t="inlineStr">
+        <is>
+          <t>Beistelltisch Drahtkorb, weiß</t>
+        </is>
+      </c>
+      <c r="F266" s="16" t="inlineStr">
+        <is>
+          <t>Runder Beistelltisch: weißer Drahtkorb mit abnehmbarer Platte in heller Holzoptik. Der Korb lässt sich als Ablage nutzen.</t>
+        </is>
+      </c>
+      <c r="G266" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H266" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="I266" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J266" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K266" s="17" t="n"/>
+      <c r="L266" s="18">
+        <f>J266-IF(K266="",0,K266)</f>
+        <v/>
+      </c>
+      <c r="M266" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N266" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O266" s="19" t="n"/>
+      <c r="P266" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q266" s="19" t="n"/>
+      <c r="R266" s="20" t="n"/>
+      <c r="S266" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T266" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U266" s="21">
+        <f>L266*S266</f>
+        <v/>
+      </c>
+      <c r="V266" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W266" s="15" t="inlineStr">
+        <is>
+          <t>F-306</t>
+        </is>
+      </c>
+      <c r="X266" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y266" s="19" t="n"/>
+      <c r="Z266" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA266" s="19" t="n"/>
+      <c r="AB266" s="19" t="n"/>
+      <c r="AC266" s="19" t="n"/>
+      <c r="AD266" s="19" t="n"/>
+      <c r="AE266" s="20" t="n"/>
+      <c r="AF266" s="21">
+        <f>IF(K266="","",K266*AE266)</f>
+        <v/>
+      </c>
+      <c r="AG266" s="19" t="n"/>
+      <c r="AH266" s="19" t="n"/>
+      <c r="AI266" s="19" t="n"/>
+      <c r="AJ266" s="19" t="n"/>
+      <c r="AK266" s="19" t="n"/>
+      <c r="AL266" s="19" t="n"/>
+      <c r="AM266" s="16" t="inlineStr">
+        <is>
+          <t>1 Tisch. Baugleich in Kupfer gibt es zwei Stück unter NU02-07.</t>
+        </is>
+      </c>
+      <c r="AN266" s="22" t="n"/>
+    </row>
+    <row r="267" ht="30" customHeight="1">
+      <c r="A267" s="15" t="inlineStr">
+        <is>
+          <t>BA04-09</t>
+        </is>
+      </c>
+      <c r="B267" s="15" t="n"/>
+      <c r="C267" s="15" t="n"/>
+      <c r="D267" s="15" t="inlineStr">
+        <is>
+          <t>BA04</t>
+        </is>
+      </c>
+      <c r="E267" s="15" t="inlineStr">
+        <is>
+          <t>Kinderschrank weiß, zwei Türen mit Schublade</t>
+        </is>
+      </c>
+      <c r="F267" s="16" t="inlineStr">
+        <is>
+          <t>Hoher Schrank in Weiß mit zwei Türen und schwarzen Griffmulden, darunter eine Schublade.</t>
+        </is>
+      </c>
+      <c r="G267" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H267" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="I267" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J267" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K267" s="17" t="n"/>
+      <c r="L267" s="18">
+        <f>J267-IF(K267="",0,K267)</f>
+        <v/>
+      </c>
+      <c r="M267" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N267" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O267" s="19" t="n"/>
+      <c r="P267" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q267" s="19" t="n"/>
+      <c r="R267" s="20" t="n"/>
+      <c r="S267" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T267" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U267" s="21">
+        <f>L267*S267</f>
+        <v/>
+      </c>
+      <c r="V267" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W267" s="15" t="inlineStr">
+        <is>
+          <t>F-308</t>
+        </is>
+      </c>
+      <c r="X267" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y267" s="19" t="n"/>
+      <c r="Z267" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA267" s="19" t="n"/>
+      <c r="AB267" s="19" t="n"/>
+      <c r="AC267" s="19" t="n"/>
+      <c r="AD267" s="19" t="n"/>
+      <c r="AE267" s="20" t="n"/>
+      <c r="AF267" s="21">
+        <f>IF(K267="","",K267*AE267)</f>
+        <v/>
+      </c>
+      <c r="AG267" s="19" t="n"/>
+      <c r="AH267" s="19" t="n"/>
+      <c r="AI267" s="19" t="n"/>
+      <c r="AJ267" s="19" t="n"/>
+      <c r="AK267" s="19" t="n"/>
+      <c r="AL267" s="19" t="n"/>
+      <c r="AM267" s="16" t="inlineStr">
+        <is>
+          <t>2 Schränke – abgebildet ist einer davon. Baugleich könnten die beiden Schränke unter BA02-08 sein.</t>
+        </is>
+      </c>
+      <c r="AN267" s="22" t="inlineStr">
+        <is>
+          <t>Zu klaeren: sind diese Schraenke baugleich mit BA02-08? Dann zu einer Position mit 4 Stueck zusammenfassen.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN262"/>
+  <autoFilter ref="A2:AN267"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -33033,7 +33644,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z262">
+  <conditionalFormatting sqref="Z3:Z267">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -33044,12 +33655,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I262">
+  <conditionalFormatting sqref="I3:I267">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P262">
+  <conditionalFormatting sqref="P3:P267">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -33140,7 +33751,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$262)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$267)</f>
         <v/>
       </c>
     </row>
@@ -33151,7 +33762,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$262,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$267,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -33162,7 +33773,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$262,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$267,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -33173,7 +33784,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$262,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$267,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -33184,7 +33795,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$262,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$267,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -33195,7 +33806,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$262)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$267)</f>
         <v/>
       </c>
     </row>
@@ -33206,7 +33817,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$262)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33224,7 +33835,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$262)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$267)</f>
         <v/>
       </c>
     </row>
@@ -33235,7 +33846,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$262,Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$267,Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
     </row>
@@ -33268,7 +33879,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$262="bezahlt")*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$267="bezahlt")*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
     </row>
@@ -33297,7 +33908,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$262,"*verkauft",Artikelstamm!$AI$3:$AI$262,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$267,"*verkauft",Artikelstamm!$AI$3:$AI$267,"")</f>
         <v/>
       </c>
     </row>
@@ -33308,7 +33919,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$262,"*verkauft",Artikelstamm!$AJ$3:$AJ$262,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$267,"*verkauft",Artikelstamm!$AJ$3:$AJ$267,"offen")</f>
         <v/>
       </c>
     </row>
@@ -33319,7 +33930,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$262,"reserviert",Artikelstamm!$AL$3:$AL$262,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$267,"reserviert",Artikelstamm!$AL$3:$AL$267,"")</f>
         <v/>
       </c>
     </row>
@@ -33330,7 +33941,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$262,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$267,"")</f>
         <v/>
       </c>
     </row>
@@ -33341,7 +33952,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$262,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$267,"")</f>
         <v/>
       </c>
     </row>
@@ -33381,15 +33992,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$262,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$267,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$262=$A30)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$267=$A30)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$262,$A30,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$267,$A30,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33400,15 +34011,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$262,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$267,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$262=$A31)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$267=$A31)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$262,$A31,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$267,$A31,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33419,15 +34030,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$262,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$267,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$262=$A32)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$267=$A32)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$262,$A32,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$267,$A32,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33486,15 +34097,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A37)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A37)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A37,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A37,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33505,15 +34116,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A38)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A38)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A38,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A38,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33524,15 +34135,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A39)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A39)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A39,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A39,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33543,15 +34154,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A40)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A40)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A40,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A40,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33562,15 +34173,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A41)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A41)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A41,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A41,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33581,15 +34192,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A42)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A42)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A42,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A42,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33600,15 +34211,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A43)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A43)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A43,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A43,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33619,15 +34230,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A44)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A44)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A44,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A44,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33638,15 +34249,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A45)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A45)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A45,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A45,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33657,15 +34268,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A46)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A46)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A46,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A46,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33676,15 +34287,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A47)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A47)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A47,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A47,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33695,15 +34306,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A48)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A48)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A48,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A48,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33714,15 +34325,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A49)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A49)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A49,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A49,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33733,15 +34344,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$262,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$262=$A50)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A50)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$262,$A50,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A50,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33800,15 +34411,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A55)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A55)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A55,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A55,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33819,15 +34430,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A56)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A56)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A56,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A56,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33838,15 +34449,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A57)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A57)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A57,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A57,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33857,15 +34468,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A58)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A58)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A58,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A58,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33876,15 +34487,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A59)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A59)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A59,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A59,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33895,15 +34506,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A60)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A60)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A60,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A60,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33914,15 +34525,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A61)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A61)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A61,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A61,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33933,15 +34544,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A62)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A62)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A62,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A62,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33952,15 +34563,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A63)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A63)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A63,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A63,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33971,15 +34582,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A64)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A64)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A64,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A64,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -33990,15 +34601,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A65)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A65)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A65,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A65,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34009,15 +34620,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A66)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A66)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A66,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A66,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34028,15 +34639,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A67)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A67)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A67,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A67,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34047,15 +34658,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A68)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A68)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A68,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A68,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34066,15 +34677,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A69)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A69)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A69,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A69,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34085,15 +34696,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A70)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A70)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A70,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A70,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34104,15 +34715,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A71)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A71)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A71,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A71,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34123,15 +34734,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A72)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A72)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A72,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A72,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34142,15 +34753,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A73)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A73)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A73,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A73,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34161,15 +34772,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A74)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A74)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A74,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A74,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34180,15 +34791,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A75)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A75)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A75,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A75,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34199,15 +34810,15 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A76)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A76)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A76,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A76,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34218,15 +34829,15 @@
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A77)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A77)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A77,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A77,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34237,15 +34848,15 @@
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A78)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A78)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A78,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A78,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34256,15 +34867,15 @@
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$262,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$262=$A79)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A79)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
       <c r="D79" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$262,$A79,Artikelstamm!$U$3:$U$262)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A79,Artikelstamm!$U$3:$U$267)</f>
         <v/>
       </c>
     </row>
@@ -34318,11 +34929,11 @@
         </is>
       </c>
       <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A84)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A84)</f>
         <v/>
       </c>
       <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A84)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A84)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
     </row>
@@ -34333,11 +34944,11 @@
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A85)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A85)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
     </row>
@@ -34348,11 +34959,11 @@
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A86)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A86)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
     </row>
@@ -34363,11 +34974,11 @@
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A87)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A87)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
     </row>
@@ -34378,11 +34989,11 @@
         </is>
       </c>
       <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A88)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A88)</f>
         <v/>
       </c>
       <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A88)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A88)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
     </row>
@@ -34393,11 +35004,11 @@
         </is>
       </c>
       <c r="B89" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$262,$A89)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A89)</f>
         <v/>
       </c>
       <c r="C89" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$262=$A89)*Artikelstamm!$K$3:$K$262*Artikelstamm!$AE$3:$AE$262)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A89)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$276</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN267"/>
+  <dimension ref="A1:AN276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30379,7 +30379,11 @@
         </is>
       </c>
       <c r="B241" s="15" t="n"/>
-      <c r="C241" s="15" t="n"/>
+      <c r="C241" s="15" t="inlineStr">
+        <is>
+          <t>BA04-09</t>
+        </is>
+      </c>
       <c r="D241" s="15" t="inlineStr">
         <is>
           <t>BA02</t>
@@ -30387,12 +30391,12 @@
       </c>
       <c r="E241" s="15" t="inlineStr">
         <is>
-          <t>Kinderschrank weiß mit Handabdrücken</t>
+          <t>IKEA Kinderschrank weiß, zwei Türen</t>
         </is>
       </c>
       <c r="F241" s="16" t="inlineStr">
         <is>
-          <t>Hoher Schrank in Weiß mit Türen und Schubladen, Griffmulden. Auf den Fronten kleben Aufkleber mit Kinderhandabdrücken in Schwarz und Rot; sie lassen sich abziehen.</t>
+          <t>Hoher Schrank von IKEA in Weiß mit zwei Türen und schwarzen Griffmulden, darunter Schubladen. Auf zwei der Schränke kleben Aufkleber mit Kinderhandabdrücken; sie lassen sich abziehen.</t>
         </is>
       </c>
       <c r="G241" s="15" t="inlineStr">
@@ -30411,7 +30415,7 @@
         </is>
       </c>
       <c r="J241" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K241" s="17" t="n"/>
       <c r="L241" s="18">
@@ -30469,7 +30473,11 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="AA241" s="19" t="n"/>
+      <c r="AA241" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
       <c r="AB241" s="19" t="n"/>
       <c r="AC241" s="19" t="n"/>
       <c r="AD241" s="19" t="n"/>
@@ -30486,10 +30494,14 @@
       <c r="AL241" s="19" t="n"/>
       <c r="AM241" s="16" t="inlineStr">
         <is>
-          <t>2 Schränke – abgebildet ist einer davon.</t>
-        </is>
-      </c>
-      <c r="AN241" s="22" t="n"/>
+          <t>4 Schränke insgesamt: 2 im Flur 2 (BA02-08) und 2 im Gruppenraum 4 (dort mit BA04-09 beschriftet). Abgebildet ist einer davon, ein weiterer auf Foto F-308.</t>
+        </is>
+      </c>
+      <c r="AN241" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA04-09.</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="30" customHeight="1">
       <c r="A242" s="15" t="inlineStr">
@@ -33045,12 +33057,12 @@
       </c>
       <c r="E263" s="15" t="inlineStr">
         <is>
-          <t>Stapelstuhl Kunststoff, weiß</t>
+          <t>Stapelstuhl Kunststoff weiß, Erwachsenengröße</t>
         </is>
       </c>
       <c r="F263" s="16" t="inlineStr">
         <is>
-          <t>Stuhl aus weißem Kunststoff in einem Stück, runde Rückenlehne, konische Beine mit Querstrebe, stapelbar. Sitzfläche mit Kratzern.</t>
+          <t>Stuhl aus weißem Kunststoff in einem Stück, runde Rückenlehne, konische Beine mit Querstrebe, stapelbar. Erwachsenengröße. Sitzfläche mit Kratzern.</t>
         </is>
       </c>
       <c r="G263" s="15" t="inlineStr">
@@ -33095,7 +33107,7 @@
       <c r="Q263" s="19" t="n"/>
       <c r="R263" s="20" t="n"/>
       <c r="S263" s="20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T263" s="19" t="inlineStr">
         <is>
@@ -33147,11 +33159,7 @@
           <t>8 Stühle – abgebildet ist einer davon.</t>
         </is>
       </c>
-      <c r="AN263" s="22" t="inlineStr">
-        <is>
-          <t>Groesse klaeren: auf dem Erfassungsblatt stehen sie als Kinderstuehle, die Proportionen im Foto sprechen eher fuer Erwachsenengroesse. Bitte Sitzhoehe messen - davon haengt der Preis ab.</t>
-        </is>
-      </c>
+      <c r="AN263" s="22" t="n"/>
     </row>
     <row r="264" ht="30" customHeight="1">
       <c r="A264" s="15" t="inlineStr">
@@ -33513,34 +33521,34 @@
     <row r="267" ht="30" customHeight="1">
       <c r="A267" s="15" t="inlineStr">
         <is>
-          <t>BA04-09</t>
+          <t>BA05-01</t>
         </is>
       </c>
       <c r="B267" s="15" t="n"/>
       <c r="C267" s="15" t="n"/>
       <c r="D267" s="15" t="inlineStr">
         <is>
-          <t>BA04</t>
+          <t>BA05</t>
         </is>
       </c>
       <c r="E267" s="15" t="inlineStr">
         <is>
-          <t>Kinderschrank weiß, zwei Türen mit Schublade</t>
+          <t>Rollkasten mit großen Kunststoff-Bausteinen</t>
         </is>
       </c>
       <c r="F267" s="16" t="inlineStr">
         <is>
-          <t>Hoher Schrank in Weiß mit zwei Türen und schwarzen Griffmulden, darunter eine Schublade.</t>
+          <t>Flacher Kasten auf Rollen, Front in Weiß, Grün oder Grau, gefüllt mit großen Kunststoff-Bausteinen in Rot, Blau, Gelb und Grün.</t>
         </is>
       </c>
       <c r="G267" s="15" t="inlineStr">
         <is>
-          <t>Möbel</t>
+          <t>Kita-Ausstattung</t>
         </is>
       </c>
       <c r="H267" s="15" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="I267" s="15" t="inlineStr">
@@ -33549,7 +33557,7 @@
         </is>
       </c>
       <c r="J267" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K267" s="17" t="n"/>
       <c r="L267" s="18">
@@ -33575,7 +33583,7 @@
       <c r="Q267" s="19" t="n"/>
       <c r="R267" s="20" t="n"/>
       <c r="S267" s="20" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="T267" s="19" t="inlineStr">
         <is>
@@ -33593,7 +33601,7 @@
       </c>
       <c r="W267" s="15" t="inlineStr">
         <is>
-          <t>F-308</t>
+          <t>F-310</t>
         </is>
       </c>
       <c r="X267" s="19" t="inlineStr">
@@ -33624,17 +33632,1100 @@
       <c r="AL267" s="19" t="n"/>
       <c r="AM267" s="16" t="inlineStr">
         <is>
-          <t>2 Schränke – abgebildet ist einer davon. Baugleich könnten die beiden Schränke unter BA02-08 sein.</t>
-        </is>
-      </c>
-      <c r="AN267" s="22" t="inlineStr">
-        <is>
-          <t>Zu klaeren: sind diese Schraenke baugleich mit BA02-08? Dann zu einer Position mit 4 Stueck zusammenfassen.</t>
+          <t>4 Kästen einschließlich der Bausteine – alle vier sind abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN267" s="22" t="n"/>
+    </row>
+    <row r="268" ht="30" customHeight="1">
+      <c r="A268" s="15" t="inlineStr">
+        <is>
+          <t>BA05-02</t>
+        </is>
+      </c>
+      <c r="B268" s="15" t="n"/>
+      <c r="C268" s="15" t="n"/>
+      <c r="D268" s="15" t="inlineStr">
+        <is>
+          <t>BA05</t>
+        </is>
+      </c>
+      <c r="E268" s="15" t="inlineStr">
+        <is>
+          <t>BENZ Turnbank</t>
+        </is>
+      </c>
+      <c r="F268" s="16" t="inlineStr">
+        <is>
+          <t>Turnbank aus Holz mit Schmalseite zum Umdrehen, rutschhemmender Belag, Aufhängehaken an einem Ende. Aufdruck: BENZ Geräte.</t>
+        </is>
+      </c>
+      <c r="G268" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H268" s="15" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="I268" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J268" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K268" s="17" t="n"/>
+      <c r="L268" s="18">
+        <f>J268-IF(K268="",0,K268)</f>
+        <v/>
+      </c>
+      <c r="M268" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N268" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O268" s="19" t="n"/>
+      <c r="P268" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q268" s="19" t="n"/>
+      <c r="R268" s="20" t="n"/>
+      <c r="S268" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="T268" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U268" s="21">
+        <f>L268*S268</f>
+        <v/>
+      </c>
+      <c r="V268" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W268" s="15" t="inlineStr">
+        <is>
+          <t>F-312</t>
+        </is>
+      </c>
+      <c r="X268" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y268" s="19" t="n"/>
+      <c r="Z268" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA268" s="19" t="inlineStr">
+        <is>
+          <t>BENZ</t>
+        </is>
+      </c>
+      <c r="AB268" s="19" t="n"/>
+      <c r="AC268" s="19" t="n"/>
+      <c r="AD268" s="19" t="n"/>
+      <c r="AE268" s="20" t="n"/>
+      <c r="AF268" s="21">
+        <f>IF(K268="","",K268*AE268)</f>
+        <v/>
+      </c>
+      <c r="AG268" s="19" t="n"/>
+      <c r="AH268" s="19" t="n"/>
+      <c r="AI268" s="19" t="n"/>
+      <c r="AJ268" s="19" t="n"/>
+      <c r="AK268" s="19" t="n"/>
+      <c r="AL268" s="19" t="n"/>
+      <c r="AM268" s="16" t="inlineStr">
+        <is>
+          <t>2 Bänke, beide abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN268" s="22" t="n"/>
+    </row>
+    <row r="269" ht="30" customHeight="1">
+      <c r="A269" s="15" t="inlineStr">
+        <is>
+          <t>BA05-03</t>
+        </is>
+      </c>
+      <c r="B269" s="15" t="n"/>
+      <c r="C269" s="15" t="n"/>
+      <c r="D269" s="15" t="inlineStr">
+        <is>
+          <t>BA05</t>
+        </is>
+      </c>
+      <c r="E269" s="15" t="inlineStr">
+        <is>
+          <t>Trampolin mit Haltestange</t>
+        </is>
+      </c>
+      <c r="F269" s="16" t="inlineStr">
+        <is>
+          <t>Rundes Fitness-Trampolin mit gepolstertem Randschutz in Rot und abnehmbarer Haltestange. Aufdruck auf dem Sprungtuch: ANCHEER. Der Randschutz ist an mehreren Stellen eingerissen.</t>
+        </is>
+      </c>
+      <c r="G269" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H269" s="15" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="I269" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J269" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K269" s="17" t="n"/>
+      <c r="L269" s="18">
+        <f>J269-IF(K269="",0,K269)</f>
+        <v/>
+      </c>
+      <c r="M269" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N269" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O269" s="19" t="n"/>
+      <c r="P269" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q269" s="19" t="n"/>
+      <c r="R269" s="20" t="n"/>
+      <c r="S269" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T269" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U269" s="21">
+        <f>L269*S269</f>
+        <v/>
+      </c>
+      <c r="V269" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W269" s="15" t="inlineStr">
+        <is>
+          <t>F-313</t>
+        </is>
+      </c>
+      <c r="X269" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y269" s="19" t="n"/>
+      <c r="Z269" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA269" s="19" t="inlineStr">
+        <is>
+          <t>ANCHEER</t>
+        </is>
+      </c>
+      <c r="AB269" s="19" t="n"/>
+      <c r="AC269" s="19" t="n"/>
+      <c r="AD269" s="19" t="n"/>
+      <c r="AE269" s="20" t="n"/>
+      <c r="AF269" s="21">
+        <f>IF(K269="","",K269*AE269)</f>
+        <v/>
+      </c>
+      <c r="AG269" s="19" t="n"/>
+      <c r="AH269" s="19" t="n"/>
+      <c r="AI269" s="19" t="n"/>
+      <c r="AJ269" s="19" t="n"/>
+      <c r="AK269" s="19" t="n"/>
+      <c r="AL269" s="19" t="n"/>
+      <c r="AM269" s="16" t="inlineStr">
+        <is>
+          <t>1 Trampolin.</t>
+        </is>
+      </c>
+      <c r="AN269" s="22" t="n"/>
+    </row>
+    <row r="270" ht="30" customHeight="1">
+      <c r="A270" s="15" t="inlineStr">
+        <is>
+          <t>BA05-04</t>
+        </is>
+      </c>
+      <c r="B270" s="15" t="n"/>
+      <c r="C270" s="15" t="n"/>
+      <c r="D270" s="15" t="inlineStr">
+        <is>
+          <t>BA05</t>
+        </is>
+      </c>
+      <c r="E270" s="15" t="inlineStr">
+        <is>
+          <t>Spielhochbett mit Bällebad und Rutsche</t>
+        </is>
+      </c>
+      <c r="F270" s="16" t="inlineStr">
+        <is>
+          <t>Großes Spielhochbett aus weiß beschichteter Platte: zwei Liegeflächen oben mit Absturzsicherung, Leiter, Rutsche, runde Bullaugen und darunter ein eingebautes Bällebad einschließlich der Bälle.</t>
+        </is>
+      </c>
+      <c r="G270" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H270" s="15" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="I270" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J270" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K270" s="17" t="n"/>
+      <c r="L270" s="18">
+        <f>J270-IF(K270="",0,K270)</f>
+        <v/>
+      </c>
+      <c r="M270" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N270" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O270" s="19" t="n"/>
+      <c r="P270" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q270" s="19" t="n"/>
+      <c r="R270" s="20" t="n"/>
+      <c r="S270" s="20" t="n">
+        <v>750</v>
+      </c>
+      <c r="T270" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U270" s="21">
+        <f>L270*S270</f>
+        <v/>
+      </c>
+      <c r="V270" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W270" s="15" t="inlineStr">
+        <is>
+          <t>F-314</t>
+        </is>
+      </c>
+      <c r="X270" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y270" s="19" t="n"/>
+      <c r="Z270" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA270" s="19" t="n"/>
+      <c r="AB270" s="19" t="n"/>
+      <c r="AC270" s="19" t="n"/>
+      <c r="AD270" s="19" t="n"/>
+      <c r="AE270" s="20" t="n"/>
+      <c r="AF270" s="21">
+        <f>IF(K270="","",K270*AE270)</f>
+        <v/>
+      </c>
+      <c r="AG270" s="19" t="n"/>
+      <c r="AH270" s="19" t="n"/>
+      <c r="AI270" s="19" t="n"/>
+      <c r="AJ270" s="19" t="n"/>
+      <c r="AK270" s="19" t="n"/>
+      <c r="AL270" s="19" t="n"/>
+      <c r="AM270" s="16" t="inlineStr">
+        <is>
+          <t>1 Anlage einschließlich der Bälle. Abbau und Transport durch den Käufer. Das Bällebad ist auf Foto F-315 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN270" s="22" t="inlineStr">
+        <is>
+          <t>Preis ist meine Schaetzung: als Schreinerarbeit neu 3.000-6.000 EUR. Bitte bestaetigen - das ist nach dem Vitra Alcove die zweitgroesste Einzelposition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="30" customHeight="1">
+      <c r="A271" s="15" t="inlineStr">
+        <is>
+          <t>BA05-05</t>
+        </is>
+      </c>
+      <c r="B271" s="15" t="n"/>
+      <c r="C271" s="15" t="n"/>
+      <c r="D271" s="15" t="inlineStr">
+        <is>
+          <t>BA05</t>
+        </is>
+      </c>
+      <c r="E271" s="15" t="inlineStr">
+        <is>
+          <t>Sprossenwand einzeln</t>
+        </is>
+      </c>
+      <c r="F271" s="16" t="inlineStr">
+        <is>
+          <t>Sprossenwand aus Massivholz zur Wandmontage, mit Querholmen über die volle Breite.</t>
+        </is>
+      </c>
+      <c r="G271" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H271" s="15" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="I271" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J271" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K271" s="17" t="n"/>
+      <c r="L271" s="18">
+        <f>J271-IF(K271="",0,K271)</f>
+        <v/>
+      </c>
+      <c r="M271" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N271" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O271" s="19" t="n"/>
+      <c r="P271" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q271" s="19" t="n"/>
+      <c r="R271" s="20" t="n"/>
+      <c r="S271" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="T271" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U271" s="21">
+        <f>L271*S271</f>
+        <v/>
+      </c>
+      <c r="V271" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W271" s="15" t="n"/>
+      <c r="X271" s="19" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="Y271" s="19" t="n"/>
+      <c r="Z271" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA271" s="19" t="n"/>
+      <c r="AB271" s="19" t="n"/>
+      <c r="AC271" s="19" t="n"/>
+      <c r="AD271" s="19" t="n"/>
+      <c r="AE271" s="20" t="n"/>
+      <c r="AF271" s="21">
+        <f>IF(K271="","",K271*AE271)</f>
+        <v/>
+      </c>
+      <c r="AG271" s="19" t="n"/>
+      <c r="AH271" s="19" t="n"/>
+      <c r="AI271" s="19" t="n"/>
+      <c r="AJ271" s="19" t="n"/>
+      <c r="AK271" s="19" t="n"/>
+      <c r="AL271" s="19" t="n"/>
+      <c r="AM271" s="16" t="inlineStr">
+        <is>
+          <t>3 Sprossenwände.</t>
+        </is>
+      </c>
+      <c r="AN271" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: Foto fehlt. Das Bild kam nur als Chatbild an, nicht als Datei - es konnte deshalb nicht in die Fotoverarbeitung. Bitte als Dateianhang nachreichen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="30" customHeight="1">
+      <c r="A272" s="15" t="inlineStr">
+        <is>
+          <t>BA05-06</t>
+        </is>
+      </c>
+      <c r="B272" s="15" t="n"/>
+      <c r="C272" s="15" t="n"/>
+      <c r="D272" s="15" t="inlineStr">
+        <is>
+          <t>BA05</t>
+        </is>
+      </c>
+      <c r="E272" s="15" t="inlineStr">
+        <is>
+          <t>Doppelsprossenwand</t>
+        </is>
+      </c>
+      <c r="F272" s="16" t="inlineStr">
+        <is>
+          <t>Breite Sprossenwand aus Massivholz zur Wandmontage, zwei Felder nebeneinander mit durchgehenden Querholmen und oberer Ausleger-Leiste.</t>
+        </is>
+      </c>
+      <c r="G272" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H272" s="15" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="I272" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J272" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K272" s="17" t="n"/>
+      <c r="L272" s="18">
+        <f>J272-IF(K272="",0,K272)</f>
+        <v/>
+      </c>
+      <c r="M272" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N272" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O272" s="19" t="n"/>
+      <c r="P272" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q272" s="19" t="n"/>
+      <c r="R272" s="20" t="n"/>
+      <c r="S272" s="20" t="n">
+        <v>180</v>
+      </c>
+      <c r="T272" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U272" s="21">
+        <f>L272*S272</f>
+        <v/>
+      </c>
+      <c r="V272" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W272" s="15" t="inlineStr">
+        <is>
+          <t>F-316</t>
+        </is>
+      </c>
+      <c r="X272" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y272" s="19" t="n"/>
+      <c r="Z272" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA272" s="19" t="n"/>
+      <c r="AB272" s="19" t="n"/>
+      <c r="AC272" s="19" t="n"/>
+      <c r="AD272" s="19" t="n"/>
+      <c r="AE272" s="20" t="n"/>
+      <c r="AF272" s="21">
+        <f>IF(K272="","",K272*AE272)</f>
+        <v/>
+      </c>
+      <c r="AG272" s="19" t="n"/>
+      <c r="AH272" s="19" t="n"/>
+      <c r="AI272" s="19" t="n"/>
+      <c r="AJ272" s="19" t="n"/>
+      <c r="AK272" s="19" t="n"/>
+      <c r="AL272" s="19" t="n"/>
+      <c r="AM272" s="16" t="inlineStr">
+        <is>
+          <t>1 Doppelsprossenwand.</t>
+        </is>
+      </c>
+      <c r="AN272" s="22" t="n"/>
+    </row>
+    <row r="273" ht="30" customHeight="1">
+      <c r="A273" s="15" t="inlineStr">
+        <is>
+          <t>BA05-07</t>
+        </is>
+      </c>
+      <c r="B273" s="15" t="n"/>
+      <c r="C273" s="15" t="n"/>
+      <c r="D273" s="15" t="inlineStr">
+        <is>
+          <t>BA05</t>
+        </is>
+      </c>
+      <c r="E273" s="15" t="inlineStr">
+        <is>
+          <t>Treppenturngerät gepolstert</t>
+        </is>
+      </c>
+      <c r="F273" s="16" t="inlineStr">
+        <is>
+          <t>Turngerät aus Schaumstoff mit Kunstlederbezug in Creme und Grau: Treppenelement mit drei Stufen und passende Rampe, zusammensteckbar.</t>
+        </is>
+      </c>
+      <c r="G273" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H273" s="15" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="I273" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J273" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K273" s="17" t="n"/>
+      <c r="L273" s="18">
+        <f>J273-IF(K273="",0,K273)</f>
+        <v/>
+      </c>
+      <c r="M273" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N273" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O273" s="19" t="n"/>
+      <c r="P273" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q273" s="19" t="n"/>
+      <c r="R273" s="20" t="n"/>
+      <c r="S273" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="T273" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U273" s="21">
+        <f>L273*S273</f>
+        <v/>
+      </c>
+      <c r="V273" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W273" s="15" t="inlineStr">
+        <is>
+          <t>F-317</t>
+        </is>
+      </c>
+      <c r="X273" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y273" s="19" t="n"/>
+      <c r="Z273" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA273" s="19" t="n"/>
+      <c r="AB273" s="19" t="n"/>
+      <c r="AC273" s="19" t="n"/>
+      <c r="AD273" s="19" t="n"/>
+      <c r="AE273" s="20" t="n"/>
+      <c r="AF273" s="21">
+        <f>IF(K273="","",K273*AE273)</f>
+        <v/>
+      </c>
+      <c r="AG273" s="19" t="n"/>
+      <c r="AH273" s="19" t="n"/>
+      <c r="AI273" s="19" t="n"/>
+      <c r="AJ273" s="19" t="n"/>
+      <c r="AK273" s="19" t="n"/>
+      <c r="AL273" s="19" t="n"/>
+      <c r="AM273" s="16" t="inlineStr">
+        <is>
+          <t>1 Gerät aus mehreren Teilen.</t>
+        </is>
+      </c>
+      <c r="AN273" s="22" t="n"/>
+    </row>
+    <row r="274" ht="30" customHeight="1">
+      <c r="A274" s="15" t="inlineStr">
+        <is>
+          <t>BA05-08</t>
+        </is>
+      </c>
+      <c r="B274" s="15" t="n"/>
+      <c r="C274" s="15" t="n"/>
+      <c r="D274" s="15" t="inlineStr">
+        <is>
+          <t>BA05</t>
+        </is>
+      </c>
+      <c r="E274" s="15" t="inlineStr">
+        <is>
+          <t>Rody Hüpfpferd rot</t>
+        </is>
+      </c>
+      <c r="F274" s="16" t="inlineStr">
+        <is>
+          <t>Hüpfpferd Rody aus rotem Gummi mit gelbem Sattelaufdruck und weißen Punkten, aufblasbar. Markenaufdruck am Bauch.</t>
+        </is>
+      </c>
+      <c r="G274" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H274" s="15" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="I274" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J274" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K274" s="17" t="n"/>
+      <c r="L274" s="18">
+        <f>J274-IF(K274="",0,K274)</f>
+        <v/>
+      </c>
+      <c r="M274" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N274" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O274" s="19" t="n"/>
+      <c r="P274" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q274" s="19" t="n"/>
+      <c r="R274" s="20" t="n"/>
+      <c r="S274" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T274" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U274" s="21">
+        <f>L274*S274</f>
+        <v/>
+      </c>
+      <c r="V274" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W274" s="15" t="inlineStr">
+        <is>
+          <t>F-318</t>
+        </is>
+      </c>
+      <c r="X274" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y274" s="19" t="n"/>
+      <c r="Z274" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA274" s="19" t="inlineStr">
+        <is>
+          <t>Rody</t>
+        </is>
+      </c>
+      <c r="AB274" s="19" t="n"/>
+      <c r="AC274" s="19" t="n"/>
+      <c r="AD274" s="19" t="n"/>
+      <c r="AE274" s="20" t="n"/>
+      <c r="AF274" s="21">
+        <f>IF(K274="","",K274*AE274)</f>
+        <v/>
+      </c>
+      <c r="AG274" s="19" t="n"/>
+      <c r="AH274" s="19" t="n"/>
+      <c r="AI274" s="19" t="n"/>
+      <c r="AJ274" s="19" t="n"/>
+      <c r="AK274" s="19" t="n"/>
+      <c r="AL274" s="19" t="n"/>
+      <c r="AM274" s="16" t="inlineStr">
+        <is>
+          <t>1 Hüpfpferd.</t>
+        </is>
+      </c>
+      <c r="AN274" s="22" t="n"/>
+    </row>
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="15" t="inlineStr">
+        <is>
+          <t>BA05-09</t>
+        </is>
+      </c>
+      <c r="B275" s="15" t="n"/>
+      <c r="C275" s="15" t="n"/>
+      <c r="D275" s="15" t="inlineStr">
+        <is>
+          <t>BA05</t>
+        </is>
+      </c>
+      <c r="E275" s="15" t="inlineStr">
+        <is>
+          <t>Softbausteine gepolstert, groß</t>
+        </is>
+      </c>
+      <c r="F275" s="16" t="inlineStr">
+        <is>
+          <t>Große Turn- und Bauelemente aus Schaumstoff mit Kunstlederbezug in Rot, Blau, Grün und Hellgrün: Treppen, Rampen, Wellen, Quader und Keile.</t>
+        </is>
+      </c>
+      <c r="G275" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H275" s="15" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="I275" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J275" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K275" s="17" t="n"/>
+      <c r="L275" s="18">
+        <f>J275-IF(K275="",0,K275)</f>
+        <v/>
+      </c>
+      <c r="M275" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N275" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O275" s="19" t="n"/>
+      <c r="P275" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q275" s="19" t="n"/>
+      <c r="R275" s="20" t="n"/>
+      <c r="S275" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T275" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U275" s="21">
+        <f>L275*S275</f>
+        <v/>
+      </c>
+      <c r="V275" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W275" s="15" t="inlineStr">
+        <is>
+          <t>F-319</t>
+        </is>
+      </c>
+      <c r="X275" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y275" s="19" t="n"/>
+      <c r="Z275" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA275" s="19" t="n"/>
+      <c r="AB275" s="19" t="n"/>
+      <c r="AC275" s="19" t="n"/>
+      <c r="AD275" s="19" t="n"/>
+      <c r="AE275" s="20" t="n"/>
+      <c r="AF275" s="21">
+        <f>IF(K275="","",K275*AE275)</f>
+        <v/>
+      </c>
+      <c r="AG275" s="19" t="n"/>
+      <c r="AH275" s="19" t="n"/>
+      <c r="AI275" s="19" t="n"/>
+      <c r="AJ275" s="19" t="n"/>
+      <c r="AK275" s="19" t="n"/>
+      <c r="AL275" s="19" t="n"/>
+      <c r="AM275" s="16" t="inlineStr">
+        <is>
+          <t>7 Elemente in verschiedenen Formen – alle abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN275" s="22" t="n"/>
+    </row>
+    <row r="276" ht="30" customHeight="1">
+      <c r="A276" s="15" t="inlineStr">
+        <is>
+          <t>BA05-10</t>
+        </is>
+      </c>
+      <c r="B276" s="15" t="n"/>
+      <c r="C276" s="15" t="n"/>
+      <c r="D276" s="15" t="inlineStr">
+        <is>
+          <t>BA05</t>
+        </is>
+      </c>
+      <c r="E276" s="15" t="inlineStr">
+        <is>
+          <t>Wandschutz grün, gepolstert</t>
+        </is>
+      </c>
+      <c r="F276" s="16" t="inlineStr">
+        <is>
+          <t>Gepolsterter Wand- und Säulenschutz mit grünem Kunstlederbezug und grauer Oberseite.</t>
+        </is>
+      </c>
+      <c r="G276" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H276" s="15" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="I276" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J276" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K276" s="17" t="n"/>
+      <c r="L276" s="18">
+        <f>J276-IF(K276="",0,K276)</f>
+        <v/>
+      </c>
+      <c r="M276" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N276" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O276" s="19" t="n"/>
+      <c r="P276" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q276" s="19" t="n"/>
+      <c r="R276" s="20" t="n"/>
+      <c r="S276" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T276" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U276" s="21">
+        <f>L276*S276</f>
+        <v/>
+      </c>
+      <c r="V276" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W276" s="15" t="n"/>
+      <c r="X276" s="19" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="Y276" s="19" t="n"/>
+      <c r="Z276" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA276" s="19" t="n"/>
+      <c r="AB276" s="19" t="n"/>
+      <c r="AC276" s="19" t="n"/>
+      <c r="AD276" s="19" t="n"/>
+      <c r="AE276" s="20" t="n"/>
+      <c r="AF276" s="21">
+        <f>IF(K276="","",K276*AE276)</f>
+        <v/>
+      </c>
+      <c r="AG276" s="19" t="n"/>
+      <c r="AH276" s="19" t="n"/>
+      <c r="AI276" s="19" t="n"/>
+      <c r="AJ276" s="19" t="n"/>
+      <c r="AK276" s="19" t="n"/>
+      <c r="AL276" s="19" t="n"/>
+      <c r="AM276" s="16" t="inlineStr">
+        <is>
+          <t>5 Elemente.</t>
+        </is>
+      </c>
+      <c r="AN276" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: Foto fehlt. Das Bild kam nur als Chatbild an, nicht als Datei - es konnte deshalb nicht in die Fotoverarbeitung. Bitte als Dateianhang nachreichen.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AN267"/>
+  <autoFilter ref="A2:AN276"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -33644,7 +34735,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z267">
+  <conditionalFormatting sqref="Z3:Z276">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -33655,12 +34746,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I267">
+  <conditionalFormatting sqref="I3:I276">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P267">
+  <conditionalFormatting sqref="P3:P276">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -33713,7 +34804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -33751,7 +34842,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$267)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$276)</f>
         <v/>
       </c>
     </row>
@@ -33762,7 +34853,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$267,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$276,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -33773,7 +34864,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$267,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$276,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -33784,7 +34875,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$267,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$276,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -33795,7 +34886,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$267,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$276,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -33806,7 +34897,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$267)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$276)</f>
         <v/>
       </c>
     </row>
@@ -33817,7 +34908,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$267)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -33835,7 +34926,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$267)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$276)</f>
         <v/>
       </c>
     </row>
@@ -33846,7 +34937,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$267,Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$276,Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
     </row>
@@ -33879,7 +34970,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$267="bezahlt")*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$276="bezahlt")*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
     </row>
@@ -33908,7 +34999,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$267,"*verkauft",Artikelstamm!$AI$3:$AI$267,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$276,"*verkauft",Artikelstamm!$AI$3:$AI$276,"")</f>
         <v/>
       </c>
     </row>
@@ -33919,7 +35010,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$267,"*verkauft",Artikelstamm!$AJ$3:$AJ$267,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$276,"*verkauft",Artikelstamm!$AJ$3:$AJ$276,"offen")</f>
         <v/>
       </c>
     </row>
@@ -33930,7 +35021,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$267,"reserviert",Artikelstamm!$AL$3:$AL$267,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$276,"reserviert",Artikelstamm!$AL$3:$AL$276,"")</f>
         <v/>
       </c>
     </row>
@@ -33941,7 +35032,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$267,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$276,"")</f>
         <v/>
       </c>
     </row>
@@ -33952,7 +35043,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$267,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$276,"")</f>
         <v/>
       </c>
     </row>
@@ -33992,15 +35083,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$267,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$276,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$267=$A30)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$276=$A30)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$267,$A30,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$276,$A30,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34011,15 +35102,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$267,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$276,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$267=$A31)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$276=$A31)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$267,$A31,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$276,$A31,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34030,15 +35121,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$267,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$276,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$267=$A32)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$276=$A32)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$267,$A32,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$276,$A32,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34097,15 +35188,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A37)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A37)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A37,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A37,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34116,15 +35207,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A38)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A38)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A38,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A38,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34135,15 +35226,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A39)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A39)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A39,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A39,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34154,15 +35245,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A40)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A40)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A40,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A40,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34173,15 +35264,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A41)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A41)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A41,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A41,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34192,15 +35283,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A42)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A42)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A42,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A42,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34211,15 +35302,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A43)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A43)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A43,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A43,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34230,15 +35321,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A44)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A44)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A44,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A44,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34249,15 +35340,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A45)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A45)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A45,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A45,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34268,15 +35359,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A46)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A46)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A46,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A46,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34287,15 +35378,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A47)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A47)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A47,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A47,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34306,15 +35397,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A48)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A48)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A48,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A48,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34325,15 +35416,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A49)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A49)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A49,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A49,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34344,15 +35435,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$267,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$267=$A50)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A50)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$267,$A50,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A50,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34411,15 +35502,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A55)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A55)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A55,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A55,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34430,15 +35521,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A56)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A56)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A56,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A56,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34449,15 +35540,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A57)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A57)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A57,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A57,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34468,15 +35559,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A58)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A58)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A58,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A58,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34487,15 +35578,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A59)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A59)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A59,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A59,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34506,15 +35597,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A60)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A60)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A60,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A60,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34525,15 +35616,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A61)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A61)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A61,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A61,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34544,15 +35635,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A62)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A62)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A62,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A62,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34563,15 +35654,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A63)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A63)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A63,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A63,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34582,15 +35673,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A64)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A64)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A64,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A64,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34601,15 +35692,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A65)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A65)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A65,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A65,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34620,15 +35711,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A66)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A66)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A66,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A66,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34639,15 +35730,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A67)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A67)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A67,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A67,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34658,15 +35749,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A68)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A68)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A68,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A68,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34677,15 +35768,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A69)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A69)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A69,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A69,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34696,15 +35787,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A70)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A70)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A70,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A70,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34715,15 +35806,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A71)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A71)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A71,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A71,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34734,15 +35825,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A72)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A72)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A72,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A72,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34753,15 +35844,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A73)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A73)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A73,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A73,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34772,15 +35863,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A74)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A74)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A74,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A74,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34791,15 +35882,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A75)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A75)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A75,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A75,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
@@ -34810,220 +35901,239 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A76)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A76)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A76,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A76,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="26" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A77)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A77)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A77,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A77,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A78)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A78)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
       <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A78,Artikelstamm!$U$3:$U$267)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A78,Artikelstamm!$U$3:$U$276)</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B79" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A79)</f>
+        <v/>
+      </c>
+      <c r="C79" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A79)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <v/>
+      </c>
+      <c r="D79" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A79,Artikelstamm!$U$3:$U$276)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$267,$A79)</f>
-        <v/>
-      </c>
-      <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$267=$A79)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
-        <v/>
-      </c>
-      <c r="D79" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$267,$A79,Artikelstamm!$U$3:$U$267)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="28" t="inlineStr">
+      <c r="B80" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A80)</f>
+        <v/>
+      </c>
+      <c r="C80" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A80)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <v/>
+      </c>
+      <c r="D80" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A80,Artikelstamm!$U$3:$U$276)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B80" s="35">
-        <f>SUM(B55:B79)</f>
-        <v/>
-      </c>
-      <c r="C80" s="36">
-        <f>SUM(C55:C79)</f>
-        <v/>
-      </c>
-      <c r="D80" s="36">
-        <f>SUM(D55:D79)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="25" t="inlineStr">
+      <c r="B81" s="35">
+        <f>SUM(B55:B80)</f>
+        <v/>
+      </c>
+      <c r="C81" s="36">
+        <f>SUM(C55:C80)</f>
+        <v/>
+      </c>
+      <c r="D81" s="36">
+        <f>SUM(D55:D80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="32" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B83" s="32" t="inlineStr">
+      <c r="B84" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C83" s="32" t="inlineStr">
+      <c r="C84" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B84" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A84)</f>
-        <v/>
-      </c>
-      <c r="C84" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A84)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
-        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A85)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A85)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A85)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A85)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A86)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A86)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A87)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A87)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A88)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A88)</f>
         <v/>
       </c>
       <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A88)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A88)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B89" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A89)</f>
+        <v/>
+      </c>
+      <c r="C89" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A89)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B89" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$267,$A89)</f>
-        <v/>
-      </c>
-      <c r="C89" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$267=$A89)*Artikelstamm!$K$3:$K$267*Artikelstamm!$AE$3:$AE$267)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="28" t="inlineStr">
+      <c r="B90" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A90)</f>
+        <v/>
+      </c>
+      <c r="C90" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A90)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B90" s="35">
-        <f>SUM(B84:B89)</f>
-        <v/>
-      </c>
-      <c r="C90" s="36">
-        <f>SUM(C84:C89)</f>
+      <c r="B91" s="35">
+        <f>SUM(B85:B90)</f>
+        <v/>
+      </c>
+      <c r="C91" s="36">
+        <f>SUM(C85:C90)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -34026,7 +34026,7 @@
       </c>
       <c r="F271" s="16" t="inlineStr">
         <is>
-          <t>Sprossenwand aus Massivholz zur Wandmontage, mit Querholmen über die volle Breite.</t>
+          <t>Sprossenwand aus Massivholz zur Wandmontage: zwei kräftige Holme mit durchgehenden Rundsprossen, oben eine ausladende Aufhängeleiste.</t>
         </is>
       </c>
       <c r="G271" s="15" t="inlineStr">
@@ -34087,10 +34087,14 @@
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="W271" s="15" t="n"/>
+      <c r="W271" s="15" t="inlineStr">
+        <is>
+          <t>F-321</t>
+        </is>
+      </c>
       <c r="X271" s="19" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="Y271" s="19" t="n"/>
@@ -34116,14 +34120,10 @@
       <c r="AL271" s="19" t="n"/>
       <c r="AM271" s="16" t="inlineStr">
         <is>
-          <t>3 Sprossenwände.</t>
-        </is>
-      </c>
-      <c r="AN271" s="22" t="inlineStr">
-        <is>
-          <t>OFFEN: Foto fehlt. Das Bild kam nur als Chatbild an, nicht als Datei - es konnte deshalb nicht in die Fotoverarbeitung. Bitte als Dateianhang nachreichen.</t>
-        </is>
-      </c>
+          <t>3 Sprossenwände – abgebildet ist eine davon.</t>
+        </is>
+      </c>
+      <c r="AN271" s="22" t="n"/>
     </row>
     <row r="272" ht="30" customHeight="1">
       <c r="A272" s="15" t="inlineStr">
@@ -34620,12 +34620,12 @@
       </c>
       <c r="E276" s="15" t="inlineStr">
         <is>
-          <t>Wandschutz grün, gepolstert</t>
+          <t>Polstersäule grün, Raumteiler</t>
         </is>
       </c>
       <c r="F276" s="16" t="inlineStr">
         <is>
-          <t>Gepolsterter Wand- und Säulenschutz mit grünem Kunstlederbezug und grauer Oberseite.</t>
+          <t>Standsäule aus Schaumstoff mit Kunstlederbezug: Mantel in Limettengrün, Oberseiten in Grau, mehrere Lappen ergeben im Querschnitt eine Blütenform. Als Wand- und Säulenschutz oder als Raumteiler nutzbar.</t>
         </is>
       </c>
       <c r="G276" s="15" t="inlineStr">
@@ -34686,10 +34686,14 @@
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="W276" s="15" t="n"/>
+      <c r="W276" s="15" t="inlineStr">
+        <is>
+          <t>F-322</t>
+        </is>
+      </c>
       <c r="X276" s="19" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="Y276" s="19" t="n"/>
@@ -34715,14 +34719,10 @@
       <c r="AL276" s="19" t="n"/>
       <c r="AM276" s="16" t="inlineStr">
         <is>
-          <t>5 Elemente.</t>
-        </is>
-      </c>
-      <c r="AN276" s="22" t="inlineStr">
-        <is>
-          <t>OFFEN: Foto fehlt. Das Bild kam nur als Chatbild an, nicht als Datei - es konnte deshalb nicht in die Fotoverarbeitung. Bitte als Dateianhang nachreichen.</t>
-        </is>
-      </c>
+          <t>5 Säulen – abgebildet sind sie zusammengestellt.</t>
+        </is>
+      </c>
+      <c r="AN276" s="22" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:AN276"/>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$276</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$287</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN276"/>
+  <dimension ref="A1:AN287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24472,7 +24472,11 @@
         </is>
       </c>
       <c r="B192" s="15" t="n"/>
-      <c r="C192" s="15" t="n"/>
+      <c r="C192" s="15" t="inlineStr">
+        <is>
+          <t>BA06-13</t>
+        </is>
+      </c>
       <c r="D192" s="15" t="inlineStr">
         <is>
           <t>NU04</t>
@@ -24504,7 +24508,7 @@
         </is>
       </c>
       <c r="J192" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K192" s="17" t="n"/>
       <c r="L192" s="18">
@@ -24579,10 +24583,14 @@
       <c r="AL192" s="19" t="n"/>
       <c r="AM192" s="16" t="inlineStr">
         <is>
-          <t>1 Raumteiler.</t>
-        </is>
-      </c>
-      <c r="AN192" s="22" t="n"/>
+          <t>2 Raumteiler: einer im Schlafraum 5 (NU04-14) und einer im Materialraum (dort mit BA06-13 beschriftet).</t>
+        </is>
+      </c>
+      <c r="AN192" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA06-13. Zusammenfassung aus dem Rautenmuster geschlossen, bitte bestaetigen.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="15" t="inlineStr">
@@ -34370,7 +34378,11 @@
         </is>
       </c>
       <c r="B274" s="15" t="n"/>
-      <c r="C274" s="15" t="n"/>
+      <c r="C274" s="15" t="inlineStr">
+        <is>
+          <t>BA06-01</t>
+        </is>
+      </c>
       <c r="D274" s="15" t="inlineStr">
         <is>
           <t>BA05</t>
@@ -34378,12 +34390,12 @@
       </c>
       <c r="E274" s="15" t="inlineStr">
         <is>
-          <t>Rody Hüpfpferd rot</t>
+          <t>Rody Hüpfpferd, rot und grün</t>
         </is>
       </c>
       <c r="F274" s="16" t="inlineStr">
         <is>
-          <t>Hüpfpferd Rody aus rotem Gummi mit gelbem Sattelaufdruck und weißen Punkten, aufblasbar. Markenaufdruck am Bauch.</t>
+          <t>Hüpfpferd Rody aus Gummi mit weißen Punkten, aufblasbar. Markenaufdruck am Bauch. Eines in Rot mit gelbem Sattel, zwei in Grün mit blauem Sattel.</t>
         </is>
       </c>
       <c r="G274" s="15" t="inlineStr">
@@ -34402,7 +34414,7 @@
         </is>
       </c>
       <c r="J274" s="17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K274" s="17" t="n"/>
       <c r="L274" s="18">
@@ -34481,10 +34493,14 @@
       <c r="AL274" s="19" t="n"/>
       <c r="AM274" s="16" t="inlineStr">
         <is>
-          <t>1 Hüpfpferd.</t>
-        </is>
-      </c>
-      <c r="AN274" s="22" t="n"/>
+          <t>3 Hüpfpferde: eines rot im Turnraum (BA05-08) und zwei grüne im Materialraum (dort mit BA06-01 beschriftet). Das rote ist auf Foto F-318 zu sehen, die grünen auf F-323.</t>
+        </is>
+      </c>
+      <c r="AN274" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA06-01.</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="30" customHeight="1">
       <c r="A275" s="15" t="inlineStr">
@@ -34724,8 +34740,1329 @@
       </c>
       <c r="AN276" s="22" t="n"/>
     </row>
+    <row r="277" ht="30" customHeight="1">
+      <c r="A277" s="15" t="inlineStr">
+        <is>
+          <t>BA06-02</t>
+        </is>
+      </c>
+      <c r="B277" s="15" t="n"/>
+      <c r="C277" s="15" t="n"/>
+      <c r="D277" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E277" s="15" t="inlineStr">
+        <is>
+          <t>BMW Baby Racer Rutscherauto</t>
+        </is>
+      </c>
+      <c r="F277" s="16" t="inlineStr">
+        <is>
+          <t>Rutscherauto in Sportwagenform, Karosserie blau mit rotem Sitz, Lenkrad mit Hupe, verchromte Felgen. BMW-Emblem an der Front. Lack stark zerkratzt.</t>
+        </is>
+      </c>
+      <c r="G277" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H277" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I277" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J277" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K277" s="17" t="n"/>
+      <c r="L277" s="18">
+        <f>J277-IF(K277="",0,K277)</f>
+        <v/>
+      </c>
+      <c r="M277" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N277" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O277" s="19" t="n"/>
+      <c r="P277" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q277" s="19" t="n"/>
+      <c r="R277" s="20" t="n"/>
+      <c r="S277" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T277" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U277" s="21">
+        <f>L277*S277</f>
+        <v/>
+      </c>
+      <c r="V277" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W277" s="15" t="inlineStr">
+        <is>
+          <t>F-325</t>
+        </is>
+      </c>
+      <c r="X277" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y277" s="19" t="n"/>
+      <c r="Z277" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA277" s="19" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="AB277" s="19" t="n"/>
+      <c r="AC277" s="19" t="n"/>
+      <c r="AD277" s="19" t="n"/>
+      <c r="AE277" s="20" t="n"/>
+      <c r="AF277" s="21">
+        <f>IF(K277="","",K277*AE277)</f>
+        <v/>
+      </c>
+      <c r="AG277" s="19" t="n"/>
+      <c r="AH277" s="19" t="n"/>
+      <c r="AI277" s="19" t="n"/>
+      <c r="AJ277" s="19" t="n"/>
+      <c r="AK277" s="19" t="n"/>
+      <c r="AL277" s="19" t="n"/>
+      <c r="AM277" s="16" t="inlineStr">
+        <is>
+          <t>1 Fahrzeug.</t>
+        </is>
+      </c>
+      <c r="AN277" s="22" t="n"/>
+    </row>
+    <row r="278" ht="30" customHeight="1">
+      <c r="A278" s="15" t="inlineStr">
+        <is>
+          <t>BA06-03</t>
+        </is>
+      </c>
+      <c r="B278" s="15" t="n"/>
+      <c r="C278" s="15" t="n"/>
+      <c r="D278" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E278" s="15" t="inlineStr">
+        <is>
+          <t>BIG Bobby Quad</t>
+        </is>
+      </c>
+      <c r="F278" s="16" t="inlineStr">
+        <is>
+          <t>Quad-Rutscherfahrzeug aus Kunststoff in Schwarz mit limettengrünen Felgen und Lenkergriffen, Stollenreifen. Aufdruck: bobby quad, BIG.</t>
+        </is>
+      </c>
+      <c r="G278" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H278" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I278" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J278" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K278" s="17" t="n"/>
+      <c r="L278" s="18">
+        <f>J278-IF(K278="",0,K278)</f>
+        <v/>
+      </c>
+      <c r="M278" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N278" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O278" s="19" t="n"/>
+      <c r="P278" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q278" s="19" t="n"/>
+      <c r="R278" s="20" t="n"/>
+      <c r="S278" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T278" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U278" s="21">
+        <f>L278*S278</f>
+        <v/>
+      </c>
+      <c r="V278" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W278" s="15" t="inlineStr">
+        <is>
+          <t>F-326</t>
+        </is>
+      </c>
+      <c r="X278" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y278" s="19" t="n"/>
+      <c r="Z278" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA278" s="19" t="inlineStr">
+        <is>
+          <t>BIG</t>
+        </is>
+      </c>
+      <c r="AB278" s="19" t="n"/>
+      <c r="AC278" s="19" t="n"/>
+      <c r="AD278" s="19" t="n"/>
+      <c r="AE278" s="20" t="n"/>
+      <c r="AF278" s="21">
+        <f>IF(K278="","",K278*AE278)</f>
+        <v/>
+      </c>
+      <c r="AG278" s="19" t="n"/>
+      <c r="AH278" s="19" t="n"/>
+      <c r="AI278" s="19" t="n"/>
+      <c r="AJ278" s="19" t="n"/>
+      <c r="AK278" s="19" t="n"/>
+      <c r="AL278" s="19" t="n"/>
+      <c r="AM278" s="16" t="inlineStr">
+        <is>
+          <t>3 Fahrzeuge – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN278" s="22" t="n"/>
+    </row>
+    <row r="279" ht="30" customHeight="1">
+      <c r="A279" s="15" t="inlineStr">
+        <is>
+          <t>BA06-04</t>
+        </is>
+      </c>
+      <c r="B279" s="15" t="n"/>
+      <c r="C279" s="15" t="n"/>
+      <c r="D279" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E279" s="15" t="inlineStr">
+        <is>
+          <t>Holz-Dreirad mit Kuhkopf</t>
+        </is>
+      </c>
+      <c r="F279" s="16" t="inlineStr">
+        <is>
+          <t>Rutschfahrzeug aus Massivholz mit vier Rädern, ovalem Sitz und Lehne, vorn ein Kuhkopf mit Stoffohren und gemaltem Gesicht.</t>
+        </is>
+      </c>
+      <c r="G279" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H279" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I279" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J279" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K279" s="17" t="n"/>
+      <c r="L279" s="18">
+        <f>J279-IF(K279="",0,K279)</f>
+        <v/>
+      </c>
+      <c r="M279" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N279" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O279" s="19" t="n"/>
+      <c r="P279" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q279" s="19" t="n"/>
+      <c r="R279" s="20" t="n"/>
+      <c r="S279" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T279" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U279" s="21">
+        <f>L279*S279</f>
+        <v/>
+      </c>
+      <c r="V279" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W279" s="15" t="inlineStr">
+        <is>
+          <t>F-324</t>
+        </is>
+      </c>
+      <c r="X279" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y279" s="19" t="n"/>
+      <c r="Z279" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA279" s="19" t="n"/>
+      <c r="AB279" s="19" t="n"/>
+      <c r="AC279" s="19" t="n"/>
+      <c r="AD279" s="19" t="n"/>
+      <c r="AE279" s="20" t="n"/>
+      <c r="AF279" s="21">
+        <f>IF(K279="","",K279*AE279)</f>
+        <v/>
+      </c>
+      <c r="AG279" s="19" t="n"/>
+      <c r="AH279" s="19" t="n"/>
+      <c r="AI279" s="19" t="n"/>
+      <c r="AJ279" s="19" t="n"/>
+      <c r="AK279" s="19" t="n"/>
+      <c r="AL279" s="19" t="n"/>
+      <c r="AM279" s="16" t="inlineStr">
+        <is>
+          <t>1 Fahrzeug.</t>
+        </is>
+      </c>
+      <c r="AN279" s="22" t="n"/>
+    </row>
+    <row r="280" ht="30" customHeight="1">
+      <c r="A280" s="15" t="inlineStr">
+        <is>
+          <t>BA06-05</t>
+        </is>
+      </c>
+      <c r="B280" s="15" t="n"/>
+      <c r="C280" s="15" t="n"/>
+      <c r="D280" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E280" s="15" t="inlineStr">
+        <is>
+          <t>Schaukel- und Rutschtier aus Formholz</t>
+        </is>
+      </c>
+      <c r="F280" s="16" t="inlineStr">
+        <is>
+          <t>Fahrzeug aus weiß lackiertem Formholz mit Naturholz-Lehne, vier kleinen Rollen und schwarzen Griffen. Lack an vielen Stellen abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="G280" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H280" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I280" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J280" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K280" s="17" t="n"/>
+      <c r="L280" s="18">
+        <f>J280-IF(K280="",0,K280)</f>
+        <v/>
+      </c>
+      <c r="M280" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N280" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O280" s="19" t="n"/>
+      <c r="P280" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q280" s="19" t="n"/>
+      <c r="R280" s="20" t="n"/>
+      <c r="S280" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T280" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U280" s="21">
+        <f>L280*S280</f>
+        <v/>
+      </c>
+      <c r="V280" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W280" s="15" t="inlineStr">
+        <is>
+          <t>F-327</t>
+        </is>
+      </c>
+      <c r="X280" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y280" s="19" t="n"/>
+      <c r="Z280" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA280" s="19" t="n"/>
+      <c r="AB280" s="19" t="n"/>
+      <c r="AC280" s="19" t="n"/>
+      <c r="AD280" s="19" t="n"/>
+      <c r="AE280" s="20" t="n"/>
+      <c r="AF280" s="21">
+        <f>IF(K280="","",K280*AE280)</f>
+        <v/>
+      </c>
+      <c r="AG280" s="19" t="n"/>
+      <c r="AH280" s="19" t="n"/>
+      <c r="AI280" s="19" t="n"/>
+      <c r="AJ280" s="19" t="n"/>
+      <c r="AK280" s="19" t="n"/>
+      <c r="AL280" s="19" t="n"/>
+      <c r="AM280" s="16" t="inlineStr">
+        <is>
+          <t>1 Fahrzeug.</t>
+        </is>
+      </c>
+      <c r="AN280" s="22" t="n"/>
+    </row>
+    <row r="281" ht="30" customHeight="1">
+      <c r="A281" s="15" t="inlineStr">
+        <is>
+          <t>BA06-06</t>
+        </is>
+      </c>
+      <c r="B281" s="15" t="n"/>
+      <c r="C281" s="15" t="n"/>
+      <c r="D281" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E281" s="15" t="inlineStr">
+        <is>
+          <t>BIG Bobby Car Feuerwehr</t>
+        </is>
+      </c>
+      <c r="F281" s="16" t="inlineStr">
+        <is>
+          <t>Rutscherauto als Feuerwehrfahrzeug aus rotem Kunststoff mit Blaulicht, drehbarem Wasserwerfer und Stollenreifen. Aufdruck: BIG.</t>
+        </is>
+      </c>
+      <c r="G281" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H281" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I281" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J281" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K281" s="17" t="n"/>
+      <c r="L281" s="18">
+        <f>J281-IF(K281="",0,K281)</f>
+        <v/>
+      </c>
+      <c r="M281" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N281" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O281" s="19" t="n"/>
+      <c r="P281" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q281" s="19" t="n"/>
+      <c r="R281" s="20" t="n"/>
+      <c r="S281" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T281" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U281" s="21">
+        <f>L281*S281</f>
+        <v/>
+      </c>
+      <c r="V281" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W281" s="15" t="inlineStr">
+        <is>
+          <t>F-328</t>
+        </is>
+      </c>
+      <c r="X281" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y281" s="19" t="n"/>
+      <c r="Z281" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA281" s="19" t="inlineStr">
+        <is>
+          <t>BIG</t>
+        </is>
+      </c>
+      <c r="AB281" s="19" t="n"/>
+      <c r="AC281" s="19" t="n"/>
+      <c r="AD281" s="19" t="n"/>
+      <c r="AE281" s="20" t="n"/>
+      <c r="AF281" s="21">
+        <f>IF(K281="","",K281*AE281)</f>
+        <v/>
+      </c>
+      <c r="AG281" s="19" t="n"/>
+      <c r="AH281" s="19" t="n"/>
+      <c r="AI281" s="19" t="n"/>
+      <c r="AJ281" s="19" t="n"/>
+      <c r="AK281" s="19" t="n"/>
+      <c r="AL281" s="19" t="n"/>
+      <c r="AM281" s="16" t="inlineStr">
+        <is>
+          <t>2 Fahrzeuge – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN281" s="22" t="n"/>
+    </row>
+    <row r="282" ht="30" customHeight="1">
+      <c r="A282" s="15" t="inlineStr">
+        <is>
+          <t>BA06-07</t>
+        </is>
+      </c>
+      <c r="B282" s="15" t="n"/>
+      <c r="C282" s="15" t="n"/>
+      <c r="D282" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E282" s="15" t="inlineStr">
+        <is>
+          <t>Klettergerüst Holz</t>
+        </is>
+      </c>
+      <c r="F282" s="16" t="inlineStr">
+        <is>
+          <t>Klettergerüst aus Buche massiv mit Rundsprossen und seitlichen Wangen, zusammenklappbar.</t>
+        </is>
+      </c>
+      <c r="G282" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H282" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I282" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J282" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K282" s="17" t="n"/>
+      <c r="L282" s="18">
+        <f>J282-IF(K282="",0,K282)</f>
+        <v/>
+      </c>
+      <c r="M282" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N282" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O282" s="19" t="n"/>
+      <c r="P282" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q282" s="19" t="n"/>
+      <c r="R282" s="20" t="n"/>
+      <c r="S282" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T282" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U282" s="21">
+        <f>L282*S282</f>
+        <v/>
+      </c>
+      <c r="V282" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W282" s="15" t="inlineStr">
+        <is>
+          <t>F-329</t>
+        </is>
+      </c>
+      <c r="X282" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y282" s="19" t="n"/>
+      <c r="Z282" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA282" s="19" t="n"/>
+      <c r="AB282" s="19" t="n"/>
+      <c r="AC282" s="19" t="n"/>
+      <c r="AD282" s="19" t="n"/>
+      <c r="AE282" s="20" t="n"/>
+      <c r="AF282" s="21">
+        <f>IF(K282="","",K282*AE282)</f>
+        <v/>
+      </c>
+      <c r="AG282" s="19" t="n"/>
+      <c r="AH282" s="19" t="n"/>
+      <c r="AI282" s="19" t="n"/>
+      <c r="AJ282" s="19" t="n"/>
+      <c r="AK282" s="19" t="n"/>
+      <c r="AL282" s="19" t="n"/>
+      <c r="AM282" s="16" t="inlineStr">
+        <is>
+          <t>2 Gerüste – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN282" s="22" t="n"/>
+    </row>
+    <row r="283" ht="30" customHeight="1">
+      <c r="A283" s="15" t="inlineStr">
+        <is>
+          <t>BA06-08</t>
+        </is>
+      </c>
+      <c r="B283" s="15" t="n"/>
+      <c r="C283" s="15" t="n"/>
+      <c r="D283" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E283" s="15" t="inlineStr">
+        <is>
+          <t>Klettergerüst grün mit Rutschbrett</t>
+        </is>
+      </c>
+      <c r="F283" s="16" t="inlineStr">
+        <is>
+          <t>Klettergerüst mit grün lackiertem Metallrahmen, Rundsprossen aus Holz und einem Rutschbrett mit dunkler Lauffläche.</t>
+        </is>
+      </c>
+      <c r="G283" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H283" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I283" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J283" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K283" s="17" t="n"/>
+      <c r="L283" s="18">
+        <f>J283-IF(K283="",0,K283)</f>
+        <v/>
+      </c>
+      <c r="M283" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N283" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O283" s="19" t="n"/>
+      <c r="P283" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q283" s="19" t="n"/>
+      <c r="R283" s="20" t="n"/>
+      <c r="S283" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="T283" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U283" s="21">
+        <f>L283*S283</f>
+        <v/>
+      </c>
+      <c r="V283" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W283" s="15" t="inlineStr">
+        <is>
+          <t>F-330</t>
+        </is>
+      </c>
+      <c r="X283" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y283" s="19" t="n"/>
+      <c r="Z283" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA283" s="19" t="n"/>
+      <c r="AB283" s="19" t="n"/>
+      <c r="AC283" s="19" t="n"/>
+      <c r="AD283" s="19" t="n"/>
+      <c r="AE283" s="20" t="n"/>
+      <c r="AF283" s="21">
+        <f>IF(K283="","",K283*AE283)</f>
+        <v/>
+      </c>
+      <c r="AG283" s="19" t="n"/>
+      <c r="AH283" s="19" t="n"/>
+      <c r="AI283" s="19" t="n"/>
+      <c r="AJ283" s="19" t="n"/>
+      <c r="AK283" s="19" t="n"/>
+      <c r="AL283" s="19" t="n"/>
+      <c r="AM283" s="16" t="inlineStr">
+        <is>
+          <t>3 Gerüste – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN283" s="22" t="n"/>
+    </row>
+    <row r="284" ht="30" customHeight="1">
+      <c r="A284" s="15" t="inlineStr">
+        <is>
+          <t>BA06-09</t>
+        </is>
+      </c>
+      <c r="B284" s="15" t="n"/>
+      <c r="C284" s="15" t="n"/>
+      <c r="D284" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E284" s="15" t="inlineStr">
+        <is>
+          <t>Holz-Lastwagen zum Rutschen</t>
+        </is>
+      </c>
+      <c r="F284" s="16" t="inlineStr">
+        <is>
+          <t>Rutschfahrzeug aus Massivholz in Lastwagenform mit offener Ladefläche, Holzlenkrad und roten Rädern.</t>
+        </is>
+      </c>
+      <c r="G284" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H284" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I284" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J284" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K284" s="17" t="n"/>
+      <c r="L284" s="18">
+        <f>J284-IF(K284="",0,K284)</f>
+        <v/>
+      </c>
+      <c r="M284" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N284" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O284" s="19" t="n"/>
+      <c r="P284" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q284" s="19" t="n"/>
+      <c r="R284" s="20" t="n"/>
+      <c r="S284" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="T284" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U284" s="21">
+        <f>L284*S284</f>
+        <v/>
+      </c>
+      <c r="V284" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W284" s="15" t="n"/>
+      <c r="X284" s="19" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="Y284" s="19" t="n"/>
+      <c r="Z284" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA284" s="19" t="n"/>
+      <c r="AB284" s="19" t="n"/>
+      <c r="AC284" s="19" t="n"/>
+      <c r="AD284" s="19" t="n"/>
+      <c r="AE284" s="20" t="n"/>
+      <c r="AF284" s="21">
+        <f>IF(K284="","",K284*AE284)</f>
+        <v/>
+      </c>
+      <c r="AG284" s="19" t="n"/>
+      <c r="AH284" s="19" t="n"/>
+      <c r="AI284" s="19" t="n"/>
+      <c r="AJ284" s="19" t="n"/>
+      <c r="AK284" s="19" t="n"/>
+      <c r="AL284" s="19" t="n"/>
+      <c r="AM284" s="16" t="inlineStr">
+        <is>
+          <t>1 Fahrzeug.</t>
+        </is>
+      </c>
+      <c r="AN284" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: Foto fehlt. Das Bild kam nur als Chatbild an, nicht als Datei. Bitte als Dateianhang nachreichen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="30" customHeight="1">
+      <c r="A285" s="15" t="inlineStr">
+        <is>
+          <t>BA06-10</t>
+        </is>
+      </c>
+      <c r="B285" s="15" t="n"/>
+      <c r="C285" s="15" t="n"/>
+      <c r="D285" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E285" s="15" t="inlineStr">
+        <is>
+          <t>Feuerwehrhaus aus Holz</t>
+        </is>
+      </c>
+      <c r="F285" s="16" t="inlineStr">
+        <is>
+          <t>Spiel-Feuerwehrhaus aus Holz mit rot lackierten Wänden, dunklem Dach, aufklappbarem Tor und Zwischenboden. Aufdruck: FIRE STATION. Farbe stark abgegriffen.</t>
+        </is>
+      </c>
+      <c r="G285" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H285" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I285" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J285" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K285" s="17" t="n"/>
+      <c r="L285" s="18">
+        <f>J285-IF(K285="",0,K285)</f>
+        <v/>
+      </c>
+      <c r="M285" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N285" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O285" s="19" t="n"/>
+      <c r="P285" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q285" s="19" t="n"/>
+      <c r="R285" s="20" t="n"/>
+      <c r="S285" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T285" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U285" s="21">
+        <f>L285*S285</f>
+        <v/>
+      </c>
+      <c r="V285" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W285" s="15" t="inlineStr">
+        <is>
+          <t>F-331</t>
+        </is>
+      </c>
+      <c r="X285" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y285" s="19" t="n"/>
+      <c r="Z285" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA285" s="19" t="n"/>
+      <c r="AB285" s="19" t="n"/>
+      <c r="AC285" s="19" t="n"/>
+      <c r="AD285" s="19" t="n"/>
+      <c r="AE285" s="20" t="n"/>
+      <c r="AF285" s="21">
+        <f>IF(K285="","",K285*AE285)</f>
+        <v/>
+      </c>
+      <c r="AG285" s="19" t="n"/>
+      <c r="AH285" s="19" t="n"/>
+      <c r="AI285" s="19" t="n"/>
+      <c r="AJ285" s="19" t="n"/>
+      <c r="AK285" s="19" t="n"/>
+      <c r="AL285" s="19" t="n"/>
+      <c r="AM285" s="16" t="inlineStr">
+        <is>
+          <t>1 Haus. Die Fahrzeuge darin gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN285" s="22" t="n"/>
+    </row>
+    <row r="286" ht="30" customHeight="1">
+      <c r="A286" s="15" t="inlineStr">
+        <is>
+          <t>BA06-11</t>
+        </is>
+      </c>
+      <c r="B286" s="15" t="n"/>
+      <c r="C286" s="15" t="n"/>
+      <c r="D286" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E286" s="15" t="inlineStr">
+        <is>
+          <t>Sitzschaukel Kunststoff mit Seilen</t>
+        </is>
+      </c>
+      <c r="F286" s="16" t="inlineStr">
+        <is>
+          <t>Babyschaukel aus Kunststoff: Sitzschale in Violett mit limettengrünem Sicherheitsbügel, Aufhängung über weiße Seile.</t>
+        </is>
+      </c>
+      <c r="G286" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H286" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I286" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J286" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K286" s="17" t="n"/>
+      <c r="L286" s="18">
+        <f>J286-IF(K286="",0,K286)</f>
+        <v/>
+      </c>
+      <c r="M286" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N286" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O286" s="19" t="n"/>
+      <c r="P286" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q286" s="19" t="n"/>
+      <c r="R286" s="20" t="n"/>
+      <c r="S286" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T286" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U286" s="21">
+        <f>L286*S286</f>
+        <v/>
+      </c>
+      <c r="V286" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W286" s="15" t="inlineStr">
+        <is>
+          <t>F-332</t>
+        </is>
+      </c>
+      <c r="X286" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y286" s="19" t="n"/>
+      <c r="Z286" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA286" s="19" t="n"/>
+      <c r="AB286" s="19" t="n"/>
+      <c r="AC286" s="19" t="n"/>
+      <c r="AD286" s="19" t="n"/>
+      <c r="AE286" s="20" t="n"/>
+      <c r="AF286" s="21">
+        <f>IF(K286="","",K286*AE286)</f>
+        <v/>
+      </c>
+      <c r="AG286" s="19" t="n"/>
+      <c r="AH286" s="19" t="n"/>
+      <c r="AI286" s="19" t="n"/>
+      <c r="AJ286" s="19" t="n"/>
+      <c r="AK286" s="19" t="n"/>
+      <c r="AL286" s="19" t="n"/>
+      <c r="AM286" s="16" t="inlineStr">
+        <is>
+          <t>1 Schaukel.</t>
+        </is>
+      </c>
+      <c r="AN286" s="22" t="n"/>
+    </row>
+    <row r="287" ht="30" customHeight="1">
+      <c r="A287" s="15" t="inlineStr">
+        <is>
+          <t>BA06-12</t>
+        </is>
+      </c>
+      <c r="B287" s="15" t="n"/>
+      <c r="C287" s="15" t="n"/>
+      <c r="D287" s="15" t="inlineStr">
+        <is>
+          <t>BA06</t>
+        </is>
+      </c>
+      <c r="E287" s="15" t="inlineStr">
+        <is>
+          <t>Spieltunnel grün</t>
+        </is>
+      </c>
+      <c r="F287" s="16" t="inlineStr">
+        <is>
+          <t>Spieltunnel aus grünem Stoff mit roten Ringen, etwa 180 cm lang und 45 cm Durchmesser, zusammenfaltbar, mit Originalkarton.</t>
+        </is>
+      </c>
+      <c r="G287" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H287" s="15" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="I287" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J287" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K287" s="17" t="n"/>
+      <c r="L287" s="18">
+        <f>J287-IF(K287="",0,K287)</f>
+        <v/>
+      </c>
+      <c r="M287" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N287" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O287" s="19" t="n"/>
+      <c r="P287" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q287" s="19" t="n"/>
+      <c r="R287" s="20" t="n"/>
+      <c r="S287" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T287" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U287" s="21">
+        <f>L287*S287</f>
+        <v/>
+      </c>
+      <c r="V287" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W287" s="15" t="n"/>
+      <c r="X287" s="19" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="Y287" s="19" t="n"/>
+      <c r="Z287" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA287" s="19" t="n"/>
+      <c r="AB287" s="19" t="n"/>
+      <c r="AC287" s="19" t="n"/>
+      <c r="AD287" s="19" t="n"/>
+      <c r="AE287" s="20" t="n"/>
+      <c r="AF287" s="21">
+        <f>IF(K287="","",K287*AE287)</f>
+        <v/>
+      </c>
+      <c r="AG287" s="19" t="n"/>
+      <c r="AH287" s="19" t="n"/>
+      <c r="AI287" s="19" t="n"/>
+      <c r="AJ287" s="19" t="n"/>
+      <c r="AK287" s="19" t="n"/>
+      <c r="AL287" s="19" t="n"/>
+      <c r="AM287" s="16" t="inlineStr">
+        <is>
+          <t>1 Tunnel.</t>
+        </is>
+      </c>
+      <c r="AN287" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: Foto fehlt. Das Bild des Kartons kam nur als Chatbild an, nicht als Datei. Besser waere ohnehin ein Foto des aufgebauten Tunnels.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN276"/>
+  <autoFilter ref="A2:AN287"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -34735,7 +36072,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z276">
+  <conditionalFormatting sqref="Z3:Z287">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -34746,12 +36083,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I276">
+  <conditionalFormatting sqref="I3:I287">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P276">
+  <conditionalFormatting sqref="P3:P287">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -34804,7 +36141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -34842,7 +36179,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$276)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$287)</f>
         <v/>
       </c>
     </row>
@@ -34853,7 +36190,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$276,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$287,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -34864,7 +36201,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$276,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$287,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -34875,7 +36212,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$276,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$287,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -34886,7 +36223,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$276,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$287,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -34897,7 +36234,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$276)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$287)</f>
         <v/>
       </c>
     </row>
@@ -34908,7 +36245,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$276)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -34926,7 +36263,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$276)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$287)</f>
         <v/>
       </c>
     </row>
@@ -34937,7 +36274,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$276,Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$287,Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
     </row>
@@ -34970,7 +36307,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$276="bezahlt")*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$287="bezahlt")*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
     </row>
@@ -34999,7 +36336,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$276,"*verkauft",Artikelstamm!$AI$3:$AI$276,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$287,"*verkauft",Artikelstamm!$AI$3:$AI$287,"")</f>
         <v/>
       </c>
     </row>
@@ -35010,7 +36347,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$276,"*verkauft",Artikelstamm!$AJ$3:$AJ$276,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$287,"*verkauft",Artikelstamm!$AJ$3:$AJ$287,"offen")</f>
         <v/>
       </c>
     </row>
@@ -35021,7 +36358,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$276,"reserviert",Artikelstamm!$AL$3:$AL$276,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$287,"reserviert",Artikelstamm!$AL$3:$AL$287,"")</f>
         <v/>
       </c>
     </row>
@@ -35032,7 +36369,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$276,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$287,"")</f>
         <v/>
       </c>
     </row>
@@ -35043,7 +36380,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$276,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$287,"")</f>
         <v/>
       </c>
     </row>
@@ -35083,15 +36420,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$276,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$287,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$276=$A30)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$287=$A30)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$276,$A30,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$287,$A30,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35102,15 +36439,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$276,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$287,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$276=$A31)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$287=$A31)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$276,$A31,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$287,$A31,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35121,15 +36458,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$276,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$287,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$276=$A32)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$287=$A32)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$276,$A32,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$287,$A32,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35188,15 +36525,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A37)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A37)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A37,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A37,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35207,15 +36544,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A38)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A38)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A38,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A38,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35226,15 +36563,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A39)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A39)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A39,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A39,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35245,15 +36582,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A40)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A40)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A40,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A40,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35264,15 +36601,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A41)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A41)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A41,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A41,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35283,15 +36620,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A42)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A42)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A42,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A42,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35302,15 +36639,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A43)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A43)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A43,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A43,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35321,15 +36658,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A44)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A44)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A44,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A44,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35340,15 +36677,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A45)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A45)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A45,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A45,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35359,15 +36696,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A46)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A46)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A46,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A46,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35378,15 +36715,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A47)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A47)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A47,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A47,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35397,15 +36734,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A48)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A48)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A48,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A48,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35416,15 +36753,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A49)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A49)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A49,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A49,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35435,15 +36772,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$276,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$276=$A50)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A50)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$276,$A50,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A50,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35502,15 +36839,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A55)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A55)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A55,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A55,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35521,15 +36858,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A56)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A56)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A56,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A56,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35540,15 +36877,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A57)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A57)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A57,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A57,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35559,15 +36896,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A58)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A58)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A58,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A58,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35578,15 +36915,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A59)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A59)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A59,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A59,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35597,15 +36934,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A60)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A60)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A60,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A60,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35616,15 +36953,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A61)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A61)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A61,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A61,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35635,15 +36972,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A62)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A62)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A62,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A62,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35654,15 +36991,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A63)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A63)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A63,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A63,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35673,15 +37010,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A64)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A64)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A64,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A64,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35692,15 +37029,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A65)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A65)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A65,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A65,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35711,15 +37048,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A66)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A66)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A66,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A66,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35730,15 +37067,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A67)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A67)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A67,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A67,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35749,15 +37086,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A68)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A68)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A68,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A68,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
@@ -35768,372 +37105,391 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A69)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A69)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A69,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A69,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="26" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A70)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A70)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A70,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A70,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="26" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A71)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A71)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A71,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A71,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A72)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A72)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A72,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A72,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum 4</t>
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A73)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A73)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A73,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A73,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="26" t="inlineStr">
         <is>
-          <t>Speisesaal</t>
+          <t>Schlafraum 5</t>
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A74)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A74)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A74,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A74,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="26" t="inlineStr">
         <is>
-          <t>Terrasse</t>
+          <t>Speisesaal</t>
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A75)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A75)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A75,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A75,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="26" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Terrasse</t>
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A76)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A76)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A76,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A76,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="26" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Treppenraum 1</t>
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A77)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A77)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A77,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A77,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A78)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A78)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A78,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A78,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A79)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A79)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
       <c r="D79" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A79,Artikelstamm!$U$3:$U$276)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A79,Artikelstamm!$U$3:$U$287)</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B80" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A80)</f>
+        <v/>
+      </c>
+      <c r="C80" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A80)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <v/>
+      </c>
+      <c r="D80" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A80,Artikelstamm!$U$3:$U$287)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$276,$A80)</f>
-        <v/>
-      </c>
-      <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$276=$A80)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
-        <v/>
-      </c>
-      <c r="D80" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$276,$A80,Artikelstamm!$U$3:$U$276)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="28" t="inlineStr">
+      <c r="B81" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A81)</f>
+        <v/>
+      </c>
+      <c r="C81" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A81)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <v/>
+      </c>
+      <c r="D81" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A81,Artikelstamm!$U$3:$U$287)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B81" s="35">
-        <f>SUM(B55:B80)</f>
-        <v/>
-      </c>
-      <c r="C81" s="36">
-        <f>SUM(C55:C80)</f>
-        <v/>
-      </c>
-      <c r="D81" s="36">
-        <f>SUM(D55:D80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="25" t="inlineStr">
+      <c r="B82" s="35">
+        <f>SUM(B55:B81)</f>
+        <v/>
+      </c>
+      <c r="C82" s="36">
+        <f>SUM(C55:C81)</f>
+        <v/>
+      </c>
+      <c r="D82" s="36">
+        <f>SUM(D55:D81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="32" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B84" s="32" t="inlineStr">
+      <c r="B85" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C84" s="32" t="inlineStr">
+      <c r="C85" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B85" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A85)</f>
-        <v/>
-      </c>
-      <c r="C85" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A85)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
-        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A86)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A86)</f>
         <v/>
       </c>
       <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A86)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A86)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A87)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A87)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A88)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A88)</f>
         <v/>
       </c>
       <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A88)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A88)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B89" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A89)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A89)</f>
         <v/>
       </c>
       <c r="C89" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A89)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A89)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B90" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A90)</f>
+        <v/>
+      </c>
+      <c r="C90" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A90)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B90" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$276,$A90)</f>
-        <v/>
-      </c>
-      <c r="C90" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$276=$A90)*Artikelstamm!$K$3:$K$276*Artikelstamm!$AE$3:$AE$276)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="28" t="inlineStr">
+      <c r="B91" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A91)</f>
+        <v/>
+      </c>
+      <c r="C91" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A91)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B91" s="35">
-        <f>SUM(B85:B90)</f>
-        <v/>
-      </c>
-      <c r="C91" s="36">
-        <f>SUM(C85:C90)</f>
+      <c r="B92" s="35">
+        <f>SUM(B86:B91)</f>
+        <v/>
+      </c>
+      <c r="C92" s="36">
+        <f>SUM(C86:C91)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -24588,7 +24588,7 @@
       </c>
       <c r="AN192" s="22" t="inlineStr">
         <is>
-          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA06-13. Zusammenfassung aus dem Rautenmuster geschlossen, bitte bestaetigen.</t>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA06-13.</t>
         </is>
       </c>
     </row>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="F284" s="16" t="inlineStr">
         <is>
-          <t>Rutschfahrzeug aus Massivholz in Lastwagenform mit offener Ladefläche, Holzlenkrad und roten Rädern.</t>
+          <t>Rutschfahrzeug aus Massivholz in Lastwagenform: offene Ladefläche mit Bordwänden, gepolsterter Sitz vor dem Führerhaus, Holzlenkrad und vier Gummiräder mit roten Felgen.</t>
         </is>
       </c>
       <c r="G284" s="15" t="inlineStr">
@@ -35666,10 +35666,14 @@
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="W284" s="15" t="n"/>
+      <c r="W284" s="15" t="inlineStr">
+        <is>
+          <t>F-335</t>
+        </is>
+      </c>
       <c r="X284" s="19" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="Y284" s="19" t="n"/>
@@ -35698,11 +35702,7 @@
           <t>1 Fahrzeug.</t>
         </is>
       </c>
-      <c r="AN284" s="22" t="inlineStr">
-        <is>
-          <t>OFFEN: Foto fehlt. Das Bild kam nur als Chatbild an, nicht als Datei. Bitte als Dateianhang nachreichen.</t>
-        </is>
-      </c>
+      <c r="AN284" s="22" t="n"/>
     </row>
     <row r="285" ht="30" customHeight="1">
       <c r="A285" s="15" t="inlineStr">
@@ -35957,12 +35957,12 @@
       </c>
       <c r="E287" s="15" t="inlineStr">
         <is>
-          <t>Spieltunnel grün</t>
+          <t>Spieltunnel grün, 180 cm</t>
         </is>
       </c>
       <c r="F287" s="16" t="inlineStr">
         <is>
-          <t>Spieltunnel aus grünem Stoff mit roten Ringen, etwa 180 cm lang und 45 cm Durchmesser, zusammenfaltbar, mit Originalkarton.</t>
+          <t>Spieltunnel aus grünem Stoff mit roten Ringen, etwa 180 cm lang bei 45 cm Durchmesser. Faltbar, mit Originalkarton.</t>
         </is>
       </c>
       <c r="G287" s="15" t="inlineStr">
@@ -36023,10 +36023,14 @@
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="W287" s="15" t="n"/>
+      <c r="W287" s="15" t="inlineStr">
+        <is>
+          <t>F-336</t>
+        </is>
+      </c>
       <c r="X287" s="19" t="inlineStr">
         <is>
-          <t>nein</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="Y287" s="19" t="n"/>
@@ -36052,14 +36056,10 @@
       <c r="AL287" s="19" t="n"/>
       <c r="AM287" s="16" t="inlineStr">
         <is>
-          <t>1 Tunnel.</t>
-        </is>
-      </c>
-      <c r="AN287" s="22" t="inlineStr">
-        <is>
-          <t>OFFEN: Foto fehlt. Das Bild des Kartons kam nur als Chatbild an, nicht als Datei. Besser waere ohnehin ein Foto des aufgebauten Tunnels.</t>
-        </is>
-      </c>
+          <t>1 Tunnel. Das Foto zeigt den Originalkarton mit der Abbildung; der Tunnel selbst ist zusammengefaltet darin.</t>
+        </is>
+      </c>
+      <c r="AN287" s="22" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:AN287"/>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$292</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN287"/>
+  <dimension ref="A1:AN292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -33414,7 +33414,11 @@
         </is>
       </c>
       <c r="B266" s="15" t="n"/>
-      <c r="C266" s="15" t="n"/>
+      <c r="C266" s="15" t="inlineStr">
+        <is>
+          <t>BA07-04</t>
+        </is>
+      </c>
       <c r="D266" s="15" t="inlineStr">
         <is>
           <t>BA04</t>
@@ -33446,7 +33450,7 @@
         </is>
       </c>
       <c r="J266" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K266" s="17" t="n"/>
       <c r="L266" s="18">
@@ -33521,10 +33525,14 @@
       <c r="AL266" s="19" t="n"/>
       <c r="AM266" s="16" t="inlineStr">
         <is>
-          <t>1 Tisch. Baugleich in Kupfer gibt es zwei Stück unter NU02-07.</t>
-        </is>
-      </c>
-      <c r="AN266" s="22" t="n"/>
+          <t>2 Tische: einer im Gruppenraum 4 (BA04-07) und einer im Klassenzimmer (dort mit BA07-04 beschriftet). Der Inhalt gehört nicht dazu. Baugleich in Kupfer gibt es zwei Stück unter NU02-07.</t>
+        </is>
+      </c>
+      <c r="AN266" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA07-04.</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="30" customHeight="1">
       <c r="A267" s="15" t="inlineStr">
@@ -36061,8 +36069,607 @@
       </c>
       <c r="AN287" s="22" t="n"/>
     </row>
+    <row r="288" ht="30" customHeight="1">
+      <c r="A288" s="15" t="inlineStr">
+        <is>
+          <t>BA07-01</t>
+        </is>
+      </c>
+      <c r="B288" s="15" t="n"/>
+      <c r="C288" s="15" t="n"/>
+      <c r="D288" s="15" t="inlineStr">
+        <is>
+          <t>BA07</t>
+        </is>
+      </c>
+      <c r="E288" s="15" t="inlineStr">
+        <is>
+          <t>Kissen in Wolkenform, hellblau</t>
+        </is>
+      </c>
+      <c r="F288" s="16" t="inlineStr">
+        <is>
+          <t>Dekokissen in Wolkenform aus hellblauem Samtstoff, mit aufgestickten Augen, Lächeln und rosa Wangen.</t>
+        </is>
+      </c>
+      <c r="G288" s="15" t="inlineStr">
+        <is>
+          <t>Textilien</t>
+        </is>
+      </c>
+      <c r="H288" s="15" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="I288" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J288" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K288" s="17" t="n"/>
+      <c r="L288" s="18">
+        <f>J288-IF(K288="",0,K288)</f>
+        <v/>
+      </c>
+      <c r="M288" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N288" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O288" s="19" t="n"/>
+      <c r="P288" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q288" s="19" t="n"/>
+      <c r="R288" s="20" t="n"/>
+      <c r="S288" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T288" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U288" s="21">
+        <f>L288*S288</f>
+        <v/>
+      </c>
+      <c r="V288" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W288" s="15" t="inlineStr">
+        <is>
+          <t>F-337</t>
+        </is>
+      </c>
+      <c r="X288" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y288" s="19" t="n"/>
+      <c r="Z288" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA288" s="19" t="n"/>
+      <c r="AB288" s="19" t="n"/>
+      <c r="AC288" s="19" t="n"/>
+      <c r="AD288" s="19" t="n"/>
+      <c r="AE288" s="20" t="n"/>
+      <c r="AF288" s="21">
+        <f>IF(K288="","",K288*AE288)</f>
+        <v/>
+      </c>
+      <c r="AG288" s="19" t="n"/>
+      <c r="AH288" s="19" t="n"/>
+      <c r="AI288" s="19" t="n"/>
+      <c r="AJ288" s="19" t="n"/>
+      <c r="AK288" s="19" t="n"/>
+      <c r="AL288" s="19" t="n"/>
+      <c r="AM288" s="16" t="inlineStr">
+        <is>
+          <t>2 Kissen, beide abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN288" s="22" t="n"/>
+    </row>
+    <row r="289" ht="30" customHeight="1">
+      <c r="A289" s="15" t="inlineStr">
+        <is>
+          <t>BA07-02</t>
+        </is>
+      </c>
+      <c r="B289" s="15" t="n"/>
+      <c r="C289" s="15" t="n"/>
+      <c r="D289" s="15" t="inlineStr">
+        <is>
+          <t>BA07</t>
+        </is>
+      </c>
+      <c r="E289" s="15" t="inlineStr">
+        <is>
+          <t>Wandleuchte rund mit Holzrand</t>
+        </is>
+      </c>
+      <c r="F289" s="16" t="inlineStr">
+        <is>
+          <t>Runde Wandleuchte: Rahmen aus gebogenem Schichtholz mit satinierter Scheibe, flache Bauform, Zuleitung sichtbar verlegt. Zwei verschiedene Durchmesser.</t>
+        </is>
+      </c>
+      <c r="G289" s="15" t="inlineStr">
+        <is>
+          <t>Leuchten</t>
+        </is>
+      </c>
+      <c r="H289" s="15" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="I289" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J289" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K289" s="17" t="n"/>
+      <c r="L289" s="18">
+        <f>J289-IF(K289="",0,K289)</f>
+        <v/>
+      </c>
+      <c r="M289" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N289" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O289" s="19" t="n"/>
+      <c r="P289" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q289" s="19" t="n"/>
+      <c r="R289" s="20" t="n"/>
+      <c r="S289" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T289" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U289" s="21">
+        <f>L289*S289</f>
+        <v/>
+      </c>
+      <c r="V289" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W289" s="15" t="inlineStr">
+        <is>
+          <t>F-338</t>
+        </is>
+      </c>
+      <c r="X289" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y289" s="19" t="n"/>
+      <c r="Z289" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA289" s="19" t="n"/>
+      <c r="AB289" s="19" t="n"/>
+      <c r="AC289" s="19" t="n"/>
+      <c r="AD289" s="19" t="n"/>
+      <c r="AE289" s="20" t="n"/>
+      <c r="AF289" s="21">
+        <f>IF(K289="","",K289*AE289)</f>
+        <v/>
+      </c>
+      <c r="AG289" s="19" t="n"/>
+      <c r="AH289" s="19" t="n"/>
+      <c r="AI289" s="19" t="n"/>
+      <c r="AJ289" s="19" t="n"/>
+      <c r="AK289" s="19" t="n"/>
+      <c r="AL289" s="19" t="n"/>
+      <c r="AM289" s="16" t="inlineStr">
+        <is>
+          <t>2 Leuchten in unterschiedlicher Größe, beide abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN289" s="22" t="n"/>
+    </row>
+    <row r="290" ht="30" customHeight="1">
+      <c r="A290" s="15" t="inlineStr">
+        <is>
+          <t>BA07-03</t>
+        </is>
+      </c>
+      <c r="B290" s="15" t="n"/>
+      <c r="C290" s="15" t="n"/>
+      <c r="D290" s="15" t="inlineStr">
+        <is>
+          <t>BA07</t>
+        </is>
+      </c>
+      <c r="E290" s="15" t="inlineStr">
+        <is>
+          <t>Standregal grau mit Wolkenaufsatz</t>
+        </is>
+      </c>
+      <c r="F290" s="16" t="inlineStr">
+        <is>
+          <t>Schmales Standregal in Grau mit drei Ablagen und vorderen Haltelleisten, oben ein ausgesägter Wolkenaufsatz, auf schrägen Holzbeinen. Als Bücherregal genutzt.</t>
+        </is>
+      </c>
+      <c r="G290" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H290" s="15" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="I290" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J290" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K290" s="17" t="n"/>
+      <c r="L290" s="18">
+        <f>J290-IF(K290="",0,K290)</f>
+        <v/>
+      </c>
+      <c r="M290" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N290" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O290" s="19" t="n"/>
+      <c r="P290" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q290" s="19" t="n"/>
+      <c r="R290" s="20" t="n"/>
+      <c r="S290" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T290" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U290" s="21">
+        <f>L290*S290</f>
+        <v/>
+      </c>
+      <c r="V290" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W290" s="15" t="inlineStr">
+        <is>
+          <t>F-339</t>
+        </is>
+      </c>
+      <c r="X290" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y290" s="19" t="n"/>
+      <c r="Z290" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA290" s="19" t="n"/>
+      <c r="AB290" s="19" t="n"/>
+      <c r="AC290" s="19" t="n"/>
+      <c r="AD290" s="19" t="n"/>
+      <c r="AE290" s="20" t="n"/>
+      <c r="AF290" s="21">
+        <f>IF(K290="","",K290*AE290)</f>
+        <v/>
+      </c>
+      <c r="AG290" s="19" t="n"/>
+      <c r="AH290" s="19" t="n"/>
+      <c r="AI290" s="19" t="n"/>
+      <c r="AJ290" s="19" t="n"/>
+      <c r="AK290" s="19" t="n"/>
+      <c r="AL290" s="19" t="n"/>
+      <c r="AM290" s="16" t="inlineStr">
+        <is>
+          <t>1 Regal.</t>
+        </is>
+      </c>
+      <c r="AN290" s="22" t="n"/>
+    </row>
+    <row r="291" ht="30" customHeight="1">
+      <c r="A291" s="15" t="inlineStr">
+        <is>
+          <t>BA07-05</t>
+        </is>
+      </c>
+      <c r="B291" s="15" t="n"/>
+      <c r="C291" s="15" t="n"/>
+      <c r="D291" s="15" t="inlineStr">
+        <is>
+          <t>BA07</t>
+        </is>
+      </c>
+      <c r="E291" s="15" t="inlineStr">
+        <is>
+          <t>Tisch weiß, lang, auf schwarzen Beinen</t>
+        </is>
+      </c>
+      <c r="F291" s="16" t="inlineStr">
+        <is>
+          <t>Langer Tisch mit weißer Platte auf vier schwarzen Rundbeinen mit Gleitern. Als Arbeits- und Ablagefläche genutzt.</t>
+        </is>
+      </c>
+      <c r="G291" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H291" s="15" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="I291" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J291" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K291" s="17" t="n"/>
+      <c r="L291" s="18">
+        <f>J291-IF(K291="",0,K291)</f>
+        <v/>
+      </c>
+      <c r="M291" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N291" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O291" s="19" t="n"/>
+      <c r="P291" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q291" s="19" t="n"/>
+      <c r="R291" s="20" t="n"/>
+      <c r="S291" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="T291" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U291" s="21">
+        <f>L291*S291</f>
+        <v/>
+      </c>
+      <c r="V291" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W291" s="15" t="inlineStr">
+        <is>
+          <t>F-341</t>
+        </is>
+      </c>
+      <c r="X291" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y291" s="19" t="n"/>
+      <c r="Z291" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA291" s="19" t="n"/>
+      <c r="AB291" s="19" t="n"/>
+      <c r="AC291" s="19" t="n"/>
+      <c r="AD291" s="19" t="n"/>
+      <c r="AE291" s="20" t="n"/>
+      <c r="AF291" s="21">
+        <f>IF(K291="","",K291*AE291)</f>
+        <v/>
+      </c>
+      <c r="AG291" s="19" t="n"/>
+      <c r="AH291" s="19" t="n"/>
+      <c r="AI291" s="19" t="n"/>
+      <c r="AJ291" s="19" t="n"/>
+      <c r="AK291" s="19" t="n"/>
+      <c r="AL291" s="19" t="n"/>
+      <c r="AM291" s="16" t="inlineStr">
+        <is>
+          <t>1 Tisch.</t>
+        </is>
+      </c>
+      <c r="AN291" s="22" t="inlineStr">
+        <is>
+          <t>Stueckzahl auf dem Erfassungsblatt nicht eingetragen, als 1 angenommen - bitte bestaetigen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="30" customHeight="1">
+      <c r="A292" s="15" t="inlineStr">
+        <is>
+          <t>BA07-06</t>
+        </is>
+      </c>
+      <c r="B292" s="15" t="n"/>
+      <c r="C292" s="15" t="n"/>
+      <c r="D292" s="15" t="inlineStr">
+        <is>
+          <t>BA07</t>
+        </is>
+      </c>
+      <c r="E292" s="15" t="inlineStr">
+        <is>
+          <t>Regal creme, 16 Fächer, auf Metallbeinen</t>
+        </is>
+      </c>
+      <c r="F292" s="16" t="inlineStr">
+        <is>
+          <t>Großes Regal in Creme mit sechzehn Fächern in vier Reihen, auf schräg gestellten schwarzen Metallbeinen.</t>
+        </is>
+      </c>
+      <c r="G292" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H292" s="15" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="I292" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J292" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K292" s="17" t="n"/>
+      <c r="L292" s="18">
+        <f>J292-IF(K292="",0,K292)</f>
+        <v/>
+      </c>
+      <c r="M292" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N292" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O292" s="19" t="n"/>
+      <c r="P292" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q292" s="19" t="n"/>
+      <c r="R292" s="20" t="n"/>
+      <c r="S292" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T292" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U292" s="21">
+        <f>L292*S292</f>
+        <v/>
+      </c>
+      <c r="V292" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W292" s="15" t="inlineStr">
+        <is>
+          <t>F-342</t>
+        </is>
+      </c>
+      <c r="X292" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y292" s="19" t="n"/>
+      <c r="Z292" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA292" s="19" t="n"/>
+      <c r="AB292" s="19" t="n"/>
+      <c r="AC292" s="19" t="n"/>
+      <c r="AD292" s="19" t="n"/>
+      <c r="AE292" s="20" t="n"/>
+      <c r="AF292" s="21">
+        <f>IF(K292="","",K292*AE292)</f>
+        <v/>
+      </c>
+      <c r="AG292" s="19" t="n"/>
+      <c r="AH292" s="19" t="n"/>
+      <c r="AI292" s="19" t="n"/>
+      <c r="AJ292" s="19" t="n"/>
+      <c r="AK292" s="19" t="n"/>
+      <c r="AL292" s="19" t="n"/>
+      <c r="AM292" s="16" t="inlineStr">
+        <is>
+          <t>1 Regal. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN292" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN287"/>
+  <autoFilter ref="A2:AN292"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -36072,7 +36679,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z287">
+  <conditionalFormatting sqref="Z3:Z292">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -36083,12 +36690,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I287">
+  <conditionalFormatting sqref="I3:I292">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P287">
+  <conditionalFormatting sqref="P3:P292">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -36141,7 +36748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -36179,7 +36786,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$287)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$292)</f>
         <v/>
       </c>
     </row>
@@ -36190,7 +36797,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$287,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$292,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -36201,7 +36808,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$287,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$292,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -36212,7 +36819,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$287,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$292,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -36223,7 +36830,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$287,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$292,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -36234,7 +36841,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$287)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$292)</f>
         <v/>
       </c>
     </row>
@@ -36245,7 +36852,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$287)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36263,7 +36870,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$287)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$292)</f>
         <v/>
       </c>
     </row>
@@ -36274,7 +36881,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$287,Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$292,Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
     </row>
@@ -36307,7 +36914,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$287="bezahlt")*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$292="bezahlt")*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
     </row>
@@ -36336,7 +36943,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$287,"*verkauft",Artikelstamm!$AI$3:$AI$287,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$292,"*verkauft",Artikelstamm!$AI$3:$AI$292,"")</f>
         <v/>
       </c>
     </row>
@@ -36347,7 +36954,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$287,"*verkauft",Artikelstamm!$AJ$3:$AJ$287,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$292,"*verkauft",Artikelstamm!$AJ$3:$AJ$292,"offen")</f>
         <v/>
       </c>
     </row>
@@ -36358,7 +36965,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$287,"reserviert",Artikelstamm!$AL$3:$AL$287,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$292,"reserviert",Artikelstamm!$AL$3:$AL$292,"")</f>
         <v/>
       </c>
     </row>
@@ -36369,7 +36976,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$287,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$292,"")</f>
         <v/>
       </c>
     </row>
@@ -36380,7 +36987,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$287,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$292,"")</f>
         <v/>
       </c>
     </row>
@@ -36420,15 +37027,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$287,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$292,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$287=$A30)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$292=$A30)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$287,$A30,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$292,$A30,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36439,15 +37046,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$287,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$292,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$287=$A31)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$292=$A31)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$287,$A31,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$292,$A31,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36458,15 +37065,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$287,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$292,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$287=$A32)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$292=$A32)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$287,$A32,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$292,$A32,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36525,15 +37132,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A37)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A37)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A37,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A37,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36544,15 +37151,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A38)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A38)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A38,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A38,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36563,15 +37170,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A39)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A39)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A39,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A39,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36582,15 +37189,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A40)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A40)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A40,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A40,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36601,15 +37208,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A41)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A41)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A41,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A41,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36620,15 +37227,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A42)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A42)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A42,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A42,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36639,15 +37246,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A43)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A43)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A43,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A43,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36658,15 +37265,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A44)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A44)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A44,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A44,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36677,15 +37284,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A45)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A45)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A45,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A45,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36696,15 +37303,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A46)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A46)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A46,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A46,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36715,15 +37322,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A47)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A47)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A47,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A47,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36734,15 +37341,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A48)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A48)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A48,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A48,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36753,15 +37360,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A49)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A49)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A49,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A49,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36772,15 +37379,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$287,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$287=$A50)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A50)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$287,$A50,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A50,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36839,15 +37446,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A55)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A55)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A55,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A55,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36858,15 +37465,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A56)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A56)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A56,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A56,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36877,15 +37484,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A57)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A57)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A57,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A57,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36896,15 +37503,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A58)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A58)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A58,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A58,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36915,15 +37522,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A59)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A59)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A59,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A59,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36934,15 +37541,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A60)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A60)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A60,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A60,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36953,15 +37560,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A61)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A61)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A61,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A61,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36972,15 +37579,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A62)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A62)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A62,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A62,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -36991,15 +37598,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A63)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A63)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A63,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A63,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -37010,15 +37617,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A64)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A64)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A64,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A64,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -37029,15 +37636,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A65)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A65)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A65,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A65,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -37048,15 +37655,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A66)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A66)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A66,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A66,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -37067,15 +37674,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A67)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A67)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A67,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A67,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
@@ -37086,410 +37693,429 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A68)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A68)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A68,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A68,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="26" t="inlineStr">
         <is>
-          <t>Küche</t>
+          <t>Klassenzimmer</t>
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A69)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A69)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A69,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A69,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="26" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Küche</t>
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A70)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A70)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A70,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A70,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="26" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A71)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A71)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A71,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A71,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="26" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A72)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A72)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A72,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A72,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A73)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A73)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A73,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A73,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum 4</t>
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A74)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A74)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A74,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A74,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="26" t="inlineStr">
         <is>
-          <t>Speisesaal</t>
+          <t>Schlafraum 5</t>
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A75)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A75)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A75,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A75,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="26" t="inlineStr">
         <is>
-          <t>Terrasse</t>
+          <t>Speisesaal</t>
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A76)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A76)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A76,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A76,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="26" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Terrasse</t>
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A77)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A77)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A77,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A77,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Treppenraum 1</t>
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A78)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A78)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A78,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A78,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A79)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A79)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D79" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A79,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A79,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A80)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A80)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
       <c r="D80" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A80,Artikelstamm!$U$3:$U$287)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A80,Artikelstamm!$U$3:$U$292)</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B81" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A81)</f>
+        <v/>
+      </c>
+      <c r="C81" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A81)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <v/>
+      </c>
+      <c r="D81" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A81,Artikelstamm!$U$3:$U$292)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$287,$A81)</f>
-        <v/>
-      </c>
-      <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$287=$A81)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
-        <v/>
-      </c>
-      <c r="D81" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$287,$A81,Artikelstamm!$U$3:$U$287)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="28" t="inlineStr">
+      <c r="B82" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A82)</f>
+        <v/>
+      </c>
+      <c r="C82" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A82)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <v/>
+      </c>
+      <c r="D82" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A82,Artikelstamm!$U$3:$U$292)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B82" s="35">
-        <f>SUM(B55:B81)</f>
-        <v/>
-      </c>
-      <c r="C82" s="36">
-        <f>SUM(C55:C81)</f>
-        <v/>
-      </c>
-      <c r="D82" s="36">
-        <f>SUM(D55:D81)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="25" t="inlineStr">
+      <c r="B83" s="35">
+        <f>SUM(B55:B82)</f>
+        <v/>
+      </c>
+      <c r="C83" s="36">
+        <f>SUM(C55:C82)</f>
+        <v/>
+      </c>
+      <c r="D83" s="36">
+        <f>SUM(D55:D82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="32" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B85" s="32" t="inlineStr">
+      <c r="B86" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C85" s="32" t="inlineStr">
+      <c r="C86" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B86" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A86)</f>
-        <v/>
-      </c>
-      <c r="C86" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A86)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
-        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A87)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A87)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A88)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A88)</f>
         <v/>
       </c>
       <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A88)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A88)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B89" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A89)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A89)</f>
         <v/>
       </c>
       <c r="C89" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A89)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A89)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B90" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A90)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A90)</f>
         <v/>
       </c>
       <c r="C90" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A90)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A90)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B91" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A91)</f>
+        <v/>
+      </c>
+      <c r="C91" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A91)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B91" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$287,$A91)</f>
-        <v/>
-      </c>
-      <c r="C91" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$287=$A91)*Artikelstamm!$K$3:$K$287*Artikelstamm!$AE$3:$AE$287)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="28" t="inlineStr">
+      <c r="B92" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A92)</f>
+        <v/>
+      </c>
+      <c r="C92" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A92)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B92" s="35">
-        <f>SUM(B86:B91)</f>
-        <v/>
-      </c>
-      <c r="C92" s="36">
-        <f>SUM(C86:C91)</f>
+      <c r="B93" s="35">
+        <f>SUM(B87:B92)</f>
+        <v/>
+      </c>
+      <c r="C93" s="36">
+        <f>SUM(C87:C92)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$292</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$300</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN292"/>
+  <dimension ref="A1:AN300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -36668,8 +36668,972 @@
       </c>
       <c r="AN292" s="22" t="n"/>
     </row>
+    <row r="293" ht="30" customHeight="1">
+      <c r="A293" s="15" t="inlineStr">
+        <is>
+          <t>BA08-05</t>
+        </is>
+      </c>
+      <c r="B293" s="15" t="n"/>
+      <c r="C293" s="15" t="n"/>
+      <c r="D293" s="15" t="inlineStr">
+        <is>
+          <t>BA08</t>
+        </is>
+      </c>
+      <c r="E293" s="15" t="inlineStr">
+        <is>
+          <t>Acrylbild schwarz-weiß, Kreise mit Punkten</t>
+        </is>
+      </c>
+      <c r="F293" s="16" t="inlineStr">
+        <is>
+          <t>Acryl auf Leinwand, großes Quadrat: mit breitem Pinsel gezogene Kreise, darin je mehrere gemalte Punkte – die Anmutung von Würfeln. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="G293" s="15" t="inlineStr">
+        <is>
+          <t>Kunst</t>
+        </is>
+      </c>
+      <c r="H293" s="15" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="I293" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J293" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K293" s="17" t="n"/>
+      <c r="L293" s="18">
+        <f>J293-IF(K293="",0,K293)</f>
+        <v/>
+      </c>
+      <c r="M293" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N293" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O293" s="19" t="n"/>
+      <c r="P293" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q293" s="19" t="n"/>
+      <c r="R293" s="20" t="n"/>
+      <c r="S293" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="T293" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U293" s="21">
+        <f>L293*S293</f>
+        <v/>
+      </c>
+      <c r="V293" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W293" s="15" t="inlineStr">
+        <is>
+          <t>F-344</t>
+        </is>
+      </c>
+      <c r="X293" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y293" s="19" t="n"/>
+      <c r="Z293" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA293" s="19" t="n"/>
+      <c r="AB293" s="19" t="n"/>
+      <c r="AC293" s="19" t="n"/>
+      <c r="AD293" s="19" t="n"/>
+      <c r="AE293" s="20" t="n"/>
+      <c r="AF293" s="21">
+        <f>IF(K293="","",K293*AE293)</f>
+        <v/>
+      </c>
+      <c r="AG293" s="19" t="n"/>
+      <c r="AH293" s="19" t="n"/>
+      <c r="AI293" s="19" t="n"/>
+      <c r="AJ293" s="19" t="n"/>
+      <c r="AK293" s="19" t="n"/>
+      <c r="AL293" s="19" t="n"/>
+      <c r="AM293" s="16" t="inlineStr">
+        <is>
+          <t>1 Bild.</t>
+        </is>
+      </c>
+      <c r="AN293" s="22" t="n"/>
+    </row>
+    <row r="294" ht="30" customHeight="1">
+      <c r="A294" s="15" t="inlineStr">
+        <is>
+          <t>BA08-06</t>
+        </is>
+      </c>
+      <c r="B294" s="15" t="n"/>
+      <c r="C294" s="15" t="n"/>
+      <c r="D294" s="15" t="inlineStr">
+        <is>
+          <t>BA08</t>
+        </is>
+      </c>
+      <c r="E294" s="15" t="inlineStr">
+        <is>
+          <t>VS Schalenstuhl grau, Vierfußgestell</t>
+        </is>
+      </c>
+      <c r="F294" s="16" t="inlineStr">
+        <is>
+          <t>Schalenstuhl von VS (Vereinigte Spezialmöbelfabriken): graue Kunststoffschale mit Rautenstruktur und Griffloch in der Lehne, auf grauem Vierfußgestell aus Rohr. Farbspritzer aus dem Atelierbetrieb auf Sitz und Lehne.</t>
+        </is>
+      </c>
+      <c r="G294" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H294" s="15" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="I294" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J294" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="K294" s="17" t="n"/>
+      <c r="L294" s="18">
+        <f>J294-IF(K294="",0,K294)</f>
+        <v/>
+      </c>
+      <c r="M294" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N294" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O294" s="19" t="n"/>
+      <c r="P294" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q294" s="19" t="n"/>
+      <c r="R294" s="20" t="n"/>
+      <c r="S294" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T294" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U294" s="21">
+        <f>L294*S294</f>
+        <v/>
+      </c>
+      <c r="V294" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W294" s="15" t="inlineStr">
+        <is>
+          <t>F-345</t>
+        </is>
+      </c>
+      <c r="X294" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y294" s="19" t="n"/>
+      <c r="Z294" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA294" s="19" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="AB294" s="19" t="n"/>
+      <c r="AC294" s="19" t="n"/>
+      <c r="AD294" s="19" t="n"/>
+      <c r="AE294" s="20" t="n"/>
+      <c r="AF294" s="21">
+        <f>IF(K294="","",K294*AE294)</f>
+        <v/>
+      </c>
+      <c r="AG294" s="19" t="n"/>
+      <c r="AH294" s="19" t="n"/>
+      <c r="AI294" s="19" t="n"/>
+      <c r="AJ294" s="19" t="n"/>
+      <c r="AK294" s="19" t="n"/>
+      <c r="AL294" s="19" t="n"/>
+      <c r="AM294" s="16" t="inlineStr">
+        <is>
+          <t>9 Stühle – abgebildet ist einer davon. Das Logo ist auf Foto F-346 zu sehen. Ein anderes VS-Modell auf Kufengestell steht unter NU02-04.</t>
+        </is>
+      </c>
+      <c r="AN294" s="22" t="n"/>
+    </row>
+    <row r="295" ht="30" customHeight="1">
+      <c r="A295" s="15" t="inlineStr">
+        <is>
+          <t>BA08-07</t>
+        </is>
+      </c>
+      <c r="B295" s="15" t="n"/>
+      <c r="C295" s="15" t="n"/>
+      <c r="D295" s="15" t="inlineStr">
+        <is>
+          <t>BA08</t>
+        </is>
+      </c>
+      <c r="E295" s="15" t="inlineStr">
+        <is>
+          <t>Konvolut Feinkrepp-Papier</t>
+        </is>
+      </c>
+      <c r="F295" s="16" t="inlineStr">
+        <is>
+          <t>Rollen Feinkrepp von Marpa Jansen, je 50 × 250 cm, in Blau, Grün, Gelb, Rot, Orange und Braun. Teils angebrochen, dazu ein Beutel mit zugeschnittenen Schnipseln.</t>
+        </is>
+      </c>
+      <c r="G295" s="15" t="inlineStr">
+        <is>
+          <t>Verbrauchsmaterial</t>
+        </is>
+      </c>
+      <c r="H295" s="15" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="I295" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J295" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K295" s="17" t="n"/>
+      <c r="L295" s="18">
+        <f>J295-IF(K295="",0,K295)</f>
+        <v/>
+      </c>
+      <c r="M295" s="15" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="N295" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O295" s="19" t="n"/>
+      <c r="P295" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q295" s="19" t="n"/>
+      <c r="R295" s="20" t="n"/>
+      <c r="S295" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T295" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U295" s="21">
+        <f>L295*S295</f>
+        <v/>
+      </c>
+      <c r="V295" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W295" s="15" t="inlineStr">
+        <is>
+          <t>F-347</t>
+        </is>
+      </c>
+      <c r="X295" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y295" s="19" t="n"/>
+      <c r="Z295" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA295" s="19" t="inlineStr">
+        <is>
+          <t>Marpa Jansen</t>
+        </is>
+      </c>
+      <c r="AB295" s="19" t="n"/>
+      <c r="AC295" s="19" t="n"/>
+      <c r="AD295" s="19" t="n"/>
+      <c r="AE295" s="20" t="n"/>
+      <c r="AF295" s="21">
+        <f>IF(K295="","",K295*AE295)</f>
+        <v/>
+      </c>
+      <c r="AG295" s="19" t="n"/>
+      <c r="AH295" s="19" t="n"/>
+      <c r="AI295" s="19" t="n"/>
+      <c r="AJ295" s="19" t="n"/>
+      <c r="AK295" s="19" t="n"/>
+      <c r="AL295" s="19" t="n"/>
+      <c r="AM295" s="16" t="inlineStr">
+        <is>
+          <t>1 Konvolut. Der Schubladeninhalt ist auf Foto F-348 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN295" s="22" t="n"/>
+    </row>
+    <row r="296" ht="30" customHeight="1">
+      <c r="A296" s="15" t="inlineStr">
+        <is>
+          <t>BA08-08</t>
+        </is>
+      </c>
+      <c r="B296" s="15" t="n"/>
+      <c r="C296" s="15" t="n"/>
+      <c r="D296" s="15" t="inlineStr">
+        <is>
+          <t>BA08</t>
+        </is>
+      </c>
+      <c r="E296" s="15" t="inlineStr">
+        <is>
+          <t>Deko-Pilze auf Holzfuß</t>
+        </is>
+      </c>
+      <c r="F296" s="16" t="inlineStr">
+        <is>
+          <t>Dekopilze mit gedrechseltem Fuß aus Massivholz: zwei mit gehämmerter Metallkappe in Silberoptik, einer mit Kappe in Betonoptik.</t>
+        </is>
+      </c>
+      <c r="G296" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H296" s="15" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="I296" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J296" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K296" s="17" t="n"/>
+      <c r="L296" s="18">
+        <f>J296-IF(K296="",0,K296)</f>
+        <v/>
+      </c>
+      <c r="M296" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N296" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O296" s="19" t="n"/>
+      <c r="P296" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q296" s="19" t="n"/>
+      <c r="R296" s="20" t="n"/>
+      <c r="S296" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="T296" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U296" s="21">
+        <f>L296*S296</f>
+        <v/>
+      </c>
+      <c r="V296" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W296" s="15" t="inlineStr">
+        <is>
+          <t>F-349</t>
+        </is>
+      </c>
+      <c r="X296" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y296" s="19" t="n"/>
+      <c r="Z296" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA296" s="19" t="n"/>
+      <c r="AB296" s="19" t="n"/>
+      <c r="AC296" s="19" t="n"/>
+      <c r="AD296" s="19" t="n"/>
+      <c r="AE296" s="20" t="n"/>
+      <c r="AF296" s="21">
+        <f>IF(K296="","",K296*AE296)</f>
+        <v/>
+      </c>
+      <c r="AG296" s="19" t="n"/>
+      <c r="AH296" s="19" t="n"/>
+      <c r="AI296" s="19" t="n"/>
+      <c r="AJ296" s="19" t="n"/>
+      <c r="AK296" s="19" t="n"/>
+      <c r="AL296" s="19" t="n"/>
+      <c r="AM296" s="16" t="inlineStr">
+        <is>
+          <t>3 Pilze, alle abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN296" s="22" t="n"/>
+    </row>
+    <row r="297" ht="30" customHeight="1">
+      <c r="A297" s="15" t="inlineStr">
+        <is>
+          <t>BA08-09</t>
+        </is>
+      </c>
+      <c r="B297" s="15" t="n"/>
+      <c r="C297" s="15" t="n"/>
+      <c r="D297" s="15" t="inlineStr">
+        <is>
+          <t>BA08</t>
+        </is>
+      </c>
+      <c r="E297" s="15" t="inlineStr">
+        <is>
+          <t>Bastelscheren im Betzold-Holzblock</t>
+        </is>
+      </c>
+      <c r="F297" s="16" t="inlineStr">
+        <is>
+          <t>Kinder-Bastelscheren mit Kunststoffgriffen in gemischten Farben, dazu ein Holzblock mit Steckbohrungen von Betzold als Ablage.</t>
+        </is>
+      </c>
+      <c r="G297" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H297" s="15" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="I297" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J297" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="K297" s="17" t="n"/>
+      <c r="L297" s="18">
+        <f>J297-IF(K297="",0,K297)</f>
+        <v/>
+      </c>
+      <c r="M297" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N297" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O297" s="19" t="n"/>
+      <c r="P297" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q297" s="19" t="n"/>
+      <c r="R297" s="20" t="n"/>
+      <c r="S297" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T297" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U297" s="21">
+        <f>L297*S297</f>
+        <v/>
+      </c>
+      <c r="V297" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W297" s="15" t="inlineStr">
+        <is>
+          <t>F-350</t>
+        </is>
+      </c>
+      <c r="X297" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y297" s="19" t="n"/>
+      <c r="Z297" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA297" s="19" t="inlineStr">
+        <is>
+          <t>Betzold</t>
+        </is>
+      </c>
+      <c r="AB297" s="19" t="n"/>
+      <c r="AC297" s="19" t="n"/>
+      <c r="AD297" s="19" t="n"/>
+      <c r="AE297" s="20" t="n"/>
+      <c r="AF297" s="21">
+        <f>IF(K297="","",K297*AE297)</f>
+        <v/>
+      </c>
+      <c r="AG297" s="19" t="n"/>
+      <c r="AH297" s="19" t="n"/>
+      <c r="AI297" s="19" t="n"/>
+      <c r="AJ297" s="19" t="n"/>
+      <c r="AK297" s="19" t="n"/>
+      <c r="AL297" s="19" t="n"/>
+      <c r="AM297" s="16" t="inlineStr">
+        <is>
+          <t>15 Scheren, der Holzblock gehört dazu.</t>
+        </is>
+      </c>
+      <c r="AN297" s="22" t="n"/>
+    </row>
+    <row r="298" ht="30" customHeight="1">
+      <c r="A298" s="15" t="inlineStr">
+        <is>
+          <t>BA08-10</t>
+        </is>
+      </c>
+      <c r="B298" s="15" t="n"/>
+      <c r="C298" s="15" t="n"/>
+      <c r="D298" s="15" t="inlineStr">
+        <is>
+          <t>BA08</t>
+        </is>
+      </c>
+      <c r="E298" s="15" t="inlineStr">
+        <is>
+          <t>Kunstpflanze Gras im weißen Topf</t>
+        </is>
+      </c>
+      <c r="F298" s="16" t="inlineStr">
+        <is>
+          <t>Künstliches Ziergras mit gedrehten Halmen in einem weißen Übertopf aus Metall mit durchbrochenem Spitzenrand.</t>
+        </is>
+      </c>
+      <c r="G298" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H298" s="15" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="I298" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J298" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K298" s="17" t="n"/>
+      <c r="L298" s="18">
+        <f>J298-IF(K298="",0,K298)</f>
+        <v/>
+      </c>
+      <c r="M298" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N298" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O298" s="19" t="n"/>
+      <c r="P298" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q298" s="19" t="n"/>
+      <c r="R298" s="20" t="n"/>
+      <c r="S298" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T298" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U298" s="21">
+        <f>L298*S298</f>
+        <v/>
+      </c>
+      <c r="V298" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W298" s="15" t="inlineStr">
+        <is>
+          <t>F-351</t>
+        </is>
+      </c>
+      <c r="X298" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y298" s="19" t="n"/>
+      <c r="Z298" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA298" s="19" t="n"/>
+      <c r="AB298" s="19" t="n"/>
+      <c r="AC298" s="19" t="n"/>
+      <c r="AD298" s="19" t="n"/>
+      <c r="AE298" s="20" t="n"/>
+      <c r="AF298" s="21">
+        <f>IF(K298="","",K298*AE298)</f>
+        <v/>
+      </c>
+      <c r="AG298" s="19" t="n"/>
+      <c r="AH298" s="19" t="n"/>
+      <c r="AI298" s="19" t="n"/>
+      <c r="AJ298" s="19" t="n"/>
+      <c r="AK298" s="19" t="n"/>
+      <c r="AL298" s="19" t="n"/>
+      <c r="AM298" s="16" t="inlineStr">
+        <is>
+          <t>2 Stück, beide abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN298" s="22" t="n"/>
+    </row>
+    <row r="299" ht="30" customHeight="1">
+      <c r="A299" s="15" t="inlineStr">
+        <is>
+          <t>BA08-11</t>
+        </is>
+      </c>
+      <c r="B299" s="15" t="n"/>
+      <c r="C299" s="15" t="n"/>
+      <c r="D299" s="15" t="inlineStr">
+        <is>
+          <t>BA08</t>
+        </is>
+      </c>
+      <c r="E299" s="15" t="inlineStr">
+        <is>
+          <t>Bilderrahmen mit Zeichenwerkzeug</t>
+        </is>
+      </c>
+      <c r="F299" s="16" t="inlineStr">
+        <is>
+          <t>Zwei schwarze Rahmen hinter Glas, gepunkteter Hintergrund: einer mit Bleistift, Lineal und gefaltetem Papier, einer mit sechs Pinseln in verschiedenen Breiten. Passend für ein Atelier oder Arbeitszimmer.</t>
+        </is>
+      </c>
+      <c r="G299" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H299" s="15" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="I299" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J299" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K299" s="17" t="n"/>
+      <c r="L299" s="18">
+        <f>J299-IF(K299="",0,K299)</f>
+        <v/>
+      </c>
+      <c r="M299" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N299" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O299" s="19" t="n"/>
+      <c r="P299" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q299" s="19" t="n"/>
+      <c r="R299" s="20" t="n"/>
+      <c r="S299" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T299" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U299" s="21">
+        <f>L299*S299</f>
+        <v/>
+      </c>
+      <c r="V299" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W299" s="15" t="inlineStr">
+        <is>
+          <t>F-352</t>
+        </is>
+      </c>
+      <c r="X299" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y299" s="19" t="n"/>
+      <c r="Z299" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA299" s="19" t="n"/>
+      <c r="AB299" s="19" t="n"/>
+      <c r="AC299" s="19" t="n"/>
+      <c r="AD299" s="19" t="n"/>
+      <c r="AE299" s="20" t="n"/>
+      <c r="AF299" s="21">
+        <f>IF(K299="","",K299*AE299)</f>
+        <v/>
+      </c>
+      <c r="AG299" s="19" t="n"/>
+      <c r="AH299" s="19" t="n"/>
+      <c r="AI299" s="19" t="n"/>
+      <c r="AJ299" s="19" t="n"/>
+      <c r="AK299" s="19" t="n"/>
+      <c r="AL299" s="19" t="n"/>
+      <c r="AM299" s="16" t="inlineStr">
+        <is>
+          <t>2 Bilder, beide abgebildet.</t>
+        </is>
+      </c>
+      <c r="AN299" s="22" t="n"/>
+    </row>
+    <row r="300" ht="30" customHeight="1">
+      <c r="A300" s="15" t="inlineStr">
+        <is>
+          <t>BA08-12</t>
+        </is>
+      </c>
+      <c r="B300" s="15" t="n"/>
+      <c r="C300" s="15" t="n"/>
+      <c r="D300" s="15" t="inlineStr">
+        <is>
+          <t>BA08</t>
+        </is>
+      </c>
+      <c r="E300" s="15" t="inlineStr">
+        <is>
+          <t>Wandregalbrett weiß</t>
+        </is>
+      </c>
+      <c r="F300" s="16" t="inlineStr">
+        <is>
+          <t>Schmales weißes Wandregalbrett mit vorderer Kante, zum Anschrauben.</t>
+        </is>
+      </c>
+      <c r="G300" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H300" s="15" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="I300" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J300" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K300" s="17" t="n"/>
+      <c r="L300" s="18">
+        <f>J300-IF(K300="",0,K300)</f>
+        <v/>
+      </c>
+      <c r="M300" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N300" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O300" s="19" t="n"/>
+      <c r="P300" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q300" s="19" t="n"/>
+      <c r="R300" s="20" t="n"/>
+      <c r="S300" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T300" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U300" s="21">
+        <f>L300*S300</f>
+        <v/>
+      </c>
+      <c r="V300" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W300" s="15" t="inlineStr">
+        <is>
+          <t>F-353</t>
+        </is>
+      </c>
+      <c r="X300" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y300" s="19" t="n"/>
+      <c r="Z300" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA300" s="19" t="n"/>
+      <c r="AB300" s="19" t="n"/>
+      <c r="AC300" s="19" t="n"/>
+      <c r="AD300" s="19" t="n"/>
+      <c r="AE300" s="20" t="n"/>
+      <c r="AF300" s="21">
+        <f>IF(K300="","",K300*AE300)</f>
+        <v/>
+      </c>
+      <c r="AG300" s="19" t="n"/>
+      <c r="AH300" s="19" t="n"/>
+      <c r="AI300" s="19" t="n"/>
+      <c r="AJ300" s="19" t="n"/>
+      <c r="AK300" s="19" t="n"/>
+      <c r="AL300" s="19" t="n"/>
+      <c r="AM300" s="16" t="inlineStr">
+        <is>
+          <t>2 Bretter. Die blauen Becher darauf gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN300" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN292"/>
+  <autoFilter ref="A2:AN300"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -36679,7 +37643,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z292">
+  <conditionalFormatting sqref="Z3:Z300">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -36690,12 +37654,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I292">
+  <conditionalFormatting sqref="I3:I300">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P292">
+  <conditionalFormatting sqref="P3:P300">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -36786,7 +37750,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$292)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$300)</f>
         <v/>
       </c>
     </row>
@@ -36797,7 +37761,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$292,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$300,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -36808,7 +37772,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$292,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$300,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -36819,7 +37783,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$292,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$300,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -36830,7 +37794,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$292,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$300,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -36841,7 +37805,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$292)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$300)</f>
         <v/>
       </c>
     </row>
@@ -36852,7 +37816,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$292)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -36870,7 +37834,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$292)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$300)</f>
         <v/>
       </c>
     </row>
@@ -36881,7 +37845,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$292,Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$300,Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
     </row>
@@ -36914,7 +37878,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$292="bezahlt")*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$300="bezahlt")*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
     </row>
@@ -36943,7 +37907,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$292,"*verkauft",Artikelstamm!$AI$3:$AI$292,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$300,"*verkauft",Artikelstamm!$AI$3:$AI$300,"")</f>
         <v/>
       </c>
     </row>
@@ -36954,7 +37918,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$292,"*verkauft",Artikelstamm!$AJ$3:$AJ$292,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$300,"*verkauft",Artikelstamm!$AJ$3:$AJ$300,"offen")</f>
         <v/>
       </c>
     </row>
@@ -36965,7 +37929,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$292,"reserviert",Artikelstamm!$AL$3:$AL$292,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$300,"reserviert",Artikelstamm!$AL$3:$AL$300,"")</f>
         <v/>
       </c>
     </row>
@@ -36976,7 +37940,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$292,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$300,"")</f>
         <v/>
       </c>
     </row>
@@ -36987,7 +37951,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$292,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$300,"")</f>
         <v/>
       </c>
     </row>
@@ -37027,15 +37991,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$292,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$300,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$292=$A30)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$300=$A30)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$292,$A30,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$300,$A30,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37046,15 +38010,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$292,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$300,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$292=$A31)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$300=$A31)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$292,$A31,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$300,$A31,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37065,15 +38029,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$292,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$300,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$292=$A32)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$300=$A32)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$292,$A32,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$300,$A32,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37132,15 +38096,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A37)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A37)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A37,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A37,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37151,15 +38115,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A38)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A38)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A38,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A38,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37170,15 +38134,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A39)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A39)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A39,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A39,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37189,15 +38153,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A40)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A40)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A40,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A40,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37208,15 +38172,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A41)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A41)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A41,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A41,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37227,15 +38191,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A42)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A42)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A42,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A42,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37246,15 +38210,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A43)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A43)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A43,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A43,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37265,15 +38229,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A44)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A44)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A44,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A44,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37284,15 +38248,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A45)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A45)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A45,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A45,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37303,15 +38267,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A46)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A46)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A46,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A46,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37322,15 +38286,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A47)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A47)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A47,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A47,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37341,15 +38305,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A48)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A48)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A48,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A48,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37360,15 +38324,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A49)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A49)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A49,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A49,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37379,15 +38343,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$292,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$292=$A50)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A50)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$292,$A50,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A50,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37446,15 +38410,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A55)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A55)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A55,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A55,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37465,15 +38429,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A56)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A56)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A56,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A56,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37484,15 +38448,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A57)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A57)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A57,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A57,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37503,15 +38467,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A58)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A58)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A58,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A58,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37522,15 +38486,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A59)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A59)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A59,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A59,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37541,15 +38505,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A60)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A60)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A60,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A60,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37560,15 +38524,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A61)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A61)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A61,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A61,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37579,15 +38543,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A62)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A62)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A62,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A62,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37598,15 +38562,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A63)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A63)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A63,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A63,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37617,15 +38581,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A64)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A64)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A64,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A64,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37636,15 +38600,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A65)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A65)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A65,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A65,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37655,15 +38619,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A66)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A66)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A66,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A66,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37674,15 +38638,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A67)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A67)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A67,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A67,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37693,15 +38657,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A68)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A68)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A68,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A68,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37712,15 +38676,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A69)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A69)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A69,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A69,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37731,15 +38695,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A70)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A70)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A70,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A70,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37750,15 +38714,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A71)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A71)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A71,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A71,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37769,15 +38733,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A72)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A72)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A72,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A72,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37788,15 +38752,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A73)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A73)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A73,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A73,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37807,15 +38771,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A74)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A74)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A74,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A74,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37826,15 +38790,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A75)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A75)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A75,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A75,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37845,15 +38809,15 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A76)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A76)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A76,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A76,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37864,15 +38828,15 @@
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A77)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A77)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A77,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A77,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37883,15 +38847,15 @@
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A78)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A78)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A78,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A78,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37902,15 +38866,15 @@
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A79)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A79)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D79" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A79,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A79,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37921,15 +38885,15 @@
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A80)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A80)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D80" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A80,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A80,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37940,15 +38904,15 @@
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A81)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A81)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D81" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A81,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A81,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -37959,15 +38923,15 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$292,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$292=$A82)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A82)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
       <c r="D82" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$292,$A82,Artikelstamm!$U$3:$U$292)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A82,Artikelstamm!$U$3:$U$300)</f>
         <v/>
       </c>
     </row>
@@ -38021,11 +38985,11 @@
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A87)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A87)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
     </row>
@@ -38036,11 +39000,11 @@
         </is>
       </c>
       <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A88)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A88)</f>
         <v/>
       </c>
       <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A88)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A88)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
     </row>
@@ -38051,11 +39015,11 @@
         </is>
       </c>
       <c r="B89" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A89)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A89)</f>
         <v/>
       </c>
       <c r="C89" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A89)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A89)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
     </row>
@@ -38066,11 +39030,11 @@
         </is>
       </c>
       <c r="B90" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A90)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A90)</f>
         <v/>
       </c>
       <c r="C90" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A90)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A90)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
     </row>
@@ -38081,11 +39045,11 @@
         </is>
       </c>
       <c r="B91" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A91)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A91)</f>
         <v/>
       </c>
       <c r="C91" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A91)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A91)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
     </row>
@@ -38096,11 +39060,11 @@
         </is>
       </c>
       <c r="B92" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$292,$A92)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A92)</f>
         <v/>
       </c>
       <c r="C92" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$292=$A92)*Artikelstamm!$K$3:$K$292*Artikelstamm!$AE$3:$AE$292)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A92)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$306</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN300"/>
+  <dimension ref="A1:AN306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23982,7 +23982,7 @@
       <c r="B188" s="15" t="n"/>
       <c r="C188" s="15" t="inlineStr">
         <is>
-          <t>NU05-05, NU07-06, BA04-03</t>
+          <t>NU05-05, NU07-06, BA04-03, BU01-03</t>
         </is>
       </c>
       <c r="D188" s="15" t="inlineStr">
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="J188" s="17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K188" s="17" t="n"/>
       <c r="L188" s="18">
@@ -24095,12 +24095,12 @@
       <c r="AL188" s="19" t="n"/>
       <c r="AM188" s="16" t="inlineStr">
         <is>
-          <t>8 Regale insgesamt: 3 im Schlafraum 5, 1 im Treppenraum 1 (NU05-05), 1 in der Garage (NU07-06) und 3 im Gruppenraum 4 (BA04-03).</t>
+          <t>10 Regale insgesamt: 3 im Schlafraum 5, 1 im Treppenraum 1 (NU05-05), 1 in der Garage (NU07-06), 3 im Gruppenraum 4 (BA04-03) und 2 im Flur 1 des Bestandsgebäudes (BU01-03).</t>
         </is>
       </c>
       <c r="AN188" s="22" t="inlineStr">
         <is>
-          <t>Zusammengefasste Position über vier Räume – Post-it-Nummern: NU05-05, NU07-06, BA04-03.</t>
+          <t>Zusammengefasste Position über fünf Räume – Post-it-Nummern: NU05-05, NU07-06, BA04-03, BU01-03.</t>
         </is>
       </c>
     </row>
@@ -37632,8 +37632,730 @@
       </c>
       <c r="AN300" s="22" t="n"/>
     </row>
+    <row r="301" ht="30" customHeight="1">
+      <c r="A301" s="15" t="inlineStr">
+        <is>
+          <t>BU01-01</t>
+        </is>
+      </c>
+      <c r="B301" s="15" t="n"/>
+      <c r="C301" s="15" t="n"/>
+      <c r="D301" s="15" t="inlineStr">
+        <is>
+          <t>BU01</t>
+        </is>
+      </c>
+      <c r="E301" s="15" t="inlineStr">
+        <is>
+          <t>Hausbett Buche massiv</t>
+        </is>
+      </c>
+      <c r="F301" s="16" t="inlineStr">
+        <is>
+          <t>Kinderbett in Hausform aus massiver Buche, natur geölt, mit Dachgiebel und umlaufendem Rahmen. Einschließlich Matratze.</t>
+        </is>
+      </c>
+      <c r="G301" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H301" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I301" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J301" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K301" s="17" t="n"/>
+      <c r="L301" s="18">
+        <f>J301-IF(K301="",0,K301)</f>
+        <v/>
+      </c>
+      <c r="M301" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N301" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O301" s="19" t="n"/>
+      <c r="P301" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q301" s="19" t="n"/>
+      <c r="R301" s="20" t="n"/>
+      <c r="S301" s="20" t="n">
+        <v>220</v>
+      </c>
+      <c r="T301" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U301" s="21">
+        <f>L301*S301</f>
+        <v/>
+      </c>
+      <c r="V301" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W301" s="15" t="inlineStr">
+        <is>
+          <t>F-356</t>
+        </is>
+      </c>
+      <c r="X301" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y301" s="19" t="n"/>
+      <c r="Z301" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA301" s="19" t="n"/>
+      <c r="AB301" s="19" t="n"/>
+      <c r="AC301" s="19" t="n"/>
+      <c r="AD301" s="19" t="n"/>
+      <c r="AE301" s="20" t="n"/>
+      <c r="AF301" s="21">
+        <f>IF(K301="","",K301*AE301)</f>
+        <v/>
+      </c>
+      <c r="AG301" s="19" t="n"/>
+      <c r="AH301" s="19" t="n"/>
+      <c r="AI301" s="19" t="n"/>
+      <c r="AJ301" s="19" t="n"/>
+      <c r="AK301" s="19" t="n"/>
+      <c r="AL301" s="19" t="n"/>
+      <c r="AM301" s="16" t="inlineStr">
+        <is>
+          <t>1 Bett einschließlich Matratze. Kissen und Bettschlange gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN301" s="22" t="n"/>
+    </row>
+    <row r="302" ht="30" customHeight="1">
+      <c r="A302" s="15" t="inlineStr">
+        <is>
+          <t>BU01-02</t>
+        </is>
+      </c>
+      <c r="B302" s="15" t="n"/>
+      <c r="C302" s="15" t="n"/>
+      <c r="D302" s="15" t="inlineStr">
+        <is>
+          <t>BU01</t>
+        </is>
+      </c>
+      <c r="E302" s="15" t="inlineStr">
+        <is>
+          <t>Spielküche klein mit Mikrowelle</t>
+        </is>
+      </c>
+      <c r="F302" s="16" t="inlineStr">
+        <is>
+          <t>Kleine Spielküche aus Birke-Multiplex mit weißen Fronten: Aufsatz mit Mikrowelle und zwei offenen Fächern, Arbeitsplatte mit Kochfeld, Spülbecken und Wasserhahn, darunter Backofen mit Sichtfenster und ein Schrank.</t>
+        </is>
+      </c>
+      <c r="G302" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H302" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I302" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J302" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K302" s="17" t="n"/>
+      <c r="L302" s="18">
+        <f>J302-IF(K302="",0,K302)</f>
+        <v/>
+      </c>
+      <c r="M302" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N302" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O302" s="19" t="n"/>
+      <c r="P302" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q302" s="19" t="n"/>
+      <c r="R302" s="20" t="n"/>
+      <c r="S302" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T302" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U302" s="21">
+        <f>L302*S302</f>
+        <v/>
+      </c>
+      <c r="V302" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W302" s="15" t="inlineStr">
+        <is>
+          <t>F-355</t>
+        </is>
+      </c>
+      <c r="X302" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y302" s="19" t="n"/>
+      <c r="Z302" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA302" s="19" t="n"/>
+      <c r="AB302" s="19" t="n"/>
+      <c r="AC302" s="19" t="n"/>
+      <c r="AD302" s="19" t="n"/>
+      <c r="AE302" s="20" t="n"/>
+      <c r="AF302" s="21">
+        <f>IF(K302="","",K302*AE302)</f>
+        <v/>
+      </c>
+      <c r="AG302" s="19" t="n"/>
+      <c r="AH302" s="19" t="n"/>
+      <c r="AI302" s="19" t="n"/>
+      <c r="AJ302" s="19" t="n"/>
+      <c r="AK302" s="19" t="n"/>
+      <c r="AL302" s="19" t="n"/>
+      <c r="AM302" s="16" t="inlineStr">
+        <is>
+          <t>1 Küche. Spielgeschirr und Zubehör gehören nicht dazu. Drei größere Spielküchen stehen unter NU03-03, NU07-03 und BA03-02.</t>
+        </is>
+      </c>
+      <c r="AN302" s="22" t="n"/>
+    </row>
+    <row r="303" ht="30" customHeight="1">
+      <c r="A303" s="15" t="inlineStr">
+        <is>
+          <t>BU01-04</t>
+        </is>
+      </c>
+      <c r="B303" s="15" t="n"/>
+      <c r="C303" s="15" t="n"/>
+      <c r="D303" s="15" t="inlineStr">
+        <is>
+          <t>BU01</t>
+        </is>
+      </c>
+      <c r="E303" s="15" t="inlineStr">
+        <is>
+          <t>Gestell Kiefer mit sechs Wannen</t>
+        </is>
+      </c>
+      <c r="F303" s="16" t="inlineStr">
+        <is>
+          <t>Gestell aus Kiefer massiv mit sechs weißen Kunststoffwannen in zwei Reihen, als Spielzeugaufbewahrung genutzt.</t>
+        </is>
+      </c>
+      <c r="G303" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H303" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I303" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J303" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K303" s="17" t="n"/>
+      <c r="L303" s="18">
+        <f>J303-IF(K303="",0,K303)</f>
+        <v/>
+      </c>
+      <c r="M303" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N303" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O303" s="19" t="n"/>
+      <c r="P303" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q303" s="19" t="n"/>
+      <c r="R303" s="20" t="n"/>
+      <c r="S303" s="20" t="n">
+        <v>55</v>
+      </c>
+      <c r="T303" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U303" s="21">
+        <f>L303*S303</f>
+        <v/>
+      </c>
+      <c r="V303" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W303" s="15" t="inlineStr">
+        <is>
+          <t>F-358</t>
+        </is>
+      </c>
+      <c r="X303" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y303" s="19" t="n"/>
+      <c r="Z303" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA303" s="19" t="n"/>
+      <c r="AB303" s="19" t="n"/>
+      <c r="AC303" s="19" t="n"/>
+      <c r="AD303" s="19" t="n"/>
+      <c r="AE303" s="20" t="n"/>
+      <c r="AF303" s="21">
+        <f>IF(K303="","",K303*AE303)</f>
+        <v/>
+      </c>
+      <c r="AG303" s="19" t="n"/>
+      <c r="AH303" s="19" t="n"/>
+      <c r="AI303" s="19" t="n"/>
+      <c r="AJ303" s="19" t="n"/>
+      <c r="AK303" s="19" t="n"/>
+      <c r="AL303" s="19" t="n"/>
+      <c r="AM303" s="16" t="inlineStr">
+        <is>
+          <t>1 Gestell einschließlich der Wannen. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN303" s="22" t="n"/>
+    </row>
+    <row r="304" ht="30" customHeight="1">
+      <c r="A304" s="15" t="inlineStr">
+        <is>
+          <t>BU01-05</t>
+        </is>
+      </c>
+      <c r="B304" s="15" t="n"/>
+      <c r="C304" s="15" t="n"/>
+      <c r="D304" s="15" t="inlineStr">
+        <is>
+          <t>BU01</t>
+        </is>
+      </c>
+      <c r="E304" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Småstad Kindertisch weiß</t>
+        </is>
+      </c>
+      <c r="F304" s="16" t="inlineStr">
+        <is>
+          <t>Niedriger Kindertisch von IKEA in Weiß mit Seitenwangen, Etikett an der Unterseite: Småstad, 804.335.42. Die Platte ist stark verkratzt und mit einer Schutzfolie belegt.</t>
+        </is>
+      </c>
+      <c r="G304" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H304" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I304" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J304" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K304" s="17" t="n"/>
+      <c r="L304" s="18">
+        <f>J304-IF(K304="",0,K304)</f>
+        <v/>
+      </c>
+      <c r="M304" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N304" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O304" s="19" t="n"/>
+      <c r="P304" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q304" s="19" t="n"/>
+      <c r="R304" s="20" t="n"/>
+      <c r="S304" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T304" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U304" s="21">
+        <f>L304*S304</f>
+        <v/>
+      </c>
+      <c r="V304" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W304" s="15" t="inlineStr">
+        <is>
+          <t>F-359</t>
+        </is>
+      </c>
+      <c r="X304" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y304" s="19" t="n"/>
+      <c r="Z304" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA304" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB304" s="19" t="n"/>
+      <c r="AC304" s="19" t="n"/>
+      <c r="AD304" s="19" t="n"/>
+      <c r="AE304" s="20" t="n"/>
+      <c r="AF304" s="21">
+        <f>IF(K304="","",K304*AE304)</f>
+        <v/>
+      </c>
+      <c r="AG304" s="19" t="n"/>
+      <c r="AH304" s="19" t="n"/>
+      <c r="AI304" s="19" t="n"/>
+      <c r="AJ304" s="19" t="n"/>
+      <c r="AK304" s="19" t="n"/>
+      <c r="AL304" s="19" t="n"/>
+      <c r="AM304" s="16" t="inlineStr">
+        <is>
+          <t>2 Tische – abgebildet ist einer davon. Das Etikett ist auf Foto F-360 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN304" s="22" t="n"/>
+    </row>
+    <row r="305" ht="30" customHeight="1">
+      <c r="A305" s="15" t="inlineStr">
+        <is>
+          <t>BU01-06</t>
+        </is>
+      </c>
+      <c r="B305" s="15" t="n"/>
+      <c r="C305" s="15" t="n"/>
+      <c r="D305" s="15" t="inlineStr">
+        <is>
+          <t>BU01</t>
+        </is>
+      </c>
+      <c r="E305" s="15" t="inlineStr">
+        <is>
+          <t>Wanddeko Lama, Steckwand</t>
+        </is>
+      </c>
+      <c r="F305" s="16" t="inlineStr">
+        <is>
+          <t>Wandelement in Lamaform aus weiß lackiertem Holz mit grauen Ohren, Gesicht und Füßen, durchgehend gelocht zum Einstecken von Haken oder Stäben.</t>
+        </is>
+      </c>
+      <c r="G305" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H305" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I305" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J305" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K305" s="17" t="n"/>
+      <c r="L305" s="18">
+        <f>J305-IF(K305="",0,K305)</f>
+        <v/>
+      </c>
+      <c r="M305" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N305" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O305" s="19" t="n"/>
+      <c r="P305" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q305" s="19" t="n"/>
+      <c r="R305" s="20" t="n"/>
+      <c r="S305" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T305" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U305" s="21">
+        <f>L305*S305</f>
+        <v/>
+      </c>
+      <c r="V305" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W305" s="15" t="inlineStr">
+        <is>
+          <t>F-361</t>
+        </is>
+      </c>
+      <c r="X305" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y305" s="19" t="n"/>
+      <c r="Z305" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA305" s="19" t="n"/>
+      <c r="AB305" s="19" t="n"/>
+      <c r="AC305" s="19" t="n"/>
+      <c r="AD305" s="19" t="n"/>
+      <c r="AE305" s="20" t="n"/>
+      <c r="AF305" s="21">
+        <f>IF(K305="","",K305*AE305)</f>
+        <v/>
+      </c>
+      <c r="AG305" s="19" t="n"/>
+      <c r="AH305" s="19" t="n"/>
+      <c r="AI305" s="19" t="n"/>
+      <c r="AJ305" s="19" t="n"/>
+      <c r="AK305" s="19" t="n"/>
+      <c r="AL305" s="19" t="n"/>
+      <c r="AM305" s="16" t="inlineStr">
+        <is>
+          <t>2 Stück – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN305" s="22" t="n"/>
+    </row>
+    <row r="306" ht="30" customHeight="1">
+      <c r="A306" s="15" t="inlineStr">
+        <is>
+          <t>BU01-07</t>
+        </is>
+      </c>
+      <c r="B306" s="15" t="n"/>
+      <c r="C306" s="15" t="n"/>
+      <c r="D306" s="15" t="inlineStr">
+        <is>
+          <t>BU01</t>
+        </is>
+      </c>
+      <c r="E306" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Grua Wandspiegel, schwarzer Rahmen</t>
+        </is>
+      </c>
+      <c r="F306" s="16" t="inlineStr">
+        <is>
+          <t>Wandspiegel mit schmalem schwarzem Rahmen und abgerundeten Ecken. Etikett auf der Rückseite: Grua, IKEA.</t>
+        </is>
+      </c>
+      <c r="G306" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H306" s="15" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="I306" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J306" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K306" s="17" t="n"/>
+      <c r="L306" s="18">
+        <f>J306-IF(K306="",0,K306)</f>
+        <v/>
+      </c>
+      <c r="M306" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N306" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O306" s="19" t="n"/>
+      <c r="P306" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q306" s="19" t="n"/>
+      <c r="R306" s="20" t="n"/>
+      <c r="S306" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T306" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U306" s="21">
+        <f>L306*S306</f>
+        <v/>
+      </c>
+      <c r="V306" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W306" s="15" t="inlineStr">
+        <is>
+          <t>F-362</t>
+        </is>
+      </c>
+      <c r="X306" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y306" s="19" t="n"/>
+      <c r="Z306" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA306" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB306" s="19" t="n"/>
+      <c r="AC306" s="19" t="n"/>
+      <c r="AD306" s="19" t="n"/>
+      <c r="AE306" s="20" t="n"/>
+      <c r="AF306" s="21">
+        <f>IF(K306="","",K306*AE306)</f>
+        <v/>
+      </c>
+      <c r="AG306" s="19" t="n"/>
+      <c r="AH306" s="19" t="n"/>
+      <c r="AI306" s="19" t="n"/>
+      <c r="AJ306" s="19" t="n"/>
+      <c r="AK306" s="19" t="n"/>
+      <c r="AL306" s="19" t="n"/>
+      <c r="AM306" s="16" t="inlineStr">
+        <is>
+          <t>1 Spiegel. Das Etikett ist auf Foto F-363 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN306" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN300"/>
+  <autoFilter ref="A2:AN306"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -37643,7 +38365,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z300">
+  <conditionalFormatting sqref="Z3:Z306">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -37654,12 +38376,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I300">
+  <conditionalFormatting sqref="I3:I306">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P300">
+  <conditionalFormatting sqref="P3:P306">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -37750,7 +38472,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$300)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$306)</f>
         <v/>
       </c>
     </row>
@@ -37761,7 +38483,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$300,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$306,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -37772,7 +38494,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$300,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$306,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -37783,7 +38505,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$300,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$306,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -37794,7 +38516,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$300,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$306,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -37805,7 +38527,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$300)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$306)</f>
         <v/>
       </c>
     </row>
@@ -37816,7 +38538,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$300)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -37834,7 +38556,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$300)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$306)</f>
         <v/>
       </c>
     </row>
@@ -37845,7 +38567,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$300,Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$306,Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
     </row>
@@ -37878,7 +38600,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$300="bezahlt")*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$306="bezahlt")*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
     </row>
@@ -37907,7 +38629,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$300,"*verkauft",Artikelstamm!$AI$3:$AI$300,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$306,"*verkauft",Artikelstamm!$AI$3:$AI$306,"")</f>
         <v/>
       </c>
     </row>
@@ -37918,7 +38640,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$300,"*verkauft",Artikelstamm!$AJ$3:$AJ$300,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$306,"*verkauft",Artikelstamm!$AJ$3:$AJ$306,"offen")</f>
         <v/>
       </c>
     </row>
@@ -37929,7 +38651,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$300,"reserviert",Artikelstamm!$AL$3:$AL$300,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$306,"reserviert",Artikelstamm!$AL$3:$AL$306,"")</f>
         <v/>
       </c>
     </row>
@@ -37940,7 +38662,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$300,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$306,"")</f>
         <v/>
       </c>
     </row>
@@ -37951,7 +38673,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$300,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$306,"")</f>
         <v/>
       </c>
     </row>
@@ -37991,15 +38713,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$300,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$306,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$300=$A30)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$306=$A30)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$300,$A30,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$306,$A30,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38010,15 +38732,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$300,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$306,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$300=$A31)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$306=$A31)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$300,$A31,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$306,$A31,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38029,15 +38751,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$300,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$306,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$300=$A32)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$306=$A32)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$300,$A32,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$306,$A32,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38096,15 +38818,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A37)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A37)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A37,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A37,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38115,15 +38837,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A38)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A38)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A38,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A38,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38134,15 +38856,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A39)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A39)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A39,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A39,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38153,15 +38875,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A40)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A40)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A40,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A40,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38172,15 +38894,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A41)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A41)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A41,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A41,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38191,15 +38913,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A42)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A42)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A42,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A42,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38210,15 +38932,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A43)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A43)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A43,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A43,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38229,15 +38951,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A44)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A44)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A44,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A44,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38248,15 +38970,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A45)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A45)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A45,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A45,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38267,15 +38989,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A46)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A46)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A46,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A46,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38286,15 +39008,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A47)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A47)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A47,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A47,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38305,15 +39027,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A48)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A48)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A48,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A48,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38324,15 +39046,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A49)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A49)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A49,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A49,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38343,15 +39065,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$300,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$300=$A50)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A50)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$300,$A50,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A50,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38410,15 +39132,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A55)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A55)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A55,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A55,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38429,15 +39151,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A56)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A56)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A56,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A56,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38448,15 +39170,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A57)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A57)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A57,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A57,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38467,15 +39189,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A58)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A58)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A58,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A58,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38486,15 +39208,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A59)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A59)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A59,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A59,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38505,15 +39227,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A60)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A60)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A60,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A60,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38524,15 +39246,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A61)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A61)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A61,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A61,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38543,15 +39265,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A62)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A62)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A62,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A62,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38562,15 +39284,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A63)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A63)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A63,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A63,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38581,15 +39303,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A64)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A64)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A64,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A64,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38600,15 +39322,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A65)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A65)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A65,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A65,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38619,15 +39341,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A66)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A66)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A66,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A66,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38638,15 +39360,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A67)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A67)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A67,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A67,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38657,15 +39379,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A68)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A68)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A68,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A68,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38676,15 +39398,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A69)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A69)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A69,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A69,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38695,15 +39417,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A70)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A70)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A70,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A70,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38714,15 +39436,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A71)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A71)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A71,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A71,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38733,15 +39455,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A72)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A72)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A72,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A72,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38752,15 +39474,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A73)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A73)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A73,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A73,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38771,15 +39493,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A74)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A74)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A74,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A74,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38790,15 +39512,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A75)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A75)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A75,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A75,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38809,15 +39531,15 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A76)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A76)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A76,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A76,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38828,15 +39550,15 @@
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A77)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A77)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A77,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A77,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38847,15 +39569,15 @@
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A78)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A78)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A78,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A78,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38866,15 +39588,15 @@
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A79)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A79)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D79" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A79,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A79,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38885,15 +39607,15 @@
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A80)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A80)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D80" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A80,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A80,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38904,15 +39626,15 @@
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A81)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A81)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D81" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A81,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A81,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38923,15 +39645,15 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$300,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$300=$A82)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A82)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
       <c r="D82" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$300,$A82,Artikelstamm!$U$3:$U$300)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A82,Artikelstamm!$U$3:$U$306)</f>
         <v/>
       </c>
     </row>
@@ -38985,11 +39707,11 @@
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A87)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A87)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
     </row>
@@ -39000,11 +39722,11 @@
         </is>
       </c>
       <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A88)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A88)</f>
         <v/>
       </c>
       <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A88)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A88)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
     </row>
@@ -39015,11 +39737,11 @@
         </is>
       </c>
       <c r="B89" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A89)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A89)</f>
         <v/>
       </c>
       <c r="C89" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A89)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A89)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
     </row>
@@ -39030,11 +39752,11 @@
         </is>
       </c>
       <c r="B90" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A90)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A90)</f>
         <v/>
       </c>
       <c r="C90" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A90)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A90)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
     </row>
@@ -39045,11 +39767,11 @@
         </is>
       </c>
       <c r="B91" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A91)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A91)</f>
         <v/>
       </c>
       <c r="C91" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A91)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A91)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
     </row>
@@ -39060,11 +39782,11 @@
         </is>
       </c>
       <c r="B92" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$300,$A92)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A92)</f>
         <v/>
       </c>
       <c r="C92" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$300=$A92)*Artikelstamm!$K$3:$K$300*Artikelstamm!$AE$3:$AE$300)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A92)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$320</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN306"/>
+  <dimension ref="A1:AN320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20090,7 +20090,7 @@
       <c r="B156" s="15" t="n"/>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>NU04-12</t>
+          <t>NU04-12, BU02-04</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
@@ -20124,7 +20124,7 @@
         </is>
       </c>
       <c r="J156" s="17" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K156" s="17" t="n"/>
       <c r="L156" s="18">
@@ -20203,12 +20203,12 @@
       <c r="AL156" s="19" t="n"/>
       <c r="AM156" s="16" t="inlineStr">
         <is>
-          <t>16 Stühle insgesamt: 10 im Gruppenraum 5 und im Nachbarraum NU03, 6 im Schlafraum 5 (dort mit NU04-12 beschriftet).</t>
+          <t>31 Stühle insgesamt: 10 im Gruppenraum 5 und im Nachbarraum NU03, 6 im Schlafraum 5 (dort mit NU04-12 beschriftet) und 15 im Flur 2 im Untergeschoss des Bestandsgebäudes (dort mit BU02-04 beschriftet). Die 15 Stühle aus dem Flur 2 sind stark gebraucht.</t>
         </is>
       </c>
       <c r="AN156" s="22" t="inlineStr">
         <is>
-          <t>Zusammengefasste Position ueber drei Raeume. Post-it-Nummer im Schlafraum 5: NU04-12. In NU03 nicht erneut anlegen.</t>
+          <t>Zusammengefasste Position ueber vier Raeume. Post-it-Nummern: NU04-12, BU02-04. In NU03 nicht erneut anlegen.</t>
         </is>
       </c>
     </row>
@@ -23982,7 +23982,7 @@
       <c r="B188" s="15" t="n"/>
       <c r="C188" s="15" t="inlineStr">
         <is>
-          <t>NU05-05, NU07-06, BA04-03, BU01-03</t>
+          <t>NU05-05, NU07-06, BA04-03, BU01-03, BU02-07</t>
         </is>
       </c>
       <c r="D188" s="15" t="inlineStr">
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="J188" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K188" s="17" t="n"/>
       <c r="L188" s="18">
@@ -24095,12 +24095,12 @@
       <c r="AL188" s="19" t="n"/>
       <c r="AM188" s="16" t="inlineStr">
         <is>
-          <t>10 Regale insgesamt: 3 im Schlafraum 5, 1 im Treppenraum 1 (NU05-05), 1 in der Garage (NU07-06), 3 im Gruppenraum 4 (BA04-03) und 2 im Flur 1 des Bestandsgebäudes (BU01-03).</t>
+          <t>12 Regale insgesamt: 3 im Schlafraum 5, 1 im Treppenraum 1 (NU05-05), 1 in der Garage (NU07-06), 3 im Gruppenraum 4 (BA04-03), 2 im Flur 1 des Bestandsgebäudes (BU01-03) und 2 im Flur 2 im Untergeschoss (BU02-07).</t>
         </is>
       </c>
       <c r="AN188" s="22" t="inlineStr">
         <is>
-          <t>Zusammengefasste Position über fünf Räume – Post-it-Nummern: NU05-05, NU07-06, BA04-03, BU01-03.</t>
+          <t>Zusammengefasste Position über sechs Räume – Post-it-Nummern: NU05-05, NU07-06, BA04-03, BU01-03, BU02-07.</t>
         </is>
       </c>
     </row>
@@ -24111,7 +24111,11 @@
         </is>
       </c>
       <c r="B189" s="15" t="n"/>
-      <c r="C189" s="15" t="n"/>
+      <c r="C189" s="15" t="inlineStr">
+        <is>
+          <t>BU02-11</t>
+        </is>
+      </c>
       <c r="D189" s="15" t="inlineStr">
         <is>
           <t>NU04</t>
@@ -24143,7 +24147,7 @@
         </is>
       </c>
       <c r="J189" s="17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K189" s="17" t="n"/>
       <c r="L189" s="18">
@@ -24218,10 +24222,14 @@
       <c r="AL189" s="19" t="n"/>
       <c r="AM189" s="16" t="inlineStr">
         <is>
-          <t>4 Stühle – abgebildet ist einer davon.</t>
-        </is>
-      </c>
-      <c r="AN189" s="22" t="n"/>
+          <t>10 Stühle insgesamt: 4 im Schlafraum 5 (NU04-10) und 6 im Flur 2 im Untergeschoss des Bestandsgebäudes (BU02-11). Abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AN189" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position über zwei Räume – Post-it-Nummer: BU02-11.</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="15" t="inlineStr">
@@ -37520,7 +37528,11 @@
         </is>
       </c>
       <c r="B300" s="15" t="n"/>
-      <c r="C300" s="15" t="n"/>
+      <c r="C300" s="15" t="inlineStr">
+        <is>
+          <t>BU02-08</t>
+        </is>
+      </c>
       <c r="D300" s="15" t="inlineStr">
         <is>
           <t>BA08</t>
@@ -37552,7 +37564,7 @@
         </is>
       </c>
       <c r="J300" s="17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K300" s="17" t="n"/>
       <c r="L300" s="18">
@@ -37627,10 +37639,14 @@
       <c r="AL300" s="19" t="n"/>
       <c r="AM300" s="16" t="inlineStr">
         <is>
-          <t>2 Bretter. Die blauen Becher darauf gehören nicht dazu.</t>
-        </is>
-      </c>
-      <c r="AN300" s="22" t="n"/>
+          <t>4 Bretter insgesamt: 2 im Atelier (BA08-12) und 2 im Flur 2 im Untergeschoss des Bestandsgebäudes (BU02-08). Die blauen Becher auf dem Foto gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN300" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position über zwei Räume – Post-it-Nummer: BU02-08.</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="30" customHeight="1">
       <c r="A301" s="15" t="inlineStr">
@@ -37865,7 +37881,7 @@
       <c r="AL302" s="19" t="n"/>
       <c r="AM302" s="16" t="inlineStr">
         <is>
-          <t>1 Küche. Spielgeschirr und Zubehör gehören nicht dazu. Drei größere Spielküchen stehen unter NU03-03, NU07-03 und BA03-02.</t>
+          <t>1 Küche. Spielgeschirr und Zubehör gehören nicht dazu. Weitere Spielküchen stehen unter NU03-03, NU07-03, BA03-02 und BU02-05.</t>
         </is>
       </c>
       <c r="AN302" s="22" t="n"/>
@@ -38119,7 +38135,11 @@
         </is>
       </c>
       <c r="B305" s="15" t="n"/>
-      <c r="C305" s="15" t="n"/>
+      <c r="C305" s="15" t="inlineStr">
+        <is>
+          <t>BU02-13</t>
+        </is>
+      </c>
       <c r="D305" s="15" t="inlineStr">
         <is>
           <t>BU01</t>
@@ -38151,7 +38171,7 @@
         </is>
       </c>
       <c r="J305" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K305" s="17" t="n"/>
       <c r="L305" s="18">
@@ -38226,10 +38246,14 @@
       <c r="AL305" s="19" t="n"/>
       <c r="AM305" s="16" t="inlineStr">
         <is>
-          <t>2 Stück – abgebildet ist eines davon.</t>
-        </is>
-      </c>
-      <c r="AN305" s="22" t="n"/>
+          <t>3 Stück insgesamt: 2 im Flur 1 (BU01-06) und 1 im Flur 2 (BU02-13), beide im Untergeschoss des Bestandsgebäudes. Abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN305" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position über zwei Räume – Post-it-Nummer: BU02-13.</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="30" customHeight="1">
       <c r="A306" s="15" t="inlineStr">
@@ -38354,8 +38378,1690 @@
       </c>
       <c r="AN306" s="22" t="n"/>
     </row>
+    <row r="307" ht="30" customHeight="1">
+      <c r="A307" s="15" t="inlineStr">
+        <is>
+          <t>BU02-01</t>
+        </is>
+      </c>
+      <c r="B307" s="15" t="n"/>
+      <c r="C307" s="15" t="n"/>
+      <c r="D307" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E307" s="15" t="inlineStr">
+        <is>
+          <t>Hausbett Holz natur mit Stoffdach</t>
+        </is>
+      </c>
+      <c r="F307" s="16" t="inlineStr">
+        <is>
+          <t>Bodenbett in Hausform aus hellem Massivholz mit vier Pfosten und aufgelegtem Stoffdach in Creme mit schwarzer Zackenkante und aufgesticktem Wolkenmotiv. Einschließlich Matratze.</t>
+        </is>
+      </c>
+      <c r="G307" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H307" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I307" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J307" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K307" s="17" t="n"/>
+      <c r="L307" s="18">
+        <f>J307-IF(K307="",0,K307)</f>
+        <v/>
+      </c>
+      <c r="M307" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N307" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O307" s="19" t="n"/>
+      <c r="P307" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q307" s="19" t="n"/>
+      <c r="R307" s="20" t="n"/>
+      <c r="S307" s="20" t="n">
+        <v>180</v>
+      </c>
+      <c r="T307" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U307" s="21">
+        <f>L307*S307</f>
+        <v/>
+      </c>
+      <c r="V307" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W307" s="15" t="inlineStr">
+        <is>
+          <t>F-365</t>
+        </is>
+      </c>
+      <c r="X307" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y307" s="19" t="n"/>
+      <c r="Z307" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA307" s="19" t="n"/>
+      <c r="AB307" s="19" t="n"/>
+      <c r="AC307" s="19" t="n"/>
+      <c r="AD307" s="19" t="n"/>
+      <c r="AE307" s="20" t="n"/>
+      <c r="AF307" s="21">
+        <f>IF(K307="","",K307*AE307)</f>
+        <v/>
+      </c>
+      <c r="AG307" s="19" t="n"/>
+      <c r="AH307" s="19" t="n"/>
+      <c r="AI307" s="19" t="n"/>
+      <c r="AJ307" s="19" t="n"/>
+      <c r="AK307" s="19" t="n"/>
+      <c r="AL307" s="19" t="n"/>
+      <c r="AM307" s="16" t="inlineStr">
+        <is>
+          <t>1 Bett mit Stoffdach und Matratze. Kissen, Decke und Puppe gehören nicht dazu. Weitere Hausbetten stehen unter BU01-01 und NU07-01.</t>
+        </is>
+      </c>
+      <c r="AN307" s="22" t="n"/>
+    </row>
+    <row r="308" ht="30" customHeight="1">
+      <c r="A308" s="15" t="inlineStr">
+        <is>
+          <t>BU02-02</t>
+        </is>
+      </c>
+      <c r="B308" s="15" t="n"/>
+      <c r="C308" s="15" t="n"/>
+      <c r="D308" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E308" s="15" t="inlineStr">
+        <is>
+          <t>Nachtlicht Marienkäfer, schwarz</t>
+        </is>
+      </c>
+      <c r="F308" s="16" t="inlineStr">
+        <is>
+          <t>Steckdosen-Nachtlicht in Marienkäferform aus schwarzem Kunststoff mit geprägten Punkten und Fühlern.</t>
+        </is>
+      </c>
+      <c r="G308" s="15" t="inlineStr">
+        <is>
+          <t>Leuchten</t>
+        </is>
+      </c>
+      <c r="H308" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I308" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J308" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K308" s="17" t="n"/>
+      <c r="L308" s="18">
+        <f>J308-IF(K308="",0,K308)</f>
+        <v/>
+      </c>
+      <c r="M308" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N308" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O308" s="19" t="n"/>
+      <c r="P308" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q308" s="19" t="n"/>
+      <c r="R308" s="20" t="n"/>
+      <c r="S308" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T308" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U308" s="21">
+        <f>L308*S308</f>
+        <v/>
+      </c>
+      <c r="V308" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W308" s="15" t="inlineStr">
+        <is>
+          <t>F-366</t>
+        </is>
+      </c>
+      <c r="X308" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y308" s="19" t="n"/>
+      <c r="Z308" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA308" s="19" t="n"/>
+      <c r="AB308" s="19" t="n"/>
+      <c r="AC308" s="19" t="n"/>
+      <c r="AD308" s="19" t="n"/>
+      <c r="AE308" s="20" t="n"/>
+      <c r="AF308" s="21">
+        <f>IF(K308="","",K308*AE308)</f>
+        <v/>
+      </c>
+      <c r="AG308" s="19" t="n"/>
+      <c r="AH308" s="19" t="n"/>
+      <c r="AI308" s="19" t="n"/>
+      <c r="AJ308" s="19" t="n"/>
+      <c r="AK308" s="19" t="n"/>
+      <c r="AL308" s="19" t="n"/>
+      <c r="AM308" s="16" t="inlineStr">
+        <is>
+          <t>2 Stück – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN308" s="22" t="n"/>
+    </row>
+    <row r="309" ht="30" customHeight="1">
+      <c r="A309" s="15" t="inlineStr">
+        <is>
+          <t>BU02-03</t>
+        </is>
+      </c>
+      <c r="B309" s="15" t="n"/>
+      <c r="C309" s="15" t="n"/>
+      <c r="D309" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E309" s="15" t="inlineStr">
+        <is>
+          <t>Kindertisch weiß, oval, aus vier Segmenten</t>
+        </is>
+      </c>
+      <c r="F309" s="16" t="inlineStr">
+        <is>
+          <t>Vier Tischsegmente mit weißer Platte und Multiplex-Kante auf verchromten Rundfüßen in Kinderhöhe: zwei halbrunde Endstücke und zwei Mittelstücke. Zusammengestellt ergeben sie einen großen ovalen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
+        </is>
+      </c>
+      <c r="G309" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H309" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I309" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J309" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K309" s="17" t="n"/>
+      <c r="L309" s="18">
+        <f>J309-IF(K309="",0,K309)</f>
+        <v/>
+      </c>
+      <c r="M309" s="15" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N309" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O309" s="19" t="n"/>
+      <c r="P309" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q309" s="19" t="n"/>
+      <c r="R309" s="20" t="n"/>
+      <c r="S309" s="20" t="n">
+        <v>160</v>
+      </c>
+      <c r="T309" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U309" s="21">
+        <f>L309*S309</f>
+        <v/>
+      </c>
+      <c r="V309" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W309" s="15" t="inlineStr">
+        <is>
+          <t>F-367</t>
+        </is>
+      </c>
+      <c r="X309" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y309" s="19" t="n"/>
+      <c r="Z309" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA309" s="19" t="n"/>
+      <c r="AB309" s="19" t="n"/>
+      <c r="AC309" s="19" t="n"/>
+      <c r="AD309" s="19" t="n"/>
+      <c r="AE309" s="20" t="n"/>
+      <c r="AF309" s="21">
+        <f>IF(K309="","",K309*AE309)</f>
+        <v/>
+      </c>
+      <c r="AG309" s="19" t="n"/>
+      <c r="AH309" s="19" t="n"/>
+      <c r="AI309" s="19" t="n"/>
+      <c r="AJ309" s="19" t="n"/>
+      <c r="AK309" s="19" t="n"/>
+      <c r="AL309" s="19" t="n"/>
+      <c r="AM309" s="16" t="inlineStr">
+        <is>
+          <t>1 Tischgruppe aus vier Segmenten. Eine zweite Tischgruppe in Sechseckform steht unter NU02-23.</t>
+        </is>
+      </c>
+      <c r="AN309" s="22" t="n"/>
+    </row>
+    <row r="310" ht="30" customHeight="1">
+      <c r="A310" s="15" t="inlineStr">
+        <is>
+          <t>BU02-05</t>
+        </is>
+      </c>
+      <c r="B310" s="15" t="n"/>
+      <c r="C310" s="15" t="n"/>
+      <c r="D310" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E310" s="15" t="inlineStr">
+        <is>
+          <t>IKEA Duktig Spielküche mit Mikrowelle</t>
+        </is>
+      </c>
+      <c r="F310" s="16" t="inlineStr">
+        <is>
+          <t>Spielküche von IKEA aus Birkenholz mit weißen Fronten: Aufsatz mit Mikrowelle und offenen Fächern, Arbeitsplatte mit Kochfeld, Spülbecken und Wasserhahn, darunter Backofen mit Sichtfenster und ein Schrank.</t>
+        </is>
+      </c>
+      <c r="G310" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H310" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I310" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J310" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K310" s="17" t="n"/>
+      <c r="L310" s="18">
+        <f>J310-IF(K310="",0,K310)</f>
+        <v/>
+      </c>
+      <c r="M310" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N310" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O310" s="19" t="n"/>
+      <c r="P310" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q310" s="19" t="n"/>
+      <c r="R310" s="20" t="n"/>
+      <c r="S310" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T310" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U310" s="21">
+        <f>L310*S310</f>
+        <v/>
+      </c>
+      <c r="V310" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W310" s="15" t="inlineStr">
+        <is>
+          <t>F-369</t>
+        </is>
+      </c>
+      <c r="X310" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y310" s="19" t="n"/>
+      <c r="Z310" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA310" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB310" s="19" t="n"/>
+      <c r="AC310" s="19" t="n"/>
+      <c r="AD310" s="19" t="n"/>
+      <c r="AE310" s="20" t="n"/>
+      <c r="AF310" s="21">
+        <f>IF(K310="","",K310*AE310)</f>
+        <v/>
+      </c>
+      <c r="AG310" s="19" t="n"/>
+      <c r="AH310" s="19" t="n"/>
+      <c r="AI310" s="19" t="n"/>
+      <c r="AJ310" s="19" t="n"/>
+      <c r="AK310" s="19" t="n"/>
+      <c r="AL310" s="19" t="n"/>
+      <c r="AM310" s="16" t="inlineStr">
+        <is>
+          <t>1 Küche. Spielgeschirr, Vorratsgläser und Zubehör gehören nicht dazu. Weitere Spielküchen stehen unter NU03-03, NU07-03, BA03-02 und BU01-02.</t>
+        </is>
+      </c>
+      <c r="AN310" s="22" t="n"/>
+    </row>
+    <row r="311" ht="30" customHeight="1">
+      <c r="A311" s="15" t="inlineStr">
+        <is>
+          <t>BU02-06</t>
+        </is>
+      </c>
+      <c r="B311" s="15" t="n"/>
+      <c r="C311" s="15" t="n"/>
+      <c r="D311" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E311" s="15" t="inlineStr">
+        <is>
+          <t>Kinder-Putzständer, fünfteilig</t>
+        </is>
+      </c>
+      <c r="F311" s="16" t="inlineStr">
+        <is>
+          <t>Ständer aus Holz und Metall in Weiß mit Ablagekasten und aufgehängtem Kinder-Reinigungsgerät: Besen, Schrubber, Kehrblech und Staubwedel.</t>
+        </is>
+      </c>
+      <c r="G311" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H311" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I311" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J311" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K311" s="17" t="n"/>
+      <c r="L311" s="18">
+        <f>J311-IF(K311="",0,K311)</f>
+        <v/>
+      </c>
+      <c r="M311" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N311" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O311" s="19" t="n"/>
+      <c r="P311" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q311" s="19" t="n"/>
+      <c r="R311" s="20" t="n"/>
+      <c r="S311" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T311" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U311" s="21">
+        <f>L311*S311</f>
+        <v/>
+      </c>
+      <c r="V311" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W311" s="15" t="inlineStr">
+        <is>
+          <t>F-370</t>
+        </is>
+      </c>
+      <c r="X311" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y311" s="19" t="n"/>
+      <c r="Z311" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA311" s="19" t="n"/>
+      <c r="AB311" s="19" t="n"/>
+      <c r="AC311" s="19" t="n"/>
+      <c r="AD311" s="19" t="n"/>
+      <c r="AE311" s="20" t="n"/>
+      <c r="AF311" s="21">
+        <f>IF(K311="","",K311*AE311)</f>
+        <v/>
+      </c>
+      <c r="AG311" s="19" t="n"/>
+      <c r="AH311" s="19" t="n"/>
+      <c r="AI311" s="19" t="n"/>
+      <c r="AJ311" s="19" t="n"/>
+      <c r="AK311" s="19" t="n"/>
+      <c r="AL311" s="19" t="n"/>
+      <c r="AM311" s="16" t="inlineStr">
+        <is>
+          <t>1 Ständer mit fünf Teilen.</t>
+        </is>
+      </c>
+      <c r="AN311" s="22" t="n"/>
+    </row>
+    <row r="312" ht="30" customHeight="1">
+      <c r="A312" s="15" t="inlineStr">
+        <is>
+          <t>BU02-09</t>
+        </is>
+      </c>
+      <c r="B312" s="15" t="n"/>
+      <c r="C312" s="15" t="n"/>
+      <c r="D312" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E312" s="15" t="inlineStr">
+        <is>
+          <t>Acrylbild Herz auf Strahlenkranz</t>
+        </is>
+      </c>
+      <c r="F312" s="16" t="inlineStr">
+        <is>
+          <t>Acryl auf Leinwand im Hochformat: breite Pinselstriche in Pink, Magenta und Grau strahlenförmig um ein ausgespartes weißes Herz. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="G312" s="15" t="inlineStr">
+        <is>
+          <t>Kunst</t>
+        </is>
+      </c>
+      <c r="H312" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I312" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J312" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K312" s="17" t="n"/>
+      <c r="L312" s="18">
+        <f>J312-IF(K312="",0,K312)</f>
+        <v/>
+      </c>
+      <c r="M312" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N312" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O312" s="19" t="n"/>
+      <c r="P312" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q312" s="19" t="n"/>
+      <c r="R312" s="20" t="n"/>
+      <c r="S312" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="T312" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U312" s="21">
+        <f>L312*S312</f>
+        <v/>
+      </c>
+      <c r="V312" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W312" s="15" t="inlineStr">
+        <is>
+          <t>F-373</t>
+        </is>
+      </c>
+      <c r="X312" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y312" s="19" t="n"/>
+      <c r="Z312" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA312" s="19" t="n"/>
+      <c r="AB312" s="19" t="n"/>
+      <c r="AC312" s="19" t="n"/>
+      <c r="AD312" s="19" t="n"/>
+      <c r="AE312" s="20" t="n"/>
+      <c r="AF312" s="21">
+        <f>IF(K312="","",K312*AE312)</f>
+        <v/>
+      </c>
+      <c r="AG312" s="19" t="n"/>
+      <c r="AH312" s="19" t="n"/>
+      <c r="AI312" s="19" t="n"/>
+      <c r="AJ312" s="19" t="n"/>
+      <c r="AK312" s="19" t="n"/>
+      <c r="AL312" s="19" t="n"/>
+      <c r="AM312" s="16" t="inlineStr">
+        <is>
+          <t>1 Bild auf Keilrahmen, ungerahmt.</t>
+        </is>
+      </c>
+      <c r="AN312" s="22" t="n"/>
+    </row>
+    <row r="313" ht="30" customHeight="1">
+      <c r="A313" s="15" t="inlineStr">
+        <is>
+          <t>BU02-10</t>
+        </is>
+      </c>
+      <c r="B313" s="15" t="n"/>
+      <c r="C313" s="15" t="n"/>
+      <c r="D313" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E313" s="15" t="inlineStr">
+        <is>
+          <t>Spieltisch Kiefer mit herausnehmbaren Platten</t>
+        </is>
+      </c>
+      <c r="F313" s="16" t="inlineStr">
+        <is>
+          <t>Kindertisch aus Kiefer massiv mit zwei herausnehmbaren weißen Platten. Darunter liegen Wannen, sodass der Tisch als Spiel- und Materialtisch genutzt werden kann. Die Platten sind an den Kanten großflächig abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="G313" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H313" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I313" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J313" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K313" s="17" t="n"/>
+      <c r="L313" s="18">
+        <f>J313-IF(K313="",0,K313)</f>
+        <v/>
+      </c>
+      <c r="M313" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N313" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O313" s="19" t="n"/>
+      <c r="P313" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q313" s="19" t="n"/>
+      <c r="R313" s="20" t="n"/>
+      <c r="S313" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="T313" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U313" s="21">
+        <f>L313*S313</f>
+        <v/>
+      </c>
+      <c r="V313" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W313" s="15" t="inlineStr">
+        <is>
+          <t>F-374</t>
+        </is>
+      </c>
+      <c r="X313" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y313" s="19" t="n"/>
+      <c r="Z313" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA313" s="19" t="n"/>
+      <c r="AB313" s="19" t="n"/>
+      <c r="AC313" s="19" t="n"/>
+      <c r="AD313" s="19" t="n"/>
+      <c r="AE313" s="20" t="n"/>
+      <c r="AF313" s="21">
+        <f>IF(K313="","",K313*AE313)</f>
+        <v/>
+      </c>
+      <c r="AG313" s="19" t="n"/>
+      <c r="AH313" s="19" t="n"/>
+      <c r="AI313" s="19" t="n"/>
+      <c r="AJ313" s="19" t="n"/>
+      <c r="AK313" s="19" t="n"/>
+      <c r="AL313" s="19" t="n"/>
+      <c r="AM313" s="16" t="inlineStr">
+        <is>
+          <t>2 Tische einschließlich der Platten und Wannen – abgebildet ist einer davon. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN313" s="22" t="n"/>
+    </row>
+    <row r="314" ht="30" customHeight="1">
+      <c r="A314" s="15" t="inlineStr">
+        <is>
+          <t>BU02-12</t>
+        </is>
+      </c>
+      <c r="B314" s="15" t="n"/>
+      <c r="C314" s="15" t="n"/>
+      <c r="D314" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E314" s="15" t="inlineStr">
+        <is>
+          <t>Wandregal weiß mit drei Wannen, geschwungen</t>
+        </is>
+      </c>
+      <c r="F314" s="16" t="inlineStr">
+        <is>
+          <t>Weißes Wandelement mit geschwungener Front, drei Fächern und drei eingeschobenen Kunststoffwannen.</t>
+        </is>
+      </c>
+      <c r="G314" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H314" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I314" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J314" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K314" s="17" t="n"/>
+      <c r="L314" s="18">
+        <f>J314-IF(K314="",0,K314)</f>
+        <v/>
+      </c>
+      <c r="M314" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N314" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O314" s="19" t="n"/>
+      <c r="P314" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q314" s="19" t="n"/>
+      <c r="R314" s="20" t="n"/>
+      <c r="S314" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T314" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U314" s="21">
+        <f>L314*S314</f>
+        <v/>
+      </c>
+      <c r="V314" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W314" s="15" t="inlineStr">
+        <is>
+          <t>F-376</t>
+        </is>
+      </c>
+      <c r="X314" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y314" s="19" t="n"/>
+      <c r="Z314" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA314" s="19" t="n"/>
+      <c r="AB314" s="19" t="n"/>
+      <c r="AC314" s="19" t="n"/>
+      <c r="AD314" s="19" t="n"/>
+      <c r="AE314" s="20" t="n"/>
+      <c r="AF314" s="21">
+        <f>IF(K314="","",K314*AE314)</f>
+        <v/>
+      </c>
+      <c r="AG314" s="19" t="n"/>
+      <c r="AH314" s="19" t="n"/>
+      <c r="AI314" s="19" t="n"/>
+      <c r="AJ314" s="19" t="n"/>
+      <c r="AK314" s="19" t="n"/>
+      <c r="AL314" s="19" t="n"/>
+      <c r="AM314" s="16" t="inlineStr">
+        <is>
+          <t>1 Regal einschließlich der Wannen. Gerade Wandregale gleicher Bauart stehen unter NE01-21.</t>
+        </is>
+      </c>
+      <c r="AN314" s="22" t="n"/>
+    </row>
+    <row r="315" ht="30" customHeight="1">
+      <c r="A315" s="15" t="inlineStr">
+        <is>
+          <t>BU02-14</t>
+        </is>
+      </c>
+      <c r="B315" s="15" t="n"/>
+      <c r="C315" s="15" t="n"/>
+      <c r="D315" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E315" s="15" t="inlineStr">
+        <is>
+          <t>Kinderschrank graugrün, zwei Türen</t>
+        </is>
+      </c>
+      <c r="F315" s="16" t="inlineStr">
+        <is>
+          <t>Hoher Kinderschrank von IKEA mit zwei graugrünen Türen und schwarzen Griffmulden, darunter eine Schublade.</t>
+        </is>
+      </c>
+      <c r="G315" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H315" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I315" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J315" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K315" s="17" t="n"/>
+      <c r="L315" s="18">
+        <f>J315-IF(K315="",0,K315)</f>
+        <v/>
+      </c>
+      <c r="M315" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N315" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O315" s="19" t="n"/>
+      <c r="P315" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q315" s="19" t="n"/>
+      <c r="R315" s="20" t="n"/>
+      <c r="S315" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T315" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U315" s="21">
+        <f>L315*S315</f>
+        <v/>
+      </c>
+      <c r="V315" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W315" s="15" t="inlineStr">
+        <is>
+          <t>F-378</t>
+        </is>
+      </c>
+      <c r="X315" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y315" s="19" t="n"/>
+      <c r="Z315" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA315" s="19" t="inlineStr">
+        <is>
+          <t>IKEA</t>
+        </is>
+      </c>
+      <c r="AB315" s="19" t="n"/>
+      <c r="AC315" s="19" t="n"/>
+      <c r="AD315" s="19" t="n"/>
+      <c r="AE315" s="20" t="n"/>
+      <c r="AF315" s="21">
+        <f>IF(K315="","",K315*AE315)</f>
+        <v/>
+      </c>
+      <c r="AG315" s="19" t="n"/>
+      <c r="AH315" s="19" t="n"/>
+      <c r="AI315" s="19" t="n"/>
+      <c r="AJ315" s="19" t="n"/>
+      <c r="AK315" s="19" t="n"/>
+      <c r="AL315" s="19" t="n"/>
+      <c r="AM315" s="16" t="inlineStr">
+        <is>
+          <t>2 Schränke – abgebildet ist einer davon. Baugleiche Schränke mit weißen Türen stehen unter BA02-08.</t>
+        </is>
+      </c>
+      <c r="AN315" s="22" t="n"/>
+    </row>
+    <row r="316" ht="30" customHeight="1">
+      <c r="A316" s="15" t="inlineStr">
+        <is>
+          <t>BU02-15</t>
+        </is>
+      </c>
+      <c r="B316" s="15" t="n"/>
+      <c r="C316" s="15" t="n"/>
+      <c r="D316" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E316" s="15" t="inlineStr">
+        <is>
+          <t>Bodensitzkissen beige, selbststehend</t>
+        </is>
+      </c>
+      <c r="F316" s="16" t="inlineStr">
+        <is>
+          <t>Selbststehendes Bodensitzkissen aus beigem Leinenstoff mit gesteppten Feldern, Rückenlehne und langer Sitzfläche. Die Lehne lässt sich flach ausklappen.</t>
+        </is>
+      </c>
+      <c r="G316" s="15" t="inlineStr">
+        <is>
+          <t>Textilien</t>
+        </is>
+      </c>
+      <c r="H316" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I316" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J316" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K316" s="17" t="n"/>
+      <c r="L316" s="18">
+        <f>J316-IF(K316="",0,K316)</f>
+        <v/>
+      </c>
+      <c r="M316" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N316" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O316" s="19" t="n"/>
+      <c r="P316" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q316" s="19" t="n"/>
+      <c r="R316" s="20" t="n"/>
+      <c r="S316" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T316" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U316" s="21">
+        <f>L316*S316</f>
+        <v/>
+      </c>
+      <c r="V316" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W316" s="15" t="inlineStr">
+        <is>
+          <t>F-379</t>
+        </is>
+      </c>
+      <c r="X316" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y316" s="19" t="n"/>
+      <c r="Z316" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA316" s="19" t="n"/>
+      <c r="AB316" s="19" t="n"/>
+      <c r="AC316" s="19" t="n"/>
+      <c r="AD316" s="19" t="n"/>
+      <c r="AE316" s="20" t="n"/>
+      <c r="AF316" s="21">
+        <f>IF(K316="","",K316*AE316)</f>
+        <v/>
+      </c>
+      <c r="AG316" s="19" t="n"/>
+      <c r="AH316" s="19" t="n"/>
+      <c r="AI316" s="19" t="n"/>
+      <c r="AJ316" s="19" t="n"/>
+      <c r="AK316" s="19" t="n"/>
+      <c r="AL316" s="19" t="n"/>
+      <c r="AM316" s="16" t="inlineStr">
+        <is>
+          <t>2 Stück – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN316" s="22" t="n"/>
+    </row>
+    <row r="317" ht="30" customHeight="1">
+      <c r="A317" s="15" t="inlineStr">
+        <is>
+          <t>BU02-16</t>
+        </is>
+      </c>
+      <c r="B317" s="15" t="n"/>
+      <c r="C317" s="15" t="n"/>
+      <c r="D317" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E317" s="15" t="inlineStr">
+        <is>
+          <t>Servierwagen Metall schwarz, drei Ebenen</t>
+        </is>
+      </c>
+      <c r="F317" s="16" t="inlineStr">
+        <is>
+          <t>Rollwagen aus schwarz lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
+        </is>
+      </c>
+      <c r="G317" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H317" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I317" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J317" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K317" s="17" t="n"/>
+      <c r="L317" s="18">
+        <f>J317-IF(K317="",0,K317)</f>
+        <v/>
+      </c>
+      <c r="M317" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N317" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O317" s="19" t="n"/>
+      <c r="P317" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q317" s="19" t="n"/>
+      <c r="R317" s="20" t="n"/>
+      <c r="S317" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T317" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U317" s="21">
+        <f>L317*S317</f>
+        <v/>
+      </c>
+      <c r="V317" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W317" s="15" t="inlineStr">
+        <is>
+          <t>F-380</t>
+        </is>
+      </c>
+      <c r="X317" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y317" s="19" t="n"/>
+      <c r="Z317" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA317" s="19" t="n"/>
+      <c r="AB317" s="19" t="n"/>
+      <c r="AC317" s="19" t="n"/>
+      <c r="AD317" s="19" t="n"/>
+      <c r="AE317" s="20" t="n"/>
+      <c r="AF317" s="21">
+        <f>IF(K317="","",K317*AE317)</f>
+        <v/>
+      </c>
+      <c r="AG317" s="19" t="n"/>
+      <c r="AH317" s="19" t="n"/>
+      <c r="AI317" s="19" t="n"/>
+      <c r="AJ317" s="19" t="n"/>
+      <c r="AK317" s="19" t="n"/>
+      <c r="AL317" s="19" t="n"/>
+      <c r="AM317" s="16" t="inlineStr">
+        <is>
+          <t>1 Wagen. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN317" s="22" t="n"/>
+    </row>
+    <row r="318" ht="30" customHeight="1">
+      <c r="A318" s="15" t="inlineStr">
+        <is>
+          <t>BU02-17</t>
+        </is>
+      </c>
+      <c r="B318" s="15" t="n"/>
+      <c r="C318" s="15" t="n"/>
+      <c r="D318" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E318" s="15" t="inlineStr">
+        <is>
+          <t>Kommode weiß, drei Schubladen</t>
+        </is>
+      </c>
+      <c r="F318" s="16" t="inlineStr">
+        <is>
+          <t>Kommode in Weiß mit drei breiten Schubladen und mittig ausgeschnittenen Griffmulden, auf umlaufendem Sockel.</t>
+        </is>
+      </c>
+      <c r="G318" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H318" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I318" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J318" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K318" s="17" t="n"/>
+      <c r="L318" s="18">
+        <f>J318-IF(K318="",0,K318)</f>
+        <v/>
+      </c>
+      <c r="M318" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N318" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O318" s="19" t="n"/>
+      <c r="P318" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q318" s="19" t="n"/>
+      <c r="R318" s="20" t="n"/>
+      <c r="S318" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T318" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U318" s="21">
+        <f>L318*S318</f>
+        <v/>
+      </c>
+      <c r="V318" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W318" s="15" t="inlineStr">
+        <is>
+          <t>F-381</t>
+        </is>
+      </c>
+      <c r="X318" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y318" s="19" t="n"/>
+      <c r="Z318" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA318" s="19" t="n"/>
+      <c r="AB318" s="19" t="n"/>
+      <c r="AC318" s="19" t="n"/>
+      <c r="AD318" s="19" t="n"/>
+      <c r="AE318" s="20" t="n"/>
+      <c r="AF318" s="21">
+        <f>IF(K318="","",K318*AE318)</f>
+        <v/>
+      </c>
+      <c r="AG318" s="19" t="n"/>
+      <c r="AH318" s="19" t="n"/>
+      <c r="AI318" s="19" t="n"/>
+      <c r="AJ318" s="19" t="n"/>
+      <c r="AK318" s="19" t="n"/>
+      <c r="AL318" s="19" t="n"/>
+      <c r="AM318" s="16" t="inlineStr">
+        <is>
+          <t>1 Kommode.</t>
+        </is>
+      </c>
+      <c r="AN318" s="22" t="n"/>
+    </row>
+    <row r="319" ht="30" customHeight="1">
+      <c r="A319" s="15" t="inlineStr">
+        <is>
+          <t>BU02-18</t>
+        </is>
+      </c>
+      <c r="B319" s="15" t="n"/>
+      <c r="C319" s="15" t="n"/>
+      <c r="D319" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E319" s="15" t="inlineStr">
+        <is>
+          <t>Hochflorteppich grau</t>
+        </is>
+      </c>
+      <c r="F319" s="16" t="inlineStr">
+        <is>
+          <t>Hochflorteppich in Grau, rechteckig. Etikett auf der Rückseite vorhanden, Maßangabe 160 × 230 cm.</t>
+        </is>
+      </c>
+      <c r="G319" s="15" t="inlineStr">
+        <is>
+          <t>Textilien</t>
+        </is>
+      </c>
+      <c r="H319" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I319" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J319" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K319" s="17" t="n"/>
+      <c r="L319" s="18">
+        <f>J319-IF(K319="",0,K319)</f>
+        <v/>
+      </c>
+      <c r="M319" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N319" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O319" s="19" t="inlineStr">
+        <is>
+          <t>160 × 230 cm</t>
+        </is>
+      </c>
+      <c r="P319" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q319" s="19" t="n"/>
+      <c r="R319" s="20" t="n"/>
+      <c r="S319" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="T319" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U319" s="21">
+        <f>L319*S319</f>
+        <v/>
+      </c>
+      <c r="V319" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W319" s="15" t="inlineStr">
+        <is>
+          <t>F-382</t>
+        </is>
+      </c>
+      <c r="X319" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y319" s="19" t="n"/>
+      <c r="Z319" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA319" s="19" t="n"/>
+      <c r="AB319" s="19" t="n"/>
+      <c r="AC319" s="19" t="n"/>
+      <c r="AD319" s="19" t="n"/>
+      <c r="AE319" s="20" t="n"/>
+      <c r="AF319" s="21">
+        <f>IF(K319="","",K319*AE319)</f>
+        <v/>
+      </c>
+      <c r="AG319" s="19" t="n"/>
+      <c r="AH319" s="19" t="n"/>
+      <c r="AI319" s="19" t="n"/>
+      <c r="AJ319" s="19" t="n"/>
+      <c r="AK319" s="19" t="n"/>
+      <c r="AL319" s="19" t="n"/>
+      <c r="AM319" s="16" t="inlineStr">
+        <is>
+          <t>1 Teppich. Das Etikett ist auf Foto F-384 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN319" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: Auf dem Erfassungsblatt steht 1,80 × 2,30 m, das Etikett nennt 160 × 230 cm – bitte nachmessen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="30" customHeight="1">
+      <c r="A320" s="15" t="inlineStr">
+        <is>
+          <t>BU02-19</t>
+        </is>
+      </c>
+      <c r="B320" s="15" t="n"/>
+      <c r="C320" s="15" t="n"/>
+      <c r="D320" s="15" t="inlineStr">
+        <is>
+          <t>BU02</t>
+        </is>
+      </c>
+      <c r="E320" s="15" t="inlineStr">
+        <is>
+          <t>Spielmöbel Kiefer, dreiteilig</t>
+        </is>
+      </c>
+      <c r="F320" s="16" t="inlineStr">
+        <is>
+          <t>Dreiteilige Kombination aus Kiefer massiv: Wandregal mit zwei Kunststoffwannen, niedrige Werkbank mit offenem Unterbau und zwei Wannen sowie ein hohes Seitenteil mit Wanne.</t>
+        </is>
+      </c>
+      <c r="G320" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H320" s="15" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="I320" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J320" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K320" s="17" t="n"/>
+      <c r="L320" s="18">
+        <f>J320-IF(K320="",0,K320)</f>
+        <v/>
+      </c>
+      <c r="M320" s="15" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N320" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O320" s="19" t="n"/>
+      <c r="P320" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q320" s="19" t="n"/>
+      <c r="R320" s="20" t="n"/>
+      <c r="S320" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T320" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U320" s="21">
+        <f>L320*S320</f>
+        <v/>
+      </c>
+      <c r="V320" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W320" s="15" t="inlineStr">
+        <is>
+          <t>F-385</t>
+        </is>
+      </c>
+      <c r="X320" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y320" s="19" t="n"/>
+      <c r="Z320" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA320" s="19" t="n"/>
+      <c r="AB320" s="19" t="n"/>
+      <c r="AC320" s="19" t="n"/>
+      <c r="AD320" s="19" t="n"/>
+      <c r="AE320" s="20" t="n"/>
+      <c r="AF320" s="21">
+        <f>IF(K320="","",K320*AE320)</f>
+        <v/>
+      </c>
+      <c r="AG320" s="19" t="n"/>
+      <c r="AH320" s="19" t="n"/>
+      <c r="AI320" s="19" t="n"/>
+      <c r="AJ320" s="19" t="n"/>
+      <c r="AK320" s="19" t="n"/>
+      <c r="AL320" s="19" t="n"/>
+      <c r="AM320" s="16" t="inlineStr">
+        <is>
+          <t>1 Kombination aus drei Teilen einschließlich der Wannen. Das Spielzeug gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN320" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN306"/>
+  <autoFilter ref="A2:AN320"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -38365,7 +40071,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z306">
+  <conditionalFormatting sqref="Z3:Z320">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -38376,12 +40082,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I306">
+  <conditionalFormatting sqref="I3:I320">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P306">
+  <conditionalFormatting sqref="P3:P320">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -38472,7 +40178,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$306)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$320)</f>
         <v/>
       </c>
     </row>
@@ -38483,7 +40189,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$306,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$320,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -38494,7 +40200,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$306,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$320,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -38505,7 +40211,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$306,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$320,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -38516,7 +40222,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$306,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$320,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -38527,7 +40233,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$306)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$320)</f>
         <v/>
       </c>
     </row>
@@ -38538,7 +40244,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$306)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38556,7 +40262,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$306)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$320)</f>
         <v/>
       </c>
     </row>
@@ -38567,7 +40273,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$306,Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$320,Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
     </row>
@@ -38600,7 +40306,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$306="bezahlt")*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$320="bezahlt")*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
     </row>
@@ -38629,7 +40335,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$306,"*verkauft",Artikelstamm!$AI$3:$AI$306,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$320,"*verkauft",Artikelstamm!$AI$3:$AI$320,"")</f>
         <v/>
       </c>
     </row>
@@ -38640,7 +40346,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$306,"*verkauft",Artikelstamm!$AJ$3:$AJ$306,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$320,"*verkauft",Artikelstamm!$AJ$3:$AJ$320,"offen")</f>
         <v/>
       </c>
     </row>
@@ -38651,7 +40357,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$306,"reserviert",Artikelstamm!$AL$3:$AL$306,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$320,"reserviert",Artikelstamm!$AL$3:$AL$320,"")</f>
         <v/>
       </c>
     </row>
@@ -38662,7 +40368,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$306,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$320,"")</f>
         <v/>
       </c>
     </row>
@@ -38673,7 +40379,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$306,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$320,"")</f>
         <v/>
       </c>
     </row>
@@ -38713,15 +40419,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$306,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$320,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$306=$A30)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$320=$A30)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$306,$A30,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$320,$A30,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38732,15 +40438,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$306,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$320,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$306=$A31)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$320=$A31)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$306,$A31,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$320,$A31,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38751,15 +40457,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$306,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$320,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$306=$A32)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$320=$A32)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$306,$A32,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$320,$A32,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38818,15 +40524,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A37)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A37)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A37,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A37,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38837,15 +40543,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A38)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A38)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A38,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A38,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38856,15 +40562,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A39)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A39)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A39,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A39,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38875,15 +40581,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A40)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A40)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A40,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A40,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38894,15 +40600,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A41)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A41)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A41,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A41,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38913,15 +40619,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A42)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A42)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A42,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A42,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38932,15 +40638,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A43)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A43)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A43,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A43,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38951,15 +40657,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A44)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A44)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A44,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A44,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38970,15 +40676,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A45)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A45)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A45,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A45,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -38989,15 +40695,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A46)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A46)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A46,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A46,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39008,15 +40714,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A47)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A47)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A47,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A47,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39027,15 +40733,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A48)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A48)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A48,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A48,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39046,15 +40752,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A49)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A49)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A49,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A49,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39065,15 +40771,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$306,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$306=$A50)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A50)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$306,$A50,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A50,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39132,15 +40838,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A55)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A55)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A55,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A55,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39151,15 +40857,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A56)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A56)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A56,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A56,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39170,15 +40876,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A57)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A57)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A57,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A57,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39189,15 +40895,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A58)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A58)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A58,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A58,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39208,15 +40914,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A59)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A59)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A59,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A59,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39227,15 +40933,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A60)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A60)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A60,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A60,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39246,15 +40952,15 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A61)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A61)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A61,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A61,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39265,15 +40971,15 @@
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A62)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A62)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A62,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A62,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39284,15 +40990,15 @@
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A63)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A63)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A63,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A63,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39303,15 +41009,15 @@
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A64)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A64)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A64,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A64,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39322,15 +41028,15 @@
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A65)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A65)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A65,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A65,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39341,15 +41047,15 @@
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A66)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A66)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A66,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A66,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39360,15 +41066,15 @@
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A67)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A67)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A67,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A67,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39379,15 +41085,15 @@
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A68)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A68)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A68,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A68,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39398,15 +41104,15 @@
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A69)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A69)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A69,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A69,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39417,15 +41123,15 @@
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A70)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A70)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A70,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A70,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39436,15 +41142,15 @@
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A71)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A71)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A71,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A71,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39455,15 +41161,15 @@
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A72)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A72)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A72,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A72,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39474,15 +41180,15 @@
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A73)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A73)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A73,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A73,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39493,15 +41199,15 @@
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A74)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A74)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A74,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A74,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39512,15 +41218,15 @@
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A75)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A75)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A75,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A75,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39531,15 +41237,15 @@
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A76)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A76)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A76,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A76,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39550,15 +41256,15 @@
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A77)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A77)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A77,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A77,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39569,15 +41275,15 @@
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A78)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A78)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A78,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A78,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39588,15 +41294,15 @@
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A79)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A79)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D79" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A79,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A79,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39607,15 +41313,15 @@
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A80)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A80)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D80" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A80,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A80,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39626,15 +41332,15 @@
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A81)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A81)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D81" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A81,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A81,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39645,15 +41351,15 @@
         </is>
       </c>
       <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$306,$A82)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A82)</f>
         <v/>
       </c>
       <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$306=$A82)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A82)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
       <c r="D82" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$306,$A82,Artikelstamm!$U$3:$U$306)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A82,Artikelstamm!$U$3:$U$320)</f>
         <v/>
       </c>
     </row>
@@ -39707,11 +41413,11 @@
         </is>
       </c>
       <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A87)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A87)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A87)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A87)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
     </row>
@@ -39722,11 +41428,11 @@
         </is>
       </c>
       <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A88)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A88)</f>
         <v/>
       </c>
       <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A88)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A88)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
     </row>
@@ -39737,11 +41443,11 @@
         </is>
       </c>
       <c r="B89" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A89)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A89)</f>
         <v/>
       </c>
       <c r="C89" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A89)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A89)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
     </row>
@@ -39752,11 +41458,11 @@
         </is>
       </c>
       <c r="B90" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A90)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A90)</f>
         <v/>
       </c>
       <c r="C90" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A90)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A90)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
     </row>
@@ -39767,11 +41473,11 @@
         </is>
       </c>
       <c r="B91" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A91)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A91)</f>
         <v/>
       </c>
       <c r="C91" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A91)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A91)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
     </row>
@@ -39782,11 +41488,11 @@
         </is>
       </c>
       <c r="B92" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$306,$A92)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A92)</f>
         <v/>
       </c>
       <c r="C92" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$306=$A92)*Artikelstamm!$K$3:$K$306*Artikelstamm!$AE$3:$AE$306)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A92)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$320</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$327</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN320"/>
+  <dimension ref="A1:AN327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30397,7 +30397,7 @@
       <c r="B241" s="15" t="n"/>
       <c r="C241" s="15" t="inlineStr">
         <is>
-          <t>BA04-09</t>
+          <t>BA04-09, BU02-14</t>
         </is>
       </c>
       <c r="D241" s="15" t="inlineStr">
@@ -30431,7 +30431,7 @@
         </is>
       </c>
       <c r="J241" s="17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K241" s="17" t="n"/>
       <c r="L241" s="18">
@@ -30510,12 +30510,12 @@
       <c r="AL241" s="19" t="n"/>
       <c r="AM241" s="16" t="inlineStr">
         <is>
-          <t>4 Schränke insgesamt: 2 im Flur 2 (BA02-08) und 2 im Gruppenraum 4 (dort mit BA04-09 beschriftet). Abgebildet ist einer davon, ein weiterer auf Foto F-308.</t>
+          <t>6 Schränke insgesamt: 2 im Flur 2 der Attika (BA02-08), 2 im Gruppenraum 4 (BA04-09) und 2 im Flur 2 im Untergeschoss des Bestandsgebäudes (BU02-14). Die beiden Schränke im Untergeschoss sind auf Foto F-378 zu sehen.</t>
         </is>
       </c>
       <c r="AN241" s="22" t="inlineStr">
         <is>
-          <t>Zusammengefasste Position – Post-it-Nummer im zweiten Raum: BA04-09.</t>
+          <t>Zusammengefasste Position über drei Räume – Post-it-Nummern: BA04-09, BU02-14.</t>
         </is>
       </c>
     </row>
@@ -39337,7 +39337,7 @@
     <row r="315" ht="30" customHeight="1">
       <c r="A315" s="15" t="inlineStr">
         <is>
-          <t>BU02-14</t>
+          <t>BU02-15</t>
         </is>
       </c>
       <c r="B315" s="15" t="n"/>
@@ -39349,17 +39349,17 @@
       </c>
       <c r="E315" s="15" t="inlineStr">
         <is>
-          <t>Kinderschrank graugrün, zwei Türen</t>
+          <t>Bodensitzkissen beige, selbststehend</t>
         </is>
       </c>
       <c r="F315" s="16" t="inlineStr">
         <is>
-          <t>Hoher Kinderschrank von IKEA mit zwei graugrünen Türen und schwarzen Griffmulden, darunter eine Schublade.</t>
+          <t>Selbststehendes Bodensitzkissen aus beigem Leinenstoff mit gesteppten Feldern, Rückenlehne und langer Sitzfläche. Die Lehne lässt sich flach ausklappen.</t>
         </is>
       </c>
       <c r="G315" s="15" t="inlineStr">
         <is>
-          <t>Möbel</t>
+          <t>Textilien</t>
         </is>
       </c>
       <c r="H315" s="15" t="inlineStr">
@@ -39369,7 +39369,7 @@
       </c>
       <c r="I315" s="15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J315" s="17" t="n">
@@ -39399,7 +39399,7 @@
       <c r="Q315" s="19" t="n"/>
       <c r="R315" s="20" t="n"/>
       <c r="S315" s="20" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="T315" s="19" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
       </c>
       <c r="W315" s="15" t="inlineStr">
         <is>
-          <t>F-378</t>
+          <t>F-379</t>
         </is>
       </c>
       <c r="X315" s="19" t="inlineStr">
@@ -39431,11 +39431,7 @@
           <t>verfügbar</t>
         </is>
       </c>
-      <c r="AA315" s="19" t="inlineStr">
-        <is>
-          <t>IKEA</t>
-        </is>
-      </c>
+      <c r="AA315" s="19" t="n"/>
       <c r="AB315" s="19" t="n"/>
       <c r="AC315" s="19" t="n"/>
       <c r="AD315" s="19" t="n"/>
@@ -39452,7 +39448,7 @@
       <c r="AL315" s="19" t="n"/>
       <c r="AM315" s="16" t="inlineStr">
         <is>
-          <t>2 Schränke – abgebildet ist einer davon. Baugleiche Schränke mit weißen Türen stehen unter BA02-08.</t>
+          <t>2 Stück – abgebildet ist eines davon.</t>
         </is>
       </c>
       <c r="AN315" s="22" t="n"/>
@@ -39460,7 +39456,7 @@
     <row r="316" ht="30" customHeight="1">
       <c r="A316" s="15" t="inlineStr">
         <is>
-          <t>BU02-15</t>
+          <t>BU02-16</t>
         </is>
       </c>
       <c r="B316" s="15" t="n"/>
@@ -39472,17 +39468,17 @@
       </c>
       <c r="E316" s="15" t="inlineStr">
         <is>
-          <t>Bodensitzkissen beige, selbststehend</t>
+          <t>Servierwagen Metall schwarz, drei Ebenen</t>
         </is>
       </c>
       <c r="F316" s="16" t="inlineStr">
         <is>
-          <t>Selbststehendes Bodensitzkissen aus beigem Leinenstoff mit gesteppten Feldern, Rückenlehne und langer Sitzfläche. Die Lehne lässt sich flach ausklappen.</t>
+          <t>Rollwagen aus schwarz lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
         </is>
       </c>
       <c r="G316" s="15" t="inlineStr">
         <is>
-          <t>Textilien</t>
+          <t>Möbel</t>
         </is>
       </c>
       <c r="H316" s="15" t="inlineStr">
@@ -39492,11 +39488,11 @@
       </c>
       <c r="I316" s="15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J316" s="17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K316" s="17" t="n"/>
       <c r="L316" s="18">
@@ -39522,7 +39518,7 @@
       <c r="Q316" s="19" t="n"/>
       <c r="R316" s="20" t="n"/>
       <c r="S316" s="20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T316" s="19" t="inlineStr">
         <is>
@@ -39540,7 +39536,7 @@
       </c>
       <c r="W316" s="15" t="inlineStr">
         <is>
-          <t>F-379</t>
+          <t>F-380</t>
         </is>
       </c>
       <c r="X316" s="19" t="inlineStr">
@@ -39571,7 +39567,7 @@
       <c r="AL316" s="19" t="n"/>
       <c r="AM316" s="16" t="inlineStr">
         <is>
-          <t>2 Stück – abgebildet ist eines davon.</t>
+          <t>1 Wagen. Der Inhalt gehört nicht dazu.</t>
         </is>
       </c>
       <c r="AN316" s="22" t="n"/>
@@ -39579,7 +39575,7 @@
     <row r="317" ht="30" customHeight="1">
       <c r="A317" s="15" t="inlineStr">
         <is>
-          <t>BU02-16</t>
+          <t>BU02-17</t>
         </is>
       </c>
       <c r="B317" s="15" t="n"/>
@@ -39591,12 +39587,12 @@
       </c>
       <c r="E317" s="15" t="inlineStr">
         <is>
-          <t>Servierwagen Metall schwarz, drei Ebenen</t>
+          <t>Kommode weiß, drei Schubladen</t>
         </is>
       </c>
       <c r="F317" s="16" t="inlineStr">
         <is>
-          <t>Rollwagen aus schwarz lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
+          <t>Kommode in Weiß mit drei breiten Schubladen und mittig ausgeschnittenen Griffmulden, auf umlaufendem Sockel.</t>
         </is>
       </c>
       <c r="G317" s="15" t="inlineStr">
@@ -39641,7 +39637,7 @@
       <c r="Q317" s="19" t="n"/>
       <c r="R317" s="20" t="n"/>
       <c r="S317" s="20" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T317" s="19" t="inlineStr">
         <is>
@@ -39659,7 +39655,7 @@
       </c>
       <c r="W317" s="15" t="inlineStr">
         <is>
-          <t>F-380</t>
+          <t>F-381</t>
         </is>
       </c>
       <c r="X317" s="19" t="inlineStr">
@@ -39690,7 +39686,7 @@
       <c r="AL317" s="19" t="n"/>
       <c r="AM317" s="16" t="inlineStr">
         <is>
-          <t>1 Wagen. Der Inhalt gehört nicht dazu.</t>
+          <t>1 Kommode.</t>
         </is>
       </c>
       <c r="AN317" s="22" t="n"/>
@@ -39698,7 +39694,7 @@
     <row r="318" ht="30" customHeight="1">
       <c r="A318" s="15" t="inlineStr">
         <is>
-          <t>BU02-17</t>
+          <t>BU02-18</t>
         </is>
       </c>
       <c r="B318" s="15" t="n"/>
@@ -39710,17 +39706,17 @@
       </c>
       <c r="E318" s="15" t="inlineStr">
         <is>
-          <t>Kommode weiß, drei Schubladen</t>
+          <t>Hochflorteppich grau</t>
         </is>
       </c>
       <c r="F318" s="16" t="inlineStr">
         <is>
-          <t>Kommode in Weiß mit drei breiten Schubladen und mittig ausgeschnittenen Griffmulden, auf umlaufendem Sockel.</t>
+          <t>Hochflorteppich in Grau, rechteckig. Maße laut Etikett auf der Rückseite: 160 × 230 cm.</t>
         </is>
       </c>
       <c r="G318" s="15" t="inlineStr">
         <is>
-          <t>Möbel</t>
+          <t>Textilien</t>
         </is>
       </c>
       <c r="H318" s="15" t="inlineStr">
@@ -39730,7 +39726,7 @@
       </c>
       <c r="I318" s="15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J318" s="17" t="n">
@@ -39751,7 +39747,11 @@
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="O318" s="19" t="n"/>
+      <c r="O318" s="19" t="inlineStr">
+        <is>
+          <t>160 × 230 cm</t>
+        </is>
+      </c>
       <c r="P318" s="19" t="inlineStr">
         <is>
           <t>ja</t>
@@ -39760,7 +39760,7 @@
       <c r="Q318" s="19" t="n"/>
       <c r="R318" s="20" t="n"/>
       <c r="S318" s="20" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="T318" s="19" t="inlineStr">
         <is>
@@ -39773,12 +39773,12 @@
       </c>
       <c r="V318" s="15" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="W318" s="15" t="inlineStr">
         <is>
-          <t>F-381</t>
+          <t>F-382</t>
         </is>
       </c>
       <c r="X318" s="19" t="inlineStr">
@@ -39809,7 +39809,7 @@
       <c r="AL318" s="19" t="n"/>
       <c r="AM318" s="16" t="inlineStr">
         <is>
-          <t>1 Kommode.</t>
+          <t>1 Teppich. Das Etikett ist auf Foto F-384 zu sehen.</t>
         </is>
       </c>
       <c r="AN318" s="22" t="n"/>
@@ -39817,7 +39817,7 @@
     <row r="319" ht="30" customHeight="1">
       <c r="A319" s="15" t="inlineStr">
         <is>
-          <t>BU02-18</t>
+          <t>BU02-19</t>
         </is>
       </c>
       <c r="B319" s="15" t="n"/>
@@ -39829,17 +39829,17 @@
       </c>
       <c r="E319" s="15" t="inlineStr">
         <is>
-          <t>Hochflorteppich grau</t>
+          <t>Spielmöbel Kiefer, dreiteilig</t>
         </is>
       </c>
       <c r="F319" s="16" t="inlineStr">
         <is>
-          <t>Hochflorteppich in Grau, rechteckig. Etikett auf der Rückseite vorhanden, Maßangabe 160 × 230 cm.</t>
+          <t>Dreiteilige Kombination aus Kiefer massiv: Wandregal mit zwei Kunststoffwannen, niedrige Werkbank mit offenem Unterbau und zwei Wannen sowie ein hohes Seitenteil mit Wanne.</t>
         </is>
       </c>
       <c r="G319" s="15" t="inlineStr">
         <is>
-          <t>Textilien</t>
+          <t>Kita-Ausstattung</t>
         </is>
       </c>
       <c r="H319" s="15" t="inlineStr">
@@ -39849,7 +39849,7 @@
       </c>
       <c r="I319" s="15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J319" s="17" t="n">
@@ -39862,7 +39862,7 @@
       </c>
       <c r="M319" s="15" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="N319" s="15" t="inlineStr">
@@ -39870,11 +39870,7 @@
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="O319" s="19" t="inlineStr">
-        <is>
-          <t>160 × 230 cm</t>
-        </is>
-      </c>
+      <c r="O319" s="19" t="n"/>
       <c r="P319" s="19" t="inlineStr">
         <is>
           <t>ja</t>
@@ -39883,7 +39879,7 @@
       <c r="Q319" s="19" t="n"/>
       <c r="R319" s="20" t="n"/>
       <c r="S319" s="20" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="T319" s="19" t="inlineStr">
         <is>
@@ -39896,12 +39892,12 @@
       </c>
       <c r="V319" s="15" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="W319" s="15" t="inlineStr">
         <is>
-          <t>F-382</t>
+          <t>F-385</t>
         </is>
       </c>
       <c r="X319" s="19" t="inlineStr">
@@ -39932,36 +39928,32 @@
       <c r="AL319" s="19" t="n"/>
       <c r="AM319" s="16" t="inlineStr">
         <is>
-          <t>1 Teppich. Das Etikett ist auf Foto F-384 zu sehen.</t>
-        </is>
-      </c>
-      <c r="AN319" s="22" t="inlineStr">
-        <is>
-          <t>OFFEN: Auf dem Erfassungsblatt steht 1,80 × 2,30 m, das Etikett nennt 160 × 230 cm – bitte nachmessen.</t>
-        </is>
-      </c>
+          <t>1 Kombination aus drei Teilen einschließlich der Wannen. Das Spielzeug gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN319" s="22" t="n"/>
     </row>
     <row r="320" ht="30" customHeight="1">
       <c r="A320" s="15" t="inlineStr">
         <is>
-          <t>BU02-19</t>
+          <t>BU03-01</t>
         </is>
       </c>
       <c r="B320" s="15" t="n"/>
       <c r="C320" s="15" t="n"/>
       <c r="D320" s="15" t="inlineStr">
         <is>
-          <t>BU02</t>
+          <t>BU03</t>
         </is>
       </c>
       <c r="E320" s="15" t="inlineStr">
         <is>
-          <t>Spielmöbel Kiefer, dreiteilig</t>
+          <t>Pinnwand Holz mit Klammerleinen</t>
         </is>
       </c>
       <c r="F320" s="16" t="inlineStr">
         <is>
-          <t>Dreiteilige Kombination aus Kiefer massiv: Wandregal mit zwei Kunststoffwannen, niedrige Werkbank mit offenem Unterbau und zwei Wannen sowie ein hohes Seitenteil mit Wanne.</t>
+          <t>Großes Wandelement aus hellem Massivholz mit vier waagerechten Bändern und Holzklammern zum Aufhängen von Bildern und Bastelarbeiten. Zwei zusätzliche Querbretter als Ablage.</t>
         </is>
       </c>
       <c r="G320" s="15" t="inlineStr">
@@ -39971,7 +39963,7 @@
       </c>
       <c r="H320" s="15" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur 3</t>
         </is>
       </c>
       <c r="I320" s="15" t="inlineStr">
@@ -39989,7 +39981,7 @@
       </c>
       <c r="M320" s="15" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="N320" s="15" t="inlineStr">
@@ -40006,7 +39998,7 @@
       <c r="Q320" s="19" t="n"/>
       <c r="R320" s="20" t="n"/>
       <c r="S320" s="20" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="T320" s="19" t="inlineStr">
         <is>
@@ -40024,7 +40016,7 @@
       </c>
       <c r="W320" s="15" t="inlineStr">
         <is>
-          <t>F-385</t>
+          <t>F-387</t>
         </is>
       </c>
       <c r="X320" s="19" t="inlineStr">
@@ -40055,13 +40047,846 @@
       <c r="AL320" s="19" t="n"/>
       <c r="AM320" s="16" t="inlineStr">
         <is>
-          <t>1 Kombination aus drei Teilen einschließlich der Wannen. Das Spielzeug gehört nicht dazu.</t>
+          <t>1 Wand einschließlich der Klammern. Die Deko-Ringe und Quasten gehören nicht dazu.</t>
         </is>
       </c>
       <c r="AN320" s="22" t="n"/>
     </row>
+    <row r="321" ht="30" customHeight="1">
+      <c r="A321" s="15" t="inlineStr">
+        <is>
+          <t>BU03-02</t>
+        </is>
+      </c>
+      <c r="B321" s="15" t="n"/>
+      <c r="C321" s="15" t="n"/>
+      <c r="D321" s="15" t="inlineStr">
+        <is>
+          <t>BU03</t>
+        </is>
+      </c>
+      <c r="E321" s="15" t="inlineStr">
+        <is>
+          <t>Schwingspiegel, geschwungene Form</t>
+        </is>
+      </c>
+      <c r="F321" s="16" t="inlineStr">
+        <is>
+          <t>Hoher Wandspiegel mit geschwungener Außenkante ohne Rahmen, zum Anschrauben.</t>
+        </is>
+      </c>
+      <c r="G321" s="15" t="inlineStr">
+        <is>
+          <t>Deko</t>
+        </is>
+      </c>
+      <c r="H321" s="15" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="I321" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J321" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K321" s="17" t="n"/>
+      <c r="L321" s="18">
+        <f>J321-IF(K321="",0,K321)</f>
+        <v/>
+      </c>
+      <c r="M321" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N321" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O321" s="19" t="n"/>
+      <c r="P321" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q321" s="19" t="n"/>
+      <c r="R321" s="20" t="n"/>
+      <c r="S321" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T321" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U321" s="21">
+        <f>L321*S321</f>
+        <v/>
+      </c>
+      <c r="V321" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W321" s="15" t="inlineStr">
+        <is>
+          <t>F-388</t>
+        </is>
+      </c>
+      <c r="X321" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y321" s="19" t="n"/>
+      <c r="Z321" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA321" s="19" t="n"/>
+      <c r="AB321" s="19" t="n"/>
+      <c r="AC321" s="19" t="n"/>
+      <c r="AD321" s="19" t="n"/>
+      <c r="AE321" s="20" t="n"/>
+      <c r="AF321" s="21">
+        <f>IF(K321="","",K321*AE321)</f>
+        <v/>
+      </c>
+      <c r="AG321" s="19" t="n"/>
+      <c r="AH321" s="19" t="n"/>
+      <c r="AI321" s="19" t="n"/>
+      <c r="AJ321" s="19" t="n"/>
+      <c r="AK321" s="19" t="n"/>
+      <c r="AL321" s="19" t="n"/>
+      <c r="AM321" s="16" t="inlineStr">
+        <is>
+          <t>2 Spiegel – abgebildet ist einer davon.</t>
+        </is>
+      </c>
+      <c r="AN321" s="22" t="n"/>
+    </row>
+    <row r="322" ht="30" customHeight="1">
+      <c r="A322" s="15" t="inlineStr">
+        <is>
+          <t>BU03-03</t>
+        </is>
+      </c>
+      <c r="B322" s="15" t="n"/>
+      <c r="C322" s="15" t="n"/>
+      <c r="D322" s="15" t="inlineStr">
+        <is>
+          <t>BU03</t>
+        </is>
+      </c>
+      <c r="E322" s="15" t="inlineStr">
+        <is>
+          <t>Schuhregal schwarz mit Chromstangen</t>
+        </is>
+      </c>
+      <c r="F322" s="16" t="inlineStr">
+        <is>
+          <t>Niedriges Schuhregal aus schwarz lackiertem Holz mit schwarzer Deckplatte und drei Ebenen aus verchromten Rundstangen, auch als Sitzbank nutzbar.</t>
+        </is>
+      </c>
+      <c r="G322" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H322" s="15" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="I322" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J322" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K322" s="17" t="n"/>
+      <c r="L322" s="18">
+        <f>J322-IF(K322="",0,K322)</f>
+        <v/>
+      </c>
+      <c r="M322" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N322" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O322" s="19" t="n"/>
+      <c r="P322" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q322" s="19" t="n"/>
+      <c r="R322" s="20" t="n"/>
+      <c r="S322" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T322" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U322" s="21">
+        <f>L322*S322</f>
+        <v/>
+      </c>
+      <c r="V322" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W322" s="15" t="inlineStr">
+        <is>
+          <t>F-389</t>
+        </is>
+      </c>
+      <c r="X322" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y322" s="19" t="n"/>
+      <c r="Z322" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA322" s="19" t="n"/>
+      <c r="AB322" s="19" t="n"/>
+      <c r="AC322" s="19" t="n"/>
+      <c r="AD322" s="19" t="n"/>
+      <c r="AE322" s="20" t="n"/>
+      <c r="AF322" s="21">
+        <f>IF(K322="","",K322*AE322)</f>
+        <v/>
+      </c>
+      <c r="AG322" s="19" t="n"/>
+      <c r="AH322" s="19" t="n"/>
+      <c r="AI322" s="19" t="n"/>
+      <c r="AJ322" s="19" t="n"/>
+      <c r="AK322" s="19" t="n"/>
+      <c r="AL322" s="19" t="n"/>
+      <c r="AM322" s="16" t="inlineStr">
+        <is>
+          <t>2 Regale – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN322" s="22" t="n"/>
+    </row>
+    <row r="323" ht="30" customHeight="1">
+      <c r="A323" s="15" t="inlineStr">
+        <is>
+          <t>BU03-04</t>
+        </is>
+      </c>
+      <c r="B323" s="15" t="n"/>
+      <c r="C323" s="15" t="n"/>
+      <c r="D323" s="15" t="inlineStr">
+        <is>
+          <t>BU03</t>
+        </is>
+      </c>
+      <c r="E323" s="15" t="inlineStr">
+        <is>
+          <t>Metallregal weiß, vier Böden</t>
+        </is>
+      </c>
+      <c r="F323" s="16" t="inlineStr">
+        <is>
+          <t>Offenes Regal mit weißem Metallgestell, Kreuzstrebe auf der Rückseite und vier weißen Böden.</t>
+        </is>
+      </c>
+      <c r="G323" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H323" s="15" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="I323" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J323" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K323" s="17" t="n"/>
+      <c r="L323" s="18">
+        <f>J323-IF(K323="",0,K323)</f>
+        <v/>
+      </c>
+      <c r="M323" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N323" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O323" s="19" t="n"/>
+      <c r="P323" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q323" s="19" t="n"/>
+      <c r="R323" s="20" t="n"/>
+      <c r="S323" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T323" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U323" s="21">
+        <f>L323*S323</f>
+        <v/>
+      </c>
+      <c r="V323" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W323" s="15" t="inlineStr">
+        <is>
+          <t>F-390</t>
+        </is>
+      </c>
+      <c r="X323" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y323" s="19" t="n"/>
+      <c r="Z323" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA323" s="19" t="n"/>
+      <c r="AB323" s="19" t="n"/>
+      <c r="AC323" s="19" t="n"/>
+      <c r="AD323" s="19" t="n"/>
+      <c r="AE323" s="20" t="n"/>
+      <c r="AF323" s="21">
+        <f>IF(K323="","",K323*AE323)</f>
+        <v/>
+      </c>
+      <c r="AG323" s="19" t="n"/>
+      <c r="AH323" s="19" t="n"/>
+      <c r="AI323" s="19" t="n"/>
+      <c r="AJ323" s="19" t="n"/>
+      <c r="AK323" s="19" t="n"/>
+      <c r="AL323" s="19" t="n"/>
+      <c r="AM323" s="16" t="inlineStr">
+        <is>
+          <t>2 Regale – abgebildet ist eines davon.</t>
+        </is>
+      </c>
+      <c r="AN323" s="22" t="n"/>
+    </row>
+    <row r="324" ht="30" customHeight="1">
+      <c r="A324" s="15" t="inlineStr">
+        <is>
+          <t>BU03-05</t>
+        </is>
+      </c>
+      <c r="B324" s="15" t="n"/>
+      <c r="C324" s="15" t="n"/>
+      <c r="D324" s="15" t="inlineStr">
+        <is>
+          <t>BU03</t>
+        </is>
+      </c>
+      <c r="E324" s="15" t="inlineStr">
+        <is>
+          <t>Schuhschrank weiß mit Klappfächern</t>
+        </is>
+      </c>
+      <c r="F324" s="16" t="inlineStr">
+        <is>
+          <t>Schmaler Schuhschrank in Weiß mit zwei Klappfächern und schwarzen Knöpfen. Die Schuhablagen sind innen verschmutzt und an den Kanten abgestoßen.</t>
+        </is>
+      </c>
+      <c r="G324" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H324" s="15" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="I324" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J324" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K324" s="17" t="n"/>
+      <c r="L324" s="18">
+        <f>J324-IF(K324="",0,K324)</f>
+        <v/>
+      </c>
+      <c r="M324" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N324" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O324" s="19" t="n"/>
+      <c r="P324" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q324" s="19" t="n"/>
+      <c r="R324" s="20" t="n"/>
+      <c r="S324" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T324" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U324" s="21">
+        <f>L324*S324</f>
+        <v/>
+      </c>
+      <c r="V324" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W324" s="15" t="inlineStr">
+        <is>
+          <t>F-391</t>
+        </is>
+      </c>
+      <c r="X324" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y324" s="19" t="n"/>
+      <c r="Z324" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA324" s="19" t="n"/>
+      <c r="AB324" s="19" t="n"/>
+      <c r="AC324" s="19" t="n"/>
+      <c r="AD324" s="19" t="n"/>
+      <c r="AE324" s="20" t="n"/>
+      <c r="AF324" s="21">
+        <f>IF(K324="","",K324*AE324)</f>
+        <v/>
+      </c>
+      <c r="AG324" s="19" t="n"/>
+      <c r="AH324" s="19" t="n"/>
+      <c r="AI324" s="19" t="n"/>
+      <c r="AJ324" s="19" t="n"/>
+      <c r="AK324" s="19" t="n"/>
+      <c r="AL324" s="19" t="n"/>
+      <c r="AM324" s="16" t="inlineStr">
+        <is>
+          <t>1 Schrank.</t>
+        </is>
+      </c>
+      <c r="AN324" s="22" t="n"/>
+    </row>
+    <row r="325" ht="30" customHeight="1">
+      <c r="A325" s="15" t="inlineStr">
+        <is>
+          <t>BU03-06</t>
+        </is>
+      </c>
+      <c r="B325" s="15" t="n"/>
+      <c r="C325" s="15" t="n"/>
+      <c r="D325" s="15" t="inlineStr">
+        <is>
+          <t>BU03</t>
+        </is>
+      </c>
+      <c r="E325" s="15" t="inlineStr">
+        <is>
+          <t>Wäschekorb anthrazit mit Deckel, hoch</t>
+        </is>
+      </c>
+      <c r="F325" s="16" t="inlineStr">
+        <is>
+          <t>Hoher Wäschekorb aus Kunststoff in Flechtoptik, anthrazit, nach unten verjüngt, mit aufklappbarem Deckel und Griffloch.</t>
+        </is>
+      </c>
+      <c r="G325" s="15" t="inlineStr">
+        <is>
+          <t>Sonstiges</t>
+        </is>
+      </c>
+      <c r="H325" s="15" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="I325" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J325" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K325" s="17" t="n"/>
+      <c r="L325" s="18">
+        <f>J325-IF(K325="",0,K325)</f>
+        <v/>
+      </c>
+      <c r="M325" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N325" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O325" s="19" t="n"/>
+      <c r="P325" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q325" s="19" t="n"/>
+      <c r="R325" s="20" t="n"/>
+      <c r="S325" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T325" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U325" s="21">
+        <f>L325*S325</f>
+        <v/>
+      </c>
+      <c r="V325" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W325" s="15" t="inlineStr">
+        <is>
+          <t>F-392</t>
+        </is>
+      </c>
+      <c r="X325" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y325" s="19" t="n"/>
+      <c r="Z325" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA325" s="19" t="n"/>
+      <c r="AB325" s="19" t="n"/>
+      <c r="AC325" s="19" t="n"/>
+      <c r="AD325" s="19" t="n"/>
+      <c r="AE325" s="20" t="n"/>
+      <c r="AF325" s="21">
+        <f>IF(K325="","",K325*AE325)</f>
+        <v/>
+      </c>
+      <c r="AG325" s="19" t="n"/>
+      <c r="AH325" s="19" t="n"/>
+      <c r="AI325" s="19" t="n"/>
+      <c r="AJ325" s="19" t="n"/>
+      <c r="AK325" s="19" t="n"/>
+      <c r="AL325" s="19" t="n"/>
+      <c r="AM325" s="16" t="inlineStr">
+        <is>
+          <t>1 Korb. Drei niedrigere Wäschekörbe stehen unter NE02-03.</t>
+        </is>
+      </c>
+      <c r="AN325" s="22" t="n"/>
+    </row>
+    <row r="326" ht="30" customHeight="1">
+      <c r="A326" s="15" t="inlineStr">
+        <is>
+          <t>BU03-07</t>
+        </is>
+      </c>
+      <c r="B326" s="15" t="n"/>
+      <c r="C326" s="15" t="n"/>
+      <c r="D326" s="15" t="inlineStr">
+        <is>
+          <t>BU03</t>
+        </is>
+      </c>
+      <c r="E326" s="15" t="inlineStr">
+        <is>
+          <t>Tischleuchte Holzgestell mit Stoffschirm</t>
+        </is>
+      </c>
+      <c r="F326" s="16" t="inlineStr">
+        <is>
+          <t>Tischleuchte mit dreieckigem Gestell aus hellem Holz und zylindrischem Stoffschirm in Hellgrau, mit Schnurschalter.</t>
+        </is>
+      </c>
+      <c r="G326" s="15" t="inlineStr">
+        <is>
+          <t>Leuchten</t>
+        </is>
+      </c>
+      <c r="H326" s="15" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="I326" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J326" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K326" s="17" t="n"/>
+      <c r="L326" s="18">
+        <f>J326-IF(K326="",0,K326)</f>
+        <v/>
+      </c>
+      <c r="M326" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N326" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O326" s="19" t="n"/>
+      <c r="P326" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q326" s="19" t="n"/>
+      <c r="R326" s="20" t="n"/>
+      <c r="S326" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T326" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U326" s="21">
+        <f>L326*S326</f>
+        <v/>
+      </c>
+      <c r="V326" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W326" s="15" t="inlineStr">
+        <is>
+          <t>F-393</t>
+        </is>
+      </c>
+      <c r="X326" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y326" s="19" t="n"/>
+      <c r="Z326" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA326" s="19" t="n"/>
+      <c r="AB326" s="19" t="n"/>
+      <c r="AC326" s="19" t="n"/>
+      <c r="AD326" s="19" t="n"/>
+      <c r="AE326" s="20" t="n"/>
+      <c r="AF326" s="21">
+        <f>IF(K326="","",K326*AE326)</f>
+        <v/>
+      </c>
+      <c r="AG326" s="19" t="n"/>
+      <c r="AH326" s="19" t="n"/>
+      <c r="AI326" s="19" t="n"/>
+      <c r="AJ326" s="19" t="n"/>
+      <c r="AK326" s="19" t="n"/>
+      <c r="AL326" s="19" t="n"/>
+      <c r="AM326" s="16" t="inlineStr">
+        <is>
+          <t>1 Leuchte ohne Leuchtmittel. Auf dem Erfassungsblatt als Stehlampe geführt – es ist eine Tischleuchte.</t>
+        </is>
+      </c>
+      <c r="AN326" s="22" t="n"/>
+    </row>
+    <row r="327" ht="30" customHeight="1">
+      <c r="A327" s="15" t="inlineStr">
+        <is>
+          <t>BU03-08</t>
+        </is>
+      </c>
+      <c r="B327" s="15" t="n"/>
+      <c r="C327" s="15" t="n"/>
+      <c r="D327" s="15" t="inlineStr">
+        <is>
+          <t>BU03</t>
+        </is>
+      </c>
+      <c r="E327" s="15" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund türkis mit Hairpin-Beinen</t>
+        </is>
+      </c>
+      <c r="F327" s="16" t="inlineStr">
+        <is>
+          <t>Kleiner runder Beistelltisch mit türkis lackierter Holzplatte auf drei schwarzen Hairpin-Beinen aus Rundstahl. Die Platte ist leicht verkratzt.</t>
+        </is>
+      </c>
+      <c r="G327" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H327" s="15" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="I327" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J327" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K327" s="17" t="n"/>
+      <c r="L327" s="18">
+        <f>J327-IF(K327="",0,K327)</f>
+        <v/>
+      </c>
+      <c r="M327" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N327" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O327" s="19" t="n"/>
+      <c r="P327" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q327" s="19" t="n"/>
+      <c r="R327" s="20" t="n"/>
+      <c r="S327" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T327" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U327" s="21">
+        <f>L327*S327</f>
+        <v/>
+      </c>
+      <c r="V327" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W327" s="15" t="inlineStr">
+        <is>
+          <t>F-394</t>
+        </is>
+      </c>
+      <c r="X327" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y327" s="19" t="n"/>
+      <c r="Z327" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA327" s="19" t="n"/>
+      <c r="AB327" s="19" t="n"/>
+      <c r="AC327" s="19" t="n"/>
+      <c r="AD327" s="19" t="n"/>
+      <c r="AE327" s="20" t="n"/>
+      <c r="AF327" s="21">
+        <f>IF(K327="","",K327*AE327)</f>
+        <v/>
+      </c>
+      <c r="AG327" s="19" t="n"/>
+      <c r="AH327" s="19" t="n"/>
+      <c r="AI327" s="19" t="n"/>
+      <c r="AJ327" s="19" t="n"/>
+      <c r="AK327" s="19" t="n"/>
+      <c r="AL327" s="19" t="n"/>
+      <c r="AM327" s="16" t="inlineStr">
+        <is>
+          <t>1 Tisch.</t>
+        </is>
+      </c>
+      <c r="AN327" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN320"/>
+  <autoFilter ref="A2:AN327"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -40071,7 +40896,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z320">
+  <conditionalFormatting sqref="Z3:Z327">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -40082,12 +40907,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I320">
+  <conditionalFormatting sqref="I3:I327">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P320">
+  <conditionalFormatting sqref="P3:P327">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -40140,7 +40965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -40178,7 +41003,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$320)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$327)</f>
         <v/>
       </c>
     </row>
@@ -40189,7 +41014,7 @@
         </is>
       </c>
       <c r="B6" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$320,"verfügbar")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$327,"verfügbar")</f>
         <v/>
       </c>
     </row>
@@ -40200,7 +41025,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$320,"reserviert")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$327,"reserviert")</f>
         <v/>
       </c>
     </row>
@@ -40211,7 +41036,7 @@
         </is>
       </c>
       <c r="B8" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$320,"teilverkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$327,"teilverkauft")</f>
         <v/>
       </c>
     </row>
@@ -40222,7 +41047,7 @@
         </is>
       </c>
       <c r="B9" s="27">
-        <f>COUNTIF(Artikelstamm!$Z$3:$Z$320,"verkauft")</f>
+        <f>COUNTIF(Artikelstamm!$Z$3:$Z$327,"verkauft")</f>
         <v/>
       </c>
     </row>
@@ -40233,7 +41058,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>SUM(Artikelstamm!$L$3:$L$320)</f>
+        <f>SUM(Artikelstamm!$L$3:$L$327)</f>
         <v/>
       </c>
     </row>
@@ -40244,7 +41069,7 @@
         </is>
       </c>
       <c r="B11" s="29">
-        <f>SUM(Artikelstamm!$U$3:$U$320)</f>
+        <f>SUM(Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40262,7 +41087,7 @@
         </is>
       </c>
       <c r="B13" s="27">
-        <f>SUM(Artikelstamm!$K$3:$K$320)</f>
+        <f>SUM(Artikelstamm!$K$3:$K$327)</f>
         <v/>
       </c>
     </row>
@@ -40273,7 +41098,7 @@
         </is>
       </c>
       <c r="B14" s="30">
-        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$320,Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT(Artikelstamm!$K$3:$K$327,Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
     </row>
@@ -40306,7 +41131,7 @@
         </is>
       </c>
       <c r="B17" s="30">
-        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$320="bezahlt")*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AJ$3:$AJ$327="bezahlt")*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
     </row>
@@ -40335,7 +41160,7 @@
         </is>
       </c>
       <c r="B21" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$320,"*verkauft",Artikelstamm!$AI$3:$AI$320,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$327,"*verkauft",Artikelstamm!$AI$3:$AI$327,"")</f>
         <v/>
       </c>
     </row>
@@ -40346,7 +41171,7 @@
         </is>
       </c>
       <c r="B22" s="31">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$320,"*verkauft",Artikelstamm!$AJ$3:$AJ$320,"offen")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$327,"*verkauft",Artikelstamm!$AJ$3:$AJ$327,"offen")</f>
         <v/>
       </c>
     </row>
@@ -40357,7 +41182,7 @@
         </is>
       </c>
       <c r="B23" s="27">
-        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$320,"reserviert",Artikelstamm!$AL$3:$AL$320,"")</f>
+        <f>COUNTIFS(Artikelstamm!$Z$3:$Z$327,"reserviert",Artikelstamm!$AL$3:$AL$327,"")</f>
         <v/>
       </c>
     </row>
@@ -40368,7 +41193,7 @@
         </is>
       </c>
       <c r="B24" s="27">
-        <f>COUNTIFS(Artikelstamm!$S$3:$S$320,"")</f>
+        <f>COUNTIFS(Artikelstamm!$S$3:$S$327,"")</f>
         <v/>
       </c>
     </row>
@@ -40379,7 +41204,7 @@
         </is>
       </c>
       <c r="B25" s="27">
-        <f>COUNTIFS(Artikelstamm!$O$3:$O$320,"")</f>
+        <f>COUNTIFS(Artikelstamm!$O$3:$O$327,"")</f>
         <v/>
       </c>
     </row>
@@ -40419,15 +41244,15 @@
         </is>
       </c>
       <c r="B30" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$320,$A30)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$327,$A30)</f>
         <v/>
       </c>
       <c r="C30" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$320=$A30)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$327=$A30)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D30" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$320,$A30,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$327,$A30,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40438,15 +41263,15 @@
         </is>
       </c>
       <c r="B31" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$320,$A31)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$327,$A31)</f>
         <v/>
       </c>
       <c r="C31" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$320=$A31)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$327=$A31)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D31" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$320,$A31,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$327,$A31,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40457,15 +41282,15 @@
         </is>
       </c>
       <c r="B32" s="33">
-        <f>COUNTIF(Artikelstamm!$I$3:$I$320,$A32)</f>
+        <f>COUNTIF(Artikelstamm!$I$3:$I$327,$A32)</f>
         <v/>
       </c>
       <c r="C32" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$320=$A32)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$I$3:$I$327=$A32)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D32" s="34">
-        <f>SUMIF(Artikelstamm!$I$3:$I$320,$A32,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$I$3:$I$327,$A32,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40524,15 +41349,15 @@
         </is>
       </c>
       <c r="B37" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A37)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A37)</f>
         <v/>
       </c>
       <c r="C37" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A37)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A37)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D37" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A37,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A37,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40543,15 +41368,15 @@
         </is>
       </c>
       <c r="B38" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A38)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A38)</f>
         <v/>
       </c>
       <c r="C38" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A38)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A38)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D38" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A38,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A38,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40562,15 +41387,15 @@
         </is>
       </c>
       <c r="B39" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A39)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A39)</f>
         <v/>
       </c>
       <c r="C39" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A39)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A39)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D39" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A39,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A39,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40581,15 +41406,15 @@
         </is>
       </c>
       <c r="B40" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A40)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A40)</f>
         <v/>
       </c>
       <c r="C40" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A40)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A40)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D40" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A40,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A40,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40600,15 +41425,15 @@
         </is>
       </c>
       <c r="B41" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A41)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A41)</f>
         <v/>
       </c>
       <c r="C41" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A41)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A41)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D41" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A41,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A41,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40619,15 +41444,15 @@
         </is>
       </c>
       <c r="B42" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A42)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A42)</f>
         <v/>
       </c>
       <c r="C42" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A42)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A42)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D42" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A42,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A42,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40638,15 +41463,15 @@
         </is>
       </c>
       <c r="B43" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A43)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A43)</f>
         <v/>
       </c>
       <c r="C43" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A43)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A43)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D43" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A43,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A43,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40657,15 +41482,15 @@
         </is>
       </c>
       <c r="B44" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A44)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A44)</f>
         <v/>
       </c>
       <c r="C44" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A44)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A44)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D44" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A44,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A44,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40676,15 +41501,15 @@
         </is>
       </c>
       <c r="B45" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A45)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A45)</f>
         <v/>
       </c>
       <c r="C45" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A45)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A45)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D45" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A45,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A45,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40695,15 +41520,15 @@
         </is>
       </c>
       <c r="B46" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A46)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A46)</f>
         <v/>
       </c>
       <c r="C46" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A46)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A46)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D46" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A46,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A46,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40714,15 +41539,15 @@
         </is>
       </c>
       <c r="B47" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A47)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A47)</f>
         <v/>
       </c>
       <c r="C47" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A47)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A47)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D47" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A47,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A47,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40733,15 +41558,15 @@
         </is>
       </c>
       <c r="B48" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A48)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A48)</f>
         <v/>
       </c>
       <c r="C48" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A48)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A48)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D48" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A48,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A48,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40752,15 +41577,15 @@
         </is>
       </c>
       <c r="B49" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A49)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A49)</f>
         <v/>
       </c>
       <c r="C49" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A49)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A49)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D49" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A49,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A49,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40771,15 +41596,15 @@
         </is>
       </c>
       <c r="B50" s="33">
-        <f>COUNTIF(Artikelstamm!$G$3:$G$320,$A50)</f>
+        <f>COUNTIF(Artikelstamm!$G$3:$G$327,$A50)</f>
         <v/>
       </c>
       <c r="C50" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$320=$A50)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$G$3:$G$327=$A50)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D50" s="34">
-        <f>SUMIF(Artikelstamm!$G$3:$G$320,$A50,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$G$3:$G$327,$A50,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40838,15 +41663,15 @@
         </is>
       </c>
       <c r="B55" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A55)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A55)</f>
         <v/>
       </c>
       <c r="C55" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A55)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A55)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D55" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A55,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A55,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40857,15 +41682,15 @@
         </is>
       </c>
       <c r="B56" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A56)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A56)</f>
         <v/>
       </c>
       <c r="C56" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A56)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A56)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D56" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A56,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A56,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40876,15 +41701,15 @@
         </is>
       </c>
       <c r="B57" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A57)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A57)</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A57)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A57)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D57" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A57,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A57,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40895,15 +41720,15 @@
         </is>
       </c>
       <c r="B58" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A58)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A58)</f>
         <v/>
       </c>
       <c r="C58" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A58)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A58)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D58" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A58,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A58,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40914,15 +41739,15 @@
         </is>
       </c>
       <c r="B59" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A59)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A59)</f>
         <v/>
       </c>
       <c r="C59" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A59)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A59)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D59" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A59,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A59,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40933,15 +41758,15 @@
         </is>
       </c>
       <c r="B60" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A60)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A60)</f>
         <v/>
       </c>
       <c r="C60" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A60)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A60)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D60" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A60,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A60,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
@@ -40952,562 +41777,581 @@
         </is>
       </c>
       <c r="B61" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A61)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A61)</f>
         <v/>
       </c>
       <c r="C61" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A61)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A61)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D61" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A61,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A61,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="26" t="inlineStr">
         <is>
-          <t>Galerie</t>
+          <t>Flur 3</t>
         </is>
       </c>
       <c r="B62" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A62)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A62)</f>
         <v/>
       </c>
       <c r="C62" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A62)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A62)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D62" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A62,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A62,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="26" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Galerie</t>
         </is>
       </c>
       <c r="B63" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A63)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A63)</f>
         <v/>
       </c>
       <c r="C63" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A63)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A63)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D63" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A63,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A63,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="26" t="inlineStr">
         <is>
-          <t>Gartenanlage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="B64" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A64)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A64)</f>
         <v/>
       </c>
       <c r="C64" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A64)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A64)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D64" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A64,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A64,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum</t>
+          <t>Gartenanlage</t>
         </is>
       </c>
       <c r="B65" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A65)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A65)</f>
         <v/>
       </c>
       <c r="C65" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A65)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A65)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D65" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A65,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A65,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 2</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="B66" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A66)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A66)</f>
         <v/>
       </c>
       <c r="C66" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A66)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A66)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D66" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A66,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A66,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Gruppenraum 2</t>
         </is>
       </c>
       <c r="B67" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A67)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A67)</f>
         <v/>
       </c>
       <c r="C67" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A67)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A67)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D67" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A67,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A67,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="26" t="inlineStr">
         <is>
-          <t>Gruppenraum 5</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="B68" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A68)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A68)</f>
         <v/>
       </c>
       <c r="C68" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A68)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A68)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D68" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A68,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A68,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="26" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Gruppenraum 5</t>
         </is>
       </c>
       <c r="B69" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A69)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A69)</f>
         <v/>
       </c>
       <c r="C69" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A69)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A69)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D69" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A69,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A69,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="26" t="inlineStr">
         <is>
-          <t>Küche</t>
+          <t>Klassenzimmer</t>
         </is>
       </c>
       <c r="B70" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A70)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A70)</f>
         <v/>
       </c>
       <c r="C70" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A70)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A70)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D70" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A70,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A70,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="26" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Küche</t>
         </is>
       </c>
       <c r="B71" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A71)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A71)</f>
         <v/>
       </c>
       <c r="C71" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A71)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A71)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D71" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A71,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A71,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="26" t="inlineStr">
         <is>
-          <t>Personal</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="B72" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A72)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A72)</f>
         <v/>
       </c>
       <c r="C72" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A72)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A72)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D72" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A72,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A72,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="26" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Personal</t>
         </is>
       </c>
       <c r="B73" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A73)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A73)</f>
         <v/>
       </c>
       <c r="C73" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A73)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A73)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D73" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A73,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A73,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 4</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="B74" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A74)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A74)</f>
         <v/>
       </c>
       <c r="C74" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A74)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A74)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D74" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A74,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A74,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="26" t="inlineStr">
         <is>
-          <t>Schlafraum 5</t>
+          <t>Schlafraum 4</t>
         </is>
       </c>
       <c r="B75" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A75)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A75)</f>
         <v/>
       </c>
       <c r="C75" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A75)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A75)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D75" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A75,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A75,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="26" t="inlineStr">
         <is>
-          <t>Speisesaal</t>
+          <t>Schlafraum 5</t>
         </is>
       </c>
       <c r="B76" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A76)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A76)</f>
         <v/>
       </c>
       <c r="C76" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A76)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A76)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D76" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A76,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A76,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="26" t="inlineStr">
         <is>
-          <t>Terrasse</t>
+          <t>Speisesaal</t>
         </is>
       </c>
       <c r="B77" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A77)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A77)</f>
         <v/>
       </c>
       <c r="C77" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A77)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A77)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D77" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A77,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A77,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="26" t="inlineStr">
         <is>
-          <t>Treppenraum 1</t>
+          <t>Terrasse</t>
         </is>
       </c>
       <c r="B78" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A78)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A78)</f>
         <v/>
       </c>
       <c r="C78" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A78)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A78)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D78" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A78,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A78,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="26" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Treppenraum 1</t>
         </is>
       </c>
       <c r="B79" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A79)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A79)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A79)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A79)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D79" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A79,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A79,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="26" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="B80" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A80)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A80)</f>
         <v/>
       </c>
       <c r="C80" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A80)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A80)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D80" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A80,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A80,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="26" t="inlineStr">
         <is>
-          <t>WC Personal</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B81" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A81)</f>
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A81)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A81)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A81)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
       <c r="D81" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A81,Artikelstamm!$U$3:$U$320)</f>
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A81,Artikelstamm!$U$3:$U$327)</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="26" t="inlineStr">
         <is>
+          <t>WC Personal</t>
+        </is>
+      </c>
+      <c r="B82" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A82)</f>
+        <v/>
+      </c>
+      <c r="C82" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A82)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
+        <v/>
+      </c>
+      <c r="D82" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A82,Artikelstamm!$U$3:$U$327)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="26" t="inlineStr">
+        <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="B82" s="33">
-        <f>COUNTIF(Artikelstamm!$H$3:$H$320,$A82)</f>
-        <v/>
-      </c>
-      <c r="C82" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$320=$A82)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
-        <v/>
-      </c>
-      <c r="D82" s="34">
-        <f>SUMIF(Artikelstamm!$H$3:$H$320,$A82,Artikelstamm!$U$3:$U$320)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="28" t="inlineStr">
+      <c r="B83" s="33">
+        <f>COUNTIF(Artikelstamm!$H$3:$H$327,$A83)</f>
+        <v/>
+      </c>
+      <c r="C83" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$H$3:$H$327=$A83)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
+        <v/>
+      </c>
+      <c r="D83" s="34">
+        <f>SUMIF(Artikelstamm!$H$3:$H$327,$A83,Artikelstamm!$U$3:$U$327)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B83" s="35">
-        <f>SUM(B55:B82)</f>
-        <v/>
-      </c>
-      <c r="C83" s="36">
-        <f>SUM(C55:C82)</f>
-        <v/>
-      </c>
-      <c r="D83" s="36">
-        <f>SUM(D55:D82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="25" t="inlineStr">
+      <c r="B84" s="35">
+        <f>SUM(B55:B83)</f>
+        <v/>
+      </c>
+      <c r="C84" s="36">
+        <f>SUM(C55:C83)</f>
+        <v/>
+      </c>
+      <c r="D84" s="36">
+        <f>SUM(D55:D83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="25" t="inlineStr">
         <is>
           <t>Nach Verkaufskanal</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="32" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="32" t="inlineStr">
         <is>
           <t>Verkaufskanal</t>
         </is>
       </c>
-      <c r="B86" s="32" t="inlineStr">
+      <c r="B87" s="32" t="inlineStr">
         <is>
           <t>Positionen</t>
         </is>
       </c>
-      <c r="C86" s="32" t="inlineStr">
+      <c r="C87" s="32" t="inlineStr">
         <is>
           <t>Umsatz netto</t>
         </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="26" t="inlineStr">
-        <is>
-          <t>Klinik</t>
-        </is>
-      </c>
-      <c r="B87" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A87)</f>
-        <v/>
-      </c>
-      <c r="C87" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A87)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
-        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="26" t="inlineStr">
         <is>
-          <t>Kleinanzeigen</t>
+          <t>Klinik</t>
         </is>
       </c>
       <c r="B88" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A88)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$327,$A88)</f>
         <v/>
       </c>
       <c r="C88" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A88)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$327=$A88)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="26" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Kleinanzeigen</t>
         </is>
       </c>
       <c r="B89" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A89)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$327,$A89)</f>
         <v/>
       </c>
       <c r="C89" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A89)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$327=$A89)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="26" t="inlineStr">
         <is>
-          <t>Direkt</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="B90" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A90)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$327,$A90)</f>
         <v/>
       </c>
       <c r="C90" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A90)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$327=$A90)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="26" t="inlineStr">
         <is>
-          <t>Händler</t>
+          <t>Direkt</t>
         </is>
       </c>
       <c r="B91" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A91)</f>
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$327,$A91)</f>
         <v/>
       </c>
       <c r="C91" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A91)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$327=$A91)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="26" t="inlineStr">
         <is>
+          <t>Händler</t>
+        </is>
+      </c>
+      <c r="B92" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$327,$A92)</f>
+        <v/>
+      </c>
+      <c r="C92" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$327=$A92)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="26" t="inlineStr">
+        <is>
           <t>Verkaufstag</t>
         </is>
       </c>
-      <c r="B92" s="33">
-        <f>COUNTIF(Artikelstamm!$AC$3:$AC$320,$A92)</f>
-        <v/>
-      </c>
-      <c r="C92" s="34">
-        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$320=$A92)*Artikelstamm!$K$3:$K$320*Artikelstamm!$AE$3:$AE$320)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="28" t="inlineStr">
+      <c r="B93" s="33">
+        <f>COUNTIF(Artikelstamm!$AC$3:$AC$327,$A93)</f>
+        <v/>
+      </c>
+      <c r="C93" s="34">
+        <f>SUMPRODUCT((Artikelstamm!$AC$3:$AC$327=$A93)*Artikelstamm!$K$3:$K$327*Artikelstamm!$AE$3:$AE$327)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="28" t="inlineStr">
         <is>
           <t>Summe</t>
         </is>
       </c>
-      <c r="B93" s="35">
-        <f>SUM(B87:B92)</f>
-        <v/>
-      </c>
-      <c r="C93" s="36">
-        <f>SUM(C87:C92)</f>
+      <c r="B94" s="35">
+        <f>SUM(B88:B93)</f>
+        <v/>
+      </c>
+      <c r="C94" s="36">
+        <f>SUM(C88:C93)</f>
         <v/>
       </c>
     </row>

--- a/ausgabe/01_Artikelstamm_kikripp.xlsx
+++ b/ausgabe/01_Artikelstamm_kikripp.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$327</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Artikelstamm'!$A$2:$AN$335</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1019,7 +1019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN327"/>
+  <dimension ref="A1:AN335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5129,7 +5129,7 @@
       <c r="AL33" s="19" t="n"/>
       <c r="AM33" s="16" t="inlineStr">
         <is>
-          <t>1 Kübel im Bild (Bepflanzung enthalten)</t>
+          <t>1 Kübel einschließlich Bepflanzung. Der Kübel steht inzwischen im Schlafraum 5 (NU04) – die Nummer BU04-02 bleibt.</t>
         </is>
       </c>
       <c r="AN33" s="22" t="n"/>
@@ -5411,7 +5411,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>BU04-05</t>
+          <t>BU04-16</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="X36" s="19" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="Y36" s="19" t="n"/>
@@ -5529,7 +5529,11 @@
           <t>1 Set im Bild</t>
         </is>
       </c>
-      <c r="AN36" s="22" t="n"/>
+      <c r="AN36" s="22" t="inlineStr">
+        <is>
+          <t>OFFEN: NICHT VEROEFFENTLICHEN, bis geklaert ist, ob das Set noch da ist. Auf dem Erfassungsblatt BU04 ist die Zeile durchgestrichen, die Nummer BU04-05 klebt jetzt auf den Hochstuehlen. Frueher BU04-05 / K-117.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="15" t="inlineStr">
@@ -23603,7 +23607,11 @@
         </is>
       </c>
       <c r="B185" s="15" t="n"/>
-      <c r="C185" s="15" t="n"/>
+      <c r="C185" s="15" t="inlineStr">
+        <is>
+          <t>BU04-05</t>
+        </is>
+      </c>
       <c r="D185" s="15" t="inlineStr">
         <is>
           <t>NU03</t>
@@ -23616,7 +23624,7 @@
       </c>
       <c r="F185" s="16" t="inlineStr">
         <is>
-          <t>Kinderhochstuhl von IKEA: weiße Kunststoffschale, graue Stahlbeine, Sicherheitsgurt. Ohne Esstablett.</t>
+          <t>Kinderhochstuhl von IKEA: weiße Kunststoffschale, graue Stahlbeine, Sicherheitsgurt. Ein Teil der Stühle hat ein Esstablett.</t>
         </is>
       </c>
       <c r="G185" s="15" t="inlineStr">
@@ -23635,7 +23643,7 @@
         </is>
       </c>
       <c r="J185" s="17" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="K185" s="17" t="n"/>
       <c r="L185" s="18">
@@ -23714,12 +23722,12 @@
       <c r="AL185" s="19" t="n"/>
       <c r="AM185" s="16" t="inlineStr">
         <is>
-          <t>9 Stühle – abgebildet ist einer davon.</t>
+          <t>19 Stühle insgesamt: 9 im Schlafraum 4 (NU03-10, ohne Esstablett) und 10 im Gruppenraum im Untergeschoss (BU04-05, mit Esstablett). Abgebildet ist einer der Stühle ohne Tablett; die gestapelten Stühle mit Tablett sind auf Foto F-396 zu sehen.</t>
         </is>
       </c>
       <c r="AN185" s="22" t="inlineStr">
         <is>
-          <t>OFFEN: waechst noch. Aus weiteren Raeumen kommen zusaetzliche Hochstuehle dazu - am Ende des Rundgangs auf die Gesamtzahl bringen und die Post-it-Nummern der anderen Raeume in Weitere_ArtNr.</t>
+          <t>OFFEN: waechst noch. Aus weiteren Raeumen kommen zusaetzliche Hochstuehle dazu - am Ende des Rundgangs auf die Gesamtzahl bringen und die Post-it-Nummern in Weitere_ArtNr ergaenzen. Bisher: BU04-05.</t>
         </is>
       </c>
     </row>
@@ -30397,7 +30405,7 @@
       <c r="B241" s="15" t="n"/>
       <c r="C241" s="15" t="inlineStr">
         <is>
-          <t>BA04-09, BU02-14</t>
+          <t>BA04-09, BU02-14, BU04-12</t>
         </is>
       </c>
       <c r="D241" s="15" t="inlineStr">
@@ -30431,7 +30439,7 @@
         </is>
       </c>
       <c r="J241" s="17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K241" s="17" t="n"/>
       <c r="L241" s="18">
@@ -30510,12 +30518,12 @@
       <c r="AL241" s="19" t="n"/>
       <c r="AM241" s="16" t="inlineStr">
         <is>
-          <t>6 Schränke insgesamt: 2 im Flur 2 der Attika (BA02-08), 2 im Gruppenraum 4 (BA04-09) und 2 im Flur 2 im Untergeschoss des Bestandsgebäudes (BU02-14). Die beiden Schränke im Untergeschoss sind auf Foto F-378 zu sehen.</t>
+          <t>8 Schränke insgesamt: 2 im Flur 2 der Attika (BA02-08), 2 im Gruppenraum 4 (BA04-09), 2 im Flur 2 im Untergeschoss (BU02-14, Foto F-378) und 2 im Gruppenraum im Untergeschoss (BU04-12, Foto F-401). Die beiden Schränke im Gruppenraum sind stark gebraucht.</t>
         </is>
       </c>
       <c r="AN241" s="22" t="inlineStr">
         <is>
-          <t>Zusammengefasste Position über drei Räume – Post-it-Nummern: BA04-09, BU02-14.</t>
+          <t>Zusammengefasste Position über vier Räume – Post-it-Nummern: BA04-09, BU02-14, BU04-12.</t>
         </is>
       </c>
     </row>
@@ -39821,7 +39829,11 @@
         </is>
       </c>
       <c r="B319" s="15" t="n"/>
-      <c r="C319" s="15" t="n"/>
+      <c r="C319" s="15" t="inlineStr">
+        <is>
+          <t>BU04-09</t>
+        </is>
+      </c>
       <c r="D319" s="15" t="inlineStr">
         <is>
           <t>BU02</t>
@@ -39853,7 +39865,7 @@
         </is>
       </c>
       <c r="J319" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K319" s="17" t="n"/>
       <c r="L319" s="18">
@@ -39928,10 +39940,14 @@
       <c r="AL319" s="19" t="n"/>
       <c r="AM319" s="16" t="inlineStr">
         <is>
-          <t>1 Kombination aus drei Teilen einschließlich der Wannen. Das Spielzeug gehört nicht dazu.</t>
-        </is>
-      </c>
-      <c r="AN319" s="22" t="n"/>
+          <t>2 Kombinationen aus je drei Teilen einschließlich der Wannen: 1 im Flur 2 (BU02-19, Foto F-385) und 1 im Gruppenraum (BU04-09, Foto F-399), beide im Untergeschoss des Bestandsgebäudes. Die beiden Kombinationen sind unterschiedlich zusammengestellt. Das Spielzeug gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN319" s="22" t="inlineStr">
+        <is>
+          <t>Zusammengefasste Position über zwei Räume – Post-it-Nummer: BU04-09.</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="30" customHeight="1">
       <c r="A320" s="15" t="inlineStr">
@@ -40885,8 +40901,964 @@
       </c>
       <c r="AN327" s="22" t="n"/>
     </row>
+    <row r="328" ht="30" customHeight="1">
+      <c r="A328" s="15" t="inlineStr">
+        <is>
+          <t>BU04-06</t>
+        </is>
+      </c>
+      <c r="B328" s="15" t="n"/>
+      <c r="C328" s="15" t="n"/>
+      <c r="D328" s="15" t="inlineStr">
+        <is>
+          <t>BU04</t>
+        </is>
+      </c>
+      <c r="E328" s="15" t="inlineStr">
+        <is>
+          <t>Kindertisch weiß, lang, zweiteilig</t>
+        </is>
+      </c>
+      <c r="F328" s="16" t="inlineStr">
+        <is>
+          <t>Langer Kindertisch aus zwei aneinandergestellten Platten in Weiß mit cremefarbener Kante, auf cremefarbenen Vierkantfüßen aus Metall mit Gleitern. Die Platten sind an den Kanten abgestoßen.</t>
+        </is>
+      </c>
+      <c r="G328" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H328" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="I328" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J328" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K328" s="17" t="n"/>
+      <c r="L328" s="18">
+        <f>J328-IF(K328="",0,K328)</f>
+        <v/>
+      </c>
+      <c r="M328" s="15" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N328" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O328" s="19" t="n"/>
+      <c r="P328" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q328" s="19" t="n"/>
+      <c r="R328" s="20" t="n"/>
+      <c r="S328" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="T328" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U328" s="21">
+        <f>L328*S328</f>
+        <v/>
+      </c>
+      <c r="V328" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W328" s="15" t="inlineStr">
+        <is>
+          <t>F-406</t>
+        </is>
+      </c>
+      <c r="X328" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y328" s="19" t="n"/>
+      <c r="Z328" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA328" s="19" t="n"/>
+      <c r="AB328" s="19" t="n"/>
+      <c r="AC328" s="19" t="n"/>
+      <c r="AD328" s="19" t="n"/>
+      <c r="AE328" s="20" t="n"/>
+      <c r="AF328" s="21">
+        <f>IF(K328="","",K328*AE328)</f>
+        <v/>
+      </c>
+      <c r="AG328" s="19" t="n"/>
+      <c r="AH328" s="19" t="n"/>
+      <c r="AI328" s="19" t="n"/>
+      <c r="AJ328" s="19" t="n"/>
+      <c r="AK328" s="19" t="n"/>
+      <c r="AL328" s="19" t="n"/>
+      <c r="AM328" s="16" t="inlineStr">
+        <is>
+          <t>1 Tisch aus zwei Platten. Das Spielzeug gehört nicht dazu. Der ganze Tisch ist auf Foto F-404 zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN328" s="22" t="n"/>
+    </row>
+    <row r="329" ht="30" customHeight="1">
+      <c r="A329" s="15" t="inlineStr">
+        <is>
+          <t>BU04-07</t>
+        </is>
+      </c>
+      <c r="B329" s="15" t="n"/>
+      <c r="C329" s="15" t="n"/>
+      <c r="D329" s="15" t="inlineStr">
+        <is>
+          <t>BU04</t>
+        </is>
+      </c>
+      <c r="E329" s="15" t="inlineStr">
+        <is>
+          <t>Gemälde Schwarzwaldfrau mit Planeten</t>
+        </is>
+      </c>
+      <c r="F329" s="16" t="inlineStr">
+        <is>
+          <t>Acryl auf Leinwand im Hochformat: Frau in Schwarzwälder Tracht mit Bollenhut, umgeben von gemalten Planeten und Sternen. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="G329" s="15" t="inlineStr">
+        <is>
+          <t>Kunst</t>
+        </is>
+      </c>
+      <c r="H329" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="I329" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J329" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K329" s="17" t="n"/>
+      <c r="L329" s="18">
+        <f>J329-IF(K329="",0,K329)</f>
+        <v/>
+      </c>
+      <c r="M329" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N329" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O329" s="19" t="n"/>
+      <c r="P329" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q329" s="19" t="n"/>
+      <c r="R329" s="20" t="n"/>
+      <c r="S329" s="20" t="n">
+        <v>250</v>
+      </c>
+      <c r="T329" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U329" s="21">
+        <f>L329*S329</f>
+        <v/>
+      </c>
+      <c r="V329" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W329" s="15" t="inlineStr">
+        <is>
+          <t>F-397</t>
+        </is>
+      </c>
+      <c r="X329" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y329" s="19" t="n"/>
+      <c r="Z329" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA329" s="19" t="n"/>
+      <c r="AB329" s="19" t="inlineStr">
+        <is>
+          <t>Schwarzwald</t>
+        </is>
+      </c>
+      <c r="AC329" s="19" t="n"/>
+      <c r="AD329" s="19" t="n"/>
+      <c r="AE329" s="20" t="n"/>
+      <c r="AF329" s="21">
+        <f>IF(K329="","",K329*AE329)</f>
+        <v/>
+      </c>
+      <c r="AG329" s="19" t="n"/>
+      <c r="AH329" s="19" t="n"/>
+      <c r="AI329" s="19" t="n"/>
+      <c r="AJ329" s="19" t="n"/>
+      <c r="AK329" s="19" t="n"/>
+      <c r="AL329" s="19" t="n"/>
+      <c r="AM329" s="16" t="inlineStr">
+        <is>
+          <t>1 Bild auf Keilrahmen, ungerahmt.</t>
+        </is>
+      </c>
+      <c r="AN329" s="22" t="n"/>
+    </row>
+    <row r="330" ht="30" customHeight="1">
+      <c r="A330" s="15" t="inlineStr">
+        <is>
+          <t>BU04-08</t>
+        </is>
+      </c>
+      <c r="B330" s="15" t="n"/>
+      <c r="C330" s="15" t="n"/>
+      <c r="D330" s="15" t="inlineStr">
+        <is>
+          <t>BU04</t>
+        </is>
+      </c>
+      <c r="E330" s="15" t="inlineStr">
+        <is>
+          <t>Garderobenständer bunt, Stangenform</t>
+        </is>
+      </c>
+      <c r="F330" s="16" t="inlineStr">
+        <is>
+          <t>Stehender Garderobenständer: weiße Rundstange mit farbig lackierten Ringen in Grün, Blau, Rot, Orange und Gelb und passenden Haken in mehreren Höhen, auf Tellerfuß.</t>
+        </is>
+      </c>
+      <c r="G330" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H330" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="I330" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J330" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K330" s="17" t="n"/>
+      <c r="L330" s="18">
+        <f>J330-IF(K330="",0,K330)</f>
+        <v/>
+      </c>
+      <c r="M330" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N330" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O330" s="19" t="n"/>
+      <c r="P330" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q330" s="19" t="n"/>
+      <c r="R330" s="20" t="n"/>
+      <c r="S330" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="T330" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U330" s="21">
+        <f>L330*S330</f>
+        <v/>
+      </c>
+      <c r="V330" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W330" s="15" t="inlineStr">
+        <is>
+          <t>F-398</t>
+        </is>
+      </c>
+      <c r="X330" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y330" s="19" t="n"/>
+      <c r="Z330" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA330" s="19" t="n"/>
+      <c r="AB330" s="19" t="n"/>
+      <c r="AC330" s="19" t="n"/>
+      <c r="AD330" s="19" t="n"/>
+      <c r="AE330" s="20" t="n"/>
+      <c r="AF330" s="21">
+        <f>IF(K330="","",K330*AE330)</f>
+        <v/>
+      </c>
+      <c r="AG330" s="19" t="n"/>
+      <c r="AH330" s="19" t="n"/>
+      <c r="AI330" s="19" t="n"/>
+      <c r="AJ330" s="19" t="n"/>
+      <c r="AK330" s="19" t="n"/>
+      <c r="AL330" s="19" t="n"/>
+      <c r="AM330" s="16" t="inlineStr">
+        <is>
+          <t>2 Ständer – beide auf dem Foto zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN330" s="22" t="n"/>
+    </row>
+    <row r="331" ht="30" customHeight="1">
+      <c r="A331" s="15" t="inlineStr">
+        <is>
+          <t>BU04-10</t>
+        </is>
+      </c>
+      <c r="B331" s="15" t="n"/>
+      <c r="C331" s="15" t="n"/>
+      <c r="D331" s="15" t="inlineStr">
+        <is>
+          <t>BU04</t>
+        </is>
+      </c>
+      <c r="E331" s="15" t="inlineStr">
+        <is>
+          <t>Kindertisch weiß aus fünf Segmenten</t>
+        </is>
+      </c>
+      <c r="F331" s="16" t="inlineStr">
+        <is>
+          <t>Fünf Tischsegmente mit weißer Platte, Multiplex-Kante und verchromten Rundfüßen in Kinderhöhe. Zusammengestellt ergeben sie einen großen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
+        </is>
+      </c>
+      <c r="G331" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H331" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="I331" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J331" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K331" s="17" t="n"/>
+      <c r="L331" s="18">
+        <f>J331-IF(K331="",0,K331)</f>
+        <v/>
+      </c>
+      <c r="M331" s="15" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="N331" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O331" s="19" t="n"/>
+      <c r="P331" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q331" s="19" t="n"/>
+      <c r="R331" s="20" t="n"/>
+      <c r="S331" s="20" t="n">
+        <v>190</v>
+      </c>
+      <c r="T331" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U331" s="21">
+        <f>L331*S331</f>
+        <v/>
+      </c>
+      <c r="V331" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W331" s="15" t="inlineStr">
+        <is>
+          <t>F-400</t>
+        </is>
+      </c>
+      <c r="X331" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y331" s="19" t="n"/>
+      <c r="Z331" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA331" s="19" t="n"/>
+      <c r="AB331" s="19" t="n"/>
+      <c r="AC331" s="19" t="n"/>
+      <c r="AD331" s="19" t="n"/>
+      <c r="AE331" s="20" t="n"/>
+      <c r="AF331" s="21">
+        <f>IF(K331="","",K331*AE331)</f>
+        <v/>
+      </c>
+      <c r="AG331" s="19" t="n"/>
+      <c r="AH331" s="19" t="n"/>
+      <c r="AI331" s="19" t="n"/>
+      <c r="AJ331" s="19" t="n"/>
+      <c r="AK331" s="19" t="n"/>
+      <c r="AL331" s="19" t="n"/>
+      <c r="AM331" s="16" t="inlineStr">
+        <is>
+          <t>1 Tischgruppe aus fünf Segmenten. Weitere Tischgruppen gleicher Bauart stehen unter NU02-23 und BU02-03.</t>
+        </is>
+      </c>
+      <c r="AN331" s="22" t="n"/>
+    </row>
+    <row r="332" ht="30" customHeight="1">
+      <c r="A332" s="15" t="inlineStr">
+        <is>
+          <t>BU04-11</t>
+        </is>
+      </c>
+      <c r="B332" s="15" t="n"/>
+      <c r="C332" s="15" t="n"/>
+      <c r="D332" s="15" t="inlineStr">
+        <is>
+          <t>BU04</t>
+        </is>
+      </c>
+      <c r="E332" s="15" t="inlineStr">
+        <is>
+          <t>Regal weiß, vier Böden</t>
+        </is>
+      </c>
+      <c r="F332" s="16" t="inlineStr">
+        <is>
+          <t>Offenes Regal in Weiß mit vier Böden, eines der beiden Regale hat zusätzlich zwei Schubladen. Böden und Kanten sind großflächig verschmutzt und abgestoßen.</t>
+        </is>
+      </c>
+      <c r="G332" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H332" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="I332" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J332" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K332" s="17" t="n"/>
+      <c r="L332" s="18">
+        <f>J332-IF(K332="",0,K332)</f>
+        <v/>
+      </c>
+      <c r="M332" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N332" s="15" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="O332" s="19" t="n"/>
+      <c r="P332" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q332" s="19" t="n"/>
+      <c r="R332" s="20" t="n"/>
+      <c r="S332" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T332" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U332" s="21">
+        <f>L332*S332</f>
+        <v/>
+      </c>
+      <c r="V332" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W332" s="15" t="inlineStr">
+        <is>
+          <t>F-405</t>
+        </is>
+      </c>
+      <c r="X332" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y332" s="19" t="n"/>
+      <c r="Z332" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA332" s="19" t="n"/>
+      <c r="AB332" s="19" t="n"/>
+      <c r="AC332" s="19" t="n"/>
+      <c r="AD332" s="19" t="n"/>
+      <c r="AE332" s="20" t="n"/>
+      <c r="AF332" s="21">
+        <f>IF(K332="","",K332*AE332)</f>
+        <v/>
+      </c>
+      <c r="AG332" s="19" t="n"/>
+      <c r="AH332" s="19" t="n"/>
+      <c r="AI332" s="19" t="n"/>
+      <c r="AJ332" s="19" t="n"/>
+      <c r="AK332" s="19" t="n"/>
+      <c r="AL332" s="19" t="n"/>
+      <c r="AM332" s="16" t="inlineStr">
+        <is>
+          <t>2 Regale, davon eines mit zwei Schubladen – abgebildet ist eines davon. Der Inhalt gehört nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN332" s="22" t="n"/>
+    </row>
+    <row r="333" ht="30" customHeight="1">
+      <c r="A333" s="15" t="inlineStr">
+        <is>
+          <t>BU04-13</t>
+        </is>
+      </c>
+      <c r="B333" s="15" t="n"/>
+      <c r="C333" s="15" t="n"/>
+      <c r="D333" s="15" t="inlineStr">
+        <is>
+          <t>BU04</t>
+        </is>
+      </c>
+      <c r="E333" s="15" t="inlineStr">
+        <is>
+          <t>Servierwagen Metall grau, drei Ebenen</t>
+        </is>
+      </c>
+      <c r="F333" s="16" t="inlineStr">
+        <is>
+          <t>Rollwagen aus dunkelgrau lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
+        </is>
+      </c>
+      <c r="G333" s="15" t="inlineStr">
+        <is>
+          <t>Möbel</t>
+        </is>
+      </c>
+      <c r="H333" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="I333" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J333" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K333" s="17" t="n"/>
+      <c r="L333" s="18">
+        <f>J333-IF(K333="",0,K333)</f>
+        <v/>
+      </c>
+      <c r="M333" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N333" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O333" s="19" t="n"/>
+      <c r="P333" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q333" s="19" t="n"/>
+      <c r="R333" s="20" t="n"/>
+      <c r="S333" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="T333" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U333" s="21">
+        <f>L333*S333</f>
+        <v/>
+      </c>
+      <c r="V333" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W333" s="15" t="inlineStr">
+        <is>
+          <t>F-402</t>
+        </is>
+      </c>
+      <c r="X333" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y333" s="19" t="n"/>
+      <c r="Z333" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA333" s="19" t="n"/>
+      <c r="AB333" s="19" t="n"/>
+      <c r="AC333" s="19" t="n"/>
+      <c r="AD333" s="19" t="n"/>
+      <c r="AE333" s="20" t="n"/>
+      <c r="AF333" s="21">
+        <f>IF(K333="","",K333*AE333)</f>
+        <v/>
+      </c>
+      <c r="AG333" s="19" t="n"/>
+      <c r="AH333" s="19" t="n"/>
+      <c r="AI333" s="19" t="n"/>
+      <c r="AJ333" s="19" t="n"/>
+      <c r="AK333" s="19" t="n"/>
+      <c r="AL333" s="19" t="n"/>
+      <c r="AM333" s="16" t="inlineStr">
+        <is>
+          <t>1 Wagen. Der Inhalt gehört nicht dazu. Ein baugleicher Wagen in Schwarz steht unter BU02-16.</t>
+        </is>
+      </c>
+      <c r="AN333" s="22" t="n"/>
+    </row>
+    <row r="334" ht="30" customHeight="1">
+      <c r="A334" s="15" t="inlineStr">
+        <is>
+          <t>BU04-14</t>
+        </is>
+      </c>
+      <c r="B334" s="15" t="n"/>
+      <c r="C334" s="15" t="n"/>
+      <c r="D334" s="15" t="inlineStr">
+        <is>
+          <t>BU04</t>
+        </is>
+      </c>
+      <c r="E334" s="15" t="inlineStr">
+        <is>
+          <t>Bücherregal creme mit Wolkenaufsatz</t>
+        </is>
+      </c>
+      <c r="F334" s="16" t="inlineStr">
+        <is>
+          <t>Stehendes Bücherregal aus Holz, creme lackiert, mit geschwungenem Wolkenaufsatz und drei Ablagen mit vorderer Haltelatte für nach vorn zeigende Bilderbücher.</t>
+        </is>
+      </c>
+      <c r="G334" s="15" t="inlineStr">
+        <is>
+          <t>Kita-Ausstattung</t>
+        </is>
+      </c>
+      <c r="H334" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="I334" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J334" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K334" s="17" t="n"/>
+      <c r="L334" s="18">
+        <f>J334-IF(K334="",0,K334)</f>
+        <v/>
+      </c>
+      <c r="M334" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N334" s="15" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="O334" s="19" t="n"/>
+      <c r="P334" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q334" s="19" t="n"/>
+      <c r="R334" s="20" t="n"/>
+      <c r="S334" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="T334" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U334" s="21">
+        <f>L334*S334</f>
+        <v/>
+      </c>
+      <c r="V334" s="15" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="W334" s="15" t="inlineStr">
+        <is>
+          <t>F-403</t>
+        </is>
+      </c>
+      <c r="X334" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y334" s="19" t="n"/>
+      <c r="Z334" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA334" s="19" t="n"/>
+      <c r="AB334" s="19" t="n"/>
+      <c r="AC334" s="19" t="n"/>
+      <c r="AD334" s="19" t="n"/>
+      <c r="AE334" s="20" t="n"/>
+      <c r="AF334" s="21">
+        <f>IF(K334="","",K334*AE334)</f>
+        <v/>
+      </c>
+      <c r="AG334" s="19" t="n"/>
+      <c r="AH334" s="19" t="n"/>
+      <c r="AI334" s="19" t="n"/>
+      <c r="AJ334" s="19" t="n"/>
+      <c r="AK334" s="19" t="n"/>
+      <c r="AL334" s="19" t="n"/>
+      <c r="AM334" s="16" t="inlineStr">
+        <is>
+          <t>1 Regal. Die Bücher gehören nicht dazu.</t>
+        </is>
+      </c>
+      <c r="AN334" s="22" t="n"/>
+    </row>
+    <row r="335" ht="30" customHeight="1">
+      <c r="A335" s="15" t="inlineStr">
+        <is>
+          <t>BU04-15</t>
+        </is>
+      </c>
+      <c r="B335" s="15" t="n"/>
+      <c r="C335" s="15" t="n"/>
+      <c r="D335" s="15" t="inlineStr">
+        <is>
+          <t>BU04</t>
+        </is>
+      </c>
+      <c r="E335" s="15" t="inlineStr">
+        <is>
+          <t>Acrylbilder Roboter, schwarz-weiß</t>
+        </is>
+      </c>
+      <c r="F335" s="16" t="inlineStr">
+        <is>
+          <t>Zwei Bilder auf Leinwand im Quadrat: Roboterfiguren mit breitem Pinsel in Schwarz auf weißem Grund. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="G335" s="15" t="inlineStr">
+        <is>
+          <t>Kunst</t>
+        </is>
+      </c>
+      <c r="H335" s="15" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="I335" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J335" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K335" s="17" t="n"/>
+      <c r="L335" s="18">
+        <f>J335-IF(K335="",0,K335)</f>
+        <v/>
+      </c>
+      <c r="M335" s="15" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="N335" s="15" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="O335" s="19" t="n"/>
+      <c r="P335" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Q335" s="19" t="n"/>
+      <c r="R335" s="20" t="n"/>
+      <c r="S335" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="T335" s="19" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="U335" s="21">
+        <f>L335*S335</f>
+        <v/>
+      </c>
+      <c r="V335" s="15" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="W335" s="15" t="inlineStr">
+        <is>
+          <t>F-407</t>
+        </is>
+      </c>
+      <c r="X335" s="19" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="Y335" s="19" t="n"/>
+      <c r="Z335" s="19" t="inlineStr">
+        <is>
+          <t>verfügbar</t>
+        </is>
+      </c>
+      <c r="AA335" s="19" t="n"/>
+      <c r="AB335" s="19" t="n"/>
+      <c r="AC335" s="19" t="n"/>
+      <c r="AD335" s="19" t="n"/>
+      <c r="AE335" s="20" t="n"/>
+      <c r="AF335" s="21">
+        <f>IF(K335="","",K335*AE335)</f>
+        <v/>
+      </c>
+      <c r="AG335" s="19" t="n"/>
+      <c r="AH335" s="19" t="n"/>
+      <c r="AI335" s="19" t="n"/>
+      <c r="AJ335" s="19" t="n"/>
+      <c r="AK335" s="19" t="n"/>
+      <c r="AL335" s="19" t="n"/>
+      <c r="AM335" s="16" t="inlineStr">
+        <is>
+          <t>2 Bilder auf Keilrahmen, ungerahmt – beide auf dem Foto zu sehen.</t>
+        </is>
+      </c>
+      <c r="AN335" s="22" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:AN327"/>
+  <autoFilter ref="A2:AN335"/>
   <mergeCells count="7">
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="V1:AD1"/>
@@ -40896,7 +41868,7 @@
     <mergeCell ref="AE1:AH1"/>
     <mergeCell ref="AM1:AN1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Z3:Z327">
+  <conditionalFormatting sqref="Z3:Z335">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"reserviert"</formula>
     </cfRule>
@@ -40907,12 +41879,12 @@
       <formula>"verkauft"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I3:I327">
+  <conditionalFormatting sqref="I3:I335">
     <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
       <formula>"A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P327">
+  <conditionalFormatting sqref="P3:P335">
     <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
       <formula>"entfällt"</formula>
     </cfRule>
@@ -41003,7 +41975,7 @@
         </is>
       </c>
       <c r="B5" s="27">
-        <f>COUNTA(Artikelstamm!$A$3:$A$327)</f>
+        <f>COUNTA(Artikelstamm!$A$3:$A$335)</f>
         <v/>
     